--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -241,12 +241,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFe8d5c4"/>
         <bgColor rgb="FFe8d5c4"/>
       </patternFill>
@@ -315,6 +309,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
         <bgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -576,7 +576,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -644,10 +644,13 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -671,25 +674,22 @@
     <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,13 +698,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,10 +722,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -740,7 +740,7 @@
     <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -773,16 +773,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="N3" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="O3" s="27" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O4" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -1572,16 +1572,16 @@
         <v>28</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H7" s="69" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="M7" s="23" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="N7" s="69" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="O7" s="27" t="inlineStr">
@@ -1641,11 +1641,11 @@
         <v>8</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
+        <v>8</v>
+      </c>
+      <c r="H8" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -1670,17 +1670,17 @@
       </c>
       <c r="M8" s="23" t="inlineStr">
         <is>
-          <t>7/8</t>
-        </is>
-      </c>
-      <c r="N8" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="N8" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O8" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -1710,11 +1710,11 @@
         <v>132</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="H9" s="69" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="M9" s="23" t="inlineStr">
         <is>
-          <t>69/87</t>
+          <t>86/87</t>
         </is>
       </c>
       <c r="N9" s="69" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="O9" s="27" t="inlineStr">
@@ -1779,16 +1779,16 @@
         <v>54</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H10" s="69" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="M10" s="23" t="inlineStr">
         <is>
-          <t>25/34</t>
+          <t>26/34</t>
         </is>
       </c>
       <c r="N10" s="69" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="O10" s="27" t="inlineStr">
@@ -1917,21 +1917,21 @@
         <v>98</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>87</v>
-      </c>
-      <c r="H12" s="69" t="inlineStr">
-        <is>
-          <t>89%</t>
+        <v>98</v>
+      </c>
+      <c r="H12" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>35/44</t>
+          <t>44/44</t>
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr">
@@ -1949,14 +1949,14 @@
           <t>47/47</t>
         </is>
       </c>
-      <c r="N12" s="69" t="inlineStr">
-        <is>
-          <t>89%</t>
+      <c r="N12" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(FULL)</t>
         </is>
       </c>
     </row>
@@ -1983,14 +1983,14 @@
         </is>
       </c>
       <c r="F13" s="23" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H13" s="70" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="M13" s="23" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="N13" s="70" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="O13" s="27" t="inlineStr">
@@ -2193,21 +2193,21 @@
         <v>151</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>59</v>
-      </c>
-      <c r="H16" s="70" t="inlineStr">
-        <is>
-          <t>39%</t>
+        <v>148</v>
+      </c>
+      <c r="H16" s="54" t="inlineStr">
+        <is>
+          <t>98%</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
-          <t>0/8</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>59/143</t>
+          <t>142/143</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr">
@@ -2225,9 +2225,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N16" s="70" t="inlineStr">
-        <is>
-          <t>39%</t>
+      <c r="N16" s="54" t="inlineStr">
+        <is>
+          <t>98%</t>
         </is>
       </c>
       <c r="O16" s="27" t="inlineStr">
@@ -2331,11 +2331,11 @@
         <v>34</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>29</v>
-      </c>
-      <c r="H18" s="69" t="inlineStr">
-        <is>
-          <t>85%</t>
+        <v>31</v>
+      </c>
+      <c r="H18" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>28/33</t>
+          <t>30/33</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr">
@@ -2363,9 +2363,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N18" s="69" t="inlineStr">
-        <is>
-          <t>85%</t>
+      <c r="N18" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="O18" s="27" t="inlineStr">
@@ -2400,11 +2400,11 @@
         <v>62</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>46</v>
-      </c>
-      <c r="H19" s="69" t="inlineStr">
-        <is>
-          <t>74%</t>
+        <v>59</v>
+      </c>
+      <c r="H19" s="54" t="inlineStr">
+        <is>
+          <t>95%</t>
         </is>
       </c>
       <c r="I19" s="23" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>46/62</t>
+          <t>59/62</t>
         </is>
       </c>
       <c r="K19" s="23" t="inlineStr">
@@ -2432,9 +2432,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N19" s="69" t="inlineStr">
-        <is>
-          <t>74%</t>
+      <c r="N19" s="54" t="inlineStr">
+        <is>
+          <t>95%</t>
         </is>
       </c>
       <c r="O19" s="27" t="inlineStr">
@@ -2469,11 +2469,11 @@
         <v>23</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="H20" s="69" t="inlineStr">
-        <is>
-          <t>65%</t>
+        <v>23</v>
+      </c>
+      <c r="H20" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>15/23</t>
+          <t>23/23</t>
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr">
@@ -2501,9 +2501,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N20" s="69" t="inlineStr">
-        <is>
-          <t>65%</t>
+      <c r="N20" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O20" s="27" t="inlineStr">
@@ -2538,11 +2538,11 @@
         <v>47</v>
       </c>
       <c r="G21" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="H21" s="70" t="inlineStr">
-        <is>
-          <t>19%</t>
+        <v>46</v>
+      </c>
+      <c r="H21" s="54" t="inlineStr">
+        <is>
+          <t>98%</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="J21" s="23" t="inlineStr">
         <is>
-          <t>9/47</t>
+          <t>46/47</t>
         </is>
       </c>
       <c r="K21" s="23" t="inlineStr">
@@ -2570,9 +2570,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N21" s="70" t="inlineStr">
-        <is>
-          <t>19%</t>
+      <c r="N21" s="54" t="inlineStr">
+        <is>
+          <t>98%</t>
         </is>
       </c>
       <c r="O21" s="27" t="inlineStr">
@@ -2607,11 +2607,11 @@
         <v>62</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>46</v>
-      </c>
-      <c r="H22" s="69" t="inlineStr">
-        <is>
-          <t>74%</t>
+        <v>62</v>
+      </c>
+      <c r="H22" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>46/62</t>
+          <t>62/62</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr">
@@ -2639,9 +2639,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N22" s="69" t="inlineStr">
-        <is>
-          <t>74%</t>
+      <c r="N22" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O22" s="27" t="inlineStr">
@@ -2676,11 +2676,11 @@
         <v>64</v>
       </c>
       <c r="G23" s="23" t="n">
-        <v>38</v>
-      </c>
-      <c r="H23" s="69" t="inlineStr">
-        <is>
-          <t>59%</t>
+        <v>64</v>
+      </c>
+      <c r="H23" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="J23" s="23" t="inlineStr">
         <is>
-          <t>38/64</t>
+          <t>64/64</t>
         </is>
       </c>
       <c r="K23" s="23" t="inlineStr">
@@ -2708,9 +2708,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N23" s="69" t="inlineStr">
-        <is>
-          <t>59%</t>
+      <c r="N23" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O23" s="27" t="inlineStr">
@@ -2745,11 +2745,11 @@
         <v>64</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="H24" s="70" t="inlineStr">
-        <is>
-          <t>22%</t>
+        <v>63</v>
+      </c>
+      <c r="H24" s="54" t="inlineStr">
+        <is>
+          <t>98%</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>14/64</t>
+          <t>63/64</t>
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr">
@@ -2777,9 +2777,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N24" s="70" t="inlineStr">
-        <is>
-          <t>22%</t>
+      <c r="N24" s="54" t="inlineStr">
+        <is>
+          <t>98%</t>
         </is>
       </c>
       <c r="O24" s="27" t="inlineStr">
@@ -2814,11 +2814,11 @@
         <v>35</v>
       </c>
       <c r="G25" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="70" t="inlineStr">
-        <is>
-          <t>6%</t>
+        <v>22</v>
+      </c>
+      <c r="H25" s="69" t="inlineStr">
+        <is>
+          <t>63%</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="J25" s="23" t="inlineStr">
         <is>
-          <t>2/35</t>
+          <t>22/35</t>
         </is>
       </c>
       <c r="K25" s="23" t="inlineStr">
@@ -2846,9 +2846,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N25" s="70" t="inlineStr">
-        <is>
-          <t>6%</t>
+      <c r="N25" s="69" t="inlineStr">
+        <is>
+          <t>63%</t>
         </is>
       </c>
       <c r="O25" s="27" t="inlineStr">
@@ -2883,11 +2883,11 @@
         <v>12</v>
       </c>
       <c r="G26" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="70" t="inlineStr">
-        <is>
-          <t>25%</t>
+        <v>12</v>
+      </c>
+      <c r="H26" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>12/12</t>
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr">
@@ -2915,9 +2915,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N26" s="70" t="inlineStr">
-        <is>
-          <t>25%</t>
+      <c r="N26" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O26" s="27" t="inlineStr">
@@ -4157,9 +4157,9 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="N44" s="70" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="N44" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O44" s="69" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="N46" s="69" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="O46" s="27" t="inlineStr">
@@ -4608,11 +4608,11 @@
         <v>230</v>
       </c>
       <c r="G51" s="23" t="n">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="H51" s="70" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="I51" s="23" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="K51" s="23" t="inlineStr">
         <is>
-          <t>12/230</t>
+          <t>82/230</t>
         </is>
       </c>
       <c r="L51" s="23" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="N51" s="70" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="O51" s="27" t="inlineStr">
@@ -5574,11 +5574,11 @@
         <v>74</v>
       </c>
       <c r="G65" s="23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H65" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="I65" s="23" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="K65" s="23" t="inlineStr">
         <is>
-          <t>0/73</t>
+          <t>10/73</t>
         </is>
       </c>
       <c r="L65" s="23" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="N65" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="O65" s="27" t="inlineStr">
@@ -5781,11 +5781,11 @@
         <v>250</v>
       </c>
       <c r="G68" s="23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H68" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="I68" s="23" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="K68" s="23" t="inlineStr">
         <is>
-          <t>0/250</t>
+          <t>10/250</t>
         </is>
       </c>
       <c r="L68" s="23" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="N68" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="O68" s="27" t="inlineStr">
@@ -6126,11 +6126,11 @@
         <v>249</v>
       </c>
       <c r="G73" s="23" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H73" s="70" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="I73" s="23" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="K73" s="23" t="inlineStr">
         <is>
-          <t>25/243</t>
+          <t>31/243</t>
         </is>
       </c>
       <c r="L73" s="23" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="N73" s="70" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="O73" s="27" t="inlineStr">
@@ -6540,16 +6540,16 @@
         <v>1102</v>
       </c>
       <c r="G79" s="23" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="H79" s="70" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="I79" s="23" t="inlineStr">
         <is>
-          <t>17/380</t>
+          <t>41/380</t>
         </is>
       </c>
       <c r="J79" s="23" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="N79" s="70" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="O79" s="27" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="O81" s="27" t="inlineStr">
         <is>
-          <t>DONE(partial)</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -6816,11 +6816,11 @@
         <v>147</v>
       </c>
       <c r="G83" s="23" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="H83" s="69" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="I83" s="23" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="J83" s="23" t="inlineStr">
         <is>
-          <t>34/84</t>
+          <t>44/84</t>
         </is>
       </c>
       <c r="K83" s="23" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="M83" s="23" t="inlineStr">
         <is>
-          <t>35/46</t>
+          <t>39/46</t>
         </is>
       </c>
       <c r="N83" s="69" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="O83" s="27" t="inlineStr">
@@ -6885,21 +6885,21 @@
         <v>223</v>
       </c>
       <c r="G84" s="23" t="n">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="H84" s="69" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="I84" s="23" t="inlineStr">
         <is>
-          <t>71/95</t>
+          <t>73/95</t>
         </is>
       </c>
       <c r="J84" s="23" t="inlineStr">
         <is>
-          <t>49/95</t>
+          <t>69/95</t>
         </is>
       </c>
       <c r="K84" s="23" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="M84" s="23" t="inlineStr">
         <is>
-          <t>19/24</t>
+          <t>23/24</t>
         </is>
       </c>
       <c r="N84" s="69" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="O84" s="27" t="inlineStr">
@@ -6954,21 +6954,21 @@
         <v>220</v>
       </c>
       <c r="G85" s="23" t="n">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="H85" s="69" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="I85" s="23" t="inlineStr">
         <is>
-          <t>65/92</t>
+          <t>72/92</t>
         </is>
       </c>
       <c r="J85" s="23" t="inlineStr">
         <is>
-          <t>34/95</t>
+          <t>58/95</t>
         </is>
       </c>
       <c r="K85" s="23" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="M85" s="23" t="inlineStr">
         <is>
-          <t>18/24</t>
+          <t>23/24</t>
         </is>
       </c>
       <c r="N85" s="69" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="O85" s="27" t="inlineStr">
@@ -7023,21 +7023,21 @@
         <v>220</v>
       </c>
       <c r="G86" s="23" t="n">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="H86" s="69" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="I86" s="23" t="inlineStr">
         <is>
-          <t>65/92</t>
+          <t>71/92</t>
         </is>
       </c>
       <c r="J86" s="23" t="inlineStr">
         <is>
-          <t>44/95</t>
+          <t>57/95</t>
         </is>
       </c>
       <c r="K86" s="23" t="inlineStr">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="M86" s="23" t="inlineStr">
         <is>
-          <t>18/24</t>
+          <t>23/24</t>
         </is>
       </c>
       <c r="N86" s="69" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="O86" s="27" t="inlineStr">
@@ -7092,21 +7092,21 @@
         <v>48</v>
       </c>
       <c r="G87" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="H87" s="70" t="inlineStr">
-        <is>
-          <t>35%</t>
+        <v>28</v>
+      </c>
+      <c r="H87" s="69" t="inlineStr">
+        <is>
+          <t>58%</t>
         </is>
       </c>
       <c r="I87" s="23" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="J87" s="23" t="inlineStr">
         <is>
-          <t>10/33</t>
+          <t>14/33</t>
         </is>
       </c>
       <c r="K87" s="23" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="M87" s="23" t="inlineStr">
         <is>
-          <t>4/9</t>
-        </is>
-      </c>
-      <c r="N87" s="70" t="inlineStr">
-        <is>
-          <t>35%</t>
+          <t>8/9</t>
+        </is>
+      </c>
+      <c r="N87" s="69" t="inlineStr">
+        <is>
+          <t>58%</t>
         </is>
       </c>
       <c r="O87" s="27" t="inlineStr">
@@ -7161,21 +7161,21 @@
         <v>56</v>
       </c>
       <c r="G88" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="H88" s="70" t="inlineStr">
-        <is>
-          <t>39%</t>
+        <v>32</v>
+      </c>
+      <c r="H88" s="69" t="inlineStr">
+        <is>
+          <t>57%</t>
         </is>
       </c>
       <c r="I88" s="23" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="J88" s="23" t="inlineStr">
         <is>
-          <t>9/32</t>
+          <t>12/32</t>
         </is>
       </c>
       <c r="K88" s="23" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="M88" s="23" t="inlineStr">
         <is>
-          <t>11/19</t>
-        </is>
-      </c>
-      <c r="N88" s="70" t="inlineStr">
-        <is>
-          <t>39%</t>
+          <t>16/19</t>
+        </is>
+      </c>
+      <c r="N88" s="69" t="inlineStr">
+        <is>
+          <t>57%</t>
         </is>
       </c>
       <c r="O88" s="27" t="inlineStr">
@@ -7230,21 +7230,21 @@
         <v>123</v>
       </c>
       <c r="G89" s="23" t="n">
-        <v>59</v>
-      </c>
-      <c r="H89" s="70" t="inlineStr">
-        <is>
-          <t>48%</t>
+        <v>101</v>
+      </c>
+      <c r="H89" s="69" t="inlineStr">
+        <is>
+          <t>82%</t>
         </is>
       </c>
       <c r="I89" s="23" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>10/12</t>
         </is>
       </c>
       <c r="J89" s="23" t="inlineStr">
         <is>
-          <t>19/73</t>
+          <t>57/73</t>
         </is>
       </c>
       <c r="K89" s="23" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="M89" s="23" t="inlineStr">
         <is>
-          <t>29/35</t>
-        </is>
-      </c>
-      <c r="N89" s="70" t="inlineStr">
-        <is>
-          <t>47%</t>
+          <t>31/35</t>
+        </is>
+      </c>
+      <c r="N89" s="69" t="inlineStr">
+        <is>
+          <t>82%</t>
         </is>
       </c>
       <c r="O89" s="27" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="N90" s="69" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="O90" s="27" t="inlineStr">
@@ -7437,21 +7437,21 @@
         <v>104</v>
       </c>
       <c r="G92" s="23" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="H92" s="69" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="I92" s="23" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="J92" s="23" t="inlineStr">
         <is>
-          <t>10/35</t>
+          <t>27/35</t>
         </is>
       </c>
       <c r="K92" s="23" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="M92" s="23" t="inlineStr">
         <is>
-          <t>50/56</t>
+          <t>54/56</t>
         </is>
       </c>
       <c r="N92" s="69" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="O92" s="27" t="inlineStr">
@@ -7506,11 +7506,11 @@
         <v>105</v>
       </c>
       <c r="G93" s="23" t="n">
-        <v>85</v>
-      </c>
-      <c r="H93" s="69" t="inlineStr">
-        <is>
-          <t>81%</t>
+        <v>99</v>
+      </c>
+      <c r="H93" s="54" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="I93" s="23" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="J93" s="23" t="inlineStr">
         <is>
-          <t>23/38</t>
+          <t>37/38</t>
         </is>
       </c>
       <c r="K93" s="23" t="inlineStr">
@@ -7538,14 +7538,14 @@
           <t>46/46</t>
         </is>
       </c>
-      <c r="N93" s="69" t="inlineStr">
-        <is>
-          <t>81%</t>
+      <c r="N93" s="54" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="O93" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(FULL)</t>
         </is>
       </c>
     </row>
@@ -7575,11 +7575,11 @@
         <v>11</v>
       </c>
       <c r="G94" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="H94" s="69" t="inlineStr">
-        <is>
-          <t>64%</t>
+        <v>11</v>
+      </c>
+      <c r="H94" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I94" s="23" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="J94" s="23" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="K94" s="23" t="inlineStr">
@@ -7604,17 +7604,17 @@
       </c>
       <c r="M94" s="23" t="inlineStr">
         <is>
-          <t>7/9</t>
-        </is>
-      </c>
-      <c r="N94" s="69" t="inlineStr">
-        <is>
-          <t>55%</t>
+          <t>9/9</t>
+        </is>
+      </c>
+      <c r="N94" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="O94" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -7644,11 +7644,11 @@
         <v>64</v>
       </c>
       <c r="G95" s="23" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="H95" s="69" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="I95" s="23" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="J95" s="23" t="inlineStr">
         <is>
-          <t>4/20</t>
+          <t>15/20</t>
         </is>
       </c>
       <c r="K95" s="23" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="M95" s="23" t="inlineStr">
         <is>
-          <t>31/36</t>
+          <t>36/36</t>
         </is>
       </c>
       <c r="N95" s="69" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="O95" s="27" t="inlineStr">
@@ -7713,11 +7713,11 @@
         <v>278</v>
       </c>
       <c r="G96" s="23" t="n">
-        <v>223</v>
-      </c>
-      <c r="H96" s="69" t="inlineStr">
-        <is>
-          <t>80%</t>
+        <v>258</v>
+      </c>
+      <c r="H96" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="I96" s="23" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="M96" s="23" t="inlineStr">
         <is>
-          <t>222/273</t>
-        </is>
-      </c>
-      <c r="N96" s="69" t="inlineStr">
-        <is>
-          <t>77%</t>
+          <t>257/273</t>
+        </is>
+      </c>
+      <c r="N96" s="54" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
       <c r="O96" s="27" t="inlineStr">
@@ -7782,11 +7782,11 @@
         <v>70</v>
       </c>
       <c r="G97" s="23" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H97" s="70" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="I97" s="23" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="M97" s="23" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
       <c r="N97" s="70" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="O97" s="27" t="inlineStr">
@@ -7851,11 +7851,11 @@
         <v>14</v>
       </c>
       <c r="G98" s="23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H98" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="I98" s="23" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="M98" s="23" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
       <c r="N98" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="O98" s="27" t="inlineStr">
@@ -7989,11 +7989,11 @@
         <v>13</v>
       </c>
       <c r="G100" s="23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H100" s="69" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="I100" s="23" t="inlineStr">
@@ -8018,12 +8018,12 @@
       </c>
       <c r="M100" s="23" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="N100" s="69" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="O100" s="27" t="inlineStr">
@@ -8127,21 +8127,21 @@
         <v>68</v>
       </c>
       <c r="G102" s="23" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H102" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="I102" s="23" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="J102" s="23" t="inlineStr">
         <is>
-          <t>8/24</t>
+          <t>15/24</t>
         </is>
       </c>
       <c r="K102" s="23" t="inlineStr">
@@ -8156,12 +8156,12 @@
       </c>
       <c r="M102" s="23" t="inlineStr">
         <is>
-          <t>29/35</t>
+          <t>34/35</t>
         </is>
       </c>
       <c r="N102" s="69" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="O102" s="27" t="inlineStr">
@@ -8196,21 +8196,21 @@
         <v>68</v>
       </c>
       <c r="G103" s="23" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="H103" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="I103" s="23" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="J103" s="23" t="inlineStr">
         <is>
-          <t>8/24</t>
+          <t>15/24</t>
         </is>
       </c>
       <c r="K103" s="23" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="M103" s="23" t="inlineStr">
         <is>
-          <t>29/35</t>
+          <t>32/35</t>
         </is>
       </c>
       <c r="N103" s="69" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="O103" s="27" t="inlineStr">
@@ -8265,21 +8265,21 @@
         <v>68</v>
       </c>
       <c r="G104" s="23" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="H104" s="69" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="I104" s="23" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="J104" s="23" t="inlineStr">
         <is>
-          <t>7/24</t>
+          <t>15/24</t>
         </is>
       </c>
       <c r="K104" s="23" t="inlineStr">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="M104" s="23" t="inlineStr">
         <is>
-          <t>26/35</t>
+          <t>32/35</t>
         </is>
       </c>
       <c r="N104" s="69" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="O104" s="27" t="inlineStr">
@@ -8334,11 +8334,11 @@
         <v>11</v>
       </c>
       <c r="G105" s="23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H105" s="69" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="I105" s="23" t="inlineStr">
@@ -8363,12 +8363,12 @@
       </c>
       <c r="M105" s="23" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="N105" s="69" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="O105" s="27" t="inlineStr">
@@ -8403,11 +8403,11 @@
         <v>83</v>
       </c>
       <c r="G106" s="23" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="H106" s="69" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="I106" s="23" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="J106" s="23" t="inlineStr">
         <is>
-          <t>13/37</t>
+          <t>24/37</t>
         </is>
       </c>
       <c r="K106" s="23" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="M106" s="23" t="inlineStr">
         <is>
-          <t>21/24</t>
-        </is>
-      </c>
-      <c r="N106" s="70" t="inlineStr">
-        <is>
-          <t>49%</t>
+          <t>23/24</t>
+        </is>
+      </c>
+      <c r="N106" s="69" t="inlineStr">
+        <is>
+          <t>70%</t>
         </is>
       </c>
       <c r="O106" s="27" t="inlineStr">
@@ -8472,11 +8472,11 @@
         <v>26</v>
       </c>
       <c r="G107" s="23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H107" s="70" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="I107" s="23" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="M107" s="23" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>9/13</t>
         </is>
       </c>
       <c r="N107" s="70" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="O107" s="27" t="inlineStr">
@@ -8541,11 +8541,11 @@
         <v>26</v>
       </c>
       <c r="G108" s="23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H108" s="70" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="I108" s="23" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="M108" s="23" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
       <c r="N108" s="70" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="O108" s="27" t="inlineStr">
@@ -8610,11 +8610,11 @@
         <v>24</v>
       </c>
       <c r="G109" s="23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H109" s="70" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="I109" s="23" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="M109" s="23" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
       <c r="N109" s="70" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="O109" s="27" t="inlineStr">
@@ -8679,21 +8679,21 @@
         <v>46</v>
       </c>
       <c r="G110" s="23" t="n">
-        <v>35</v>
-      </c>
-      <c r="H110" s="69" t="inlineStr">
-        <is>
-          <t>76%</t>
+        <v>42</v>
+      </c>
+      <c r="H110" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="I110" s="23" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="J110" s="23" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="K110" s="23" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="M110" s="23" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
         </is>
       </c>
       <c r="N110" s="69" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="O110" s="27" t="inlineStr">
@@ -8748,21 +8748,21 @@
         <v>29</v>
       </c>
       <c r="G111" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="H111" s="70" t="inlineStr">
-        <is>
-          <t>34%</t>
+        <v>17</v>
+      </c>
+      <c r="H111" s="69" t="inlineStr">
+        <is>
+          <t>59%</t>
         </is>
       </c>
       <c r="I111" s="23" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>4/8</t>
         </is>
       </c>
       <c r="J111" s="23" t="inlineStr">
         <is>
-          <t>2/7</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="K111" s="23" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="M111" s="23" t="inlineStr">
         <is>
-          <t>4/8</t>
-        </is>
-      </c>
-      <c r="N111" s="70" t="inlineStr">
-        <is>
-          <t>34%</t>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="N111" s="69" t="inlineStr">
+        <is>
+          <t>59%</t>
         </is>
       </c>
       <c r="O111" s="27" t="inlineStr">
@@ -8817,11 +8817,11 @@
         <v>17</v>
       </c>
       <c r="G112" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="H112" s="70" t="inlineStr">
-        <is>
-          <t>47%</t>
+        <v>10</v>
+      </c>
+      <c r="H112" s="69" t="inlineStr">
+        <is>
+          <t>59%</t>
         </is>
       </c>
       <c r="I112" s="23" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="M112" s="23" t="inlineStr">
         <is>
-          <t>8/14</t>
-        </is>
-      </c>
-      <c r="N112" s="70" t="inlineStr">
-        <is>
-          <t>35%</t>
+          <t>10/14</t>
+        </is>
+      </c>
+      <c r="N112" s="69" t="inlineStr">
+        <is>
+          <t>59%</t>
         </is>
       </c>
       <c r="O112" s="27" t="inlineStr">
@@ -8955,11 +8955,11 @@
         <v>58</v>
       </c>
       <c r="G114" s="23" t="n">
-        <v>44</v>
-      </c>
-      <c r="H114" s="69" t="inlineStr">
-        <is>
-          <t>76%</t>
+        <v>56</v>
+      </c>
+      <c r="H114" s="54" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="I114" s="23" t="inlineStr">
@@ -8984,12 +8984,12 @@
       </c>
       <c r="M114" s="23" t="inlineStr">
         <is>
-          <t>44/58</t>
+          <t>56/58</t>
         </is>
       </c>
       <c r="N114" s="69" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="O114" s="27" t="inlineStr">
@@ -9024,11 +9024,11 @@
         <v>39</v>
       </c>
       <c r="G115" s="23" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H115" s="69" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="I115" s="23" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="M115" s="23" t="inlineStr">
         <is>
-          <t>28/39</t>
+          <t>33/39</t>
         </is>
       </c>
       <c r="N115" s="69" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="O115" s="27" t="inlineStr">
@@ -9231,16 +9231,16 @@
         <v>24</v>
       </c>
       <c r="G118" s="23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H118" s="69" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="I118" s="23" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>18/18</t>
         </is>
       </c>
       <c r="J118" s="23" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="N118" s="69" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="O118" s="27" t="inlineStr">
@@ -9438,16 +9438,16 @@
         <v>22</v>
       </c>
       <c r="G121" s="23" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H121" s="69" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="I121" s="23" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="J121" s="23" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="N121" s="69" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="O121" s="27" t="inlineStr">
@@ -9507,21 +9507,21 @@
         <v>169</v>
       </c>
       <c r="G122" s="23" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H122" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="I122" s="23" t="inlineStr">
         <is>
-          <t>87/89</t>
+          <t>89/89</t>
         </is>
       </c>
       <c r="J122" s="23" t="inlineStr">
         <is>
-          <t>47/50</t>
+          <t>48/50</t>
         </is>
       </c>
       <c r="K122" s="23" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="N122" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="O122" s="27" t="inlineStr">
@@ -9645,16 +9645,16 @@
         <v>24</v>
       </c>
       <c r="G124" s="23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H124" s="69" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="I124" s="23" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>18/18</t>
         </is>
       </c>
       <c r="J124" s="23" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="N124" s="69" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="O124" s="27" t="inlineStr">
@@ -9714,21 +9714,21 @@
         <v>199</v>
       </c>
       <c r="G125" s="23" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H125" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="I125" s="23" t="inlineStr">
         <is>
-          <t>91/93</t>
+          <t>93/93</t>
         </is>
       </c>
       <c r="J125" s="23" t="inlineStr">
         <is>
-          <t>57/63</t>
+          <t>58/63</t>
         </is>
       </c>
       <c r="K125" s="23" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="N125" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="O125" s="27" t="inlineStr">
@@ -9783,11 +9783,11 @@
         <v>52</v>
       </c>
       <c r="G126" s="23" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H126" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="I126" s="23" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="J126" s="23" t="inlineStr">
         <is>
-          <t>37/38</t>
+          <t>38/38</t>
         </is>
       </c>
       <c r="K126" s="23" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="N126" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="O126" s="27" t="inlineStr">
@@ -9852,16 +9852,16 @@
         <v>22</v>
       </c>
       <c r="G127" s="23" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H127" s="69" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="I127" s="23" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="J127" s="23" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="N127" s="69" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="O127" s="27" t="inlineStr">
@@ -9921,21 +9921,21 @@
         <v>169</v>
       </c>
       <c r="G128" s="23" t="n">
-        <v>111</v>
-      </c>
-      <c r="H128" s="69" t="inlineStr">
-        <is>
-          <t>66%</t>
+        <v>164</v>
+      </c>
+      <c r="H128" s="54" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="I128" s="23" t="inlineStr">
         <is>
-          <t>61/89</t>
+          <t>87/89</t>
         </is>
       </c>
       <c r="J128" s="23" t="inlineStr">
         <is>
-          <t>22/50</t>
+          <t>47/50</t>
         </is>
       </c>
       <c r="K128" s="23" t="inlineStr">
@@ -9950,17 +9950,17 @@
       </c>
       <c r="M128" s="23" t="inlineStr">
         <is>
-          <t>20/22</t>
-        </is>
-      </c>
-      <c r="N128" s="69" t="inlineStr">
-        <is>
-          <t>66%</t>
+          <t>22/22</t>
+        </is>
+      </c>
+      <c r="N128" s="54" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="O128" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -9990,21 +9990,21 @@
         <v>52</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="H129" s="70" t="inlineStr">
-        <is>
-          <t>46%</t>
+        <v>47</v>
+      </c>
+      <c r="H129" s="54" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="I129" s="23" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="J129" s="23" t="inlineStr">
         <is>
-          <t>17/38</t>
+          <t>38/38</t>
         </is>
       </c>
       <c r="K129" s="23" t="inlineStr">
@@ -10022,9 +10022,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N129" s="70" t="inlineStr">
-        <is>
-          <t>46%</t>
+      <c r="N129" s="54" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="O129" s="27" t="inlineStr">
@@ -10059,16 +10059,16 @@
         <v>24</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="H130" s="70" t="inlineStr">
-        <is>
-          <t>46%</t>
+        <v>21</v>
+      </c>
+      <c r="H130" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="I130" s="23" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>18/18</t>
         </is>
       </c>
       <c r="J130" s="23" t="inlineStr">
@@ -10091,9 +10091,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N130" s="70" t="inlineStr">
-        <is>
-          <t>46%</t>
+      <c r="N130" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="O130" s="27" t="inlineStr">
@@ -10128,21 +10128,21 @@
         <v>199</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>120</v>
-      </c>
-      <c r="H131" s="69" t="inlineStr">
-        <is>
-          <t>60%</t>
+        <v>188</v>
+      </c>
+      <c r="H131" s="54" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="I131" s="23" t="inlineStr">
         <is>
-          <t>61/93</t>
+          <t>91/93</t>
         </is>
       </c>
       <c r="J131" s="23" t="inlineStr">
         <is>
-          <t>24/63</t>
+          <t>60/63</t>
         </is>
       </c>
       <c r="K131" s="23" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="M131" s="23" t="inlineStr">
         <is>
-          <t>20/22</t>
-        </is>
-      </c>
-      <c r="N131" s="69" t="inlineStr">
-        <is>
-          <t>60%</t>
+          <t>22/22</t>
+        </is>
+      </c>
+      <c r="N131" s="54" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="O131" s="27" t="inlineStr">
@@ -10197,21 +10197,21 @@
         <v>52</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="H132" s="70" t="inlineStr">
-        <is>
-          <t>38%</t>
+        <v>46</v>
+      </c>
+      <c r="H132" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="I132" s="23" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="J132" s="23" t="inlineStr">
         <is>
-          <t>13/38</t>
+          <t>37/38</t>
         </is>
       </c>
       <c r="K132" s="23" t="inlineStr">
@@ -10229,9 +10229,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N132" s="70" t="inlineStr">
-        <is>
-          <t>38%</t>
+      <c r="N132" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="O132" s="27" t="inlineStr">
@@ -10266,16 +10266,16 @@
         <v>22</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H133" s="70" t="inlineStr">
-        <is>
-          <t>23%</t>
+        <v>19</v>
+      </c>
+      <c r="H133" s="69" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
       <c r="I133" s="23" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="J133" s="23" t="inlineStr">
@@ -10298,9 +10298,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N133" s="70" t="inlineStr">
-        <is>
-          <t>23%</t>
+      <c r="N133" s="69" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
       <c r="O133" s="27" t="inlineStr">
@@ -10335,21 +10335,21 @@
         <v>170</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="H134" s="69" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="I134" s="23" t="inlineStr">
         <is>
-          <t>49/89</t>
+          <t>65/89</t>
         </is>
       </c>
       <c r="J134" s="23" t="inlineStr">
         <is>
-          <t>16/50</t>
+          <t>20/50</t>
         </is>
       </c>
       <c r="K134" s="23" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="M134" s="23" t="inlineStr">
         <is>
-          <t>20/22</t>
+          <t>22/22</t>
         </is>
       </c>
       <c r="N134" s="69" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="O134" s="27" t="inlineStr">
@@ -10404,28 +10404,28 @@
         <v>50</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H135" s="70" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="I135" s="23" t="inlineStr">
         <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="J135" s="23" t="inlineStr">
+        <is>
+          <t>12/38</t>
+        </is>
+      </c>
+      <c r="K135" s="23" t="inlineStr">
+        <is>
           <t>3/6</t>
         </is>
       </c>
-      <c r="J135" s="23" t="inlineStr">
-        <is>
-          <t>12/38</t>
-        </is>
-      </c>
-      <c r="K135" s="23" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
       <c r="L135" s="23" t="inlineStr">
         <is>
           <t>0/0</t>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="N135" s="70" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="O135" s="27" t="inlineStr">
@@ -10473,16 +10473,16 @@
         <v>24</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="H136" s="70" t="inlineStr">
-        <is>
-          <t>33%</t>
+        <v>20</v>
+      </c>
+      <c r="H136" s="69" t="inlineStr">
+        <is>
+          <t>83%</t>
         </is>
       </c>
       <c r="I136" s="23" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>17/18</t>
         </is>
       </c>
       <c r="J136" s="23" t="inlineStr">
@@ -10505,9 +10505,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N136" s="70" t="inlineStr">
-        <is>
-          <t>33%</t>
+      <c r="N136" s="69" t="inlineStr">
+        <is>
+          <t>83%</t>
         </is>
       </c>
       <c r="O136" s="27" t="inlineStr">
@@ -10542,21 +10542,21 @@
         <v>117</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H137" s="69" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="I137" s="23" t="inlineStr">
         <is>
-          <t>49/57</t>
+          <t>50/57</t>
         </is>
       </c>
       <c r="J137" s="23" t="inlineStr">
         <is>
-          <t>34/48</t>
+          <t>35/48</t>
         </is>
       </c>
       <c r="K137" s="23" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="N137" s="69" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="O137" s="27" t="inlineStr">
@@ -11232,11 +11232,11 @@
         <v>13</v>
       </c>
       <c r="G147" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="H147" s="69" t="inlineStr">
-        <is>
-          <t>69%</t>
+        <v>13</v>
+      </c>
+      <c r="H147" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I147" s="23" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="J147" s="23" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K147" s="23" t="inlineStr">
@@ -11261,17 +11261,17 @@
       </c>
       <c r="M147" s="23" t="inlineStr">
         <is>
-          <t>6/9</t>
-        </is>
-      </c>
-      <c r="N147" s="69" t="inlineStr">
-        <is>
-          <t>62%</t>
+          <t>9/9</t>
+        </is>
+      </c>
+      <c r="N147" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O147" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -11301,11 +11301,11 @@
         <v>13</v>
       </c>
       <c r="G148" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="H148" s="69" t="inlineStr">
-        <is>
-          <t>69%</t>
+        <v>13</v>
+      </c>
+      <c r="H148" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I148" s="23" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="J148" s="23" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K148" s="23" t="inlineStr">
@@ -11330,17 +11330,17 @@
       </c>
       <c r="M148" s="23" t="inlineStr">
         <is>
-          <t>6/9</t>
-        </is>
-      </c>
-      <c r="N148" s="69" t="inlineStr">
-        <is>
-          <t>62%</t>
+          <t>9/9</t>
+        </is>
+      </c>
+      <c r="N148" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O148" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -11370,11 +11370,11 @@
         <v>13</v>
       </c>
       <c r="G149" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="H149" s="69" t="inlineStr">
-        <is>
-          <t>62%</t>
+        <v>13</v>
+      </c>
+      <c r="H149" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I149" s="23" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="J149" s="23" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K149" s="23" t="inlineStr">
@@ -11399,17 +11399,17 @@
       </c>
       <c r="M149" s="23" t="inlineStr">
         <is>
-          <t>7/9</t>
-        </is>
-      </c>
-      <c r="N149" s="69" t="inlineStr">
-        <is>
-          <t>62%</t>
+          <t>9/9</t>
+        </is>
+      </c>
+      <c r="N149" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O149" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -11715,16 +11715,16 @@
         <v>33</v>
       </c>
       <c r="G154" s="23" t="n">
-        <v>27</v>
-      </c>
-      <c r="H154" s="69" t="inlineStr">
-        <is>
-          <t>82%</t>
+        <v>33</v>
+      </c>
+      <c r="H154" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I154" s="23" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="J154" s="23" t="inlineStr">
@@ -11744,17 +11744,17 @@
       </c>
       <c r="M154" s="23" t="inlineStr">
         <is>
-          <t>14/17</t>
-        </is>
-      </c>
-      <c r="N154" s="69" t="inlineStr">
-        <is>
-          <t>82%</t>
+          <t>17/17</t>
+        </is>
+      </c>
+      <c r="N154" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O154" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -11784,16 +11784,16 @@
         <v>34</v>
       </c>
       <c r="G155" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="H155" s="69" t="inlineStr">
-        <is>
-          <t>82%</t>
+        <v>34</v>
+      </c>
+      <c r="H155" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I155" s="23" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="J155" s="23" t="inlineStr">
@@ -11813,17 +11813,17 @@
       </c>
       <c r="M155" s="23" t="inlineStr">
         <is>
-          <t>14/17</t>
-        </is>
-      </c>
-      <c r="N155" s="69" t="inlineStr">
-        <is>
-          <t>82%</t>
+          <t>17/17</t>
+        </is>
+      </c>
+      <c r="N155" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O155" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -11853,11 +11853,11 @@
         <v>34</v>
       </c>
       <c r="G156" s="23" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H156" s="69" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="I156" s="23" t="inlineStr">
@@ -11882,12 +11882,12 @@
       </c>
       <c r="M156" s="23" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>16/17</t>
         </is>
       </c>
       <c r="N156" s="69" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="O156" s="27" t="inlineStr">
@@ -12198,21 +12198,21 @@
         <v>27</v>
       </c>
       <c r="G161" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="H161" s="69" t="inlineStr">
-        <is>
-          <t>81%</t>
+        <v>27</v>
+      </c>
+      <c r="H161" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I161" s="23" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="J161" s="23" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K161" s="23" t="inlineStr">
@@ -12227,12 +12227,12 @@
       </c>
       <c r="M161" s="23" t="inlineStr">
         <is>
-          <t>16/19</t>
-        </is>
-      </c>
-      <c r="N161" s="69" t="inlineStr">
-        <is>
-          <t>81%</t>
+          <t>19/19</t>
+        </is>
+      </c>
+      <c r="N161" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O161" s="27" t="inlineStr">
@@ -12267,21 +12267,21 @@
         <v>27</v>
       </c>
       <c r="G162" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="H162" s="69" t="inlineStr">
-        <is>
-          <t>81%</t>
+        <v>27</v>
+      </c>
+      <c r="H162" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I162" s="23" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="J162" s="23" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K162" s="23" t="inlineStr">
@@ -12296,17 +12296,17 @@
       </c>
       <c r="M162" s="23" t="inlineStr">
         <is>
-          <t>16/19</t>
-        </is>
-      </c>
-      <c r="N162" s="69" t="inlineStr">
-        <is>
-          <t>81%</t>
+          <t>19/19</t>
+        </is>
+      </c>
+      <c r="N162" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O162" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -12336,21 +12336,21 @@
         <v>27</v>
       </c>
       <c r="G163" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="H163" s="69" t="inlineStr">
-        <is>
-          <t>74%</t>
+        <v>25</v>
+      </c>
+      <c r="H163" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="I163" s="23" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="J163" s="23" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="K163" s="23" t="inlineStr">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="M163" s="23" t="inlineStr">
         <is>
-          <t>16/19</t>
-        </is>
-      </c>
-      <c r="N163" s="69" t="inlineStr">
-        <is>
-          <t>74%</t>
+          <t>19/19</t>
+        </is>
+      </c>
+      <c r="N163" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="O163" s="27" t="inlineStr">
@@ -12612,16 +12612,16 @@
         <v>35</v>
       </c>
       <c r="G167" s="23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H167" s="69" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="I167" s="23" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="J167" s="23" t="inlineStr">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="N167" s="69" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="O167" s="27" t="inlineStr">
@@ -12681,26 +12681,26 @@
         <v>35</v>
       </c>
       <c r="G168" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="H168" s="69" t="inlineStr">
-        <is>
-          <t>69%</t>
+        <v>33</v>
+      </c>
+      <c r="H168" s="54" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="I168" s="23" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="J168" s="23" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>10/11</t>
         </is>
       </c>
       <c r="K168" s="23" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L168" s="23" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="M168" s="23" t="inlineStr">
         <is>
-          <t>13/15</t>
-        </is>
-      </c>
-      <c r="N168" s="69" t="inlineStr">
-        <is>
-          <t>66%</t>
+          <t>15/15</t>
+        </is>
+      </c>
+      <c r="N168" s="54" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="O168" s="27" t="inlineStr">
@@ -12750,26 +12750,26 @@
         <v>35</v>
       </c>
       <c r="G169" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="H169" s="69" t="inlineStr">
-        <is>
-          <t>69%</t>
+        <v>32</v>
+      </c>
+      <c r="H169" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="I169" s="23" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="J169" s="23" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>10/11</t>
         </is>
       </c>
       <c r="K169" s="23" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L169" s="23" t="inlineStr">
@@ -12779,12 +12779,12 @@
       </c>
       <c r="M169" s="23" t="inlineStr">
         <is>
-          <t>13/15</t>
-        </is>
-      </c>
-      <c r="N169" s="69" t="inlineStr">
-        <is>
-          <t>66%</t>
+          <t>15/15</t>
+        </is>
+      </c>
+      <c r="N169" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="O169" s="27" t="inlineStr">
@@ -12819,11 +12819,11 @@
         <v>35</v>
       </c>
       <c r="G170" s="23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H170" s="69" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="I170" s="23" t="inlineStr">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="K170" s="23" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L170" s="23" t="inlineStr">
@@ -12848,12 +12848,12 @@
       </c>
       <c r="M170" s="23" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>14/15</t>
         </is>
       </c>
       <c r="N170" s="69" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="O170" s="27" t="inlineStr">
@@ -12888,11 +12888,11 @@
         <v>66</v>
       </c>
       <c r="G171" s="23" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H171" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I171" s="23" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="J171" s="23" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="K171" s="23" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="N171" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O171" s="27" t="inlineStr">
@@ -12957,16 +12957,16 @@
         <v>34</v>
       </c>
       <c r="G172" s="23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H172" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I172" s="23" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="J172" s="23" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="N172" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="O172" s="27" t="inlineStr">
@@ -13026,11 +13026,11 @@
         <v>67</v>
       </c>
       <c r="G173" s="23" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H173" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="I173" s="23" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="J173" s="23" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="K173" s="23" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="N173" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="O173" s="27" t="inlineStr">
@@ -13095,16 +13095,16 @@
         <v>34</v>
       </c>
       <c r="G174" s="23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H174" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I174" s="23" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="J174" s="23" t="inlineStr">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="N174" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="O174" s="27" t="inlineStr">
@@ -13164,16 +13164,16 @@
         <v>67</v>
       </c>
       <c r="G175" s="23" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H175" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I175" s="23" t="inlineStr">
         <is>
-          <t>36/38</t>
+          <t>38/38</t>
         </is>
       </c>
       <c r="J175" s="23" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="N175" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="O175" s="27" t="inlineStr">
@@ -13233,16 +13233,16 @@
         <v>34</v>
       </c>
       <c r="G176" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="H176" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
+        <v>33</v>
+      </c>
+      <c r="H176" s="54" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="I176" s="23" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="J176" s="23" t="inlineStr">
@@ -13265,9 +13265,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N176" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
+      <c r="N176" s="54" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="O176" s="27" t="inlineStr">
@@ -13302,11 +13302,11 @@
         <v>67</v>
       </c>
       <c r="G177" s="23" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H177" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I177" s="23" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="J177" s="23" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="K177" s="23" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="N177" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O177" s="27" t="inlineStr">
@@ -13371,16 +13371,16 @@
         <v>34</v>
       </c>
       <c r="G178" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="H178" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
+        <v>33</v>
+      </c>
+      <c r="H178" s="54" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="I178" s="23" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="J178" s="23" t="inlineStr">
@@ -13403,9 +13403,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N178" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
+      <c r="N178" s="54" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="O178" s="27" t="inlineStr">
@@ -13440,21 +13440,21 @@
         <v>67</v>
       </c>
       <c r="G179" s="23" t="n">
-        <v>35</v>
-      </c>
-      <c r="H179" s="69" t="inlineStr">
-        <is>
-          <t>52%</t>
+        <v>62</v>
+      </c>
+      <c r="H179" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="I179" s="23" t="inlineStr">
         <is>
-          <t>15/38</t>
+          <t>37/38</t>
         </is>
       </c>
       <c r="J179" s="23" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>5/8</t>
         </is>
       </c>
       <c r="K179" s="23" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="M179" s="23" t="inlineStr">
         <is>
-          <t>13/17</t>
-        </is>
-      </c>
-      <c r="N179" s="69" t="inlineStr">
-        <is>
-          <t>52%</t>
+          <t>16/17</t>
+        </is>
+      </c>
+      <c r="N179" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="O179" s="27" t="inlineStr">
@@ -13509,26 +13509,26 @@
         <v>34</v>
       </c>
       <c r="G180" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="H180" s="70" t="inlineStr">
-        <is>
-          <t>29%</t>
+        <v>30</v>
+      </c>
+      <c r="H180" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="I180" s="23" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>7/10</t>
         </is>
       </c>
       <c r="J180" s="23" t="inlineStr">
         <is>
-          <t>6/22</t>
+          <t>22/22</t>
         </is>
       </c>
       <c r="K180" s="23" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L180" s="23" t="inlineStr">
@@ -13541,9 +13541,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N180" s="70" t="inlineStr">
-        <is>
-          <t>29%</t>
+      <c r="N180" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="O180" s="27" t="inlineStr">
@@ -13578,21 +13578,21 @@
         <v>67</v>
       </c>
       <c r="G181" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="H181" s="70" t="inlineStr">
-        <is>
-          <t>48%</t>
+        <v>62</v>
+      </c>
+      <c r="H181" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="I181" s="23" t="inlineStr">
         <is>
-          <t>12/38</t>
+          <t>37/38</t>
         </is>
       </c>
       <c r="J181" s="23" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>5/8</t>
         </is>
       </c>
       <c r="K181" s="23" t="inlineStr">
@@ -13607,12 +13607,12 @@
       </c>
       <c r="M181" s="23" t="inlineStr">
         <is>
-          <t>13/17</t>
-        </is>
-      </c>
-      <c r="N181" s="70" t="inlineStr">
-        <is>
-          <t>48%</t>
+          <t>16/17</t>
+        </is>
+      </c>
+      <c r="N181" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="O181" s="27" t="inlineStr">
@@ -13647,26 +13647,26 @@
         <v>34</v>
       </c>
       <c r="G182" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="H182" s="70" t="inlineStr">
-        <is>
-          <t>29%</t>
+        <v>30</v>
+      </c>
+      <c r="H182" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="I182" s="23" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>7/10</t>
         </is>
       </c>
       <c r="J182" s="23" t="inlineStr">
         <is>
-          <t>6/22</t>
+          <t>22/22</t>
         </is>
       </c>
       <c r="K182" s="23" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L182" s="23" t="inlineStr">
@@ -13679,9 +13679,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N182" s="70" t="inlineStr">
-        <is>
-          <t>29%</t>
+      <c r="N182" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="O182" s="27" t="inlineStr">
@@ -13716,11 +13716,11 @@
         <v>67</v>
       </c>
       <c r="G183" s="23" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H183" s="70" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="I183" s="23" t="inlineStr">
@@ -13745,12 +13745,12 @@
       </c>
       <c r="M183" s="23" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>15/17</t>
         </is>
       </c>
       <c r="N183" s="70" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="O183" s="27" t="inlineStr">
@@ -13785,11 +13785,11 @@
         <v>34</v>
       </c>
       <c r="G184" s="23" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H184" s="70" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="I184" s="23" t="inlineStr">
@@ -13799,12 +13799,12 @@
       </c>
       <c r="J184" s="23" t="inlineStr">
         <is>
-          <t>6/22</t>
+          <t>9/22</t>
         </is>
       </c>
       <c r="K184" s="23" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L184" s="23" t="inlineStr">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="N184" s="70" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="O184" s="27" t="inlineStr">
@@ -14130,16 +14130,16 @@
         <v>70</v>
       </c>
       <c r="G189" s="23" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H189" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I189" s="23" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="J189" s="23" t="inlineStr">
@@ -14159,17 +14159,17 @@
       </c>
       <c r="M189" s="23" t="inlineStr">
         <is>
-          <t>37/40</t>
+          <t>40/40</t>
         </is>
       </c>
       <c r="N189" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O189" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>PLATFORM ISSUE</t>
         </is>
       </c>
     </row>
@@ -14199,16 +14199,16 @@
         <v>70</v>
       </c>
       <c r="G190" s="23" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H190" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I190" s="23" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="J190" s="23" t="inlineStr">
@@ -14228,17 +14228,17 @@
       </c>
       <c r="M190" s="23" t="inlineStr">
         <is>
-          <t>37/40</t>
+          <t>40/40</t>
         </is>
       </c>
       <c r="N190" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O190" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -14268,21 +14268,21 @@
         <v>70</v>
       </c>
       <c r="G191" s="23" t="n">
-        <v>41</v>
-      </c>
-      <c r="H191" s="69" t="inlineStr">
-        <is>
-          <t>59%</t>
+        <v>63</v>
+      </c>
+      <c r="H191" s="54" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="I191" s="23" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="J191" s="23" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>9/16</t>
         </is>
       </c>
       <c r="K191" s="23" t="inlineStr">
@@ -14297,12 +14297,12 @@
       </c>
       <c r="M191" s="23" t="inlineStr">
         <is>
-          <t>29/40</t>
-        </is>
-      </c>
-      <c r="N191" s="69" t="inlineStr">
-        <is>
-          <t>59%</t>
+          <t>40/40</t>
+        </is>
+      </c>
+      <c r="N191" s="54" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="O191" s="27" t="inlineStr">
@@ -14337,16 +14337,16 @@
         <v>82</v>
       </c>
       <c r="G192" s="23" t="n">
-        <v>71</v>
-      </c>
-      <c r="H192" s="69" t="inlineStr">
-        <is>
-          <t>87%</t>
+        <v>74</v>
+      </c>
+      <c r="H192" s="54" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="I192" s="23" t="inlineStr">
         <is>
-          <t>63/74</t>
+          <t>66/74</t>
         </is>
       </c>
       <c r="J192" s="23" t="inlineStr">
@@ -14369,9 +14369,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N192" s="69" t="inlineStr">
-        <is>
-          <t>87%</t>
+      <c r="N192" s="54" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="O192" s="27" t="inlineStr">
@@ -14406,16 +14406,16 @@
         <v>34</v>
       </c>
       <c r="G193" s="23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H193" s="69" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="I193" s="23" t="inlineStr">
         <is>
-          <t>20/32</t>
+          <t>27/32</t>
         </is>
       </c>
       <c r="J193" s="23" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="N193" s="69" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="O193" s="27" t="inlineStr">
@@ -14475,16 +14475,16 @@
         <v>34</v>
       </c>
       <c r="G194" s="23" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H194" s="69" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="I194" s="23" t="inlineStr">
         <is>
-          <t>20/32</t>
+          <t>26/32</t>
         </is>
       </c>
       <c r="J194" s="23" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="N194" s="69" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="O194" s="27" t="inlineStr">
@@ -14682,16 +14682,16 @@
         <v>94</v>
       </c>
       <c r="G197" s="23" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H197" s="69" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="I197" s="23" t="inlineStr">
         <is>
-          <t>54/94</t>
+          <t>63/94</t>
         </is>
       </c>
       <c r="J197" s="23" t="inlineStr">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="N197" s="69" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="O197" s="27" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="O198" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -14820,16 +14820,16 @@
         <v>28</v>
       </c>
       <c r="G199" s="23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H199" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="I199" s="23" t="inlineStr">
         <is>
-          <t>0/28</t>
+          <t>6/28</t>
         </is>
       </c>
       <c r="J199" s="23" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="N199" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="O199" s="27" t="inlineStr">
@@ -14958,16 +14958,16 @@
         <v>4</v>
       </c>
       <c r="G201" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H201" s="70" t="inlineStr">
-        <is>
-          <t>25%</t>
+        <v>4</v>
+      </c>
+      <c r="H201" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I201" s="23" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="J201" s="23" t="inlineStr">
@@ -14990,9 +14990,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N201" s="70" t="inlineStr">
-        <is>
-          <t>25%</t>
+      <c r="N201" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O201" s="27" t="inlineStr">
@@ -15027,16 +15027,16 @@
         <v>4</v>
       </c>
       <c r="G202" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H202" s="69" t="inlineStr">
-        <is>
-          <t>50%</t>
+        <v>4</v>
+      </c>
+      <c r="H202" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I202" s="23" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="J202" s="23" t="inlineStr">
@@ -15059,9 +15059,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N202" s="69" t="inlineStr">
-        <is>
-          <t>50%</t>
+      <c r="N202" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O202" s="27" t="inlineStr">
@@ -15441,16 +15441,16 @@
         <v>4</v>
       </c>
       <c r="G208" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H208" s="70" t="inlineStr">
-        <is>
-          <t>25%</t>
+        <v>2</v>
+      </c>
+      <c r="H208" s="69" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="I208" s="23" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="J208" s="23" t="inlineStr">
@@ -15473,9 +15473,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N208" s="70" t="inlineStr">
-        <is>
-          <t>25%</t>
+      <c r="N208" s="69" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="O208" s="27" t="inlineStr">
@@ -15510,16 +15510,16 @@
         <v>4</v>
       </c>
       <c r="G209" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H209" s="70" t="inlineStr">
-        <is>
-          <t>25%</t>
+        <v>4</v>
+      </c>
+      <c r="H209" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I209" s="23" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="J209" s="23" t="inlineStr">
@@ -15542,9 +15542,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N209" s="70" t="inlineStr">
-        <is>
-          <t>25%</t>
+      <c r="N209" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O209" s="27" t="inlineStr">
@@ -15648,16 +15648,16 @@
         <v>19</v>
       </c>
       <c r="G211" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H211" s="70" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="I211" s="23" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>5/19</t>
         </is>
       </c>
       <c r="J211" s="23" t="inlineStr">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="N211" s="70" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="O211" s="27" t="inlineStr">
@@ -15717,16 +15717,16 @@
         <v>17</v>
       </c>
       <c r="G212" s="23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H212" s="70" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="I212" s="23" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>6/17</t>
         </is>
       </c>
       <c r="J212" s="23" t="inlineStr">
@@ -15751,7 +15751,7 @@
       </c>
       <c r="N212" s="70" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="O212" s="27" t="inlineStr">
@@ -15924,16 +15924,16 @@
         <v>39</v>
       </c>
       <c r="G215" s="23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H215" s="70" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="I215" s="23" t="inlineStr">
         <is>
-          <t>3/39</t>
+          <t>8/39</t>
         </is>
       </c>
       <c r="J215" s="23" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="N215" s="70" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="O215" s="27" t="inlineStr">
@@ -16094,9 +16094,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N217" s="69" t="inlineStr">
-        <is>
-          <t>73%</t>
+      <c r="N217" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="O217" s="27" t="inlineStr">
@@ -16163,9 +16163,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N218" s="69" t="inlineStr">
-        <is>
-          <t>74%</t>
+      <c r="N218" s="54" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="O218" s="27" t="inlineStr">
@@ -17166,11 +17166,11 @@
         <v>94</v>
       </c>
       <c r="G233" s="23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H233" s="70" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="I233" s="23" t="inlineStr">
@@ -17195,12 +17195,12 @@
       </c>
       <c r="M233" s="23" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>25/30</t>
         </is>
       </c>
       <c r="N233" s="70" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="O233" s="27" t="inlineStr">
@@ -17235,11 +17235,11 @@
         <v>17</v>
       </c>
       <c r="G234" s="23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H234" s="69" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="I234" s="23" t="inlineStr">
@@ -17264,12 +17264,12 @@
       </c>
       <c r="M234" s="23" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>9/10</t>
         </is>
       </c>
       <c r="N234" s="69" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="O234" s="27" t="inlineStr">
@@ -17373,21 +17373,21 @@
         <v>128</v>
       </c>
       <c r="G236" s="23" t="n">
-        <v>53</v>
-      </c>
-      <c r="H236" s="70" t="inlineStr">
-        <is>
-          <t>41%</t>
+        <v>65</v>
+      </c>
+      <c r="H236" s="69" t="inlineStr">
+        <is>
+          <t>51%</t>
         </is>
       </c>
       <c r="I236" s="23" t="inlineStr">
         <is>
-          <t>8/22</t>
+          <t>11/22</t>
         </is>
       </c>
       <c r="J236" s="23" t="inlineStr">
         <is>
-          <t>8/58</t>
+          <t>11/58</t>
         </is>
       </c>
       <c r="K236" s="23" t="inlineStr">
@@ -17402,12 +17402,12 @@
       </c>
       <c r="M236" s="23" t="inlineStr">
         <is>
-          <t>35/46</t>
-        </is>
-      </c>
-      <c r="N236" s="70" t="inlineStr">
-        <is>
-          <t>41%</t>
+          <t>41/46</t>
+        </is>
+      </c>
+      <c r="N236" s="69" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="O236" s="27" t="inlineStr">
@@ -17442,21 +17442,21 @@
         <v>64</v>
       </c>
       <c r="G237" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="H237" s="70" t="inlineStr">
-        <is>
-          <t>38%</t>
+        <v>32</v>
+      </c>
+      <c r="H237" s="69" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="I237" s="23" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="J237" s="23" t="inlineStr">
         <is>
-          <t>10/35</t>
+          <t>12/35</t>
         </is>
       </c>
       <c r="K237" s="23" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="M237" s="23" t="inlineStr">
         <is>
-          <t>10/14</t>
-        </is>
-      </c>
-      <c r="N237" s="70" t="inlineStr">
-        <is>
-          <t>36%</t>
+          <t>13/14</t>
+        </is>
+      </c>
+      <c r="N237" s="69" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="O237" s="27" t="inlineStr">
@@ -17511,11 +17511,11 @@
         <v>62</v>
       </c>
       <c r="G238" s="23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H238" s="69" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="I238" s="23" t="inlineStr">
@@ -17540,12 +17540,12 @@
       </c>
       <c r="M238" s="23" t="inlineStr">
         <is>
-          <t>22/22</t>
+          <t>21/22</t>
         </is>
       </c>
       <c r="N238" s="69" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="O238" s="27" t="inlineStr">
@@ -17580,11 +17580,11 @@
         <v>112</v>
       </c>
       <c r="G239" s="23" t="n">
-        <v>47</v>
-      </c>
-      <c r="H239" s="70" t="inlineStr">
-        <is>
-          <t>42%</t>
+        <v>59</v>
+      </c>
+      <c r="H239" s="69" t="inlineStr">
+        <is>
+          <t>53%</t>
         </is>
       </c>
       <c r="I239" s="23" t="inlineStr">
@@ -17594,7 +17594,7 @@
       </c>
       <c r="J239" s="23" t="inlineStr">
         <is>
-          <t>31/44</t>
+          <t>43/44</t>
         </is>
       </c>
       <c r="K239" s="23" t="inlineStr">
@@ -17612,9 +17612,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N239" s="70" t="inlineStr">
-        <is>
-          <t>42%</t>
+      <c r="N239" s="69" t="inlineStr">
+        <is>
+          <t>53%</t>
         </is>
       </c>
       <c r="O239" s="27" t="inlineStr">
@@ -17649,11 +17649,11 @@
         <v>73</v>
       </c>
       <c r="G240" s="23" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H240" s="54" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="I240" s="23" t="inlineStr">
@@ -17663,7 +17663,7 @@
       </c>
       <c r="J240" s="23" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
       <c r="K240" s="23" t="inlineStr">
@@ -17683,12 +17683,12 @@
       </c>
       <c r="N240" s="54" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="O240" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -17787,21 +17787,21 @@
         <v>124</v>
       </c>
       <c r="G242" s="23" t="n">
-        <v>55</v>
-      </c>
-      <c r="H242" s="70" t="inlineStr">
-        <is>
-          <t>44%</t>
+        <v>66</v>
+      </c>
+      <c r="H242" s="69" t="inlineStr">
+        <is>
+          <t>53%</t>
         </is>
       </c>
       <c r="I242" s="23" t="inlineStr">
         <is>
-          <t>12/24</t>
+          <t>15/24</t>
         </is>
       </c>
       <c r="J242" s="23" t="inlineStr">
         <is>
-          <t>21/69</t>
+          <t>24/69</t>
         </is>
       </c>
       <c r="K242" s="23" t="inlineStr">
@@ -17816,12 +17816,12 @@
       </c>
       <c r="M242" s="23" t="inlineStr">
         <is>
-          <t>21/30</t>
-        </is>
-      </c>
-      <c r="N242" s="70" t="inlineStr">
-        <is>
-          <t>44%</t>
+          <t>26/30</t>
+        </is>
+      </c>
+      <c r="N242" s="69" t="inlineStr">
+        <is>
+          <t>53%</t>
         </is>
       </c>
       <c r="O242" s="27" t="inlineStr">
@@ -17856,21 +17856,21 @@
         <v>56</v>
       </c>
       <c r="G243" s="23" t="n">
-        <v>25</v>
-      </c>
-      <c r="H243" s="70" t="inlineStr">
-        <is>
-          <t>45%</t>
+        <v>37</v>
+      </c>
+      <c r="H243" s="69" t="inlineStr">
+        <is>
+          <t>66%</t>
         </is>
       </c>
       <c r="I243" s="23" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>5/10</t>
         </is>
       </c>
       <c r="J243" s="23" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>19/27</t>
         </is>
       </c>
       <c r="K243" s="23" t="inlineStr">
@@ -17885,12 +17885,12 @@
       </c>
       <c r="M243" s="23" t="inlineStr">
         <is>
-          <t>10/14</t>
-        </is>
-      </c>
-      <c r="N243" s="70" t="inlineStr">
-        <is>
-          <t>43%</t>
+          <t>12/14</t>
+        </is>
+      </c>
+      <c r="N243" s="69" t="inlineStr">
+        <is>
+          <t>66%</t>
         </is>
       </c>
       <c r="O243" s="27" t="inlineStr">
@@ -17925,21 +17925,21 @@
         <v>25</v>
       </c>
       <c r="G244" s="23" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H244" s="69" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="I244" s="23" t="inlineStr">
         <is>
-          <t>2/7</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="J244" s="23" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K244" s="23" t="inlineStr">
@@ -17949,17 +17949,17 @@
       </c>
       <c r="L244" s="23" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="M244" s="23" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="N244" s="69" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="O244" s="27" t="inlineStr">
@@ -17994,21 +17994,21 @@
         <v>55</v>
       </c>
       <c r="G245" s="23" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H245" s="69" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="I245" s="23" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>3/8</t>
         </is>
       </c>
       <c r="J245" s="23" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>20/27</t>
         </is>
       </c>
       <c r="K245" s="23" t="inlineStr">
@@ -18023,12 +18023,12 @@
       </c>
       <c r="M245" s="23" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
       <c r="N245" s="69" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="O245" s="27" t="inlineStr">
@@ -18063,21 +18063,21 @@
         <v>33</v>
       </c>
       <c r="G246" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="H246" s="70" t="inlineStr">
-        <is>
-          <t>36%</t>
+        <v>23</v>
+      </c>
+      <c r="H246" s="69" t="inlineStr">
+        <is>
+          <t>70%</t>
         </is>
       </c>
       <c r="I246" s="23" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>4/8</t>
         </is>
       </c>
       <c r="J246" s="23" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="K246" s="23" t="inlineStr">
@@ -18087,17 +18087,17 @@
       </c>
       <c r="L246" s="23" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="M246" s="23" t="inlineStr">
         <is>
-          <t>6/9</t>
-        </is>
-      </c>
-      <c r="N246" s="70" t="inlineStr">
-        <is>
-          <t>36%</t>
+          <t>7/9</t>
+        </is>
+      </c>
+      <c r="N246" s="69" t="inlineStr">
+        <is>
+          <t>58%</t>
         </is>
       </c>
       <c r="O246" s="27" t="inlineStr">
@@ -18132,11 +18132,11 @@
         <v>31</v>
       </c>
       <c r="G247" s="23" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H247" s="69" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="I247" s="23" t="inlineStr">
@@ -18146,7 +18146,7 @@
       </c>
       <c r="J247" s="23" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>10/13</t>
         </is>
       </c>
       <c r="K247" s="23" t="inlineStr">
@@ -18161,17 +18161,17 @@
       </c>
       <c r="M247" s="23" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
       <c r="N247" s="69" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="O247" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -18408,11 +18408,11 @@
         <v>55</v>
       </c>
       <c r="G251" s="23" t="n">
-        <v>48</v>
-      </c>
-      <c r="H251" s="69" t="inlineStr">
-        <is>
-          <t>87%</t>
+        <v>50</v>
+      </c>
+      <c r="H251" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="I251" s="23" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="J251" s="23" t="inlineStr">
         <is>
-          <t>18/25</t>
+          <t>20/25</t>
         </is>
       </c>
       <c r="K251" s="23" t="inlineStr">
@@ -18440,9 +18440,9 @@
           <t>14/14</t>
         </is>
       </c>
-      <c r="N251" s="69" t="inlineStr">
-        <is>
-          <t>87%</t>
+      <c r="N251" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="O251" s="27" t="inlineStr">
@@ -18615,21 +18615,21 @@
         <v>8</v>
       </c>
       <c r="G254" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H254" s="70" t="inlineStr">
-        <is>
-          <t>38%</t>
+        <v>7</v>
+      </c>
+      <c r="H254" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="I254" s="23" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="J254" s="23" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="K254" s="23" t="inlineStr">
@@ -18647,14 +18647,14 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="N254" s="70" t="inlineStr">
-        <is>
-          <t>38%</t>
+      <c r="N254" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="O254" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -18684,21 +18684,21 @@
         <v>9</v>
       </c>
       <c r="G255" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H255" s="70" t="inlineStr">
-        <is>
-          <t>22%</t>
+        <v>7</v>
+      </c>
+      <c r="H255" s="69" t="inlineStr">
+        <is>
+          <t>78%</t>
         </is>
       </c>
       <c r="I255" s="23" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="J255" s="23" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K255" s="23" t="inlineStr">
@@ -18716,9 +18716,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N255" s="70" t="inlineStr">
-        <is>
-          <t>22%</t>
+      <c r="N255" s="69" t="inlineStr">
+        <is>
+          <t>78%</t>
         </is>
       </c>
       <c r="O255" s="27" t="inlineStr">
@@ -18753,11 +18753,11 @@
         <v>20</v>
       </c>
       <c r="G256" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="H256" s="69" t="inlineStr">
-        <is>
-          <t>60%</t>
+        <v>20</v>
+      </c>
+      <c r="H256" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I256" s="23" t="inlineStr">
@@ -18767,7 +18767,7 @@
       </c>
       <c r="J256" s="23" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K256" s="23" t="inlineStr">
@@ -18782,17 +18782,17 @@
       </c>
       <c r="M256" s="23" t="inlineStr">
         <is>
-          <t>11/16</t>
-        </is>
-      </c>
-      <c r="N256" s="69" t="inlineStr">
-        <is>
-          <t>60%</t>
+          <t>16/16</t>
+        </is>
+      </c>
+      <c r="N256" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O256" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -18822,11 +18822,11 @@
         <v>16</v>
       </c>
       <c r="G257" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H257" s="70" t="inlineStr">
-        <is>
-          <t>38%</t>
+        <v>12</v>
+      </c>
+      <c r="H257" s="69" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
       <c r="I257" s="23" t="inlineStr">
@@ -18836,7 +18836,7 @@
       </c>
       <c r="J257" s="23" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="K257" s="23" t="inlineStr">
@@ -18854,9 +18854,9 @@
           <t>5/8</t>
         </is>
       </c>
-      <c r="N257" s="70" t="inlineStr">
-        <is>
-          <t>31%</t>
+      <c r="N257" s="69" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
       <c r="O257" s="27" t="inlineStr">
@@ -18891,11 +18891,11 @@
         <v>30</v>
       </c>
       <c r="G258" s="23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H258" s="70" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="I258" s="23" t="inlineStr">
@@ -18920,12 +18920,12 @@
       </c>
       <c r="M258" s="23" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
       <c r="N258" s="70" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="O258" s="27" t="inlineStr">
@@ -18960,11 +18960,11 @@
         <v>24</v>
       </c>
       <c r="G259" s="23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H259" s="69" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="I259" s="23" t="inlineStr">
@@ -18989,12 +18989,12 @@
       </c>
       <c r="M259" s="23" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
       <c r="N259" s="69" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="O259" s="27" t="inlineStr">
@@ -19029,11 +19029,11 @@
         <v>25</v>
       </c>
       <c r="G260" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="H260" s="70" t="inlineStr">
-        <is>
-          <t>48%</t>
+        <v>15</v>
+      </c>
+      <c r="H260" s="69" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
       <c r="I260" s="23" t="inlineStr">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="J260" s="23" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="K260" s="23" t="inlineStr">
@@ -19058,12 +19058,12 @@
       </c>
       <c r="M260" s="23" t="inlineStr">
         <is>
-          <t>10/15</t>
-        </is>
-      </c>
-      <c r="N260" s="70" t="inlineStr">
-        <is>
-          <t>48%</t>
+          <t>11/15</t>
+        </is>
+      </c>
+      <c r="N260" s="69" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
       <c r="O260" s="27" t="inlineStr">
@@ -19167,16 +19167,16 @@
         <v>69</v>
       </c>
       <c r="G262" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H262" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="I262" s="23" t="inlineStr">
         <is>
-          <t>2/67</t>
+          <t>4/67</t>
         </is>
       </c>
       <c r="J262" s="23" t="inlineStr">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="N262" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="O262" s="27" t="inlineStr">
@@ -19305,16 +19305,16 @@
         <v>69</v>
       </c>
       <c r="G264" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H264" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="I264" s="23" t="inlineStr">
         <is>
-          <t>2/67</t>
+          <t>4/67</t>
         </is>
       </c>
       <c r="J264" s="23" t="inlineStr">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="N264" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="O264" s="27" t="inlineStr">
@@ -19374,16 +19374,16 @@
         <v>65</v>
       </c>
       <c r="G265" s="23" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H265" s="70" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="I265" s="23" t="inlineStr">
         <is>
-          <t>2/63</t>
+          <t>17/63</t>
         </is>
       </c>
       <c r="J265" s="23" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="N265" s="70" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="O265" s="27" t="inlineStr">
@@ -19443,16 +19443,16 @@
         <v>67</v>
       </c>
       <c r="G266" s="23" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H266" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="I266" s="23" t="inlineStr">
         <is>
-          <t>2/65</t>
+          <t>13/65</t>
         </is>
       </c>
       <c r="J266" s="23" t="inlineStr">
@@ -19477,7 +19477,7 @@
       </c>
       <c r="N266" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="O266" s="27" t="inlineStr">
@@ -19581,16 +19581,16 @@
         <v>75</v>
       </c>
       <c r="G268" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H268" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="I268" s="23" t="inlineStr">
         <is>
-          <t>2/73</t>
+          <t>3/73</t>
         </is>
       </c>
       <c r="J268" s="23" t="inlineStr">
@@ -19615,7 +19615,7 @@
       </c>
       <c r="N268" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="O268" s="27" t="inlineStr">
@@ -19719,16 +19719,16 @@
         <v>75</v>
       </c>
       <c r="G270" s="23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H270" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I270" s="23" t="inlineStr">
         <is>
-          <t>2/73</t>
+          <t>5/73</t>
         </is>
       </c>
       <c r="J270" s="23" t="inlineStr">
@@ -19753,7 +19753,7 @@
       </c>
       <c r="N270" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="O270" s="27" t="inlineStr">
@@ -19788,16 +19788,16 @@
         <v>71</v>
       </c>
       <c r="G271" s="23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H271" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I271" s="23" t="inlineStr">
         <is>
-          <t>2/69</t>
+          <t>5/69</t>
         </is>
       </c>
       <c r="J271" s="23" t="inlineStr">
@@ -19857,16 +19857,16 @@
         <v>71</v>
       </c>
       <c r="G272" s="23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H272" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I272" s="23" t="inlineStr">
         <is>
-          <t>2/69</t>
+          <t>5/69</t>
         </is>
       </c>
       <c r="J272" s="23" t="inlineStr">
@@ -19926,16 +19926,16 @@
         <v>81</v>
       </c>
       <c r="G273" s="23" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H273" s="70" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="I273" s="23" t="inlineStr">
         <is>
-          <t>0/79</t>
+          <t>17/79</t>
         </is>
       </c>
       <c r="J273" s="23" t="inlineStr">
@@ -20202,11 +20202,11 @@
         <v>8</v>
       </c>
       <c r="G277" s="23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H277" s="69" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="I277" s="23" t="inlineStr">
@@ -20231,12 +20231,12 @@
       </c>
       <c r="M277" s="23" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="N277" s="69" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="O277" s="27" t="inlineStr">
@@ -20271,11 +20271,11 @@
         <v>12</v>
       </c>
       <c r="G278" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H278" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I278" s="23" t="inlineStr">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="N278" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="O278" s="27" t="inlineStr">
@@ -20340,11 +20340,11 @@
         <v>12</v>
       </c>
       <c r="G279" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H279" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I279" s="23" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="N279" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="O279" s="27" t="inlineStr">
@@ -20478,16 +20478,16 @@
         <v>3</v>
       </c>
       <c r="G281" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H281" s="69" t="inlineStr">
-        <is>
-          <t>67%</t>
+        <v>3</v>
+      </c>
+      <c r="H281" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I281" s="23" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="J281" s="23" t="inlineStr">
@@ -20510,14 +20510,14 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N281" s="69" t="inlineStr">
-        <is>
-          <t>67%</t>
+      <c r="N281" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="O281" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(FULL)</t>
         </is>
       </c>
     </row>
@@ -20547,11 +20547,11 @@
         <v>12</v>
       </c>
       <c r="G282" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H282" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="I282" s="23" t="inlineStr">
@@ -20581,7 +20581,7 @@
       </c>
       <c r="N282" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="O282" s="27" t="inlineStr">
@@ -20616,11 +20616,11 @@
         <v>9</v>
       </c>
       <c r="G283" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H283" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="I283" s="23" t="inlineStr">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="N283" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="O283" s="27" t="inlineStr">
@@ -20724,7 +20724,7 @@
       </c>
       <c r="O284" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -20793,7 +20793,7 @@
       </c>
       <c r="O285" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -21168,16 +21168,16 @@
         <v>3</v>
       </c>
       <c r="G291" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H291" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="I291" s="23" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="J291" s="23" t="inlineStr">
@@ -21202,7 +21202,7 @@
       </c>
       <c r="N291" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="O291" s="27" t="inlineStr">
@@ -21237,11 +21237,11 @@
         <v>3</v>
       </c>
       <c r="G292" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H292" s="70" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="H292" s="69" t="inlineStr">
+        <is>
+          <t>67%</t>
         </is>
       </c>
       <c r="I292" s="23" t="inlineStr">
@@ -21269,14 +21269,14 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N292" s="70" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="N292" s="69" t="inlineStr">
+        <is>
+          <t>67%</t>
         </is>
       </c>
       <c r="O292" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>RE WALKDOWN</t>
         </is>
       </c>
     </row>

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -1335,7 +1335,7 @@
       </c>
       <c r="O3" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O4" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="O5" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="O6" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1572,21 +1572,21 @@
         <v>28</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="H7" s="69" t="inlineStr">
-        <is>
-          <t>68%</t>
+        <v>26</v>
+      </c>
+      <c r="H7" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="K7" s="23" t="inlineStr">
@@ -1604,9 +1604,9 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N7" s="69" t="inlineStr">
-        <is>
-          <t>68%</t>
+      <c r="N7" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="O7" s="27" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="O8" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1710,11 +1710,11 @@
         <v>132</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="H9" s="69" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="N9" s="69" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="O9" s="27" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="O12" s="27" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1986,11 +1986,11 @@
         <v>85</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H13" s="70" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="J13" s="23" t="inlineStr">
         <is>
-          <t>9/74</t>
+          <t>29/74</t>
         </is>
       </c>
       <c r="K13" s="23" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="N13" s="70" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="O13" s="27" t="inlineStr">
@@ -2193,16 +2193,16 @@
         <v>151</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H16" s="54" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="N16" s="54" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="O16" s="27" t="inlineStr">
@@ -2400,11 +2400,11 @@
         <v>62</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H19" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I19" s="23" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>59/62</t>
+          <t>60/62</t>
         </is>
       </c>
       <c r="K19" s="23" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="N19" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="O19" s="27" t="inlineStr">
@@ -2814,11 +2814,11 @@
         <v>35</v>
       </c>
       <c r="G25" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="H25" s="69" t="inlineStr">
-        <is>
-          <t>63%</t>
+        <v>32</v>
+      </c>
+      <c r="H25" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="J25" s="23" t="inlineStr">
         <is>
-          <t>22/35</t>
+          <t>32/35</t>
         </is>
       </c>
       <c r="K25" s="23" t="inlineStr">
@@ -2846,9 +2846,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N25" s="69" t="inlineStr">
-        <is>
-          <t>63%</t>
+      <c r="N25" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="O25" s="27" t="inlineStr">
@@ -4677,11 +4677,11 @@
         <v>18</v>
       </c>
       <c r="G52" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H52" s="70" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="I52" s="23" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="K52" s="23" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
       <c r="L52" s="23" t="inlineStr">
@@ -5574,11 +5574,11 @@
         <v>74</v>
       </c>
       <c r="G65" s="23" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H65" s="70" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="I65" s="23" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="K65" s="23" t="inlineStr">
         <is>
-          <t>10/73</t>
+          <t>22/73</t>
         </is>
       </c>
       <c r="L65" s="23" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="N65" s="70" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="O65" s="27" t="inlineStr">
@@ -6126,11 +6126,11 @@
         <v>249</v>
       </c>
       <c r="G73" s="23" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H73" s="70" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="I73" s="23" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="K73" s="23" t="inlineStr">
         <is>
-          <t>31/243</t>
+          <t>40/243</t>
         </is>
       </c>
       <c r="L73" s="23" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="O81" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -6816,21 +6816,21 @@
         <v>147</v>
       </c>
       <c r="G83" s="23" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="H83" s="69" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="I83" s="23" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>14/15</t>
         </is>
       </c>
       <c r="J83" s="23" t="inlineStr">
         <is>
-          <t>44/84</t>
+          <t>53/84</t>
         </is>
       </c>
       <c r="K83" s="23" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="M83" s="23" t="inlineStr">
         <is>
-          <t>39/46</t>
+          <t>42/46</t>
         </is>
       </c>
       <c r="N83" s="69" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="O83" s="27" t="inlineStr">
@@ -6885,7 +6885,7 @@
         <v>223</v>
       </c>
       <c r="G84" s="23" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H84" s="69" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="J84" s="23" t="inlineStr">
         <is>
-          <t>69/95</t>
+          <t>71/95</t>
         </is>
       </c>
       <c r="K84" s="23" t="inlineStr">
@@ -6954,11 +6954,11 @@
         <v>220</v>
       </c>
       <c r="G85" s="23" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H85" s="69" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="I85" s="23" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="J85" s="23" t="inlineStr">
         <is>
-          <t>58/95</t>
+          <t>60/95</t>
         </is>
       </c>
       <c r="K85" s="23" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="N85" s="69" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="O85" s="27" t="inlineStr">
@@ -7023,7 +7023,7 @@
         <v>220</v>
       </c>
       <c r="G86" s="23" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H86" s="69" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="J86" s="23" t="inlineStr">
         <is>
-          <t>57/95</t>
+          <t>58/95</t>
         </is>
       </c>
       <c r="K86" s="23" t="inlineStr">
@@ -7092,11 +7092,11 @@
         <v>48</v>
       </c>
       <c r="G87" s="23" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H87" s="69" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="I87" s="23" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="J87" s="23" t="inlineStr">
         <is>
-          <t>14/33</t>
+          <t>19/33</t>
         </is>
       </c>
       <c r="K87" s="23" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="N87" s="69" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="O87" s="27" t="inlineStr">
@@ -7161,11 +7161,11 @@
         <v>56</v>
       </c>
       <c r="G88" s="23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H88" s="69" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="I88" s="23" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="M88" s="23" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
       <c r="N88" s="69" t="inlineStr">
@@ -7230,11 +7230,11 @@
         <v>123</v>
       </c>
       <c r="G89" s="23" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H89" s="69" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="I89" s="23" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="M89" s="23" t="inlineStr">
         <is>
-          <t>31/35</t>
+          <t>33/35</t>
         </is>
       </c>
       <c r="N89" s="69" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="O89" s="27" t="inlineStr">
@@ -7299,11 +7299,11 @@
         <v>14</v>
       </c>
       <c r="G90" s="23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H90" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="I90" s="23" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="M90" s="23" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
       <c r="N90" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="O90" s="27" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="O91" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -7437,21 +7437,21 @@
         <v>104</v>
       </c>
       <c r="G92" s="23" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H92" s="69" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="I92" s="23" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
       <c r="J92" s="23" t="inlineStr">
         <is>
-          <t>27/35</t>
+          <t>29/35</t>
         </is>
       </c>
       <c r="K92" s="23" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="N92" s="69" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="O92" s="27" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="O93" s="27" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="N94" s="54" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O94" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -7644,41 +7644,41 @@
         <v>64</v>
       </c>
       <c r="G95" s="23" t="n">
-        <v>56</v>
-      </c>
-      <c r="H95" s="69" t="inlineStr">
+        <v>59</v>
+      </c>
+      <c r="H95" s="54" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="I95" s="23" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="J95" s="23" t="inlineStr">
+        <is>
+          <t>16/20</t>
+        </is>
+      </c>
+      <c r="K95" s="23" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="L95" s="23" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+      <c r="M95" s="23" t="inlineStr">
+        <is>
+          <t>36/36</t>
+        </is>
+      </c>
+      <c r="N95" s="69" t="inlineStr">
         <is>
           <t>88%</t>
-        </is>
-      </c>
-      <c r="I95" s="23" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="J95" s="23" t="inlineStr">
-        <is>
-          <t>15/20</t>
-        </is>
-      </c>
-      <c r="K95" s="23" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="L95" s="23" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="M95" s="23" t="inlineStr">
-        <is>
-          <t>36/36</t>
-        </is>
-      </c>
-      <c r="N95" s="69" t="inlineStr">
-        <is>
-          <t>84%</t>
         </is>
       </c>
       <c r="O95" s="27" t="inlineStr">
@@ -7713,11 +7713,11 @@
         <v>278</v>
       </c>
       <c r="G96" s="23" t="n">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H96" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="I96" s="23" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="M96" s="23" t="inlineStr">
         <is>
-          <t>257/273</t>
+          <t>261/273</t>
         </is>
       </c>
       <c r="N96" s="54" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="O96" s="27" t="inlineStr">
@@ -7782,11 +7782,11 @@
         <v>70</v>
       </c>
       <c r="G97" s="23" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H97" s="70" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="I97" s="23" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="J97" s="23" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
       <c r="K97" s="23" t="inlineStr">
@@ -7851,11 +7851,11 @@
         <v>14</v>
       </c>
       <c r="G98" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="H98" s="69" t="inlineStr">
-        <is>
-          <t>86%</t>
+        <v>13</v>
+      </c>
+      <c r="H98" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="I98" s="23" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="M98" s="23" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
       <c r="N98" s="69" t="inlineStr">
@@ -8127,11 +8127,11 @@
         <v>68</v>
       </c>
       <c r="G102" s="23" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H102" s="69" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="I102" s="23" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="J102" s="23" t="inlineStr">
         <is>
-          <t>15/24</t>
+          <t>16/24</t>
         </is>
       </c>
       <c r="K102" s="23" t="inlineStr">
@@ -8196,11 +8196,11 @@
         <v>68</v>
       </c>
       <c r="G103" s="23" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H103" s="69" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="I103" s="23" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="J103" s="23" t="inlineStr">
         <is>
-          <t>15/24</t>
+          <t>17/24</t>
         </is>
       </c>
       <c r="K103" s="23" t="inlineStr">
@@ -8265,11 +8265,11 @@
         <v>68</v>
       </c>
       <c r="G104" s="23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H104" s="69" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="I104" s="23" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="J104" s="23" t="inlineStr">
         <is>
-          <t>15/24</t>
+          <t>16/24</t>
         </is>
       </c>
       <c r="K104" s="23" t="inlineStr">
@@ -8334,41 +8334,41 @@
         <v>11</v>
       </c>
       <c r="G105" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="H105" s="69" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="H105" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I105" s="23" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J105" s="23" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+      <c r="K105" s="23" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="L105" s="23" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="M105" s="23" t="inlineStr">
+        <is>
+          <t>9/9</t>
+        </is>
+      </c>
+      <c r="N105" s="69" t="inlineStr">
         <is>
           <t>82%</t>
-        </is>
-      </c>
-      <c r="I105" s="23" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="J105" s="23" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="K105" s="23" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="L105" s="23" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="M105" s="23" t="inlineStr">
-        <is>
-          <t>9/9</t>
-        </is>
-      </c>
-      <c r="N105" s="69" t="inlineStr">
-        <is>
-          <t>73%</t>
         </is>
       </c>
       <c r="O105" s="27" t="inlineStr">
@@ -8403,11 +8403,11 @@
         <v>83</v>
       </c>
       <c r="G106" s="23" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H106" s="69" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="I106" s="23" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="M106" s="23" t="inlineStr">
         <is>
-          <t>23/24</t>
+          <t>24/24</t>
         </is>
       </c>
       <c r="N106" s="69" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="O106" s="27" t="inlineStr">
@@ -8610,11 +8610,11 @@
         <v>24</v>
       </c>
       <c r="G109" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="H109" s="70" t="inlineStr">
-        <is>
-          <t>38%</t>
+        <v>12</v>
+      </c>
+      <c r="H109" s="69" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="I109" s="23" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="J109" s="23" t="inlineStr">
         <is>
-          <t>1/7</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="K109" s="23" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="M109" s="23" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
       <c r="N109" s="70" t="inlineStr">
@@ -8676,14 +8676,14 @@
         </is>
       </c>
       <c r="F110" s="23" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G110" s="23" t="n">
         <v>42</v>
       </c>
-      <c r="H110" s="54" t="inlineStr">
-        <is>
-          <t>91%</t>
+      <c r="H110" s="69" t="inlineStr">
+        <is>
+          <t>89%</t>
         </is>
       </c>
       <c r="I110" s="23" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="M110" s="23" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>27/30</t>
         </is>
       </c>
       <c r="N110" s="69" t="inlineStr">
@@ -8716,9 +8716,9 @@
           <t>89%</t>
         </is>
       </c>
-      <c r="O110" s="27" t="inlineStr">
-        <is>
-          <t>DONE(partial)</t>
+      <c r="O110" s="69" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -8748,21 +8748,21 @@
         <v>29</v>
       </c>
       <c r="G111" s="23" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H111" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="I111" s="23" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="J111" s="23" t="inlineStr">
         <is>
-          <t>4/7</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="K111" s="23" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="M111" s="23" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="N111" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="O111" s="27" t="inlineStr">
@@ -8817,11 +8817,11 @@
         <v>17</v>
       </c>
       <c r="G112" s="23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H112" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="I112" s="23" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="M112" s="23" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
       <c r="N112" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="O112" s="27" t="inlineStr">
@@ -8987,9 +8987,9 @@
           <t>56/58</t>
         </is>
       </c>
-      <c r="N114" s="69" t="inlineStr">
-        <is>
-          <t>83%</t>
+      <c r="N114" s="54" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="O114" s="27" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="N115" s="69" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="O115" s="27" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="O116" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="O119" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -9369,11 +9369,11 @@
         <v>52</v>
       </c>
       <c r="G120" s="23" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H120" s="54" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="I120" s="23" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="K120" s="23" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="L120" s="23" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="O122" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -9576,11 +9576,11 @@
         <v>52</v>
       </c>
       <c r="G123" s="23" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H123" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="I123" s="23" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="K123" s="23" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="L123" s="23" t="inlineStr">
@@ -9714,46 +9714,46 @@
         <v>199</v>
       </c>
       <c r="G125" s="23" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H125" s="54" t="inlineStr">
         <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="I125" s="23" t="inlineStr">
+        <is>
+          <t>93/93</t>
+        </is>
+      </c>
+      <c r="J125" s="23" t="inlineStr">
+        <is>
+          <t>58/63</t>
+        </is>
+      </c>
+      <c r="K125" s="23" t="inlineStr">
+        <is>
+          <t>11/12</t>
+        </is>
+      </c>
+      <c r="L125" s="23" t="inlineStr">
+        <is>
+          <t>9/9</t>
+        </is>
+      </c>
+      <c r="M125" s="23" t="inlineStr">
+        <is>
+          <t>22/22</t>
+        </is>
+      </c>
+      <c r="N125" s="54" t="inlineStr">
+        <is>
           <t>94%</t>
         </is>
       </c>
-      <c r="I125" s="23" t="inlineStr">
-        <is>
-          <t>93/93</t>
-        </is>
-      </c>
-      <c r="J125" s="23" t="inlineStr">
-        <is>
-          <t>58/63</t>
-        </is>
-      </c>
-      <c r="K125" s="23" t="inlineStr">
-        <is>
-          <t>6/12</t>
-        </is>
-      </c>
-      <c r="L125" s="23" t="inlineStr">
-        <is>
-          <t>9/9</t>
-        </is>
-      </c>
-      <c r="M125" s="23" t="inlineStr">
-        <is>
-          <t>22/22</t>
-        </is>
-      </c>
-      <c r="N125" s="54" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
       <c r="O125" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -9783,11 +9783,11 @@
         <v>52</v>
       </c>
       <c r="G126" s="23" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H126" s="54" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="I126" s="23" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="K126" s="23" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="L126" s="23" t="inlineStr">
@@ -9921,21 +9921,21 @@
         <v>169</v>
       </c>
       <c r="G128" s="23" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H128" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="I128" s="23" t="inlineStr">
         <is>
-          <t>87/89</t>
+          <t>88/89</t>
         </is>
       </c>
       <c r="J128" s="23" t="inlineStr">
         <is>
-          <t>47/50</t>
+          <t>48/50</t>
         </is>
       </c>
       <c r="K128" s="23" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="N128" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="O128" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -9990,11 +9990,11 @@
         <v>52</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H129" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="I129" s="23" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K129" s="23" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="L129" s="23" t="inlineStr">
@@ -10128,26 +10128,26 @@
         <v>199</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="H131" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="I131" s="23" t="inlineStr">
         <is>
-          <t>91/93</t>
+          <t>92/93</t>
         </is>
       </c>
       <c r="J131" s="23" t="inlineStr">
         <is>
-          <t>60/63</t>
+          <t>62/63</t>
         </is>
       </c>
       <c r="K131" s="23" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>10/12</t>
         </is>
       </c>
       <c r="L131" s="23" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="N131" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="O131" s="27" t="inlineStr">
@@ -10197,11 +10197,11 @@
         <v>52</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>46</v>
-      </c>
-      <c r="H132" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
+        <v>49</v>
+      </c>
+      <c r="H132" s="54" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="I132" s="23" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="K132" s="23" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="L132" s="23" t="inlineStr">
@@ -10335,21 +10335,21 @@
         <v>170</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>116</v>
-      </c>
-      <c r="H134" s="69" t="inlineStr">
-        <is>
-          <t>68%</t>
+        <v>163</v>
+      </c>
+      <c r="H134" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="I134" s="23" t="inlineStr">
         <is>
-          <t>65/89</t>
+          <t>87/89</t>
         </is>
       </c>
       <c r="J134" s="23" t="inlineStr">
         <is>
-          <t>20/50</t>
+          <t>45/50</t>
         </is>
       </c>
       <c r="K134" s="23" t="inlineStr">
@@ -10367,9 +10367,9 @@
           <t>22/22</t>
         </is>
       </c>
-      <c r="N134" s="69" t="inlineStr">
-        <is>
-          <t>68%</t>
+      <c r="N134" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="O134" s="27" t="inlineStr">
@@ -10404,11 +10404,11 @@
         <v>50</v>
       </c>
       <c r="G135" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="H135" s="70" t="inlineStr">
-        <is>
-          <t>40%</t>
+        <v>37</v>
+      </c>
+      <c r="H135" s="69" t="inlineStr">
+        <is>
+          <t>74%</t>
         </is>
       </c>
       <c r="I135" s="23" t="inlineStr">
@@ -10418,12 +10418,12 @@
       </c>
       <c r="J135" s="23" t="inlineStr">
         <is>
-          <t>12/38</t>
+          <t>26/38</t>
         </is>
       </c>
       <c r="K135" s="23" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="L135" s="23" t="inlineStr">
@@ -10436,9 +10436,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N135" s="70" t="inlineStr">
-        <is>
-          <t>40%</t>
+      <c r="N135" s="69" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
       <c r="O135" s="27" t="inlineStr">
@@ -10473,11 +10473,11 @@
         <v>24</v>
       </c>
       <c r="G136" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="H136" s="69" t="inlineStr">
-        <is>
-          <t>83%</t>
+        <v>22</v>
+      </c>
+      <c r="H136" s="54" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
       <c r="I136" s="23" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="J136" s="23" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K136" s="23" t="inlineStr">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="O138" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="O139" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="O140" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="O141" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="O142" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="O144" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11133,7 @@
       </c>
       <c r="O145" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="O146" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="O147" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="O148" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="O149" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="O151" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="O152" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="O153" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="O154" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="O155" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11853,16 +11853,16 @@
         <v>34</v>
       </c>
       <c r="G156" s="23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H156" s="69" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="I156" s="23" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="J156" s="23" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="N156" s="69" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="O156" s="27" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="O158" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -12099,7 +12099,7 @@
       </c>
       <c r="O159" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="O160" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="O162" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -12444,7 +12444,7 @@
       </c>
       <c r="O164" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="O165" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="O166" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -12651,7 +12651,7 @@
       </c>
       <c r="O167" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -12819,16 +12819,16 @@
         <v>35</v>
       </c>
       <c r="G170" s="23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H170" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="I170" s="23" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="J170" s="23" t="inlineStr">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="K170" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L170" s="23" t="inlineStr">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="N170" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="O170" s="27" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="O171" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -13026,11 +13026,11 @@
         <v>67</v>
       </c>
       <c r="G173" s="23" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H173" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I173" s="23" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="J173" s="23" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="K173" s="23" t="inlineStr">
@@ -13060,12 +13060,12 @@
       </c>
       <c r="N173" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O173" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -13164,11 +13164,11 @@
         <v>67</v>
       </c>
       <c r="G175" s="23" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H175" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I175" s="23" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="J175" s="23" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="K175" s="23" t="inlineStr">
@@ -13198,12 +13198,12 @@
       </c>
       <c r="N175" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O175" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -13341,7 +13341,7 @@
       </c>
       <c r="O177" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -13440,11 +13440,11 @@
         <v>67</v>
       </c>
       <c r="G179" s="23" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H179" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="I179" s="23" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="J179" s="23" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="K179" s="23" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="N179" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="O179" s="27" t="inlineStr">
@@ -13509,16 +13509,16 @@
         <v>34</v>
       </c>
       <c r="G180" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="H180" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
+        <v>31</v>
+      </c>
+      <c r="H180" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="I180" s="23" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
       <c r="J180" s="23" t="inlineStr">
@@ -13578,11 +13578,11 @@
         <v>67</v>
       </c>
       <c r="G181" s="23" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H181" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="I181" s="23" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="J181" s="23" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="K181" s="23" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="N181" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="O181" s="27" t="inlineStr">
@@ -13647,16 +13647,16 @@
         <v>34</v>
       </c>
       <c r="G182" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="H182" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
+        <v>31</v>
+      </c>
+      <c r="H182" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="I182" s="23" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
       <c r="J182" s="23" t="inlineStr">
@@ -13716,21 +13716,21 @@
         <v>67</v>
       </c>
       <c r="G183" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="H183" s="70" t="inlineStr">
-        <is>
-          <t>46%</t>
+        <v>59</v>
+      </c>
+      <c r="H183" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="I183" s="23" t="inlineStr">
         <is>
-          <t>10/38</t>
+          <t>35/38</t>
         </is>
       </c>
       <c r="J183" s="23" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>4/8</t>
         </is>
       </c>
       <c r="K183" s="23" t="inlineStr">
@@ -13745,12 +13745,12 @@
       </c>
       <c r="M183" s="23" t="inlineStr">
         <is>
-          <t>15/17</t>
-        </is>
-      </c>
-      <c r="N183" s="70" t="inlineStr">
-        <is>
-          <t>46%</t>
+          <t>16/17</t>
+        </is>
+      </c>
+      <c r="N183" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="O183" s="27" t="inlineStr">
@@ -13785,26 +13785,26 @@
         <v>34</v>
       </c>
       <c r="G184" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="H184" s="70" t="inlineStr">
-        <is>
-          <t>41%</t>
+        <v>25</v>
+      </c>
+      <c r="H184" s="69" t="inlineStr">
+        <is>
+          <t>74%</t>
         </is>
       </c>
       <c r="I184" s="23" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>7/10</t>
         </is>
       </c>
       <c r="J184" s="23" t="inlineStr">
         <is>
-          <t>9/22</t>
+          <t>16/22</t>
         </is>
       </c>
       <c r="K184" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L184" s="23" t="inlineStr">
@@ -13817,9 +13817,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N184" s="70" t="inlineStr">
-        <is>
-          <t>41%</t>
+      <c r="N184" s="69" t="inlineStr">
+        <is>
+          <t>71%</t>
         </is>
       </c>
       <c r="O184" s="27" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="O185" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -13962,7 +13962,7 @@
       </c>
       <c r="O186" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -14031,7 +14031,7 @@
       </c>
       <c r="O187" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -14100,7 +14100,7 @@
       </c>
       <c r="O188" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="O190" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -14268,11 +14268,11 @@
         <v>70</v>
       </c>
       <c r="G191" s="23" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H191" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I191" s="23" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="J191" s="23" t="inlineStr">
         <is>
-          <t>9/16</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="K191" s="23" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="O192" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -14406,16 +14406,16 @@
         <v>34</v>
       </c>
       <c r="G193" s="23" t="n">
-        <v>29</v>
-      </c>
-      <c r="H193" s="69" t="inlineStr">
-        <is>
-          <t>85%</t>
+        <v>34</v>
+      </c>
+      <c r="H193" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I193" s="23" t="inlineStr">
         <is>
-          <t>27/32</t>
+          <t>32/32</t>
         </is>
       </c>
       <c r="J193" s="23" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="N193" s="69" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="O193" s="27" t="inlineStr">
@@ -14475,16 +14475,16 @@
         <v>34</v>
       </c>
       <c r="G194" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="H194" s="69" t="inlineStr">
-        <is>
-          <t>82%</t>
+        <v>33</v>
+      </c>
+      <c r="H194" s="54" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="I194" s="23" t="inlineStr">
         <is>
-          <t>26/32</t>
+          <t>31/32</t>
         </is>
       </c>
       <c r="J194" s="23" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="N194" s="69" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="O194" s="27" t="inlineStr">
@@ -14751,16 +14751,16 @@
         <v>67</v>
       </c>
       <c r="G198" s="23" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H198" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I198" s="23" t="inlineStr">
         <is>
-          <t>64/65</t>
+          <t>65/65</t>
         </is>
       </c>
       <c r="J198" s="23" t="inlineStr">
@@ -14785,12 +14785,12 @@
       </c>
       <c r="N198" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O198" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -15924,16 +15924,16 @@
         <v>39</v>
       </c>
       <c r="G215" s="23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H215" s="70" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="I215" s="23" t="inlineStr">
         <is>
-          <t>8/39</t>
+          <t>9/39</t>
         </is>
       </c>
       <c r="J215" s="23" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="N215" s="70" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="O215" s="27" t="inlineStr">
@@ -17166,11 +17166,11 @@
         <v>94</v>
       </c>
       <c r="G233" s="23" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H233" s="70" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="I233" s="23" t="inlineStr">
@@ -17195,12 +17195,12 @@
       </c>
       <c r="M233" s="23" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>27/30</t>
         </is>
       </c>
       <c r="N233" s="70" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="O233" s="27" t="inlineStr">
@@ -17235,11 +17235,11 @@
         <v>17</v>
       </c>
       <c r="G234" s="23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H234" s="69" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="I234" s="23" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="J234" s="23" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="K234" s="23" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="N234" s="69" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="O234" s="27" t="inlineStr">
@@ -17370,10 +17370,10 @@
         </is>
       </c>
       <c r="F236" s="23" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G236" s="23" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H236" s="69" t="inlineStr">
         <is>
@@ -17402,12 +17402,12 @@
       </c>
       <c r="M236" s="23" t="inlineStr">
         <is>
-          <t>41/46</t>
+          <t>42/47</t>
         </is>
       </c>
       <c r="N236" s="69" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="O236" s="27" t="inlineStr">
@@ -17442,21 +17442,21 @@
         <v>64</v>
       </c>
       <c r="G237" s="23" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H237" s="69" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="I237" s="23" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>8/10</t>
         </is>
       </c>
       <c r="J237" s="23" t="inlineStr">
         <is>
-          <t>12/35</t>
+          <t>22/35</t>
         </is>
       </c>
       <c r="K237" s="23" t="inlineStr">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="L237" s="23" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="M237" s="23" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="N237" s="69" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="O237" s="27" t="inlineStr">
@@ -17511,11 +17511,11 @@
         <v>62</v>
       </c>
       <c r="G238" s="23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H238" s="69" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="I238" s="23" t="inlineStr">
@@ -17525,7 +17525,7 @@
       </c>
       <c r="J238" s="23" t="inlineStr">
         <is>
-          <t>7/34</t>
+          <t>9/34</t>
         </is>
       </c>
       <c r="K238" s="23" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="N238" s="69" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="O238" s="27" t="inlineStr">
@@ -17688,7 +17688,7 @@
       </c>
       <c r="O240" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -17784,7 +17784,7 @@
         </is>
       </c>
       <c r="F242" s="23" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G242" s="23" t="n">
         <v>66</v>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="M242" s="23" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>26/31</t>
         </is>
       </c>
       <c r="N242" s="69" t="inlineStr">
@@ -17856,16 +17856,16 @@
         <v>56</v>
       </c>
       <c r="G243" s="23" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H243" s="69" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="I243" s="23" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>7/10</t>
         </is>
       </c>
       <c r="J243" s="23" t="inlineStr">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="L243" s="23" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="M243" s="23" t="inlineStr">
@@ -17925,16 +17925,16 @@
         <v>25</v>
       </c>
       <c r="G244" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="H244" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
+        <v>24</v>
+      </c>
+      <c r="H244" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="I244" s="23" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="J244" s="23" t="inlineStr">
@@ -17954,7 +17954,7 @@
       </c>
       <c r="M244" s="23" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="N244" s="69" t="inlineStr">
@@ -17991,14 +17991,14 @@
         </is>
       </c>
       <c r="F245" s="23" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G245" s="23" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H245" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="I245" s="23" t="inlineStr">
@@ -18023,12 +18023,12 @@
       </c>
       <c r="M245" s="23" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>17/20</t>
         </is>
       </c>
       <c r="N245" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="O245" s="27" t="inlineStr">
@@ -18063,21 +18063,21 @@
         <v>33</v>
       </c>
       <c r="G246" s="23" t="n">
-        <v>23</v>
-      </c>
-      <c r="H246" s="69" t="inlineStr">
-        <is>
-          <t>70%</t>
+        <v>33</v>
+      </c>
+      <c r="H246" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="I246" s="23" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="J246" s="23" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="K246" s="23" t="inlineStr">
@@ -18092,12 +18092,12 @@
       </c>
       <c r="M246" s="23" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="N246" s="69" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="O246" s="27" t="inlineStr">
@@ -18132,11 +18132,11 @@
         <v>31</v>
       </c>
       <c r="G247" s="23" t="n">
-        <v>25</v>
-      </c>
-      <c r="H247" s="69" t="inlineStr">
-        <is>
-          <t>81%</t>
+        <v>28</v>
+      </c>
+      <c r="H247" s="54" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="I247" s="23" t="inlineStr">
@@ -18161,17 +18161,17 @@
       </c>
       <c r="M247" s="23" t="inlineStr">
         <is>
-          <t>15/18</t>
-        </is>
-      </c>
-      <c r="N247" s="69" t="inlineStr">
-        <is>
-          <t>81%</t>
+          <t>18/18</t>
+        </is>
+      </c>
+      <c r="N247" s="54" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="O247" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -18201,11 +18201,11 @@
         <v>53</v>
       </c>
       <c r="G248" s="23" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H248" s="69" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="I248" s="23" t="inlineStr">
@@ -18215,7 +18215,7 @@
       </c>
       <c r="J248" s="23" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
       <c r="K248" s="23" t="inlineStr">
@@ -18235,12 +18235,12 @@
       </c>
       <c r="N248" s="69" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="O248" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -18378,7 +18378,7 @@
       </c>
       <c r="O250" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -18447,7 +18447,7 @@
       </c>
       <c r="O251" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="O254" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -18792,7 +18792,7 @@
       </c>
       <c r="O256" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -18822,11 +18822,11 @@
         <v>16</v>
       </c>
       <c r="G257" s="23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H257" s="69" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="I257" s="23" t="inlineStr">
@@ -18836,7 +18836,7 @@
       </c>
       <c r="J257" s="23" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="K257" s="23" t="inlineStr">
@@ -18851,12 +18851,12 @@
       </c>
       <c r="M257" s="23" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="N257" s="69" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="O257" s="27" t="inlineStr">
@@ -18891,11 +18891,11 @@
         <v>30</v>
       </c>
       <c r="G258" s="23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H258" s="70" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="I258" s="23" t="inlineStr">
@@ -18920,12 +18920,12 @@
       </c>
       <c r="M258" s="23" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
       <c r="N258" s="70" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="O258" s="27" t="inlineStr">
@@ -19029,11 +19029,11 @@
         <v>25</v>
       </c>
       <c r="G260" s="23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H260" s="69" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="I260" s="23" t="inlineStr">
@@ -19058,12 +19058,12 @@
       </c>
       <c r="M260" s="23" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
       <c r="N260" s="69" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="O260" s="27" t="inlineStr">
@@ -19135,9 +19135,9 @@
           <t>73%</t>
         </is>
       </c>
-      <c r="O261" s="27" t="inlineStr">
-        <is>
-          <t>DONE(partial)</t>
+      <c r="O261" s="69" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -19167,16 +19167,16 @@
         <v>69</v>
       </c>
       <c r="G262" s="23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H262" s="70" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="I262" s="23" t="inlineStr">
         <is>
-          <t>4/67</t>
+          <t>10/67</t>
         </is>
       </c>
       <c r="J262" s="23" t="inlineStr">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="N262" s="70" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="O262" s="27" t="inlineStr">
@@ -19236,16 +19236,16 @@
         <v>71</v>
       </c>
       <c r="G263" s="23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H263" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I263" s="23" t="inlineStr">
         <is>
-          <t>2/69</t>
+          <t>6/69</t>
         </is>
       </c>
       <c r="J263" s="23" t="inlineStr">
@@ -19270,7 +19270,7 @@
       </c>
       <c r="N263" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="O263" s="27" t="inlineStr">
@@ -19305,16 +19305,16 @@
         <v>69</v>
       </c>
       <c r="G264" s="23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H264" s="70" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="I264" s="23" t="inlineStr">
         <is>
-          <t>4/67</t>
+          <t>6/67</t>
         </is>
       </c>
       <c r="J264" s="23" t="inlineStr">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="N264" s="70" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="O264" s="27" t="inlineStr">
@@ -19374,16 +19374,16 @@
         <v>65</v>
       </c>
       <c r="G265" s="23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H265" s="70" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="I265" s="23" t="inlineStr">
         <is>
-          <t>17/63</t>
+          <t>19/63</t>
         </is>
       </c>
       <c r="J265" s="23" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="N265" s="70" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="O265" s="27" t="inlineStr">
@@ -19443,16 +19443,16 @@
         <v>67</v>
       </c>
       <c r="G266" s="23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H266" s="70" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="I266" s="23" t="inlineStr">
         <is>
-          <t>13/65</t>
+          <t>15/65</t>
         </is>
       </c>
       <c r="J266" s="23" t="inlineStr">
@@ -19477,7 +19477,7 @@
       </c>
       <c r="N266" s="70" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="O266" s="27" t="inlineStr">
@@ -19512,16 +19512,16 @@
         <v>75</v>
       </c>
       <c r="G267" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H267" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="I267" s="23" t="inlineStr">
         <is>
-          <t>2/73</t>
+          <t>4/73</t>
         </is>
       </c>
       <c r="J267" s="23" t="inlineStr">
@@ -19546,7 +19546,7 @@
       </c>
       <c r="N267" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="O267" s="27" t="inlineStr">
@@ -19581,16 +19581,16 @@
         <v>75</v>
       </c>
       <c r="G268" s="23" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H268" s="70" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="I268" s="23" t="inlineStr">
         <is>
-          <t>3/73</t>
+          <t>14/73</t>
         </is>
       </c>
       <c r="J268" s="23" t="inlineStr">
@@ -19615,7 +19615,7 @@
       </c>
       <c r="N268" s="70" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="O268" s="27" t="inlineStr">
@@ -19650,16 +19650,16 @@
         <v>75</v>
       </c>
       <c r="G269" s="23" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H269" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="I269" s="23" t="inlineStr">
         <is>
-          <t>2/73</t>
+          <t>18/73</t>
         </is>
       </c>
       <c r="J269" s="23" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="N269" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="O269" s="27" t="inlineStr">
@@ -19719,16 +19719,16 @@
         <v>75</v>
       </c>
       <c r="G270" s="23" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H270" s="70" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="I270" s="23" t="inlineStr">
         <is>
-          <t>5/73</t>
+          <t>14/73</t>
         </is>
       </c>
       <c r="J270" s="23" t="inlineStr">
@@ -19753,7 +19753,7 @@
       </c>
       <c r="N270" s="70" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="O270" s="27" t="inlineStr">
@@ -19788,16 +19788,16 @@
         <v>71</v>
       </c>
       <c r="G271" s="23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H271" s="70" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="I271" s="23" t="inlineStr">
         <is>
-          <t>5/69</t>
+          <t>7/69</t>
         </is>
       </c>
       <c r="J271" s="23" t="inlineStr">
@@ -19822,7 +19822,7 @@
       </c>
       <c r="N271" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="O271" s="27" t="inlineStr">
@@ -19857,16 +19857,16 @@
         <v>71</v>
       </c>
       <c r="G272" s="23" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H272" s="70" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="I272" s="23" t="inlineStr">
         <is>
-          <t>5/69</t>
+          <t>14/69</t>
         </is>
       </c>
       <c r="J272" s="23" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="N272" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="O272" s="27" t="inlineStr">
@@ -19926,16 +19926,16 @@
         <v>81</v>
       </c>
       <c r="G273" s="23" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H273" s="70" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="I273" s="23" t="inlineStr">
         <is>
-          <t>17/79</t>
+          <t>24/79</t>
         </is>
       </c>
       <c r="J273" s="23" t="inlineStr">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="N273" s="70" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="O273" s="27" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="O281" s="27" t="inlineStr">
         <is>
-          <t>DONE(FULL)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -20544,14 +20544,14 @@
         </is>
       </c>
       <c r="F282" s="23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G282" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H282" s="70" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="I282" s="23" t="inlineStr">
@@ -20581,7 +20581,7 @@
       </c>
       <c r="N282" s="70" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="O282" s="27" t="inlineStr">
@@ -20724,7 +20724,7 @@
       </c>
       <c r="O284" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -20793,7 +20793,7 @@
       </c>
       <c r="O285" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -303,12 +303,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -504,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -518,6 +512,9 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -527,10 +524,10 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -542,19 +539,16 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -564,10 +558,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -579,21 +573,21 @@
     <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -683,13 +677,10 @@
     <xf numFmtId="0" fontId="11" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -707,10 +698,7 @@
     <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,13 +710,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -737,37 +719,37 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1178,20 +1160,20 @@
           <t>PS5 COMPLETION PLATFORM  |  SUB SYSTEM - 290 subsystem(s)</t>
         </is>
       </c>
-      <c r="B1" s="100" t="n"/>
-      <c r="C1" s="100" t="n"/>
-      <c r="D1" s="100" t="n"/>
-      <c r="E1" s="100" t="n"/>
-      <c r="F1" s="100" t="n"/>
-      <c r="G1" s="100" t="n"/>
-      <c r="H1" s="100" t="n"/>
-      <c r="I1" s="100" t="n"/>
-      <c r="J1" s="100" t="n"/>
-      <c r="K1" s="100" t="n"/>
-      <c r="L1" s="100" t="n"/>
-      <c r="M1" s="100" t="n"/>
-      <c r="N1" s="100" t="n"/>
-      <c r="O1" s="101" t="n"/>
+      <c r="B1" s="96" t="n"/>
+      <c r="C1" s="96" t="n"/>
+      <c r="D1" s="96" t="n"/>
+      <c r="E1" s="96" t="n"/>
+      <c r="F1" s="96" t="n"/>
+      <c r="G1" s="96" t="n"/>
+      <c r="H1" s="96" t="n"/>
+      <c r="I1" s="96" t="n"/>
+      <c r="J1" s="96" t="n"/>
+      <c r="K1" s="96" t="n"/>
+      <c r="L1" s="96" t="n"/>
+      <c r="M1" s="96" t="n"/>
+      <c r="N1" s="96" t="n"/>
+      <c r="O1" s="97" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1276,7 +1258,7 @@
           <t>PS5-01-01</t>
         </is>
       </c>
-      <c r="B3" s="83" t="inlineStr">
+      <c r="B3" s="79" t="inlineStr">
         <is>
           <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
@@ -1287,7 +1269,7 @@
       <c r="D3" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="70" t="inlineStr">
+      <c r="E3" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -1345,7 +1327,7 @@
           <t>PS5-01-02</t>
         </is>
       </c>
-      <c r="B4" s="83" t="inlineStr">
+      <c r="B4" s="79" t="inlineStr">
         <is>
           <t>PS5-01-02 - Fire Water Pump A</t>
         </is>
@@ -1356,7 +1338,7 @@
       <c r="D4" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="70" t="inlineStr">
+      <c r="E4" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -1414,7 +1396,7 @@
           <t>PS5-01-03</t>
         </is>
       </c>
-      <c r="B5" s="83" t="inlineStr">
+      <c r="B5" s="79" t="inlineStr">
         <is>
           <t>PS5-01-03 - Fire Water Pump B</t>
         </is>
@@ -1425,7 +1407,7 @@
       <c r="D5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="70" t="inlineStr">
+      <c r="E5" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1483,7 +1465,7 @@
           <t>PS5-01-04</t>
         </is>
       </c>
-      <c r="B6" s="83" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -1494,7 +1476,7 @@
       <c r="D6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="70" t="inlineStr">
+      <c r="E6" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1552,7 +1534,7 @@
           <t>PS5-01-05</t>
         </is>
       </c>
-      <c r="B7" s="83" t="inlineStr">
+      <c r="B7" s="79" t="inlineStr">
         <is>
           <t>PS5-01-05 - Foam Skid</t>
         </is>
@@ -1563,7 +1545,7 @@
       <c r="D7" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="70" t="inlineStr">
+      <c r="E7" s="69" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -1621,7 +1603,7 @@
           <t>PS5-01-06</t>
         </is>
       </c>
-      <c r="B8" s="83" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -1632,7 +1614,7 @@
       <c r="D8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="70" t="inlineStr">
+      <c r="E8" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1690,7 +1672,7 @@
           <t>PS5-01-07</t>
         </is>
       </c>
-      <c r="B9" s="83" t="inlineStr">
+      <c r="B9" s="79" t="inlineStr">
         <is>
           <t>PS5-01-07 - Fire Water Ring Main &amp; Distribution</t>
         </is>
@@ -1701,7 +1683,7 @@
       <c r="D9" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="70" t="inlineStr">
+      <c r="E9" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1712,7 +1694,7 @@
       <c r="G9" s="23" t="n">
         <v>117</v>
       </c>
-      <c r="H9" s="69" t="inlineStr">
+      <c r="H9" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -1742,7 +1724,7 @@
           <t>86/87</t>
         </is>
       </c>
-      <c r="N9" s="69" t="inlineStr">
+      <c r="N9" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -1759,7 +1741,7 @@
           <t>PS5-01-08</t>
         </is>
       </c>
-      <c r="B10" s="83" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>PS5-01-08 - PS5 Deluge Valve Skid (PS5-01-UK-6100)</t>
         </is>
@@ -1770,7 +1752,7 @@
       <c r="D10" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="70" t="inlineStr">
+      <c r="E10" s="69" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -1781,7 +1763,7 @@
       <c r="G10" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H10" s="69" t="inlineStr">
+      <c r="H10" s="68" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -1811,7 +1793,7 @@
           <t>26/34</t>
         </is>
       </c>
-      <c r="N10" s="69" t="inlineStr">
+      <c r="N10" s="68" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -1828,7 +1810,7 @@
           <t>PS5-01-09</t>
         </is>
       </c>
-      <c r="B11" s="83" t="inlineStr">
+      <c r="B11" s="79" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -1839,7 +1821,7 @@
       <c r="D11" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="69" t="inlineStr">
+      <c r="E11" s="68" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1887,7 +1869,7 @@
       </c>
       <c r="O11" s="27" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1879,7 @@
           <t>PS5-01-10</t>
         </is>
       </c>
-      <c r="B12" s="83" t="inlineStr">
+      <c r="B12" s="79" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -1908,7 +1890,7 @@
       <c r="D12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="70" t="inlineStr">
+      <c r="E12" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -1966,7 +1948,7 @@
           <t>PS5-01-11</t>
         </is>
       </c>
-      <c r="B13" s="83" t="inlineStr">
+      <c r="B13" s="79" t="inlineStr">
         <is>
           <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
@@ -1977,7 +1959,7 @@
       <c r="D13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="70" t="inlineStr">
+      <c r="E13" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1988,7 +1970,7 @@
       <c r="G13" s="23" t="n">
         <v>39</v>
       </c>
-      <c r="H13" s="70" t="inlineStr">
+      <c r="H13" s="69" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -2018,7 +2000,7 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="N13" s="70" t="inlineStr">
+      <c r="N13" s="69" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -2035,7 +2017,7 @@
           <t>PS5-02-01</t>
         </is>
       </c>
-      <c r="B14" s="83" t="inlineStr">
+      <c r="B14" s="79" t="inlineStr">
         <is>
           <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
@@ -2046,7 +2028,7 @@
       <c r="D14" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="70" t="inlineStr">
+      <c r="E14" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2057,7 +2039,7 @@
       <c r="G14" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="70" t="inlineStr">
+      <c r="H14" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -2087,7 +2069,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N14" s="70" t="inlineStr">
+      <c r="N14" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -2104,7 +2086,7 @@
           <t>PS5-02-02</t>
         </is>
       </c>
-      <c r="B15" s="83" t="inlineStr">
+      <c r="B15" s="79" t="inlineStr">
         <is>
           <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
@@ -2115,7 +2097,7 @@
       <c r="D15" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="70" t="inlineStr">
+      <c r="E15" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2126,7 +2108,7 @@
       <c r="G15" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="70" t="inlineStr">
+      <c r="H15" s="69" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -2156,7 +2138,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N15" s="70" t="inlineStr">
+      <c r="N15" s="69" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -2173,7 +2155,7 @@
           <t>PS5-03-01</t>
         </is>
       </c>
-      <c r="B16" s="83" t="inlineStr">
+      <c r="B16" s="79" t="inlineStr">
         <is>
           <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
@@ -2184,7 +2166,7 @@
       <c r="D16" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="95" t="inlineStr">
+      <c r="E16" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2242,7 +2224,7 @@
           <t>PS5-03-03</t>
         </is>
       </c>
-      <c r="B17" s="83" t="inlineStr">
+      <c r="B17" s="79" t="inlineStr">
         <is>
           <t>PS5-03-03 - FZ-03 - Buildings Area</t>
         </is>
@@ -2253,7 +2235,7 @@
       <c r="D17" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="95" t="inlineStr">
+      <c r="E17" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2264,7 +2246,7 @@
       <c r="G17" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="70" t="inlineStr">
+      <c r="H17" s="69" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -2294,7 +2276,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N17" s="70" t="inlineStr">
+      <c r="N17" s="69" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -2311,7 +2293,7 @@
           <t>PS5-03-04</t>
         </is>
       </c>
-      <c r="B18" s="83" t="inlineStr">
+      <c r="B18" s="79" t="inlineStr">
         <is>
           <t>PS5-03-04 - FZ-04 - Utilities - Diesel and Firewater Pumps Areas</t>
         </is>
@@ -2322,7 +2304,7 @@
       <c r="D18" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="95" t="inlineStr">
+      <c r="E18" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2380,7 +2362,7 @@
           <t>PS5-03-06</t>
         </is>
       </c>
-      <c r="B19" s="83" t="inlineStr">
+      <c r="B19" s="79" t="inlineStr">
         <is>
           <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
@@ -2449,7 +2431,7 @@
           <t>PS5-03-07</t>
         </is>
       </c>
-      <c r="B20" s="83" t="inlineStr">
+      <c r="B20" s="79" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -2460,7 +2442,7 @@
       <c r="D20" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="95" t="inlineStr">
+      <c r="E20" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2518,7 +2500,7 @@
           <t>PS5-03-08</t>
         </is>
       </c>
-      <c r="B21" s="83" t="inlineStr">
+      <c r="B21" s="79" t="inlineStr">
         <is>
           <t>PS5-03-08 - FZ-08 - Utilities - Power Generation Area - External</t>
         </is>
@@ -2529,7 +2511,7 @@
       <c r="D21" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="95" t="inlineStr">
+      <c r="E21" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2587,7 +2569,7 @@
           <t>PS5-03-09</t>
         </is>
       </c>
-      <c r="B22" s="83" t="inlineStr">
+      <c r="B22" s="79" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -2598,7 +2580,7 @@
       <c r="D22" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="70" t="inlineStr">
+      <c r="E22" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2656,7 +2638,7 @@
           <t>PS5-03-10</t>
         </is>
       </c>
-      <c r="B23" s="83" t="inlineStr">
+      <c r="B23" s="79" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -2667,7 +2649,7 @@
       <c r="D23" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="95" t="inlineStr">
+      <c r="E23" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2725,7 +2707,7 @@
           <t>PS5-03-11</t>
         </is>
       </c>
-      <c r="B24" s="83" t="inlineStr">
+      <c r="B24" s="79" t="inlineStr">
         <is>
           <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
@@ -2736,7 +2718,7 @@
       <c r="D24" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="95" t="inlineStr">
+      <c r="E24" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2794,7 +2776,7 @@
           <t>PS5-03-12</t>
         </is>
       </c>
-      <c r="B25" s="83" t="inlineStr">
+      <c r="B25" s="79" t="inlineStr">
         <is>
           <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
@@ -2805,7 +2787,7 @@
       <c r="D25" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="95" t="inlineStr">
+      <c r="E25" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2863,7 +2845,7 @@
           <t>PS5-03-13</t>
         </is>
       </c>
-      <c r="B26" s="83" t="inlineStr">
+      <c r="B26" s="79" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -2874,7 +2856,7 @@
       <c r="D26" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="95" t="inlineStr">
+      <c r="E26" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2932,7 +2914,7 @@
           <t>PS5-03-14</t>
         </is>
       </c>
-      <c r="B27" s="83" t="inlineStr">
+      <c r="B27" s="79" t="inlineStr">
         <is>
           <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
@@ -2943,7 +2925,7 @@
       <c r="D27" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="70" t="inlineStr">
+      <c r="E27" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2954,7 +2936,7 @@
       <c r="G27" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H27" s="70" t="inlineStr">
+      <c r="H27" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2984,7 +2966,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N27" s="70" t="inlineStr">
+      <c r="N27" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -3001,7 +2983,7 @@
           <t>PS5-03-15</t>
         </is>
       </c>
-      <c r="B28" s="83" t="inlineStr">
+      <c r="B28" s="79" t="inlineStr">
         <is>
           <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
@@ -3012,7 +2994,7 @@
       <c r="D28" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="95" t="inlineStr">
+      <c r="E28" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3023,7 +3005,7 @@
       <c r="G28" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="70" t="inlineStr">
+      <c r="H28" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3053,7 +3035,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N28" s="70" t="inlineStr">
+      <c r="N28" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3070,7 +3052,7 @@
           <t>PS5-03-16</t>
         </is>
       </c>
-      <c r="B29" s="83" t="inlineStr">
+      <c r="B29" s="79" t="inlineStr">
         <is>
           <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
@@ -3081,7 +3063,7 @@
       <c r="D29" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="95" t="inlineStr">
+      <c r="E29" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3092,7 +3074,7 @@
       <c r="G29" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="70" t="inlineStr">
+      <c r="H29" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3122,7 +3104,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N29" s="70" t="inlineStr">
+      <c r="N29" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3139,7 +3121,7 @@
           <t>PS5-03-17</t>
         </is>
       </c>
-      <c r="B30" s="83" t="inlineStr">
+      <c r="B30" s="79" t="inlineStr">
         <is>
           <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
@@ -3150,7 +3132,7 @@
       <c r="D30" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="95" t="inlineStr">
+      <c r="E30" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3161,7 +3143,7 @@
       <c r="G30" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="70" t="inlineStr">
+      <c r="H30" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3191,7 +3173,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N30" s="70" t="inlineStr">
+      <c r="N30" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3208,7 +3190,7 @@
           <t>PS5-03-18</t>
         </is>
       </c>
-      <c r="B31" s="83" t="inlineStr">
+      <c r="B31" s="79" t="inlineStr">
         <is>
           <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
@@ -3219,7 +3201,7 @@
       <c r="D31" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="95" t="inlineStr">
+      <c r="E31" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3230,7 +3212,7 @@
       <c r="G31" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="70" t="inlineStr">
+      <c r="H31" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3260,7 +3242,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N31" s="70" t="inlineStr">
+      <c r="N31" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3277,7 +3259,7 @@
           <t>PS5-03-19</t>
         </is>
       </c>
-      <c r="B32" s="83" t="inlineStr">
+      <c r="B32" s="79" t="inlineStr">
         <is>
           <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
@@ -3288,7 +3270,7 @@
       <c r="D32" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="95" t="inlineStr">
+      <c r="E32" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3299,7 +3281,7 @@
       <c r="G32" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="70" t="inlineStr">
+      <c r="H32" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3329,7 +3311,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N32" s="70" t="inlineStr">
+      <c r="N32" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3346,7 +3328,7 @@
           <t>PS5-03-20</t>
         </is>
       </c>
-      <c r="B33" s="83" t="inlineStr">
+      <c r="B33" s="79" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -3357,7 +3339,7 @@
       <c r="D33" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="70" t="inlineStr">
+      <c r="E33" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3405,7 +3387,7 @@
       </c>
       <c r="O33" s="27" t="inlineStr">
         <is>
-          <t>07-Aug-26</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3397,7 @@
           <t>PS5-03-21</t>
         </is>
       </c>
-      <c r="B34" s="83" t="inlineStr">
+      <c r="B34" s="79" t="inlineStr">
         <is>
           <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
@@ -3426,7 +3408,7 @@
       <c r="D34" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="95" t="inlineStr">
+      <c r="E34" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3437,7 +3419,7 @@
       <c r="G34" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="70" t="inlineStr">
+      <c r="H34" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3467,7 +3449,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N34" s="70" t="inlineStr">
+      <c r="N34" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3484,7 +3466,7 @@
           <t>PS5-03-22</t>
         </is>
       </c>
-      <c r="B35" s="83" t="inlineStr">
+      <c r="B35" s="79" t="inlineStr">
         <is>
           <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
@@ -3495,7 +3477,7 @@
       <c r="D35" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="95" t="inlineStr">
+      <c r="E35" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3506,7 +3488,7 @@
       <c r="G35" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="70" t="inlineStr">
+      <c r="H35" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3536,7 +3518,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N35" s="70" t="inlineStr">
+      <c r="N35" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3553,7 +3535,7 @@
           <t>PS5-03-23</t>
         </is>
       </c>
-      <c r="B36" s="83" t="inlineStr">
+      <c r="B36" s="79" t="inlineStr">
         <is>
           <t>PS5-03-23 - FZ-E1 to E3 - EITS Building</t>
         </is>
@@ -3564,7 +3546,7 @@
       <c r="D36" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="70" t="inlineStr">
+      <c r="E36" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3575,7 +3557,7 @@
       <c r="G36" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="95" t="inlineStr">
+      <c r="H36" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3622,7 +3604,7 @@
           <t>PS5-03-24</t>
         </is>
       </c>
-      <c r="B37" s="83" t="inlineStr">
+      <c r="B37" s="79" t="inlineStr">
         <is>
           <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
@@ -3633,7 +3615,7 @@
       <c r="D37" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="95" t="inlineStr">
+      <c r="E37" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3644,7 +3626,7 @@
       <c r="G37" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="70" t="inlineStr">
+      <c r="H37" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3674,7 +3656,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N37" s="70" t="inlineStr">
+      <c r="N37" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3691,7 +3673,7 @@
           <t>PS5-03-25</t>
         </is>
       </c>
-      <c r="B38" s="83" t="inlineStr">
+      <c r="B38" s="79" t="inlineStr">
         <is>
           <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
@@ -3702,7 +3684,7 @@
       <c r="D38" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="95" t="inlineStr">
+      <c r="E38" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3713,7 +3695,7 @@
       <c r="G38" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="70" t="inlineStr">
+      <c r="H38" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3743,7 +3725,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N38" s="70" t="inlineStr">
+      <c r="N38" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3760,7 +3742,7 @@
           <t>PS5-04-01</t>
         </is>
       </c>
-      <c r="B39" s="83" t="inlineStr">
+      <c r="B39" s="79" t="inlineStr">
         <is>
           <t>PS5-04-01 - Office Building PCS System</t>
         </is>
@@ -3771,7 +3753,7 @@
       <c r="D39" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="95" t="inlineStr">
+      <c r="E39" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3782,7 +3764,7 @@
       <c r="G39" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="95" t="inlineStr">
+      <c r="H39" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3812,7 +3794,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N39" s="70" t="inlineStr">
+      <c r="N39" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3829,7 +3811,7 @@
           <t>PS5-04-02</t>
         </is>
       </c>
-      <c r="B40" s="83" t="inlineStr">
+      <c r="B40" s="79" t="inlineStr">
         <is>
           <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
@@ -3840,7 +3822,7 @@
       <c r="D40" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="95" t="inlineStr">
+      <c r="E40" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3851,7 +3833,7 @@
       <c r="G40" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="70" t="inlineStr">
+      <c r="H40" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3881,7 +3863,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N40" s="70" t="inlineStr">
+      <c r="N40" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3898,7 +3880,7 @@
           <t>PS5-04-03</t>
         </is>
       </c>
-      <c r="B41" s="83" t="inlineStr">
+      <c r="B41" s="79" t="inlineStr">
         <is>
           <t>PS5-04-03 - 33kV ICSS System</t>
         </is>
@@ -3909,7 +3891,7 @@
       <c r="D41" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="69" t="inlineStr">
+      <c r="E41" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -3920,7 +3902,7 @@
       <c r="G41" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="95" t="inlineStr">
+      <c r="H41" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3967,7 +3949,7 @@
           <t>PS5-04-04</t>
         </is>
       </c>
-      <c r="B42" s="83" t="inlineStr">
+      <c r="B42" s="79" t="inlineStr">
         <is>
           <t>PS5-04-04 - 33kV PCS System</t>
         </is>
@@ -3978,7 +3960,7 @@
       <c r="D42" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="E42" s="69" t="inlineStr">
+      <c r="E42" s="68" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -3989,7 +3971,7 @@
       <c r="G42" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="95" t="inlineStr">
+      <c r="H42" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4036,7 +4018,7 @@
           <t>PS5-04-05</t>
         </is>
       </c>
-      <c r="B43" s="83" t="inlineStr">
+      <c r="B43" s="79" t="inlineStr">
         <is>
           <t>PS5-04-05 - 33kV SIS/FGS System</t>
         </is>
@@ -4058,7 +4040,7 @@
       <c r="G43" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="95" t="inlineStr">
+      <c r="H43" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4088,7 +4070,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N43" s="69" t="inlineStr">
+      <c r="N43" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -4105,7 +4087,7 @@
           <t>PS5-05-01</t>
         </is>
       </c>
-      <c r="B44" s="83" t="inlineStr">
+      <c r="B44" s="79" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -4162,9 +4144,9 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O44" s="69" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="O44" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4156,7 @@
           <t>PS5-05-02</t>
         </is>
       </c>
-      <c r="B45" s="83" t="inlineStr">
+      <c r="B45" s="79" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -4185,7 +4167,7 @@
       <c r="D45" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="70" t="inlineStr">
+      <c r="E45" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4231,9 +4213,9 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O45" s="54" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
+      <c r="O45" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4225,7 @@
           <t>PS5-06-01</t>
         </is>
       </c>
-      <c r="B46" s="83" t="inlineStr">
+      <c r="B46" s="79" t="inlineStr">
         <is>
           <t>PS5-06-01 - AC UPS - EITS Building</t>
         </is>
@@ -4254,7 +4236,7 @@
       <c r="D46" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E46" s="69" t="inlineStr">
+      <c r="E46" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -4265,7 +4247,7 @@
       <c r="G46" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="95" t="inlineStr">
+      <c r="H46" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4295,7 +4277,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N46" s="69" t="inlineStr">
+      <c r="N46" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -4312,7 +4294,7 @@
           <t>PS5-06-02</t>
         </is>
       </c>
-      <c r="B47" s="83" t="inlineStr">
+      <c r="B47" s="79" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -4323,7 +4305,7 @@
       <c r="D47" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E47" s="70" t="inlineStr">
+      <c r="E47" s="69" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -4381,7 +4363,7 @@
           <t>PS5-06-03</t>
         </is>
       </c>
-      <c r="B48" s="83" t="inlineStr">
+      <c r="B48" s="79" t="inlineStr">
         <is>
           <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
@@ -4392,7 +4374,7 @@
       <c r="D48" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="95" t="inlineStr">
+      <c r="E48" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4403,7 +4385,7 @@
       <c r="G48" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="70" t="inlineStr">
+      <c r="H48" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4433,7 +4415,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N48" s="70" t="inlineStr">
+      <c r="N48" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4450,7 +4432,7 @@
           <t>PS5-06-04</t>
         </is>
       </c>
-      <c r="B49" s="83" t="inlineStr">
+      <c r="B49" s="79" t="inlineStr">
         <is>
           <t>PS5-06-04 - AC UPS - Guard House</t>
         </is>
@@ -4461,7 +4443,7 @@
       <c r="D49" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E49" s="95" t="inlineStr">
+      <c r="E49" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4472,7 +4454,7 @@
       <c r="G49" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="70" t="inlineStr">
+      <c r="H49" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4502,7 +4484,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N49" s="70" t="inlineStr">
+      <c r="N49" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4519,7 +4501,7 @@
           <t>PS5-06-05</t>
         </is>
       </c>
-      <c r="B50" s="83" t="inlineStr">
+      <c r="B50" s="79" t="inlineStr">
         <is>
           <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
@@ -4530,7 +4512,7 @@
       <c r="D50" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="95" t="inlineStr">
+      <c r="E50" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4541,7 +4523,7 @@
       <c r="G50" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="70" t="inlineStr">
+      <c r="H50" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4571,7 +4553,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N50" s="70" t="inlineStr">
+      <c r="N50" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4588,7 +4570,7 @@
           <t>PS5-08-01</t>
         </is>
       </c>
-      <c r="B51" s="83" t="inlineStr">
+      <c r="B51" s="79" t="inlineStr">
         <is>
           <t>PS5-08-01 - PAGA</t>
         </is>
@@ -4599,7 +4581,7 @@
       <c r="D51" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="70" t="inlineStr">
+      <c r="E51" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4610,7 +4592,7 @@
       <c r="G51" s="23" t="n">
         <v>82</v>
       </c>
-      <c r="H51" s="70" t="inlineStr">
+      <c r="H51" s="69" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -4640,7 +4622,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N51" s="70" t="inlineStr">
+      <c r="N51" s="69" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -4657,7 +4639,7 @@
           <t>PS5-08-03</t>
         </is>
       </c>
-      <c r="B52" s="83" t="inlineStr">
+      <c r="B52" s="79" t="inlineStr">
         <is>
           <t>PS5-08-03 - Telephone</t>
         </is>
@@ -4668,7 +4650,7 @@
       <c r="D52" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="95" t="inlineStr">
+      <c r="E52" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4679,7 +4661,7 @@
       <c r="G52" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H52" s="70" t="inlineStr">
+      <c r="H52" s="69" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -4709,7 +4691,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N52" s="70" t="inlineStr">
+      <c r="N52" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -4726,7 +4708,7 @@
           <t>PS5-08-04</t>
         </is>
       </c>
-      <c r="B53" s="83" t="inlineStr">
+      <c r="B53" s="79" t="inlineStr">
         <is>
           <t>PS5-08-04 - Hotline</t>
         </is>
@@ -4737,7 +4719,7 @@
       <c r="D53" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="95" t="inlineStr">
+      <c r="E53" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4748,7 +4730,7 @@
       <c r="G53" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="95" t="inlineStr">
+      <c r="H53" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4778,7 +4760,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N53" s="70" t="inlineStr">
+      <c r="N53" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4795,7 +4777,7 @@
           <t>PS5-08-07</t>
         </is>
       </c>
-      <c r="B54" s="83" t="inlineStr">
+      <c r="B54" s="79" t="inlineStr">
         <is>
           <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
@@ -4806,7 +4788,7 @@
       <c r="D54" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="95" t="inlineStr">
+      <c r="E54" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4817,7 +4799,7 @@
       <c r="G54" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="95" t="inlineStr">
+      <c r="H54" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4847,7 +4829,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N54" s="70" t="inlineStr">
+      <c r="N54" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4864,7 +4846,7 @@
           <t>PS5-08-11</t>
         </is>
       </c>
-      <c r="B55" s="83" t="inlineStr">
+      <c r="B55" s="79" t="inlineStr">
         <is>
           <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
@@ -4875,7 +4857,7 @@
       <c r="D55" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E55" s="70" t="inlineStr">
+      <c r="E55" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4886,7 +4868,7 @@
       <c r="G55" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H55" s="70" t="inlineStr">
+      <c r="H55" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4916,7 +4898,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N55" s="70" t="inlineStr">
+      <c r="N55" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4933,7 +4915,7 @@
           <t>PS5-08-12</t>
         </is>
       </c>
-      <c r="B56" s="83" t="inlineStr">
+      <c r="B56" s="79" t="inlineStr">
         <is>
           <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
@@ -4944,7 +4926,7 @@
       <c r="D56" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="95" t="inlineStr">
+      <c r="E56" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4955,7 +4937,7 @@
       <c r="G56" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="70" t="inlineStr">
+      <c r="H56" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4985,7 +4967,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N56" s="70" t="inlineStr">
+      <c r="N56" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5002,7 +4984,7 @@
           <t>PS5-08-13</t>
         </is>
       </c>
-      <c r="B57" s="83" t="inlineStr">
+      <c r="B57" s="79" t="inlineStr">
         <is>
           <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
@@ -5013,7 +4995,7 @@
       <c r="D57" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="69" t="inlineStr">
+      <c r="E57" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -5024,7 +5006,7 @@
       <c r="G57" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="70" t="inlineStr">
+      <c r="H57" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5054,7 +5036,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N57" s="70" t="inlineStr">
+      <c r="N57" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5071,7 +5053,7 @@
           <t>PS5-08-14</t>
         </is>
       </c>
-      <c r="B58" s="83" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
@@ -5082,7 +5064,7 @@
       <c r="D58" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E58" s="95" t="inlineStr">
+      <c r="E58" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5093,7 +5075,7 @@
       <c r="G58" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="70" t="inlineStr">
+      <c r="H58" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5123,7 +5105,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N58" s="70" t="inlineStr">
+      <c r="N58" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5140,7 +5122,7 @@
           <t>PS5-08-15</t>
         </is>
       </c>
-      <c r="B59" s="83" t="inlineStr">
+      <c r="B59" s="79" t="inlineStr">
         <is>
           <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
@@ -5151,7 +5133,7 @@
       <c r="D59" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E59" s="70" t="inlineStr">
+      <c r="E59" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -5162,7 +5144,7 @@
       <c r="G59" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="70" t="inlineStr">
+      <c r="H59" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5192,7 +5174,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N59" s="70" t="inlineStr">
+      <c r="N59" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5209,7 +5191,7 @@
           <t>PS5-08-23</t>
         </is>
       </c>
-      <c r="B60" s="83" t="inlineStr">
+      <c r="B60" s="79" t="inlineStr">
         <is>
           <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
@@ -5220,7 +5202,7 @@
       <c r="D60" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="70" t="inlineStr">
+      <c r="E60" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5231,7 +5213,7 @@
       <c r="G60" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="70" t="inlineStr">
+      <c r="H60" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5261,7 +5243,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N60" s="70" t="inlineStr">
+      <c r="N60" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5278,7 +5260,7 @@
           <t>PS5-08-34</t>
         </is>
       </c>
-      <c r="B61" s="83" t="inlineStr">
+      <c r="B61" s="79" t="inlineStr">
         <is>
           <t>PS5-08-34 - Satphone</t>
         </is>
@@ -5289,7 +5271,7 @@
       <c r="D61" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E61" s="95" t="inlineStr">
+      <c r="E61" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5300,7 +5282,7 @@
       <c r="G61" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="70" t="inlineStr">
+      <c r="H61" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5330,7 +5312,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N61" s="70" t="inlineStr">
+      <c r="N61" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5347,7 +5329,7 @@
           <t>PS5-08-35</t>
         </is>
       </c>
-      <c r="B62" s="83" t="inlineStr">
+      <c r="B62" s="79" t="inlineStr">
         <is>
           <t>PS5-08-35 - Optical Transport Network</t>
         </is>
@@ -5358,7 +5340,7 @@
       <c r="D62" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E62" s="70" t="inlineStr">
+      <c r="E62" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5369,7 +5351,7 @@
       <c r="G62" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="95" t="inlineStr">
+      <c r="H62" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5399,7 +5381,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N62" s="69" t="inlineStr">
+      <c r="N62" s="68" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -5416,7 +5398,7 @@
           <t>PS5-08-36</t>
         </is>
       </c>
-      <c r="B63" s="83" t="inlineStr">
+      <c r="B63" s="79" t="inlineStr">
         <is>
           <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
@@ -5427,7 +5409,7 @@
       <c r="D63" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E63" s="95" t="inlineStr">
+      <c r="E63" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5438,7 +5420,7 @@
       <c r="G63" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="70" t="inlineStr">
+      <c r="H63" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5468,7 +5450,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N63" s="70" t="inlineStr">
+      <c r="N63" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5485,7 +5467,7 @@
           <t>PS5-08-51</t>
         </is>
       </c>
-      <c r="B64" s="83" t="inlineStr">
+      <c r="B64" s="79" t="inlineStr">
         <is>
           <t>PS5-08-51 - Entertainment</t>
         </is>
@@ -5496,7 +5478,7 @@
       <c r="D64" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="95" t="inlineStr">
+      <c r="E64" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5507,7 +5489,7 @@
       <c r="G64" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H64" s="70" t="inlineStr">
+      <c r="H64" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5537,7 +5519,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N64" s="70" t="inlineStr">
+      <c r="N64" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5554,7 +5536,7 @@
           <t>PS5-08-52</t>
         </is>
       </c>
-      <c r="B65" s="83" t="inlineStr">
+      <c r="B65" s="79" t="inlineStr">
         <is>
           <t>PS5-08-52 - Process &amp; Security CCTV</t>
         </is>
@@ -5565,7 +5547,7 @@
       <c r="D65" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="95" t="inlineStr">
+      <c r="E65" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5576,7 +5558,7 @@
       <c r="G65" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="H65" s="70" t="inlineStr">
+      <c r="H65" s="69" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -5606,7 +5588,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N65" s="70" t="inlineStr">
+      <c r="N65" s="69" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -5623,7 +5605,7 @@
           <t>PS5-08-55</t>
         </is>
       </c>
-      <c r="B66" s="83" t="inlineStr">
+      <c r="B66" s="79" t="inlineStr">
         <is>
           <t>PS5-08-55 - Videoconference</t>
         </is>
@@ -5634,7 +5616,7 @@
       <c r="D66" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="95" t="inlineStr">
+      <c r="E66" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5645,7 +5627,7 @@
       <c r="G66" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H66" s="95" t="inlineStr">
+      <c r="H66" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5675,7 +5657,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N66" s="70" t="inlineStr">
+      <c r="N66" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5692,7 +5674,7 @@
           <t>PS5-08-61</t>
         </is>
       </c>
-      <c r="B67" s="83" t="inlineStr">
+      <c r="B67" s="79" t="inlineStr">
         <is>
           <t>PS5-08-61 - Meteocean</t>
         </is>
@@ -5703,7 +5685,7 @@
       <c r="D67" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="95" t="inlineStr">
+      <c r="E67" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5714,7 +5696,7 @@
       <c r="G67" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H67" s="70" t="inlineStr">
+      <c r="H67" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5744,7 +5726,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N67" s="70" t="inlineStr">
+      <c r="N67" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5761,7 +5743,7 @@
           <t>PS5-08-71</t>
         </is>
       </c>
-      <c r="B68" s="83" t="inlineStr">
+      <c r="B68" s="79" t="inlineStr">
         <is>
           <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
@@ -5772,7 +5754,7 @@
       <c r="D68" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E68" s="95" t="inlineStr">
+      <c r="E68" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5783,7 +5765,7 @@
       <c r="G68" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H68" s="70" t="inlineStr">
+      <c r="H68" s="69" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -5813,7 +5795,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N68" s="70" t="inlineStr">
+      <c r="N68" s="69" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -5830,7 +5812,7 @@
           <t>PS5-08-72</t>
         </is>
       </c>
-      <c r="B69" s="83" t="inlineStr">
+      <c r="B69" s="79" t="inlineStr">
         <is>
           <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
@@ -5841,7 +5823,7 @@
       <c r="D69" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E69" s="95" t="inlineStr">
+      <c r="E69" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5852,7 +5834,7 @@
       <c r="G69" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="70" t="inlineStr">
+      <c r="H69" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5882,7 +5864,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N69" s="70" t="inlineStr">
+      <c r="N69" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5899,7 +5881,7 @@
           <t>PS5-08-81</t>
         </is>
       </c>
-      <c r="B70" s="83" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>PS5-08-81 - Guard tour</t>
         </is>
@@ -5910,7 +5892,7 @@
       <c r="D70" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E70" s="95" t="inlineStr">
+      <c r="E70" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5921,7 +5903,7 @@
       <c r="G70" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H70" s="95" t="inlineStr">
+      <c r="H70" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5951,7 +5933,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N70" s="70" t="inlineStr">
+      <c r="N70" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5968,7 +5950,7 @@
           <t>PS5-08-82</t>
         </is>
       </c>
-      <c r="B71" s="83" t="inlineStr">
+      <c r="B71" s="79" t="inlineStr">
         <is>
           <t>PS5-08-82 - Key Management</t>
         </is>
@@ -5979,7 +5961,7 @@
       <c r="D71" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E71" s="95" t="inlineStr">
+      <c r="E71" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5990,7 +5972,7 @@
       <c r="G71" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H71" s="95" t="inlineStr">
+      <c r="H71" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6020,7 +6002,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N71" s="70" t="inlineStr">
+      <c r="N71" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6037,7 +6019,7 @@
           <t>PS5-08-83</t>
         </is>
       </c>
-      <c r="B72" s="83" t="inlineStr">
+      <c r="B72" s="79" t="inlineStr">
         <is>
           <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
@@ -6048,7 +6030,7 @@
       <c r="D72" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="95" t="inlineStr">
+      <c r="E72" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6059,7 +6041,7 @@
       <c r="G72" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="70" t="inlineStr">
+      <c r="H72" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6089,7 +6071,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N72" s="70" t="inlineStr">
+      <c r="N72" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6106,7 +6088,7 @@
           <t>PS5-08-85</t>
         </is>
       </c>
-      <c r="B73" s="83" t="inlineStr">
+      <c r="B73" s="79" t="inlineStr">
         <is>
           <t>PS5-08-85 - Access Control, POB &amp; e-Mustering</t>
         </is>
@@ -6128,7 +6110,7 @@
       <c r="G73" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="H73" s="70" t="inlineStr">
+      <c r="H73" s="69" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -6158,7 +6140,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N73" s="70" t="inlineStr">
+      <c r="N73" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -6175,7 +6157,7 @@
           <t>PS5-08-86</t>
         </is>
       </c>
-      <c r="B74" s="83" t="inlineStr">
+      <c r="B74" s="79" t="inlineStr">
         <is>
           <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
@@ -6186,7 +6168,7 @@
       <c r="D74" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="95" t="inlineStr">
+      <c r="E74" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6197,7 +6179,7 @@
       <c r="G74" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="95" t="inlineStr">
+      <c r="H74" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6227,7 +6209,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N74" s="70" t="inlineStr">
+      <c r="N74" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6244,7 +6226,7 @@
           <t>PS5-08-92</t>
         </is>
       </c>
-      <c r="B75" s="83" t="inlineStr">
+      <c r="B75" s="79" t="inlineStr">
         <is>
           <t>PS5-08-92 - Telecom Mast</t>
         </is>
@@ -6255,7 +6237,7 @@
       <c r="D75" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E75" s="95" t="inlineStr">
+      <c r="E75" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6266,7 +6248,7 @@
       <c r="G75" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H75" s="95" t="inlineStr">
+      <c r="H75" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6296,7 +6278,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N75" s="70" t="inlineStr">
+      <c r="N75" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6313,7 +6295,7 @@
           <t>PS5-08-93</t>
         </is>
       </c>
-      <c r="B76" s="83" t="inlineStr">
+      <c r="B76" s="79" t="inlineStr">
         <is>
           <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
@@ -6324,7 +6306,7 @@
       <c r="D76" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E76" s="95" t="inlineStr">
+      <c r="E76" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6335,7 +6317,7 @@
       <c r="G76" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H76" s="70" t="inlineStr">
+      <c r="H76" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6365,7 +6347,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N76" s="70" t="inlineStr">
+      <c r="N76" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6382,7 +6364,7 @@
           <t>PS5-09-01</t>
         </is>
       </c>
-      <c r="B77" s="83" t="inlineStr">
+      <c r="B77" s="79" t="inlineStr">
         <is>
           <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
@@ -6393,7 +6375,7 @@
       <c r="D77" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="95" t="inlineStr">
+      <c r="E77" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6404,7 +6386,7 @@
       <c r="G77" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H77" s="70" t="inlineStr">
+      <c r="H77" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6434,7 +6416,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N77" s="70" t="inlineStr">
+      <c r="N77" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6451,7 +6433,7 @@
           <t>PS5-09-02</t>
         </is>
       </c>
-      <c r="B78" s="83" t="inlineStr">
+      <c r="B78" s="79" t="inlineStr">
         <is>
           <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
@@ -6462,7 +6444,7 @@
       <c r="D78" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E78" s="95" t="inlineStr">
+      <c r="E78" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6473,7 +6455,7 @@
       <c r="G78" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H78" s="70" t="inlineStr">
+      <c r="H78" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6503,7 +6485,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N78" s="70" t="inlineStr">
+      <c r="N78" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6520,7 +6502,7 @@
           <t>PS5-09-03</t>
         </is>
       </c>
-      <c r="B79" s="83" t="inlineStr">
+      <c r="B79" s="79" t="inlineStr">
         <is>
           <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
@@ -6531,7 +6513,7 @@
       <c r="D79" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E79" s="70" t="inlineStr">
+      <c r="E79" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -6542,7 +6524,7 @@
       <c r="G79" s="23" t="n">
         <v>53</v>
       </c>
-      <c r="H79" s="70" t="inlineStr">
+      <c r="H79" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -6572,7 +6554,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N79" s="70" t="inlineStr">
+      <c r="N79" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -6589,7 +6571,7 @@
           <t>PS5-09-04</t>
         </is>
       </c>
-      <c r="B80" s="83" t="inlineStr">
+      <c r="B80" s="79" t="inlineStr">
         <is>
           <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
@@ -6600,7 +6582,7 @@
       <c r="D80" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E80" s="95" t="inlineStr">
+      <c r="E80" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6611,7 +6593,7 @@
       <c r="G80" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="70" t="inlineStr">
+      <c r="H80" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6641,7 +6623,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N80" s="70" t="inlineStr">
+      <c r="N80" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6658,7 +6640,7 @@
           <t>PS5-09-05</t>
         </is>
       </c>
-      <c r="B81" s="83" t="inlineStr">
+      <c r="B81" s="79" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -6669,7 +6651,7 @@
       <c r="D81" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="E81" s="69" t="inlineStr">
+      <c r="E81" s="68" t="inlineStr">
         <is>
           <t>56%</t>
         </is>
@@ -6727,7 +6709,7 @@
           <t>PS5-0H-01</t>
         </is>
       </c>
-      <c r="B82" s="83" t="inlineStr">
+      <c r="B82" s="79" t="inlineStr">
         <is>
           <t>PS5-0H-01 - HIPPS</t>
         </is>
@@ -6738,7 +6720,7 @@
       <c r="D82" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E82" s="70" t="inlineStr">
+      <c r="E82" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -6749,7 +6731,7 @@
       <c r="G82" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="95" t="inlineStr">
+      <c r="H82" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6779,7 +6761,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N82" s="69" t="inlineStr">
+      <c r="N82" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -6796,7 +6778,7 @@
           <t>PS5-25-01</t>
         </is>
       </c>
-      <c r="B83" s="83" t="inlineStr">
+      <c r="B83" s="79" t="inlineStr">
         <is>
           <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
@@ -6807,7 +6789,7 @@
       <c r="D83" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E83" s="70" t="inlineStr">
+      <c r="E83" s="69" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -6818,7 +6800,7 @@
       <c r="G83" s="23" t="n">
         <v>111</v>
       </c>
-      <c r="H83" s="69" t="inlineStr">
+      <c r="H83" s="68" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -6848,7 +6830,7 @@
           <t>42/46</t>
         </is>
       </c>
-      <c r="N83" s="69" t="inlineStr">
+      <c r="N83" s="68" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -6865,7 +6847,7 @@
           <t>PS5-25-02</t>
         </is>
       </c>
-      <c r="B84" s="83" t="inlineStr">
+      <c r="B84" s="79" t="inlineStr">
         <is>
           <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
@@ -6876,7 +6858,7 @@
       <c r="D84" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="E84" s="70" t="inlineStr">
+      <c r="E84" s="69" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -6887,7 +6869,7 @@
       <c r="G84" s="23" t="n">
         <v>175</v>
       </c>
-      <c r="H84" s="69" t="inlineStr">
+      <c r="H84" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -6917,7 +6899,7 @@
           <t>23/24</t>
         </is>
       </c>
-      <c r="N84" s="69" t="inlineStr">
+      <c r="N84" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -6934,7 +6916,7 @@
           <t>PS5-25-03</t>
         </is>
       </c>
-      <c r="B85" s="83" t="inlineStr">
+      <c r="B85" s="79" t="inlineStr">
         <is>
           <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
@@ -6945,7 +6927,7 @@
       <c r="D85" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="E85" s="70" t="inlineStr">
+      <c r="E85" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -6956,7 +6938,7 @@
       <c r="G85" s="23" t="n">
         <v>164</v>
       </c>
-      <c r="H85" s="69" t="inlineStr">
+      <c r="H85" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -6986,7 +6968,7 @@
           <t>23/24</t>
         </is>
       </c>
-      <c r="N85" s="69" t="inlineStr">
+      <c r="N85" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -7003,7 +6985,7 @@
           <t>PS5-25-04</t>
         </is>
       </c>
-      <c r="B86" s="83" t="inlineStr">
+      <c r="B86" s="79" t="inlineStr">
         <is>
           <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
@@ -7014,7 +6996,7 @@
       <c r="D86" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E86" s="70" t="inlineStr">
+      <c r="E86" s="69" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -7025,7 +7007,7 @@
       <c r="G86" s="23" t="n">
         <v>161</v>
       </c>
-      <c r="H86" s="69" t="inlineStr">
+      <c r="H86" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -7055,7 +7037,7 @@
           <t>23/24</t>
         </is>
       </c>
-      <c r="N86" s="69" t="inlineStr">
+      <c r="N86" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -7072,7 +7054,7 @@
           <t>PS5-25-05</t>
         </is>
       </c>
-      <c r="B87" s="83" t="inlineStr">
+      <c r="B87" s="79" t="inlineStr">
         <is>
           <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
@@ -7094,7 +7076,7 @@
       <c r="G87" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H87" s="69" t="inlineStr">
+      <c r="H87" s="68" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
@@ -7124,7 +7106,7 @@
           <t>8/9</t>
         </is>
       </c>
-      <c r="N87" s="69" t="inlineStr">
+      <c r="N87" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -7141,7 +7123,7 @@
           <t>PS5-25-06</t>
         </is>
       </c>
-      <c r="B88" s="83" t="inlineStr">
+      <c r="B88" s="79" t="inlineStr">
         <is>
           <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
@@ -7152,7 +7134,7 @@
       <c r="D88" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E88" s="70" t="inlineStr">
+      <c r="E88" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7163,7 +7145,7 @@
       <c r="G88" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H88" s="69" t="inlineStr">
+      <c r="H88" s="68" t="inlineStr">
         <is>
           <t>59%</t>
         </is>
@@ -7193,7 +7175,7 @@
           <t>17/19</t>
         </is>
       </c>
-      <c r="N88" s="69" t="inlineStr">
+      <c r="N88" s="68" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -7210,7 +7192,7 @@
           <t>PS5-25-07</t>
         </is>
       </c>
-      <c r="B89" s="83" t="inlineStr">
+      <c r="B89" s="79" t="inlineStr">
         <is>
           <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
@@ -7221,7 +7203,7 @@
       <c r="D89" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E89" s="70" t="inlineStr">
+      <c r="E89" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -7232,7 +7214,7 @@
       <c r="G89" s="23" t="n">
         <v>103</v>
       </c>
-      <c r="H89" s="69" t="inlineStr">
+      <c r="H89" s="68" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -7262,7 +7244,7 @@
           <t>33/35</t>
         </is>
       </c>
-      <c r="N89" s="69" t="inlineStr">
+      <c r="N89" s="68" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -7279,7 +7261,7 @@
           <t>PS5-28-01</t>
         </is>
       </c>
-      <c r="B90" s="83" t="inlineStr">
+      <c r="B90" s="79" t="inlineStr">
         <is>
           <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
@@ -7290,7 +7272,7 @@
       <c r="D90" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E90" s="95" t="inlineStr">
+      <c r="E90" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7301,7 +7283,7 @@
       <c r="G90" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H90" s="69" t="inlineStr">
+      <c r="H90" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -7331,7 +7313,7 @@
           <t>12/14</t>
         </is>
       </c>
-      <c r="N90" s="69" t="inlineStr">
+      <c r="N90" s="68" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -7348,7 +7330,7 @@
           <t>PS5-28-02</t>
         </is>
       </c>
-      <c r="B91" s="83" t="inlineStr">
+      <c r="B91" s="79" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -7359,7 +7341,7 @@
       <c r="D91" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E91" s="70" t="inlineStr">
+      <c r="E91" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7417,7 +7399,7 @@
           <t>PS5-28-03</t>
         </is>
       </c>
-      <c r="B92" s="83" t="inlineStr">
+      <c r="B92" s="79" t="inlineStr">
         <is>
           <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
@@ -7428,7 +7410,7 @@
       <c r="D92" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E92" s="70" t="inlineStr">
+      <c r="E92" s="69" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -7439,7 +7421,7 @@
       <c r="G92" s="23" t="n">
         <v>93</v>
       </c>
-      <c r="H92" s="69" t="inlineStr">
+      <c r="H92" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -7469,7 +7451,7 @@
           <t>54/56</t>
         </is>
       </c>
-      <c r="N92" s="69" t="inlineStr">
+      <c r="N92" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -7486,7 +7468,7 @@
           <t>PS5-28-04</t>
         </is>
       </c>
-      <c r="B93" s="83" t="inlineStr">
+      <c r="B93" s="79" t="inlineStr">
         <is>
           <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
@@ -7497,7 +7479,7 @@
       <c r="D93" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E93" s="70" t="inlineStr">
+      <c r="E93" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -7555,7 +7537,7 @@
           <t>PS5-28-05</t>
         </is>
       </c>
-      <c r="B94" s="83" t="inlineStr">
+      <c r="B94" s="79" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -7566,7 +7548,7 @@
       <c r="D94" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E94" s="70" t="inlineStr">
+      <c r="E94" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7624,7 +7606,7 @@
           <t>PS5-28-06</t>
         </is>
       </c>
-      <c r="B95" s="83" t="inlineStr">
+      <c r="B95" s="79" t="inlineStr">
         <is>
           <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
@@ -7635,7 +7617,7 @@
       <c r="D95" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E95" s="70" t="inlineStr">
+      <c r="E95" s="69" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -7676,7 +7658,7 @@
           <t>36/36</t>
         </is>
       </c>
-      <c r="N95" s="69" t="inlineStr">
+      <c r="N95" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -7693,7 +7675,7 @@
           <t>PS5-28-07</t>
         </is>
       </c>
-      <c r="B96" s="83" t="inlineStr">
+      <c r="B96" s="79" t="inlineStr">
         <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
@@ -7704,7 +7686,7 @@
       <c r="D96" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E96" s="70" t="inlineStr">
+      <c r="E96" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -7762,7 +7744,7 @@
           <t>PS5-28-08</t>
         </is>
       </c>
-      <c r="B97" s="83" t="inlineStr">
+      <c r="B97" s="79" t="inlineStr">
         <is>
           <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
@@ -7773,7 +7755,7 @@
       <c r="D97" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E97" s="70" t="inlineStr">
+      <c r="E97" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7784,7 +7766,7 @@
       <c r="G97" s="23" t="n">
         <v>34</v>
       </c>
-      <c r="H97" s="70" t="inlineStr">
+      <c r="H97" s="69" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
@@ -7814,7 +7796,7 @@
           <t>23/29</t>
         </is>
       </c>
-      <c r="N97" s="70" t="inlineStr">
+      <c r="N97" s="69" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -7831,7 +7813,7 @@
           <t>PS5-28-09</t>
         </is>
       </c>
-      <c r="B98" s="83" t="inlineStr">
+      <c r="B98" s="79" t="inlineStr">
         <is>
           <t>PS5-28-09 - Observation Basin</t>
         </is>
@@ -7842,7 +7824,7 @@
       <c r="D98" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E98" s="70" t="inlineStr">
+      <c r="E98" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7883,7 +7865,7 @@
           <t>13/14</t>
         </is>
       </c>
-      <c r="N98" s="69" t="inlineStr">
+      <c r="N98" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -7900,7 +7882,7 @@
           <t>PS5-28-10</t>
         </is>
       </c>
-      <c r="B99" s="83" t="inlineStr">
+      <c r="B99" s="79" t="inlineStr">
         <is>
           <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
@@ -7911,7 +7893,7 @@
       <c r="D99" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E99" s="70" t="inlineStr">
+      <c r="E99" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7922,7 +7904,7 @@
       <c r="G99" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H99" s="70" t="inlineStr">
+      <c r="H99" s="69" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -7952,7 +7934,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N99" s="70" t="inlineStr">
+      <c r="N99" s="69" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -7969,7 +7951,7 @@
           <t>PS5-28-11</t>
         </is>
       </c>
-      <c r="B100" s="83" t="inlineStr">
+      <c r="B100" s="79" t="inlineStr">
         <is>
           <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
@@ -7980,7 +7962,7 @@
       <c r="D100" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E100" s="70" t="inlineStr">
+      <c r="E100" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7991,7 +7973,7 @@
       <c r="G100" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H100" s="69" t="inlineStr">
+      <c r="H100" s="68" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -8021,7 +8003,7 @@
           <t>8/8</t>
         </is>
       </c>
-      <c r="N100" s="69" t="inlineStr">
+      <c r="N100" s="68" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -8038,7 +8020,7 @@
           <t>PS5-28-12</t>
         </is>
       </c>
-      <c r="B101" s="83" t="inlineStr">
+      <c r="B101" s="79" t="inlineStr">
         <is>
           <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
@@ -8049,7 +8031,7 @@
       <c r="D101" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E101" s="70" t="inlineStr">
+      <c r="E101" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8060,7 +8042,7 @@
       <c r="G101" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="H101" s="69" t="inlineStr">
+      <c r="H101" s="68" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8090,7 +8072,7 @@
           <t>28/43</t>
         </is>
       </c>
-      <c r="N101" s="69" t="inlineStr">
+      <c r="N101" s="68" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8107,7 +8089,7 @@
           <t>PS5-28-13</t>
         </is>
       </c>
-      <c r="B102" s="83" t="inlineStr">
+      <c r="B102" s="79" t="inlineStr">
         <is>
           <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
@@ -8118,7 +8100,7 @@
       <c r="D102" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E102" s="69" t="inlineStr">
+      <c r="E102" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8129,7 +8111,7 @@
       <c r="G102" s="23" t="n">
         <v>54</v>
       </c>
-      <c r="H102" s="69" t="inlineStr">
+      <c r="H102" s="68" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -8159,7 +8141,7 @@
           <t>34/35</t>
         </is>
       </c>
-      <c r="N102" s="69" t="inlineStr">
+      <c r="N102" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -8176,7 +8158,7 @@
           <t>PS5-28-14</t>
         </is>
       </c>
-      <c r="B103" s="83" t="inlineStr">
+      <c r="B103" s="79" t="inlineStr">
         <is>
           <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
@@ -8187,7 +8169,7 @@
       <c r="D103" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="69" t="inlineStr">
+      <c r="E103" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8198,7 +8180,7 @@
       <c r="G103" s="23" t="n">
         <v>53</v>
       </c>
-      <c r="H103" s="69" t="inlineStr">
+      <c r="H103" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -8228,7 +8210,7 @@
           <t>32/35</t>
         </is>
       </c>
-      <c r="N103" s="69" t="inlineStr">
+      <c r="N103" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8245,7 +8227,7 @@
           <t>PS5-28-15</t>
         </is>
       </c>
-      <c r="B104" s="83" t="inlineStr">
+      <c r="B104" s="79" t="inlineStr">
         <is>
           <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
@@ -8256,7 +8238,7 @@
       <c r="D104" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E104" s="69" t="inlineStr">
+      <c r="E104" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8267,7 +8249,7 @@
       <c r="G104" s="23" t="n">
         <v>52</v>
       </c>
-      <c r="H104" s="69" t="inlineStr">
+      <c r="H104" s="68" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -8297,7 +8279,7 @@
           <t>32/35</t>
         </is>
       </c>
-      <c r="N104" s="69" t="inlineStr">
+      <c r="N104" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8314,7 +8296,7 @@
           <t>PS5-28-16</t>
         </is>
       </c>
-      <c r="B105" s="83" t="inlineStr">
+      <c r="B105" s="79" t="inlineStr">
         <is>
           <t>PS5-28-16 - LP Relief Header</t>
         </is>
@@ -8325,7 +8307,7 @@
       <c r="D105" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E105" s="95" t="inlineStr">
+      <c r="E105" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8366,7 +8348,7 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N105" s="69" t="inlineStr">
+      <c r="N105" s="68" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -8383,7 +8365,7 @@
           <t>PS5-28-17</t>
         </is>
       </c>
-      <c r="B106" s="83" t="inlineStr">
+      <c r="B106" s="79" t="inlineStr">
         <is>
           <t>PS5-28-17 - Reinjection Pump</t>
         </is>
@@ -8394,7 +8376,7 @@
       <c r="D106" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E106" s="70" t="inlineStr">
+      <c r="E106" s="69" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -8405,7 +8387,7 @@
       <c r="G106" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H106" s="69" t="inlineStr">
+      <c r="H106" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -8435,7 +8417,7 @@
           <t>24/24</t>
         </is>
       </c>
-      <c r="N106" s="69" t="inlineStr">
+      <c r="N106" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -8452,7 +8434,7 @@
           <t>PS5-50-01</t>
         </is>
       </c>
-      <c r="B107" s="83" t="inlineStr">
+      <c r="B107" s="79" t="inlineStr">
         <is>
           <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
@@ -8463,7 +8445,7 @@
       <c r="D107" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E107" s="95" t="inlineStr">
+      <c r="E107" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8474,7 +8456,7 @@
       <c r="G107" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H107" s="70" t="inlineStr">
+      <c r="H107" s="69" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8504,7 +8486,7 @@
           <t>9/13</t>
         </is>
       </c>
-      <c r="N107" s="70" t="inlineStr">
+      <c r="N107" s="69" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8521,7 +8503,7 @@
           <t>PS5-50-02</t>
         </is>
       </c>
-      <c r="B108" s="83" t="inlineStr">
+      <c r="B108" s="79" t="inlineStr">
         <is>
           <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
@@ -8532,7 +8514,7 @@
       <c r="D108" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E108" s="95" t="inlineStr">
+      <c r="E108" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8543,7 +8525,7 @@
       <c r="G108" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H108" s="70" t="inlineStr">
+      <c r="H108" s="69" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -8573,7 +8555,7 @@
           <t>10/13</t>
         </is>
       </c>
-      <c r="N108" s="70" t="inlineStr">
+      <c r="N108" s="69" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -8590,7 +8572,7 @@
           <t>PS5-50-03</t>
         </is>
       </c>
-      <c r="B109" s="83" t="inlineStr">
+      <c r="B109" s="79" t="inlineStr">
         <is>
           <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
@@ -8601,7 +8583,7 @@
       <c r="D109" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="70" t="inlineStr">
+      <c r="E109" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8612,7 +8594,7 @@
       <c r="G109" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H109" s="69" t="inlineStr">
+      <c r="H109" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8642,7 +8624,7 @@
           <t>10/15</t>
         </is>
       </c>
-      <c r="N109" s="70" t="inlineStr">
+      <c r="N109" s="69" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8659,7 +8641,7 @@
           <t>PS5-53-01</t>
         </is>
       </c>
-      <c r="B110" s="83" t="inlineStr">
+      <c r="B110" s="79" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -8670,7 +8652,7 @@
       <c r="D110" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E110" s="69" t="inlineStr">
+      <c r="E110" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -8681,7 +8663,7 @@
       <c r="G110" s="23" t="n">
         <v>42</v>
       </c>
-      <c r="H110" s="69" t="inlineStr">
+      <c r="H110" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -8711,12 +8693,12 @@
           <t>27/30</t>
         </is>
       </c>
-      <c r="N110" s="69" t="inlineStr">
+      <c r="N110" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="O110" s="69" t="inlineStr">
+      <c r="O110" s="68" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -8728,7 +8710,7 @@
           <t>PS5-53-02</t>
         </is>
       </c>
-      <c r="B111" s="83" t="inlineStr">
+      <c r="B111" s="79" t="inlineStr">
         <is>
           <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
@@ -8739,7 +8721,7 @@
       <c r="D111" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="70" t="inlineStr">
+      <c r="E111" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8750,7 +8732,7 @@
       <c r="G111" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H111" s="69" t="inlineStr">
+      <c r="H111" s="68" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
@@ -8780,7 +8762,7 @@
           <t>8/8</t>
         </is>
       </c>
-      <c r="N111" s="69" t="inlineStr">
+      <c r="N111" s="68" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -8797,7 +8779,7 @@
           <t>PS5-53-03</t>
         </is>
       </c>
-      <c r="B112" s="83" t="inlineStr">
+      <c r="B112" s="79" t="inlineStr">
         <is>
           <t>PS5-53-03 - Water Softener Package</t>
         </is>
@@ -8808,7 +8790,7 @@
       <c r="D112" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E112" s="95" t="inlineStr">
+      <c r="E112" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8819,7 +8801,7 @@
       <c r="G112" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H112" s="69" t="inlineStr">
+      <c r="H112" s="68" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8849,7 +8831,7 @@
           <t>11/14</t>
         </is>
       </c>
-      <c r="N112" s="69" t="inlineStr">
+      <c r="N112" s="68" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8866,7 +8848,7 @@
           <t>PS5-53-04</t>
         </is>
       </c>
-      <c r="B113" s="83" t="inlineStr">
+      <c r="B113" s="79" t="inlineStr">
         <is>
           <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
@@ -8877,7 +8859,7 @@
       <c r="D113" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="95" t="inlineStr">
+      <c r="E113" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8888,7 +8870,7 @@
       <c r="G113" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="70" t="inlineStr">
+      <c r="H113" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8918,7 +8900,7 @@
           <t>0/1</t>
         </is>
       </c>
-      <c r="N113" s="70" t="inlineStr">
+      <c r="N113" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8935,7 +8917,7 @@
           <t>PS5-53-05</t>
         </is>
       </c>
-      <c r="B114" s="83" t="inlineStr">
+      <c r="B114" s="79" t="inlineStr">
         <is>
           <t>PS5-53-05 - Water Distribution Header</t>
         </is>
@@ -8946,7 +8928,7 @@
       <c r="D114" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E114" s="95" t="inlineStr">
+      <c r="E114" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9004,7 +8986,7 @@
           <t>PS5-53-06</t>
         </is>
       </c>
-      <c r="B115" s="83" t="inlineStr">
+      <c r="B115" s="79" t="inlineStr">
         <is>
           <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
@@ -9015,7 +8997,7 @@
       <c r="D115" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E115" s="95" t="inlineStr">
+      <c r="E115" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9026,7 +9008,7 @@
       <c r="G115" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H115" s="69" t="inlineStr">
+      <c r="H115" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -9056,7 +9038,7 @@
           <t>33/39</t>
         </is>
       </c>
-      <c r="N115" s="69" t="inlineStr">
+      <c r="N115" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -9073,7 +9055,7 @@
           <t>PS5-60-01</t>
         </is>
       </c>
-      <c r="B116" s="83" t="inlineStr">
+      <c r="B116" s="79" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -9084,7 +9066,7 @@
       <c r="D116" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="E116" s="70" t="inlineStr">
+      <c r="E116" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -9142,7 +9124,7 @@
           <t>PS5-60-02</t>
         </is>
       </c>
-      <c r="B117" s="83" t="inlineStr">
+      <c r="B117" s="79" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -9153,7 +9135,7 @@
       <c r="D117" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E117" s="70" t="inlineStr">
+      <c r="E117" s="69" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -9211,7 +9193,7 @@
           <t>PS5-60-03</t>
         </is>
       </c>
-      <c r="B118" s="83" t="inlineStr">
+      <c r="B118" s="79" t="inlineStr">
         <is>
           <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9222,7 +9204,7 @@
       <c r="D118" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E118" s="70" t="inlineStr">
+      <c r="E118" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -9233,7 +9215,7 @@
       <c r="G118" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H118" s="69" t="inlineStr">
+      <c r="H118" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9263,7 +9245,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N118" s="69" t="inlineStr">
+      <c r="N118" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9280,7 +9262,7 @@
           <t>PS5-60-04</t>
         </is>
       </c>
-      <c r="B119" s="83" t="inlineStr">
+      <c r="B119" s="79" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -9291,7 +9273,7 @@
       <c r="D119" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E119" s="70" t="inlineStr">
+      <c r="E119" s="69" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -9349,7 +9331,7 @@
           <t>PS5-60-05</t>
         </is>
       </c>
-      <c r="B120" s="83" t="inlineStr">
+      <c r="B120" s="79" t="inlineStr">
         <is>
           <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
@@ -9360,7 +9342,7 @@
       <c r="D120" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E120" s="70" t="inlineStr">
+      <c r="E120" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9418,7 +9400,7 @@
           <t>PS5-60-06</t>
         </is>
       </c>
-      <c r="B121" s="83" t="inlineStr">
+      <c r="B121" s="79" t="inlineStr">
         <is>
           <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9429,7 +9411,7 @@
       <c r="D121" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="70" t="inlineStr">
+      <c r="E121" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9440,7 +9422,7 @@
       <c r="G121" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H121" s="69" t="inlineStr">
+      <c r="H121" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9470,7 +9452,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N121" s="69" t="inlineStr">
+      <c r="N121" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9487,7 +9469,7 @@
           <t>PS5-60-07</t>
         </is>
       </c>
-      <c r="B122" s="83" t="inlineStr">
+      <c r="B122" s="79" t="inlineStr">
         <is>
           <t>PS5-60-07 - Power Generation Package C</t>
         </is>
@@ -9498,7 +9480,7 @@
       <c r="D122" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E122" s="70" t="inlineStr">
+      <c r="E122" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -9556,7 +9538,7 @@
           <t>PS5-60-08</t>
         </is>
       </c>
-      <c r="B123" s="83" t="inlineStr">
+      <c r="B123" s="79" t="inlineStr">
         <is>
           <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
@@ -9567,7 +9549,7 @@
       <c r="D123" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E123" s="70" t="inlineStr">
+      <c r="E123" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9625,7 +9607,7 @@
           <t>PS5-60-09</t>
         </is>
       </c>
-      <c r="B124" s="83" t="inlineStr">
+      <c r="B124" s="79" t="inlineStr">
         <is>
           <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9636,7 +9618,7 @@
       <c r="D124" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E124" s="95" t="inlineStr">
+      <c r="E124" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9647,7 +9629,7 @@
       <c r="G124" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H124" s="69" t="inlineStr">
+      <c r="H124" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9677,7 +9659,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N124" s="69" t="inlineStr">
+      <c r="N124" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9694,7 +9676,7 @@
           <t>PS5-60-10</t>
         </is>
       </c>
-      <c r="B125" s="83" t="inlineStr">
+      <c r="B125" s="79" t="inlineStr">
         <is>
           <t>PS5-60-10 - Power Generation Package D</t>
         </is>
@@ -9705,7 +9687,7 @@
       <c r="D125" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E125" s="70" t="inlineStr">
+      <c r="E125" s="69" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -9763,7 +9745,7 @@
           <t>PS5-60-11</t>
         </is>
       </c>
-      <c r="B126" s="83" t="inlineStr">
+      <c r="B126" s="79" t="inlineStr">
         <is>
           <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
@@ -9774,7 +9756,7 @@
       <c r="D126" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E126" s="95" t="inlineStr">
+      <c r="E126" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9832,7 +9814,7 @@
           <t>PS5-60-12</t>
         </is>
       </c>
-      <c r="B127" s="83" t="inlineStr">
+      <c r="B127" s="79" t="inlineStr">
         <is>
           <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9843,7 +9825,7 @@
       <c r="D127" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E127" s="95" t="inlineStr">
+      <c r="E127" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9854,7 +9836,7 @@
       <c r="G127" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H127" s="69" t="inlineStr">
+      <c r="H127" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9884,7 +9866,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N127" s="69" t="inlineStr">
+      <c r="N127" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9901,7 +9883,7 @@
           <t>PS5-60-13</t>
         </is>
       </c>
-      <c r="B128" s="83" t="inlineStr">
+      <c r="B128" s="79" t="inlineStr">
         <is>
           <t>PS5-60-13 - Power Generation Package E</t>
         </is>
@@ -9912,7 +9894,7 @@
       <c r="D128" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="E128" s="70" t="inlineStr">
+      <c r="E128" s="69" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -9970,7 +9952,7 @@
           <t>PS5-60-14</t>
         </is>
       </c>
-      <c r="B129" s="83" t="inlineStr">
+      <c r="B129" s="79" t="inlineStr">
         <is>
           <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
@@ -9981,7 +9963,7 @@
       <c r="D129" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E129" s="95" t="inlineStr">
+      <c r="E129" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10039,7 +10021,7 @@
           <t>PS5-60-15</t>
         </is>
       </c>
-      <c r="B130" s="83" t="inlineStr">
+      <c r="B130" s="79" t="inlineStr">
         <is>
           <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10050,7 +10032,7 @@
       <c r="D130" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E130" s="95" t="inlineStr">
+      <c r="E130" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10061,7 +10043,7 @@
       <c r="G130" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H130" s="69" t="inlineStr">
+      <c r="H130" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10091,7 +10073,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N130" s="69" t="inlineStr">
+      <c r="N130" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10108,7 +10090,7 @@
           <t>PS5-60-16</t>
         </is>
       </c>
-      <c r="B131" s="83" t="inlineStr">
+      <c r="B131" s="79" t="inlineStr">
         <is>
           <t>PS5-60-16 - Power Generation Package F</t>
         </is>
@@ -10119,7 +10101,7 @@
       <c r="D131" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E131" s="70" t="inlineStr">
+      <c r="E131" s="69" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -10177,7 +10159,7 @@
           <t>PS5-60-17</t>
         </is>
       </c>
-      <c r="B132" s="83" t="inlineStr">
+      <c r="B132" s="79" t="inlineStr">
         <is>
           <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
@@ -10188,7 +10170,7 @@
       <c r="D132" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E132" s="95" t="inlineStr">
+      <c r="E132" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10229,7 +10211,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N132" s="69" t="inlineStr">
+      <c r="N132" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10246,7 +10228,7 @@
           <t>PS5-60-18</t>
         </is>
       </c>
-      <c r="B133" s="83" t="inlineStr">
+      <c r="B133" s="79" t="inlineStr">
         <is>
           <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10257,7 +10239,7 @@
       <c r="D133" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E133" s="95" t="inlineStr">
+      <c r="E133" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10268,7 +10250,7 @@
       <c r="G133" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H133" s="69" t="inlineStr">
+      <c r="H133" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -10298,7 +10280,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N133" s="69" t="inlineStr">
+      <c r="N133" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -10315,7 +10297,7 @@
           <t>PS5-60-19</t>
         </is>
       </c>
-      <c r="B134" s="83" t="inlineStr">
+      <c r="B134" s="79" t="inlineStr">
         <is>
           <t>PS5-60-19 - Power Generation Package G</t>
         </is>
@@ -10326,7 +10308,7 @@
       <c r="D134" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E134" s="70" t="inlineStr">
+      <c r="E134" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -10384,7 +10366,7 @@
           <t>PS5-60-20</t>
         </is>
       </c>
-      <c r="B135" s="83" t="inlineStr">
+      <c r="B135" s="79" t="inlineStr">
         <is>
           <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
@@ -10395,7 +10377,7 @@
       <c r="D135" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E135" s="95" t="inlineStr">
+      <c r="E135" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10406,7 +10388,7 @@
       <c r="G135" s="23" t="n">
         <v>37</v>
       </c>
-      <c r="H135" s="69" t="inlineStr">
+      <c r="H135" s="68" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -10436,7 +10418,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N135" s="69" t="inlineStr">
+      <c r="N135" s="68" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -10453,7 +10435,7 @@
           <t>PS5-60-21</t>
         </is>
       </c>
-      <c r="B136" s="83" t="inlineStr">
+      <c r="B136" s="79" t="inlineStr">
         <is>
           <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10464,7 +10446,7 @@
       <c r="D136" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E136" s="95" t="inlineStr">
+      <c r="E136" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10505,7 +10487,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N136" s="69" t="inlineStr">
+      <c r="N136" s="68" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -10522,7 +10504,7 @@
           <t>PS5-60-22</t>
         </is>
       </c>
-      <c r="B137" s="83" t="inlineStr">
+      <c r="B137" s="79" t="inlineStr">
         <is>
           <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
@@ -10533,7 +10515,7 @@
       <c r="D137" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E137" s="70" t="inlineStr">
+      <c r="E137" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10544,7 +10526,7 @@
       <c r="G137" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="H137" s="69" t="inlineStr">
+      <c r="H137" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -10574,7 +10556,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N137" s="69" t="inlineStr">
+      <c r="N137" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -10591,7 +10573,7 @@
           <t>PS5-60-23</t>
         </is>
       </c>
-      <c r="B138" s="83" t="inlineStr">
+      <c r="B138" s="79" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -10602,7 +10584,7 @@
       <c r="D138" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E138" s="70" t="inlineStr">
+      <c r="E138" s="69" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -10660,7 +10642,7 @@
           <t>PS5-60-24</t>
         </is>
       </c>
-      <c r="B139" s="83" t="inlineStr">
+      <c r="B139" s="79" t="inlineStr">
         <is>
           <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
@@ -10671,7 +10653,7 @@
       <c r="D139" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E139" s="70" t="inlineStr">
+      <c r="E139" s="69" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -10729,7 +10711,7 @@
           <t>PS5-60-25</t>
         </is>
       </c>
-      <c r="B140" s="83" t="inlineStr">
+      <c r="B140" s="79" t="inlineStr">
         <is>
           <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
@@ -10740,7 +10722,7 @@
       <c r="D140" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E140" s="70" t="inlineStr">
+      <c r="E140" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -10798,7 +10780,7 @@
           <t>PS5-60-26</t>
         </is>
       </c>
-      <c r="B141" s="83" t="inlineStr">
+      <c r="B141" s="79" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -10809,7 +10791,7 @@
       <c r="D141" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E141" s="70" t="inlineStr">
+      <c r="E141" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -10867,7 +10849,7 @@
           <t>PS5-60-27</t>
         </is>
       </c>
-      <c r="B142" s="83" t="inlineStr">
+      <c r="B142" s="79" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -10878,7 +10860,7 @@
       <c r="D142" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E142" s="70" t="inlineStr">
+      <c r="E142" s="69" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -10936,7 +10918,7 @@
           <t>PS5-60-28</t>
         </is>
       </c>
-      <c r="B143" s="83" t="inlineStr">
+      <c r="B143" s="79" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -10947,7 +10929,7 @@
       <c r="D143" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E143" s="70" t="inlineStr">
+      <c r="E143" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -10993,9 +10975,9 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O143" s="69" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="O143" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11005,7 +10987,7 @@
           <t>PS5-60-29</t>
         </is>
       </c>
-      <c r="B144" s="83" t="inlineStr">
+      <c r="B144" s="79" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -11016,7 +10998,7 @@
       <c r="D144" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E144" s="70" t="inlineStr">
+      <c r="E144" s="69" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -11074,7 +11056,7 @@
           <t>PS5-60-30</t>
         </is>
       </c>
-      <c r="B145" s="83" t="inlineStr">
+      <c r="B145" s="79" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -11085,7 +11067,7 @@
       <c r="D145" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E145" s="70" t="inlineStr">
+      <c r="E145" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -11143,7 +11125,7 @@
           <t>PS5-60-31</t>
         </is>
       </c>
-      <c r="B146" s="83" t="inlineStr">
+      <c r="B146" s="79" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -11154,7 +11136,7 @@
       <c r="D146" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E146" s="70" t="inlineStr">
+      <c r="E146" s="69" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -11212,7 +11194,7 @@
           <t>PS5-60-32</t>
         </is>
       </c>
-      <c r="B147" s="83" t="inlineStr">
+      <c r="B147" s="79" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -11223,7 +11205,7 @@
       <c r="D147" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E147" s="69" t="inlineStr">
+      <c r="E147" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11281,7 +11263,7 @@
           <t>PS5-60-33</t>
         </is>
       </c>
-      <c r="B148" s="83" t="inlineStr">
+      <c r="B148" s="79" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -11292,7 +11274,7 @@
       <c r="D148" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E148" s="69" t="inlineStr">
+      <c r="E148" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11350,7 +11332,7 @@
           <t>PS5-60-34</t>
         </is>
       </c>
-      <c r="B149" s="83" t="inlineStr">
+      <c r="B149" s="79" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -11361,7 +11343,7 @@
       <c r="D149" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E149" s="70" t="inlineStr">
+      <c r="E149" s="69" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -11419,7 +11401,7 @@
           <t>PS5-60-35</t>
         </is>
       </c>
-      <c r="B150" s="83" t="inlineStr">
+      <c r="B150" s="79" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -11430,7 +11412,7 @@
       <c r="D150" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E150" s="70" t="inlineStr">
+      <c r="E150" s="69" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -11476,9 +11458,9 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O150" s="54" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
+      <c r="O150" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11488,7 +11470,7 @@
           <t>PS5-60-36</t>
         </is>
       </c>
-      <c r="B151" s="83" t="inlineStr">
+      <c r="B151" s="79" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -11499,7 +11481,7 @@
       <c r="D151" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E151" s="70" t="inlineStr">
+      <c r="E151" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -11557,7 +11539,7 @@
           <t>PS5-60-37</t>
         </is>
       </c>
-      <c r="B152" s="83" t="inlineStr">
+      <c r="B152" s="79" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -11568,7 +11550,7 @@
       <c r="D152" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E152" s="70" t="inlineStr">
+      <c r="E152" s="69" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -11626,7 +11608,7 @@
           <t>PS5-60-38</t>
         </is>
       </c>
-      <c r="B153" s="83" t="inlineStr">
+      <c r="B153" s="79" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -11637,7 +11619,7 @@
       <c r="D153" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E153" s="69" t="inlineStr">
+      <c r="E153" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11695,7 +11677,7 @@
           <t>PS5-60-39</t>
         </is>
       </c>
-      <c r="B154" s="83" t="inlineStr">
+      <c r="B154" s="79" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -11706,7 +11688,7 @@
       <c r="D154" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E154" s="69" t="inlineStr">
+      <c r="E154" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11764,7 +11746,7 @@
           <t>PS5-60-40</t>
         </is>
       </c>
-      <c r="B155" s="83" t="inlineStr">
+      <c r="B155" s="79" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -11775,7 +11757,7 @@
       <c r="D155" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E155" s="69" t="inlineStr">
+      <c r="E155" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -11833,7 +11815,7 @@
           <t>PS5-60-41</t>
         </is>
       </c>
-      <c r="B156" s="83" t="inlineStr">
+      <c r="B156" s="79" t="inlineStr">
         <is>
           <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
@@ -11844,7 +11826,7 @@
       <c r="D156" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E156" s="69" t="inlineStr">
+      <c r="E156" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -11855,7 +11837,7 @@
       <c r="G156" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="H156" s="69" t="inlineStr">
+      <c r="H156" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -11885,7 +11867,7 @@
           <t>16/17</t>
         </is>
       </c>
-      <c r="N156" s="69" t="inlineStr">
+      <c r="N156" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -11902,7 +11884,7 @@
           <t>PS5-60-42</t>
         </is>
       </c>
-      <c r="B157" s="83" t="inlineStr">
+      <c r="B157" s="79" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -11913,7 +11895,7 @@
       <c r="D157" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E157" s="70" t="inlineStr">
+      <c r="E157" s="69" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -11959,9 +11941,9 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O157" s="54" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
+      <c r="O157" s="27" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -11971,7 +11953,7 @@
           <t>PS5-60-43</t>
         </is>
       </c>
-      <c r="B158" s="83" t="inlineStr">
+      <c r="B158" s="79" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -11982,7 +11964,7 @@
       <c r="D158" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E158" s="70" t="inlineStr">
+      <c r="E158" s="69" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -12040,7 +12022,7 @@
           <t>PS5-60-44</t>
         </is>
       </c>
-      <c r="B159" s="83" t="inlineStr">
+      <c r="B159" s="79" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -12051,7 +12033,7 @@
       <c r="D159" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E159" s="70" t="inlineStr">
+      <c r="E159" s="69" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -12109,7 +12091,7 @@
           <t>PS5-60-45</t>
         </is>
       </c>
-      <c r="B160" s="83" t="inlineStr">
+      <c r="B160" s="79" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -12120,7 +12102,7 @@
       <c r="D160" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E160" s="70" t="inlineStr">
+      <c r="E160" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -12178,7 +12160,7 @@
           <t>PS5-60-46</t>
         </is>
       </c>
-      <c r="B161" s="83" t="inlineStr">
+      <c r="B161" s="79" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -12189,7 +12171,7 @@
       <c r="D161" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E161" s="69" t="inlineStr">
+      <c r="E161" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -12247,7 +12229,7 @@
           <t>PS5-60-47</t>
         </is>
       </c>
-      <c r="B162" s="83" t="inlineStr">
+      <c r="B162" s="79" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -12258,7 +12240,7 @@
       <c r="D162" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E162" s="69" t="inlineStr">
+      <c r="E162" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -12316,7 +12298,7 @@
           <t>PS5-60-48</t>
         </is>
       </c>
-      <c r="B163" s="83" t="inlineStr">
+      <c r="B163" s="79" t="inlineStr">
         <is>
           <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
@@ -12327,7 +12309,7 @@
       <c r="D163" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E163" s="70" t="inlineStr">
+      <c r="E163" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -12385,7 +12367,7 @@
           <t>PS5-60-49</t>
         </is>
       </c>
-      <c r="B164" s="83" t="inlineStr">
+      <c r="B164" s="79" t="inlineStr">
         <is>
           <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
@@ -12396,7 +12378,7 @@
       <c r="D164" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E164" s="70" t="inlineStr">
+      <c r="E164" s="69" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -12454,7 +12436,7 @@
           <t>PS5-60-50</t>
         </is>
       </c>
-      <c r="B165" s="83" t="inlineStr">
+      <c r="B165" s="79" t="inlineStr">
         <is>
           <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
@@ -12465,7 +12447,7 @@
       <c r="D165" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E165" s="70" t="inlineStr">
+      <c r="E165" s="69" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -12523,7 +12505,7 @@
           <t>PS5-60-51</t>
         </is>
       </c>
-      <c r="B166" s="83" t="inlineStr">
+      <c r="B166" s="79" t="inlineStr">
         <is>
           <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
@@ -12534,7 +12516,7 @@
       <c r="D166" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E166" s="69" t="inlineStr">
+      <c r="E166" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -12592,7 +12574,7 @@
           <t>PS5-60-52</t>
         </is>
       </c>
-      <c r="B167" s="83" t="inlineStr">
+      <c r="B167" s="79" t="inlineStr">
         <is>
           <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
@@ -12603,7 +12585,7 @@
       <c r="D167" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E167" s="70" t="inlineStr">
+      <c r="E167" s="69" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -12614,7 +12596,7 @@
       <c r="G167" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="H167" s="69" t="inlineStr">
+      <c r="H167" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -12644,7 +12626,7 @@
           <t>15/15</t>
         </is>
       </c>
-      <c r="N167" s="69" t="inlineStr">
+      <c r="N167" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -12661,7 +12643,7 @@
           <t>PS5-60-53</t>
         </is>
       </c>
-      <c r="B168" s="83" t="inlineStr">
+      <c r="B168" s="79" t="inlineStr">
         <is>
           <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
@@ -12672,7 +12654,7 @@
       <c r="D168" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E168" s="69" t="inlineStr">
+      <c r="E168" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -12730,7 +12712,7 @@
           <t>PS5-60-54</t>
         </is>
       </c>
-      <c r="B169" s="83" t="inlineStr">
+      <c r="B169" s="79" t="inlineStr">
         <is>
           <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
@@ -12741,7 +12723,7 @@
       <c r="D169" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E169" s="69" t="inlineStr">
+      <c r="E169" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -12799,7 +12781,7 @@
           <t>PS5-60-55</t>
         </is>
       </c>
-      <c r="B170" s="83" t="inlineStr">
+      <c r="B170" s="79" t="inlineStr">
         <is>
           <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
@@ -12821,7 +12803,7 @@
       <c r="G170" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="H170" s="69" t="inlineStr">
+      <c r="H170" s="68" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -12851,7 +12833,7 @@
           <t>14/15</t>
         </is>
       </c>
-      <c r="N170" s="69" t="inlineStr">
+      <c r="N170" s="68" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -12868,7 +12850,7 @@
           <t>PS5-60-56</t>
         </is>
       </c>
-      <c r="B171" s="83" t="inlineStr">
+      <c r="B171" s="79" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -12879,7 +12861,7 @@
       <c r="D171" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E171" s="70" t="inlineStr">
+      <c r="E171" s="69" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -12937,7 +12919,7 @@
           <t>PS5-60-57</t>
         </is>
       </c>
-      <c r="B172" s="83" t="inlineStr">
+      <c r="B172" s="79" t="inlineStr">
         <is>
           <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
@@ -12948,7 +12930,7 @@
       <c r="D172" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E172" s="70" t="inlineStr">
+      <c r="E172" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13006,7 +12988,7 @@
           <t>PS5-60-58</t>
         </is>
       </c>
-      <c r="B173" s="83" t="inlineStr">
+      <c r="B173" s="79" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -13017,7 +12999,7 @@
       <c r="D173" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E173" s="70" t="inlineStr">
+      <c r="E173" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -13075,7 +13057,7 @@
           <t>PS5-60-59</t>
         </is>
       </c>
-      <c r="B174" s="83" t="inlineStr">
+      <c r="B174" s="79" t="inlineStr">
         <is>
           <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
@@ -13086,7 +13068,7 @@
       <c r="D174" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E174" s="70" t="inlineStr">
+      <c r="E174" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13144,7 +13126,7 @@
           <t>PS5-60-60</t>
         </is>
       </c>
-      <c r="B175" s="83" t="inlineStr">
+      <c r="B175" s="79" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -13155,7 +13137,7 @@
       <c r="D175" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E175" s="70" t="inlineStr">
+      <c r="E175" s="69" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -13213,7 +13195,7 @@
           <t>PS5-60-61</t>
         </is>
       </c>
-      <c r="B176" s="83" t="inlineStr">
+      <c r="B176" s="79" t="inlineStr">
         <is>
           <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
@@ -13224,7 +13206,7 @@
       <c r="D176" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E176" s="95" t="inlineStr">
+      <c r="E176" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13282,7 +13264,7 @@
           <t>PS5-60-62</t>
         </is>
       </c>
-      <c r="B177" s="83" t="inlineStr">
+      <c r="B177" s="79" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -13293,7 +13275,7 @@
       <c r="D177" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E177" s="70" t="inlineStr">
+      <c r="E177" s="69" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -13351,7 +13333,7 @@
           <t>PS5-60-63</t>
         </is>
       </c>
-      <c r="B178" s="83" t="inlineStr">
+      <c r="B178" s="79" t="inlineStr">
         <is>
           <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
@@ -13362,7 +13344,7 @@
       <c r="D178" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E178" s="95" t="inlineStr">
+      <c r="E178" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13420,7 +13402,7 @@
           <t>PS5-60-64</t>
         </is>
       </c>
-      <c r="B179" s="83" t="inlineStr">
+      <c r="B179" s="79" t="inlineStr">
         <is>
           <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
@@ -13431,7 +13413,7 @@
       <c r="D179" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E179" s="69" t="inlineStr">
+      <c r="E179" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -13489,7 +13471,7 @@
           <t>PS5-60-65</t>
         </is>
       </c>
-      <c r="B180" s="83" t="inlineStr">
+      <c r="B180" s="79" t="inlineStr">
         <is>
           <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
@@ -13500,7 +13482,7 @@
       <c r="D180" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E180" s="95" t="inlineStr">
+      <c r="E180" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13541,7 +13523,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N180" s="69" t="inlineStr">
+      <c r="N180" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13558,7 +13540,7 @@
           <t>PS5-60-66</t>
         </is>
       </c>
-      <c r="B181" s="83" t="inlineStr">
+      <c r="B181" s="79" t="inlineStr">
         <is>
           <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
@@ -13569,7 +13551,7 @@
       <c r="D181" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E181" s="70" t="inlineStr">
+      <c r="E181" s="69" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -13627,7 +13609,7 @@
           <t>PS5-60-67</t>
         </is>
       </c>
-      <c r="B182" s="83" t="inlineStr">
+      <c r="B182" s="79" t="inlineStr">
         <is>
           <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
@@ -13638,7 +13620,7 @@
       <c r="D182" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E182" s="95" t="inlineStr">
+      <c r="E182" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13679,7 +13661,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N182" s="69" t="inlineStr">
+      <c r="N182" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13696,7 +13678,7 @@
           <t>PS5-60-68</t>
         </is>
       </c>
-      <c r="B183" s="83" t="inlineStr">
+      <c r="B183" s="79" t="inlineStr">
         <is>
           <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
@@ -13707,7 +13689,7 @@
       <c r="D183" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E183" s="70" t="inlineStr">
+      <c r="E183" s="69" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -13718,7 +13700,7 @@
       <c r="G183" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H183" s="69" t="inlineStr">
+      <c r="H183" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13748,7 +13730,7 @@
           <t>16/17</t>
         </is>
       </c>
-      <c r="N183" s="69" t="inlineStr">
+      <c r="N183" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13765,7 +13747,7 @@
           <t>PS5-60-69</t>
         </is>
       </c>
-      <c r="B184" s="83" t="inlineStr">
+      <c r="B184" s="79" t="inlineStr">
         <is>
           <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
@@ -13776,7 +13758,7 @@
       <c r="D184" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E184" s="95" t="inlineStr">
+      <c r="E184" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13787,7 +13769,7 @@
       <c r="G184" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="H184" s="69" t="inlineStr">
+      <c r="H184" s="68" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -13817,7 +13799,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N184" s="69" t="inlineStr">
+      <c r="N184" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -13834,7 +13816,7 @@
           <t>PS5-60-70</t>
         </is>
       </c>
-      <c r="B185" s="83" t="inlineStr">
+      <c r="B185" s="79" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -13845,7 +13827,7 @@
       <c r="D185" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="E185" s="70" t="inlineStr">
+      <c r="E185" s="69" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -13903,7 +13885,7 @@
           <t>PS5-60-71</t>
         </is>
       </c>
-      <c r="B186" s="83" t="inlineStr">
+      <c r="B186" s="79" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -13914,7 +13896,7 @@
       <c r="D186" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="E186" s="70" t="inlineStr">
+      <c r="E186" s="69" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
@@ -13972,7 +13954,7 @@
           <t>PS5-60-72</t>
         </is>
       </c>
-      <c r="B187" s="83" t="inlineStr">
+      <c r="B187" s="79" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -13983,7 +13965,7 @@
       <c r="D187" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="E187" s="70" t="inlineStr">
+      <c r="E187" s="69" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
@@ -14041,7 +14023,7 @@
           <t>PS5-60-73</t>
         </is>
       </c>
-      <c r="B188" s="83" t="inlineStr">
+      <c r="B188" s="79" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -14052,7 +14034,7 @@
       <c r="D188" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E188" s="70" t="inlineStr">
+      <c r="E188" s="69" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -14110,7 +14092,7 @@
           <t>PS5-60-74</t>
         </is>
       </c>
-      <c r="B189" s="83" t="inlineStr">
+      <c r="B189" s="79" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -14121,7 +14103,7 @@
       <c r="D189" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E189" s="70" t="inlineStr">
+      <c r="E189" s="69" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -14179,7 +14161,7 @@
           <t>PS5-60-75</t>
         </is>
       </c>
-      <c r="B190" s="83" t="inlineStr">
+      <c r="B190" s="79" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -14190,7 +14172,7 @@
       <c r="D190" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E190" s="70" t="inlineStr">
+      <c r="E190" s="69" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -14248,7 +14230,7 @@
           <t>PS5-60-76</t>
         </is>
       </c>
-      <c r="B191" s="83" t="inlineStr">
+      <c r="B191" s="79" t="inlineStr">
         <is>
           <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
@@ -14259,7 +14241,7 @@
       <c r="D191" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E191" s="70" t="inlineStr">
+      <c r="E191" s="69" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -14317,7 +14299,7 @@
           <t>PS5-61-01</t>
         </is>
       </c>
-      <c r="B192" s="83" t="inlineStr">
+      <c r="B192" s="79" t="inlineStr">
         <is>
           <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
@@ -14328,7 +14310,7 @@
       <c r="D192" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E192" s="70" t="inlineStr">
+      <c r="E192" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -14386,7 +14368,7 @@
           <t>PS5-61-02</t>
         </is>
       </c>
-      <c r="B193" s="83" t="inlineStr">
+      <c r="B193" s="79" t="inlineStr">
         <is>
           <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
@@ -14397,7 +14379,7 @@
       <c r="D193" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E193" s="70" t="inlineStr">
+      <c r="E193" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14438,7 +14420,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N193" s="69" t="inlineStr">
+      <c r="N193" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -14455,7 +14437,7 @@
           <t>PS5-61-03</t>
         </is>
       </c>
-      <c r="B194" s="83" t="inlineStr">
+      <c r="B194" s="79" t="inlineStr">
         <is>
           <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
@@ -14466,7 +14448,7 @@
       <c r="D194" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E194" s="70" t="inlineStr">
+      <c r="E194" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -14507,7 +14489,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N194" s="69" t="inlineStr">
+      <c r="N194" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -14524,7 +14506,7 @@
           <t>PS5-61-04</t>
         </is>
       </c>
-      <c r="B195" s="83" t="inlineStr">
+      <c r="B195" s="79" t="inlineStr">
         <is>
           <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
@@ -14535,7 +14517,7 @@
       <c r="D195" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E195" s="95" t="inlineStr">
+      <c r="E195" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14546,7 +14528,7 @@
       <c r="G195" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H195" s="70" t="inlineStr">
+      <c r="H195" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14576,7 +14558,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N195" s="70" t="inlineStr">
+      <c r="N195" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14593,7 +14575,7 @@
           <t>PS5-61-05</t>
         </is>
       </c>
-      <c r="B196" s="83" t="inlineStr">
+      <c r="B196" s="79" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -14662,7 +14644,7 @@
           <t>PS5-61-06</t>
         </is>
       </c>
-      <c r="B197" s="83" t="inlineStr">
+      <c r="B197" s="79" t="inlineStr">
         <is>
           <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
@@ -14684,7 +14666,7 @@
       <c r="G197" s="23" t="n">
         <v>63</v>
       </c>
-      <c r="H197" s="69" t="inlineStr">
+      <c r="H197" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -14714,7 +14696,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N197" s="69" t="inlineStr">
+      <c r="N197" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -14731,7 +14713,7 @@
           <t>PS5-61-07</t>
         </is>
       </c>
-      <c r="B198" s="83" t="inlineStr">
+      <c r="B198" s="79" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -14742,7 +14724,7 @@
       <c r="D198" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E198" s="70" t="inlineStr">
+      <c r="E198" s="69" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -14800,7 +14782,7 @@
           <t>PS5-61-08</t>
         </is>
       </c>
-      <c r="B199" s="83" t="inlineStr">
+      <c r="B199" s="79" t="inlineStr">
         <is>
           <t>PS5-61-08 - Electrical Control System</t>
         </is>
@@ -14811,7 +14793,7 @@
       <c r="D199" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E199" s="69" t="inlineStr">
+      <c r="E199" s="68" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -14822,7 +14804,7 @@
       <c r="G199" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H199" s="70" t="inlineStr">
+      <c r="H199" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -14852,7 +14834,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N199" s="70" t="inlineStr">
+      <c r="N199" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -14869,7 +14851,7 @@
           <t>PS5-61-09</t>
         </is>
       </c>
-      <c r="B200" s="83" t="inlineStr">
+      <c r="B200" s="79" t="inlineStr">
         <is>
           <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
@@ -14880,7 +14862,7 @@
       <c r="D200" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E200" s="95" t="inlineStr">
+      <c r="E200" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14891,7 +14873,7 @@
       <c r="G200" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H200" s="70" t="inlineStr">
+      <c r="H200" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -14921,7 +14903,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N200" s="70" t="inlineStr">
+      <c r="N200" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -14938,7 +14920,7 @@
           <t>PS5-61-10</t>
         </is>
       </c>
-      <c r="B201" s="83" t="inlineStr">
+      <c r="B201" s="79" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -14949,7 +14931,7 @@
       <c r="D201" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E201" s="95" t="inlineStr">
+      <c r="E201" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15007,7 +14989,7 @@
           <t>PS5-61-11</t>
         </is>
       </c>
-      <c r="B202" s="83" t="inlineStr">
+      <c r="B202" s="79" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -15018,7 +15000,7 @@
       <c r="D202" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E202" s="95" t="inlineStr">
+      <c r="E202" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15076,7 +15058,7 @@
           <t>PS5-61-12</t>
         </is>
       </c>
-      <c r="B203" s="83" t="inlineStr">
+      <c r="B203" s="79" t="inlineStr">
         <is>
           <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
@@ -15087,7 +15069,7 @@
       <c r="D203" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E203" s="95" t="inlineStr">
+      <c r="E203" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15098,7 +15080,7 @@
       <c r="G203" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H203" s="95" t="inlineStr">
+      <c r="H203" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15128,7 +15110,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N203" s="70" t="inlineStr">
+      <c r="N203" s="69" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -15145,7 +15127,7 @@
           <t>PS5-61-13</t>
         </is>
       </c>
-      <c r="B204" s="83" t="inlineStr">
+      <c r="B204" s="79" t="inlineStr">
         <is>
           <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
@@ -15156,7 +15138,7 @@
       <c r="D204" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E204" s="95" t="inlineStr">
+      <c r="E204" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15167,7 +15149,7 @@
       <c r="G204" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H204" s="70" t="inlineStr">
+      <c r="H204" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15197,7 +15179,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N204" s="70" t="inlineStr">
+      <c r="N204" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15214,7 +15196,7 @@
           <t>PS5-61-14</t>
         </is>
       </c>
-      <c r="B205" s="83" t="inlineStr">
+      <c r="B205" s="79" t="inlineStr">
         <is>
           <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
@@ -15225,7 +15207,7 @@
       <c r="D205" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E205" s="95" t="inlineStr">
+      <c r="E205" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15236,7 +15218,7 @@
       <c r="G205" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H205" s="70" t="inlineStr">
+      <c r="H205" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15266,7 +15248,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N205" s="70" t="inlineStr">
+      <c r="N205" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15283,7 +15265,7 @@
           <t>PS5-62-01</t>
         </is>
       </c>
-      <c r="B206" s="83" t="inlineStr">
+      <c r="B206" s="79" t="inlineStr">
         <is>
           <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
@@ -15305,7 +15287,7 @@
       <c r="G206" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H206" s="70" t="inlineStr">
+      <c r="H206" s="69" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -15335,7 +15317,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N206" s="70" t="inlineStr">
+      <c r="N206" s="69" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -15352,7 +15334,7 @@
           <t>PS5-62-02</t>
         </is>
       </c>
-      <c r="B207" s="83" t="inlineStr">
+      <c r="B207" s="79" t="inlineStr">
         <is>
           <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
@@ -15374,7 +15356,7 @@
       <c r="G207" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H207" s="70" t="inlineStr">
+      <c r="H207" s="69" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -15404,7 +15386,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N207" s="70" t="inlineStr">
+      <c r="N207" s="69" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -15421,7 +15403,7 @@
           <t>PS5-62-03</t>
         </is>
       </c>
-      <c r="B208" s="83" t="inlineStr">
+      <c r="B208" s="79" t="inlineStr">
         <is>
           <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
@@ -15432,7 +15414,7 @@
       <c r="D208" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E208" s="95" t="inlineStr">
+      <c r="E208" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15443,7 +15425,7 @@
       <c r="G208" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H208" s="69" t="inlineStr">
+      <c r="H208" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15473,7 +15455,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N208" s="69" t="inlineStr">
+      <c r="N208" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15490,7 +15472,7 @@
           <t>PS5-62-04</t>
         </is>
       </c>
-      <c r="B209" s="83" t="inlineStr">
+      <c r="B209" s="79" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -15501,7 +15483,7 @@
       <c r="D209" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E209" s="95" t="inlineStr">
+      <c r="E209" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15559,7 +15541,7 @@
           <t>PS5-62-05</t>
         </is>
       </c>
-      <c r="B210" s="83" t="inlineStr">
+      <c r="B210" s="79" t="inlineStr">
         <is>
           <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
@@ -15570,7 +15552,7 @@
       <c r="D210" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E210" s="95" t="inlineStr">
+      <c r="E210" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15581,7 +15563,7 @@
       <c r="G210" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H210" s="70" t="inlineStr">
+      <c r="H210" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15611,7 +15593,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N210" s="70" t="inlineStr">
+      <c r="N210" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15628,7 +15610,7 @@
           <t>PS5-62-06</t>
         </is>
       </c>
-      <c r="B211" s="83" t="inlineStr">
+      <c r="B211" s="79" t="inlineStr">
         <is>
           <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
@@ -15639,7 +15621,7 @@
       <c r="D211" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E211" s="95" t="inlineStr">
+      <c r="E211" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15650,7 +15632,7 @@
       <c r="G211" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H211" s="70" t="inlineStr">
+      <c r="H211" s="69" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -15680,7 +15662,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N211" s="70" t="inlineStr">
+      <c r="N211" s="69" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -15697,7 +15679,7 @@
           <t>PS5-62-07</t>
         </is>
       </c>
-      <c r="B212" s="83" t="inlineStr">
+      <c r="B212" s="79" t="inlineStr">
         <is>
           <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
@@ -15708,7 +15690,7 @@
       <c r="D212" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E212" s="70" t="inlineStr">
+      <c r="E212" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15719,7 +15701,7 @@
       <c r="G212" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H212" s="70" t="inlineStr">
+      <c r="H212" s="69" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -15749,7 +15731,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N212" s="70" t="inlineStr">
+      <c r="N212" s="69" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -15766,7 +15748,7 @@
           <t>PS5-62-08</t>
         </is>
       </c>
-      <c r="B213" s="83" t="inlineStr">
+      <c r="B213" s="79" t="inlineStr">
         <is>
           <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
@@ -15777,7 +15759,7 @@
       <c r="D213" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E213" s="95" t="inlineStr">
+      <c r="E213" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15788,7 +15770,7 @@
       <c r="G213" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H213" s="70" t="inlineStr">
+      <c r="H213" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -15818,7 +15800,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N213" s="70" t="inlineStr">
+      <c r="N213" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -15835,7 +15817,7 @@
           <t>PS5-62-09</t>
         </is>
       </c>
-      <c r="B214" s="83" t="inlineStr">
+      <c r="B214" s="79" t="inlineStr">
         <is>
           <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
@@ -15846,7 +15828,7 @@
       <c r="D214" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E214" s="70" t="inlineStr">
+      <c r="E214" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15857,7 +15839,7 @@
       <c r="G214" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H214" s="70" t="inlineStr">
+      <c r="H214" s="69" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -15887,7 +15869,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N214" s="70" t="inlineStr">
+      <c r="N214" s="69" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -15904,7 +15886,7 @@
           <t>PS5-62-10</t>
         </is>
       </c>
-      <c r="B215" s="83" t="inlineStr">
+      <c r="B215" s="79" t="inlineStr">
         <is>
           <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
@@ -15915,7 +15897,7 @@
       <c r="D215" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E215" s="70" t="inlineStr">
+      <c r="E215" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15926,7 +15908,7 @@
       <c r="G215" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="H215" s="70" t="inlineStr">
+      <c r="H215" s="69" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -15956,7 +15938,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N215" s="70" t="inlineStr">
+      <c r="N215" s="69" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -15973,7 +15955,7 @@
           <t>PS5-62-11</t>
         </is>
       </c>
-      <c r="B216" s="83" t="inlineStr">
+      <c r="B216" s="79" t="inlineStr">
         <is>
           <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
@@ -15984,7 +15966,7 @@
       <c r="D216" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E216" s="95" t="inlineStr">
+      <c r="E216" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15995,7 +15977,7 @@
       <c r="G216" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H216" s="70" t="inlineStr">
+      <c r="H216" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -16025,7 +16007,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N216" s="70" t="inlineStr">
+      <c r="N216" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -16042,7 +16024,7 @@
           <t>PS5-62-12</t>
         </is>
       </c>
-      <c r="B217" s="83" t="inlineStr">
+      <c r="B217" s="79" t="inlineStr">
         <is>
           <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
@@ -16053,7 +16035,7 @@
       <c r="D217" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E217" s="95" t="inlineStr">
+      <c r="E217" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16064,7 +16046,7 @@
       <c r="G217" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H217" s="95" t="inlineStr">
+      <c r="H217" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16111,7 +16093,7 @@
           <t>PS5-62-13</t>
         </is>
       </c>
-      <c r="B218" s="83" t="inlineStr">
+      <c r="B218" s="79" t="inlineStr">
         <is>
           <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
@@ -16122,7 +16104,7 @@
       <c r="D218" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E218" s="70" t="inlineStr">
+      <c r="E218" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16133,7 +16115,7 @@
       <c r="G218" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H218" s="95" t="inlineStr">
+      <c r="H218" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16180,7 +16162,7 @@
           <t>PS5-62-14</t>
         </is>
       </c>
-      <c r="B219" s="83" t="inlineStr">
+      <c r="B219" s="79" t="inlineStr">
         <is>
           <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
@@ -16191,7 +16173,7 @@
       <c r="D219" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E219" s="95" t="inlineStr">
+      <c r="E219" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16202,7 +16184,7 @@
       <c r="G219" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H219" s="70" t="inlineStr">
+      <c r="H219" s="69" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16232,7 +16214,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N219" s="70" t="inlineStr">
+      <c r="N219" s="69" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16249,7 +16231,7 @@
           <t>PS5-62-15</t>
         </is>
       </c>
-      <c r="B220" s="83" t="inlineStr">
+      <c r="B220" s="79" t="inlineStr">
         <is>
           <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
@@ -16260,7 +16242,7 @@
       <c r="D220" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E220" s="95" t="inlineStr">
+      <c r="E220" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16271,7 +16253,7 @@
       <c r="G220" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H220" s="70" t="inlineStr">
+      <c r="H220" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16301,7 +16283,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N220" s="70" t="inlineStr">
+      <c r="N220" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16318,7 +16300,7 @@
           <t>PS5-62-16</t>
         </is>
       </c>
-      <c r="B221" s="83" t="inlineStr">
+      <c r="B221" s="79" t="inlineStr">
         <is>
           <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
@@ -16329,7 +16311,7 @@
       <c r="D221" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E221" s="95" t="inlineStr">
+      <c r="E221" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16340,7 +16322,7 @@
       <c r="G221" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H221" s="70" t="inlineStr">
+      <c r="H221" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16370,7 +16352,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N221" s="70" t="inlineStr">
+      <c r="N221" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16387,7 +16369,7 @@
           <t>PS5-62-17</t>
         </is>
       </c>
-      <c r="B222" s="83" t="inlineStr">
+      <c r="B222" s="79" t="inlineStr">
         <is>
           <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
@@ -16398,7 +16380,7 @@
       <c r="D222" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E222" s="95" t="inlineStr">
+      <c r="E222" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16409,7 +16391,7 @@
       <c r="G222" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H222" s="70" t="inlineStr">
+      <c r="H222" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16439,7 +16421,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N222" s="70" t="inlineStr">
+      <c r="N222" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16456,7 +16438,7 @@
           <t>PS5-62-18</t>
         </is>
       </c>
-      <c r="B223" s="83" t="inlineStr">
+      <c r="B223" s="79" t="inlineStr">
         <is>
           <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
@@ -16467,7 +16449,7 @@
       <c r="D223" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E223" s="95" t="inlineStr">
+      <c r="E223" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16478,7 +16460,7 @@
       <c r="G223" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H223" s="70" t="inlineStr">
+      <c r="H223" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16508,7 +16490,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N223" s="70" t="inlineStr">
+      <c r="N223" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16525,7 +16507,7 @@
           <t>PS5-62-19</t>
         </is>
       </c>
-      <c r="B224" s="83" t="inlineStr">
+      <c r="B224" s="79" t="inlineStr">
         <is>
           <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
@@ -16536,7 +16518,7 @@
       <c r="D224" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E224" s="95" t="inlineStr">
+      <c r="E224" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16547,7 +16529,7 @@
       <c r="G224" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H224" s="70" t="inlineStr">
+      <c r="H224" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16577,7 +16559,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N224" s="70" t="inlineStr">
+      <c r="N224" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16594,7 +16576,7 @@
           <t>PS5-62-20</t>
         </is>
       </c>
-      <c r="B225" s="83" t="inlineStr">
+      <c r="B225" s="79" t="inlineStr">
         <is>
           <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
@@ -16605,7 +16587,7 @@
       <c r="D225" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E225" s="95" t="inlineStr">
+      <c r="E225" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16616,7 +16598,7 @@
       <c r="G225" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H225" s="70" t="inlineStr">
+      <c r="H225" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16646,7 +16628,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N225" s="70" t="inlineStr">
+      <c r="N225" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16663,7 +16645,7 @@
           <t>PS5-63-01</t>
         </is>
       </c>
-      <c r="B226" s="83" t="inlineStr">
+      <c r="B226" s="79" t="inlineStr">
         <is>
           <t>PS5-63-01 - Electrical Earthing</t>
         </is>
@@ -16674,7 +16656,7 @@
       <c r="D226" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E226" s="70" t="inlineStr">
+      <c r="E226" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16685,7 +16667,7 @@
       <c r="G226" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="H226" s="70" t="inlineStr">
+      <c r="H226" s="69" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -16715,7 +16697,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N226" s="70" t="inlineStr">
+      <c r="N226" s="69" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -16732,7 +16714,7 @@
           <t>PS5-63-02</t>
         </is>
       </c>
-      <c r="B227" s="83" t="inlineStr">
+      <c r="B227" s="79" t="inlineStr">
         <is>
           <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
@@ -16743,7 +16725,7 @@
       <c r="D227" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E227" s="95" t="inlineStr">
+      <c r="E227" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16754,7 +16736,7 @@
       <c r="G227" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H227" s="70" t="inlineStr">
+      <c r="H227" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16784,7 +16766,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N227" s="70" t="inlineStr">
+      <c r="N227" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16801,7 +16783,7 @@
           <t>PS5-63-03</t>
         </is>
       </c>
-      <c r="B228" s="83" t="inlineStr">
+      <c r="B228" s="79" t="inlineStr">
         <is>
           <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
@@ -16812,7 +16794,7 @@
       <c r="D228" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E228" s="95" t="inlineStr">
+      <c r="E228" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16823,7 +16805,7 @@
       <c r="G228" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H228" s="69" t="inlineStr">
+      <c r="H228" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16853,7 +16835,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N228" s="69" t="inlineStr">
+      <c r="N228" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16870,7 +16852,7 @@
           <t>PS5-63-04</t>
         </is>
       </c>
-      <c r="B229" s="83" t="inlineStr">
+      <c r="B229" s="79" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -16881,7 +16863,7 @@
       <c r="D229" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E229" s="70" t="inlineStr">
+      <c r="E229" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -16892,7 +16874,7 @@
       <c r="G229" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H229" s="95" t="inlineStr">
+      <c r="H229" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16939,7 +16921,7 @@
           <t>PS5-63-05</t>
         </is>
       </c>
-      <c r="B230" s="83" t="inlineStr">
+      <c r="B230" s="79" t="inlineStr">
         <is>
           <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
@@ -16950,7 +16932,7 @@
       <c r="D230" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E230" s="95" t="inlineStr">
+      <c r="E230" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16961,7 +16943,7 @@
       <c r="G230" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H230" s="70" t="inlineStr">
+      <c r="H230" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16991,7 +16973,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N230" s="70" t="inlineStr">
+      <c r="N230" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17008,7 +16990,7 @@
           <t>PS5-63-06</t>
         </is>
       </c>
-      <c r="B231" s="83" t="inlineStr">
+      <c r="B231" s="79" t="inlineStr">
         <is>
           <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
@@ -17019,7 +17001,7 @@
       <c r="D231" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E231" s="95" t="inlineStr">
+      <c r="E231" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17030,7 +17012,7 @@
       <c r="G231" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H231" s="70" t="inlineStr">
+      <c r="H231" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17060,7 +17042,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N231" s="70" t="inlineStr">
+      <c r="N231" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17077,7 +17059,7 @@
           <t>PS5-63-07</t>
         </is>
       </c>
-      <c r="B232" s="83" t="inlineStr">
+      <c r="B232" s="79" t="inlineStr">
         <is>
           <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
@@ -17088,7 +17070,7 @@
       <c r="D232" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E232" s="95" t="inlineStr">
+      <c r="E232" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17099,7 +17081,7 @@
       <c r="G232" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H232" s="70" t="inlineStr">
+      <c r="H232" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17129,7 +17111,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N232" s="70" t="inlineStr">
+      <c r="N232" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17146,7 +17128,7 @@
           <t>PS5-71-01</t>
         </is>
       </c>
-      <c r="B233" s="83" t="inlineStr">
+      <c r="B233" s="79" t="inlineStr">
         <is>
           <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
@@ -17157,7 +17139,7 @@
       <c r="D233" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E233" s="70" t="inlineStr">
+      <c r="E233" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -17168,7 +17150,7 @@
       <c r="G233" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="H233" s="70" t="inlineStr">
+      <c r="H233" s="69" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -17198,7 +17180,7 @@
           <t>27/30</t>
         </is>
       </c>
-      <c r="N233" s="70" t="inlineStr">
+      <c r="N233" s="69" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -17215,7 +17197,7 @@
           <t>PS5-71-02</t>
         </is>
       </c>
-      <c r="B234" s="83" t="inlineStr">
+      <c r="B234" s="79" t="inlineStr">
         <is>
           <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
@@ -17226,7 +17208,7 @@
       <c r="D234" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E234" s="70" t="inlineStr">
+      <c r="E234" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -17237,7 +17219,7 @@
       <c r="G234" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H234" s="69" t="inlineStr">
+      <c r="H234" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -17267,7 +17249,7 @@
           <t>9/10</t>
         </is>
       </c>
-      <c r="N234" s="69" t="inlineStr">
+      <c r="N234" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -17284,7 +17266,7 @@
           <t>PS5-71-03</t>
         </is>
       </c>
-      <c r="B235" s="83" t="inlineStr">
+      <c r="B235" s="79" t="inlineStr">
         <is>
           <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
@@ -17295,7 +17277,7 @@
       <c r="D235" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E235" s="95" t="inlineStr">
+      <c r="E235" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17306,7 +17288,7 @@
       <c r="G235" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H235" s="95" t="inlineStr">
+      <c r="H235" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17336,7 +17318,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N235" s="70" t="inlineStr">
+      <c r="N235" s="69" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -17353,7 +17335,7 @@
           <t>PS5-71-04</t>
         </is>
       </c>
-      <c r="B236" s="83" t="inlineStr">
+      <c r="B236" s="79" t="inlineStr">
         <is>
           <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
@@ -17364,7 +17346,7 @@
       <c r="D236" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E236" s="69" t="inlineStr">
+      <c r="E236" s="68" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -17375,7 +17357,7 @@
       <c r="G236" s="23" t="n">
         <v>66</v>
       </c>
-      <c r="H236" s="69" t="inlineStr">
+      <c r="H236" s="68" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -17405,7 +17387,7 @@
           <t>42/47</t>
         </is>
       </c>
-      <c r="N236" s="69" t="inlineStr">
+      <c r="N236" s="68" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -17422,7 +17404,7 @@
           <t>PS5-71-05</t>
         </is>
       </c>
-      <c r="B237" s="83" t="inlineStr">
+      <c r="B237" s="79" t="inlineStr">
         <is>
           <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
@@ -17433,7 +17415,7 @@
       <c r="D237" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E237" s="70" t="inlineStr">
+      <c r="E237" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -17444,7 +17426,7 @@
       <c r="G237" s="23" t="n">
         <v>48</v>
       </c>
-      <c r="H237" s="69" t="inlineStr">
+      <c r="H237" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -17474,7 +17456,7 @@
           <t>13/14</t>
         </is>
       </c>
-      <c r="N237" s="69" t="inlineStr">
+      <c r="N237" s="68" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -17491,7 +17473,7 @@
           <t>PS5-71-06</t>
         </is>
       </c>
-      <c r="B238" s="83" t="inlineStr">
+      <c r="B238" s="79" t="inlineStr">
         <is>
           <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
@@ -17502,7 +17484,7 @@
       <c r="D238" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E238" s="69" t="inlineStr">
+      <c r="E238" s="68" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -17513,7 +17495,7 @@
       <c r="G238" s="23" t="n">
         <v>36</v>
       </c>
-      <c r="H238" s="69" t="inlineStr">
+      <c r="H238" s="68" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -17543,7 +17525,7 @@
           <t>21/22</t>
         </is>
       </c>
-      <c r="N238" s="69" t="inlineStr">
+      <c r="N238" s="68" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -17560,7 +17542,7 @@
           <t>PS5-71-07</t>
         </is>
       </c>
-      <c r="B239" s="83" t="inlineStr">
+      <c r="B239" s="79" t="inlineStr">
         <is>
           <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
@@ -17571,7 +17553,7 @@
       <c r="D239" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E239" s="70" t="inlineStr">
+      <c r="E239" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17582,7 +17564,7 @@
       <c r="G239" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H239" s="69" t="inlineStr">
+      <c r="H239" s="68" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17612,7 +17594,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N239" s="69" t="inlineStr">
+      <c r="N239" s="68" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17629,7 +17611,7 @@
           <t>PS5-71-08</t>
         </is>
       </c>
-      <c r="B240" s="83" t="inlineStr">
+      <c r="B240" s="79" t="inlineStr">
         <is>
           <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
@@ -17640,7 +17622,7 @@
       <c r="D240" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E240" s="70" t="inlineStr">
+      <c r="E240" s="69" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -17698,7 +17680,7 @@
           <t>PS5-71-09</t>
         </is>
       </c>
-      <c r="B241" s="83" t="inlineStr">
+      <c r="B241" s="79" t="inlineStr">
         <is>
           <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
@@ -17709,7 +17691,7 @@
       <c r="D241" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E241" s="70" t="inlineStr">
+      <c r="E241" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17767,7 +17749,7 @@
           <t>PS5-71-12</t>
         </is>
       </c>
-      <c r="B242" s="83" t="inlineStr">
+      <c r="B242" s="79" t="inlineStr">
         <is>
           <t>PS5-71-12 - CFO Service Tank</t>
         </is>
@@ -17778,7 +17760,7 @@
       <c r="D242" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="E242" s="69" t="inlineStr">
+      <c r="E242" s="68" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -17789,7 +17771,7 @@
       <c r="G242" s="23" t="n">
         <v>66</v>
       </c>
-      <c r="H242" s="69" t="inlineStr">
+      <c r="H242" s="68" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17819,7 +17801,7 @@
           <t>26/31</t>
         </is>
       </c>
-      <c r="N242" s="69" t="inlineStr">
+      <c r="N242" s="68" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17836,7 +17818,7 @@
           <t>PS5-71-13</t>
         </is>
       </c>
-      <c r="B243" s="83" t="inlineStr">
+      <c r="B243" s="79" t="inlineStr">
         <is>
           <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
@@ -17847,7 +17829,7 @@
       <c r="D243" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E243" s="70" t="inlineStr">
+      <c r="E243" s="69" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -17858,7 +17840,7 @@
       <c r="G243" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="H243" s="69" t="inlineStr">
+      <c r="H243" s="68" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -17888,7 +17870,7 @@
           <t>12/14</t>
         </is>
       </c>
-      <c r="N243" s="69" t="inlineStr">
+      <c r="N243" s="68" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -17905,7 +17887,7 @@
           <t>PS5-71-14</t>
         </is>
       </c>
-      <c r="B244" s="83" t="inlineStr">
+      <c r="B244" s="79" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
@@ -17916,7 +17898,7 @@
       <c r="D244" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E244" s="70" t="inlineStr">
+      <c r="E244" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -17957,7 +17939,7 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N244" s="69" t="inlineStr">
+      <c r="N244" s="68" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -17974,7 +17956,7 @@
           <t>PS5-71-15</t>
         </is>
       </c>
-      <c r="B245" s="83" t="inlineStr">
+      <c r="B245" s="79" t="inlineStr">
         <is>
           <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
@@ -17985,7 +17967,7 @@
       <c r="D245" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E245" s="70" t="inlineStr">
+      <c r="E245" s="69" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
@@ -17996,7 +17978,7 @@
       <c r="G245" s="23" t="n">
         <v>41</v>
       </c>
-      <c r="H245" s="69" t="inlineStr">
+      <c r="H245" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -18026,7 +18008,7 @@
           <t>17/20</t>
         </is>
       </c>
-      <c r="N245" s="69" t="inlineStr">
+      <c r="N245" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -18043,7 +18025,7 @@
           <t>PS5-71-16</t>
         </is>
       </c>
-      <c r="B246" s="83" t="inlineStr">
+      <c r="B246" s="79" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
@@ -18054,7 +18036,7 @@
       <c r="D246" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E246" s="70" t="inlineStr">
+      <c r="E246" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18095,7 +18077,7 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N246" s="69" t="inlineStr">
+      <c r="N246" s="68" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -18112,7 +18094,7 @@
           <t>PS5-71-17</t>
         </is>
       </c>
-      <c r="B247" s="83" t="inlineStr">
+      <c r="B247" s="79" t="inlineStr">
         <is>
           <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
@@ -18123,7 +18105,7 @@
       <c r="D247" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E247" s="70" t="inlineStr">
+      <c r="E247" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18181,7 +18163,7 @@
           <t>PS5-71-18</t>
         </is>
       </c>
-      <c r="B248" s="83" t="inlineStr">
+      <c r="B248" s="79" t="inlineStr">
         <is>
           <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
@@ -18192,7 +18174,7 @@
       <c r="D248" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E248" s="69" t="inlineStr">
+      <c r="E248" s="68" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
@@ -18203,7 +18185,7 @@
       <c r="G248" s="23" t="n">
         <v>47</v>
       </c>
-      <c r="H248" s="69" t="inlineStr">
+      <c r="H248" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18233,7 +18215,7 @@
           <t>20/20</t>
         </is>
       </c>
-      <c r="N248" s="69" t="inlineStr">
+      <c r="N248" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18250,7 +18232,7 @@
           <t>PS5-71-19</t>
         </is>
       </c>
-      <c r="B249" s="83" t="inlineStr">
+      <c r="B249" s="79" t="inlineStr">
         <is>
           <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
@@ -18261,7 +18243,7 @@
       <c r="D249" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E249" s="70" t="inlineStr">
+      <c r="E249" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18272,7 +18254,7 @@
       <c r="G249" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="H249" s="69" t="inlineStr">
+      <c r="H249" s="68" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -18302,7 +18284,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N249" s="69" t="inlineStr">
+      <c r="N249" s="68" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -18319,7 +18301,7 @@
           <t>PS5-71-20</t>
         </is>
       </c>
-      <c r="B250" s="83" t="inlineStr">
+      <c r="B250" s="79" t="inlineStr">
         <is>
           <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
@@ -18330,7 +18312,7 @@
       <c r="D250" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E250" s="69" t="inlineStr">
+      <c r="E250" s="68" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -18341,7 +18323,7 @@
       <c r="G250" s="23" t="n">
         <v>49</v>
       </c>
-      <c r="H250" s="69" t="inlineStr">
+      <c r="H250" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18371,7 +18353,7 @@
           <t>20/20</t>
         </is>
       </c>
-      <c r="N250" s="69" t="inlineStr">
+      <c r="N250" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18388,7 +18370,7 @@
           <t>PS5-71-21</t>
         </is>
       </c>
-      <c r="B251" s="83" t="inlineStr">
+      <c r="B251" s="79" t="inlineStr">
         <is>
           <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
@@ -18399,7 +18381,7 @@
       <c r="D251" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E251" s="70" t="inlineStr">
+      <c r="E251" s="69" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -18457,7 +18439,7 @@
           <t>PS5-71-22</t>
         </is>
       </c>
-      <c r="B252" s="83" t="inlineStr">
+      <c r="B252" s="79" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -18468,7 +18450,7 @@
       <c r="D252" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="E252" s="70" t="inlineStr">
+      <c r="E252" s="69" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -18516,7 +18498,7 @@
       </c>
       <c r="O252" s="27" t="inlineStr">
         <is>
-          <t>DONE(full)</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -18526,7 +18508,7 @@
           <t>PS5-71-23</t>
         </is>
       </c>
-      <c r="B253" s="83" t="inlineStr">
+      <c r="B253" s="79" t="inlineStr">
         <is>
           <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
@@ -18537,7 +18519,7 @@
       <c r="D253" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E253" s="70" t="inlineStr">
+      <c r="E253" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -18548,7 +18530,7 @@
       <c r="G253" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H253" s="69" t="inlineStr">
+      <c r="H253" s="68" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -18578,7 +18560,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N253" s="69" t="inlineStr">
+      <c r="N253" s="68" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -18595,7 +18577,7 @@
           <t>PS5-74-01</t>
         </is>
       </c>
-      <c r="B254" s="83" t="inlineStr">
+      <c r="B254" s="79" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
@@ -18606,7 +18588,7 @@
       <c r="D254" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E254" s="70" t="inlineStr">
+      <c r="E254" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -18617,7 +18599,7 @@
       <c r="G254" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H254" s="69" t="inlineStr">
+      <c r="H254" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -18647,7 +18629,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="N254" s="69" t="inlineStr">
+      <c r="N254" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -18664,7 +18646,7 @@
           <t>PS5-74-02</t>
         </is>
       </c>
-      <c r="B255" s="83" t="inlineStr">
+      <c r="B255" s="79" t="inlineStr">
         <is>
           <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
@@ -18686,7 +18668,7 @@
       <c r="G255" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H255" s="69" t="inlineStr">
+      <c r="H255" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -18716,7 +18698,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N255" s="69" t="inlineStr">
+      <c r="N255" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -18733,7 +18715,7 @@
           <t>PS5-74-03</t>
         </is>
       </c>
-      <c r="B256" s="83" t="inlineStr">
+      <c r="B256" s="79" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -18744,7 +18726,7 @@
       <c r="D256" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E256" s="70" t="inlineStr">
+      <c r="E256" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -18802,7 +18784,7 @@
           <t>PS5-74-04</t>
         </is>
       </c>
-      <c r="B257" s="83" t="inlineStr">
+      <c r="B257" s="79" t="inlineStr">
         <is>
           <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
@@ -18813,7 +18795,7 @@
       <c r="D257" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E257" s="95" t="inlineStr">
+      <c r="E257" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18824,7 +18806,7 @@
       <c r="G257" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="H257" s="69" t="inlineStr">
+      <c r="H257" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -18854,7 +18836,7 @@
           <t>6/8</t>
         </is>
       </c>
-      <c r="N257" s="69" t="inlineStr">
+      <c r="N257" s="68" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
@@ -18871,7 +18853,7 @@
           <t>PS5-75-01</t>
         </is>
       </c>
-      <c r="B258" s="83" t="inlineStr">
+      <c r="B258" s="79" t="inlineStr">
         <is>
           <t>PS5-75-01 - DRA Injection Package</t>
         </is>
@@ -18882,7 +18864,7 @@
       <c r="D258" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E258" s="95" t="inlineStr">
+      <c r="E258" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18893,7 +18875,7 @@
       <c r="G258" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H258" s="70" t="inlineStr">
+      <c r="H258" s="69" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -18923,7 +18905,7 @@
           <t>12/15</t>
         </is>
       </c>
-      <c r="N258" s="70" t="inlineStr">
+      <c r="N258" s="69" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -18940,7 +18922,7 @@
           <t>PS5-75-02</t>
         </is>
       </c>
-      <c r="B259" s="83" t="inlineStr">
+      <c r="B259" s="79" t="inlineStr">
         <is>
           <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
@@ -18951,7 +18933,7 @@
       <c r="D259" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E259" s="70" t="inlineStr">
+      <c r="E259" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -18962,7 +18944,7 @@
       <c r="G259" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H259" s="69" t="inlineStr">
+      <c r="H259" s="68" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -18992,7 +18974,7 @@
           <t>13/14</t>
         </is>
       </c>
-      <c r="N259" s="69" t="inlineStr">
+      <c r="N259" s="68" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -19009,7 +18991,7 @@
           <t>PS5-75-03</t>
         </is>
       </c>
-      <c r="B260" s="83" t="inlineStr">
+      <c r="B260" s="79" t="inlineStr">
         <is>
           <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
@@ -19020,7 +19002,7 @@
       <c r="D260" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E260" s="70" t="inlineStr">
+      <c r="E260" s="69" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
@@ -19031,7 +19013,7 @@
       <c r="G260" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H260" s="69" t="inlineStr">
+      <c r="H260" s="68" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -19061,7 +19043,7 @@
           <t>12/15</t>
         </is>
       </c>
-      <c r="N260" s="69" t="inlineStr">
+      <c r="N260" s="68" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -19078,7 +19060,7 @@
           <t>PS5-78-01</t>
         </is>
       </c>
-      <c r="B261" s="83" t="inlineStr">
+      <c r="B261" s="79" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -19089,7 +19071,7 @@
       <c r="D261" s="23" t="n">
         <v>71</v>
       </c>
-      <c r="E261" s="69" t="inlineStr">
+      <c r="E261" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -19100,7 +19082,7 @@
       <c r="G261" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H261" s="69" t="inlineStr">
+      <c r="H261" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -19130,12 +19112,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N261" s="69" t="inlineStr">
+      <c r="N261" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
       </c>
-      <c r="O261" s="69" t="inlineStr">
+      <c r="O261" s="68" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -19147,7 +19129,7 @@
           <t>PS5-79-01</t>
         </is>
       </c>
-      <c r="B262" s="83" t="inlineStr">
+      <c r="B262" s="79" t="inlineStr">
         <is>
           <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
@@ -19158,7 +19140,7 @@
       <c r="D262" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E262" s="95" t="inlineStr">
+      <c r="E262" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19169,7 +19151,7 @@
       <c r="G262" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H262" s="70" t="inlineStr">
+      <c r="H262" s="69" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -19199,7 +19181,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N262" s="70" t="inlineStr">
+      <c r="N262" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19216,7 +19198,7 @@
           <t>PS5-79-02</t>
         </is>
       </c>
-      <c r="B263" s="83" t="inlineStr">
+      <c r="B263" s="79" t="inlineStr">
         <is>
           <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
@@ -19227,7 +19209,7 @@
       <c r="D263" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E263" s="95" t="inlineStr">
+      <c r="E263" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19238,7 +19220,7 @@
       <c r="G263" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H263" s="70" t="inlineStr">
+      <c r="H263" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19268,7 +19250,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N263" s="70" t="inlineStr">
+      <c r="N263" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -19285,7 +19267,7 @@
           <t>PS5-79-03</t>
         </is>
       </c>
-      <c r="B264" s="83" t="inlineStr">
+      <c r="B264" s="79" t="inlineStr">
         <is>
           <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
@@ -19296,7 +19278,7 @@
       <c r="D264" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E264" s="95" t="inlineStr">
+      <c r="E264" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19307,7 +19289,7 @@
       <c r="G264" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H264" s="70" t="inlineStr">
+      <c r="H264" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19337,7 +19319,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N264" s="70" t="inlineStr">
+      <c r="N264" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19354,7 +19336,7 @@
           <t>PS5-79-04</t>
         </is>
       </c>
-      <c r="B265" s="83" t="inlineStr">
+      <c r="B265" s="79" t="inlineStr">
         <is>
           <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
@@ -19365,7 +19347,7 @@
       <c r="D265" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E265" s="95" t="inlineStr">
+      <c r="E265" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19376,7 +19358,7 @@
       <c r="G265" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H265" s="70" t="inlineStr">
+      <c r="H265" s="69" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19406,7 +19388,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N265" s="70" t="inlineStr">
+      <c r="N265" s="69" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19423,7 +19405,7 @@
           <t>PS5-79-05</t>
         </is>
       </c>
-      <c r="B266" s="83" t="inlineStr">
+      <c r="B266" s="79" t="inlineStr">
         <is>
           <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
@@ -19434,7 +19416,7 @@
       <c r="D266" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E266" s="95" t="inlineStr">
+      <c r="E266" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19445,7 +19427,7 @@
       <c r="G266" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H266" s="70" t="inlineStr">
+      <c r="H266" s="69" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -19475,7 +19457,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N266" s="70" t="inlineStr">
+      <c r="N266" s="69" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -19492,7 +19474,7 @@
           <t>PS5-79-06</t>
         </is>
       </c>
-      <c r="B267" s="83" t="inlineStr">
+      <c r="B267" s="79" t="inlineStr">
         <is>
           <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
@@ -19503,7 +19485,7 @@
       <c r="D267" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E267" s="95" t="inlineStr">
+      <c r="E267" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19514,7 +19496,7 @@
       <c r="G267" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H267" s="70" t="inlineStr">
+      <c r="H267" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -19544,7 +19526,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N267" s="70" t="inlineStr">
+      <c r="N267" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -19561,7 +19543,7 @@
           <t>PS5-79-07</t>
         </is>
       </c>
-      <c r="B268" s="83" t="inlineStr">
+      <c r="B268" s="79" t="inlineStr">
         <is>
           <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
@@ -19572,7 +19554,7 @@
       <c r="D268" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E268" s="95" t="inlineStr">
+      <c r="E268" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19583,7 +19565,7 @@
       <c r="G268" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H268" s="70" t="inlineStr">
+      <c r="H268" s="69" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -19613,7 +19595,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N268" s="70" t="inlineStr">
+      <c r="N268" s="69" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -19630,7 +19612,7 @@
           <t>PS5-79-08</t>
         </is>
       </c>
-      <c r="B269" s="83" t="inlineStr">
+      <c r="B269" s="79" t="inlineStr">
         <is>
           <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
@@ -19641,7 +19623,7 @@
       <c r="D269" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E269" s="95" t="inlineStr">
+      <c r="E269" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19652,7 +19634,7 @@
       <c r="G269" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H269" s="70" t="inlineStr">
+      <c r="H269" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -19682,7 +19664,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N269" s="70" t="inlineStr">
+      <c r="N269" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -19699,7 +19681,7 @@
           <t>PS5-79-09</t>
         </is>
       </c>
-      <c r="B270" s="83" t="inlineStr">
+      <c r="B270" s="79" t="inlineStr">
         <is>
           <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
@@ -19710,7 +19692,7 @@
       <c r="D270" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E270" s="95" t="inlineStr">
+      <c r="E270" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19721,7 +19703,7 @@
       <c r="G270" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H270" s="70" t="inlineStr">
+      <c r="H270" s="69" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -19751,7 +19733,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N270" s="70" t="inlineStr">
+      <c r="N270" s="69" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -19768,7 +19750,7 @@
           <t>PS5-79-10</t>
         </is>
       </c>
-      <c r="B271" s="83" t="inlineStr">
+      <c r="B271" s="79" t="inlineStr">
         <is>
           <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
@@ -19779,7 +19761,7 @@
       <c r="D271" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E271" s="95" t="inlineStr">
+      <c r="E271" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19790,7 +19772,7 @@
       <c r="G271" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="H271" s="70" t="inlineStr">
+      <c r="H271" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -19820,7 +19802,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N271" s="70" t="inlineStr">
+      <c r="N271" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -19837,7 +19819,7 @@
           <t>PS5-79-11</t>
         </is>
       </c>
-      <c r="B272" s="83" t="inlineStr">
+      <c r="B272" s="79" t="inlineStr">
         <is>
           <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
@@ -19848,7 +19830,7 @@
       <c r="D272" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E272" s="95" t="inlineStr">
+      <c r="E272" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19859,7 +19841,7 @@
       <c r="G272" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H272" s="70" t="inlineStr">
+      <c r="H272" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -19889,7 +19871,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N272" s="70" t="inlineStr">
+      <c r="N272" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -19906,7 +19888,7 @@
           <t>PS5-79-12</t>
         </is>
       </c>
-      <c r="B273" s="83" t="inlineStr">
+      <c r="B273" s="79" t="inlineStr">
         <is>
           <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
@@ -19917,7 +19899,7 @@
       <c r="D273" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E273" s="95" t="inlineStr">
+      <c r="E273" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19928,7 +19910,7 @@
       <c r="G273" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="H273" s="70" t="inlineStr">
+      <c r="H273" s="69" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19958,7 +19940,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N273" s="70" t="inlineStr">
+      <c r="N273" s="69" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19975,7 +19957,7 @@
           <t>PS5-82-01</t>
         </is>
       </c>
-      <c r="B274" s="83" t="inlineStr">
+      <c r="B274" s="79" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
@@ -19986,7 +19968,7 @@
       <c r="D274" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E274" s="95" t="inlineStr">
+      <c r="E274" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19997,7 +19979,7 @@
       <c r="G274" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="H274" s="69" t="inlineStr">
+      <c r="H274" s="68" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -20027,7 +20009,7 @@
           <t>30/50</t>
         </is>
       </c>
-      <c r="N274" s="69" t="inlineStr">
+      <c r="N274" s="68" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -20044,7 +20026,7 @@
           <t>PS5-82-02</t>
         </is>
       </c>
-      <c r="B275" s="83" t="inlineStr">
+      <c r="B275" s="79" t="inlineStr">
         <is>
           <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
@@ -20055,7 +20037,7 @@
       <c r="D275" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E275" s="70" t="inlineStr">
+      <c r="E275" s="69" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
@@ -20066,7 +20048,7 @@
       <c r="G275" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H275" s="70" t="inlineStr">
+      <c r="H275" s="69" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -20096,7 +20078,7 @@
           <t>0/1</t>
         </is>
       </c>
-      <c r="N275" s="70" t="inlineStr">
+      <c r="N275" s="69" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -20113,7 +20095,7 @@
           <t>PS5-82-03</t>
         </is>
       </c>
-      <c r="B276" s="83" t="inlineStr">
+      <c r="B276" s="79" t="inlineStr">
         <is>
           <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
@@ -20124,7 +20106,7 @@
       <c r="D276" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E276" s="95" t="inlineStr">
+      <c r="E276" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20135,7 +20117,7 @@
       <c r="G276" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H276" s="70" t="inlineStr">
+      <c r="H276" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20165,7 +20147,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N276" s="70" t="inlineStr">
+      <c r="N276" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20182,7 +20164,7 @@
           <t>PS5-82-04</t>
         </is>
       </c>
-      <c r="B277" s="83" t="inlineStr">
+      <c r="B277" s="79" t="inlineStr">
         <is>
           <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
@@ -20193,7 +20175,7 @@
       <c r="D277" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E277" s="95" t="inlineStr">
+      <c r="E277" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20204,7 +20186,7 @@
       <c r="G277" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H277" s="69" t="inlineStr">
+      <c r="H277" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -20234,7 +20216,7 @@
           <t>6/8</t>
         </is>
       </c>
-      <c r="N277" s="69" t="inlineStr">
+      <c r="N277" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -20251,7 +20233,7 @@
           <t>PS5-82-05</t>
         </is>
       </c>
-      <c r="B278" s="83" t="inlineStr">
+      <c r="B278" s="79" t="inlineStr">
         <is>
           <t>PS5-82-05 - Office and Facilities building</t>
         </is>
@@ -20262,7 +20244,7 @@
       <c r="D278" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E278" s="95" t="inlineStr">
+      <c r="E278" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20273,7 +20255,7 @@
       <c r="G278" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H278" s="70" t="inlineStr">
+      <c r="H278" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20303,7 +20285,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N278" s="70" t="inlineStr">
+      <c r="N278" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20320,7 +20302,7 @@
           <t>PS5-82-06</t>
         </is>
       </c>
-      <c r="B279" s="83" t="inlineStr">
+      <c r="B279" s="79" t="inlineStr">
         <is>
           <t>PS5-82-06 - Guard House Building</t>
         </is>
@@ -20331,7 +20313,7 @@
       <c r="D279" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E279" s="95" t="inlineStr">
+      <c r="E279" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20342,7 +20324,7 @@
       <c r="G279" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H279" s="70" t="inlineStr">
+      <c r="H279" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20372,7 +20354,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N279" s="70" t="inlineStr">
+      <c r="N279" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20389,7 +20371,7 @@
           <t>PS5-82-07</t>
         </is>
       </c>
-      <c r="B280" s="83" t="inlineStr">
+      <c r="B280" s="79" t="inlineStr">
         <is>
           <t>PS5-82-07 - Guard Huts</t>
         </is>
@@ -20400,7 +20382,7 @@
       <c r="D280" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E280" s="95" t="inlineStr">
+      <c r="E280" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20411,7 +20393,7 @@
       <c r="G280" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H280" s="70" t="inlineStr">
+      <c r="H280" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20441,7 +20423,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N280" s="70" t="inlineStr">
+      <c r="N280" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20458,7 +20440,7 @@
           <t>PS5-83-01</t>
         </is>
       </c>
-      <c r="B281" s="83" t="inlineStr">
+      <c r="B281" s="79" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -20469,7 +20451,7 @@
       <c r="D281" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="E281" s="69" t="inlineStr">
+      <c r="E281" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20527,7 +20509,7 @@
           <t>PS5-84-01</t>
         </is>
       </c>
-      <c r="B282" s="83" t="inlineStr">
+      <c r="B282" s="79" t="inlineStr">
         <is>
           <t>PS5-84-01 - Generator Building</t>
         </is>
@@ -20538,7 +20520,7 @@
       <c r="D282" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E282" s="95" t="inlineStr">
+      <c r="E282" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20549,7 +20531,7 @@
       <c r="G282" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H282" s="70" t="inlineStr">
+      <c r="H282" s="69" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -20579,7 +20561,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N282" s="70" t="inlineStr">
+      <c r="N282" s="69" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -20596,7 +20578,7 @@
           <t>PS5-84-02</t>
         </is>
       </c>
-      <c r="B283" s="83" t="inlineStr">
+      <c r="B283" s="79" t="inlineStr">
         <is>
           <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
@@ -20607,7 +20589,7 @@
       <c r="D283" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E283" s="95" t="inlineStr">
+      <c r="E283" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20618,7 +20600,7 @@
       <c r="G283" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H283" s="70" t="inlineStr">
+      <c r="H283" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -20648,7 +20630,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N283" s="70" t="inlineStr">
+      <c r="N283" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -20665,7 +20647,7 @@
           <t>PS5-84-03</t>
         </is>
       </c>
-      <c r="B284" s="83" t="inlineStr">
+      <c r="B284" s="79" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -20676,7 +20658,7 @@
       <c r="D284" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E284" s="95" t="inlineStr">
+      <c r="E284" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20734,7 +20716,7 @@
           <t>PS5-86-01</t>
         </is>
       </c>
-      <c r="B285" s="83" t="inlineStr">
+      <c r="B285" s="79" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -20745,7 +20727,7 @@
       <c r="D285" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E285" s="95" t="inlineStr">
+      <c r="E285" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20803,7 +20785,7 @@
           <t>PS5-91-01</t>
         </is>
       </c>
-      <c r="B286" s="83" t="inlineStr">
+      <c r="B286" s="79" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -20814,7 +20796,7 @@
       <c r="D286" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E286" s="70" t="inlineStr">
+      <c r="E286" s="69" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -20872,7 +20854,7 @@
           <t>PS5-99-01</t>
         </is>
       </c>
-      <c r="B287" s="83" t="inlineStr">
+      <c r="B287" s="79" t="inlineStr">
         <is>
           <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
@@ -20883,7 +20865,7 @@
       <c r="D287" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E287" s="95" t="inlineStr">
+      <c r="E287" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20894,7 +20876,7 @@
       <c r="G287" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H287" s="70" t="inlineStr">
+      <c r="H287" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20924,7 +20906,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N287" s="70" t="inlineStr">
+      <c r="N287" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20941,7 +20923,7 @@
           <t>PS5-99-02</t>
         </is>
       </c>
-      <c r="B288" s="83" t="inlineStr">
+      <c r="B288" s="79" t="inlineStr">
         <is>
           <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
@@ -20952,7 +20934,7 @@
       <c r="D288" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E288" s="95" t="inlineStr">
+      <c r="E288" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20963,7 +20945,7 @@
       <c r="G288" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H288" s="70" t="inlineStr">
+      <c r="H288" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20993,7 +20975,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N288" s="70" t="inlineStr">
+      <c r="N288" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21010,7 +20992,7 @@
           <t>PS5-99-03</t>
         </is>
       </c>
-      <c r="B289" s="83" t="inlineStr">
+      <c r="B289" s="79" t="inlineStr">
         <is>
           <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
@@ -21021,7 +21003,7 @@
       <c r="D289" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E289" s="95" t="inlineStr">
+      <c r="E289" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21032,7 +21014,7 @@
       <c r="G289" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H289" s="70" t="inlineStr">
+      <c r="H289" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21062,7 +21044,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N289" s="70" t="inlineStr">
+      <c r="N289" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21079,7 +21061,7 @@
           <t>PS5-99-04</t>
         </is>
       </c>
-      <c r="B290" s="83" t="inlineStr">
+      <c r="B290" s="79" t="inlineStr">
         <is>
           <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
@@ -21090,7 +21072,7 @@
       <c r="D290" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E290" s="95" t="inlineStr">
+      <c r="E290" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21101,7 +21083,7 @@
       <c r="G290" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H290" s="70" t="inlineStr">
+      <c r="H290" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21131,7 +21113,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N290" s="70" t="inlineStr">
+      <c r="N290" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21148,7 +21130,7 @@
           <t>PS5-99-05</t>
         </is>
       </c>
-      <c r="B291" s="83" t="inlineStr">
+      <c r="B291" s="79" t="inlineStr">
         <is>
           <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
@@ -21159,7 +21141,7 @@
       <c r="D291" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E291" s="95" t="inlineStr">
+      <c r="E291" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21170,7 +21152,7 @@
       <c r="G291" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H291" s="70" t="inlineStr">
+      <c r="H291" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -21200,7 +21182,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N291" s="70" t="inlineStr">
+      <c r="N291" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -21217,7 +21199,7 @@
           <t>PS5-99-06</t>
         </is>
       </c>
-      <c r="B292" s="83" t="inlineStr">
+      <c r="B292" s="79" t="inlineStr">
         <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
@@ -21228,7 +21210,7 @@
       <c r="D292" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E292" s="95" t="inlineStr">
+      <c r="E292" s="91" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21239,7 +21221,7 @@
       <c r="G292" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H292" s="69" t="inlineStr">
+      <c r="H292" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -21269,7 +21251,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N292" s="69" t="inlineStr">
+      <c r="N292" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -303,6 +303,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -498,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -512,9 +518,6 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,10 +527,10 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -539,16 +542,19 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -558,10 +564,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -573,21 +579,21 @@
     <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -677,10 +683,13 @@
     <xf numFmtId="0" fontId="11" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,7 +707,10 @@
     <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -710,7 +722,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -719,37 +737,37 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1160,20 +1178,20 @@
           <t>PS5 COMPLETION PLATFORM  |  SUB SYSTEM - 290 subsystem(s)</t>
         </is>
       </c>
-      <c r="B1" s="96" t="n"/>
-      <c r="C1" s="96" t="n"/>
-      <c r="D1" s="96" t="n"/>
-      <c r="E1" s="96" t="n"/>
-      <c r="F1" s="96" t="n"/>
-      <c r="G1" s="96" t="n"/>
-      <c r="H1" s="96" t="n"/>
-      <c r="I1" s="96" t="n"/>
-      <c r="J1" s="96" t="n"/>
-      <c r="K1" s="96" t="n"/>
-      <c r="L1" s="96" t="n"/>
-      <c r="M1" s="96" t="n"/>
-      <c r="N1" s="96" t="n"/>
-      <c r="O1" s="97" t="n"/>
+      <c r="B1" s="100" t="n"/>
+      <c r="C1" s="100" t="n"/>
+      <c r="D1" s="100" t="n"/>
+      <c r="E1" s="100" t="n"/>
+      <c r="F1" s="100" t="n"/>
+      <c r="G1" s="100" t="n"/>
+      <c r="H1" s="100" t="n"/>
+      <c r="I1" s="100" t="n"/>
+      <c r="J1" s="100" t="n"/>
+      <c r="K1" s="100" t="n"/>
+      <c r="L1" s="100" t="n"/>
+      <c r="M1" s="100" t="n"/>
+      <c r="N1" s="100" t="n"/>
+      <c r="O1" s="101" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1258,7 +1276,7 @@
           <t>PS5-01-01</t>
         </is>
       </c>
-      <c r="B3" s="79" t="inlineStr">
+      <c r="B3" s="83" t="inlineStr">
         <is>
           <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
@@ -1269,7 +1287,7 @@
       <c r="D3" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="69" t="inlineStr">
+      <c r="E3" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -1327,7 +1345,7 @@
           <t>PS5-01-02</t>
         </is>
       </c>
-      <c r="B4" s="79" t="inlineStr">
+      <c r="B4" s="83" t="inlineStr">
         <is>
           <t>PS5-01-02 - Fire Water Pump A</t>
         </is>
@@ -1338,7 +1356,7 @@
       <c r="D4" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="69" t="inlineStr">
+      <c r="E4" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -1396,7 +1414,7 @@
           <t>PS5-01-03</t>
         </is>
       </c>
-      <c r="B5" s="79" t="inlineStr">
+      <c r="B5" s="83" t="inlineStr">
         <is>
           <t>PS5-01-03 - Fire Water Pump B</t>
         </is>
@@ -1407,7 +1425,7 @@
       <c r="D5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="69" t="inlineStr">
+      <c r="E5" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1465,7 +1483,7 @@
           <t>PS5-01-04</t>
         </is>
       </c>
-      <c r="B6" s="79" t="inlineStr">
+      <c r="B6" s="83" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -1476,7 +1494,7 @@
       <c r="D6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="69" t="inlineStr">
+      <c r="E6" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1534,7 +1552,7 @@
           <t>PS5-01-05</t>
         </is>
       </c>
-      <c r="B7" s="79" t="inlineStr">
+      <c r="B7" s="83" t="inlineStr">
         <is>
           <t>PS5-01-05 - Foam Skid</t>
         </is>
@@ -1545,7 +1563,7 @@
       <c r="D7" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="69" t="inlineStr">
+      <c r="E7" s="70" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -1603,7 +1621,7 @@
           <t>PS5-01-06</t>
         </is>
       </c>
-      <c r="B8" s="79" t="inlineStr">
+      <c r="B8" s="83" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -1614,7 +1632,7 @@
       <c r="D8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="69" t="inlineStr">
+      <c r="E8" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1672,7 +1690,7 @@
           <t>PS5-01-07</t>
         </is>
       </c>
-      <c r="B9" s="79" t="inlineStr">
+      <c r="B9" s="83" t="inlineStr">
         <is>
           <t>PS5-01-07 - Fire Water Ring Main &amp; Distribution</t>
         </is>
@@ -1683,7 +1701,7 @@
       <c r="D9" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="69" t="inlineStr">
+      <c r="E9" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1694,7 +1712,7 @@
       <c r="G9" s="23" t="n">
         <v>117</v>
       </c>
-      <c r="H9" s="68" t="inlineStr">
+      <c r="H9" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -1724,7 +1742,7 @@
           <t>86/87</t>
         </is>
       </c>
-      <c r="N9" s="68" t="inlineStr">
+      <c r="N9" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -1741,7 +1759,7 @@
           <t>PS5-01-08</t>
         </is>
       </c>
-      <c r="B10" s="79" t="inlineStr">
+      <c r="B10" s="83" t="inlineStr">
         <is>
           <t>PS5-01-08 - PS5 Deluge Valve Skid (PS5-01-UK-6100)</t>
         </is>
@@ -1752,7 +1770,7 @@
       <c r="D10" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="69" t="inlineStr">
+      <c r="E10" s="70" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -1763,7 +1781,7 @@
       <c r="G10" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H10" s="68" t="inlineStr">
+      <c r="H10" s="69" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -1793,7 +1811,7 @@
           <t>26/34</t>
         </is>
       </c>
-      <c r="N10" s="68" t="inlineStr">
+      <c r="N10" s="69" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -1810,7 +1828,7 @@
           <t>PS5-01-09</t>
         </is>
       </c>
-      <c r="B11" s="79" t="inlineStr">
+      <c r="B11" s="83" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -1821,7 +1839,7 @@
       <c r="D11" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="68" t="inlineStr">
+      <c r="E11" s="69" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1869,7 +1887,7 @@
       </c>
       <c r="O11" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1897,7 @@
           <t>PS5-01-10</t>
         </is>
       </c>
-      <c r="B12" s="79" t="inlineStr">
+      <c r="B12" s="83" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -1890,7 +1908,7 @@
       <c r="D12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="69" t="inlineStr">
+      <c r="E12" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -1948,7 +1966,7 @@
           <t>PS5-01-11</t>
         </is>
       </c>
-      <c r="B13" s="79" t="inlineStr">
+      <c r="B13" s="83" t="inlineStr">
         <is>
           <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
@@ -1959,7 +1977,7 @@
       <c r="D13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="69" t="inlineStr">
+      <c r="E13" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1970,7 +1988,7 @@
       <c r="G13" s="23" t="n">
         <v>39</v>
       </c>
-      <c r="H13" s="69" t="inlineStr">
+      <c r="H13" s="70" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -2000,7 +2018,7 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="N13" s="69" t="inlineStr">
+      <c r="N13" s="70" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -2017,7 +2035,7 @@
           <t>PS5-02-01</t>
         </is>
       </c>
-      <c r="B14" s="79" t="inlineStr">
+      <c r="B14" s="83" t="inlineStr">
         <is>
           <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
@@ -2028,7 +2046,7 @@
       <c r="D14" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="69" t="inlineStr">
+      <c r="E14" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2039,7 +2057,7 @@
       <c r="G14" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="69" t="inlineStr">
+      <c r="H14" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -2069,7 +2087,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N14" s="69" t="inlineStr">
+      <c r="N14" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -2086,7 +2104,7 @@
           <t>PS5-02-02</t>
         </is>
       </c>
-      <c r="B15" s="79" t="inlineStr">
+      <c r="B15" s="83" t="inlineStr">
         <is>
           <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
@@ -2097,7 +2115,7 @@
       <c r="D15" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="69" t="inlineStr">
+      <c r="E15" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2108,7 +2126,7 @@
       <c r="G15" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="69" t="inlineStr">
+      <c r="H15" s="70" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -2138,7 +2156,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N15" s="69" t="inlineStr">
+      <c r="N15" s="70" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -2155,7 +2173,7 @@
           <t>PS5-03-01</t>
         </is>
       </c>
-      <c r="B16" s="79" t="inlineStr">
+      <c r="B16" s="83" t="inlineStr">
         <is>
           <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
@@ -2166,7 +2184,7 @@
       <c r="D16" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="91" t="inlineStr">
+      <c r="E16" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2224,7 +2242,7 @@
           <t>PS5-03-03</t>
         </is>
       </c>
-      <c r="B17" s="79" t="inlineStr">
+      <c r="B17" s="83" t="inlineStr">
         <is>
           <t>PS5-03-03 - FZ-03 - Buildings Area</t>
         </is>
@@ -2235,7 +2253,7 @@
       <c r="D17" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="91" t="inlineStr">
+      <c r="E17" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2246,7 +2264,7 @@
       <c r="G17" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="69" t="inlineStr">
+      <c r="H17" s="70" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -2276,7 +2294,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N17" s="69" t="inlineStr">
+      <c r="N17" s="70" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -2293,7 +2311,7 @@
           <t>PS5-03-04</t>
         </is>
       </c>
-      <c r="B18" s="79" t="inlineStr">
+      <c r="B18" s="83" t="inlineStr">
         <is>
           <t>PS5-03-04 - FZ-04 - Utilities - Diesel and Firewater Pumps Areas</t>
         </is>
@@ -2304,7 +2322,7 @@
       <c r="D18" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="91" t="inlineStr">
+      <c r="E18" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2362,7 +2380,7 @@
           <t>PS5-03-06</t>
         </is>
       </c>
-      <c r="B19" s="79" t="inlineStr">
+      <c r="B19" s="83" t="inlineStr">
         <is>
           <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
@@ -2431,7 +2449,7 @@
           <t>PS5-03-07</t>
         </is>
       </c>
-      <c r="B20" s="79" t="inlineStr">
+      <c r="B20" s="83" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -2442,7 +2460,7 @@
       <c r="D20" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="91" t="inlineStr">
+      <c r="E20" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2500,7 +2518,7 @@
           <t>PS5-03-08</t>
         </is>
       </c>
-      <c r="B21" s="79" t="inlineStr">
+      <c r="B21" s="83" t="inlineStr">
         <is>
           <t>PS5-03-08 - FZ-08 - Utilities - Power Generation Area - External</t>
         </is>
@@ -2511,7 +2529,7 @@
       <c r="D21" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="91" t="inlineStr">
+      <c r="E21" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2569,7 +2587,7 @@
           <t>PS5-03-09</t>
         </is>
       </c>
-      <c r="B22" s="79" t="inlineStr">
+      <c r="B22" s="83" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -2580,7 +2598,7 @@
       <c r="D22" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="69" t="inlineStr">
+      <c r="E22" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2638,7 +2656,7 @@
           <t>PS5-03-10</t>
         </is>
       </c>
-      <c r="B23" s="79" t="inlineStr">
+      <c r="B23" s="83" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -2649,7 +2667,7 @@
       <c r="D23" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="91" t="inlineStr">
+      <c r="E23" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2707,7 +2725,7 @@
           <t>PS5-03-11</t>
         </is>
       </c>
-      <c r="B24" s="79" t="inlineStr">
+      <c r="B24" s="83" t="inlineStr">
         <is>
           <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
@@ -2718,7 +2736,7 @@
       <c r="D24" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="91" t="inlineStr">
+      <c r="E24" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2776,7 +2794,7 @@
           <t>PS5-03-12</t>
         </is>
       </c>
-      <c r="B25" s="79" t="inlineStr">
+      <c r="B25" s="83" t="inlineStr">
         <is>
           <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
@@ -2787,7 +2805,7 @@
       <c r="D25" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="91" t="inlineStr">
+      <c r="E25" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2845,7 +2863,7 @@
           <t>PS5-03-13</t>
         </is>
       </c>
-      <c r="B26" s="79" t="inlineStr">
+      <c r="B26" s="83" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -2856,7 +2874,7 @@
       <c r="D26" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="91" t="inlineStr">
+      <c r="E26" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2914,7 +2932,7 @@
           <t>PS5-03-14</t>
         </is>
       </c>
-      <c r="B27" s="79" t="inlineStr">
+      <c r="B27" s="83" t="inlineStr">
         <is>
           <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
@@ -2925,7 +2943,7 @@
       <c r="D27" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="69" t="inlineStr">
+      <c r="E27" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2936,7 +2954,7 @@
       <c r="G27" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H27" s="69" t="inlineStr">
+      <c r="H27" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2966,7 +2984,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N27" s="69" t="inlineStr">
+      <c r="N27" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2983,7 +3001,7 @@
           <t>PS5-03-15</t>
         </is>
       </c>
-      <c r="B28" s="79" t="inlineStr">
+      <c r="B28" s="83" t="inlineStr">
         <is>
           <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
@@ -2994,7 +3012,7 @@
       <c r="D28" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="91" t="inlineStr">
+      <c r="E28" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3005,7 +3023,7 @@
       <c r="G28" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="69" t="inlineStr">
+      <c r="H28" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3035,7 +3053,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N28" s="69" t="inlineStr">
+      <c r="N28" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3052,7 +3070,7 @@
           <t>PS5-03-16</t>
         </is>
       </c>
-      <c r="B29" s="79" t="inlineStr">
+      <c r="B29" s="83" t="inlineStr">
         <is>
           <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
@@ -3063,7 +3081,7 @@
       <c r="D29" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="91" t="inlineStr">
+      <c r="E29" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3074,7 +3092,7 @@
       <c r="G29" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="69" t="inlineStr">
+      <c r="H29" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3104,7 +3122,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N29" s="69" t="inlineStr">
+      <c r="N29" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3121,7 +3139,7 @@
           <t>PS5-03-17</t>
         </is>
       </c>
-      <c r="B30" s="79" t="inlineStr">
+      <c r="B30" s="83" t="inlineStr">
         <is>
           <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
@@ -3132,7 +3150,7 @@
       <c r="D30" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="91" t="inlineStr">
+      <c r="E30" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3143,7 +3161,7 @@
       <c r="G30" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="69" t="inlineStr">
+      <c r="H30" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3173,7 +3191,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N30" s="69" t="inlineStr">
+      <c r="N30" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3190,7 +3208,7 @@
           <t>PS5-03-18</t>
         </is>
       </c>
-      <c r="B31" s="79" t="inlineStr">
+      <c r="B31" s="83" t="inlineStr">
         <is>
           <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
@@ -3201,7 +3219,7 @@
       <c r="D31" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="91" t="inlineStr">
+      <c r="E31" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3212,7 +3230,7 @@
       <c r="G31" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="69" t="inlineStr">
+      <c r="H31" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3242,7 +3260,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N31" s="69" t="inlineStr">
+      <c r="N31" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3259,7 +3277,7 @@
           <t>PS5-03-19</t>
         </is>
       </c>
-      <c r="B32" s="79" t="inlineStr">
+      <c r="B32" s="83" t="inlineStr">
         <is>
           <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
@@ -3270,7 +3288,7 @@
       <c r="D32" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="91" t="inlineStr">
+      <c r="E32" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3281,7 +3299,7 @@
       <c r="G32" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="69" t="inlineStr">
+      <c r="H32" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3311,7 +3329,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N32" s="69" t="inlineStr">
+      <c r="N32" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3328,7 +3346,7 @@
           <t>PS5-03-20</t>
         </is>
       </c>
-      <c r="B33" s="79" t="inlineStr">
+      <c r="B33" s="83" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -3339,7 +3357,7 @@
       <c r="D33" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="69" t="inlineStr">
+      <c r="E33" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3387,7 +3405,7 @@
       </c>
       <c r="O33" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>07-Aug-26</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3415,7 @@
           <t>PS5-03-21</t>
         </is>
       </c>
-      <c r="B34" s="79" t="inlineStr">
+      <c r="B34" s="83" t="inlineStr">
         <is>
           <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
@@ -3408,7 +3426,7 @@
       <c r="D34" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="91" t="inlineStr">
+      <c r="E34" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3419,7 +3437,7 @@
       <c r="G34" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="69" t="inlineStr">
+      <c r="H34" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3449,7 +3467,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N34" s="69" t="inlineStr">
+      <c r="N34" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3466,7 +3484,7 @@
           <t>PS5-03-22</t>
         </is>
       </c>
-      <c r="B35" s="79" t="inlineStr">
+      <c r="B35" s="83" t="inlineStr">
         <is>
           <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
@@ -3477,7 +3495,7 @@
       <c r="D35" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="91" t="inlineStr">
+      <c r="E35" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3488,7 +3506,7 @@
       <c r="G35" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="69" t="inlineStr">
+      <c r="H35" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3518,7 +3536,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N35" s="69" t="inlineStr">
+      <c r="N35" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3535,7 +3553,7 @@
           <t>PS5-03-23</t>
         </is>
       </c>
-      <c r="B36" s="79" t="inlineStr">
+      <c r="B36" s="83" t="inlineStr">
         <is>
           <t>PS5-03-23 - FZ-E1 to E3 - EITS Building</t>
         </is>
@@ -3546,7 +3564,7 @@
       <c r="D36" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="69" t="inlineStr">
+      <c r="E36" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3557,7 +3575,7 @@
       <c r="G36" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="91" t="inlineStr">
+      <c r="H36" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3604,7 +3622,7 @@
           <t>PS5-03-24</t>
         </is>
       </c>
-      <c r="B37" s="79" t="inlineStr">
+      <c r="B37" s="83" t="inlineStr">
         <is>
           <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
@@ -3615,7 +3633,7 @@
       <c r="D37" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="91" t="inlineStr">
+      <c r="E37" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3626,7 +3644,7 @@
       <c r="G37" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="69" t="inlineStr">
+      <c r="H37" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3656,7 +3674,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N37" s="69" t="inlineStr">
+      <c r="N37" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3673,7 +3691,7 @@
           <t>PS5-03-25</t>
         </is>
       </c>
-      <c r="B38" s="79" t="inlineStr">
+      <c r="B38" s="83" t="inlineStr">
         <is>
           <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
@@ -3684,7 +3702,7 @@
       <c r="D38" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="91" t="inlineStr">
+      <c r="E38" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3695,7 +3713,7 @@
       <c r="G38" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="69" t="inlineStr">
+      <c r="H38" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3725,7 +3743,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N38" s="69" t="inlineStr">
+      <c r="N38" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3742,7 +3760,7 @@
           <t>PS5-04-01</t>
         </is>
       </c>
-      <c r="B39" s="79" t="inlineStr">
+      <c r="B39" s="83" t="inlineStr">
         <is>
           <t>PS5-04-01 - Office Building PCS System</t>
         </is>
@@ -3753,7 +3771,7 @@
       <c r="D39" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="91" t="inlineStr">
+      <c r="E39" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3764,7 +3782,7 @@
       <c r="G39" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="91" t="inlineStr">
+      <c r="H39" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3794,7 +3812,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N39" s="69" t="inlineStr">
+      <c r="N39" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3811,7 +3829,7 @@
           <t>PS5-04-02</t>
         </is>
       </c>
-      <c r="B40" s="79" t="inlineStr">
+      <c r="B40" s="83" t="inlineStr">
         <is>
           <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
@@ -3822,7 +3840,7 @@
       <c r="D40" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="91" t="inlineStr">
+      <c r="E40" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3833,7 +3851,7 @@
       <c r="G40" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="69" t="inlineStr">
+      <c r="H40" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3863,7 +3881,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N40" s="69" t="inlineStr">
+      <c r="N40" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3880,7 +3898,7 @@
           <t>PS5-04-03</t>
         </is>
       </c>
-      <c r="B41" s="79" t="inlineStr">
+      <c r="B41" s="83" t="inlineStr">
         <is>
           <t>PS5-04-03 - 33kV ICSS System</t>
         </is>
@@ -3891,7 +3909,7 @@
       <c r="D41" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="68" t="inlineStr">
+      <c r="E41" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -3902,7 +3920,7 @@
       <c r="G41" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="91" t="inlineStr">
+      <c r="H41" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3949,7 +3967,7 @@
           <t>PS5-04-04</t>
         </is>
       </c>
-      <c r="B42" s="79" t="inlineStr">
+      <c r="B42" s="83" t="inlineStr">
         <is>
           <t>PS5-04-04 - 33kV PCS System</t>
         </is>
@@ -3960,7 +3978,7 @@
       <c r="D42" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="E42" s="68" t="inlineStr">
+      <c r="E42" s="69" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -3971,7 +3989,7 @@
       <c r="G42" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="91" t="inlineStr">
+      <c r="H42" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4018,7 +4036,7 @@
           <t>PS5-04-05</t>
         </is>
       </c>
-      <c r="B43" s="79" t="inlineStr">
+      <c r="B43" s="83" t="inlineStr">
         <is>
           <t>PS5-04-05 - 33kV SIS/FGS System</t>
         </is>
@@ -4040,7 +4058,7 @@
       <c r="G43" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="91" t="inlineStr">
+      <c r="H43" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4070,7 +4088,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N43" s="68" t="inlineStr">
+      <c r="N43" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -4087,7 +4105,7 @@
           <t>PS5-05-01</t>
         </is>
       </c>
-      <c r="B44" s="79" t="inlineStr">
+      <c r="B44" s="83" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -4144,9 +4162,9 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O44" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="O44" s="69" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4174,7 @@
           <t>PS5-05-02</t>
         </is>
       </c>
-      <c r="B45" s="79" t="inlineStr">
+      <c r="B45" s="83" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -4167,7 +4185,7 @@
       <c r="D45" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="69" t="inlineStr">
+      <c r="E45" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4213,9 +4231,9 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O45" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="O45" s="54" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4243,7 @@
           <t>PS5-06-01</t>
         </is>
       </c>
-      <c r="B46" s="79" t="inlineStr">
+      <c r="B46" s="83" t="inlineStr">
         <is>
           <t>PS5-06-01 - AC UPS - EITS Building</t>
         </is>
@@ -4236,7 +4254,7 @@
       <c r="D46" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E46" s="68" t="inlineStr">
+      <c r="E46" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -4247,7 +4265,7 @@
       <c r="G46" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="91" t="inlineStr">
+      <c r="H46" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4277,7 +4295,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N46" s="68" t="inlineStr">
+      <c r="N46" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -4294,7 +4312,7 @@
           <t>PS5-06-02</t>
         </is>
       </c>
-      <c r="B47" s="79" t="inlineStr">
+      <c r="B47" s="83" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -4305,7 +4323,7 @@
       <c r="D47" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E47" s="69" t="inlineStr">
+      <c r="E47" s="70" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -4363,7 +4381,7 @@
           <t>PS5-06-03</t>
         </is>
       </c>
-      <c r="B48" s="79" t="inlineStr">
+      <c r="B48" s="83" t="inlineStr">
         <is>
           <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
@@ -4374,7 +4392,7 @@
       <c r="D48" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="91" t="inlineStr">
+      <c r="E48" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4385,7 +4403,7 @@
       <c r="G48" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="69" t="inlineStr">
+      <c r="H48" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4415,7 +4433,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N48" s="69" t="inlineStr">
+      <c r="N48" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4432,7 +4450,7 @@
           <t>PS5-06-04</t>
         </is>
       </c>
-      <c r="B49" s="79" t="inlineStr">
+      <c r="B49" s="83" t="inlineStr">
         <is>
           <t>PS5-06-04 - AC UPS - Guard House</t>
         </is>
@@ -4443,7 +4461,7 @@
       <c r="D49" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E49" s="91" t="inlineStr">
+      <c r="E49" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4454,7 +4472,7 @@
       <c r="G49" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="69" t="inlineStr">
+      <c r="H49" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4484,7 +4502,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N49" s="69" t="inlineStr">
+      <c r="N49" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4501,7 +4519,7 @@
           <t>PS5-06-05</t>
         </is>
       </c>
-      <c r="B50" s="79" t="inlineStr">
+      <c r="B50" s="83" t="inlineStr">
         <is>
           <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
@@ -4512,7 +4530,7 @@
       <c r="D50" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="91" t="inlineStr">
+      <c r="E50" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4523,7 +4541,7 @@
       <c r="G50" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="69" t="inlineStr">
+      <c r="H50" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4553,7 +4571,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N50" s="69" t="inlineStr">
+      <c r="N50" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4570,7 +4588,7 @@
           <t>PS5-08-01</t>
         </is>
       </c>
-      <c r="B51" s="79" t="inlineStr">
+      <c r="B51" s="83" t="inlineStr">
         <is>
           <t>PS5-08-01 - PAGA</t>
         </is>
@@ -4581,7 +4599,7 @@
       <c r="D51" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="69" t="inlineStr">
+      <c r="E51" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4592,7 +4610,7 @@
       <c r="G51" s="23" t="n">
         <v>82</v>
       </c>
-      <c r="H51" s="69" t="inlineStr">
+      <c r="H51" s="70" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -4622,7 +4640,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N51" s="69" t="inlineStr">
+      <c r="N51" s="70" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -4639,7 +4657,7 @@
           <t>PS5-08-03</t>
         </is>
       </c>
-      <c r="B52" s="79" t="inlineStr">
+      <c r="B52" s="83" t="inlineStr">
         <is>
           <t>PS5-08-03 - Telephone</t>
         </is>
@@ -4650,7 +4668,7 @@
       <c r="D52" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="91" t="inlineStr">
+      <c r="E52" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4661,7 +4679,7 @@
       <c r="G52" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H52" s="69" t="inlineStr">
+      <c r="H52" s="70" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -4691,7 +4709,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N52" s="69" t="inlineStr">
+      <c r="N52" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -4708,7 +4726,7 @@
           <t>PS5-08-04</t>
         </is>
       </c>
-      <c r="B53" s="79" t="inlineStr">
+      <c r="B53" s="83" t="inlineStr">
         <is>
           <t>PS5-08-04 - Hotline</t>
         </is>
@@ -4719,7 +4737,7 @@
       <c r="D53" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="91" t="inlineStr">
+      <c r="E53" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4730,7 +4748,7 @@
       <c r="G53" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="91" t="inlineStr">
+      <c r="H53" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4760,7 +4778,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N53" s="69" t="inlineStr">
+      <c r="N53" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4777,7 +4795,7 @@
           <t>PS5-08-07</t>
         </is>
       </c>
-      <c r="B54" s="79" t="inlineStr">
+      <c r="B54" s="83" t="inlineStr">
         <is>
           <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
@@ -4788,7 +4806,7 @@
       <c r="D54" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="91" t="inlineStr">
+      <c r="E54" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4799,7 +4817,7 @@
       <c r="G54" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="91" t="inlineStr">
+      <c r="H54" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4829,7 +4847,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N54" s="69" t="inlineStr">
+      <c r="N54" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4846,7 +4864,7 @@
           <t>PS5-08-11</t>
         </is>
       </c>
-      <c r="B55" s="79" t="inlineStr">
+      <c r="B55" s="83" t="inlineStr">
         <is>
           <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
@@ -4857,7 +4875,7 @@
       <c r="D55" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E55" s="69" t="inlineStr">
+      <c r="E55" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4868,7 +4886,7 @@
       <c r="G55" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H55" s="69" t="inlineStr">
+      <c r="H55" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4898,7 +4916,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N55" s="69" t="inlineStr">
+      <c r="N55" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4915,7 +4933,7 @@
           <t>PS5-08-12</t>
         </is>
       </c>
-      <c r="B56" s="79" t="inlineStr">
+      <c r="B56" s="83" t="inlineStr">
         <is>
           <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
@@ -4926,7 +4944,7 @@
       <c r="D56" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="91" t="inlineStr">
+      <c r="E56" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4937,7 +4955,7 @@
       <c r="G56" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="69" t="inlineStr">
+      <c r="H56" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4967,7 +4985,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N56" s="69" t="inlineStr">
+      <c r="N56" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4984,7 +5002,7 @@
           <t>PS5-08-13</t>
         </is>
       </c>
-      <c r="B57" s="79" t="inlineStr">
+      <c r="B57" s="83" t="inlineStr">
         <is>
           <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
@@ -4995,7 +5013,7 @@
       <c r="D57" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="68" t="inlineStr">
+      <c r="E57" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -5006,7 +5024,7 @@
       <c r="G57" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="69" t="inlineStr">
+      <c r="H57" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5036,7 +5054,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N57" s="69" t="inlineStr">
+      <c r="N57" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5053,7 +5071,7 @@
           <t>PS5-08-14</t>
         </is>
       </c>
-      <c r="B58" s="79" t="inlineStr">
+      <c r="B58" s="83" t="inlineStr">
         <is>
           <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
@@ -5064,7 +5082,7 @@
       <c r="D58" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E58" s="91" t="inlineStr">
+      <c r="E58" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5075,7 +5093,7 @@
       <c r="G58" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="69" t="inlineStr">
+      <c r="H58" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5105,7 +5123,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N58" s="69" t="inlineStr">
+      <c r="N58" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5122,7 +5140,7 @@
           <t>PS5-08-15</t>
         </is>
       </c>
-      <c r="B59" s="79" t="inlineStr">
+      <c r="B59" s="83" t="inlineStr">
         <is>
           <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
@@ -5133,7 +5151,7 @@
       <c r="D59" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E59" s="69" t="inlineStr">
+      <c r="E59" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -5144,7 +5162,7 @@
       <c r="G59" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="69" t="inlineStr">
+      <c r="H59" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5174,7 +5192,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N59" s="69" t="inlineStr">
+      <c r="N59" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5191,7 +5209,7 @@
           <t>PS5-08-23</t>
         </is>
       </c>
-      <c r="B60" s="79" t="inlineStr">
+      <c r="B60" s="83" t="inlineStr">
         <is>
           <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
@@ -5202,7 +5220,7 @@
       <c r="D60" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="69" t="inlineStr">
+      <c r="E60" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5213,7 +5231,7 @@
       <c r="G60" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="69" t="inlineStr">
+      <c r="H60" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5243,7 +5261,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N60" s="69" t="inlineStr">
+      <c r="N60" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5260,7 +5278,7 @@
           <t>PS5-08-34</t>
         </is>
       </c>
-      <c r="B61" s="79" t="inlineStr">
+      <c r="B61" s="83" t="inlineStr">
         <is>
           <t>PS5-08-34 - Satphone</t>
         </is>
@@ -5271,7 +5289,7 @@
       <c r="D61" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E61" s="91" t="inlineStr">
+      <c r="E61" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5282,7 +5300,7 @@
       <c r="G61" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="69" t="inlineStr">
+      <c r="H61" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5312,7 +5330,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N61" s="69" t="inlineStr">
+      <c r="N61" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5329,7 +5347,7 @@
           <t>PS5-08-35</t>
         </is>
       </c>
-      <c r="B62" s="79" t="inlineStr">
+      <c r="B62" s="83" t="inlineStr">
         <is>
           <t>PS5-08-35 - Optical Transport Network</t>
         </is>
@@ -5340,7 +5358,7 @@
       <c r="D62" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E62" s="69" t="inlineStr">
+      <c r="E62" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5351,7 +5369,7 @@
       <c r="G62" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="91" t="inlineStr">
+      <c r="H62" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5381,7 +5399,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N62" s="68" t="inlineStr">
+      <c r="N62" s="69" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -5398,7 +5416,7 @@
           <t>PS5-08-36</t>
         </is>
       </c>
-      <c r="B63" s="79" t="inlineStr">
+      <c r="B63" s="83" t="inlineStr">
         <is>
           <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
@@ -5409,7 +5427,7 @@
       <c r="D63" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E63" s="91" t="inlineStr">
+      <c r="E63" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5420,7 +5438,7 @@
       <c r="G63" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="69" t="inlineStr">
+      <c r="H63" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5450,7 +5468,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N63" s="69" t="inlineStr">
+      <c r="N63" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5467,7 +5485,7 @@
           <t>PS5-08-51</t>
         </is>
       </c>
-      <c r="B64" s="79" t="inlineStr">
+      <c r="B64" s="83" t="inlineStr">
         <is>
           <t>PS5-08-51 - Entertainment</t>
         </is>
@@ -5478,7 +5496,7 @@
       <c r="D64" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="91" t="inlineStr">
+      <c r="E64" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5489,7 +5507,7 @@
       <c r="G64" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H64" s="69" t="inlineStr">
+      <c r="H64" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5519,7 +5537,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N64" s="69" t="inlineStr">
+      <c r="N64" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5536,7 +5554,7 @@
           <t>PS5-08-52</t>
         </is>
       </c>
-      <c r="B65" s="79" t="inlineStr">
+      <c r="B65" s="83" t="inlineStr">
         <is>
           <t>PS5-08-52 - Process &amp; Security CCTV</t>
         </is>
@@ -5547,7 +5565,7 @@
       <c r="D65" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="91" t="inlineStr">
+      <c r="E65" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5558,7 +5576,7 @@
       <c r="G65" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="H65" s="69" t="inlineStr">
+      <c r="H65" s="70" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -5588,7 +5606,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N65" s="69" t="inlineStr">
+      <c r="N65" s="70" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -5605,7 +5623,7 @@
           <t>PS5-08-55</t>
         </is>
       </c>
-      <c r="B66" s="79" t="inlineStr">
+      <c r="B66" s="83" t="inlineStr">
         <is>
           <t>PS5-08-55 - Videoconference</t>
         </is>
@@ -5616,7 +5634,7 @@
       <c r="D66" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="91" t="inlineStr">
+      <c r="E66" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5627,7 +5645,7 @@
       <c r="G66" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H66" s="91" t="inlineStr">
+      <c r="H66" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5657,7 +5675,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N66" s="69" t="inlineStr">
+      <c r="N66" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5674,7 +5692,7 @@
           <t>PS5-08-61</t>
         </is>
       </c>
-      <c r="B67" s="79" t="inlineStr">
+      <c r="B67" s="83" t="inlineStr">
         <is>
           <t>PS5-08-61 - Meteocean</t>
         </is>
@@ -5685,7 +5703,7 @@
       <c r="D67" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="91" t="inlineStr">
+      <c r="E67" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5696,7 +5714,7 @@
       <c r="G67" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H67" s="69" t="inlineStr">
+      <c r="H67" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5726,7 +5744,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N67" s="69" t="inlineStr">
+      <c r="N67" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5743,7 +5761,7 @@
           <t>PS5-08-71</t>
         </is>
       </c>
-      <c r="B68" s="79" t="inlineStr">
+      <c r="B68" s="83" t="inlineStr">
         <is>
           <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
@@ -5754,7 +5772,7 @@
       <c r="D68" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E68" s="91" t="inlineStr">
+      <c r="E68" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5765,7 +5783,7 @@
       <c r="G68" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H68" s="69" t="inlineStr">
+      <c r="H68" s="70" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -5795,7 +5813,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N68" s="69" t="inlineStr">
+      <c r="N68" s="70" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -5812,7 +5830,7 @@
           <t>PS5-08-72</t>
         </is>
       </c>
-      <c r="B69" s="79" t="inlineStr">
+      <c r="B69" s="83" t="inlineStr">
         <is>
           <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
@@ -5823,7 +5841,7 @@
       <c r="D69" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E69" s="91" t="inlineStr">
+      <c r="E69" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5834,7 +5852,7 @@
       <c r="G69" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="69" t="inlineStr">
+      <c r="H69" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5864,7 +5882,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N69" s="69" t="inlineStr">
+      <c r="N69" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5881,7 +5899,7 @@
           <t>PS5-08-81</t>
         </is>
       </c>
-      <c r="B70" s="79" t="inlineStr">
+      <c r="B70" s="83" t="inlineStr">
         <is>
           <t>PS5-08-81 - Guard tour</t>
         </is>
@@ -5892,7 +5910,7 @@
       <c r="D70" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E70" s="91" t="inlineStr">
+      <c r="E70" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5903,7 +5921,7 @@
       <c r="G70" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H70" s="91" t="inlineStr">
+      <c r="H70" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5933,7 +5951,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N70" s="69" t="inlineStr">
+      <c r="N70" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5950,7 +5968,7 @@
           <t>PS5-08-82</t>
         </is>
       </c>
-      <c r="B71" s="79" t="inlineStr">
+      <c r="B71" s="83" t="inlineStr">
         <is>
           <t>PS5-08-82 - Key Management</t>
         </is>
@@ -5961,7 +5979,7 @@
       <c r="D71" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E71" s="91" t="inlineStr">
+      <c r="E71" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5972,7 +5990,7 @@
       <c r="G71" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H71" s="91" t="inlineStr">
+      <c r="H71" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6002,7 +6020,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N71" s="69" t="inlineStr">
+      <c r="N71" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6019,7 +6037,7 @@
           <t>PS5-08-83</t>
         </is>
       </c>
-      <c r="B72" s="79" t="inlineStr">
+      <c r="B72" s="83" t="inlineStr">
         <is>
           <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
@@ -6030,7 +6048,7 @@
       <c r="D72" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="91" t="inlineStr">
+      <c r="E72" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6041,7 +6059,7 @@
       <c r="G72" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="69" t="inlineStr">
+      <c r="H72" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6071,7 +6089,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N72" s="69" t="inlineStr">
+      <c r="N72" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6088,7 +6106,7 @@
           <t>PS5-08-85</t>
         </is>
       </c>
-      <c r="B73" s="79" t="inlineStr">
+      <c r="B73" s="83" t="inlineStr">
         <is>
           <t>PS5-08-85 - Access Control, POB &amp; e-Mustering</t>
         </is>
@@ -6110,7 +6128,7 @@
       <c r="G73" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="H73" s="69" t="inlineStr">
+      <c r="H73" s="70" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -6140,7 +6158,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N73" s="69" t="inlineStr">
+      <c r="N73" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -6157,7 +6175,7 @@
           <t>PS5-08-86</t>
         </is>
       </c>
-      <c r="B74" s="79" t="inlineStr">
+      <c r="B74" s="83" t="inlineStr">
         <is>
           <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
@@ -6168,7 +6186,7 @@
       <c r="D74" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="91" t="inlineStr">
+      <c r="E74" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6179,7 +6197,7 @@
       <c r="G74" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="91" t="inlineStr">
+      <c r="H74" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6209,7 +6227,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N74" s="69" t="inlineStr">
+      <c r="N74" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6226,7 +6244,7 @@
           <t>PS5-08-92</t>
         </is>
       </c>
-      <c r="B75" s="79" t="inlineStr">
+      <c r="B75" s="83" t="inlineStr">
         <is>
           <t>PS5-08-92 - Telecom Mast</t>
         </is>
@@ -6237,7 +6255,7 @@
       <c r="D75" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E75" s="91" t="inlineStr">
+      <c r="E75" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6248,7 +6266,7 @@
       <c r="G75" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H75" s="91" t="inlineStr">
+      <c r="H75" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6278,7 +6296,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N75" s="69" t="inlineStr">
+      <c r="N75" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6295,7 +6313,7 @@
           <t>PS5-08-93</t>
         </is>
       </c>
-      <c r="B76" s="79" t="inlineStr">
+      <c r="B76" s="83" t="inlineStr">
         <is>
           <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
@@ -6306,7 +6324,7 @@
       <c r="D76" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E76" s="91" t="inlineStr">
+      <c r="E76" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6317,7 +6335,7 @@
       <c r="G76" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H76" s="69" t="inlineStr">
+      <c r="H76" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6347,7 +6365,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N76" s="69" t="inlineStr">
+      <c r="N76" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6364,7 +6382,7 @@
           <t>PS5-09-01</t>
         </is>
       </c>
-      <c r="B77" s="79" t="inlineStr">
+      <c r="B77" s="83" t="inlineStr">
         <is>
           <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
@@ -6375,7 +6393,7 @@
       <c r="D77" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="91" t="inlineStr">
+      <c r="E77" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6386,7 +6404,7 @@
       <c r="G77" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H77" s="69" t="inlineStr">
+      <c r="H77" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6416,7 +6434,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N77" s="69" t="inlineStr">
+      <c r="N77" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6433,7 +6451,7 @@
           <t>PS5-09-02</t>
         </is>
       </c>
-      <c r="B78" s="79" t="inlineStr">
+      <c r="B78" s="83" t="inlineStr">
         <is>
           <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
@@ -6444,7 +6462,7 @@
       <c r="D78" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E78" s="91" t="inlineStr">
+      <c r="E78" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6455,7 +6473,7 @@
       <c r="G78" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H78" s="69" t="inlineStr">
+      <c r="H78" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6485,7 +6503,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N78" s="69" t="inlineStr">
+      <c r="N78" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6502,7 +6520,7 @@
           <t>PS5-09-03</t>
         </is>
       </c>
-      <c r="B79" s="79" t="inlineStr">
+      <c r="B79" s="83" t="inlineStr">
         <is>
           <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
@@ -6513,7 +6531,7 @@
       <c r="D79" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E79" s="69" t="inlineStr">
+      <c r="E79" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -6524,7 +6542,7 @@
       <c r="G79" s="23" t="n">
         <v>53</v>
       </c>
-      <c r="H79" s="69" t="inlineStr">
+      <c r="H79" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -6554,7 +6572,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N79" s="69" t="inlineStr">
+      <c r="N79" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -6571,7 +6589,7 @@
           <t>PS5-09-04</t>
         </is>
       </c>
-      <c r="B80" s="79" t="inlineStr">
+      <c r="B80" s="83" t="inlineStr">
         <is>
           <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
@@ -6582,7 +6600,7 @@
       <c r="D80" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E80" s="91" t="inlineStr">
+      <c r="E80" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6593,7 +6611,7 @@
       <c r="G80" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="69" t="inlineStr">
+      <c r="H80" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6623,7 +6641,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N80" s="69" t="inlineStr">
+      <c r="N80" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6640,7 +6658,7 @@
           <t>PS5-09-05</t>
         </is>
       </c>
-      <c r="B81" s="79" t="inlineStr">
+      <c r="B81" s="83" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -6651,7 +6669,7 @@
       <c r="D81" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="E81" s="68" t="inlineStr">
+      <c r="E81" s="69" t="inlineStr">
         <is>
           <t>56%</t>
         </is>
@@ -6709,7 +6727,7 @@
           <t>PS5-0H-01</t>
         </is>
       </c>
-      <c r="B82" s="79" t="inlineStr">
+      <c r="B82" s="83" t="inlineStr">
         <is>
           <t>PS5-0H-01 - HIPPS</t>
         </is>
@@ -6720,7 +6738,7 @@
       <c r="D82" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E82" s="69" t="inlineStr">
+      <c r="E82" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -6731,7 +6749,7 @@
       <c r="G82" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="91" t="inlineStr">
+      <c r="H82" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6761,7 +6779,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N82" s="68" t="inlineStr">
+      <c r="N82" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -6778,7 +6796,7 @@
           <t>PS5-25-01</t>
         </is>
       </c>
-      <c r="B83" s="79" t="inlineStr">
+      <c r="B83" s="83" t="inlineStr">
         <is>
           <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
@@ -6789,7 +6807,7 @@
       <c r="D83" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E83" s="69" t="inlineStr">
+      <c r="E83" s="70" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -6800,7 +6818,7 @@
       <c r="G83" s="23" t="n">
         <v>111</v>
       </c>
-      <c r="H83" s="68" t="inlineStr">
+      <c r="H83" s="69" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -6830,7 +6848,7 @@
           <t>42/46</t>
         </is>
       </c>
-      <c r="N83" s="68" t="inlineStr">
+      <c r="N83" s="69" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -6847,7 +6865,7 @@
           <t>PS5-25-02</t>
         </is>
       </c>
-      <c r="B84" s="79" t="inlineStr">
+      <c r="B84" s="83" t="inlineStr">
         <is>
           <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
@@ -6858,7 +6876,7 @@
       <c r="D84" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="E84" s="69" t="inlineStr">
+      <c r="E84" s="70" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -6869,7 +6887,7 @@
       <c r="G84" s="23" t="n">
         <v>175</v>
       </c>
-      <c r="H84" s="68" t="inlineStr">
+      <c r="H84" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -6899,7 +6917,7 @@
           <t>23/24</t>
         </is>
       </c>
-      <c r="N84" s="68" t="inlineStr">
+      <c r="N84" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -6916,7 +6934,7 @@
           <t>PS5-25-03</t>
         </is>
       </c>
-      <c r="B85" s="79" t="inlineStr">
+      <c r="B85" s="83" t="inlineStr">
         <is>
           <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
@@ -6927,7 +6945,7 @@
       <c r="D85" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="E85" s="69" t="inlineStr">
+      <c r="E85" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -6938,7 +6956,7 @@
       <c r="G85" s="23" t="n">
         <v>164</v>
       </c>
-      <c r="H85" s="68" t="inlineStr">
+      <c r="H85" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -6968,7 +6986,7 @@
           <t>23/24</t>
         </is>
       </c>
-      <c r="N85" s="68" t="inlineStr">
+      <c r="N85" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -6985,7 +7003,7 @@
           <t>PS5-25-04</t>
         </is>
       </c>
-      <c r="B86" s="79" t="inlineStr">
+      <c r="B86" s="83" t="inlineStr">
         <is>
           <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
@@ -6996,7 +7014,7 @@
       <c r="D86" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E86" s="69" t="inlineStr">
+      <c r="E86" s="70" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -7007,7 +7025,7 @@
       <c r="G86" s="23" t="n">
         <v>161</v>
       </c>
-      <c r="H86" s="68" t="inlineStr">
+      <c r="H86" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -7037,7 +7055,7 @@
           <t>23/24</t>
         </is>
       </c>
-      <c r="N86" s="68" t="inlineStr">
+      <c r="N86" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -7054,7 +7072,7 @@
           <t>PS5-25-05</t>
         </is>
       </c>
-      <c r="B87" s="79" t="inlineStr">
+      <c r="B87" s="83" t="inlineStr">
         <is>
           <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
@@ -7076,7 +7094,7 @@
       <c r="G87" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H87" s="68" t="inlineStr">
+      <c r="H87" s="69" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
@@ -7106,7 +7124,7 @@
           <t>8/9</t>
         </is>
       </c>
-      <c r="N87" s="68" t="inlineStr">
+      <c r="N87" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -7123,7 +7141,7 @@
           <t>PS5-25-06</t>
         </is>
       </c>
-      <c r="B88" s="79" t="inlineStr">
+      <c r="B88" s="83" t="inlineStr">
         <is>
           <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
@@ -7134,7 +7152,7 @@
       <c r="D88" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E88" s="69" t="inlineStr">
+      <c r="E88" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7145,7 +7163,7 @@
       <c r="G88" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H88" s="68" t="inlineStr">
+      <c r="H88" s="69" t="inlineStr">
         <is>
           <t>59%</t>
         </is>
@@ -7175,7 +7193,7 @@
           <t>17/19</t>
         </is>
       </c>
-      <c r="N88" s="68" t="inlineStr">
+      <c r="N88" s="69" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -7192,7 +7210,7 @@
           <t>PS5-25-07</t>
         </is>
       </c>
-      <c r="B89" s="79" t="inlineStr">
+      <c r="B89" s="83" t="inlineStr">
         <is>
           <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
@@ -7203,7 +7221,7 @@
       <c r="D89" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E89" s="69" t="inlineStr">
+      <c r="E89" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -7214,7 +7232,7 @@
       <c r="G89" s="23" t="n">
         <v>103</v>
       </c>
-      <c r="H89" s="68" t="inlineStr">
+      <c r="H89" s="69" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -7244,7 +7262,7 @@
           <t>33/35</t>
         </is>
       </c>
-      <c r="N89" s="68" t="inlineStr">
+      <c r="N89" s="69" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -7261,7 +7279,7 @@
           <t>PS5-28-01</t>
         </is>
       </c>
-      <c r="B90" s="79" t="inlineStr">
+      <c r="B90" s="83" t="inlineStr">
         <is>
           <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
@@ -7272,7 +7290,7 @@
       <c r="D90" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E90" s="91" t="inlineStr">
+      <c r="E90" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7283,7 +7301,7 @@
       <c r="G90" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H90" s="68" t="inlineStr">
+      <c r="H90" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -7313,7 +7331,7 @@
           <t>12/14</t>
         </is>
       </c>
-      <c r="N90" s="68" t="inlineStr">
+      <c r="N90" s="69" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -7330,7 +7348,7 @@
           <t>PS5-28-02</t>
         </is>
       </c>
-      <c r="B91" s="79" t="inlineStr">
+      <c r="B91" s="83" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -7341,7 +7359,7 @@
       <c r="D91" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E91" s="69" t="inlineStr">
+      <c r="E91" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7399,7 +7417,7 @@
           <t>PS5-28-03</t>
         </is>
       </c>
-      <c r="B92" s="79" t="inlineStr">
+      <c r="B92" s="83" t="inlineStr">
         <is>
           <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
@@ -7410,7 +7428,7 @@
       <c r="D92" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E92" s="69" t="inlineStr">
+      <c r="E92" s="70" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -7421,7 +7439,7 @@
       <c r="G92" s="23" t="n">
         <v>93</v>
       </c>
-      <c r="H92" s="68" t="inlineStr">
+      <c r="H92" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -7451,7 +7469,7 @@
           <t>54/56</t>
         </is>
       </c>
-      <c r="N92" s="68" t="inlineStr">
+      <c r="N92" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -7468,7 +7486,7 @@
           <t>PS5-28-04</t>
         </is>
       </c>
-      <c r="B93" s="79" t="inlineStr">
+      <c r="B93" s="83" t="inlineStr">
         <is>
           <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
@@ -7479,7 +7497,7 @@
       <c r="D93" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E93" s="69" t="inlineStr">
+      <c r="E93" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -7537,7 +7555,7 @@
           <t>PS5-28-05</t>
         </is>
       </c>
-      <c r="B94" s="79" t="inlineStr">
+      <c r="B94" s="83" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -7548,7 +7566,7 @@
       <c r="D94" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E94" s="69" t="inlineStr">
+      <c r="E94" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7606,7 +7624,7 @@
           <t>PS5-28-06</t>
         </is>
       </c>
-      <c r="B95" s="79" t="inlineStr">
+      <c r="B95" s="83" t="inlineStr">
         <is>
           <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
@@ -7617,7 +7635,7 @@
       <c r="D95" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E95" s="69" t="inlineStr">
+      <c r="E95" s="70" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -7658,7 +7676,7 @@
           <t>36/36</t>
         </is>
       </c>
-      <c r="N95" s="68" t="inlineStr">
+      <c r="N95" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -7675,7 +7693,7 @@
           <t>PS5-28-07</t>
         </is>
       </c>
-      <c r="B96" s="79" t="inlineStr">
+      <c r="B96" s="83" t="inlineStr">
         <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
@@ -7686,7 +7704,7 @@
       <c r="D96" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E96" s="69" t="inlineStr">
+      <c r="E96" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -7744,7 +7762,7 @@
           <t>PS5-28-08</t>
         </is>
       </c>
-      <c r="B97" s="79" t="inlineStr">
+      <c r="B97" s="83" t="inlineStr">
         <is>
           <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
@@ -7755,7 +7773,7 @@
       <c r="D97" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E97" s="69" t="inlineStr">
+      <c r="E97" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7766,7 +7784,7 @@
       <c r="G97" s="23" t="n">
         <v>34</v>
       </c>
-      <c r="H97" s="69" t="inlineStr">
+      <c r="H97" s="70" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
@@ -7796,7 +7814,7 @@
           <t>23/29</t>
         </is>
       </c>
-      <c r="N97" s="69" t="inlineStr">
+      <c r="N97" s="70" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -7813,7 +7831,7 @@
           <t>PS5-28-09</t>
         </is>
       </c>
-      <c r="B98" s="79" t="inlineStr">
+      <c r="B98" s="83" t="inlineStr">
         <is>
           <t>PS5-28-09 - Observation Basin</t>
         </is>
@@ -7824,7 +7842,7 @@
       <c r="D98" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E98" s="69" t="inlineStr">
+      <c r="E98" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7865,7 +7883,7 @@
           <t>13/14</t>
         </is>
       </c>
-      <c r="N98" s="68" t="inlineStr">
+      <c r="N98" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -7882,7 +7900,7 @@
           <t>PS5-28-10</t>
         </is>
       </c>
-      <c r="B99" s="79" t="inlineStr">
+      <c r="B99" s="83" t="inlineStr">
         <is>
           <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
@@ -7893,7 +7911,7 @@
       <c r="D99" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E99" s="69" t="inlineStr">
+      <c r="E99" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7904,7 +7922,7 @@
       <c r="G99" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H99" s="69" t="inlineStr">
+      <c r="H99" s="70" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -7934,7 +7952,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N99" s="69" t="inlineStr">
+      <c r="N99" s="70" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -7951,7 +7969,7 @@
           <t>PS5-28-11</t>
         </is>
       </c>
-      <c r="B100" s="79" t="inlineStr">
+      <c r="B100" s="83" t="inlineStr">
         <is>
           <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
@@ -7962,7 +7980,7 @@
       <c r="D100" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E100" s="69" t="inlineStr">
+      <c r="E100" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7973,7 +7991,7 @@
       <c r="G100" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H100" s="68" t="inlineStr">
+      <c r="H100" s="69" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -8003,7 +8021,7 @@
           <t>8/8</t>
         </is>
       </c>
-      <c r="N100" s="68" t="inlineStr">
+      <c r="N100" s="69" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -8020,7 +8038,7 @@
           <t>PS5-28-12</t>
         </is>
       </c>
-      <c r="B101" s="79" t="inlineStr">
+      <c r="B101" s="83" t="inlineStr">
         <is>
           <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
@@ -8031,7 +8049,7 @@
       <c r="D101" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E101" s="69" t="inlineStr">
+      <c r="E101" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8042,7 +8060,7 @@
       <c r="G101" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="H101" s="68" t="inlineStr">
+      <c r="H101" s="69" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8072,7 +8090,7 @@
           <t>28/43</t>
         </is>
       </c>
-      <c r="N101" s="68" t="inlineStr">
+      <c r="N101" s="69" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8089,7 +8107,7 @@
           <t>PS5-28-13</t>
         </is>
       </c>
-      <c r="B102" s="79" t="inlineStr">
+      <c r="B102" s="83" t="inlineStr">
         <is>
           <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
@@ -8100,7 +8118,7 @@
       <c r="D102" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E102" s="68" t="inlineStr">
+      <c r="E102" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8111,7 +8129,7 @@
       <c r="G102" s="23" t="n">
         <v>54</v>
       </c>
-      <c r="H102" s="68" t="inlineStr">
+      <c r="H102" s="69" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -8141,7 +8159,7 @@
           <t>34/35</t>
         </is>
       </c>
-      <c r="N102" s="68" t="inlineStr">
+      <c r="N102" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -8158,7 +8176,7 @@
           <t>PS5-28-14</t>
         </is>
       </c>
-      <c r="B103" s="79" t="inlineStr">
+      <c r="B103" s="83" t="inlineStr">
         <is>
           <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
@@ -8169,7 +8187,7 @@
       <c r="D103" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="68" t="inlineStr">
+      <c r="E103" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8180,7 +8198,7 @@
       <c r="G103" s="23" t="n">
         <v>53</v>
       </c>
-      <c r="H103" s="68" t="inlineStr">
+      <c r="H103" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -8210,7 +8228,7 @@
           <t>32/35</t>
         </is>
       </c>
-      <c r="N103" s="68" t="inlineStr">
+      <c r="N103" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8227,7 +8245,7 @@
           <t>PS5-28-15</t>
         </is>
       </c>
-      <c r="B104" s="79" t="inlineStr">
+      <c r="B104" s="83" t="inlineStr">
         <is>
           <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
@@ -8238,7 +8256,7 @@
       <c r="D104" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E104" s="68" t="inlineStr">
+      <c r="E104" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8249,7 +8267,7 @@
       <c r="G104" s="23" t="n">
         <v>52</v>
       </c>
-      <c r="H104" s="68" t="inlineStr">
+      <c r="H104" s="69" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -8279,7 +8297,7 @@
           <t>32/35</t>
         </is>
       </c>
-      <c r="N104" s="68" t="inlineStr">
+      <c r="N104" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8296,7 +8314,7 @@
           <t>PS5-28-16</t>
         </is>
       </c>
-      <c r="B105" s="79" t="inlineStr">
+      <c r="B105" s="83" t="inlineStr">
         <is>
           <t>PS5-28-16 - LP Relief Header</t>
         </is>
@@ -8307,7 +8325,7 @@
       <c r="D105" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E105" s="91" t="inlineStr">
+      <c r="E105" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8348,7 +8366,7 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N105" s="68" t="inlineStr">
+      <c r="N105" s="69" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -8365,7 +8383,7 @@
           <t>PS5-28-17</t>
         </is>
       </c>
-      <c r="B106" s="79" t="inlineStr">
+      <c r="B106" s="83" t="inlineStr">
         <is>
           <t>PS5-28-17 - Reinjection Pump</t>
         </is>
@@ -8376,7 +8394,7 @@
       <c r="D106" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E106" s="69" t="inlineStr">
+      <c r="E106" s="70" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -8387,7 +8405,7 @@
       <c r="G106" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H106" s="68" t="inlineStr">
+      <c r="H106" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -8417,7 +8435,7 @@
           <t>24/24</t>
         </is>
       </c>
-      <c r="N106" s="68" t="inlineStr">
+      <c r="N106" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -8434,7 +8452,7 @@
           <t>PS5-50-01</t>
         </is>
       </c>
-      <c r="B107" s="79" t="inlineStr">
+      <c r="B107" s="83" t="inlineStr">
         <is>
           <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
@@ -8445,7 +8463,7 @@
       <c r="D107" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E107" s="91" t="inlineStr">
+      <c r="E107" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8456,7 +8474,7 @@
       <c r="G107" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H107" s="69" t="inlineStr">
+      <c r="H107" s="70" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8486,7 +8504,7 @@
           <t>9/13</t>
         </is>
       </c>
-      <c r="N107" s="69" t="inlineStr">
+      <c r="N107" s="70" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8503,7 +8521,7 @@
           <t>PS5-50-02</t>
         </is>
       </c>
-      <c r="B108" s="79" t="inlineStr">
+      <c r="B108" s="83" t="inlineStr">
         <is>
           <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
@@ -8514,7 +8532,7 @@
       <c r="D108" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E108" s="91" t="inlineStr">
+      <c r="E108" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8525,7 +8543,7 @@
       <c r="G108" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H108" s="69" t="inlineStr">
+      <c r="H108" s="70" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -8555,7 +8573,7 @@
           <t>10/13</t>
         </is>
       </c>
-      <c r="N108" s="69" t="inlineStr">
+      <c r="N108" s="70" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -8572,7 +8590,7 @@
           <t>PS5-50-03</t>
         </is>
       </c>
-      <c r="B109" s="79" t="inlineStr">
+      <c r="B109" s="83" t="inlineStr">
         <is>
           <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
@@ -8583,7 +8601,7 @@
       <c r="D109" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="69" t="inlineStr">
+      <c r="E109" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8594,7 +8612,7 @@
       <c r="G109" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H109" s="68" t="inlineStr">
+      <c r="H109" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8624,7 +8642,7 @@
           <t>10/15</t>
         </is>
       </c>
-      <c r="N109" s="69" t="inlineStr">
+      <c r="N109" s="70" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8641,7 +8659,7 @@
           <t>PS5-53-01</t>
         </is>
       </c>
-      <c r="B110" s="79" t="inlineStr">
+      <c r="B110" s="83" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -8652,7 +8670,7 @@
       <c r="D110" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E110" s="68" t="inlineStr">
+      <c r="E110" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -8663,7 +8681,7 @@
       <c r="G110" s="23" t="n">
         <v>42</v>
       </c>
-      <c r="H110" s="68" t="inlineStr">
+      <c r="H110" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -8693,12 +8711,12 @@
           <t>27/30</t>
         </is>
       </c>
-      <c r="N110" s="68" t="inlineStr">
+      <c r="N110" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="O110" s="68" t="inlineStr">
+      <c r="O110" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -8710,7 +8728,7 @@
           <t>PS5-53-02</t>
         </is>
       </c>
-      <c r="B111" s="79" t="inlineStr">
+      <c r="B111" s="83" t="inlineStr">
         <is>
           <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
@@ -8721,7 +8739,7 @@
       <c r="D111" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="69" t="inlineStr">
+      <c r="E111" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8732,7 +8750,7 @@
       <c r="G111" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H111" s="68" t="inlineStr">
+      <c r="H111" s="69" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
@@ -8762,7 +8780,7 @@
           <t>8/8</t>
         </is>
       </c>
-      <c r="N111" s="68" t="inlineStr">
+      <c r="N111" s="69" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -8779,7 +8797,7 @@
           <t>PS5-53-03</t>
         </is>
       </c>
-      <c r="B112" s="79" t="inlineStr">
+      <c r="B112" s="83" t="inlineStr">
         <is>
           <t>PS5-53-03 - Water Softener Package</t>
         </is>
@@ -8790,7 +8808,7 @@
       <c r="D112" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E112" s="91" t="inlineStr">
+      <c r="E112" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8801,7 +8819,7 @@
       <c r="G112" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H112" s="68" t="inlineStr">
+      <c r="H112" s="69" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8831,7 +8849,7 @@
           <t>11/14</t>
         </is>
       </c>
-      <c r="N112" s="68" t="inlineStr">
+      <c r="N112" s="69" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8848,7 +8866,7 @@
           <t>PS5-53-04</t>
         </is>
       </c>
-      <c r="B113" s="79" t="inlineStr">
+      <c r="B113" s="83" t="inlineStr">
         <is>
           <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
@@ -8859,7 +8877,7 @@
       <c r="D113" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="91" t="inlineStr">
+      <c r="E113" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8870,7 +8888,7 @@
       <c r="G113" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="69" t="inlineStr">
+      <c r="H113" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8900,7 +8918,7 @@
           <t>0/1</t>
         </is>
       </c>
-      <c r="N113" s="69" t="inlineStr">
+      <c r="N113" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8917,7 +8935,7 @@
           <t>PS5-53-05</t>
         </is>
       </c>
-      <c r="B114" s="79" t="inlineStr">
+      <c r="B114" s="83" t="inlineStr">
         <is>
           <t>PS5-53-05 - Water Distribution Header</t>
         </is>
@@ -8928,7 +8946,7 @@
       <c r="D114" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E114" s="91" t="inlineStr">
+      <c r="E114" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8986,7 +9004,7 @@
           <t>PS5-53-06</t>
         </is>
       </c>
-      <c r="B115" s="79" t="inlineStr">
+      <c r="B115" s="83" t="inlineStr">
         <is>
           <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
@@ -8997,7 +9015,7 @@
       <c r="D115" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E115" s="91" t="inlineStr">
+      <c r="E115" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9008,7 +9026,7 @@
       <c r="G115" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H115" s="68" t="inlineStr">
+      <c r="H115" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -9038,7 +9056,7 @@
           <t>33/39</t>
         </is>
       </c>
-      <c r="N115" s="68" t="inlineStr">
+      <c r="N115" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -9055,7 +9073,7 @@
           <t>PS5-60-01</t>
         </is>
       </c>
-      <c r="B116" s="79" t="inlineStr">
+      <c r="B116" s="83" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -9066,7 +9084,7 @@
       <c r="D116" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="E116" s="69" t="inlineStr">
+      <c r="E116" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -9124,7 +9142,7 @@
           <t>PS5-60-02</t>
         </is>
       </c>
-      <c r="B117" s="79" t="inlineStr">
+      <c r="B117" s="83" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -9135,7 +9153,7 @@
       <c r="D117" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E117" s="69" t="inlineStr">
+      <c r="E117" s="70" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -9193,7 +9211,7 @@
           <t>PS5-60-03</t>
         </is>
       </c>
-      <c r="B118" s="79" t="inlineStr">
+      <c r="B118" s="83" t="inlineStr">
         <is>
           <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9204,7 +9222,7 @@
       <c r="D118" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E118" s="69" t="inlineStr">
+      <c r="E118" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -9215,7 +9233,7 @@
       <c r="G118" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H118" s="68" t="inlineStr">
+      <c r="H118" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9245,7 +9263,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N118" s="68" t="inlineStr">
+      <c r="N118" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9262,7 +9280,7 @@
           <t>PS5-60-04</t>
         </is>
       </c>
-      <c r="B119" s="79" t="inlineStr">
+      <c r="B119" s="83" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -9273,7 +9291,7 @@
       <c r="D119" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E119" s="69" t="inlineStr">
+      <c r="E119" s="70" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -9331,7 +9349,7 @@
           <t>PS5-60-05</t>
         </is>
       </c>
-      <c r="B120" s="79" t="inlineStr">
+      <c r="B120" s="83" t="inlineStr">
         <is>
           <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
@@ -9342,7 +9360,7 @@
       <c r="D120" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E120" s="69" t="inlineStr">
+      <c r="E120" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9400,7 +9418,7 @@
           <t>PS5-60-06</t>
         </is>
       </c>
-      <c r="B121" s="79" t="inlineStr">
+      <c r="B121" s="83" t="inlineStr">
         <is>
           <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9411,7 +9429,7 @@
       <c r="D121" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="69" t="inlineStr">
+      <c r="E121" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9422,7 +9440,7 @@
       <c r="G121" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H121" s="68" t="inlineStr">
+      <c r="H121" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9452,7 +9470,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N121" s="68" t="inlineStr">
+      <c r="N121" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9469,7 +9487,7 @@
           <t>PS5-60-07</t>
         </is>
       </c>
-      <c r="B122" s="79" t="inlineStr">
+      <c r="B122" s="83" t="inlineStr">
         <is>
           <t>PS5-60-07 - Power Generation Package C</t>
         </is>
@@ -9480,7 +9498,7 @@
       <c r="D122" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E122" s="69" t="inlineStr">
+      <c r="E122" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -9538,7 +9556,7 @@
           <t>PS5-60-08</t>
         </is>
       </c>
-      <c r="B123" s="79" t="inlineStr">
+      <c r="B123" s="83" t="inlineStr">
         <is>
           <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
@@ -9549,7 +9567,7 @@
       <c r="D123" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E123" s="69" t="inlineStr">
+      <c r="E123" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9607,7 +9625,7 @@
           <t>PS5-60-09</t>
         </is>
       </c>
-      <c r="B124" s="79" t="inlineStr">
+      <c r="B124" s="83" t="inlineStr">
         <is>
           <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9618,7 +9636,7 @@
       <c r="D124" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E124" s="91" t="inlineStr">
+      <c r="E124" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9629,7 +9647,7 @@
       <c r="G124" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H124" s="68" t="inlineStr">
+      <c r="H124" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9659,7 +9677,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N124" s="68" t="inlineStr">
+      <c r="N124" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9676,7 +9694,7 @@
           <t>PS5-60-10</t>
         </is>
       </c>
-      <c r="B125" s="79" t="inlineStr">
+      <c r="B125" s="83" t="inlineStr">
         <is>
           <t>PS5-60-10 - Power Generation Package D</t>
         </is>
@@ -9687,7 +9705,7 @@
       <c r="D125" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E125" s="69" t="inlineStr">
+      <c r="E125" s="70" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -9745,7 +9763,7 @@
           <t>PS5-60-11</t>
         </is>
       </c>
-      <c r="B126" s="79" t="inlineStr">
+      <c r="B126" s="83" t="inlineStr">
         <is>
           <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
@@ -9756,7 +9774,7 @@
       <c r="D126" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E126" s="91" t="inlineStr">
+      <c r="E126" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9814,7 +9832,7 @@
           <t>PS5-60-12</t>
         </is>
       </c>
-      <c r="B127" s="79" t="inlineStr">
+      <c r="B127" s="83" t="inlineStr">
         <is>
           <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9825,7 +9843,7 @@
       <c r="D127" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E127" s="91" t="inlineStr">
+      <c r="E127" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9836,7 +9854,7 @@
       <c r="G127" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H127" s="68" t="inlineStr">
+      <c r="H127" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9866,7 +9884,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N127" s="68" t="inlineStr">
+      <c r="N127" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9883,7 +9901,7 @@
           <t>PS5-60-13</t>
         </is>
       </c>
-      <c r="B128" s="79" t="inlineStr">
+      <c r="B128" s="83" t="inlineStr">
         <is>
           <t>PS5-60-13 - Power Generation Package E</t>
         </is>
@@ -9894,7 +9912,7 @@
       <c r="D128" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="E128" s="69" t="inlineStr">
+      <c r="E128" s="70" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -9952,7 +9970,7 @@
           <t>PS5-60-14</t>
         </is>
       </c>
-      <c r="B129" s="79" t="inlineStr">
+      <c r="B129" s="83" t="inlineStr">
         <is>
           <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
@@ -9963,7 +9981,7 @@
       <c r="D129" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E129" s="91" t="inlineStr">
+      <c r="E129" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10021,7 +10039,7 @@
           <t>PS5-60-15</t>
         </is>
       </c>
-      <c r="B130" s="79" t="inlineStr">
+      <c r="B130" s="83" t="inlineStr">
         <is>
           <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10032,7 +10050,7 @@
       <c r="D130" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E130" s="91" t="inlineStr">
+      <c r="E130" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10043,7 +10061,7 @@
       <c r="G130" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H130" s="68" t="inlineStr">
+      <c r="H130" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10073,7 +10091,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N130" s="68" t="inlineStr">
+      <c r="N130" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10090,7 +10108,7 @@
           <t>PS5-60-16</t>
         </is>
       </c>
-      <c r="B131" s="79" t="inlineStr">
+      <c r="B131" s="83" t="inlineStr">
         <is>
           <t>PS5-60-16 - Power Generation Package F</t>
         </is>
@@ -10101,7 +10119,7 @@
       <c r="D131" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E131" s="69" t="inlineStr">
+      <c r="E131" s="70" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -10159,7 +10177,7 @@
           <t>PS5-60-17</t>
         </is>
       </c>
-      <c r="B132" s="79" t="inlineStr">
+      <c r="B132" s="83" t="inlineStr">
         <is>
           <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
@@ -10170,7 +10188,7 @@
       <c r="D132" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E132" s="91" t="inlineStr">
+      <c r="E132" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10211,7 +10229,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N132" s="68" t="inlineStr">
+      <c r="N132" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10228,7 +10246,7 @@
           <t>PS5-60-18</t>
         </is>
       </c>
-      <c r="B133" s="79" t="inlineStr">
+      <c r="B133" s="83" t="inlineStr">
         <is>
           <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10239,7 +10257,7 @@
       <c r="D133" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E133" s="91" t="inlineStr">
+      <c r="E133" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10250,7 +10268,7 @@
       <c r="G133" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H133" s="68" t="inlineStr">
+      <c r="H133" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -10280,7 +10298,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N133" s="68" t="inlineStr">
+      <c r="N133" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -10297,7 +10315,7 @@
           <t>PS5-60-19</t>
         </is>
       </c>
-      <c r="B134" s="79" t="inlineStr">
+      <c r="B134" s="83" t="inlineStr">
         <is>
           <t>PS5-60-19 - Power Generation Package G</t>
         </is>
@@ -10308,7 +10326,7 @@
       <c r="D134" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E134" s="69" t="inlineStr">
+      <c r="E134" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -10366,7 +10384,7 @@
           <t>PS5-60-20</t>
         </is>
       </c>
-      <c r="B135" s="79" t="inlineStr">
+      <c r="B135" s="83" t="inlineStr">
         <is>
           <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
@@ -10377,7 +10395,7 @@
       <c r="D135" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E135" s="91" t="inlineStr">
+      <c r="E135" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10388,7 +10406,7 @@
       <c r="G135" s="23" t="n">
         <v>37</v>
       </c>
-      <c r="H135" s="68" t="inlineStr">
+      <c r="H135" s="69" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -10418,7 +10436,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N135" s="68" t="inlineStr">
+      <c r="N135" s="69" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -10435,7 +10453,7 @@
           <t>PS5-60-21</t>
         </is>
       </c>
-      <c r="B136" s="79" t="inlineStr">
+      <c r="B136" s="83" t="inlineStr">
         <is>
           <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10446,7 +10464,7 @@
       <c r="D136" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E136" s="91" t="inlineStr">
+      <c r="E136" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10487,7 +10505,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N136" s="68" t="inlineStr">
+      <c r="N136" s="69" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -10504,7 +10522,7 @@
           <t>PS5-60-22</t>
         </is>
       </c>
-      <c r="B137" s="79" t="inlineStr">
+      <c r="B137" s="83" t="inlineStr">
         <is>
           <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
@@ -10515,7 +10533,7 @@
       <c r="D137" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E137" s="69" t="inlineStr">
+      <c r="E137" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10526,7 +10544,7 @@
       <c r="G137" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="H137" s="68" t="inlineStr">
+      <c r="H137" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -10556,7 +10574,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N137" s="68" t="inlineStr">
+      <c r="N137" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -10573,7 +10591,7 @@
           <t>PS5-60-23</t>
         </is>
       </c>
-      <c r="B138" s="79" t="inlineStr">
+      <c r="B138" s="83" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -10584,7 +10602,7 @@
       <c r="D138" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E138" s="69" t="inlineStr">
+      <c r="E138" s="70" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -10642,7 +10660,7 @@
           <t>PS5-60-24</t>
         </is>
       </c>
-      <c r="B139" s="79" t="inlineStr">
+      <c r="B139" s="83" t="inlineStr">
         <is>
           <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
@@ -10653,7 +10671,7 @@
       <c r="D139" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E139" s="69" t="inlineStr">
+      <c r="E139" s="70" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -10711,7 +10729,7 @@
           <t>PS5-60-25</t>
         </is>
       </c>
-      <c r="B140" s="79" t="inlineStr">
+      <c r="B140" s="83" t="inlineStr">
         <is>
           <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
@@ -10722,7 +10740,7 @@
       <c r="D140" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E140" s="69" t="inlineStr">
+      <c r="E140" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -10780,7 +10798,7 @@
           <t>PS5-60-26</t>
         </is>
       </c>
-      <c r="B141" s="79" t="inlineStr">
+      <c r="B141" s="83" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -10791,7 +10809,7 @@
       <c r="D141" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E141" s="69" t="inlineStr">
+      <c r="E141" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -10849,7 +10867,7 @@
           <t>PS5-60-27</t>
         </is>
       </c>
-      <c r="B142" s="79" t="inlineStr">
+      <c r="B142" s="83" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -10860,7 +10878,7 @@
       <c r="D142" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E142" s="69" t="inlineStr">
+      <c r="E142" s="70" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -10918,7 +10936,7 @@
           <t>PS5-60-28</t>
         </is>
       </c>
-      <c r="B143" s="79" t="inlineStr">
+      <c r="B143" s="83" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -10929,7 +10947,7 @@
       <c r="D143" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E143" s="69" t="inlineStr">
+      <c r="E143" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -10975,9 +10993,9 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O143" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="O143" s="69" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
     </row>
@@ -10987,7 +11005,7 @@
           <t>PS5-60-29</t>
         </is>
       </c>
-      <c r="B144" s="79" t="inlineStr">
+      <c r="B144" s="83" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -10998,7 +11016,7 @@
       <c r="D144" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E144" s="69" t="inlineStr">
+      <c r="E144" s="70" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -11056,7 +11074,7 @@
           <t>PS5-60-30</t>
         </is>
       </c>
-      <c r="B145" s="79" t="inlineStr">
+      <c r="B145" s="83" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -11067,7 +11085,7 @@
       <c r="D145" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E145" s="69" t="inlineStr">
+      <c r="E145" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -11125,7 +11143,7 @@
           <t>PS5-60-31</t>
         </is>
       </c>
-      <c r="B146" s="79" t="inlineStr">
+      <c r="B146" s="83" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -11136,7 +11154,7 @@
       <c r="D146" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E146" s="69" t="inlineStr">
+      <c r="E146" s="70" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -11194,7 +11212,7 @@
           <t>PS5-60-32</t>
         </is>
       </c>
-      <c r="B147" s="79" t="inlineStr">
+      <c r="B147" s="83" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -11205,7 +11223,7 @@
       <c r="D147" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E147" s="68" t="inlineStr">
+      <c r="E147" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11263,7 +11281,7 @@
           <t>PS5-60-33</t>
         </is>
       </c>
-      <c r="B148" s="79" t="inlineStr">
+      <c r="B148" s="83" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -11274,7 +11292,7 @@
       <c r="D148" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E148" s="68" t="inlineStr">
+      <c r="E148" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11332,7 +11350,7 @@
           <t>PS5-60-34</t>
         </is>
       </c>
-      <c r="B149" s="79" t="inlineStr">
+      <c r="B149" s="83" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -11343,7 +11361,7 @@
       <c r="D149" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E149" s="69" t="inlineStr">
+      <c r="E149" s="70" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -11401,7 +11419,7 @@
           <t>PS5-60-35</t>
         </is>
       </c>
-      <c r="B150" s="79" t="inlineStr">
+      <c r="B150" s="83" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -11412,7 +11430,7 @@
       <c r="D150" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E150" s="69" t="inlineStr">
+      <c r="E150" s="70" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -11458,9 +11476,9 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O150" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="O150" s="54" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11488,7 @@
           <t>PS5-60-36</t>
         </is>
       </c>
-      <c r="B151" s="79" t="inlineStr">
+      <c r="B151" s="83" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -11481,7 +11499,7 @@
       <c r="D151" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E151" s="69" t="inlineStr">
+      <c r="E151" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -11539,7 +11557,7 @@
           <t>PS5-60-37</t>
         </is>
       </c>
-      <c r="B152" s="79" t="inlineStr">
+      <c r="B152" s="83" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -11550,7 +11568,7 @@
       <c r="D152" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E152" s="69" t="inlineStr">
+      <c r="E152" s="70" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -11608,7 +11626,7 @@
           <t>PS5-60-38</t>
         </is>
       </c>
-      <c r="B153" s="79" t="inlineStr">
+      <c r="B153" s="83" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -11619,7 +11637,7 @@
       <c r="D153" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E153" s="68" t="inlineStr">
+      <c r="E153" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11677,7 +11695,7 @@
           <t>PS5-60-39</t>
         </is>
       </c>
-      <c r="B154" s="79" t="inlineStr">
+      <c r="B154" s="83" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -11688,7 +11706,7 @@
       <c r="D154" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E154" s="68" t="inlineStr">
+      <c r="E154" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11746,7 +11764,7 @@
           <t>PS5-60-40</t>
         </is>
       </c>
-      <c r="B155" s="79" t="inlineStr">
+      <c r="B155" s="83" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -11757,7 +11775,7 @@
       <c r="D155" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E155" s="68" t="inlineStr">
+      <c r="E155" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -11815,7 +11833,7 @@
           <t>PS5-60-41</t>
         </is>
       </c>
-      <c r="B156" s="79" t="inlineStr">
+      <c r="B156" s="83" t="inlineStr">
         <is>
           <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
@@ -11826,7 +11844,7 @@
       <c r="D156" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E156" s="68" t="inlineStr">
+      <c r="E156" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -11837,7 +11855,7 @@
       <c r="G156" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="H156" s="68" t="inlineStr">
+      <c r="H156" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -11867,7 +11885,7 @@
           <t>16/17</t>
         </is>
       </c>
-      <c r="N156" s="68" t="inlineStr">
+      <c r="N156" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -11884,7 +11902,7 @@
           <t>PS5-60-42</t>
         </is>
       </c>
-      <c r="B157" s="79" t="inlineStr">
+      <c r="B157" s="83" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -11895,7 +11913,7 @@
       <c r="D157" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E157" s="69" t="inlineStr">
+      <c r="E157" s="70" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -11941,9 +11959,9 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O157" s="27" t="inlineStr">
-        <is>
-          <t>Full</t>
+      <c r="O157" s="54" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
@@ -11953,7 +11971,7 @@
           <t>PS5-60-43</t>
         </is>
       </c>
-      <c r="B158" s="79" t="inlineStr">
+      <c r="B158" s="83" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -11964,7 +11982,7 @@
       <c r="D158" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E158" s="69" t="inlineStr">
+      <c r="E158" s="70" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -12022,7 +12040,7 @@
           <t>PS5-60-44</t>
         </is>
       </c>
-      <c r="B159" s="79" t="inlineStr">
+      <c r="B159" s="83" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -12033,7 +12051,7 @@
       <c r="D159" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E159" s="69" t="inlineStr">
+      <c r="E159" s="70" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -12091,7 +12109,7 @@
           <t>PS5-60-45</t>
         </is>
       </c>
-      <c r="B160" s="79" t="inlineStr">
+      <c r="B160" s="83" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -12102,7 +12120,7 @@
       <c r="D160" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E160" s="69" t="inlineStr">
+      <c r="E160" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -12160,7 +12178,7 @@
           <t>PS5-60-46</t>
         </is>
       </c>
-      <c r="B161" s="79" t="inlineStr">
+      <c r="B161" s="83" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -12171,7 +12189,7 @@
       <c r="D161" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E161" s="68" t="inlineStr">
+      <c r="E161" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -12229,7 +12247,7 @@
           <t>PS5-60-47</t>
         </is>
       </c>
-      <c r="B162" s="79" t="inlineStr">
+      <c r="B162" s="83" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -12240,7 +12258,7 @@
       <c r="D162" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E162" s="68" t="inlineStr">
+      <c r="E162" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -12298,7 +12316,7 @@
           <t>PS5-60-48</t>
         </is>
       </c>
-      <c r="B163" s="79" t="inlineStr">
+      <c r="B163" s="83" t="inlineStr">
         <is>
           <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
@@ -12309,7 +12327,7 @@
       <c r="D163" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E163" s="69" t="inlineStr">
+      <c r="E163" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -12367,7 +12385,7 @@
           <t>PS5-60-49</t>
         </is>
       </c>
-      <c r="B164" s="79" t="inlineStr">
+      <c r="B164" s="83" t="inlineStr">
         <is>
           <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
@@ -12378,7 +12396,7 @@
       <c r="D164" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E164" s="69" t="inlineStr">
+      <c r="E164" s="70" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -12436,7 +12454,7 @@
           <t>PS5-60-50</t>
         </is>
       </c>
-      <c r="B165" s="79" t="inlineStr">
+      <c r="B165" s="83" t="inlineStr">
         <is>
           <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
@@ -12447,7 +12465,7 @@
       <c r="D165" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E165" s="69" t="inlineStr">
+      <c r="E165" s="70" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -12505,7 +12523,7 @@
           <t>PS5-60-51</t>
         </is>
       </c>
-      <c r="B166" s="79" t="inlineStr">
+      <c r="B166" s="83" t="inlineStr">
         <is>
           <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
@@ -12516,7 +12534,7 @@
       <c r="D166" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E166" s="68" t="inlineStr">
+      <c r="E166" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -12574,7 +12592,7 @@
           <t>PS5-60-52</t>
         </is>
       </c>
-      <c r="B167" s="79" t="inlineStr">
+      <c r="B167" s="83" t="inlineStr">
         <is>
           <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
@@ -12585,7 +12603,7 @@
       <c r="D167" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E167" s="69" t="inlineStr">
+      <c r="E167" s="70" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -12596,7 +12614,7 @@
       <c r="G167" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="H167" s="68" t="inlineStr">
+      <c r="H167" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -12626,7 +12644,7 @@
           <t>15/15</t>
         </is>
       </c>
-      <c r="N167" s="68" t="inlineStr">
+      <c r="N167" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -12643,7 +12661,7 @@
           <t>PS5-60-53</t>
         </is>
       </c>
-      <c r="B168" s="79" t="inlineStr">
+      <c r="B168" s="83" t="inlineStr">
         <is>
           <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
@@ -12654,7 +12672,7 @@
       <c r="D168" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E168" s="68" t="inlineStr">
+      <c r="E168" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -12712,7 +12730,7 @@
           <t>PS5-60-54</t>
         </is>
       </c>
-      <c r="B169" s="79" t="inlineStr">
+      <c r="B169" s="83" t="inlineStr">
         <is>
           <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
@@ -12723,7 +12741,7 @@
       <c r="D169" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E169" s="68" t="inlineStr">
+      <c r="E169" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -12781,7 +12799,7 @@
           <t>PS5-60-55</t>
         </is>
       </c>
-      <c r="B170" s="79" t="inlineStr">
+      <c r="B170" s="83" t="inlineStr">
         <is>
           <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
@@ -12803,7 +12821,7 @@
       <c r="G170" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="H170" s="68" t="inlineStr">
+      <c r="H170" s="69" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -12833,7 +12851,7 @@
           <t>14/15</t>
         </is>
       </c>
-      <c r="N170" s="68" t="inlineStr">
+      <c r="N170" s="69" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -12850,7 +12868,7 @@
           <t>PS5-60-56</t>
         </is>
       </c>
-      <c r="B171" s="79" t="inlineStr">
+      <c r="B171" s="83" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -12861,7 +12879,7 @@
       <c r="D171" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E171" s="69" t="inlineStr">
+      <c r="E171" s="70" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -12919,7 +12937,7 @@
           <t>PS5-60-57</t>
         </is>
       </c>
-      <c r="B172" s="79" t="inlineStr">
+      <c r="B172" s="83" t="inlineStr">
         <is>
           <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
@@ -12930,7 +12948,7 @@
       <c r="D172" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E172" s="69" t="inlineStr">
+      <c r="E172" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12988,7 +13006,7 @@
           <t>PS5-60-58</t>
         </is>
       </c>
-      <c r="B173" s="79" t="inlineStr">
+      <c r="B173" s="83" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -12999,7 +13017,7 @@
       <c r="D173" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E173" s="69" t="inlineStr">
+      <c r="E173" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -13057,7 +13075,7 @@
           <t>PS5-60-59</t>
         </is>
       </c>
-      <c r="B174" s="79" t="inlineStr">
+      <c r="B174" s="83" t="inlineStr">
         <is>
           <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
@@ -13068,7 +13086,7 @@
       <c r="D174" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E174" s="69" t="inlineStr">
+      <c r="E174" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13126,7 +13144,7 @@
           <t>PS5-60-60</t>
         </is>
       </c>
-      <c r="B175" s="79" t="inlineStr">
+      <c r="B175" s="83" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -13137,7 +13155,7 @@
       <c r="D175" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E175" s="69" t="inlineStr">
+      <c r="E175" s="70" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -13195,7 +13213,7 @@
           <t>PS5-60-61</t>
         </is>
       </c>
-      <c r="B176" s="79" t="inlineStr">
+      <c r="B176" s="83" t="inlineStr">
         <is>
           <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
@@ -13206,7 +13224,7 @@
       <c r="D176" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E176" s="91" t="inlineStr">
+      <c r="E176" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13264,7 +13282,7 @@
           <t>PS5-60-62</t>
         </is>
       </c>
-      <c r="B177" s="79" t="inlineStr">
+      <c r="B177" s="83" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -13275,7 +13293,7 @@
       <c r="D177" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E177" s="69" t="inlineStr">
+      <c r="E177" s="70" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -13333,7 +13351,7 @@
           <t>PS5-60-63</t>
         </is>
       </c>
-      <c r="B178" s="79" t="inlineStr">
+      <c r="B178" s="83" t="inlineStr">
         <is>
           <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
@@ -13344,7 +13362,7 @@
       <c r="D178" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E178" s="91" t="inlineStr">
+      <c r="E178" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13402,7 +13420,7 @@
           <t>PS5-60-64</t>
         </is>
       </c>
-      <c r="B179" s="79" t="inlineStr">
+      <c r="B179" s="83" t="inlineStr">
         <is>
           <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
@@ -13413,7 +13431,7 @@
       <c r="D179" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E179" s="68" t="inlineStr">
+      <c r="E179" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -13471,7 +13489,7 @@
           <t>PS5-60-65</t>
         </is>
       </c>
-      <c r="B180" s="79" t="inlineStr">
+      <c r="B180" s="83" t="inlineStr">
         <is>
           <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
@@ -13482,7 +13500,7 @@
       <c r="D180" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E180" s="91" t="inlineStr">
+      <c r="E180" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13523,7 +13541,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N180" s="68" t="inlineStr">
+      <c r="N180" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13540,7 +13558,7 @@
           <t>PS5-60-66</t>
         </is>
       </c>
-      <c r="B181" s="79" t="inlineStr">
+      <c r="B181" s="83" t="inlineStr">
         <is>
           <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
@@ -13551,7 +13569,7 @@
       <c r="D181" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E181" s="69" t="inlineStr">
+      <c r="E181" s="70" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -13609,7 +13627,7 @@
           <t>PS5-60-67</t>
         </is>
       </c>
-      <c r="B182" s="79" t="inlineStr">
+      <c r="B182" s="83" t="inlineStr">
         <is>
           <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
@@ -13620,7 +13638,7 @@
       <c r="D182" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E182" s="91" t="inlineStr">
+      <c r="E182" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13661,7 +13679,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N182" s="68" t="inlineStr">
+      <c r="N182" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13678,7 +13696,7 @@
           <t>PS5-60-68</t>
         </is>
       </c>
-      <c r="B183" s="79" t="inlineStr">
+      <c r="B183" s="83" t="inlineStr">
         <is>
           <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
@@ -13689,7 +13707,7 @@
       <c r="D183" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E183" s="69" t="inlineStr">
+      <c r="E183" s="70" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -13700,7 +13718,7 @@
       <c r="G183" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H183" s="68" t="inlineStr">
+      <c r="H183" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13730,7 +13748,7 @@
           <t>16/17</t>
         </is>
       </c>
-      <c r="N183" s="68" t="inlineStr">
+      <c r="N183" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13747,7 +13765,7 @@
           <t>PS5-60-69</t>
         </is>
       </c>
-      <c r="B184" s="79" t="inlineStr">
+      <c r="B184" s="83" t="inlineStr">
         <is>
           <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
@@ -13758,7 +13776,7 @@
       <c r="D184" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E184" s="91" t="inlineStr">
+      <c r="E184" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13769,7 +13787,7 @@
       <c r="G184" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="H184" s="68" t="inlineStr">
+      <c r="H184" s="69" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -13799,7 +13817,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N184" s="68" t="inlineStr">
+      <c r="N184" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -13816,7 +13834,7 @@
           <t>PS5-60-70</t>
         </is>
       </c>
-      <c r="B185" s="79" t="inlineStr">
+      <c r="B185" s="83" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -13827,7 +13845,7 @@
       <c r="D185" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="E185" s="69" t="inlineStr">
+      <c r="E185" s="70" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -13885,7 +13903,7 @@
           <t>PS5-60-71</t>
         </is>
       </c>
-      <c r="B186" s="79" t="inlineStr">
+      <c r="B186" s="83" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -13896,7 +13914,7 @@
       <c r="D186" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="E186" s="69" t="inlineStr">
+      <c r="E186" s="70" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
@@ -13954,7 +13972,7 @@
           <t>PS5-60-72</t>
         </is>
       </c>
-      <c r="B187" s="79" t="inlineStr">
+      <c r="B187" s="83" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -13965,7 +13983,7 @@
       <c r="D187" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="E187" s="69" t="inlineStr">
+      <c r="E187" s="70" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
@@ -14023,7 +14041,7 @@
           <t>PS5-60-73</t>
         </is>
       </c>
-      <c r="B188" s="79" t="inlineStr">
+      <c r="B188" s="83" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -14034,7 +14052,7 @@
       <c r="D188" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E188" s="69" t="inlineStr">
+      <c r="E188" s="70" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -14092,7 +14110,7 @@
           <t>PS5-60-74</t>
         </is>
       </c>
-      <c r="B189" s="79" t="inlineStr">
+      <c r="B189" s="83" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -14103,7 +14121,7 @@
       <c r="D189" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E189" s="69" t="inlineStr">
+      <c r="E189" s="70" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -14161,7 +14179,7 @@
           <t>PS5-60-75</t>
         </is>
       </c>
-      <c r="B190" s="79" t="inlineStr">
+      <c r="B190" s="83" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -14172,7 +14190,7 @@
       <c r="D190" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E190" s="69" t="inlineStr">
+      <c r="E190" s="70" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -14230,7 +14248,7 @@
           <t>PS5-60-76</t>
         </is>
       </c>
-      <c r="B191" s="79" t="inlineStr">
+      <c r="B191" s="83" t="inlineStr">
         <is>
           <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
@@ -14241,7 +14259,7 @@
       <c r="D191" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E191" s="69" t="inlineStr">
+      <c r="E191" s="70" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -14299,7 +14317,7 @@
           <t>PS5-61-01</t>
         </is>
       </c>
-      <c r="B192" s="79" t="inlineStr">
+      <c r="B192" s="83" t="inlineStr">
         <is>
           <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
@@ -14310,7 +14328,7 @@
       <c r="D192" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E192" s="69" t="inlineStr">
+      <c r="E192" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -14368,7 +14386,7 @@
           <t>PS5-61-02</t>
         </is>
       </c>
-      <c r="B193" s="79" t="inlineStr">
+      <c r="B193" s="83" t="inlineStr">
         <is>
           <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
@@ -14379,7 +14397,7 @@
       <c r="D193" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E193" s="69" t="inlineStr">
+      <c r="E193" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14420,7 +14438,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N193" s="68" t="inlineStr">
+      <c r="N193" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -14437,7 +14455,7 @@
           <t>PS5-61-03</t>
         </is>
       </c>
-      <c r="B194" s="79" t="inlineStr">
+      <c r="B194" s="83" t="inlineStr">
         <is>
           <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
@@ -14448,7 +14466,7 @@
       <c r="D194" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E194" s="69" t="inlineStr">
+      <c r="E194" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -14489,7 +14507,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N194" s="68" t="inlineStr">
+      <c r="N194" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -14506,7 +14524,7 @@
           <t>PS5-61-04</t>
         </is>
       </c>
-      <c r="B195" s="79" t="inlineStr">
+      <c r="B195" s="83" t="inlineStr">
         <is>
           <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
@@ -14517,7 +14535,7 @@
       <c r="D195" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E195" s="91" t="inlineStr">
+      <c r="E195" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14528,7 +14546,7 @@
       <c r="G195" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H195" s="69" t="inlineStr">
+      <c r="H195" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14558,7 +14576,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N195" s="69" t="inlineStr">
+      <c r="N195" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14575,7 +14593,7 @@
           <t>PS5-61-05</t>
         </is>
       </c>
-      <c r="B196" s="79" t="inlineStr">
+      <c r="B196" s="83" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -14644,7 +14662,7 @@
           <t>PS5-61-06</t>
         </is>
       </c>
-      <c r="B197" s="79" t="inlineStr">
+      <c r="B197" s="83" t="inlineStr">
         <is>
           <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
@@ -14666,7 +14684,7 @@
       <c r="G197" s="23" t="n">
         <v>63</v>
       </c>
-      <c r="H197" s="68" t="inlineStr">
+      <c r="H197" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -14696,7 +14714,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N197" s="68" t="inlineStr">
+      <c r="N197" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -14713,7 +14731,7 @@
           <t>PS5-61-07</t>
         </is>
       </c>
-      <c r="B198" s="79" t="inlineStr">
+      <c r="B198" s="83" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -14724,7 +14742,7 @@
       <c r="D198" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E198" s="69" t="inlineStr">
+      <c r="E198" s="70" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -14782,7 +14800,7 @@
           <t>PS5-61-08</t>
         </is>
       </c>
-      <c r="B199" s="79" t="inlineStr">
+      <c r="B199" s="83" t="inlineStr">
         <is>
           <t>PS5-61-08 - Electrical Control System</t>
         </is>
@@ -14793,7 +14811,7 @@
       <c r="D199" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E199" s="68" t="inlineStr">
+      <c r="E199" s="69" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -14804,7 +14822,7 @@
       <c r="G199" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H199" s="69" t="inlineStr">
+      <c r="H199" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -14834,7 +14852,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N199" s="69" t="inlineStr">
+      <c r="N199" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -14851,7 +14869,7 @@
           <t>PS5-61-09</t>
         </is>
       </c>
-      <c r="B200" s="79" t="inlineStr">
+      <c r="B200" s="83" t="inlineStr">
         <is>
           <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
@@ -14862,7 +14880,7 @@
       <c r="D200" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E200" s="91" t="inlineStr">
+      <c r="E200" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14873,7 +14891,7 @@
       <c r="G200" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H200" s="69" t="inlineStr">
+      <c r="H200" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -14903,7 +14921,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N200" s="69" t="inlineStr">
+      <c r="N200" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -14920,7 +14938,7 @@
           <t>PS5-61-10</t>
         </is>
       </c>
-      <c r="B201" s="79" t="inlineStr">
+      <c r="B201" s="83" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -14931,7 +14949,7 @@
       <c r="D201" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E201" s="91" t="inlineStr">
+      <c r="E201" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14989,7 +15007,7 @@
           <t>PS5-61-11</t>
         </is>
       </c>
-      <c r="B202" s="79" t="inlineStr">
+      <c r="B202" s="83" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -15000,7 +15018,7 @@
       <c r="D202" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E202" s="91" t="inlineStr">
+      <c r="E202" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15058,7 +15076,7 @@
           <t>PS5-61-12</t>
         </is>
       </c>
-      <c r="B203" s="79" t="inlineStr">
+      <c r="B203" s="83" t="inlineStr">
         <is>
           <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
@@ -15069,7 +15087,7 @@
       <c r="D203" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E203" s="91" t="inlineStr">
+      <c r="E203" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15080,7 +15098,7 @@
       <c r="G203" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H203" s="91" t="inlineStr">
+      <c r="H203" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15110,7 +15128,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N203" s="69" t="inlineStr">
+      <c r="N203" s="70" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -15127,7 +15145,7 @@
           <t>PS5-61-13</t>
         </is>
       </c>
-      <c r="B204" s="79" t="inlineStr">
+      <c r="B204" s="83" t="inlineStr">
         <is>
           <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
@@ -15138,7 +15156,7 @@
       <c r="D204" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E204" s="91" t="inlineStr">
+      <c r="E204" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15149,7 +15167,7 @@
       <c r="G204" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H204" s="69" t="inlineStr">
+      <c r="H204" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15179,7 +15197,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N204" s="69" t="inlineStr">
+      <c r="N204" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15196,7 +15214,7 @@
           <t>PS5-61-14</t>
         </is>
       </c>
-      <c r="B205" s="79" t="inlineStr">
+      <c r="B205" s="83" t="inlineStr">
         <is>
           <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
@@ -15207,7 +15225,7 @@
       <c r="D205" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E205" s="91" t="inlineStr">
+      <c r="E205" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15218,7 +15236,7 @@
       <c r="G205" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H205" s="69" t="inlineStr">
+      <c r="H205" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15248,7 +15266,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N205" s="69" t="inlineStr">
+      <c r="N205" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15265,7 +15283,7 @@
           <t>PS5-62-01</t>
         </is>
       </c>
-      <c r="B206" s="79" t="inlineStr">
+      <c r="B206" s="83" t="inlineStr">
         <is>
           <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
@@ -15287,7 +15305,7 @@
       <c r="G206" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H206" s="69" t="inlineStr">
+      <c r="H206" s="70" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -15317,7 +15335,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N206" s="69" t="inlineStr">
+      <c r="N206" s="70" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -15334,7 +15352,7 @@
           <t>PS5-62-02</t>
         </is>
       </c>
-      <c r="B207" s="79" t="inlineStr">
+      <c r="B207" s="83" t="inlineStr">
         <is>
           <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
@@ -15356,7 +15374,7 @@
       <c r="G207" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H207" s="69" t="inlineStr">
+      <c r="H207" s="70" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -15386,7 +15404,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N207" s="69" t="inlineStr">
+      <c r="N207" s="70" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -15403,7 +15421,7 @@
           <t>PS5-62-03</t>
         </is>
       </c>
-      <c r="B208" s="79" t="inlineStr">
+      <c r="B208" s="83" t="inlineStr">
         <is>
           <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
@@ -15414,7 +15432,7 @@
       <c r="D208" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E208" s="91" t="inlineStr">
+      <c r="E208" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15425,7 +15443,7 @@
       <c r="G208" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H208" s="68" t="inlineStr">
+      <c r="H208" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15455,7 +15473,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N208" s="68" t="inlineStr">
+      <c r="N208" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15472,7 +15490,7 @@
           <t>PS5-62-04</t>
         </is>
       </c>
-      <c r="B209" s="79" t="inlineStr">
+      <c r="B209" s="83" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -15483,7 +15501,7 @@
       <c r="D209" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E209" s="91" t="inlineStr">
+      <c r="E209" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15541,7 +15559,7 @@
           <t>PS5-62-05</t>
         </is>
       </c>
-      <c r="B210" s="79" t="inlineStr">
+      <c r="B210" s="83" t="inlineStr">
         <is>
           <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
@@ -15552,7 +15570,7 @@
       <c r="D210" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E210" s="91" t="inlineStr">
+      <c r="E210" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15563,7 +15581,7 @@
       <c r="G210" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H210" s="69" t="inlineStr">
+      <c r="H210" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15593,7 +15611,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N210" s="69" t="inlineStr">
+      <c r="N210" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15610,7 +15628,7 @@
           <t>PS5-62-06</t>
         </is>
       </c>
-      <c r="B211" s="79" t="inlineStr">
+      <c r="B211" s="83" t="inlineStr">
         <is>
           <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
@@ -15621,7 +15639,7 @@
       <c r="D211" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E211" s="91" t="inlineStr">
+      <c r="E211" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15632,7 +15650,7 @@
       <c r="G211" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H211" s="69" t="inlineStr">
+      <c r="H211" s="70" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -15662,7 +15680,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N211" s="69" t="inlineStr">
+      <c r="N211" s="70" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -15679,7 +15697,7 @@
           <t>PS5-62-07</t>
         </is>
       </c>
-      <c r="B212" s="79" t="inlineStr">
+      <c r="B212" s="83" t="inlineStr">
         <is>
           <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
@@ -15690,7 +15708,7 @@
       <c r="D212" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E212" s="69" t="inlineStr">
+      <c r="E212" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15701,7 +15719,7 @@
       <c r="G212" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H212" s="69" t="inlineStr">
+      <c r="H212" s="70" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -15731,7 +15749,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N212" s="69" t="inlineStr">
+      <c r="N212" s="70" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -15748,7 +15766,7 @@
           <t>PS5-62-08</t>
         </is>
       </c>
-      <c r="B213" s="79" t="inlineStr">
+      <c r="B213" s="83" t="inlineStr">
         <is>
           <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
@@ -15759,7 +15777,7 @@
       <c r="D213" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E213" s="91" t="inlineStr">
+      <c r="E213" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15770,7 +15788,7 @@
       <c r="G213" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H213" s="69" t="inlineStr">
+      <c r="H213" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -15800,7 +15818,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N213" s="69" t="inlineStr">
+      <c r="N213" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -15817,7 +15835,7 @@
           <t>PS5-62-09</t>
         </is>
       </c>
-      <c r="B214" s="79" t="inlineStr">
+      <c r="B214" s="83" t="inlineStr">
         <is>
           <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
@@ -15828,7 +15846,7 @@
       <c r="D214" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E214" s="69" t="inlineStr">
+      <c r="E214" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15839,7 +15857,7 @@
       <c r="G214" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H214" s="69" t="inlineStr">
+      <c r="H214" s="70" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -15869,7 +15887,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N214" s="69" t="inlineStr">
+      <c r="N214" s="70" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -15886,7 +15904,7 @@
           <t>PS5-62-10</t>
         </is>
       </c>
-      <c r="B215" s="79" t="inlineStr">
+      <c r="B215" s="83" t="inlineStr">
         <is>
           <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
@@ -15897,7 +15915,7 @@
       <c r="D215" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E215" s="69" t="inlineStr">
+      <c r="E215" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15908,7 +15926,7 @@
       <c r="G215" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="H215" s="69" t="inlineStr">
+      <c r="H215" s="70" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -15938,7 +15956,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N215" s="69" t="inlineStr">
+      <c r="N215" s="70" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -15955,7 +15973,7 @@
           <t>PS5-62-11</t>
         </is>
       </c>
-      <c r="B216" s="79" t="inlineStr">
+      <c r="B216" s="83" t="inlineStr">
         <is>
           <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
@@ -15966,7 +15984,7 @@
       <c r="D216" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E216" s="91" t="inlineStr">
+      <c r="E216" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15977,7 +15995,7 @@
       <c r="G216" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H216" s="69" t="inlineStr">
+      <c r="H216" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -16007,7 +16025,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N216" s="69" t="inlineStr">
+      <c r="N216" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -16024,7 +16042,7 @@
           <t>PS5-62-12</t>
         </is>
       </c>
-      <c r="B217" s="79" t="inlineStr">
+      <c r="B217" s="83" t="inlineStr">
         <is>
           <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
@@ -16035,7 +16053,7 @@
       <c r="D217" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E217" s="91" t="inlineStr">
+      <c r="E217" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16046,7 +16064,7 @@
       <c r="G217" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H217" s="91" t="inlineStr">
+      <c r="H217" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16093,7 +16111,7 @@
           <t>PS5-62-13</t>
         </is>
       </c>
-      <c r="B218" s="79" t="inlineStr">
+      <c r="B218" s="83" t="inlineStr">
         <is>
           <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
@@ -16104,7 +16122,7 @@
       <c r="D218" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E218" s="69" t="inlineStr">
+      <c r="E218" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16115,7 +16133,7 @@
       <c r="G218" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H218" s="91" t="inlineStr">
+      <c r="H218" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16162,7 +16180,7 @@
           <t>PS5-62-14</t>
         </is>
       </c>
-      <c r="B219" s="79" t="inlineStr">
+      <c r="B219" s="83" t="inlineStr">
         <is>
           <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
@@ -16173,7 +16191,7 @@
       <c r="D219" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E219" s="91" t="inlineStr">
+      <c r="E219" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16184,7 +16202,7 @@
       <c r="G219" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H219" s="69" t="inlineStr">
+      <c r="H219" s="70" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16214,7 +16232,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N219" s="69" t="inlineStr">
+      <c r="N219" s="70" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16231,7 +16249,7 @@
           <t>PS5-62-15</t>
         </is>
       </c>
-      <c r="B220" s="79" t="inlineStr">
+      <c r="B220" s="83" t="inlineStr">
         <is>
           <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
@@ -16242,7 +16260,7 @@
       <c r="D220" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E220" s="91" t="inlineStr">
+      <c r="E220" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16253,7 +16271,7 @@
       <c r="G220" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H220" s="69" t="inlineStr">
+      <c r="H220" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16283,7 +16301,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N220" s="69" t="inlineStr">
+      <c r="N220" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16300,7 +16318,7 @@
           <t>PS5-62-16</t>
         </is>
       </c>
-      <c r="B221" s="79" t="inlineStr">
+      <c r="B221" s="83" t="inlineStr">
         <is>
           <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
@@ -16311,7 +16329,7 @@
       <c r="D221" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E221" s="91" t="inlineStr">
+      <c r="E221" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16322,7 +16340,7 @@
       <c r="G221" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H221" s="69" t="inlineStr">
+      <c r="H221" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16352,7 +16370,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N221" s="69" t="inlineStr">
+      <c r="N221" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16369,7 +16387,7 @@
           <t>PS5-62-17</t>
         </is>
       </c>
-      <c r="B222" s="79" t="inlineStr">
+      <c r="B222" s="83" t="inlineStr">
         <is>
           <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
@@ -16380,7 +16398,7 @@
       <c r="D222" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E222" s="91" t="inlineStr">
+      <c r="E222" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16391,7 +16409,7 @@
       <c r="G222" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H222" s="69" t="inlineStr">
+      <c r="H222" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16421,7 +16439,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N222" s="69" t="inlineStr">
+      <c r="N222" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16438,7 +16456,7 @@
           <t>PS5-62-18</t>
         </is>
       </c>
-      <c r="B223" s="79" t="inlineStr">
+      <c r="B223" s="83" t="inlineStr">
         <is>
           <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
@@ -16449,7 +16467,7 @@
       <c r="D223" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E223" s="91" t="inlineStr">
+      <c r="E223" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16460,7 +16478,7 @@
       <c r="G223" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H223" s="69" t="inlineStr">
+      <c r="H223" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16490,7 +16508,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N223" s="69" t="inlineStr">
+      <c r="N223" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16507,7 +16525,7 @@
           <t>PS5-62-19</t>
         </is>
       </c>
-      <c r="B224" s="79" t="inlineStr">
+      <c r="B224" s="83" t="inlineStr">
         <is>
           <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
@@ -16518,7 +16536,7 @@
       <c r="D224" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E224" s="91" t="inlineStr">
+      <c r="E224" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16529,7 +16547,7 @@
       <c r="G224" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H224" s="69" t="inlineStr">
+      <c r="H224" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16559,7 +16577,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N224" s="69" t="inlineStr">
+      <c r="N224" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16576,7 +16594,7 @@
           <t>PS5-62-20</t>
         </is>
       </c>
-      <c r="B225" s="79" t="inlineStr">
+      <c r="B225" s="83" t="inlineStr">
         <is>
           <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
@@ -16587,7 +16605,7 @@
       <c r="D225" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E225" s="91" t="inlineStr">
+      <c r="E225" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16598,7 +16616,7 @@
       <c r="G225" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H225" s="69" t="inlineStr">
+      <c r="H225" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16628,7 +16646,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N225" s="69" t="inlineStr">
+      <c r="N225" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16645,7 +16663,7 @@
           <t>PS5-63-01</t>
         </is>
       </c>
-      <c r="B226" s="79" t="inlineStr">
+      <c r="B226" s="83" t="inlineStr">
         <is>
           <t>PS5-63-01 - Electrical Earthing</t>
         </is>
@@ -16656,7 +16674,7 @@
       <c r="D226" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E226" s="69" t="inlineStr">
+      <c r="E226" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16667,7 +16685,7 @@
       <c r="G226" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="H226" s="69" t="inlineStr">
+      <c r="H226" s="70" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -16697,7 +16715,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N226" s="69" t="inlineStr">
+      <c r="N226" s="70" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -16714,7 +16732,7 @@
           <t>PS5-63-02</t>
         </is>
       </c>
-      <c r="B227" s="79" t="inlineStr">
+      <c r="B227" s="83" t="inlineStr">
         <is>
           <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
@@ -16725,7 +16743,7 @@
       <c r="D227" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E227" s="91" t="inlineStr">
+      <c r="E227" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16736,7 +16754,7 @@
       <c r="G227" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H227" s="69" t="inlineStr">
+      <c r="H227" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16766,7 +16784,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N227" s="69" t="inlineStr">
+      <c r="N227" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16783,7 +16801,7 @@
           <t>PS5-63-03</t>
         </is>
       </c>
-      <c r="B228" s="79" t="inlineStr">
+      <c r="B228" s="83" t="inlineStr">
         <is>
           <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
@@ -16794,7 +16812,7 @@
       <c r="D228" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E228" s="91" t="inlineStr">
+      <c r="E228" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16805,7 +16823,7 @@
       <c r="G228" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H228" s="68" t="inlineStr">
+      <c r="H228" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16835,7 +16853,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N228" s="68" t="inlineStr">
+      <c r="N228" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16852,7 +16870,7 @@
           <t>PS5-63-04</t>
         </is>
       </c>
-      <c r="B229" s="79" t="inlineStr">
+      <c r="B229" s="83" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -16863,7 +16881,7 @@
       <c r="D229" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E229" s="69" t="inlineStr">
+      <c r="E229" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -16874,7 +16892,7 @@
       <c r="G229" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H229" s="91" t="inlineStr">
+      <c r="H229" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16921,7 +16939,7 @@
           <t>PS5-63-05</t>
         </is>
       </c>
-      <c r="B230" s="79" t="inlineStr">
+      <c r="B230" s="83" t="inlineStr">
         <is>
           <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
@@ -16932,7 +16950,7 @@
       <c r="D230" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E230" s="91" t="inlineStr">
+      <c r="E230" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16943,7 +16961,7 @@
       <c r="G230" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H230" s="69" t="inlineStr">
+      <c r="H230" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16973,7 +16991,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N230" s="69" t="inlineStr">
+      <c r="N230" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16990,7 +17008,7 @@
           <t>PS5-63-06</t>
         </is>
       </c>
-      <c r="B231" s="79" t="inlineStr">
+      <c r="B231" s="83" t="inlineStr">
         <is>
           <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
@@ -17001,7 +17019,7 @@
       <c r="D231" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E231" s="91" t="inlineStr">
+      <c r="E231" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17012,7 +17030,7 @@
       <c r="G231" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H231" s="69" t="inlineStr">
+      <c r="H231" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17042,7 +17060,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N231" s="69" t="inlineStr">
+      <c r="N231" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17059,7 +17077,7 @@
           <t>PS5-63-07</t>
         </is>
       </c>
-      <c r="B232" s="79" t="inlineStr">
+      <c r="B232" s="83" t="inlineStr">
         <is>
           <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
@@ -17070,7 +17088,7 @@
       <c r="D232" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E232" s="91" t="inlineStr">
+      <c r="E232" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17081,7 +17099,7 @@
       <c r="G232" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H232" s="69" t="inlineStr">
+      <c r="H232" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17111,7 +17129,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N232" s="69" t="inlineStr">
+      <c r="N232" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17128,7 +17146,7 @@
           <t>PS5-71-01</t>
         </is>
       </c>
-      <c r="B233" s="79" t="inlineStr">
+      <c r="B233" s="83" t="inlineStr">
         <is>
           <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
@@ -17139,7 +17157,7 @@
       <c r="D233" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E233" s="69" t="inlineStr">
+      <c r="E233" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -17150,7 +17168,7 @@
       <c r="G233" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="H233" s="69" t="inlineStr">
+      <c r="H233" s="70" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -17180,7 +17198,7 @@
           <t>27/30</t>
         </is>
       </c>
-      <c r="N233" s="69" t="inlineStr">
+      <c r="N233" s="70" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -17197,7 +17215,7 @@
           <t>PS5-71-02</t>
         </is>
       </c>
-      <c r="B234" s="79" t="inlineStr">
+      <c r="B234" s="83" t="inlineStr">
         <is>
           <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
@@ -17208,7 +17226,7 @@
       <c r="D234" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E234" s="69" t="inlineStr">
+      <c r="E234" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -17219,7 +17237,7 @@
       <c r="G234" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H234" s="68" t="inlineStr">
+      <c r="H234" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -17249,7 +17267,7 @@
           <t>9/10</t>
         </is>
       </c>
-      <c r="N234" s="68" t="inlineStr">
+      <c r="N234" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -17266,7 +17284,7 @@
           <t>PS5-71-03</t>
         </is>
       </c>
-      <c r="B235" s="79" t="inlineStr">
+      <c r="B235" s="83" t="inlineStr">
         <is>
           <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
@@ -17277,7 +17295,7 @@
       <c r="D235" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E235" s="91" t="inlineStr">
+      <c r="E235" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17288,7 +17306,7 @@
       <c r="G235" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H235" s="91" t="inlineStr">
+      <c r="H235" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17318,7 +17336,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N235" s="69" t="inlineStr">
+      <c r="N235" s="70" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -17335,7 +17353,7 @@
           <t>PS5-71-04</t>
         </is>
       </c>
-      <c r="B236" s="79" t="inlineStr">
+      <c r="B236" s="83" t="inlineStr">
         <is>
           <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
@@ -17346,7 +17364,7 @@
       <c r="D236" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E236" s="68" t="inlineStr">
+      <c r="E236" s="69" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -17357,7 +17375,7 @@
       <c r="G236" s="23" t="n">
         <v>66</v>
       </c>
-      <c r="H236" s="68" t="inlineStr">
+      <c r="H236" s="69" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -17387,7 +17405,7 @@
           <t>42/47</t>
         </is>
       </c>
-      <c r="N236" s="68" t="inlineStr">
+      <c r="N236" s="69" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -17404,7 +17422,7 @@
           <t>PS5-71-05</t>
         </is>
       </c>
-      <c r="B237" s="79" t="inlineStr">
+      <c r="B237" s="83" t="inlineStr">
         <is>
           <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
@@ -17415,7 +17433,7 @@
       <c r="D237" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E237" s="69" t="inlineStr">
+      <c r="E237" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -17426,7 +17444,7 @@
       <c r="G237" s="23" t="n">
         <v>48</v>
       </c>
-      <c r="H237" s="68" t="inlineStr">
+      <c r="H237" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -17456,7 +17474,7 @@
           <t>13/14</t>
         </is>
       </c>
-      <c r="N237" s="68" t="inlineStr">
+      <c r="N237" s="69" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -17473,7 +17491,7 @@
           <t>PS5-71-06</t>
         </is>
       </c>
-      <c r="B238" s="79" t="inlineStr">
+      <c r="B238" s="83" t="inlineStr">
         <is>
           <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
@@ -17484,7 +17502,7 @@
       <c r="D238" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E238" s="68" t="inlineStr">
+      <c r="E238" s="69" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -17495,7 +17513,7 @@
       <c r="G238" s="23" t="n">
         <v>36</v>
       </c>
-      <c r="H238" s="68" t="inlineStr">
+      <c r="H238" s="69" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -17525,7 +17543,7 @@
           <t>21/22</t>
         </is>
       </c>
-      <c r="N238" s="68" t="inlineStr">
+      <c r="N238" s="69" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -17542,7 +17560,7 @@
           <t>PS5-71-07</t>
         </is>
       </c>
-      <c r="B239" s="79" t="inlineStr">
+      <c r="B239" s="83" t="inlineStr">
         <is>
           <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
@@ -17553,7 +17571,7 @@
       <c r="D239" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E239" s="69" t="inlineStr">
+      <c r="E239" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17564,7 +17582,7 @@
       <c r="G239" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H239" s="68" t="inlineStr">
+      <c r="H239" s="69" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17594,7 +17612,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N239" s="68" t="inlineStr">
+      <c r="N239" s="69" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17611,7 +17629,7 @@
           <t>PS5-71-08</t>
         </is>
       </c>
-      <c r="B240" s="79" t="inlineStr">
+      <c r="B240" s="83" t="inlineStr">
         <is>
           <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
@@ -17622,7 +17640,7 @@
       <c r="D240" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E240" s="69" t="inlineStr">
+      <c r="E240" s="70" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -17680,7 +17698,7 @@
           <t>PS5-71-09</t>
         </is>
       </c>
-      <c r="B241" s="79" t="inlineStr">
+      <c r="B241" s="83" t="inlineStr">
         <is>
           <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
@@ -17691,7 +17709,7 @@
       <c r="D241" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E241" s="69" t="inlineStr">
+      <c r="E241" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17749,7 +17767,7 @@
           <t>PS5-71-12</t>
         </is>
       </c>
-      <c r="B242" s="79" t="inlineStr">
+      <c r="B242" s="83" t="inlineStr">
         <is>
           <t>PS5-71-12 - CFO Service Tank</t>
         </is>
@@ -17760,7 +17778,7 @@
       <c r="D242" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="E242" s="68" t="inlineStr">
+      <c r="E242" s="69" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -17771,7 +17789,7 @@
       <c r="G242" s="23" t="n">
         <v>66</v>
       </c>
-      <c r="H242" s="68" t="inlineStr">
+      <c r="H242" s="69" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17801,7 +17819,7 @@
           <t>26/31</t>
         </is>
       </c>
-      <c r="N242" s="68" t="inlineStr">
+      <c r="N242" s="69" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17818,7 +17836,7 @@
           <t>PS5-71-13</t>
         </is>
       </c>
-      <c r="B243" s="79" t="inlineStr">
+      <c r="B243" s="83" t="inlineStr">
         <is>
           <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
@@ -17829,7 +17847,7 @@
       <c r="D243" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E243" s="69" t="inlineStr">
+      <c r="E243" s="70" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -17840,7 +17858,7 @@
       <c r="G243" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="H243" s="68" t="inlineStr">
+      <c r="H243" s="69" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -17870,7 +17888,7 @@
           <t>12/14</t>
         </is>
       </c>
-      <c r="N243" s="68" t="inlineStr">
+      <c r="N243" s="69" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -17887,7 +17905,7 @@
           <t>PS5-71-14</t>
         </is>
       </c>
-      <c r="B244" s="79" t="inlineStr">
+      <c r="B244" s="83" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
@@ -17898,7 +17916,7 @@
       <c r="D244" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E244" s="69" t="inlineStr">
+      <c r="E244" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -17939,7 +17957,7 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N244" s="68" t="inlineStr">
+      <c r="N244" s="69" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -17956,7 +17974,7 @@
           <t>PS5-71-15</t>
         </is>
       </c>
-      <c r="B245" s="79" t="inlineStr">
+      <c r="B245" s="83" t="inlineStr">
         <is>
           <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
@@ -17967,7 +17985,7 @@
       <c r="D245" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E245" s="69" t="inlineStr">
+      <c r="E245" s="70" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
@@ -17978,7 +17996,7 @@
       <c r="G245" s="23" t="n">
         <v>41</v>
       </c>
-      <c r="H245" s="68" t="inlineStr">
+      <c r="H245" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -18008,7 +18026,7 @@
           <t>17/20</t>
         </is>
       </c>
-      <c r="N245" s="68" t="inlineStr">
+      <c r="N245" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -18025,7 +18043,7 @@
           <t>PS5-71-16</t>
         </is>
       </c>
-      <c r="B246" s="79" t="inlineStr">
+      <c r="B246" s="83" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
@@ -18036,7 +18054,7 @@
       <c r="D246" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E246" s="69" t="inlineStr">
+      <c r="E246" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18077,7 +18095,7 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N246" s="68" t="inlineStr">
+      <c r="N246" s="69" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -18094,7 +18112,7 @@
           <t>PS5-71-17</t>
         </is>
       </c>
-      <c r="B247" s="79" t="inlineStr">
+      <c r="B247" s="83" t="inlineStr">
         <is>
           <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
@@ -18105,7 +18123,7 @@
       <c r="D247" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E247" s="69" t="inlineStr">
+      <c r="E247" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18163,7 +18181,7 @@
           <t>PS5-71-18</t>
         </is>
       </c>
-      <c r="B248" s="79" t="inlineStr">
+      <c r="B248" s="83" t="inlineStr">
         <is>
           <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
@@ -18174,7 +18192,7 @@
       <c r="D248" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E248" s="68" t="inlineStr">
+      <c r="E248" s="69" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
@@ -18185,7 +18203,7 @@
       <c r="G248" s="23" t="n">
         <v>47</v>
       </c>
-      <c r="H248" s="68" t="inlineStr">
+      <c r="H248" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18215,7 +18233,7 @@
           <t>20/20</t>
         </is>
       </c>
-      <c r="N248" s="68" t="inlineStr">
+      <c r="N248" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18232,7 +18250,7 @@
           <t>PS5-71-19</t>
         </is>
       </c>
-      <c r="B249" s="79" t="inlineStr">
+      <c r="B249" s="83" t="inlineStr">
         <is>
           <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
@@ -18243,7 +18261,7 @@
       <c r="D249" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E249" s="69" t="inlineStr">
+      <c r="E249" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18254,7 +18272,7 @@
       <c r="G249" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="H249" s="68" t="inlineStr">
+      <c r="H249" s="69" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -18284,7 +18302,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N249" s="68" t="inlineStr">
+      <c r="N249" s="69" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -18301,7 +18319,7 @@
           <t>PS5-71-20</t>
         </is>
       </c>
-      <c r="B250" s="79" t="inlineStr">
+      <c r="B250" s="83" t="inlineStr">
         <is>
           <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
@@ -18312,7 +18330,7 @@
       <c r="D250" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E250" s="68" t="inlineStr">
+      <c r="E250" s="69" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -18323,7 +18341,7 @@
       <c r="G250" s="23" t="n">
         <v>49</v>
       </c>
-      <c r="H250" s="68" t="inlineStr">
+      <c r="H250" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18353,7 +18371,7 @@
           <t>20/20</t>
         </is>
       </c>
-      <c r="N250" s="68" t="inlineStr">
+      <c r="N250" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18370,7 +18388,7 @@
           <t>PS5-71-21</t>
         </is>
       </c>
-      <c r="B251" s="79" t="inlineStr">
+      <c r="B251" s="83" t="inlineStr">
         <is>
           <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
@@ -18381,7 +18399,7 @@
       <c r="D251" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E251" s="69" t="inlineStr">
+      <c r="E251" s="70" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -18439,7 +18457,7 @@
           <t>PS5-71-22</t>
         </is>
       </c>
-      <c r="B252" s="79" t="inlineStr">
+      <c r="B252" s="83" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -18450,7 +18468,7 @@
       <c r="D252" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="E252" s="69" t="inlineStr">
+      <c r="E252" s="70" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -18498,7 +18516,7 @@
       </c>
       <c r="O252" s="27" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>DONE(full)</t>
         </is>
       </c>
     </row>
@@ -18508,7 +18526,7 @@
           <t>PS5-71-23</t>
         </is>
       </c>
-      <c r="B253" s="79" t="inlineStr">
+      <c r="B253" s="83" t="inlineStr">
         <is>
           <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
@@ -18519,7 +18537,7 @@
       <c r="D253" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E253" s="69" t="inlineStr">
+      <c r="E253" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -18530,7 +18548,7 @@
       <c r="G253" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H253" s="68" t="inlineStr">
+      <c r="H253" s="69" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -18560,7 +18578,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N253" s="68" t="inlineStr">
+      <c r="N253" s="69" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -18577,7 +18595,7 @@
           <t>PS5-74-01</t>
         </is>
       </c>
-      <c r="B254" s="79" t="inlineStr">
+      <c r="B254" s="83" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
@@ -18588,7 +18606,7 @@
       <c r="D254" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E254" s="69" t="inlineStr">
+      <c r="E254" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -18599,7 +18617,7 @@
       <c r="G254" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H254" s="68" t="inlineStr">
+      <c r="H254" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -18629,7 +18647,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="N254" s="68" t="inlineStr">
+      <c r="N254" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -18646,7 +18664,7 @@
           <t>PS5-74-02</t>
         </is>
       </c>
-      <c r="B255" s="79" t="inlineStr">
+      <c r="B255" s="83" t="inlineStr">
         <is>
           <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
@@ -18668,7 +18686,7 @@
       <c r="G255" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H255" s="68" t="inlineStr">
+      <c r="H255" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -18698,7 +18716,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N255" s="68" t="inlineStr">
+      <c r="N255" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -18715,7 +18733,7 @@
           <t>PS5-74-03</t>
         </is>
       </c>
-      <c r="B256" s="79" t="inlineStr">
+      <c r="B256" s="83" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -18726,7 +18744,7 @@
       <c r="D256" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E256" s="69" t="inlineStr">
+      <c r="E256" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -18784,7 +18802,7 @@
           <t>PS5-74-04</t>
         </is>
       </c>
-      <c r="B257" s="79" t="inlineStr">
+      <c r="B257" s="83" t="inlineStr">
         <is>
           <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
@@ -18795,7 +18813,7 @@
       <c r="D257" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E257" s="91" t="inlineStr">
+      <c r="E257" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18806,7 +18824,7 @@
       <c r="G257" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="H257" s="68" t="inlineStr">
+      <c r="H257" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -18836,7 +18854,7 @@
           <t>6/8</t>
         </is>
       </c>
-      <c r="N257" s="68" t="inlineStr">
+      <c r="N257" s="69" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
@@ -18853,7 +18871,7 @@
           <t>PS5-75-01</t>
         </is>
       </c>
-      <c r="B258" s="79" t="inlineStr">
+      <c r="B258" s="83" t="inlineStr">
         <is>
           <t>PS5-75-01 - DRA Injection Package</t>
         </is>
@@ -18864,7 +18882,7 @@
       <c r="D258" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E258" s="91" t="inlineStr">
+      <c r="E258" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18875,7 +18893,7 @@
       <c r="G258" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H258" s="69" t="inlineStr">
+      <c r="H258" s="70" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -18905,7 +18923,7 @@
           <t>12/15</t>
         </is>
       </c>
-      <c r="N258" s="69" t="inlineStr">
+      <c r="N258" s="70" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -18922,7 +18940,7 @@
           <t>PS5-75-02</t>
         </is>
       </c>
-      <c r="B259" s="79" t="inlineStr">
+      <c r="B259" s="83" t="inlineStr">
         <is>
           <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
@@ -18933,7 +18951,7 @@
       <c r="D259" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E259" s="69" t="inlineStr">
+      <c r="E259" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -18944,7 +18962,7 @@
       <c r="G259" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H259" s="68" t="inlineStr">
+      <c r="H259" s="69" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -18974,7 +18992,7 @@
           <t>13/14</t>
         </is>
       </c>
-      <c r="N259" s="68" t="inlineStr">
+      <c r="N259" s="69" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -18991,7 +19009,7 @@
           <t>PS5-75-03</t>
         </is>
       </c>
-      <c r="B260" s="79" t="inlineStr">
+      <c r="B260" s="83" t="inlineStr">
         <is>
           <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
@@ -19002,7 +19020,7 @@
       <c r="D260" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E260" s="69" t="inlineStr">
+      <c r="E260" s="70" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
@@ -19013,7 +19031,7 @@
       <c r="G260" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H260" s="68" t="inlineStr">
+      <c r="H260" s="69" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -19043,7 +19061,7 @@
           <t>12/15</t>
         </is>
       </c>
-      <c r="N260" s="68" t="inlineStr">
+      <c r="N260" s="69" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -19060,7 +19078,7 @@
           <t>PS5-78-01</t>
         </is>
       </c>
-      <c r="B261" s="79" t="inlineStr">
+      <c r="B261" s="83" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -19071,7 +19089,7 @@
       <c r="D261" s="23" t="n">
         <v>71</v>
       </c>
-      <c r="E261" s="68" t="inlineStr">
+      <c r="E261" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -19082,7 +19100,7 @@
       <c r="G261" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H261" s="68" t="inlineStr">
+      <c r="H261" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -19112,12 +19130,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N261" s="68" t="inlineStr">
+      <c r="N261" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
       </c>
-      <c r="O261" s="68" t="inlineStr">
+      <c r="O261" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -19129,7 +19147,7 @@
           <t>PS5-79-01</t>
         </is>
       </c>
-      <c r="B262" s="79" t="inlineStr">
+      <c r="B262" s="83" t="inlineStr">
         <is>
           <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
@@ -19140,7 +19158,7 @@
       <c r="D262" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E262" s="91" t="inlineStr">
+      <c r="E262" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19151,7 +19169,7 @@
       <c r="G262" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H262" s="69" t="inlineStr">
+      <c r="H262" s="70" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -19181,7 +19199,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N262" s="69" t="inlineStr">
+      <c r="N262" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19198,7 +19216,7 @@
           <t>PS5-79-02</t>
         </is>
       </c>
-      <c r="B263" s="79" t="inlineStr">
+      <c r="B263" s="83" t="inlineStr">
         <is>
           <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
@@ -19209,7 +19227,7 @@
       <c r="D263" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E263" s="91" t="inlineStr">
+      <c r="E263" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19220,7 +19238,7 @@
       <c r="G263" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H263" s="69" t="inlineStr">
+      <c r="H263" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19250,7 +19268,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N263" s="69" t="inlineStr">
+      <c r="N263" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -19267,7 +19285,7 @@
           <t>PS5-79-03</t>
         </is>
       </c>
-      <c r="B264" s="79" t="inlineStr">
+      <c r="B264" s="83" t="inlineStr">
         <is>
           <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
@@ -19278,7 +19296,7 @@
       <c r="D264" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E264" s="91" t="inlineStr">
+      <c r="E264" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19289,7 +19307,7 @@
       <c r="G264" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H264" s="69" t="inlineStr">
+      <c r="H264" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19319,7 +19337,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N264" s="69" t="inlineStr">
+      <c r="N264" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19336,7 +19354,7 @@
           <t>PS5-79-04</t>
         </is>
       </c>
-      <c r="B265" s="79" t="inlineStr">
+      <c r="B265" s="83" t="inlineStr">
         <is>
           <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
@@ -19347,7 +19365,7 @@
       <c r="D265" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E265" s="91" t="inlineStr">
+      <c r="E265" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19358,7 +19376,7 @@
       <c r="G265" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H265" s="69" t="inlineStr">
+      <c r="H265" s="70" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19388,7 +19406,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N265" s="69" t="inlineStr">
+      <c r="N265" s="70" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19405,7 +19423,7 @@
           <t>PS5-79-05</t>
         </is>
       </c>
-      <c r="B266" s="79" t="inlineStr">
+      <c r="B266" s="83" t="inlineStr">
         <is>
           <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
@@ -19416,7 +19434,7 @@
       <c r="D266" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E266" s="91" t="inlineStr">
+      <c r="E266" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19427,7 +19445,7 @@
       <c r="G266" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H266" s="69" t="inlineStr">
+      <c r="H266" s="70" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -19457,7 +19475,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N266" s="69" t="inlineStr">
+      <c r="N266" s="70" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -19474,7 +19492,7 @@
           <t>PS5-79-06</t>
         </is>
       </c>
-      <c r="B267" s="79" t="inlineStr">
+      <c r="B267" s="83" t="inlineStr">
         <is>
           <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
@@ -19485,7 +19503,7 @@
       <c r="D267" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E267" s="91" t="inlineStr">
+      <c r="E267" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19496,7 +19514,7 @@
       <c r="G267" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H267" s="69" t="inlineStr">
+      <c r="H267" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -19526,7 +19544,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N267" s="69" t="inlineStr">
+      <c r="N267" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -19543,7 +19561,7 @@
           <t>PS5-79-07</t>
         </is>
       </c>
-      <c r="B268" s="79" t="inlineStr">
+      <c r="B268" s="83" t="inlineStr">
         <is>
           <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
@@ -19554,7 +19572,7 @@
       <c r="D268" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E268" s="91" t="inlineStr">
+      <c r="E268" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19565,7 +19583,7 @@
       <c r="G268" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H268" s="69" t="inlineStr">
+      <c r="H268" s="70" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -19595,7 +19613,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N268" s="69" t="inlineStr">
+      <c r="N268" s="70" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -19612,7 +19630,7 @@
           <t>PS5-79-08</t>
         </is>
       </c>
-      <c r="B269" s="79" t="inlineStr">
+      <c r="B269" s="83" t="inlineStr">
         <is>
           <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
@@ -19623,7 +19641,7 @@
       <c r="D269" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E269" s="91" t="inlineStr">
+      <c r="E269" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19634,7 +19652,7 @@
       <c r="G269" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H269" s="69" t="inlineStr">
+      <c r="H269" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -19664,7 +19682,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N269" s="69" t="inlineStr">
+      <c r="N269" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -19681,7 +19699,7 @@
           <t>PS5-79-09</t>
         </is>
       </c>
-      <c r="B270" s="79" t="inlineStr">
+      <c r="B270" s="83" t="inlineStr">
         <is>
           <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
@@ -19692,7 +19710,7 @@
       <c r="D270" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E270" s="91" t="inlineStr">
+      <c r="E270" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19703,7 +19721,7 @@
       <c r="G270" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H270" s="69" t="inlineStr">
+      <c r="H270" s="70" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -19733,7 +19751,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N270" s="69" t="inlineStr">
+      <c r="N270" s="70" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -19750,7 +19768,7 @@
           <t>PS5-79-10</t>
         </is>
       </c>
-      <c r="B271" s="79" t="inlineStr">
+      <c r="B271" s="83" t="inlineStr">
         <is>
           <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
@@ -19761,7 +19779,7 @@
       <c r="D271" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E271" s="91" t="inlineStr">
+      <c r="E271" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19772,7 +19790,7 @@
       <c r="G271" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="H271" s="69" t="inlineStr">
+      <c r="H271" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -19802,7 +19820,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N271" s="69" t="inlineStr">
+      <c r="N271" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -19819,7 +19837,7 @@
           <t>PS5-79-11</t>
         </is>
       </c>
-      <c r="B272" s="79" t="inlineStr">
+      <c r="B272" s="83" t="inlineStr">
         <is>
           <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
@@ -19830,7 +19848,7 @@
       <c r="D272" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E272" s="91" t="inlineStr">
+      <c r="E272" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19841,7 +19859,7 @@
       <c r="G272" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H272" s="69" t="inlineStr">
+      <c r="H272" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -19871,7 +19889,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N272" s="69" t="inlineStr">
+      <c r="N272" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -19888,7 +19906,7 @@
           <t>PS5-79-12</t>
         </is>
       </c>
-      <c r="B273" s="79" t="inlineStr">
+      <c r="B273" s="83" t="inlineStr">
         <is>
           <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
@@ -19899,7 +19917,7 @@
       <c r="D273" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E273" s="91" t="inlineStr">
+      <c r="E273" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19910,7 +19928,7 @@
       <c r="G273" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="H273" s="69" t="inlineStr">
+      <c r="H273" s="70" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19940,7 +19958,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N273" s="69" t="inlineStr">
+      <c r="N273" s="70" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19957,7 +19975,7 @@
           <t>PS5-82-01</t>
         </is>
       </c>
-      <c r="B274" s="79" t="inlineStr">
+      <c r="B274" s="83" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
@@ -19968,7 +19986,7 @@
       <c r="D274" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E274" s="91" t="inlineStr">
+      <c r="E274" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19979,7 +19997,7 @@
       <c r="G274" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="H274" s="68" t="inlineStr">
+      <c r="H274" s="69" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -20009,7 +20027,7 @@
           <t>30/50</t>
         </is>
       </c>
-      <c r="N274" s="68" t="inlineStr">
+      <c r="N274" s="69" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -20026,7 +20044,7 @@
           <t>PS5-82-02</t>
         </is>
       </c>
-      <c r="B275" s="79" t="inlineStr">
+      <c r="B275" s="83" t="inlineStr">
         <is>
           <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
@@ -20037,7 +20055,7 @@
       <c r="D275" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E275" s="69" t="inlineStr">
+      <c r="E275" s="70" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
@@ -20048,7 +20066,7 @@
       <c r="G275" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H275" s="69" t="inlineStr">
+      <c r="H275" s="70" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -20078,7 +20096,7 @@
           <t>0/1</t>
         </is>
       </c>
-      <c r="N275" s="69" t="inlineStr">
+      <c r="N275" s="70" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -20095,7 +20113,7 @@
           <t>PS5-82-03</t>
         </is>
       </c>
-      <c r="B276" s="79" t="inlineStr">
+      <c r="B276" s="83" t="inlineStr">
         <is>
           <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
@@ -20106,7 +20124,7 @@
       <c r="D276" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E276" s="91" t="inlineStr">
+      <c r="E276" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20117,7 +20135,7 @@
       <c r="G276" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H276" s="69" t="inlineStr">
+      <c r="H276" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20147,7 +20165,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N276" s="69" t="inlineStr">
+      <c r="N276" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20164,7 +20182,7 @@
           <t>PS5-82-04</t>
         </is>
       </c>
-      <c r="B277" s="79" t="inlineStr">
+      <c r="B277" s="83" t="inlineStr">
         <is>
           <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
@@ -20175,7 +20193,7 @@
       <c r="D277" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E277" s="91" t="inlineStr">
+      <c r="E277" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20186,7 +20204,7 @@
       <c r="G277" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H277" s="68" t="inlineStr">
+      <c r="H277" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -20216,7 +20234,7 @@
           <t>6/8</t>
         </is>
       </c>
-      <c r="N277" s="68" t="inlineStr">
+      <c r="N277" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -20233,7 +20251,7 @@
           <t>PS5-82-05</t>
         </is>
       </c>
-      <c r="B278" s="79" t="inlineStr">
+      <c r="B278" s="83" t="inlineStr">
         <is>
           <t>PS5-82-05 - Office and Facilities building</t>
         </is>
@@ -20244,7 +20262,7 @@
       <c r="D278" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E278" s="91" t="inlineStr">
+      <c r="E278" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20255,7 +20273,7 @@
       <c r="G278" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H278" s="69" t="inlineStr">
+      <c r="H278" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20285,7 +20303,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N278" s="69" t="inlineStr">
+      <c r="N278" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20302,7 +20320,7 @@
           <t>PS5-82-06</t>
         </is>
       </c>
-      <c r="B279" s="79" t="inlineStr">
+      <c r="B279" s="83" t="inlineStr">
         <is>
           <t>PS5-82-06 - Guard House Building</t>
         </is>
@@ -20313,7 +20331,7 @@
       <c r="D279" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E279" s="91" t="inlineStr">
+      <c r="E279" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20324,7 +20342,7 @@
       <c r="G279" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H279" s="69" t="inlineStr">
+      <c r="H279" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20354,7 +20372,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N279" s="69" t="inlineStr">
+      <c r="N279" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20371,7 +20389,7 @@
           <t>PS5-82-07</t>
         </is>
       </c>
-      <c r="B280" s="79" t="inlineStr">
+      <c r="B280" s="83" t="inlineStr">
         <is>
           <t>PS5-82-07 - Guard Huts</t>
         </is>
@@ -20382,7 +20400,7 @@
       <c r="D280" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E280" s="91" t="inlineStr">
+      <c r="E280" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20393,7 +20411,7 @@
       <c r="G280" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H280" s="69" t="inlineStr">
+      <c r="H280" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20423,7 +20441,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N280" s="69" t="inlineStr">
+      <c r="N280" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20440,7 +20458,7 @@
           <t>PS5-83-01</t>
         </is>
       </c>
-      <c r="B281" s="79" t="inlineStr">
+      <c r="B281" s="83" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -20451,7 +20469,7 @@
       <c r="D281" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="E281" s="68" t="inlineStr">
+      <c r="E281" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20509,7 +20527,7 @@
           <t>PS5-84-01</t>
         </is>
       </c>
-      <c r="B282" s="79" t="inlineStr">
+      <c r="B282" s="83" t="inlineStr">
         <is>
           <t>PS5-84-01 - Generator Building</t>
         </is>
@@ -20520,7 +20538,7 @@
       <c r="D282" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E282" s="91" t="inlineStr">
+      <c r="E282" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20531,7 +20549,7 @@
       <c r="G282" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H282" s="69" t="inlineStr">
+      <c r="H282" s="70" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -20561,7 +20579,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N282" s="69" t="inlineStr">
+      <c r="N282" s="70" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -20578,7 +20596,7 @@
           <t>PS5-84-02</t>
         </is>
       </c>
-      <c r="B283" s="79" t="inlineStr">
+      <c r="B283" s="83" t="inlineStr">
         <is>
           <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
@@ -20589,7 +20607,7 @@
       <c r="D283" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E283" s="91" t="inlineStr">
+      <c r="E283" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20600,7 +20618,7 @@
       <c r="G283" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H283" s="69" t="inlineStr">
+      <c r="H283" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -20630,7 +20648,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N283" s="69" t="inlineStr">
+      <c r="N283" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -20647,7 +20665,7 @@
           <t>PS5-84-03</t>
         </is>
       </c>
-      <c r="B284" s="79" t="inlineStr">
+      <c r="B284" s="83" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -20658,7 +20676,7 @@
       <c r="D284" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E284" s="91" t="inlineStr">
+      <c r="E284" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20716,7 +20734,7 @@
           <t>PS5-86-01</t>
         </is>
       </c>
-      <c r="B285" s="79" t="inlineStr">
+      <c r="B285" s="83" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -20727,7 +20745,7 @@
       <c r="D285" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E285" s="91" t="inlineStr">
+      <c r="E285" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20785,7 +20803,7 @@
           <t>PS5-91-01</t>
         </is>
       </c>
-      <c r="B286" s="79" t="inlineStr">
+      <c r="B286" s="83" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -20796,7 +20814,7 @@
       <c r="D286" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E286" s="69" t="inlineStr">
+      <c r="E286" s="70" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -20854,7 +20872,7 @@
           <t>PS5-99-01</t>
         </is>
       </c>
-      <c r="B287" s="79" t="inlineStr">
+      <c r="B287" s="83" t="inlineStr">
         <is>
           <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
@@ -20865,7 +20883,7 @@
       <c r="D287" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E287" s="91" t="inlineStr">
+      <c r="E287" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20876,7 +20894,7 @@
       <c r="G287" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H287" s="69" t="inlineStr">
+      <c r="H287" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20906,7 +20924,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N287" s="69" t="inlineStr">
+      <c r="N287" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20923,7 +20941,7 @@
           <t>PS5-99-02</t>
         </is>
       </c>
-      <c r="B288" s="79" t="inlineStr">
+      <c r="B288" s="83" t="inlineStr">
         <is>
           <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
@@ -20934,7 +20952,7 @@
       <c r="D288" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E288" s="91" t="inlineStr">
+      <c r="E288" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20945,7 +20963,7 @@
       <c r="G288" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H288" s="69" t="inlineStr">
+      <c r="H288" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20975,7 +20993,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N288" s="69" t="inlineStr">
+      <c r="N288" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20992,7 +21010,7 @@
           <t>PS5-99-03</t>
         </is>
       </c>
-      <c r="B289" s="79" t="inlineStr">
+      <c r="B289" s="83" t="inlineStr">
         <is>
           <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
@@ -21003,7 +21021,7 @@
       <c r="D289" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E289" s="91" t="inlineStr">
+      <c r="E289" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21014,7 +21032,7 @@
       <c r="G289" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H289" s="69" t="inlineStr">
+      <c r="H289" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21044,7 +21062,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N289" s="69" t="inlineStr">
+      <c r="N289" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21061,7 +21079,7 @@
           <t>PS5-99-04</t>
         </is>
       </c>
-      <c r="B290" s="79" t="inlineStr">
+      <c r="B290" s="83" t="inlineStr">
         <is>
           <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
@@ -21072,7 +21090,7 @@
       <c r="D290" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E290" s="91" t="inlineStr">
+      <c r="E290" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21083,7 +21101,7 @@
       <c r="G290" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H290" s="69" t="inlineStr">
+      <c r="H290" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21113,7 +21131,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N290" s="69" t="inlineStr">
+      <c r="N290" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21130,7 +21148,7 @@
           <t>PS5-99-05</t>
         </is>
       </c>
-      <c r="B291" s="79" t="inlineStr">
+      <c r="B291" s="83" t="inlineStr">
         <is>
           <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
@@ -21141,7 +21159,7 @@
       <c r="D291" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E291" s="91" t="inlineStr">
+      <c r="E291" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21152,7 +21170,7 @@
       <c r="G291" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H291" s="69" t="inlineStr">
+      <c r="H291" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -21182,7 +21200,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N291" s="69" t="inlineStr">
+      <c r="N291" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -21199,7 +21217,7 @@
           <t>PS5-99-06</t>
         </is>
       </c>
-      <c r="B292" s="79" t="inlineStr">
+      <c r="B292" s="83" t="inlineStr">
         <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
@@ -21210,7 +21228,7 @@
       <c r="D292" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E292" s="91" t="inlineStr">
+      <c r="E292" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21221,7 +21239,7 @@
       <c r="G292" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H292" s="68" t="inlineStr">
+      <c r="H292" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -21251,7 +21269,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N292" s="68" t="inlineStr">
+      <c r="N292" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -241,6 +241,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFe8d5c4"/>
         <bgColor rgb="FFe8d5c4"/>
       </patternFill>
@@ -309,12 +315,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
         <bgColor rgb="FFBDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -576,7 +576,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -644,13 +644,10 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -674,22 +671,25 @@
     <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,13 +698,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,10 +722,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -740,7 +740,7 @@
     <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -773,16 +773,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="N3" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O3" s="27" t="inlineStr">

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -1572,16 +1572,16 @@
         <v>28</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H7" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
@@ -2193,11 +2193,11 @@
         <v>151</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H16" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>142/143</t>
+          <t>143/143</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr">
@@ -2331,11 +2331,11 @@
         <v>34</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H18" s="54" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>30/33</t>
+          <t>31/33</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr">
@@ -2745,11 +2745,11 @@
         <v>64</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H24" s="54" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>63/64</t>
+          <t>64/64</t>
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr">
@@ -6816,11 +6816,11 @@
         <v>147</v>
       </c>
       <c r="G83" s="23" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H83" s="69" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="I83" s="23" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="J83" s="23" t="inlineStr">
         <is>
-          <t>53/84</t>
+          <t>58/84</t>
         </is>
       </c>
       <c r="K83" s="23" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="M83" s="23" t="inlineStr">
         <is>
-          <t>42/46</t>
+          <t>43/46</t>
         </is>
       </c>
       <c r="N83" s="69" t="inlineStr">
@@ -7092,11 +7092,11 @@
         <v>48</v>
       </c>
       <c r="G87" s="23" t="n">
-        <v>33</v>
-      </c>
-      <c r="H87" s="69" t="inlineStr">
-        <is>
-          <t>69%</t>
+        <v>44</v>
+      </c>
+      <c r="H87" s="54" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
       <c r="I87" s="23" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="J87" s="23" t="inlineStr">
         <is>
-          <t>19/33</t>
+          <t>30/33</t>
         </is>
       </c>
       <c r="K87" s="23" t="inlineStr">
@@ -7161,11 +7161,11 @@
         <v>56</v>
       </c>
       <c r="G88" s="23" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H88" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="I88" s="23" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="J88" s="23" t="inlineStr">
         <is>
-          <t>12/32</t>
+          <t>15/32</t>
         </is>
       </c>
       <c r="K88" s="23" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="M88" s="23" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>18/19</t>
         </is>
       </c>
       <c r="N88" s="69" t="inlineStr">
@@ -7230,11 +7230,11 @@
         <v>123</v>
       </c>
       <c r="G89" s="23" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H89" s="69" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="I89" s="23" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="J89" s="23" t="inlineStr">
         <is>
-          <t>57/73</t>
+          <t>62/73</t>
         </is>
       </c>
       <c r="K89" s="23" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="M89" s="23" t="inlineStr">
         <is>
-          <t>33/35</t>
+          <t>34/35</t>
         </is>
       </c>
       <c r="N89" s="69" t="inlineStr">
@@ -7299,11 +7299,11 @@
         <v>14</v>
       </c>
       <c r="G90" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="H90" s="69" t="inlineStr">
-        <is>
-          <t>86%</t>
+        <v>13</v>
+      </c>
+      <c r="H90" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
         </is>
       </c>
       <c r="I90" s="23" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="M90" s="23" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
       <c r="N90" s="69" t="inlineStr">
@@ -7437,11 +7437,11 @@
         <v>104</v>
       </c>
       <c r="G92" s="23" t="n">
-        <v>93</v>
-      </c>
-      <c r="H92" s="69" t="inlineStr">
-        <is>
-          <t>89%</t>
+        <v>94</v>
+      </c>
+      <c r="H92" s="54" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="I92" s="23" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="J92" s="23" t="inlineStr">
         <is>
-          <t>29/35</t>
+          <t>30/35</t>
         </is>
       </c>
       <c r="K92" s="23" t="inlineStr">
@@ -7644,21 +7644,21 @@
         <v>64</v>
       </c>
       <c r="G95" s="23" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H95" s="54" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I95" s="23" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="J95" s="23" t="inlineStr">
         <is>
-          <t>16/20</t>
+          <t>20/20</t>
         </is>
       </c>
       <c r="K95" s="23" t="inlineStr">
@@ -7782,11 +7782,11 @@
         <v>70</v>
       </c>
       <c r="G97" s="23" t="n">
-        <v>34</v>
-      </c>
-      <c r="H97" s="70" t="inlineStr">
-        <is>
-          <t>49%</t>
+        <v>37</v>
+      </c>
+      <c r="H97" s="69" t="inlineStr">
+        <is>
+          <t>53%</t>
         </is>
       </c>
       <c r="I97" s="23" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="J97" s="23" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
       <c r="K97" s="23" t="inlineStr">
@@ -8196,11 +8196,11 @@
         <v>68</v>
       </c>
       <c r="G103" s="23" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H103" s="69" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="I103" s="23" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="M103" s="23" t="inlineStr">
         <is>
-          <t>32/35</t>
+          <t>33/35</t>
         </is>
       </c>
       <c r="N103" s="69" t="inlineStr">
@@ -8265,11 +8265,11 @@
         <v>68</v>
       </c>
       <c r="G104" s="23" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H104" s="69" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="I104" s="23" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="M104" s="23" t="inlineStr">
         <is>
-          <t>32/35</t>
+          <t>33/35</t>
         </is>
       </c>
       <c r="N104" s="69" t="inlineStr">
@@ -8403,11 +8403,11 @@
         <v>83</v>
       </c>
       <c r="G106" s="23" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H106" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="I106" s="23" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="J106" s="23" t="inlineStr">
         <is>
-          <t>24/37</t>
+          <t>26/37</t>
         </is>
       </c>
       <c r="K106" s="23" t="inlineStr">
@@ -8817,11 +8817,11 @@
         <v>17</v>
       </c>
       <c r="G112" s="23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H112" s="69" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="I112" s="23" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="M112" s="23" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
       <c r="N112" s="69" t="inlineStr">
@@ -8955,11 +8955,11 @@
         <v>58</v>
       </c>
       <c r="G114" s="23" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H114" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I114" s="23" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="M114" s="23" t="inlineStr">
         <is>
-          <t>56/58</t>
+          <t>58/58</t>
         </is>
       </c>
       <c r="N114" s="54" t="inlineStr">
@@ -9231,11 +9231,11 @@
         <v>24</v>
       </c>
       <c r="G118" s="23" t="n">
-        <v>21</v>
-      </c>
-      <c r="H118" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
+        <v>23</v>
+      </c>
+      <c r="H118" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="I118" s="23" t="inlineStr">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="J118" s="23" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K118" s="23" t="inlineStr">
@@ -9438,11 +9438,11 @@
         <v>22</v>
       </c>
       <c r="G121" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="H121" s="69" t="inlineStr">
-        <is>
-          <t>86%</t>
+        <v>21</v>
+      </c>
+      <c r="H121" s="54" t="inlineStr">
+        <is>
+          <t>95%</t>
         </is>
       </c>
       <c r="I121" s="23" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="J121" s="23" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K121" s="23" t="inlineStr">
@@ -9576,16 +9576,16 @@
         <v>52</v>
       </c>
       <c r="G123" s="23" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H123" s="54" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I123" s="23" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="J123" s="23" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="K123" s="23" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="L123" s="23" t="inlineStr">
@@ -9645,11 +9645,11 @@
         <v>24</v>
       </c>
       <c r="G124" s="23" t="n">
-        <v>21</v>
-      </c>
-      <c r="H124" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
+        <v>23</v>
+      </c>
+      <c r="H124" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="I124" s="23" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="J124" s="23" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K124" s="23" t="inlineStr">
@@ -9783,11 +9783,11 @@
         <v>52</v>
       </c>
       <c r="G126" s="23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H126" s="54" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I126" s="23" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="K126" s="23" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="L126" s="23" t="inlineStr">
@@ -9852,11 +9852,11 @@
         <v>22</v>
       </c>
       <c r="G127" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="H127" s="69" t="inlineStr">
-        <is>
-          <t>86%</t>
+        <v>21</v>
+      </c>
+      <c r="H127" s="54" t="inlineStr">
+        <is>
+          <t>95%</t>
         </is>
       </c>
       <c r="I127" s="23" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="J127" s="23" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K127" s="23" t="inlineStr">
@@ -9921,16 +9921,16 @@
         <v>169</v>
       </c>
       <c r="G128" s="23" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H128" s="54" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="I128" s="23" t="inlineStr">
         <is>
-          <t>88/89</t>
+          <t>89/89</t>
         </is>
       </c>
       <c r="J128" s="23" t="inlineStr">
@@ -9990,16 +9990,16 @@
         <v>52</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H129" s="54" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="I129" s="23" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="J129" s="23" t="inlineStr">
@@ -10059,11 +10059,11 @@
         <v>24</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>21</v>
-      </c>
-      <c r="H130" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
+        <v>23</v>
+      </c>
+      <c r="H130" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="I130" s="23" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="J130" s="23" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K130" s="23" t="inlineStr">
@@ -10128,26 +10128,26 @@
         <v>199</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H131" s="54" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="I131" s="23" t="inlineStr">
         <is>
-          <t>92/93</t>
+          <t>93/93</t>
         </is>
       </c>
       <c r="J131" s="23" t="inlineStr">
         <is>
-          <t>62/63</t>
+          <t>63/63</t>
         </is>
       </c>
       <c r="K131" s="23" t="inlineStr">
         <is>
-          <t>10/12</t>
+          <t>11/12</t>
         </is>
       </c>
       <c r="L131" s="23" t="inlineStr">
@@ -10197,16 +10197,16 @@
         <v>52</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H132" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="I132" s="23" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="J132" s="23" t="inlineStr">
@@ -10266,11 +10266,11 @@
         <v>22</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="H133" s="69" t="inlineStr">
-        <is>
-          <t>86%</t>
+        <v>21</v>
+      </c>
+      <c r="H133" s="54" t="inlineStr">
+        <is>
+          <t>95%</t>
         </is>
       </c>
       <c r="I133" s="23" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="J133" s="23" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K133" s="23" t="inlineStr">
@@ -10542,11 +10542,11 @@
         <v>117</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H137" s="69" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="I137" s="23" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="J137" s="23" t="inlineStr">
         <is>
-          <t>35/48</t>
+          <t>37/48</t>
         </is>
       </c>
       <c r="K137" s="23" t="inlineStr">
@@ -11853,11 +11853,11 @@
         <v>34</v>
       </c>
       <c r="G156" s="23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H156" s="69" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="I156" s="23" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="M156" s="23" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
       <c r="N156" s="69" t="inlineStr">
@@ -12405,11 +12405,11 @@
         <v>35</v>
       </c>
       <c r="G164" s="23" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H164" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I164" s="23" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="K164" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L164" s="23" t="inlineStr">
@@ -12474,11 +12474,11 @@
         <v>35</v>
       </c>
       <c r="G165" s="23" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H165" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I165" s="23" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="K165" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L165" s="23" t="inlineStr">
@@ -12543,11 +12543,11 @@
         <v>35</v>
       </c>
       <c r="G166" s="23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H166" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I166" s="23" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="K166" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L166" s="23" t="inlineStr">
@@ -12612,11 +12612,11 @@
         <v>35</v>
       </c>
       <c r="G167" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="H167" s="69" t="inlineStr">
-        <is>
-          <t>89%</t>
+        <v>34</v>
+      </c>
+      <c r="H167" s="54" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="I167" s="23" t="inlineStr">
@@ -12626,12 +12626,12 @@
       </c>
       <c r="J167" s="23" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
       <c r="K167" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L167" s="23" t="inlineStr">
@@ -12681,11 +12681,11 @@
         <v>35</v>
       </c>
       <c r="G168" s="23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H168" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I168" s="23" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="K168" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L168" s="23" t="inlineStr">
@@ -12750,11 +12750,11 @@
         <v>35</v>
       </c>
       <c r="G169" s="23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H169" s="54" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="I169" s="23" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="K169" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L169" s="23" t="inlineStr">
@@ -12819,11 +12819,11 @@
         <v>35</v>
       </c>
       <c r="G170" s="23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H170" s="69" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="I170" s="23" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="M170" s="23" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
       <c r="N170" s="69" t="inlineStr">
@@ -12957,11 +12957,11 @@
         <v>34</v>
       </c>
       <c r="G172" s="23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H172" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I172" s="23" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="K172" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L172" s="23" t="inlineStr">
@@ -13095,11 +13095,11 @@
         <v>34</v>
       </c>
       <c r="G174" s="23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H174" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I174" s="23" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="K174" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L174" s="23" t="inlineStr">
@@ -13233,11 +13233,11 @@
         <v>34</v>
       </c>
       <c r="G176" s="23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H176" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I176" s="23" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="K176" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L176" s="23" t="inlineStr">
@@ -13371,11 +13371,11 @@
         <v>34</v>
       </c>
       <c r="G178" s="23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H178" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I178" s="23" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="K178" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L178" s="23" t="inlineStr">
@@ -13509,11 +13509,11 @@
         <v>34</v>
       </c>
       <c r="G180" s="23" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H180" s="54" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="I180" s="23" t="inlineStr">
@@ -13528,7 +13528,7 @@
       </c>
       <c r="K180" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L180" s="23" t="inlineStr">
@@ -13647,11 +13647,11 @@
         <v>34</v>
       </c>
       <c r="G182" s="23" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H182" s="54" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="I182" s="23" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="K182" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L182" s="23" t="inlineStr">
@@ -15303,16 +15303,16 @@
         <v>64</v>
       </c>
       <c r="G206" s="23" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H206" s="70" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="I206" s="23" t="inlineStr">
         <is>
-          <t>4/64</t>
+          <t>16/64</t>
         </is>
       </c>
       <c r="J206" s="23" t="inlineStr">
@@ -15372,16 +15372,16 @@
         <v>67</v>
       </c>
       <c r="G207" s="23" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H207" s="70" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="I207" s="23" t="inlineStr">
         <is>
-          <t>3/67</t>
+          <t>18/67</t>
         </is>
       </c>
       <c r="J207" s="23" t="inlineStr">
@@ -17166,11 +17166,11 @@
         <v>94</v>
       </c>
       <c r="G233" s="23" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H233" s="70" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="I233" s="23" t="inlineStr">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="M233" s="23" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/30</t>
         </is>
       </c>
       <c r="N233" s="70" t="inlineStr">
@@ -17373,11 +17373,11 @@
         <v>129</v>
       </c>
       <c r="G236" s="23" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H236" s="69" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="I236" s="23" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="J236" s="23" t="inlineStr">
         <is>
-          <t>11/58</t>
+          <t>14/58</t>
         </is>
       </c>
       <c r="K236" s="23" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="M236" s="23" t="inlineStr">
         <is>
-          <t>42/47</t>
+          <t>43/47</t>
         </is>
       </c>
       <c r="N236" s="69" t="inlineStr">
@@ -17442,11 +17442,11 @@
         <v>64</v>
       </c>
       <c r="G237" s="23" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H237" s="69" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="I237" s="23" t="inlineStr">
@@ -17456,7 +17456,7 @@
       </c>
       <c r="J237" s="23" t="inlineStr">
         <is>
-          <t>22/35</t>
+          <t>24/35</t>
         </is>
       </c>
       <c r="K237" s="23" t="inlineStr">
@@ -17511,11 +17511,11 @@
         <v>62</v>
       </c>
       <c r="G238" s="23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H238" s="69" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="I238" s="23" t="inlineStr">
@@ -17525,7 +17525,7 @@
       </c>
       <c r="J238" s="23" t="inlineStr">
         <is>
-          <t>9/34</t>
+          <t>11/34</t>
         </is>
       </c>
       <c r="K238" s="23" t="inlineStr">
@@ -17580,11 +17580,11 @@
         <v>112</v>
       </c>
       <c r="G239" s="23" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H239" s="69" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="I239" s="23" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="K239" s="23" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="L239" s="23" t="inlineStr">
@@ -17787,11 +17787,11 @@
         <v>125</v>
       </c>
       <c r="G242" s="23" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H242" s="69" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="I242" s="23" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="M242" s="23" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
       <c r="N242" s="69" t="inlineStr">
@@ -17856,11 +17856,11 @@
         <v>56</v>
       </c>
       <c r="G243" s="23" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H243" s="69" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="I243" s="23" t="inlineStr">
@@ -17870,7 +17870,7 @@
       </c>
       <c r="J243" s="23" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>21/27</t>
         </is>
       </c>
       <c r="K243" s="23" t="inlineStr">
@@ -17885,7 +17885,7 @@
       </c>
       <c r="M243" s="23" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
       <c r="N243" s="69" t="inlineStr">
@@ -17994,11 +17994,11 @@
         <v>56</v>
       </c>
       <c r="G245" s="23" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H245" s="69" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="I245" s="23" t="inlineStr">
@@ -18008,7 +18008,7 @@
       </c>
       <c r="J245" s="23" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>21/27</t>
         </is>
       </c>
       <c r="K245" s="23" t="inlineStr">
@@ -18023,7 +18023,7 @@
       </c>
       <c r="M245" s="23" t="inlineStr">
         <is>
-          <t>17/20</t>
+          <t>18/20</t>
         </is>
       </c>
       <c r="N245" s="69" t="inlineStr">
@@ -18201,11 +18201,11 @@
         <v>53</v>
       </c>
       <c r="G248" s="23" t="n">
-        <v>47</v>
-      </c>
-      <c r="H248" s="69" t="inlineStr">
-        <is>
-          <t>89%</t>
+        <v>49</v>
+      </c>
+      <c r="H248" s="54" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
       <c r="I248" s="23" t="inlineStr">
@@ -18215,7 +18215,7 @@
       </c>
       <c r="J248" s="23" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
       <c r="K248" s="23" t="inlineStr">
@@ -18270,11 +18270,11 @@
         <v>37</v>
       </c>
       <c r="G249" s="23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H249" s="69" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="I249" s="23" t="inlineStr">
@@ -18289,7 +18289,7 @@
       </c>
       <c r="K249" s="23" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="L249" s="23" t="inlineStr">
@@ -18546,11 +18546,11 @@
         <v>25</v>
       </c>
       <c r="G253" s="23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H253" s="69" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="I253" s="23" t="inlineStr">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="K253" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="L253" s="23" t="inlineStr">
@@ -18822,11 +18822,11 @@
         <v>16</v>
       </c>
       <c r="G257" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="H257" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
+        <v>15</v>
+      </c>
+      <c r="H257" s="54" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="I257" s="23" t="inlineStr">
@@ -18851,7 +18851,7 @@
       </c>
       <c r="M257" s="23" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="N257" s="69" t="inlineStr">
@@ -19029,11 +19029,11 @@
         <v>25</v>
       </c>
       <c r="G260" s="23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H260" s="69" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="I260" s="23" t="inlineStr">
@@ -19058,7 +19058,7 @@
       </c>
       <c r="M260" s="23" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
       <c r="N260" s="69" t="inlineStr">
@@ -20202,11 +20202,11 @@
         <v>8</v>
       </c>
       <c r="G277" s="23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H277" s="69" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="I277" s="23" t="inlineStr">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="M277" s="23" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="N277" s="69" t="inlineStr">

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -1572,16 +1572,16 @@
         <v>28</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H7" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="J7" s="23" t="inlineStr">
@@ -2193,11 +2193,11 @@
         <v>151</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H16" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>143/143</t>
+          <t>142/143</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr">
@@ -2331,11 +2331,11 @@
         <v>34</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H18" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>31/33</t>
+          <t>30/33</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr">
@@ -2745,11 +2745,11 @@
         <v>64</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H24" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>64/64</t>
+          <t>63/64</t>
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr">
@@ -6816,11 +6816,11 @@
         <v>147</v>
       </c>
       <c r="G83" s="23" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H83" s="69" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="I83" s="23" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="J83" s="23" t="inlineStr">
         <is>
-          <t>58/84</t>
+          <t>53/84</t>
         </is>
       </c>
       <c r="K83" s="23" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="M83" s="23" t="inlineStr">
         <is>
-          <t>43/46</t>
+          <t>42/46</t>
         </is>
       </c>
       <c r="N83" s="69" t="inlineStr">
@@ -7092,11 +7092,11 @@
         <v>48</v>
       </c>
       <c r="G87" s="23" t="n">
-        <v>44</v>
-      </c>
-      <c r="H87" s="54" t="inlineStr">
-        <is>
-          <t>92%</t>
+        <v>33</v>
+      </c>
+      <c r="H87" s="69" t="inlineStr">
+        <is>
+          <t>69%</t>
         </is>
       </c>
       <c r="I87" s="23" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="J87" s="23" t="inlineStr">
         <is>
-          <t>30/33</t>
+          <t>19/33</t>
         </is>
       </c>
       <c r="K87" s="23" t="inlineStr">
@@ -7161,11 +7161,11 @@
         <v>56</v>
       </c>
       <c r="G88" s="23" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H88" s="69" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="I88" s="23" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="J88" s="23" t="inlineStr">
         <is>
-          <t>15/32</t>
+          <t>12/32</t>
         </is>
       </c>
       <c r="K88" s="23" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="M88" s="23" t="inlineStr">
         <is>
-          <t>18/19</t>
+          <t>17/19</t>
         </is>
       </c>
       <c r="N88" s="69" t="inlineStr">
@@ -7230,11 +7230,11 @@
         <v>123</v>
       </c>
       <c r="G89" s="23" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H89" s="69" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="I89" s="23" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="J89" s="23" t="inlineStr">
         <is>
-          <t>62/73</t>
+          <t>57/73</t>
         </is>
       </c>
       <c r="K89" s="23" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="M89" s="23" t="inlineStr">
         <is>
-          <t>34/35</t>
+          <t>33/35</t>
         </is>
       </c>
       <c r="N89" s="69" t="inlineStr">
@@ -7299,11 +7299,11 @@
         <v>14</v>
       </c>
       <c r="G90" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="H90" s="54" t="inlineStr">
-        <is>
-          <t>93%</t>
+        <v>12</v>
+      </c>
+      <c r="H90" s="69" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
       <c r="I90" s="23" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="M90" s="23" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
       <c r="N90" s="69" t="inlineStr">
@@ -7437,11 +7437,11 @@
         <v>104</v>
       </c>
       <c r="G92" s="23" t="n">
-        <v>94</v>
-      </c>
-      <c r="H92" s="54" t="inlineStr">
-        <is>
-          <t>90%</t>
+        <v>93</v>
+      </c>
+      <c r="H92" s="69" t="inlineStr">
+        <is>
+          <t>89%</t>
         </is>
       </c>
       <c r="I92" s="23" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="J92" s="23" t="inlineStr">
         <is>
-          <t>30/35</t>
+          <t>29/35</t>
         </is>
       </c>
       <c r="K92" s="23" t="inlineStr">
@@ -7644,21 +7644,21 @@
         <v>64</v>
       </c>
       <c r="G95" s="23" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H95" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="I95" s="23" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="J95" s="23" t="inlineStr">
         <is>
-          <t>20/20</t>
+          <t>16/20</t>
         </is>
       </c>
       <c r="K95" s="23" t="inlineStr">
@@ -7782,11 +7782,11 @@
         <v>70</v>
       </c>
       <c r="G97" s="23" t="n">
-        <v>37</v>
-      </c>
-      <c r="H97" s="69" t="inlineStr">
-        <is>
-          <t>53%</t>
+        <v>34</v>
+      </c>
+      <c r="H97" s="70" t="inlineStr">
+        <is>
+          <t>49%</t>
         </is>
       </c>
       <c r="I97" s="23" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="J97" s="23" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
       <c r="K97" s="23" t="inlineStr">
@@ -8196,11 +8196,11 @@
         <v>68</v>
       </c>
       <c r="G103" s="23" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H103" s="69" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="I103" s="23" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="M103" s="23" t="inlineStr">
         <is>
-          <t>33/35</t>
+          <t>32/35</t>
         </is>
       </c>
       <c r="N103" s="69" t="inlineStr">
@@ -8265,11 +8265,11 @@
         <v>68</v>
       </c>
       <c r="G104" s="23" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H104" s="69" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="I104" s="23" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="M104" s="23" t="inlineStr">
         <is>
-          <t>33/35</t>
+          <t>32/35</t>
         </is>
       </c>
       <c r="N104" s="69" t="inlineStr">
@@ -8403,11 +8403,11 @@
         <v>83</v>
       </c>
       <c r="G106" s="23" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H106" s="69" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="I106" s="23" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="J106" s="23" t="inlineStr">
         <is>
-          <t>26/37</t>
+          <t>24/37</t>
         </is>
       </c>
       <c r="K106" s="23" t="inlineStr">
@@ -8817,11 +8817,11 @@
         <v>17</v>
       </c>
       <c r="G112" s="23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H112" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="I112" s="23" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="M112" s="23" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
       <c r="N112" s="69" t="inlineStr">
@@ -8955,11 +8955,11 @@
         <v>58</v>
       </c>
       <c r="G114" s="23" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H114" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I114" s="23" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="M114" s="23" t="inlineStr">
         <is>
-          <t>58/58</t>
+          <t>56/58</t>
         </is>
       </c>
       <c r="N114" s="54" t="inlineStr">
@@ -9231,11 +9231,11 @@
         <v>24</v>
       </c>
       <c r="G118" s="23" t="n">
-        <v>23</v>
-      </c>
-      <c r="H118" s="54" t="inlineStr">
-        <is>
-          <t>96%</t>
+        <v>21</v>
+      </c>
+      <c r="H118" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="I118" s="23" t="inlineStr">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="J118" s="23" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K118" s="23" t="inlineStr">
@@ -9438,11 +9438,11 @@
         <v>22</v>
       </c>
       <c r="G121" s="23" t="n">
-        <v>21</v>
-      </c>
-      <c r="H121" s="54" t="inlineStr">
-        <is>
-          <t>95%</t>
+        <v>19</v>
+      </c>
+      <c r="H121" s="69" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
       <c r="I121" s="23" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="J121" s="23" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K121" s="23" t="inlineStr">
@@ -9576,16 +9576,16 @@
         <v>52</v>
       </c>
       <c r="G123" s="23" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H123" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="I123" s="23" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="J123" s="23" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="K123" s="23" t="inlineStr">
         <is>
-          <t>8/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="L123" s="23" t="inlineStr">
@@ -9645,11 +9645,11 @@
         <v>24</v>
       </c>
       <c r="G124" s="23" t="n">
-        <v>23</v>
-      </c>
-      <c r="H124" s="54" t="inlineStr">
-        <is>
-          <t>96%</t>
+        <v>21</v>
+      </c>
+      <c r="H124" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="I124" s="23" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="J124" s="23" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K124" s="23" t="inlineStr">
@@ -9783,11 +9783,11 @@
         <v>52</v>
       </c>
       <c r="G126" s="23" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H126" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="I126" s="23" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="K126" s="23" t="inlineStr">
         <is>
-          <t>8/8</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="L126" s="23" t="inlineStr">
@@ -9852,11 +9852,11 @@
         <v>22</v>
       </c>
       <c r="G127" s="23" t="n">
-        <v>21</v>
-      </c>
-      <c r="H127" s="54" t="inlineStr">
-        <is>
-          <t>95%</t>
+        <v>19</v>
+      </c>
+      <c r="H127" s="69" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
       <c r="I127" s="23" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="J127" s="23" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K127" s="23" t="inlineStr">
@@ -9921,16 +9921,16 @@
         <v>169</v>
       </c>
       <c r="G128" s="23" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H128" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="I128" s="23" t="inlineStr">
         <is>
-          <t>89/89</t>
+          <t>88/89</t>
         </is>
       </c>
       <c r="J128" s="23" t="inlineStr">
@@ -9990,16 +9990,16 @@
         <v>52</v>
       </c>
       <c r="G129" s="23" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H129" s="54" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="I129" s="23" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="J129" s="23" t="inlineStr">
@@ -10059,11 +10059,11 @@
         <v>24</v>
       </c>
       <c r="G130" s="23" t="n">
-        <v>23</v>
-      </c>
-      <c r="H130" s="54" t="inlineStr">
-        <is>
-          <t>96%</t>
+        <v>21</v>
+      </c>
+      <c r="H130" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="I130" s="23" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="J130" s="23" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K130" s="23" t="inlineStr">
@@ -10128,26 +10128,26 @@
         <v>199</v>
       </c>
       <c r="G131" s="23" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H131" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="I131" s="23" t="inlineStr">
         <is>
-          <t>93/93</t>
+          <t>92/93</t>
         </is>
       </c>
       <c r="J131" s="23" t="inlineStr">
         <is>
-          <t>63/63</t>
+          <t>62/63</t>
         </is>
       </c>
       <c r="K131" s="23" t="inlineStr">
         <is>
-          <t>11/12</t>
+          <t>10/12</t>
         </is>
       </c>
       <c r="L131" s="23" t="inlineStr">
@@ -10197,16 +10197,16 @@
         <v>52</v>
       </c>
       <c r="G132" s="23" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H132" s="54" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="I132" s="23" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="J132" s="23" t="inlineStr">
@@ -10266,11 +10266,11 @@
         <v>22</v>
       </c>
       <c r="G133" s="23" t="n">
-        <v>21</v>
-      </c>
-      <c r="H133" s="54" t="inlineStr">
-        <is>
-          <t>95%</t>
+        <v>19</v>
+      </c>
+      <c r="H133" s="69" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
       <c r="I133" s="23" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="J133" s="23" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K133" s="23" t="inlineStr">
@@ -10542,11 +10542,11 @@
         <v>117</v>
       </c>
       <c r="G137" s="23" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H137" s="69" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="I137" s="23" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="J137" s="23" t="inlineStr">
         <is>
-          <t>37/48</t>
+          <t>35/48</t>
         </is>
       </c>
       <c r="K137" s="23" t="inlineStr">
@@ -11853,11 +11853,11 @@
         <v>34</v>
       </c>
       <c r="G156" s="23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H156" s="69" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="I156" s="23" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="M156" s="23" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>16/17</t>
         </is>
       </c>
       <c r="N156" s="69" t="inlineStr">
@@ -12405,11 +12405,11 @@
         <v>35</v>
       </c>
       <c r="G164" s="23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H164" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I164" s="23" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="K164" s="23" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L164" s="23" t="inlineStr">
@@ -12474,11 +12474,11 @@
         <v>35</v>
       </c>
       <c r="G165" s="23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H165" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I165" s="23" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="K165" s="23" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L165" s="23" t="inlineStr">
@@ -12543,11 +12543,11 @@
         <v>35</v>
       </c>
       <c r="G166" s="23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H166" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="I166" s="23" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="K166" s="23" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L166" s="23" t="inlineStr">
@@ -12612,11 +12612,11 @@
         <v>35</v>
       </c>
       <c r="G167" s="23" t="n">
-        <v>34</v>
-      </c>
-      <c r="H167" s="54" t="inlineStr">
-        <is>
-          <t>97%</t>
+        <v>31</v>
+      </c>
+      <c r="H167" s="69" t="inlineStr">
+        <is>
+          <t>89%</t>
         </is>
       </c>
       <c r="I167" s="23" t="inlineStr">
@@ -12626,12 +12626,12 @@
       </c>
       <c r="J167" s="23" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
       <c r="K167" s="23" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L167" s="23" t="inlineStr">
@@ -12681,11 +12681,11 @@
         <v>35</v>
       </c>
       <c r="G168" s="23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H168" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="I168" s="23" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="K168" s="23" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L168" s="23" t="inlineStr">
@@ -12750,11 +12750,11 @@
         <v>35</v>
       </c>
       <c r="G169" s="23" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H169" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="I169" s="23" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="K169" s="23" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L169" s="23" t="inlineStr">
@@ -12819,11 +12819,11 @@
         <v>35</v>
       </c>
       <c r="G170" s="23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H170" s="69" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="I170" s="23" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="M170" s="23" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
       <c r="N170" s="69" t="inlineStr">
@@ -12957,11 +12957,11 @@
         <v>34</v>
       </c>
       <c r="G172" s="23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H172" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I172" s="23" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="K172" s="23" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L172" s="23" t="inlineStr">
@@ -13095,11 +13095,11 @@
         <v>34</v>
       </c>
       <c r="G174" s="23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H174" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I174" s="23" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="K174" s="23" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L174" s="23" t="inlineStr">
@@ -13233,11 +13233,11 @@
         <v>34</v>
       </c>
       <c r="G176" s="23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H176" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I176" s="23" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="K176" s="23" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L176" s="23" t="inlineStr">
@@ -13371,11 +13371,11 @@
         <v>34</v>
       </c>
       <c r="G178" s="23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H178" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I178" s="23" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="K178" s="23" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L178" s="23" t="inlineStr">
@@ -13509,11 +13509,11 @@
         <v>34</v>
       </c>
       <c r="G180" s="23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H180" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="I180" s="23" t="inlineStr">
@@ -13528,7 +13528,7 @@
       </c>
       <c r="K180" s="23" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L180" s="23" t="inlineStr">
@@ -13647,11 +13647,11 @@
         <v>34</v>
       </c>
       <c r="G182" s="23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H182" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="I182" s="23" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="K182" s="23" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L182" s="23" t="inlineStr">
@@ -15303,16 +15303,16 @@
         <v>64</v>
       </c>
       <c r="G206" s="23" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H206" s="70" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="I206" s="23" t="inlineStr">
         <is>
-          <t>16/64</t>
+          <t>4/64</t>
         </is>
       </c>
       <c r="J206" s="23" t="inlineStr">
@@ -15372,16 +15372,16 @@
         <v>67</v>
       </c>
       <c r="G207" s="23" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H207" s="70" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="I207" s="23" t="inlineStr">
         <is>
-          <t>18/67</t>
+          <t>3/67</t>
         </is>
       </c>
       <c r="J207" s="23" t="inlineStr">
@@ -17166,11 +17166,11 @@
         <v>94</v>
       </c>
       <c r="G233" s="23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H233" s="70" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="I233" s="23" t="inlineStr">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="M233" s="23" t="inlineStr">
         <is>
-          <t>28/30</t>
+          <t>27/30</t>
         </is>
       </c>
       <c r="N233" s="70" t="inlineStr">
@@ -17373,11 +17373,11 @@
         <v>129</v>
       </c>
       <c r="G236" s="23" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H236" s="69" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="I236" s="23" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="J236" s="23" t="inlineStr">
         <is>
-          <t>14/58</t>
+          <t>11/58</t>
         </is>
       </c>
       <c r="K236" s="23" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="M236" s="23" t="inlineStr">
         <is>
-          <t>43/47</t>
+          <t>42/47</t>
         </is>
       </c>
       <c r="N236" s="69" t="inlineStr">
@@ -17442,11 +17442,11 @@
         <v>64</v>
       </c>
       <c r="G237" s="23" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H237" s="69" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="I237" s="23" t="inlineStr">
@@ -17456,7 +17456,7 @@
       </c>
       <c r="J237" s="23" t="inlineStr">
         <is>
-          <t>24/35</t>
+          <t>22/35</t>
         </is>
       </c>
       <c r="K237" s="23" t="inlineStr">
@@ -17511,11 +17511,11 @@
         <v>62</v>
       </c>
       <c r="G238" s="23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H238" s="69" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="I238" s="23" t="inlineStr">
@@ -17525,7 +17525,7 @@
       </c>
       <c r="J238" s="23" t="inlineStr">
         <is>
-          <t>11/34</t>
+          <t>9/34</t>
         </is>
       </c>
       <c r="K238" s="23" t="inlineStr">
@@ -17580,11 +17580,11 @@
         <v>112</v>
       </c>
       <c r="G239" s="23" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H239" s="69" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="I239" s="23" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="K239" s="23" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="L239" s="23" t="inlineStr">
@@ -17787,11 +17787,11 @@
         <v>125</v>
       </c>
       <c r="G242" s="23" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H242" s="69" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="I242" s="23" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="M242" s="23" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>26/31</t>
         </is>
       </c>
       <c r="N242" s="69" t="inlineStr">
@@ -17856,11 +17856,11 @@
         <v>56</v>
       </c>
       <c r="G243" s="23" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H243" s="69" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="I243" s="23" t="inlineStr">
@@ -17870,7 +17870,7 @@
       </c>
       <c r="J243" s="23" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>19/27</t>
         </is>
       </c>
       <c r="K243" s="23" t="inlineStr">
@@ -17885,7 +17885,7 @@
       </c>
       <c r="M243" s="23" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
       <c r="N243" s="69" t="inlineStr">
@@ -17994,11 +17994,11 @@
         <v>56</v>
       </c>
       <c r="G245" s="23" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H245" s="69" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="I245" s="23" t="inlineStr">
@@ -18008,7 +18008,7 @@
       </c>
       <c r="J245" s="23" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>20/27</t>
         </is>
       </c>
       <c r="K245" s="23" t="inlineStr">
@@ -18023,7 +18023,7 @@
       </c>
       <c r="M245" s="23" t="inlineStr">
         <is>
-          <t>18/20</t>
+          <t>17/20</t>
         </is>
       </c>
       <c r="N245" s="69" t="inlineStr">
@@ -18201,11 +18201,11 @@
         <v>53</v>
       </c>
       <c r="G248" s="23" t="n">
-        <v>49</v>
-      </c>
-      <c r="H248" s="54" t="inlineStr">
-        <is>
-          <t>92%</t>
+        <v>47</v>
+      </c>
+      <c r="H248" s="69" t="inlineStr">
+        <is>
+          <t>89%</t>
         </is>
       </c>
       <c r="I248" s="23" t="inlineStr">
@@ -18215,7 +18215,7 @@
       </c>
       <c r="J248" s="23" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>22/28</t>
         </is>
       </c>
       <c r="K248" s="23" t="inlineStr">
@@ -18270,11 +18270,11 @@
         <v>37</v>
       </c>
       <c r="G249" s="23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H249" s="69" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="I249" s="23" t="inlineStr">
@@ -18289,7 +18289,7 @@
       </c>
       <c r="K249" s="23" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="L249" s="23" t="inlineStr">
@@ -18546,11 +18546,11 @@
         <v>25</v>
       </c>
       <c r="G253" s="23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H253" s="69" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="I253" s="23" t="inlineStr">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="K253" s="23" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="L253" s="23" t="inlineStr">
@@ -18822,11 +18822,11 @@
         <v>16</v>
       </c>
       <c r="G257" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="H257" s="54" t="inlineStr">
-        <is>
-          <t>94%</t>
+        <v>14</v>
+      </c>
+      <c r="H257" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="I257" s="23" t="inlineStr">
@@ -18851,7 +18851,7 @@
       </c>
       <c r="M257" s="23" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="N257" s="69" t="inlineStr">
@@ -19029,11 +19029,11 @@
         <v>25</v>
       </c>
       <c r="G260" s="23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H260" s="69" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="I260" s="23" t="inlineStr">
@@ -19058,7 +19058,7 @@
       </c>
       <c r="M260" s="23" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
       <c r="N260" s="69" t="inlineStr">
@@ -20202,11 +20202,11 @@
         <v>8</v>
       </c>
       <c r="G277" s="23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H277" s="69" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="I277" s="23" t="inlineStr">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="M277" s="23" t="inlineStr">
         <is>
-          <t>7/8</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="N277" s="69" t="inlineStr">

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -309,12 +309,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -504,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -518,6 +512,9 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -527,10 +524,10 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -542,19 +539,16 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -564,10 +558,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -579,21 +573,21 @@
     <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -683,9 +677,6 @@
     <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -707,10 +698,10 @@
     <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,13 +713,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -737,7 +722,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -746,28 +731,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1178,20 +1163,20 @@
           <t>PS5 COMPLETION PLATFORM  |  SUB SYSTEM - 290 subsystem(s)</t>
         </is>
       </c>
-      <c r="B1" s="100" t="n"/>
-      <c r="C1" s="100" t="n"/>
-      <c r="D1" s="100" t="n"/>
-      <c r="E1" s="100" t="n"/>
-      <c r="F1" s="100" t="n"/>
-      <c r="G1" s="100" t="n"/>
-      <c r="H1" s="100" t="n"/>
-      <c r="I1" s="100" t="n"/>
-      <c r="J1" s="100" t="n"/>
-      <c r="K1" s="100" t="n"/>
-      <c r="L1" s="100" t="n"/>
-      <c r="M1" s="100" t="n"/>
-      <c r="N1" s="100" t="n"/>
-      <c r="O1" s="101" t="n"/>
+      <c r="B1" s="97" t="n"/>
+      <c r="C1" s="97" t="n"/>
+      <c r="D1" s="97" t="n"/>
+      <c r="E1" s="97" t="n"/>
+      <c r="F1" s="97" t="n"/>
+      <c r="G1" s="97" t="n"/>
+      <c r="H1" s="97" t="n"/>
+      <c r="I1" s="97" t="n"/>
+      <c r="J1" s="97" t="n"/>
+      <c r="K1" s="97" t="n"/>
+      <c r="L1" s="97" t="n"/>
+      <c r="M1" s="97" t="n"/>
+      <c r="N1" s="97" t="n"/>
+      <c r="O1" s="98" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1276,7 +1261,7 @@
           <t>PS5-01-01</t>
         </is>
       </c>
-      <c r="B3" s="83" t="inlineStr">
+      <c r="B3" s="80" t="inlineStr">
         <is>
           <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
@@ -1287,7 +1272,7 @@
       <c r="D3" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="70" t="inlineStr">
+      <c r="E3" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -1345,7 +1330,7 @@
           <t>PS5-01-02</t>
         </is>
       </c>
-      <c r="B4" s="83" t="inlineStr">
+      <c r="B4" s="80" t="inlineStr">
         <is>
           <t>PS5-01-02 - Fire Water Pump A</t>
         </is>
@@ -1356,7 +1341,7 @@
       <c r="D4" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="70" t="inlineStr">
+      <c r="E4" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -1414,7 +1399,7 @@
           <t>PS5-01-03</t>
         </is>
       </c>
-      <c r="B5" s="83" t="inlineStr">
+      <c r="B5" s="80" t="inlineStr">
         <is>
           <t>PS5-01-03 - Fire Water Pump B</t>
         </is>
@@ -1425,7 +1410,7 @@
       <c r="D5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="70" t="inlineStr">
+      <c r="E5" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1483,7 +1468,7 @@
           <t>PS5-01-04</t>
         </is>
       </c>
-      <c r="B6" s="83" t="inlineStr">
+      <c r="B6" s="80" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -1494,7 +1479,7 @@
       <c r="D6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="70" t="inlineStr">
+      <c r="E6" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1552,7 +1537,7 @@
           <t>PS5-01-05</t>
         </is>
       </c>
-      <c r="B7" s="83" t="inlineStr">
+      <c r="B7" s="80" t="inlineStr">
         <is>
           <t>PS5-01-05 - Foam Skid</t>
         </is>
@@ -1563,7 +1548,7 @@
       <c r="D7" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="70" t="inlineStr">
+      <c r="E7" s="69" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -1621,7 +1606,7 @@
           <t>PS5-01-06</t>
         </is>
       </c>
-      <c r="B8" s="83" t="inlineStr">
+      <c r="B8" s="80" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -1632,7 +1617,7 @@
       <c r="D8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="70" t="inlineStr">
+      <c r="E8" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1690,7 +1675,7 @@
           <t>PS5-01-07</t>
         </is>
       </c>
-      <c r="B9" s="83" t="inlineStr">
+      <c r="B9" s="80" t="inlineStr">
         <is>
           <t>PS5-01-07 - Fire Water Ring Main &amp; Distribution</t>
         </is>
@@ -1701,7 +1686,7 @@
       <c r="D9" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="70" t="inlineStr">
+      <c r="E9" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1712,7 +1697,7 @@
       <c r="G9" s="23" t="n">
         <v>117</v>
       </c>
-      <c r="H9" s="69" t="inlineStr">
+      <c r="H9" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -1742,7 +1727,7 @@
           <t>86/87</t>
         </is>
       </c>
-      <c r="N9" s="69" t="inlineStr">
+      <c r="N9" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -1759,7 +1744,7 @@
           <t>PS5-01-08</t>
         </is>
       </c>
-      <c r="B10" s="83" t="inlineStr">
+      <c r="B10" s="80" t="inlineStr">
         <is>
           <t>PS5-01-08 - PS5 Deluge Valve Skid (PS5-01-UK-6100)</t>
         </is>
@@ -1770,7 +1755,7 @@
       <c r="D10" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="70" t="inlineStr">
+      <c r="E10" s="69" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -1781,7 +1766,7 @@
       <c r="G10" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H10" s="69" t="inlineStr">
+      <c r="H10" s="68" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -1811,7 +1796,7 @@
           <t>26/34</t>
         </is>
       </c>
-      <c r="N10" s="69" t="inlineStr">
+      <c r="N10" s="68" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -1828,7 +1813,7 @@
           <t>PS5-01-09</t>
         </is>
       </c>
-      <c r="B11" s="83" t="inlineStr">
+      <c r="B11" s="80" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -1839,7 +1824,7 @@
       <c r="D11" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="69" t="inlineStr">
+      <c r="E11" s="68" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1897,7 +1882,7 @@
           <t>PS5-01-10</t>
         </is>
       </c>
-      <c r="B12" s="83" t="inlineStr">
+      <c r="B12" s="80" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -1908,7 +1893,7 @@
       <c r="D12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="70" t="inlineStr">
+      <c r="E12" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -1966,7 +1951,7 @@
           <t>PS5-01-11</t>
         </is>
       </c>
-      <c r="B13" s="83" t="inlineStr">
+      <c r="B13" s="80" t="inlineStr">
         <is>
           <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
@@ -1977,7 +1962,7 @@
       <c r="D13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="70" t="inlineStr">
+      <c r="E13" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1988,7 +1973,7 @@
       <c r="G13" s="23" t="n">
         <v>39</v>
       </c>
-      <c r="H13" s="70" t="inlineStr">
+      <c r="H13" s="69" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -2018,7 +2003,7 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="N13" s="70" t="inlineStr">
+      <c r="N13" s="69" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -2035,7 +2020,7 @@
           <t>PS5-02-01</t>
         </is>
       </c>
-      <c r="B14" s="83" t="inlineStr">
+      <c r="B14" s="80" t="inlineStr">
         <is>
           <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
@@ -2046,7 +2031,7 @@
       <c r="D14" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="70" t="inlineStr">
+      <c r="E14" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2057,7 +2042,7 @@
       <c r="G14" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="70" t="inlineStr">
+      <c r="H14" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -2087,7 +2072,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N14" s="70" t="inlineStr">
+      <c r="N14" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -2104,7 +2089,7 @@
           <t>PS5-02-02</t>
         </is>
       </c>
-      <c r="B15" s="83" t="inlineStr">
+      <c r="B15" s="80" t="inlineStr">
         <is>
           <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
@@ -2115,7 +2100,7 @@
       <c r="D15" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="70" t="inlineStr">
+      <c r="E15" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2126,7 +2111,7 @@
       <c r="G15" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="70" t="inlineStr">
+      <c r="H15" s="69" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -2156,7 +2141,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N15" s="70" t="inlineStr">
+      <c r="N15" s="69" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -2173,7 +2158,7 @@
           <t>PS5-03-01</t>
         </is>
       </c>
-      <c r="B16" s="83" t="inlineStr">
+      <c r="B16" s="80" t="inlineStr">
         <is>
           <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
@@ -2184,7 +2169,7 @@
       <c r="D16" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="95" t="inlineStr">
+      <c r="E16" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2242,7 +2227,7 @@
           <t>PS5-03-03</t>
         </is>
       </c>
-      <c r="B17" s="83" t="inlineStr">
+      <c r="B17" s="80" t="inlineStr">
         <is>
           <t>PS5-03-03 - FZ-03 - Buildings Area</t>
         </is>
@@ -2253,7 +2238,7 @@
       <c r="D17" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="95" t="inlineStr">
+      <c r="E17" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2264,7 +2249,7 @@
       <c r="G17" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="70" t="inlineStr">
+      <c r="H17" s="69" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -2294,7 +2279,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N17" s="70" t="inlineStr">
+      <c r="N17" s="69" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -2311,7 +2296,7 @@
           <t>PS5-03-04</t>
         </is>
       </c>
-      <c r="B18" s="83" t="inlineStr">
+      <c r="B18" s="80" t="inlineStr">
         <is>
           <t>PS5-03-04 - FZ-04 - Utilities - Diesel and Firewater Pumps Areas</t>
         </is>
@@ -2322,7 +2307,7 @@
       <c r="D18" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="95" t="inlineStr">
+      <c r="E18" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2380,7 +2365,7 @@
           <t>PS5-03-06</t>
         </is>
       </c>
-      <c r="B19" s="83" t="inlineStr">
+      <c r="B19" s="80" t="inlineStr">
         <is>
           <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
@@ -2449,7 +2434,7 @@
           <t>PS5-03-07</t>
         </is>
       </c>
-      <c r="B20" s="83" t="inlineStr">
+      <c r="B20" s="80" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -2460,7 +2445,7 @@
       <c r="D20" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="95" t="inlineStr">
+      <c r="E20" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2518,7 +2503,7 @@
           <t>PS5-03-08</t>
         </is>
       </c>
-      <c r="B21" s="83" t="inlineStr">
+      <c r="B21" s="80" t="inlineStr">
         <is>
           <t>PS5-03-08 - FZ-08 - Utilities - Power Generation Area - External</t>
         </is>
@@ -2529,7 +2514,7 @@
       <c r="D21" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="95" t="inlineStr">
+      <c r="E21" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2587,7 +2572,7 @@
           <t>PS5-03-09</t>
         </is>
       </c>
-      <c r="B22" s="83" t="inlineStr">
+      <c r="B22" s="80" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -2598,7 +2583,7 @@
       <c r="D22" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="70" t="inlineStr">
+      <c r="E22" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2656,7 +2641,7 @@
           <t>PS5-03-10</t>
         </is>
       </c>
-      <c r="B23" s="83" t="inlineStr">
+      <c r="B23" s="80" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -2667,7 +2652,7 @@
       <c r="D23" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="95" t="inlineStr">
+      <c r="E23" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2725,7 +2710,7 @@
           <t>PS5-03-11</t>
         </is>
       </c>
-      <c r="B24" s="83" t="inlineStr">
+      <c r="B24" s="80" t="inlineStr">
         <is>
           <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
@@ -2736,7 +2721,7 @@
       <c r="D24" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="95" t="inlineStr">
+      <c r="E24" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2794,7 +2779,7 @@
           <t>PS5-03-12</t>
         </is>
       </c>
-      <c r="B25" s="83" t="inlineStr">
+      <c r="B25" s="80" t="inlineStr">
         <is>
           <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
@@ -2805,7 +2790,7 @@
       <c r="D25" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="95" t="inlineStr">
+      <c r="E25" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2863,7 +2848,7 @@
           <t>PS5-03-13</t>
         </is>
       </c>
-      <c r="B26" s="83" t="inlineStr">
+      <c r="B26" s="80" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -2874,7 +2859,7 @@
       <c r="D26" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="95" t="inlineStr">
+      <c r="E26" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2932,7 +2917,7 @@
           <t>PS5-03-14</t>
         </is>
       </c>
-      <c r="B27" s="83" t="inlineStr">
+      <c r="B27" s="80" t="inlineStr">
         <is>
           <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
@@ -2943,7 +2928,7 @@
       <c r="D27" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="70" t="inlineStr">
+      <c r="E27" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2954,7 +2939,7 @@
       <c r="G27" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H27" s="70" t="inlineStr">
+      <c r="H27" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2984,7 +2969,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N27" s="70" t="inlineStr">
+      <c r="N27" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -3001,7 +2986,7 @@
           <t>PS5-03-15</t>
         </is>
       </c>
-      <c r="B28" s="83" t="inlineStr">
+      <c r="B28" s="80" t="inlineStr">
         <is>
           <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
@@ -3012,7 +2997,7 @@
       <c r="D28" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="95" t="inlineStr">
+      <c r="E28" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3023,7 +3008,7 @@
       <c r="G28" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="70" t="inlineStr">
+      <c r="H28" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3053,7 +3038,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N28" s="70" t="inlineStr">
+      <c r="N28" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3070,7 +3055,7 @@
           <t>PS5-03-16</t>
         </is>
       </c>
-      <c r="B29" s="83" t="inlineStr">
+      <c r="B29" s="80" t="inlineStr">
         <is>
           <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
@@ -3081,7 +3066,7 @@
       <c r="D29" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="95" t="inlineStr">
+      <c r="E29" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3092,7 +3077,7 @@
       <c r="G29" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="70" t="inlineStr">
+      <c r="H29" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3122,7 +3107,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N29" s="70" t="inlineStr">
+      <c r="N29" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3139,7 +3124,7 @@
           <t>PS5-03-17</t>
         </is>
       </c>
-      <c r="B30" s="83" t="inlineStr">
+      <c r="B30" s="80" t="inlineStr">
         <is>
           <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
@@ -3150,7 +3135,7 @@
       <c r="D30" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="95" t="inlineStr">
+      <c r="E30" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3161,7 +3146,7 @@
       <c r="G30" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="70" t="inlineStr">
+      <c r="H30" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3191,7 +3176,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N30" s="70" t="inlineStr">
+      <c r="N30" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3208,7 +3193,7 @@
           <t>PS5-03-18</t>
         </is>
       </c>
-      <c r="B31" s="83" t="inlineStr">
+      <c r="B31" s="80" t="inlineStr">
         <is>
           <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
@@ -3219,7 +3204,7 @@
       <c r="D31" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="95" t="inlineStr">
+      <c r="E31" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3230,7 +3215,7 @@
       <c r="G31" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="70" t="inlineStr">
+      <c r="H31" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3260,7 +3245,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N31" s="70" t="inlineStr">
+      <c r="N31" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3277,7 +3262,7 @@
           <t>PS5-03-19</t>
         </is>
       </c>
-      <c r="B32" s="83" t="inlineStr">
+      <c r="B32" s="80" t="inlineStr">
         <is>
           <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
@@ -3288,7 +3273,7 @@
       <c r="D32" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="95" t="inlineStr">
+      <c r="E32" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3299,7 +3284,7 @@
       <c r="G32" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="70" t="inlineStr">
+      <c r="H32" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3329,7 +3314,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N32" s="70" t="inlineStr">
+      <c r="N32" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3346,7 +3331,7 @@
           <t>PS5-03-20</t>
         </is>
       </c>
-      <c r="B33" s="83" t="inlineStr">
+      <c r="B33" s="80" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -3357,7 +3342,7 @@
       <c r="D33" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="70" t="inlineStr">
+      <c r="E33" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3415,7 +3400,7 @@
           <t>PS5-03-21</t>
         </is>
       </c>
-      <c r="B34" s="83" t="inlineStr">
+      <c r="B34" s="80" t="inlineStr">
         <is>
           <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
@@ -3426,7 +3411,7 @@
       <c r="D34" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="95" t="inlineStr">
+      <c r="E34" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3437,7 +3422,7 @@
       <c r="G34" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="70" t="inlineStr">
+      <c r="H34" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3467,7 +3452,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N34" s="70" t="inlineStr">
+      <c r="N34" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3484,7 +3469,7 @@
           <t>PS5-03-22</t>
         </is>
       </c>
-      <c r="B35" s="83" t="inlineStr">
+      <c r="B35" s="80" t="inlineStr">
         <is>
           <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
@@ -3495,7 +3480,7 @@
       <c r="D35" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="95" t="inlineStr">
+      <c r="E35" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3506,7 +3491,7 @@
       <c r="G35" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="70" t="inlineStr">
+      <c r="H35" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3536,7 +3521,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N35" s="70" t="inlineStr">
+      <c r="N35" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3553,7 +3538,7 @@
           <t>PS5-03-23</t>
         </is>
       </c>
-      <c r="B36" s="83" t="inlineStr">
+      <c r="B36" s="80" t="inlineStr">
         <is>
           <t>PS5-03-23 - FZ-E1 to E3 - EITS Building</t>
         </is>
@@ -3564,7 +3549,7 @@
       <c r="D36" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="70" t="inlineStr">
+      <c r="E36" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3575,7 +3560,7 @@
       <c r="G36" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="95" t="inlineStr">
+      <c r="H36" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3622,7 +3607,7 @@
           <t>PS5-03-24</t>
         </is>
       </c>
-      <c r="B37" s="83" t="inlineStr">
+      <c r="B37" s="80" t="inlineStr">
         <is>
           <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
@@ -3633,7 +3618,7 @@
       <c r="D37" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="95" t="inlineStr">
+      <c r="E37" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3644,7 +3629,7 @@
       <c r="G37" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="70" t="inlineStr">
+      <c r="H37" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3674,7 +3659,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N37" s="70" t="inlineStr">
+      <c r="N37" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3691,7 +3676,7 @@
           <t>PS5-03-25</t>
         </is>
       </c>
-      <c r="B38" s="83" t="inlineStr">
+      <c r="B38" s="80" t="inlineStr">
         <is>
           <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
@@ -3702,7 +3687,7 @@
       <c r="D38" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="95" t="inlineStr">
+      <c r="E38" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3713,7 +3698,7 @@
       <c r="G38" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="70" t="inlineStr">
+      <c r="H38" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3743,7 +3728,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N38" s="70" t="inlineStr">
+      <c r="N38" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3760,7 +3745,7 @@
           <t>PS5-04-01</t>
         </is>
       </c>
-      <c r="B39" s="83" t="inlineStr">
+      <c r="B39" s="80" t="inlineStr">
         <is>
           <t>PS5-04-01 - Office Building PCS System</t>
         </is>
@@ -3771,7 +3756,7 @@
       <c r="D39" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="95" t="inlineStr">
+      <c r="E39" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3782,7 +3767,7 @@
       <c r="G39" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="95" t="inlineStr">
+      <c r="H39" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3812,7 +3797,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N39" s="70" t="inlineStr">
+      <c r="N39" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3829,7 +3814,7 @@
           <t>PS5-04-02</t>
         </is>
       </c>
-      <c r="B40" s="83" t="inlineStr">
+      <c r="B40" s="80" t="inlineStr">
         <is>
           <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
@@ -3840,7 +3825,7 @@
       <c r="D40" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="95" t="inlineStr">
+      <c r="E40" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3851,7 +3836,7 @@
       <c r="G40" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="70" t="inlineStr">
+      <c r="H40" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3881,7 +3866,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N40" s="70" t="inlineStr">
+      <c r="N40" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3898,7 +3883,7 @@
           <t>PS5-04-03</t>
         </is>
       </c>
-      <c r="B41" s="83" t="inlineStr">
+      <c r="B41" s="80" t="inlineStr">
         <is>
           <t>PS5-04-03 - 33kV ICSS System</t>
         </is>
@@ -3909,7 +3894,7 @@
       <c r="D41" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="69" t="inlineStr">
+      <c r="E41" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -3920,7 +3905,7 @@
       <c r="G41" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="95" t="inlineStr">
+      <c r="H41" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3967,7 +3952,7 @@
           <t>PS5-04-04</t>
         </is>
       </c>
-      <c r="B42" s="83" t="inlineStr">
+      <c r="B42" s="80" t="inlineStr">
         <is>
           <t>PS5-04-04 - 33kV PCS System</t>
         </is>
@@ -3978,7 +3963,7 @@
       <c r="D42" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="E42" s="69" t="inlineStr">
+      <c r="E42" s="68" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -3989,7 +3974,7 @@
       <c r="G42" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="95" t="inlineStr">
+      <c r="H42" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4036,7 +4021,7 @@
           <t>PS5-04-05</t>
         </is>
       </c>
-      <c r="B43" s="83" t="inlineStr">
+      <c r="B43" s="80" t="inlineStr">
         <is>
           <t>PS5-04-05 - 33kV SIS/FGS System</t>
         </is>
@@ -4058,7 +4043,7 @@
       <c r="G43" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="95" t="inlineStr">
+      <c r="H43" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4088,7 +4073,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N43" s="69" t="inlineStr">
+      <c r="N43" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -4105,7 +4090,7 @@
           <t>PS5-05-01</t>
         </is>
       </c>
-      <c r="B44" s="83" t="inlineStr">
+      <c r="B44" s="80" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -4162,7 +4147,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O44" s="69" t="inlineStr">
+      <c r="O44" s="68" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4174,7 +4159,7 @@
           <t>PS5-05-02</t>
         </is>
       </c>
-      <c r="B45" s="83" t="inlineStr">
+      <c r="B45" s="80" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -4185,7 +4170,7 @@
       <c r="D45" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="70" t="inlineStr">
+      <c r="E45" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4243,7 +4228,7 @@
           <t>PS5-06-01</t>
         </is>
       </c>
-      <c r="B46" s="83" t="inlineStr">
+      <c r="B46" s="80" t="inlineStr">
         <is>
           <t>PS5-06-01 - AC UPS - EITS Building</t>
         </is>
@@ -4254,7 +4239,7 @@
       <c r="D46" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E46" s="69" t="inlineStr">
+      <c r="E46" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -4265,7 +4250,7 @@
       <c r="G46" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="95" t="inlineStr">
+      <c r="H46" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4295,7 +4280,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N46" s="69" t="inlineStr">
+      <c r="N46" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -4312,7 +4297,7 @@
           <t>PS5-06-02</t>
         </is>
       </c>
-      <c r="B47" s="83" t="inlineStr">
+      <c r="B47" s="80" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -4323,7 +4308,7 @@
       <c r="D47" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E47" s="70" t="inlineStr">
+      <c r="E47" s="69" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -4381,7 +4366,7 @@
           <t>PS5-06-03</t>
         </is>
       </c>
-      <c r="B48" s="83" t="inlineStr">
+      <c r="B48" s="80" t="inlineStr">
         <is>
           <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
@@ -4392,7 +4377,7 @@
       <c r="D48" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="95" t="inlineStr">
+      <c r="E48" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4403,7 +4388,7 @@
       <c r="G48" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="70" t="inlineStr">
+      <c r="H48" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4433,7 +4418,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N48" s="70" t="inlineStr">
+      <c r="N48" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4450,7 +4435,7 @@
           <t>PS5-06-04</t>
         </is>
       </c>
-      <c r="B49" s="83" t="inlineStr">
+      <c r="B49" s="80" t="inlineStr">
         <is>
           <t>PS5-06-04 - AC UPS - Guard House</t>
         </is>
@@ -4461,7 +4446,7 @@
       <c r="D49" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E49" s="95" t="inlineStr">
+      <c r="E49" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4472,7 +4457,7 @@
       <c r="G49" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="70" t="inlineStr">
+      <c r="H49" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4502,7 +4487,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N49" s="70" t="inlineStr">
+      <c r="N49" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4519,7 +4504,7 @@
           <t>PS5-06-05</t>
         </is>
       </c>
-      <c r="B50" s="83" t="inlineStr">
+      <c r="B50" s="80" t="inlineStr">
         <is>
           <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
@@ -4530,7 +4515,7 @@
       <c r="D50" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="95" t="inlineStr">
+      <c r="E50" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4541,7 +4526,7 @@
       <c r="G50" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="70" t="inlineStr">
+      <c r="H50" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4571,7 +4556,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N50" s="70" t="inlineStr">
+      <c r="N50" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4588,7 +4573,7 @@
           <t>PS5-08-01</t>
         </is>
       </c>
-      <c r="B51" s="83" t="inlineStr">
+      <c r="B51" s="80" t="inlineStr">
         <is>
           <t>PS5-08-01 - PAGA</t>
         </is>
@@ -4599,7 +4584,7 @@
       <c r="D51" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="70" t="inlineStr">
+      <c r="E51" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4610,7 +4595,7 @@
       <c r="G51" s="23" t="n">
         <v>82</v>
       </c>
-      <c r="H51" s="70" t="inlineStr">
+      <c r="H51" s="69" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -4640,7 +4625,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N51" s="70" t="inlineStr">
+      <c r="N51" s="69" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -4657,7 +4642,7 @@
           <t>PS5-08-03</t>
         </is>
       </c>
-      <c r="B52" s="83" t="inlineStr">
+      <c r="B52" s="80" t="inlineStr">
         <is>
           <t>PS5-08-03 - Telephone</t>
         </is>
@@ -4668,7 +4653,7 @@
       <c r="D52" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="95" t="inlineStr">
+      <c r="E52" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4679,7 +4664,7 @@
       <c r="G52" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H52" s="70" t="inlineStr">
+      <c r="H52" s="69" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -4709,7 +4694,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N52" s="70" t="inlineStr">
+      <c r="N52" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -4726,7 +4711,7 @@
           <t>PS5-08-04</t>
         </is>
       </c>
-      <c r="B53" s="83" t="inlineStr">
+      <c r="B53" s="80" t="inlineStr">
         <is>
           <t>PS5-08-04 - Hotline</t>
         </is>
@@ -4737,7 +4722,7 @@
       <c r="D53" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="95" t="inlineStr">
+      <c r="E53" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4748,7 +4733,7 @@
       <c r="G53" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="95" t="inlineStr">
+      <c r="H53" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4778,7 +4763,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N53" s="70" t="inlineStr">
+      <c r="N53" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4795,7 +4780,7 @@
           <t>PS5-08-07</t>
         </is>
       </c>
-      <c r="B54" s="83" t="inlineStr">
+      <c r="B54" s="80" t="inlineStr">
         <is>
           <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
@@ -4806,7 +4791,7 @@
       <c r="D54" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="95" t="inlineStr">
+      <c r="E54" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4817,7 +4802,7 @@
       <c r="G54" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="95" t="inlineStr">
+      <c r="H54" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4847,7 +4832,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N54" s="70" t="inlineStr">
+      <c r="N54" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4864,7 +4849,7 @@
           <t>PS5-08-11</t>
         </is>
       </c>
-      <c r="B55" s="83" t="inlineStr">
+      <c r="B55" s="80" t="inlineStr">
         <is>
           <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
@@ -4875,7 +4860,7 @@
       <c r="D55" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E55" s="70" t="inlineStr">
+      <c r="E55" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4886,7 +4871,7 @@
       <c r="G55" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H55" s="70" t="inlineStr">
+      <c r="H55" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4916,7 +4901,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N55" s="70" t="inlineStr">
+      <c r="N55" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4933,7 +4918,7 @@
           <t>PS5-08-12</t>
         </is>
       </c>
-      <c r="B56" s="83" t="inlineStr">
+      <c r="B56" s="80" t="inlineStr">
         <is>
           <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
@@ -4944,7 +4929,7 @@
       <c r="D56" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="95" t="inlineStr">
+      <c r="E56" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4955,7 +4940,7 @@
       <c r="G56" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="70" t="inlineStr">
+      <c r="H56" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4985,7 +4970,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N56" s="70" t="inlineStr">
+      <c r="N56" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5002,7 +4987,7 @@
           <t>PS5-08-13</t>
         </is>
       </c>
-      <c r="B57" s="83" t="inlineStr">
+      <c r="B57" s="80" t="inlineStr">
         <is>
           <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
@@ -5013,7 +4998,7 @@
       <c r="D57" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="69" t="inlineStr">
+      <c r="E57" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -5024,7 +5009,7 @@
       <c r="G57" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="70" t="inlineStr">
+      <c r="H57" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5054,7 +5039,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N57" s="70" t="inlineStr">
+      <c r="N57" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5071,7 +5056,7 @@
           <t>PS5-08-14</t>
         </is>
       </c>
-      <c r="B58" s="83" t="inlineStr">
+      <c r="B58" s="80" t="inlineStr">
         <is>
           <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
@@ -5082,7 +5067,7 @@
       <c r="D58" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E58" s="95" t="inlineStr">
+      <c r="E58" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5093,7 +5078,7 @@
       <c r="G58" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="70" t="inlineStr">
+      <c r="H58" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5123,7 +5108,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N58" s="70" t="inlineStr">
+      <c r="N58" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5140,7 +5125,7 @@
           <t>PS5-08-15</t>
         </is>
       </c>
-      <c r="B59" s="83" t="inlineStr">
+      <c r="B59" s="80" t="inlineStr">
         <is>
           <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
@@ -5151,7 +5136,7 @@
       <c r="D59" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E59" s="70" t="inlineStr">
+      <c r="E59" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -5162,7 +5147,7 @@
       <c r="G59" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="70" t="inlineStr">
+      <c r="H59" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5192,7 +5177,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N59" s="70" t="inlineStr">
+      <c r="N59" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5209,7 +5194,7 @@
           <t>PS5-08-23</t>
         </is>
       </c>
-      <c r="B60" s="83" t="inlineStr">
+      <c r="B60" s="80" t="inlineStr">
         <is>
           <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
@@ -5220,7 +5205,7 @@
       <c r="D60" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="70" t="inlineStr">
+      <c r="E60" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5231,7 +5216,7 @@
       <c r="G60" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="70" t="inlineStr">
+      <c r="H60" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5261,7 +5246,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N60" s="70" t="inlineStr">
+      <c r="N60" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5278,7 +5263,7 @@
           <t>PS5-08-34</t>
         </is>
       </c>
-      <c r="B61" s="83" t="inlineStr">
+      <c r="B61" s="80" t="inlineStr">
         <is>
           <t>PS5-08-34 - Satphone</t>
         </is>
@@ -5289,7 +5274,7 @@
       <c r="D61" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E61" s="95" t="inlineStr">
+      <c r="E61" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5300,7 +5285,7 @@
       <c r="G61" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="70" t="inlineStr">
+      <c r="H61" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5330,7 +5315,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N61" s="70" t="inlineStr">
+      <c r="N61" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5347,7 +5332,7 @@
           <t>PS5-08-35</t>
         </is>
       </c>
-      <c r="B62" s="83" t="inlineStr">
+      <c r="B62" s="80" t="inlineStr">
         <is>
           <t>PS5-08-35 - Optical Transport Network</t>
         </is>
@@ -5358,7 +5343,7 @@
       <c r="D62" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E62" s="70" t="inlineStr">
+      <c r="E62" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5369,7 +5354,7 @@
       <c r="G62" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="95" t="inlineStr">
+      <c r="H62" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5399,7 +5384,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N62" s="69" t="inlineStr">
+      <c r="N62" s="68" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -5416,7 +5401,7 @@
           <t>PS5-08-36</t>
         </is>
       </c>
-      <c r="B63" s="83" t="inlineStr">
+      <c r="B63" s="80" t="inlineStr">
         <is>
           <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
@@ -5427,7 +5412,7 @@
       <c r="D63" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E63" s="95" t="inlineStr">
+      <c r="E63" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5438,7 +5423,7 @@
       <c r="G63" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="70" t="inlineStr">
+      <c r="H63" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5468,7 +5453,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N63" s="70" t="inlineStr">
+      <c r="N63" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5485,7 +5470,7 @@
           <t>PS5-08-51</t>
         </is>
       </c>
-      <c r="B64" s="83" t="inlineStr">
+      <c r="B64" s="80" t="inlineStr">
         <is>
           <t>PS5-08-51 - Entertainment</t>
         </is>
@@ -5496,7 +5481,7 @@
       <c r="D64" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="95" t="inlineStr">
+      <c r="E64" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5507,7 +5492,7 @@
       <c r="G64" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H64" s="70" t="inlineStr">
+      <c r="H64" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5537,7 +5522,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N64" s="70" t="inlineStr">
+      <c r="N64" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5554,7 +5539,7 @@
           <t>PS5-08-52</t>
         </is>
       </c>
-      <c r="B65" s="83" t="inlineStr">
+      <c r="B65" s="80" t="inlineStr">
         <is>
           <t>PS5-08-52 - Process &amp; Security CCTV</t>
         </is>
@@ -5565,7 +5550,7 @@
       <c r="D65" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="95" t="inlineStr">
+      <c r="E65" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5576,7 +5561,7 @@
       <c r="G65" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="H65" s="70" t="inlineStr">
+      <c r="H65" s="69" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -5606,7 +5591,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N65" s="70" t="inlineStr">
+      <c r="N65" s="69" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -5623,7 +5608,7 @@
           <t>PS5-08-55</t>
         </is>
       </c>
-      <c r="B66" s="83" t="inlineStr">
+      <c r="B66" s="80" t="inlineStr">
         <is>
           <t>PS5-08-55 - Videoconference</t>
         </is>
@@ -5634,7 +5619,7 @@
       <c r="D66" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="95" t="inlineStr">
+      <c r="E66" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5645,7 +5630,7 @@
       <c r="G66" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H66" s="95" t="inlineStr">
+      <c r="H66" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5675,7 +5660,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N66" s="70" t="inlineStr">
+      <c r="N66" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5692,7 +5677,7 @@
           <t>PS5-08-61</t>
         </is>
       </c>
-      <c r="B67" s="83" t="inlineStr">
+      <c r="B67" s="80" t="inlineStr">
         <is>
           <t>PS5-08-61 - Meteocean</t>
         </is>
@@ -5703,7 +5688,7 @@
       <c r="D67" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="95" t="inlineStr">
+      <c r="E67" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5714,7 +5699,7 @@
       <c r="G67" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H67" s="70" t="inlineStr">
+      <c r="H67" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5744,7 +5729,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N67" s="70" t="inlineStr">
+      <c r="N67" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5761,7 +5746,7 @@
           <t>PS5-08-71</t>
         </is>
       </c>
-      <c r="B68" s="83" t="inlineStr">
+      <c r="B68" s="80" t="inlineStr">
         <is>
           <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
@@ -5772,7 +5757,7 @@
       <c r="D68" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E68" s="95" t="inlineStr">
+      <c r="E68" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5783,7 +5768,7 @@
       <c r="G68" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H68" s="70" t="inlineStr">
+      <c r="H68" s="69" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -5813,7 +5798,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N68" s="70" t="inlineStr">
+      <c r="N68" s="69" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -5830,7 +5815,7 @@
           <t>PS5-08-72</t>
         </is>
       </c>
-      <c r="B69" s="83" t="inlineStr">
+      <c r="B69" s="80" t="inlineStr">
         <is>
           <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
@@ -5841,7 +5826,7 @@
       <c r="D69" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E69" s="95" t="inlineStr">
+      <c r="E69" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5852,7 +5837,7 @@
       <c r="G69" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="70" t="inlineStr">
+      <c r="H69" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5882,7 +5867,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N69" s="70" t="inlineStr">
+      <c r="N69" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5899,7 +5884,7 @@
           <t>PS5-08-81</t>
         </is>
       </c>
-      <c r="B70" s="83" t="inlineStr">
+      <c r="B70" s="80" t="inlineStr">
         <is>
           <t>PS5-08-81 - Guard tour</t>
         </is>
@@ -5910,7 +5895,7 @@
       <c r="D70" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E70" s="95" t="inlineStr">
+      <c r="E70" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5921,7 +5906,7 @@
       <c r="G70" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H70" s="95" t="inlineStr">
+      <c r="H70" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5951,7 +5936,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N70" s="70" t="inlineStr">
+      <c r="N70" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5968,7 +5953,7 @@
           <t>PS5-08-82</t>
         </is>
       </c>
-      <c r="B71" s="83" t="inlineStr">
+      <c r="B71" s="80" t="inlineStr">
         <is>
           <t>PS5-08-82 - Key Management</t>
         </is>
@@ -5979,7 +5964,7 @@
       <c r="D71" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E71" s="95" t="inlineStr">
+      <c r="E71" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5990,7 +5975,7 @@
       <c r="G71" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H71" s="95" t="inlineStr">
+      <c r="H71" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6020,7 +6005,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N71" s="70" t="inlineStr">
+      <c r="N71" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6037,7 +6022,7 @@
           <t>PS5-08-83</t>
         </is>
       </c>
-      <c r="B72" s="83" t="inlineStr">
+      <c r="B72" s="80" t="inlineStr">
         <is>
           <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
@@ -6048,7 +6033,7 @@
       <c r="D72" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="95" t="inlineStr">
+      <c r="E72" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6059,7 +6044,7 @@
       <c r="G72" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="70" t="inlineStr">
+      <c r="H72" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6089,7 +6074,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N72" s="70" t="inlineStr">
+      <c r="N72" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6106,7 +6091,7 @@
           <t>PS5-08-85</t>
         </is>
       </c>
-      <c r="B73" s="83" t="inlineStr">
+      <c r="B73" s="80" t="inlineStr">
         <is>
           <t>PS5-08-85 - Access Control, POB &amp; e-Mustering</t>
         </is>
@@ -6128,7 +6113,7 @@
       <c r="G73" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="H73" s="70" t="inlineStr">
+      <c r="H73" s="69" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -6158,7 +6143,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N73" s="70" t="inlineStr">
+      <c r="N73" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -6175,7 +6160,7 @@
           <t>PS5-08-86</t>
         </is>
       </c>
-      <c r="B74" s="83" t="inlineStr">
+      <c r="B74" s="80" t="inlineStr">
         <is>
           <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
@@ -6186,7 +6171,7 @@
       <c r="D74" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="95" t="inlineStr">
+      <c r="E74" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6197,7 +6182,7 @@
       <c r="G74" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="95" t="inlineStr">
+      <c r="H74" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6227,7 +6212,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N74" s="70" t="inlineStr">
+      <c r="N74" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6244,7 +6229,7 @@
           <t>PS5-08-92</t>
         </is>
       </c>
-      <c r="B75" s="83" t="inlineStr">
+      <c r="B75" s="80" t="inlineStr">
         <is>
           <t>PS5-08-92 - Telecom Mast</t>
         </is>
@@ -6255,7 +6240,7 @@
       <c r="D75" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E75" s="95" t="inlineStr">
+      <c r="E75" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6266,7 +6251,7 @@
       <c r="G75" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H75" s="95" t="inlineStr">
+      <c r="H75" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6296,7 +6281,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N75" s="70" t="inlineStr">
+      <c r="N75" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6313,7 +6298,7 @@
           <t>PS5-08-93</t>
         </is>
       </c>
-      <c r="B76" s="83" t="inlineStr">
+      <c r="B76" s="80" t="inlineStr">
         <is>
           <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
@@ -6324,7 +6309,7 @@
       <c r="D76" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E76" s="95" t="inlineStr">
+      <c r="E76" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6335,7 +6320,7 @@
       <c r="G76" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H76" s="70" t="inlineStr">
+      <c r="H76" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6365,7 +6350,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N76" s="70" t="inlineStr">
+      <c r="N76" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6382,7 +6367,7 @@
           <t>PS5-09-01</t>
         </is>
       </c>
-      <c r="B77" s="83" t="inlineStr">
+      <c r="B77" s="80" t="inlineStr">
         <is>
           <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
@@ -6393,7 +6378,7 @@
       <c r="D77" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="95" t="inlineStr">
+      <c r="E77" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6404,7 +6389,7 @@
       <c r="G77" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H77" s="70" t="inlineStr">
+      <c r="H77" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6434,7 +6419,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N77" s="70" t="inlineStr">
+      <c r="N77" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6451,7 +6436,7 @@
           <t>PS5-09-02</t>
         </is>
       </c>
-      <c r="B78" s="83" t="inlineStr">
+      <c r="B78" s="80" t="inlineStr">
         <is>
           <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
@@ -6462,7 +6447,7 @@
       <c r="D78" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E78" s="95" t="inlineStr">
+      <c r="E78" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6473,7 +6458,7 @@
       <c r="G78" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H78" s="70" t="inlineStr">
+      <c r="H78" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6503,7 +6488,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N78" s="70" t="inlineStr">
+      <c r="N78" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6520,7 +6505,7 @@
           <t>PS5-09-03</t>
         </is>
       </c>
-      <c r="B79" s="83" t="inlineStr">
+      <c r="B79" s="80" t="inlineStr">
         <is>
           <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
@@ -6531,7 +6516,7 @@
       <c r="D79" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E79" s="70" t="inlineStr">
+      <c r="E79" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -6542,7 +6527,7 @@
       <c r="G79" s="23" t="n">
         <v>53</v>
       </c>
-      <c r="H79" s="70" t="inlineStr">
+      <c r="H79" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -6572,7 +6557,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N79" s="70" t="inlineStr">
+      <c r="N79" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -6589,7 +6574,7 @@
           <t>PS5-09-04</t>
         </is>
       </c>
-      <c r="B80" s="83" t="inlineStr">
+      <c r="B80" s="80" t="inlineStr">
         <is>
           <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
@@ -6600,7 +6585,7 @@
       <c r="D80" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E80" s="95" t="inlineStr">
+      <c r="E80" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6611,7 +6596,7 @@
       <c r="G80" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="70" t="inlineStr">
+      <c r="H80" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6641,7 +6626,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N80" s="70" t="inlineStr">
+      <c r="N80" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6658,7 +6643,7 @@
           <t>PS5-09-05</t>
         </is>
       </c>
-      <c r="B81" s="83" t="inlineStr">
+      <c r="B81" s="80" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -6669,7 +6654,7 @@
       <c r="D81" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="E81" s="69" t="inlineStr">
+      <c r="E81" s="68" t="inlineStr">
         <is>
           <t>56%</t>
         </is>
@@ -6727,7 +6712,7 @@
           <t>PS5-0H-01</t>
         </is>
       </c>
-      <c r="B82" s="83" t="inlineStr">
+      <c r="B82" s="80" t="inlineStr">
         <is>
           <t>PS5-0H-01 - HIPPS</t>
         </is>
@@ -6738,7 +6723,7 @@
       <c r="D82" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E82" s="70" t="inlineStr">
+      <c r="E82" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -6749,7 +6734,7 @@
       <c r="G82" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="95" t="inlineStr">
+      <c r="H82" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6779,7 +6764,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N82" s="69" t="inlineStr">
+      <c r="N82" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -6796,7 +6781,7 @@
           <t>PS5-25-01</t>
         </is>
       </c>
-      <c r="B83" s="83" t="inlineStr">
+      <c r="B83" s="80" t="inlineStr">
         <is>
           <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
@@ -6807,7 +6792,7 @@
       <c r="D83" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E83" s="70" t="inlineStr">
+      <c r="E83" s="69" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -6818,7 +6803,7 @@
       <c r="G83" s="23" t="n">
         <v>111</v>
       </c>
-      <c r="H83" s="69" t="inlineStr">
+      <c r="H83" s="68" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -6848,7 +6833,7 @@
           <t>42/46</t>
         </is>
       </c>
-      <c r="N83" s="69" t="inlineStr">
+      <c r="N83" s="68" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -6865,7 +6850,7 @@
           <t>PS5-25-02</t>
         </is>
       </c>
-      <c r="B84" s="83" t="inlineStr">
+      <c r="B84" s="80" t="inlineStr">
         <is>
           <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
@@ -6876,7 +6861,7 @@
       <c r="D84" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="E84" s="70" t="inlineStr">
+      <c r="E84" s="69" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -6887,7 +6872,7 @@
       <c r="G84" s="23" t="n">
         <v>175</v>
       </c>
-      <c r="H84" s="69" t="inlineStr">
+      <c r="H84" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -6917,7 +6902,7 @@
           <t>23/24</t>
         </is>
       </c>
-      <c r="N84" s="69" t="inlineStr">
+      <c r="N84" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -6934,7 +6919,7 @@
           <t>PS5-25-03</t>
         </is>
       </c>
-      <c r="B85" s="83" t="inlineStr">
+      <c r="B85" s="80" t="inlineStr">
         <is>
           <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
@@ -6945,7 +6930,7 @@
       <c r="D85" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="E85" s="70" t="inlineStr">
+      <c r="E85" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -6956,7 +6941,7 @@
       <c r="G85" s="23" t="n">
         <v>164</v>
       </c>
-      <c r="H85" s="69" t="inlineStr">
+      <c r="H85" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -6986,7 +6971,7 @@
           <t>23/24</t>
         </is>
       </c>
-      <c r="N85" s="69" t="inlineStr">
+      <c r="N85" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -7003,7 +6988,7 @@
           <t>PS5-25-04</t>
         </is>
       </c>
-      <c r="B86" s="83" t="inlineStr">
+      <c r="B86" s="80" t="inlineStr">
         <is>
           <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
@@ -7014,7 +6999,7 @@
       <c r="D86" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E86" s="70" t="inlineStr">
+      <c r="E86" s="69" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -7025,7 +7010,7 @@
       <c r="G86" s="23" t="n">
         <v>161</v>
       </c>
-      <c r="H86" s="69" t="inlineStr">
+      <c r="H86" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -7055,7 +7040,7 @@
           <t>23/24</t>
         </is>
       </c>
-      <c r="N86" s="69" t="inlineStr">
+      <c r="N86" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -7072,7 +7057,7 @@
           <t>PS5-25-05</t>
         </is>
       </c>
-      <c r="B87" s="83" t="inlineStr">
+      <c r="B87" s="80" t="inlineStr">
         <is>
           <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
@@ -7094,7 +7079,7 @@
       <c r="G87" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H87" s="69" t="inlineStr">
+      <c r="H87" s="68" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
@@ -7124,7 +7109,7 @@
           <t>8/9</t>
         </is>
       </c>
-      <c r="N87" s="69" t="inlineStr">
+      <c r="N87" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -7141,7 +7126,7 @@
           <t>PS5-25-06</t>
         </is>
       </c>
-      <c r="B88" s="83" t="inlineStr">
+      <c r="B88" s="80" t="inlineStr">
         <is>
           <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
@@ -7152,7 +7137,7 @@
       <c r="D88" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E88" s="70" t="inlineStr">
+      <c r="E88" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7163,7 +7148,7 @@
       <c r="G88" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H88" s="69" t="inlineStr">
+      <c r="H88" s="68" t="inlineStr">
         <is>
           <t>59%</t>
         </is>
@@ -7193,7 +7178,7 @@
           <t>17/19</t>
         </is>
       </c>
-      <c r="N88" s="69" t="inlineStr">
+      <c r="N88" s="68" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -7210,7 +7195,7 @@
           <t>PS5-25-07</t>
         </is>
       </c>
-      <c r="B89" s="83" t="inlineStr">
+      <c r="B89" s="80" t="inlineStr">
         <is>
           <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
@@ -7221,7 +7206,7 @@
       <c r="D89" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E89" s="70" t="inlineStr">
+      <c r="E89" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -7232,7 +7217,7 @@
       <c r="G89" s="23" t="n">
         <v>103</v>
       </c>
-      <c r="H89" s="69" t="inlineStr">
+      <c r="H89" s="68" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -7262,7 +7247,7 @@
           <t>33/35</t>
         </is>
       </c>
-      <c r="N89" s="69" t="inlineStr">
+      <c r="N89" s="68" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -7279,7 +7264,7 @@
           <t>PS5-28-01</t>
         </is>
       </c>
-      <c r="B90" s="83" t="inlineStr">
+      <c r="B90" s="80" t="inlineStr">
         <is>
           <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
@@ -7290,7 +7275,7 @@
       <c r="D90" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E90" s="95" t="inlineStr">
+      <c r="E90" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7301,7 +7286,7 @@
       <c r="G90" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H90" s="69" t="inlineStr">
+      <c r="H90" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -7331,7 +7316,7 @@
           <t>12/14</t>
         </is>
       </c>
-      <c r="N90" s="69" t="inlineStr">
+      <c r="N90" s="68" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -7348,7 +7333,7 @@
           <t>PS5-28-02</t>
         </is>
       </c>
-      <c r="B91" s="83" t="inlineStr">
+      <c r="B91" s="80" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -7359,7 +7344,7 @@
       <c r="D91" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E91" s="70" t="inlineStr">
+      <c r="E91" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7417,7 +7402,7 @@
           <t>PS5-28-03</t>
         </is>
       </c>
-      <c r="B92" s="83" t="inlineStr">
+      <c r="B92" s="80" t="inlineStr">
         <is>
           <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
@@ -7428,7 +7413,7 @@
       <c r="D92" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E92" s="70" t="inlineStr">
+      <c r="E92" s="69" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -7439,7 +7424,7 @@
       <c r="G92" s="23" t="n">
         <v>93</v>
       </c>
-      <c r="H92" s="69" t="inlineStr">
+      <c r="H92" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -7469,7 +7454,7 @@
           <t>54/56</t>
         </is>
       </c>
-      <c r="N92" s="69" t="inlineStr">
+      <c r="N92" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -7486,7 +7471,7 @@
           <t>PS5-28-04</t>
         </is>
       </c>
-      <c r="B93" s="83" t="inlineStr">
+      <c r="B93" s="80" t="inlineStr">
         <is>
           <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
@@ -7497,7 +7482,7 @@
       <c r="D93" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E93" s="70" t="inlineStr">
+      <c r="E93" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -7555,7 +7540,7 @@
           <t>PS5-28-05</t>
         </is>
       </c>
-      <c r="B94" s="83" t="inlineStr">
+      <c r="B94" s="80" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -7566,7 +7551,7 @@
       <c r="D94" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E94" s="70" t="inlineStr">
+      <c r="E94" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7624,7 +7609,7 @@
           <t>PS5-28-06</t>
         </is>
       </c>
-      <c r="B95" s="83" t="inlineStr">
+      <c r="B95" s="80" t="inlineStr">
         <is>
           <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
@@ -7635,7 +7620,7 @@
       <c r="D95" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E95" s="70" t="inlineStr">
+      <c r="E95" s="69" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -7676,7 +7661,7 @@
           <t>36/36</t>
         </is>
       </c>
-      <c r="N95" s="69" t="inlineStr">
+      <c r="N95" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -7693,7 +7678,7 @@
           <t>PS5-28-07</t>
         </is>
       </c>
-      <c r="B96" s="83" t="inlineStr">
+      <c r="B96" s="80" t="inlineStr">
         <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
@@ -7704,7 +7689,7 @@
       <c r="D96" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E96" s="70" t="inlineStr">
+      <c r="E96" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -7762,7 +7747,7 @@
           <t>PS5-28-08</t>
         </is>
       </c>
-      <c r="B97" s="83" t="inlineStr">
+      <c r="B97" s="80" t="inlineStr">
         <is>
           <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
@@ -7773,7 +7758,7 @@
       <c r="D97" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E97" s="70" t="inlineStr">
+      <c r="E97" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7784,7 +7769,7 @@
       <c r="G97" s="23" t="n">
         <v>34</v>
       </c>
-      <c r="H97" s="70" t="inlineStr">
+      <c r="H97" s="69" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
@@ -7814,7 +7799,7 @@
           <t>23/29</t>
         </is>
       </c>
-      <c r="N97" s="70" t="inlineStr">
+      <c r="N97" s="69" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -7831,7 +7816,7 @@
           <t>PS5-28-09</t>
         </is>
       </c>
-      <c r="B98" s="83" t="inlineStr">
+      <c r="B98" s="80" t="inlineStr">
         <is>
           <t>PS5-28-09 - Observation Basin</t>
         </is>
@@ -7842,7 +7827,7 @@
       <c r="D98" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E98" s="70" t="inlineStr">
+      <c r="E98" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7883,7 +7868,7 @@
           <t>13/14</t>
         </is>
       </c>
-      <c r="N98" s="69" t="inlineStr">
+      <c r="N98" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -7900,7 +7885,7 @@
           <t>PS5-28-10</t>
         </is>
       </c>
-      <c r="B99" s="83" t="inlineStr">
+      <c r="B99" s="80" t="inlineStr">
         <is>
           <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
@@ -7911,7 +7896,7 @@
       <c r="D99" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E99" s="70" t="inlineStr">
+      <c r="E99" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7922,7 +7907,7 @@
       <c r="G99" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H99" s="70" t="inlineStr">
+      <c r="H99" s="69" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -7952,7 +7937,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N99" s="70" t="inlineStr">
+      <c r="N99" s="69" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -7969,7 +7954,7 @@
           <t>PS5-28-11</t>
         </is>
       </c>
-      <c r="B100" s="83" t="inlineStr">
+      <c r="B100" s="80" t="inlineStr">
         <is>
           <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
@@ -7980,7 +7965,7 @@
       <c r="D100" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E100" s="70" t="inlineStr">
+      <c r="E100" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7991,7 +7976,7 @@
       <c r="G100" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H100" s="69" t="inlineStr">
+      <c r="H100" s="68" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -8021,7 +8006,7 @@
           <t>8/8</t>
         </is>
       </c>
-      <c r="N100" s="69" t="inlineStr">
+      <c r="N100" s="68" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -8038,7 +8023,7 @@
           <t>PS5-28-12</t>
         </is>
       </c>
-      <c r="B101" s="83" t="inlineStr">
+      <c r="B101" s="80" t="inlineStr">
         <is>
           <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
@@ -8049,7 +8034,7 @@
       <c r="D101" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E101" s="70" t="inlineStr">
+      <c r="E101" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8060,7 +8045,7 @@
       <c r="G101" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="H101" s="69" t="inlineStr">
+      <c r="H101" s="68" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8090,7 +8075,7 @@
           <t>28/43</t>
         </is>
       </c>
-      <c r="N101" s="69" t="inlineStr">
+      <c r="N101" s="68" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8107,7 +8092,7 @@
           <t>PS5-28-13</t>
         </is>
       </c>
-      <c r="B102" s="83" t="inlineStr">
+      <c r="B102" s="80" t="inlineStr">
         <is>
           <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
@@ -8118,7 +8103,7 @@
       <c r="D102" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E102" s="69" t="inlineStr">
+      <c r="E102" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8129,7 +8114,7 @@
       <c r="G102" s="23" t="n">
         <v>54</v>
       </c>
-      <c r="H102" s="69" t="inlineStr">
+      <c r="H102" s="68" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -8159,7 +8144,7 @@
           <t>34/35</t>
         </is>
       </c>
-      <c r="N102" s="69" t="inlineStr">
+      <c r="N102" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -8176,7 +8161,7 @@
           <t>PS5-28-14</t>
         </is>
       </c>
-      <c r="B103" s="83" t="inlineStr">
+      <c r="B103" s="80" t="inlineStr">
         <is>
           <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
@@ -8187,7 +8172,7 @@
       <c r="D103" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="69" t="inlineStr">
+      <c r="E103" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8198,7 +8183,7 @@
       <c r="G103" s="23" t="n">
         <v>53</v>
       </c>
-      <c r="H103" s="69" t="inlineStr">
+      <c r="H103" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -8228,7 +8213,7 @@
           <t>32/35</t>
         </is>
       </c>
-      <c r="N103" s="69" t="inlineStr">
+      <c r="N103" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8245,7 +8230,7 @@
           <t>PS5-28-15</t>
         </is>
       </c>
-      <c r="B104" s="83" t="inlineStr">
+      <c r="B104" s="80" t="inlineStr">
         <is>
           <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
@@ -8256,7 +8241,7 @@
       <c r="D104" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E104" s="69" t="inlineStr">
+      <c r="E104" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8267,7 +8252,7 @@
       <c r="G104" s="23" t="n">
         <v>52</v>
       </c>
-      <c r="H104" s="69" t="inlineStr">
+      <c r="H104" s="68" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -8297,7 +8282,7 @@
           <t>32/35</t>
         </is>
       </c>
-      <c r="N104" s="69" t="inlineStr">
+      <c r="N104" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8314,7 +8299,7 @@
           <t>PS5-28-16</t>
         </is>
       </c>
-      <c r="B105" s="83" t="inlineStr">
+      <c r="B105" s="80" t="inlineStr">
         <is>
           <t>PS5-28-16 - LP Relief Header</t>
         </is>
@@ -8325,7 +8310,7 @@
       <c r="D105" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E105" s="95" t="inlineStr">
+      <c r="E105" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8366,7 +8351,7 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N105" s="69" t="inlineStr">
+      <c r="N105" s="68" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -8383,7 +8368,7 @@
           <t>PS5-28-17</t>
         </is>
       </c>
-      <c r="B106" s="83" t="inlineStr">
+      <c r="B106" s="80" t="inlineStr">
         <is>
           <t>PS5-28-17 - Reinjection Pump</t>
         </is>
@@ -8394,7 +8379,7 @@
       <c r="D106" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E106" s="70" t="inlineStr">
+      <c r="E106" s="69" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -8405,7 +8390,7 @@
       <c r="G106" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H106" s="69" t="inlineStr">
+      <c r="H106" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -8435,7 +8420,7 @@
           <t>24/24</t>
         </is>
       </c>
-      <c r="N106" s="69" t="inlineStr">
+      <c r="N106" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -8452,7 +8437,7 @@
           <t>PS5-50-01</t>
         </is>
       </c>
-      <c r="B107" s="83" t="inlineStr">
+      <c r="B107" s="80" t="inlineStr">
         <is>
           <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
@@ -8463,7 +8448,7 @@
       <c r="D107" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E107" s="95" t="inlineStr">
+      <c r="E107" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8474,7 +8459,7 @@
       <c r="G107" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H107" s="70" t="inlineStr">
+      <c r="H107" s="69" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8504,7 +8489,7 @@
           <t>9/13</t>
         </is>
       </c>
-      <c r="N107" s="70" t="inlineStr">
+      <c r="N107" s="69" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8521,7 +8506,7 @@
           <t>PS5-50-02</t>
         </is>
       </c>
-      <c r="B108" s="83" t="inlineStr">
+      <c r="B108" s="80" t="inlineStr">
         <is>
           <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
@@ -8532,7 +8517,7 @@
       <c r="D108" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E108" s="95" t="inlineStr">
+      <c r="E108" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8543,7 +8528,7 @@
       <c r="G108" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H108" s="70" t="inlineStr">
+      <c r="H108" s="69" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -8573,7 +8558,7 @@
           <t>10/13</t>
         </is>
       </c>
-      <c r="N108" s="70" t="inlineStr">
+      <c r="N108" s="69" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -8590,7 +8575,7 @@
           <t>PS5-50-03</t>
         </is>
       </c>
-      <c r="B109" s="83" t="inlineStr">
+      <c r="B109" s="80" t="inlineStr">
         <is>
           <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
@@ -8601,7 +8586,7 @@
       <c r="D109" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="70" t="inlineStr">
+      <c r="E109" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8612,7 +8597,7 @@
       <c r="G109" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H109" s="69" t="inlineStr">
+      <c r="H109" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8642,7 +8627,7 @@
           <t>10/15</t>
         </is>
       </c>
-      <c r="N109" s="70" t="inlineStr">
+      <c r="N109" s="69" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8659,7 +8644,7 @@
           <t>PS5-53-01</t>
         </is>
       </c>
-      <c r="B110" s="83" t="inlineStr">
+      <c r="B110" s="80" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -8670,7 +8655,7 @@
       <c r="D110" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E110" s="69" t="inlineStr">
+      <c r="E110" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -8681,7 +8666,7 @@
       <c r="G110" s="23" t="n">
         <v>42</v>
       </c>
-      <c r="H110" s="69" t="inlineStr">
+      <c r="H110" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -8711,12 +8696,12 @@
           <t>27/30</t>
         </is>
       </c>
-      <c r="N110" s="69" t="inlineStr">
+      <c r="N110" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="O110" s="69" t="inlineStr">
+      <c r="O110" s="68" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -8728,7 +8713,7 @@
           <t>PS5-53-02</t>
         </is>
       </c>
-      <c r="B111" s="83" t="inlineStr">
+      <c r="B111" s="80" t="inlineStr">
         <is>
           <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
@@ -8739,7 +8724,7 @@
       <c r="D111" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="70" t="inlineStr">
+      <c r="E111" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8750,7 +8735,7 @@
       <c r="G111" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H111" s="69" t="inlineStr">
+      <c r="H111" s="68" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
@@ -8780,7 +8765,7 @@
           <t>8/8</t>
         </is>
       </c>
-      <c r="N111" s="69" t="inlineStr">
+      <c r="N111" s="68" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -8797,7 +8782,7 @@
           <t>PS5-53-03</t>
         </is>
       </c>
-      <c r="B112" s="83" t="inlineStr">
+      <c r="B112" s="80" t="inlineStr">
         <is>
           <t>PS5-53-03 - Water Softener Package</t>
         </is>
@@ -8808,7 +8793,7 @@
       <c r="D112" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E112" s="95" t="inlineStr">
+      <c r="E112" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8819,7 +8804,7 @@
       <c r="G112" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H112" s="69" t="inlineStr">
+      <c r="H112" s="68" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8849,7 +8834,7 @@
           <t>11/14</t>
         </is>
       </c>
-      <c r="N112" s="69" t="inlineStr">
+      <c r="N112" s="68" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8866,7 +8851,7 @@
           <t>PS5-53-04</t>
         </is>
       </c>
-      <c r="B113" s="83" t="inlineStr">
+      <c r="B113" s="80" t="inlineStr">
         <is>
           <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
@@ -8877,7 +8862,7 @@
       <c r="D113" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="95" t="inlineStr">
+      <c r="E113" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8888,7 +8873,7 @@
       <c r="G113" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="70" t="inlineStr">
+      <c r="H113" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8918,7 +8903,7 @@
           <t>0/1</t>
         </is>
       </c>
-      <c r="N113" s="70" t="inlineStr">
+      <c r="N113" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8935,7 +8920,7 @@
           <t>PS5-53-05</t>
         </is>
       </c>
-      <c r="B114" s="83" t="inlineStr">
+      <c r="B114" s="80" t="inlineStr">
         <is>
           <t>PS5-53-05 - Water Distribution Header</t>
         </is>
@@ -8946,7 +8931,7 @@
       <c r="D114" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E114" s="95" t="inlineStr">
+      <c r="E114" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9004,7 +8989,7 @@
           <t>PS5-53-06</t>
         </is>
       </c>
-      <c r="B115" s="83" t="inlineStr">
+      <c r="B115" s="80" t="inlineStr">
         <is>
           <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
@@ -9015,7 +9000,7 @@
       <c r="D115" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E115" s="95" t="inlineStr">
+      <c r="E115" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9026,7 +9011,7 @@
       <c r="G115" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H115" s="69" t="inlineStr">
+      <c r="H115" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -9056,7 +9041,7 @@
           <t>33/39</t>
         </is>
       </c>
-      <c r="N115" s="69" t="inlineStr">
+      <c r="N115" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -9073,7 +9058,7 @@
           <t>PS5-60-01</t>
         </is>
       </c>
-      <c r="B116" s="83" t="inlineStr">
+      <c r="B116" s="80" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -9084,7 +9069,7 @@
       <c r="D116" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="E116" s="70" t="inlineStr">
+      <c r="E116" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -9142,7 +9127,7 @@
           <t>PS5-60-02</t>
         </is>
       </c>
-      <c r="B117" s="83" t="inlineStr">
+      <c r="B117" s="80" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -9153,7 +9138,7 @@
       <c r="D117" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E117" s="70" t="inlineStr">
+      <c r="E117" s="69" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -9211,7 +9196,7 @@
           <t>PS5-60-03</t>
         </is>
       </c>
-      <c r="B118" s="83" t="inlineStr">
+      <c r="B118" s="80" t="inlineStr">
         <is>
           <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9222,7 +9207,7 @@
       <c r="D118" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E118" s="70" t="inlineStr">
+      <c r="E118" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -9233,7 +9218,7 @@
       <c r="G118" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H118" s="69" t="inlineStr">
+      <c r="H118" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9263,7 +9248,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N118" s="69" t="inlineStr">
+      <c r="N118" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9280,7 +9265,7 @@
           <t>PS5-60-04</t>
         </is>
       </c>
-      <c r="B119" s="83" t="inlineStr">
+      <c r="B119" s="80" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -9291,7 +9276,7 @@
       <c r="D119" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E119" s="70" t="inlineStr">
+      <c r="E119" s="69" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -9349,7 +9334,7 @@
           <t>PS5-60-05</t>
         </is>
       </c>
-      <c r="B120" s="83" t="inlineStr">
+      <c r="B120" s="80" t="inlineStr">
         <is>
           <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
@@ -9360,7 +9345,7 @@
       <c r="D120" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E120" s="70" t="inlineStr">
+      <c r="E120" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9418,7 +9403,7 @@
           <t>PS5-60-06</t>
         </is>
       </c>
-      <c r="B121" s="83" t="inlineStr">
+      <c r="B121" s="80" t="inlineStr">
         <is>
           <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9429,7 +9414,7 @@
       <c r="D121" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="70" t="inlineStr">
+      <c r="E121" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9440,7 +9425,7 @@
       <c r="G121" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H121" s="69" t="inlineStr">
+      <c r="H121" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9470,7 +9455,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N121" s="69" t="inlineStr">
+      <c r="N121" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9487,7 +9472,7 @@
           <t>PS5-60-07</t>
         </is>
       </c>
-      <c r="B122" s="83" t="inlineStr">
+      <c r="B122" s="80" t="inlineStr">
         <is>
           <t>PS5-60-07 - Power Generation Package C</t>
         </is>
@@ -9498,7 +9483,7 @@
       <c r="D122" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E122" s="70" t="inlineStr">
+      <c r="E122" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -9556,7 +9541,7 @@
           <t>PS5-60-08</t>
         </is>
       </c>
-      <c r="B123" s="83" t="inlineStr">
+      <c r="B123" s="80" t="inlineStr">
         <is>
           <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
@@ -9567,7 +9552,7 @@
       <c r="D123" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E123" s="70" t="inlineStr">
+      <c r="E123" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9625,7 +9610,7 @@
           <t>PS5-60-09</t>
         </is>
       </c>
-      <c r="B124" s="83" t="inlineStr">
+      <c r="B124" s="80" t="inlineStr">
         <is>
           <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9636,7 +9621,7 @@
       <c r="D124" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E124" s="95" t="inlineStr">
+      <c r="E124" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9647,7 +9632,7 @@
       <c r="G124" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H124" s="69" t="inlineStr">
+      <c r="H124" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9677,7 +9662,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N124" s="69" t="inlineStr">
+      <c r="N124" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9694,7 +9679,7 @@
           <t>PS5-60-10</t>
         </is>
       </c>
-      <c r="B125" s="83" t="inlineStr">
+      <c r="B125" s="80" t="inlineStr">
         <is>
           <t>PS5-60-10 - Power Generation Package D</t>
         </is>
@@ -9705,7 +9690,7 @@
       <c r="D125" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E125" s="70" t="inlineStr">
+      <c r="E125" s="69" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -9763,7 +9748,7 @@
           <t>PS5-60-11</t>
         </is>
       </c>
-      <c r="B126" s="83" t="inlineStr">
+      <c r="B126" s="80" t="inlineStr">
         <is>
           <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
@@ -9774,7 +9759,7 @@
       <c r="D126" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E126" s="95" t="inlineStr">
+      <c r="E126" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9832,7 +9817,7 @@
           <t>PS5-60-12</t>
         </is>
       </c>
-      <c r="B127" s="83" t="inlineStr">
+      <c r="B127" s="80" t="inlineStr">
         <is>
           <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9843,7 +9828,7 @@
       <c r="D127" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E127" s="95" t="inlineStr">
+      <c r="E127" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9854,7 +9839,7 @@
       <c r="G127" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H127" s="69" t="inlineStr">
+      <c r="H127" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9884,7 +9869,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N127" s="69" t="inlineStr">
+      <c r="N127" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9901,7 +9886,7 @@
           <t>PS5-60-13</t>
         </is>
       </c>
-      <c r="B128" s="83" t="inlineStr">
+      <c r="B128" s="80" t="inlineStr">
         <is>
           <t>PS5-60-13 - Power Generation Package E</t>
         </is>
@@ -9912,7 +9897,7 @@
       <c r="D128" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="E128" s="70" t="inlineStr">
+      <c r="E128" s="69" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -9970,7 +9955,7 @@
           <t>PS5-60-14</t>
         </is>
       </c>
-      <c r="B129" s="83" t="inlineStr">
+      <c r="B129" s="80" t="inlineStr">
         <is>
           <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
@@ -9981,7 +9966,7 @@
       <c r="D129" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E129" s="95" t="inlineStr">
+      <c r="E129" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10039,7 +10024,7 @@
           <t>PS5-60-15</t>
         </is>
       </c>
-      <c r="B130" s="83" t="inlineStr">
+      <c r="B130" s="80" t="inlineStr">
         <is>
           <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10050,7 +10035,7 @@
       <c r="D130" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E130" s="95" t="inlineStr">
+      <c r="E130" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10061,7 +10046,7 @@
       <c r="G130" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H130" s="69" t="inlineStr">
+      <c r="H130" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10091,7 +10076,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N130" s="69" t="inlineStr">
+      <c r="N130" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10108,7 +10093,7 @@
           <t>PS5-60-16</t>
         </is>
       </c>
-      <c r="B131" s="83" t="inlineStr">
+      <c r="B131" s="80" t="inlineStr">
         <is>
           <t>PS5-60-16 - Power Generation Package F</t>
         </is>
@@ -10119,7 +10104,7 @@
       <c r="D131" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E131" s="70" t="inlineStr">
+      <c r="E131" s="69" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -10177,7 +10162,7 @@
           <t>PS5-60-17</t>
         </is>
       </c>
-      <c r="B132" s="83" t="inlineStr">
+      <c r="B132" s="80" t="inlineStr">
         <is>
           <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
@@ -10188,7 +10173,7 @@
       <c r="D132" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E132" s="95" t="inlineStr">
+      <c r="E132" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10229,7 +10214,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N132" s="69" t="inlineStr">
+      <c r="N132" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10246,7 +10231,7 @@
           <t>PS5-60-18</t>
         </is>
       </c>
-      <c r="B133" s="83" t="inlineStr">
+      <c r="B133" s="80" t="inlineStr">
         <is>
           <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10257,7 +10242,7 @@
       <c r="D133" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E133" s="95" t="inlineStr">
+      <c r="E133" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10268,7 +10253,7 @@
       <c r="G133" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H133" s="69" t="inlineStr">
+      <c r="H133" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -10298,7 +10283,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N133" s="69" t="inlineStr">
+      <c r="N133" s="68" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -10315,7 +10300,7 @@
           <t>PS5-60-19</t>
         </is>
       </c>
-      <c r="B134" s="83" t="inlineStr">
+      <c r="B134" s="80" t="inlineStr">
         <is>
           <t>PS5-60-19 - Power Generation Package G</t>
         </is>
@@ -10326,7 +10311,7 @@
       <c r="D134" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E134" s="70" t="inlineStr">
+      <c r="E134" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -10384,7 +10369,7 @@
           <t>PS5-60-20</t>
         </is>
       </c>
-      <c r="B135" s="83" t="inlineStr">
+      <c r="B135" s="80" t="inlineStr">
         <is>
           <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
@@ -10395,7 +10380,7 @@
       <c r="D135" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E135" s="95" t="inlineStr">
+      <c r="E135" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10406,7 +10391,7 @@
       <c r="G135" s="23" t="n">
         <v>37</v>
       </c>
-      <c r="H135" s="69" t="inlineStr">
+      <c r="H135" s="68" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -10436,7 +10421,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N135" s="69" t="inlineStr">
+      <c r="N135" s="68" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -10453,7 +10438,7 @@
           <t>PS5-60-21</t>
         </is>
       </c>
-      <c r="B136" s="83" t="inlineStr">
+      <c r="B136" s="80" t="inlineStr">
         <is>
           <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10464,7 +10449,7 @@
       <c r="D136" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E136" s="95" t="inlineStr">
+      <c r="E136" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10505,7 +10490,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N136" s="69" t="inlineStr">
+      <c r="N136" s="68" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -10522,7 +10507,7 @@
           <t>PS5-60-22</t>
         </is>
       </c>
-      <c r="B137" s="83" t="inlineStr">
+      <c r="B137" s="80" t="inlineStr">
         <is>
           <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
@@ -10533,7 +10518,7 @@
       <c r="D137" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E137" s="70" t="inlineStr">
+      <c r="E137" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10544,7 +10529,7 @@
       <c r="G137" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="H137" s="69" t="inlineStr">
+      <c r="H137" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -10574,7 +10559,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N137" s="69" t="inlineStr">
+      <c r="N137" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -10591,7 +10576,7 @@
           <t>PS5-60-23</t>
         </is>
       </c>
-      <c r="B138" s="83" t="inlineStr">
+      <c r="B138" s="80" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -10602,7 +10587,7 @@
       <c r="D138" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E138" s="70" t="inlineStr">
+      <c r="E138" s="69" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -10660,7 +10645,7 @@
           <t>PS5-60-24</t>
         </is>
       </c>
-      <c r="B139" s="83" t="inlineStr">
+      <c r="B139" s="80" t="inlineStr">
         <is>
           <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
@@ -10671,7 +10656,7 @@
       <c r="D139" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E139" s="70" t="inlineStr">
+      <c r="E139" s="69" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -10729,7 +10714,7 @@
           <t>PS5-60-25</t>
         </is>
       </c>
-      <c r="B140" s="83" t="inlineStr">
+      <c r="B140" s="80" t="inlineStr">
         <is>
           <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
@@ -10740,7 +10725,7 @@
       <c r="D140" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E140" s="70" t="inlineStr">
+      <c r="E140" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -10798,7 +10783,7 @@
           <t>PS5-60-26</t>
         </is>
       </c>
-      <c r="B141" s="83" t="inlineStr">
+      <c r="B141" s="80" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -10809,7 +10794,7 @@
       <c r="D141" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E141" s="70" t="inlineStr">
+      <c r="E141" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -10867,7 +10852,7 @@
           <t>PS5-60-27</t>
         </is>
       </c>
-      <c r="B142" s="83" t="inlineStr">
+      <c r="B142" s="80" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -10878,7 +10863,7 @@
       <c r="D142" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E142" s="70" t="inlineStr">
+      <c r="E142" s="69" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -10936,7 +10921,7 @@
           <t>PS5-60-28</t>
         </is>
       </c>
-      <c r="B143" s="83" t="inlineStr">
+      <c r="B143" s="80" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -10947,7 +10932,7 @@
       <c r="D143" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E143" s="70" t="inlineStr">
+      <c r="E143" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -10993,7 +10978,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O143" s="69" t="inlineStr">
+      <c r="O143" s="68" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -11005,7 +10990,7 @@
           <t>PS5-60-29</t>
         </is>
       </c>
-      <c r="B144" s="83" t="inlineStr">
+      <c r="B144" s="80" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -11016,7 +11001,7 @@
       <c r="D144" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E144" s="70" t="inlineStr">
+      <c r="E144" s="69" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -11074,7 +11059,7 @@
           <t>PS5-60-30</t>
         </is>
       </c>
-      <c r="B145" s="83" t="inlineStr">
+      <c r="B145" s="80" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -11085,7 +11070,7 @@
       <c r="D145" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E145" s="70" t="inlineStr">
+      <c r="E145" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -11143,7 +11128,7 @@
           <t>PS5-60-31</t>
         </is>
       </c>
-      <c r="B146" s="83" t="inlineStr">
+      <c r="B146" s="80" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -11154,7 +11139,7 @@
       <c r="D146" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E146" s="70" t="inlineStr">
+      <c r="E146" s="69" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -11212,7 +11197,7 @@
           <t>PS5-60-32</t>
         </is>
       </c>
-      <c r="B147" s="83" t="inlineStr">
+      <c r="B147" s="80" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -11223,7 +11208,7 @@
       <c r="D147" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E147" s="69" t="inlineStr">
+      <c r="E147" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11281,7 +11266,7 @@
           <t>PS5-60-33</t>
         </is>
       </c>
-      <c r="B148" s="83" t="inlineStr">
+      <c r="B148" s="80" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -11292,7 +11277,7 @@
       <c r="D148" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E148" s="69" t="inlineStr">
+      <c r="E148" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11350,7 +11335,7 @@
           <t>PS5-60-34</t>
         </is>
       </c>
-      <c r="B149" s="83" t="inlineStr">
+      <c r="B149" s="80" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -11361,7 +11346,7 @@
       <c r="D149" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E149" s="70" t="inlineStr">
+      <c r="E149" s="69" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -11419,7 +11404,7 @@
           <t>PS5-60-35</t>
         </is>
       </c>
-      <c r="B150" s="83" t="inlineStr">
+      <c r="B150" s="80" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -11430,7 +11415,7 @@
       <c r="D150" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E150" s="70" t="inlineStr">
+      <c r="E150" s="69" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -11488,7 +11473,7 @@
           <t>PS5-60-36</t>
         </is>
       </c>
-      <c r="B151" s="83" t="inlineStr">
+      <c r="B151" s="80" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -11499,7 +11484,7 @@
       <c r="D151" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E151" s="70" t="inlineStr">
+      <c r="E151" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -11557,7 +11542,7 @@
           <t>PS5-60-37</t>
         </is>
       </c>
-      <c r="B152" s="83" t="inlineStr">
+      <c r="B152" s="80" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -11568,7 +11553,7 @@
       <c r="D152" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E152" s="70" t="inlineStr">
+      <c r="E152" s="69" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -11626,7 +11611,7 @@
           <t>PS5-60-38</t>
         </is>
       </c>
-      <c r="B153" s="83" t="inlineStr">
+      <c r="B153" s="80" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -11637,7 +11622,7 @@
       <c r="D153" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E153" s="69" t="inlineStr">
+      <c r="E153" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11695,7 +11680,7 @@
           <t>PS5-60-39</t>
         </is>
       </c>
-      <c r="B154" s="83" t="inlineStr">
+      <c r="B154" s="80" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -11706,7 +11691,7 @@
       <c r="D154" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E154" s="69" t="inlineStr">
+      <c r="E154" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11764,7 +11749,7 @@
           <t>PS5-60-40</t>
         </is>
       </c>
-      <c r="B155" s="83" t="inlineStr">
+      <c r="B155" s="80" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -11775,7 +11760,7 @@
       <c r="D155" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E155" s="69" t="inlineStr">
+      <c r="E155" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -11833,7 +11818,7 @@
           <t>PS5-60-41</t>
         </is>
       </c>
-      <c r="B156" s="83" t="inlineStr">
+      <c r="B156" s="80" t="inlineStr">
         <is>
           <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
@@ -11844,7 +11829,7 @@
       <c r="D156" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E156" s="69" t="inlineStr">
+      <c r="E156" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -11855,7 +11840,7 @@
       <c r="G156" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="H156" s="69" t="inlineStr">
+      <c r="H156" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -11885,7 +11870,7 @@
           <t>16/17</t>
         </is>
       </c>
-      <c r="N156" s="69" t="inlineStr">
+      <c r="N156" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -11902,7 +11887,7 @@
           <t>PS5-60-42</t>
         </is>
       </c>
-      <c r="B157" s="83" t="inlineStr">
+      <c r="B157" s="80" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -11913,7 +11898,7 @@
       <c r="D157" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E157" s="70" t="inlineStr">
+      <c r="E157" s="69" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -11971,7 +11956,7 @@
           <t>PS5-60-43</t>
         </is>
       </c>
-      <c r="B158" s="83" t="inlineStr">
+      <c r="B158" s="80" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -11982,7 +11967,7 @@
       <c r="D158" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E158" s="70" t="inlineStr">
+      <c r="E158" s="69" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -12040,7 +12025,7 @@
           <t>PS5-60-44</t>
         </is>
       </c>
-      <c r="B159" s="83" t="inlineStr">
+      <c r="B159" s="80" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -12051,7 +12036,7 @@
       <c r="D159" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E159" s="70" t="inlineStr">
+      <c r="E159" s="69" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -12109,7 +12094,7 @@
           <t>PS5-60-45</t>
         </is>
       </c>
-      <c r="B160" s="83" t="inlineStr">
+      <c r="B160" s="80" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -12120,7 +12105,7 @@
       <c r="D160" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E160" s="70" t="inlineStr">
+      <c r="E160" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -12178,7 +12163,7 @@
           <t>PS5-60-46</t>
         </is>
       </c>
-      <c r="B161" s="83" t="inlineStr">
+      <c r="B161" s="80" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -12189,7 +12174,7 @@
       <c r="D161" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E161" s="69" t="inlineStr">
+      <c r="E161" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -12247,7 +12232,7 @@
           <t>PS5-60-47</t>
         </is>
       </c>
-      <c r="B162" s="83" t="inlineStr">
+      <c r="B162" s="80" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -12258,7 +12243,7 @@
       <c r="D162" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E162" s="69" t="inlineStr">
+      <c r="E162" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -12316,7 +12301,7 @@
           <t>PS5-60-48</t>
         </is>
       </c>
-      <c r="B163" s="83" t="inlineStr">
+      <c r="B163" s="80" t="inlineStr">
         <is>
           <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
@@ -12327,7 +12312,7 @@
       <c r="D163" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E163" s="70" t="inlineStr">
+      <c r="E163" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -12385,7 +12370,7 @@
           <t>PS5-60-49</t>
         </is>
       </c>
-      <c r="B164" s="83" t="inlineStr">
+      <c r="B164" s="80" t="inlineStr">
         <is>
           <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
@@ -12396,7 +12381,7 @@
       <c r="D164" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E164" s="70" t="inlineStr">
+      <c r="E164" s="69" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -12454,7 +12439,7 @@
           <t>PS5-60-50</t>
         </is>
       </c>
-      <c r="B165" s="83" t="inlineStr">
+      <c r="B165" s="80" t="inlineStr">
         <is>
           <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
@@ -12465,7 +12450,7 @@
       <c r="D165" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E165" s="70" t="inlineStr">
+      <c r="E165" s="69" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -12523,7 +12508,7 @@
           <t>PS5-60-51</t>
         </is>
       </c>
-      <c r="B166" s="83" t="inlineStr">
+      <c r="B166" s="80" t="inlineStr">
         <is>
           <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
@@ -12534,7 +12519,7 @@
       <c r="D166" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E166" s="69" t="inlineStr">
+      <c r="E166" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -12592,7 +12577,7 @@
           <t>PS5-60-52</t>
         </is>
       </c>
-      <c r="B167" s="83" t="inlineStr">
+      <c r="B167" s="80" t="inlineStr">
         <is>
           <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
@@ -12603,7 +12588,7 @@
       <c r="D167" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E167" s="70" t="inlineStr">
+      <c r="E167" s="69" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -12614,7 +12599,7 @@
       <c r="G167" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="H167" s="69" t="inlineStr">
+      <c r="H167" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -12644,7 +12629,7 @@
           <t>15/15</t>
         </is>
       </c>
-      <c r="N167" s="69" t="inlineStr">
+      <c r="N167" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -12661,7 +12646,7 @@
           <t>PS5-60-53</t>
         </is>
       </c>
-      <c r="B168" s="83" t="inlineStr">
+      <c r="B168" s="80" t="inlineStr">
         <is>
           <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
@@ -12672,7 +12657,7 @@
       <c r="D168" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E168" s="69" t="inlineStr">
+      <c r="E168" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -12730,7 +12715,7 @@
           <t>PS5-60-54</t>
         </is>
       </c>
-      <c r="B169" s="83" t="inlineStr">
+      <c r="B169" s="80" t="inlineStr">
         <is>
           <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
@@ -12741,7 +12726,7 @@
       <c r="D169" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E169" s="69" t="inlineStr">
+      <c r="E169" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -12799,7 +12784,7 @@
           <t>PS5-60-55</t>
         </is>
       </c>
-      <c r="B170" s="83" t="inlineStr">
+      <c r="B170" s="80" t="inlineStr">
         <is>
           <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
@@ -12821,7 +12806,7 @@
       <c r="G170" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="H170" s="69" t="inlineStr">
+      <c r="H170" s="68" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -12851,7 +12836,7 @@
           <t>14/15</t>
         </is>
       </c>
-      <c r="N170" s="69" t="inlineStr">
+      <c r="N170" s="68" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -12868,7 +12853,7 @@
           <t>PS5-60-56</t>
         </is>
       </c>
-      <c r="B171" s="83" t="inlineStr">
+      <c r="B171" s="80" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -12879,7 +12864,7 @@
       <c r="D171" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E171" s="70" t="inlineStr">
+      <c r="E171" s="69" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -12937,7 +12922,7 @@
           <t>PS5-60-57</t>
         </is>
       </c>
-      <c r="B172" s="83" t="inlineStr">
+      <c r="B172" s="80" t="inlineStr">
         <is>
           <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
@@ -12948,7 +12933,7 @@
       <c r="D172" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E172" s="70" t="inlineStr">
+      <c r="E172" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13006,7 +12991,7 @@
           <t>PS5-60-58</t>
         </is>
       </c>
-      <c r="B173" s="83" t="inlineStr">
+      <c r="B173" s="80" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -13017,7 +13002,7 @@
       <c r="D173" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E173" s="70" t="inlineStr">
+      <c r="E173" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -13075,7 +13060,7 @@
           <t>PS5-60-59</t>
         </is>
       </c>
-      <c r="B174" s="83" t="inlineStr">
+      <c r="B174" s="80" t="inlineStr">
         <is>
           <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
@@ -13086,7 +13071,7 @@
       <c r="D174" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E174" s="70" t="inlineStr">
+      <c r="E174" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13144,7 +13129,7 @@
           <t>PS5-60-60</t>
         </is>
       </c>
-      <c r="B175" s="83" t="inlineStr">
+      <c r="B175" s="80" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -13155,7 +13140,7 @@
       <c r="D175" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E175" s="70" t="inlineStr">
+      <c r="E175" s="69" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -13213,7 +13198,7 @@
           <t>PS5-60-61</t>
         </is>
       </c>
-      <c r="B176" s="83" t="inlineStr">
+      <c r="B176" s="80" t="inlineStr">
         <is>
           <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
@@ -13224,7 +13209,7 @@
       <c r="D176" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E176" s="95" t="inlineStr">
+      <c r="E176" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13282,7 +13267,7 @@
           <t>PS5-60-62</t>
         </is>
       </c>
-      <c r="B177" s="83" t="inlineStr">
+      <c r="B177" s="80" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -13293,7 +13278,7 @@
       <c r="D177" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E177" s="70" t="inlineStr">
+      <c r="E177" s="69" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -13351,7 +13336,7 @@
           <t>PS5-60-63</t>
         </is>
       </c>
-      <c r="B178" s="83" t="inlineStr">
+      <c r="B178" s="80" t="inlineStr">
         <is>
           <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
@@ -13362,7 +13347,7 @@
       <c r="D178" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E178" s="95" t="inlineStr">
+      <c r="E178" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13420,7 +13405,7 @@
           <t>PS5-60-64</t>
         </is>
       </c>
-      <c r="B179" s="83" t="inlineStr">
+      <c r="B179" s="80" t="inlineStr">
         <is>
           <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
@@ -13431,7 +13416,7 @@
       <c r="D179" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E179" s="69" t="inlineStr">
+      <c r="E179" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -13489,7 +13474,7 @@
           <t>PS5-60-65</t>
         </is>
       </c>
-      <c r="B180" s="83" t="inlineStr">
+      <c r="B180" s="80" t="inlineStr">
         <is>
           <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
@@ -13500,7 +13485,7 @@
       <c r="D180" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E180" s="95" t="inlineStr">
+      <c r="E180" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13541,7 +13526,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N180" s="69" t="inlineStr">
+      <c r="N180" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13558,7 +13543,7 @@
           <t>PS5-60-66</t>
         </is>
       </c>
-      <c r="B181" s="83" t="inlineStr">
+      <c r="B181" s="80" t="inlineStr">
         <is>
           <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
@@ -13569,7 +13554,7 @@
       <c r="D181" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E181" s="70" t="inlineStr">
+      <c r="E181" s="69" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -13627,7 +13612,7 @@
           <t>PS5-60-67</t>
         </is>
       </c>
-      <c r="B182" s="83" t="inlineStr">
+      <c r="B182" s="80" t="inlineStr">
         <is>
           <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
@@ -13638,7 +13623,7 @@
       <c r="D182" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E182" s="95" t="inlineStr">
+      <c r="E182" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13679,7 +13664,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N182" s="69" t="inlineStr">
+      <c r="N182" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13696,7 +13681,7 @@
           <t>PS5-60-68</t>
         </is>
       </c>
-      <c r="B183" s="83" t="inlineStr">
+      <c r="B183" s="80" t="inlineStr">
         <is>
           <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
@@ -13707,7 +13692,7 @@
       <c r="D183" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E183" s="70" t="inlineStr">
+      <c r="E183" s="69" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -13718,7 +13703,7 @@
       <c r="G183" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H183" s="69" t="inlineStr">
+      <c r="H183" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13748,7 +13733,7 @@
           <t>16/17</t>
         </is>
       </c>
-      <c r="N183" s="69" t="inlineStr">
+      <c r="N183" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13765,7 +13750,7 @@
           <t>PS5-60-69</t>
         </is>
       </c>
-      <c r="B184" s="83" t="inlineStr">
+      <c r="B184" s="80" t="inlineStr">
         <is>
           <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
@@ -13776,7 +13761,7 @@
       <c r="D184" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E184" s="95" t="inlineStr">
+      <c r="E184" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13787,7 +13772,7 @@
       <c r="G184" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="H184" s="69" t="inlineStr">
+      <c r="H184" s="68" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -13817,7 +13802,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N184" s="69" t="inlineStr">
+      <c r="N184" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -13834,7 +13819,7 @@
           <t>PS5-60-70</t>
         </is>
       </c>
-      <c r="B185" s="83" t="inlineStr">
+      <c r="B185" s="80" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -13845,7 +13830,7 @@
       <c r="D185" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="E185" s="70" t="inlineStr">
+      <c r="E185" s="69" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -13903,7 +13888,7 @@
           <t>PS5-60-71</t>
         </is>
       </c>
-      <c r="B186" s="83" t="inlineStr">
+      <c r="B186" s="80" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -13914,7 +13899,7 @@
       <c r="D186" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="E186" s="70" t="inlineStr">
+      <c r="E186" s="69" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
@@ -13972,7 +13957,7 @@
           <t>PS5-60-72</t>
         </is>
       </c>
-      <c r="B187" s="83" t="inlineStr">
+      <c r="B187" s="80" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -13983,7 +13968,7 @@
       <c r="D187" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="E187" s="70" t="inlineStr">
+      <c r="E187" s="69" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
@@ -14041,7 +14026,7 @@
           <t>PS5-60-73</t>
         </is>
       </c>
-      <c r="B188" s="83" t="inlineStr">
+      <c r="B188" s="80" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -14052,7 +14037,7 @@
       <c r="D188" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E188" s="70" t="inlineStr">
+      <c r="E188" s="69" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -14110,7 +14095,7 @@
           <t>PS5-60-74</t>
         </is>
       </c>
-      <c r="B189" s="83" t="inlineStr">
+      <c r="B189" s="80" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -14121,7 +14106,7 @@
       <c r="D189" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E189" s="70" t="inlineStr">
+      <c r="E189" s="69" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -14179,7 +14164,7 @@
           <t>PS5-60-75</t>
         </is>
       </c>
-      <c r="B190" s="83" t="inlineStr">
+      <c r="B190" s="80" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -14190,7 +14175,7 @@
       <c r="D190" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E190" s="70" t="inlineStr">
+      <c r="E190" s="69" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -14248,7 +14233,7 @@
           <t>PS5-60-76</t>
         </is>
       </c>
-      <c r="B191" s="83" t="inlineStr">
+      <c r="B191" s="80" t="inlineStr">
         <is>
           <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
@@ -14259,7 +14244,7 @@
       <c r="D191" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E191" s="70" t="inlineStr">
+      <c r="E191" s="69" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -14317,7 +14302,7 @@
           <t>PS5-61-01</t>
         </is>
       </c>
-      <c r="B192" s="83" t="inlineStr">
+      <c r="B192" s="80" t="inlineStr">
         <is>
           <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
@@ -14328,7 +14313,7 @@
       <c r="D192" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E192" s="70" t="inlineStr">
+      <c r="E192" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -14386,7 +14371,7 @@
           <t>PS5-61-02</t>
         </is>
       </c>
-      <c r="B193" s="83" t="inlineStr">
+      <c r="B193" s="80" t="inlineStr">
         <is>
           <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
@@ -14397,7 +14382,7 @@
       <c r="D193" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E193" s="70" t="inlineStr">
+      <c r="E193" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14438,7 +14423,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N193" s="69" t="inlineStr">
+      <c r="N193" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -14455,7 +14440,7 @@
           <t>PS5-61-03</t>
         </is>
       </c>
-      <c r="B194" s="83" t="inlineStr">
+      <c r="B194" s="80" t="inlineStr">
         <is>
           <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
@@ -14466,7 +14451,7 @@
       <c r="D194" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E194" s="70" t="inlineStr">
+      <c r="E194" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -14507,7 +14492,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N194" s="69" t="inlineStr">
+      <c r="N194" s="68" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -14524,7 +14509,7 @@
           <t>PS5-61-04</t>
         </is>
       </c>
-      <c r="B195" s="83" t="inlineStr">
+      <c r="B195" s="80" t="inlineStr">
         <is>
           <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
@@ -14535,7 +14520,7 @@
       <c r="D195" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E195" s="95" t="inlineStr">
+      <c r="E195" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14546,7 +14531,7 @@
       <c r="G195" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H195" s="70" t="inlineStr">
+      <c r="H195" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14576,7 +14561,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N195" s="70" t="inlineStr">
+      <c r="N195" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14593,7 +14578,7 @@
           <t>PS5-61-05</t>
         </is>
       </c>
-      <c r="B196" s="83" t="inlineStr">
+      <c r="B196" s="80" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -14662,7 +14647,7 @@
           <t>PS5-61-06</t>
         </is>
       </c>
-      <c r="B197" s="83" t="inlineStr">
+      <c r="B197" s="80" t="inlineStr">
         <is>
           <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
@@ -14684,7 +14669,7 @@
       <c r="G197" s="23" t="n">
         <v>63</v>
       </c>
-      <c r="H197" s="69" t="inlineStr">
+      <c r="H197" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -14714,7 +14699,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N197" s="69" t="inlineStr">
+      <c r="N197" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -14731,7 +14716,7 @@
           <t>PS5-61-07</t>
         </is>
       </c>
-      <c r="B198" s="83" t="inlineStr">
+      <c r="B198" s="80" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -14742,7 +14727,7 @@
       <c r="D198" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E198" s="70" t="inlineStr">
+      <c r="E198" s="69" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -14800,7 +14785,7 @@
           <t>PS5-61-08</t>
         </is>
       </c>
-      <c r="B199" s="83" t="inlineStr">
+      <c r="B199" s="80" t="inlineStr">
         <is>
           <t>PS5-61-08 - Electrical Control System</t>
         </is>
@@ -14811,7 +14796,7 @@
       <c r="D199" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E199" s="69" t="inlineStr">
+      <c r="E199" s="68" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -14822,7 +14807,7 @@
       <c r="G199" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H199" s="70" t="inlineStr">
+      <c r="H199" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -14852,7 +14837,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N199" s="70" t="inlineStr">
+      <c r="N199" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -14869,7 +14854,7 @@
           <t>PS5-61-09</t>
         </is>
       </c>
-      <c r="B200" s="83" t="inlineStr">
+      <c r="B200" s="80" t="inlineStr">
         <is>
           <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
@@ -14880,7 +14865,7 @@
       <c r="D200" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E200" s="95" t="inlineStr">
+      <c r="E200" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14891,7 +14876,7 @@
       <c r="G200" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H200" s="70" t="inlineStr">
+      <c r="H200" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -14921,7 +14906,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N200" s="70" t="inlineStr">
+      <c r="N200" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -14938,7 +14923,7 @@
           <t>PS5-61-10</t>
         </is>
       </c>
-      <c r="B201" s="83" t="inlineStr">
+      <c r="B201" s="80" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -14949,7 +14934,7 @@
       <c r="D201" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E201" s="95" t="inlineStr">
+      <c r="E201" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15007,7 +14992,7 @@
           <t>PS5-61-11</t>
         </is>
       </c>
-      <c r="B202" s="83" t="inlineStr">
+      <c r="B202" s="80" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -15018,7 +15003,7 @@
       <c r="D202" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E202" s="95" t="inlineStr">
+      <c r="E202" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15076,7 +15061,7 @@
           <t>PS5-61-12</t>
         </is>
       </c>
-      <c r="B203" s="83" t="inlineStr">
+      <c r="B203" s="80" t="inlineStr">
         <is>
           <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
@@ -15087,7 +15072,7 @@
       <c r="D203" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E203" s="95" t="inlineStr">
+      <c r="E203" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15098,7 +15083,7 @@
       <c r="G203" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H203" s="95" t="inlineStr">
+      <c r="H203" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15128,7 +15113,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N203" s="70" t="inlineStr">
+      <c r="N203" s="69" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -15145,7 +15130,7 @@
           <t>PS5-61-13</t>
         </is>
       </c>
-      <c r="B204" s="83" t="inlineStr">
+      <c r="B204" s="80" t="inlineStr">
         <is>
           <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
@@ -15156,7 +15141,7 @@
       <c r="D204" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E204" s="95" t="inlineStr">
+      <c r="E204" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15167,7 +15152,7 @@
       <c r="G204" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H204" s="70" t="inlineStr">
+      <c r="H204" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15197,7 +15182,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N204" s="70" t="inlineStr">
+      <c r="N204" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15214,7 +15199,7 @@
           <t>PS5-61-14</t>
         </is>
       </c>
-      <c r="B205" s="83" t="inlineStr">
+      <c r="B205" s="80" t="inlineStr">
         <is>
           <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
@@ -15225,7 +15210,7 @@
       <c r="D205" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E205" s="95" t="inlineStr">
+      <c r="E205" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15236,7 +15221,7 @@
       <c r="G205" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H205" s="70" t="inlineStr">
+      <c r="H205" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15266,7 +15251,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N205" s="70" t="inlineStr">
+      <c r="N205" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15283,7 +15268,7 @@
           <t>PS5-62-01</t>
         </is>
       </c>
-      <c r="B206" s="83" t="inlineStr">
+      <c r="B206" s="80" t="inlineStr">
         <is>
           <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
@@ -15305,7 +15290,7 @@
       <c r="G206" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H206" s="70" t="inlineStr">
+      <c r="H206" s="69" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -15335,7 +15320,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N206" s="70" t="inlineStr">
+      <c r="N206" s="69" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -15352,7 +15337,7 @@
           <t>PS5-62-02</t>
         </is>
       </c>
-      <c r="B207" s="83" t="inlineStr">
+      <c r="B207" s="80" t="inlineStr">
         <is>
           <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
@@ -15374,7 +15359,7 @@
       <c r="G207" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H207" s="70" t="inlineStr">
+      <c r="H207" s="69" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -15404,7 +15389,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N207" s="70" t="inlineStr">
+      <c r="N207" s="69" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -15421,7 +15406,7 @@
           <t>PS5-62-03</t>
         </is>
       </c>
-      <c r="B208" s="83" t="inlineStr">
+      <c r="B208" s="80" t="inlineStr">
         <is>
           <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
@@ -15432,7 +15417,7 @@
       <c r="D208" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E208" s="95" t="inlineStr">
+      <c r="E208" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15443,7 +15428,7 @@
       <c r="G208" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H208" s="69" t="inlineStr">
+      <c r="H208" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15473,7 +15458,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N208" s="69" t="inlineStr">
+      <c r="N208" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15490,7 +15475,7 @@
           <t>PS5-62-04</t>
         </is>
       </c>
-      <c r="B209" s="83" t="inlineStr">
+      <c r="B209" s="80" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -15501,7 +15486,7 @@
       <c r="D209" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E209" s="95" t="inlineStr">
+      <c r="E209" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15559,7 +15544,7 @@
           <t>PS5-62-05</t>
         </is>
       </c>
-      <c r="B210" s="83" t="inlineStr">
+      <c r="B210" s="80" t="inlineStr">
         <is>
           <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
@@ -15570,7 +15555,7 @@
       <c r="D210" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E210" s="95" t="inlineStr">
+      <c r="E210" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15581,7 +15566,7 @@
       <c r="G210" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H210" s="70" t="inlineStr">
+      <c r="H210" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15611,7 +15596,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N210" s="70" t="inlineStr">
+      <c r="N210" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15628,7 +15613,7 @@
           <t>PS5-62-06</t>
         </is>
       </c>
-      <c r="B211" s="83" t="inlineStr">
+      <c r="B211" s="80" t="inlineStr">
         <is>
           <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
@@ -15639,7 +15624,7 @@
       <c r="D211" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E211" s="95" t="inlineStr">
+      <c r="E211" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15650,7 +15635,7 @@
       <c r="G211" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H211" s="70" t="inlineStr">
+      <c r="H211" s="69" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -15680,7 +15665,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N211" s="70" t="inlineStr">
+      <c r="N211" s="69" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -15697,7 +15682,7 @@
           <t>PS5-62-07</t>
         </is>
       </c>
-      <c r="B212" s="83" t="inlineStr">
+      <c r="B212" s="80" t="inlineStr">
         <is>
           <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
@@ -15708,7 +15693,7 @@
       <c r="D212" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E212" s="70" t="inlineStr">
+      <c r="E212" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15719,7 +15704,7 @@
       <c r="G212" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H212" s="70" t="inlineStr">
+      <c r="H212" s="69" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -15749,7 +15734,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N212" s="70" t="inlineStr">
+      <c r="N212" s="69" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -15766,7 +15751,7 @@
           <t>PS5-62-08</t>
         </is>
       </c>
-      <c r="B213" s="83" t="inlineStr">
+      <c r="B213" s="80" t="inlineStr">
         <is>
           <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
@@ -15777,7 +15762,7 @@
       <c r="D213" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E213" s="95" t="inlineStr">
+      <c r="E213" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15788,7 +15773,7 @@
       <c r="G213" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H213" s="70" t="inlineStr">
+      <c r="H213" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -15818,7 +15803,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N213" s="70" t="inlineStr">
+      <c r="N213" s="69" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -15835,7 +15820,7 @@
           <t>PS5-62-09</t>
         </is>
       </c>
-      <c r="B214" s="83" t="inlineStr">
+      <c r="B214" s="80" t="inlineStr">
         <is>
           <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
@@ -15846,7 +15831,7 @@
       <c r="D214" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E214" s="70" t="inlineStr">
+      <c r="E214" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15857,7 +15842,7 @@
       <c r="G214" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H214" s="70" t="inlineStr">
+      <c r="H214" s="69" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -15887,7 +15872,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N214" s="70" t="inlineStr">
+      <c r="N214" s="69" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -15904,7 +15889,7 @@
           <t>PS5-62-10</t>
         </is>
       </c>
-      <c r="B215" s="83" t="inlineStr">
+      <c r="B215" s="80" t="inlineStr">
         <is>
           <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
@@ -15915,7 +15900,7 @@
       <c r="D215" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E215" s="70" t="inlineStr">
+      <c r="E215" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15926,7 +15911,7 @@
       <c r="G215" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="H215" s="70" t="inlineStr">
+      <c r="H215" s="69" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -15956,7 +15941,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N215" s="70" t="inlineStr">
+      <c r="N215" s="69" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -15973,7 +15958,7 @@
           <t>PS5-62-11</t>
         </is>
       </c>
-      <c r="B216" s="83" t="inlineStr">
+      <c r="B216" s="80" t="inlineStr">
         <is>
           <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
@@ -15984,7 +15969,7 @@
       <c r="D216" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E216" s="95" t="inlineStr">
+      <c r="E216" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15995,7 +15980,7 @@
       <c r="G216" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H216" s="70" t="inlineStr">
+      <c r="H216" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -16025,7 +16010,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N216" s="70" t="inlineStr">
+      <c r="N216" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -16042,7 +16027,7 @@
           <t>PS5-62-12</t>
         </is>
       </c>
-      <c r="B217" s="83" t="inlineStr">
+      <c r="B217" s="80" t="inlineStr">
         <is>
           <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
@@ -16053,7 +16038,7 @@
       <c r="D217" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E217" s="95" t="inlineStr">
+      <c r="E217" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16064,7 +16049,7 @@
       <c r="G217" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H217" s="95" t="inlineStr">
+      <c r="H217" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16111,7 +16096,7 @@
           <t>PS5-62-13</t>
         </is>
       </c>
-      <c r="B218" s="83" t="inlineStr">
+      <c r="B218" s="80" t="inlineStr">
         <is>
           <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
@@ -16122,7 +16107,7 @@
       <c r="D218" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E218" s="70" t="inlineStr">
+      <c r="E218" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16133,7 +16118,7 @@
       <c r="G218" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H218" s="95" t="inlineStr">
+      <c r="H218" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16180,7 +16165,7 @@
           <t>PS5-62-14</t>
         </is>
       </c>
-      <c r="B219" s="83" t="inlineStr">
+      <c r="B219" s="80" t="inlineStr">
         <is>
           <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
@@ -16191,7 +16176,7 @@
       <c r="D219" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E219" s="95" t="inlineStr">
+      <c r="E219" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16202,7 +16187,7 @@
       <c r="G219" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H219" s="70" t="inlineStr">
+      <c r="H219" s="69" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16232,7 +16217,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N219" s="70" t="inlineStr">
+      <c r="N219" s="69" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16249,7 +16234,7 @@
           <t>PS5-62-15</t>
         </is>
       </c>
-      <c r="B220" s="83" t="inlineStr">
+      <c r="B220" s="80" t="inlineStr">
         <is>
           <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
@@ -16260,7 +16245,7 @@
       <c r="D220" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E220" s="95" t="inlineStr">
+      <c r="E220" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16271,7 +16256,7 @@
       <c r="G220" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H220" s="70" t="inlineStr">
+      <c r="H220" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16301,7 +16286,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N220" s="70" t="inlineStr">
+      <c r="N220" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16318,7 +16303,7 @@
           <t>PS5-62-16</t>
         </is>
       </c>
-      <c r="B221" s="83" t="inlineStr">
+      <c r="B221" s="80" t="inlineStr">
         <is>
           <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
@@ -16329,7 +16314,7 @@
       <c r="D221" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E221" s="95" t="inlineStr">
+      <c r="E221" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16340,7 +16325,7 @@
       <c r="G221" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H221" s="70" t="inlineStr">
+      <c r="H221" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16370,7 +16355,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N221" s="70" t="inlineStr">
+      <c r="N221" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16387,7 +16372,7 @@
           <t>PS5-62-17</t>
         </is>
       </c>
-      <c r="B222" s="83" t="inlineStr">
+      <c r="B222" s="80" t="inlineStr">
         <is>
           <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
@@ -16398,7 +16383,7 @@
       <c r="D222" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E222" s="95" t="inlineStr">
+      <c r="E222" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16409,7 +16394,7 @@
       <c r="G222" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H222" s="70" t="inlineStr">
+      <c r="H222" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16439,7 +16424,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N222" s="70" t="inlineStr">
+      <c r="N222" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16456,7 +16441,7 @@
           <t>PS5-62-18</t>
         </is>
       </c>
-      <c r="B223" s="83" t="inlineStr">
+      <c r="B223" s="80" t="inlineStr">
         <is>
           <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
@@ -16467,7 +16452,7 @@
       <c r="D223" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E223" s="95" t="inlineStr">
+      <c r="E223" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16478,7 +16463,7 @@
       <c r="G223" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H223" s="70" t="inlineStr">
+      <c r="H223" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16508,7 +16493,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N223" s="70" t="inlineStr">
+      <c r="N223" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16525,7 +16510,7 @@
           <t>PS5-62-19</t>
         </is>
       </c>
-      <c r="B224" s="83" t="inlineStr">
+      <c r="B224" s="80" t="inlineStr">
         <is>
           <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
@@ -16536,7 +16521,7 @@
       <c r="D224" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E224" s="95" t="inlineStr">
+      <c r="E224" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16547,7 +16532,7 @@
       <c r="G224" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H224" s="70" t="inlineStr">
+      <c r="H224" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16577,7 +16562,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N224" s="70" t="inlineStr">
+      <c r="N224" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16594,7 +16579,7 @@
           <t>PS5-62-20</t>
         </is>
       </c>
-      <c r="B225" s="83" t="inlineStr">
+      <c r="B225" s="80" t="inlineStr">
         <is>
           <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
@@ -16605,7 +16590,7 @@
       <c r="D225" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E225" s="95" t="inlineStr">
+      <c r="E225" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16616,7 +16601,7 @@
       <c r="G225" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H225" s="70" t="inlineStr">
+      <c r="H225" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16646,7 +16631,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N225" s="70" t="inlineStr">
+      <c r="N225" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16663,7 +16648,7 @@
           <t>PS5-63-01</t>
         </is>
       </c>
-      <c r="B226" s="83" t="inlineStr">
+      <c r="B226" s="80" t="inlineStr">
         <is>
           <t>PS5-63-01 - Electrical Earthing</t>
         </is>
@@ -16674,7 +16659,7 @@
       <c r="D226" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E226" s="70" t="inlineStr">
+      <c r="E226" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16685,7 +16670,7 @@
       <c r="G226" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="H226" s="70" t="inlineStr">
+      <c r="H226" s="69" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -16715,7 +16700,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N226" s="70" t="inlineStr">
+      <c r="N226" s="69" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -16732,7 +16717,7 @@
           <t>PS5-63-02</t>
         </is>
       </c>
-      <c r="B227" s="83" t="inlineStr">
+      <c r="B227" s="80" t="inlineStr">
         <is>
           <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
@@ -16743,7 +16728,7 @@
       <c r="D227" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E227" s="95" t="inlineStr">
+      <c r="E227" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16754,7 +16739,7 @@
       <c r="G227" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H227" s="70" t="inlineStr">
+      <c r="H227" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16784,7 +16769,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N227" s="70" t="inlineStr">
+      <c r="N227" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16801,7 +16786,7 @@
           <t>PS5-63-03</t>
         </is>
       </c>
-      <c r="B228" s="83" t="inlineStr">
+      <c r="B228" s="80" t="inlineStr">
         <is>
           <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
@@ -16812,7 +16797,7 @@
       <c r="D228" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E228" s="95" t="inlineStr">
+      <c r="E228" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16823,7 +16808,7 @@
       <c r="G228" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H228" s="69" t="inlineStr">
+      <c r="H228" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16853,7 +16838,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N228" s="69" t="inlineStr">
+      <c r="N228" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16870,7 +16855,7 @@
           <t>PS5-63-04</t>
         </is>
       </c>
-      <c r="B229" s="83" t="inlineStr">
+      <c r="B229" s="80" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -16881,7 +16866,7 @@
       <c r="D229" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E229" s="70" t="inlineStr">
+      <c r="E229" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -16892,7 +16877,7 @@
       <c r="G229" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H229" s="95" t="inlineStr">
+      <c r="H229" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16939,7 +16924,7 @@
           <t>PS5-63-05</t>
         </is>
       </c>
-      <c r="B230" s="83" t="inlineStr">
+      <c r="B230" s="80" t="inlineStr">
         <is>
           <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
@@ -16950,7 +16935,7 @@
       <c r="D230" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E230" s="95" t="inlineStr">
+      <c r="E230" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16961,7 +16946,7 @@
       <c r="G230" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H230" s="70" t="inlineStr">
+      <c r="H230" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16991,7 +16976,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N230" s="70" t="inlineStr">
+      <c r="N230" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17008,7 +16993,7 @@
           <t>PS5-63-06</t>
         </is>
       </c>
-      <c r="B231" s="83" t="inlineStr">
+      <c r="B231" s="80" t="inlineStr">
         <is>
           <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
@@ -17019,7 +17004,7 @@
       <c r="D231" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E231" s="95" t="inlineStr">
+      <c r="E231" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17030,7 +17015,7 @@
       <c r="G231" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H231" s="70" t="inlineStr">
+      <c r="H231" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17060,7 +17045,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N231" s="70" t="inlineStr">
+      <c r="N231" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17077,7 +17062,7 @@
           <t>PS5-63-07</t>
         </is>
       </c>
-      <c r="B232" s="83" t="inlineStr">
+      <c r="B232" s="80" t="inlineStr">
         <is>
           <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
@@ -17088,7 +17073,7 @@
       <c r="D232" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E232" s="95" t="inlineStr">
+      <c r="E232" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17099,7 +17084,7 @@
       <c r="G232" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H232" s="70" t="inlineStr">
+      <c r="H232" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17129,7 +17114,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N232" s="70" t="inlineStr">
+      <c r="N232" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17146,7 +17131,7 @@
           <t>PS5-71-01</t>
         </is>
       </c>
-      <c r="B233" s="83" t="inlineStr">
+      <c r="B233" s="80" t="inlineStr">
         <is>
           <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
@@ -17157,7 +17142,7 @@
       <c r="D233" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E233" s="70" t="inlineStr">
+      <c r="E233" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -17168,7 +17153,7 @@
       <c r="G233" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="H233" s="70" t="inlineStr">
+      <c r="H233" s="69" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -17198,7 +17183,7 @@
           <t>27/30</t>
         </is>
       </c>
-      <c r="N233" s="70" t="inlineStr">
+      <c r="N233" s="69" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -17215,7 +17200,7 @@
           <t>PS5-71-02</t>
         </is>
       </c>
-      <c r="B234" s="83" t="inlineStr">
+      <c r="B234" s="80" t="inlineStr">
         <is>
           <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
@@ -17226,7 +17211,7 @@
       <c r="D234" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E234" s="70" t="inlineStr">
+      <c r="E234" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -17237,7 +17222,7 @@
       <c r="G234" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H234" s="69" t="inlineStr">
+      <c r="H234" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -17267,7 +17252,7 @@
           <t>9/10</t>
         </is>
       </c>
-      <c r="N234" s="69" t="inlineStr">
+      <c r="N234" s="68" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -17284,7 +17269,7 @@
           <t>PS5-71-03</t>
         </is>
       </c>
-      <c r="B235" s="83" t="inlineStr">
+      <c r="B235" s="80" t="inlineStr">
         <is>
           <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
@@ -17295,7 +17280,7 @@
       <c r="D235" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E235" s="95" t="inlineStr">
+      <c r="E235" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17306,7 +17291,7 @@
       <c r="G235" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H235" s="95" t="inlineStr">
+      <c r="H235" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17336,7 +17321,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N235" s="70" t="inlineStr">
+      <c r="N235" s="69" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -17353,7 +17338,7 @@
           <t>PS5-71-04</t>
         </is>
       </c>
-      <c r="B236" s="83" t="inlineStr">
+      <c r="B236" s="80" t="inlineStr">
         <is>
           <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
@@ -17364,7 +17349,7 @@
       <c r="D236" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E236" s="69" t="inlineStr">
+      <c r="E236" s="68" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -17375,7 +17360,7 @@
       <c r="G236" s="23" t="n">
         <v>66</v>
       </c>
-      <c r="H236" s="69" t="inlineStr">
+      <c r="H236" s="68" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -17405,7 +17390,7 @@
           <t>42/47</t>
         </is>
       </c>
-      <c r="N236" s="69" t="inlineStr">
+      <c r="N236" s="68" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -17422,7 +17407,7 @@
           <t>PS5-71-05</t>
         </is>
       </c>
-      <c r="B237" s="83" t="inlineStr">
+      <c r="B237" s="80" t="inlineStr">
         <is>
           <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
@@ -17433,7 +17418,7 @@
       <c r="D237" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E237" s="70" t="inlineStr">
+      <c r="E237" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -17444,7 +17429,7 @@
       <c r="G237" s="23" t="n">
         <v>48</v>
       </c>
-      <c r="H237" s="69" t="inlineStr">
+      <c r="H237" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -17474,7 +17459,7 @@
           <t>13/14</t>
         </is>
       </c>
-      <c r="N237" s="69" t="inlineStr">
+      <c r="N237" s="68" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -17491,7 +17476,7 @@
           <t>PS5-71-06</t>
         </is>
       </c>
-      <c r="B238" s="83" t="inlineStr">
+      <c r="B238" s="80" t="inlineStr">
         <is>
           <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
@@ -17502,7 +17487,7 @@
       <c r="D238" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E238" s="69" t="inlineStr">
+      <c r="E238" s="68" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -17513,7 +17498,7 @@
       <c r="G238" s="23" t="n">
         <v>36</v>
       </c>
-      <c r="H238" s="69" t="inlineStr">
+      <c r="H238" s="68" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -17543,7 +17528,7 @@
           <t>21/22</t>
         </is>
       </c>
-      <c r="N238" s="69" t="inlineStr">
+      <c r="N238" s="68" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -17560,7 +17545,7 @@
           <t>PS5-71-07</t>
         </is>
       </c>
-      <c r="B239" s="83" t="inlineStr">
+      <c r="B239" s="80" t="inlineStr">
         <is>
           <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
@@ -17571,7 +17556,7 @@
       <c r="D239" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E239" s="70" t="inlineStr">
+      <c r="E239" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17582,7 +17567,7 @@
       <c r="G239" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H239" s="69" t="inlineStr">
+      <c r="H239" s="68" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17612,7 +17597,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N239" s="69" t="inlineStr">
+      <c r="N239" s="68" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17629,7 +17614,7 @@
           <t>PS5-71-08</t>
         </is>
       </c>
-      <c r="B240" s="83" t="inlineStr">
+      <c r="B240" s="80" t="inlineStr">
         <is>
           <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
@@ -17640,7 +17625,7 @@
       <c r="D240" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E240" s="70" t="inlineStr">
+      <c r="E240" s="69" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -17698,7 +17683,7 @@
           <t>PS5-71-09</t>
         </is>
       </c>
-      <c r="B241" s="83" t="inlineStr">
+      <c r="B241" s="80" t="inlineStr">
         <is>
           <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
@@ -17709,7 +17694,7 @@
       <c r="D241" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E241" s="70" t="inlineStr">
+      <c r="E241" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17767,7 +17752,7 @@
           <t>PS5-71-12</t>
         </is>
       </c>
-      <c r="B242" s="83" t="inlineStr">
+      <c r="B242" s="80" t="inlineStr">
         <is>
           <t>PS5-71-12 - CFO Service Tank</t>
         </is>
@@ -17778,7 +17763,7 @@
       <c r="D242" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="E242" s="69" t="inlineStr">
+      <c r="E242" s="68" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -17789,7 +17774,7 @@
       <c r="G242" s="23" t="n">
         <v>66</v>
       </c>
-      <c r="H242" s="69" t="inlineStr">
+      <c r="H242" s="68" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17819,7 +17804,7 @@
           <t>26/31</t>
         </is>
       </c>
-      <c r="N242" s="69" t="inlineStr">
+      <c r="N242" s="68" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17836,7 +17821,7 @@
           <t>PS5-71-13</t>
         </is>
       </c>
-      <c r="B243" s="83" t="inlineStr">
+      <c r="B243" s="80" t="inlineStr">
         <is>
           <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
@@ -17847,7 +17832,7 @@
       <c r="D243" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E243" s="70" t="inlineStr">
+      <c r="E243" s="69" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -17858,7 +17843,7 @@
       <c r="G243" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="H243" s="69" t="inlineStr">
+      <c r="H243" s="68" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -17888,7 +17873,7 @@
           <t>12/14</t>
         </is>
       </c>
-      <c r="N243" s="69" t="inlineStr">
+      <c r="N243" s="68" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -17905,7 +17890,7 @@
           <t>PS5-71-14</t>
         </is>
       </c>
-      <c r="B244" s="83" t="inlineStr">
+      <c r="B244" s="80" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
@@ -17916,7 +17901,7 @@
       <c r="D244" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E244" s="70" t="inlineStr">
+      <c r="E244" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -17957,7 +17942,7 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N244" s="69" t="inlineStr">
+      <c r="N244" s="68" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -17974,7 +17959,7 @@
           <t>PS5-71-15</t>
         </is>
       </c>
-      <c r="B245" s="83" t="inlineStr">
+      <c r="B245" s="80" t="inlineStr">
         <is>
           <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
@@ -17985,7 +17970,7 @@
       <c r="D245" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E245" s="70" t="inlineStr">
+      <c r="E245" s="69" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
@@ -17996,7 +17981,7 @@
       <c r="G245" s="23" t="n">
         <v>41</v>
       </c>
-      <c r="H245" s="69" t="inlineStr">
+      <c r="H245" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -18026,7 +18011,7 @@
           <t>17/20</t>
         </is>
       </c>
-      <c r="N245" s="69" t="inlineStr">
+      <c r="N245" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -18043,7 +18028,7 @@
           <t>PS5-71-16</t>
         </is>
       </c>
-      <c r="B246" s="83" t="inlineStr">
+      <c r="B246" s="80" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
@@ -18054,7 +18039,7 @@
       <c r="D246" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E246" s="70" t="inlineStr">
+      <c r="E246" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18095,7 +18080,7 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N246" s="69" t="inlineStr">
+      <c r="N246" s="68" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -18112,7 +18097,7 @@
           <t>PS5-71-17</t>
         </is>
       </c>
-      <c r="B247" s="83" t="inlineStr">
+      <c r="B247" s="80" t="inlineStr">
         <is>
           <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
@@ -18123,7 +18108,7 @@
       <c r="D247" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E247" s="70" t="inlineStr">
+      <c r="E247" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18181,7 +18166,7 @@
           <t>PS5-71-18</t>
         </is>
       </c>
-      <c r="B248" s="83" t="inlineStr">
+      <c r="B248" s="80" t="inlineStr">
         <is>
           <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
@@ -18192,7 +18177,7 @@
       <c r="D248" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E248" s="69" t="inlineStr">
+      <c r="E248" s="68" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
@@ -18203,7 +18188,7 @@
       <c r="G248" s="23" t="n">
         <v>47</v>
       </c>
-      <c r="H248" s="69" t="inlineStr">
+      <c r="H248" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18233,7 +18218,7 @@
           <t>20/20</t>
         </is>
       </c>
-      <c r="N248" s="69" t="inlineStr">
+      <c r="N248" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18250,7 +18235,7 @@
           <t>PS5-71-19</t>
         </is>
       </c>
-      <c r="B249" s="83" t="inlineStr">
+      <c r="B249" s="80" t="inlineStr">
         <is>
           <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
@@ -18261,7 +18246,7 @@
       <c r="D249" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E249" s="70" t="inlineStr">
+      <c r="E249" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18272,7 +18257,7 @@
       <c r="G249" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="H249" s="69" t="inlineStr">
+      <c r="H249" s="68" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -18302,7 +18287,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N249" s="69" t="inlineStr">
+      <c r="N249" s="68" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -18319,7 +18304,7 @@
           <t>PS5-71-20</t>
         </is>
       </c>
-      <c r="B250" s="83" t="inlineStr">
+      <c r="B250" s="80" t="inlineStr">
         <is>
           <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
@@ -18330,7 +18315,7 @@
       <c r="D250" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E250" s="69" t="inlineStr">
+      <c r="E250" s="68" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -18341,7 +18326,7 @@
       <c r="G250" s="23" t="n">
         <v>49</v>
       </c>
-      <c r="H250" s="69" t="inlineStr">
+      <c r="H250" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18371,7 +18356,7 @@
           <t>20/20</t>
         </is>
       </c>
-      <c r="N250" s="69" t="inlineStr">
+      <c r="N250" s="68" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18388,7 +18373,7 @@
           <t>PS5-71-21</t>
         </is>
       </c>
-      <c r="B251" s="83" t="inlineStr">
+      <c r="B251" s="80" t="inlineStr">
         <is>
           <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
@@ -18399,7 +18384,7 @@
       <c r="D251" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E251" s="70" t="inlineStr">
+      <c r="E251" s="69" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -18457,7 +18442,7 @@
           <t>PS5-71-22</t>
         </is>
       </c>
-      <c r="B252" s="83" t="inlineStr">
+      <c r="B252" s="80" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -18468,7 +18453,7 @@
       <c r="D252" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="E252" s="70" t="inlineStr">
+      <c r="E252" s="69" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -18526,7 +18511,7 @@
           <t>PS5-71-23</t>
         </is>
       </c>
-      <c r="B253" s="83" t="inlineStr">
+      <c r="B253" s="80" t="inlineStr">
         <is>
           <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
@@ -18537,7 +18522,7 @@
       <c r="D253" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E253" s="70" t="inlineStr">
+      <c r="E253" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -18548,7 +18533,7 @@
       <c r="G253" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H253" s="69" t="inlineStr">
+      <c r="H253" s="68" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -18578,7 +18563,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N253" s="69" t="inlineStr">
+      <c r="N253" s="68" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -18595,7 +18580,7 @@
           <t>PS5-74-01</t>
         </is>
       </c>
-      <c r="B254" s="83" t="inlineStr">
+      <c r="B254" s="80" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
@@ -18606,7 +18591,7 @@
       <c r="D254" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E254" s="70" t="inlineStr">
+      <c r="E254" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -18617,7 +18602,7 @@
       <c r="G254" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H254" s="69" t="inlineStr">
+      <c r="H254" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -18647,7 +18632,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="N254" s="69" t="inlineStr">
+      <c r="N254" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -18664,7 +18649,7 @@
           <t>PS5-74-02</t>
         </is>
       </c>
-      <c r="B255" s="83" t="inlineStr">
+      <c r="B255" s="80" t="inlineStr">
         <is>
           <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
@@ -18686,7 +18671,7 @@
       <c r="G255" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H255" s="69" t="inlineStr">
+      <c r="H255" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -18716,7 +18701,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N255" s="69" t="inlineStr">
+      <c r="N255" s="68" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -18733,7 +18718,7 @@
           <t>PS5-74-03</t>
         </is>
       </c>
-      <c r="B256" s="83" t="inlineStr">
+      <c r="B256" s="80" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -18744,7 +18729,7 @@
       <c r="D256" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E256" s="70" t="inlineStr">
+      <c r="E256" s="69" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -18802,7 +18787,7 @@
           <t>PS5-74-04</t>
         </is>
       </c>
-      <c r="B257" s="83" t="inlineStr">
+      <c r="B257" s="80" t="inlineStr">
         <is>
           <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
@@ -18813,7 +18798,7 @@
       <c r="D257" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E257" s="95" t="inlineStr">
+      <c r="E257" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18824,7 +18809,7 @@
       <c r="G257" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="H257" s="69" t="inlineStr">
+      <c r="H257" s="68" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -18854,7 +18839,7 @@
           <t>6/8</t>
         </is>
       </c>
-      <c r="N257" s="69" t="inlineStr">
+      <c r="N257" s="68" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
@@ -18871,7 +18856,7 @@
           <t>PS5-75-01</t>
         </is>
       </c>
-      <c r="B258" s="83" t="inlineStr">
+      <c r="B258" s="80" t="inlineStr">
         <is>
           <t>PS5-75-01 - DRA Injection Package</t>
         </is>
@@ -18882,7 +18867,7 @@
       <c r="D258" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E258" s="95" t="inlineStr">
+      <c r="E258" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18893,7 +18878,7 @@
       <c r="G258" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H258" s="70" t="inlineStr">
+      <c r="H258" s="69" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -18923,7 +18908,7 @@
           <t>12/15</t>
         </is>
       </c>
-      <c r="N258" s="70" t="inlineStr">
+      <c r="N258" s="69" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -18940,7 +18925,7 @@
           <t>PS5-75-02</t>
         </is>
       </c>
-      <c r="B259" s="83" t="inlineStr">
+      <c r="B259" s="80" t="inlineStr">
         <is>
           <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
@@ -18951,7 +18936,7 @@
       <c r="D259" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E259" s="70" t="inlineStr">
+      <c r="E259" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -18962,7 +18947,7 @@
       <c r="G259" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H259" s="69" t="inlineStr">
+      <c r="H259" s="68" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -18992,7 +18977,7 @@
           <t>13/14</t>
         </is>
       </c>
-      <c r="N259" s="69" t="inlineStr">
+      <c r="N259" s="68" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -19009,7 +18994,7 @@
           <t>PS5-75-03</t>
         </is>
       </c>
-      <c r="B260" s="83" t="inlineStr">
+      <c r="B260" s="80" t="inlineStr">
         <is>
           <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
@@ -19020,7 +19005,7 @@
       <c r="D260" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E260" s="70" t="inlineStr">
+      <c r="E260" s="69" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
@@ -19031,7 +19016,7 @@
       <c r="G260" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H260" s="69" t="inlineStr">
+      <c r="H260" s="68" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -19061,7 +19046,7 @@
           <t>12/15</t>
         </is>
       </c>
-      <c r="N260" s="69" t="inlineStr">
+      <c r="N260" s="68" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -19078,7 +19063,7 @@
           <t>PS5-78-01</t>
         </is>
       </c>
-      <c r="B261" s="83" t="inlineStr">
+      <c r="B261" s="80" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -19089,7 +19074,7 @@
       <c r="D261" s="23" t="n">
         <v>71</v>
       </c>
-      <c r="E261" s="69" t="inlineStr">
+      <c r="E261" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -19100,7 +19085,7 @@
       <c r="G261" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H261" s="69" t="inlineStr">
+      <c r="H261" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -19130,12 +19115,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N261" s="69" t="inlineStr">
+      <c r="N261" s="68" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
       </c>
-      <c r="O261" s="69" t="inlineStr">
+      <c r="O261" s="68" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -19147,7 +19132,7 @@
           <t>PS5-79-01</t>
         </is>
       </c>
-      <c r="B262" s="83" t="inlineStr">
+      <c r="B262" s="80" t="inlineStr">
         <is>
           <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
@@ -19158,7 +19143,7 @@
       <c r="D262" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E262" s="95" t="inlineStr">
+      <c r="E262" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19169,7 +19154,7 @@
       <c r="G262" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H262" s="70" t="inlineStr">
+      <c r="H262" s="69" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -19199,7 +19184,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N262" s="70" t="inlineStr">
+      <c r="N262" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19216,7 +19201,7 @@
           <t>PS5-79-02</t>
         </is>
       </c>
-      <c r="B263" s="83" t="inlineStr">
+      <c r="B263" s="80" t="inlineStr">
         <is>
           <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
@@ -19227,7 +19212,7 @@
       <c r="D263" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E263" s="95" t="inlineStr">
+      <c r="E263" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19238,7 +19223,7 @@
       <c r="G263" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H263" s="70" t="inlineStr">
+      <c r="H263" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19268,7 +19253,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N263" s="70" t="inlineStr">
+      <c r="N263" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -19285,7 +19270,7 @@
           <t>PS5-79-03</t>
         </is>
       </c>
-      <c r="B264" s="83" t="inlineStr">
+      <c r="B264" s="80" t="inlineStr">
         <is>
           <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
@@ -19296,7 +19281,7 @@
       <c r="D264" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E264" s="95" t="inlineStr">
+      <c r="E264" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19307,7 +19292,7 @@
       <c r="G264" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H264" s="70" t="inlineStr">
+      <c r="H264" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19337,7 +19322,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N264" s="70" t="inlineStr">
+      <c r="N264" s="69" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19354,7 +19339,7 @@
           <t>PS5-79-04</t>
         </is>
       </c>
-      <c r="B265" s="83" t="inlineStr">
+      <c r="B265" s="80" t="inlineStr">
         <is>
           <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
@@ -19365,7 +19350,7 @@
       <c r="D265" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E265" s="95" t="inlineStr">
+      <c r="E265" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19376,7 +19361,7 @@
       <c r="G265" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H265" s="70" t="inlineStr">
+      <c r="H265" s="69" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19406,7 +19391,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N265" s="70" t="inlineStr">
+      <c r="N265" s="69" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19423,7 +19408,7 @@
           <t>PS5-79-05</t>
         </is>
       </c>
-      <c r="B266" s="83" t="inlineStr">
+      <c r="B266" s="80" t="inlineStr">
         <is>
           <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
@@ -19434,7 +19419,7 @@
       <c r="D266" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E266" s="95" t="inlineStr">
+      <c r="E266" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19445,7 +19430,7 @@
       <c r="G266" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H266" s="70" t="inlineStr">
+      <c r="H266" s="69" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -19475,7 +19460,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N266" s="70" t="inlineStr">
+      <c r="N266" s="69" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -19492,7 +19477,7 @@
           <t>PS5-79-06</t>
         </is>
       </c>
-      <c r="B267" s="83" t="inlineStr">
+      <c r="B267" s="80" t="inlineStr">
         <is>
           <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
@@ -19503,7 +19488,7 @@
       <c r="D267" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E267" s="95" t="inlineStr">
+      <c r="E267" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19514,7 +19499,7 @@
       <c r="G267" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H267" s="70" t="inlineStr">
+      <c r="H267" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -19544,7 +19529,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N267" s="70" t="inlineStr">
+      <c r="N267" s="69" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -19561,7 +19546,7 @@
           <t>PS5-79-07</t>
         </is>
       </c>
-      <c r="B268" s="83" t="inlineStr">
+      <c r="B268" s="80" t="inlineStr">
         <is>
           <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
@@ -19572,7 +19557,7 @@
       <c r="D268" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E268" s="95" t="inlineStr">
+      <c r="E268" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19583,7 +19568,7 @@
       <c r="G268" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H268" s="70" t="inlineStr">
+      <c r="H268" s="69" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -19613,7 +19598,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N268" s="70" t="inlineStr">
+      <c r="N268" s="69" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -19630,7 +19615,7 @@
           <t>PS5-79-08</t>
         </is>
       </c>
-      <c r="B269" s="83" t="inlineStr">
+      <c r="B269" s="80" t="inlineStr">
         <is>
           <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
@@ -19641,7 +19626,7 @@
       <c r="D269" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E269" s="95" t="inlineStr">
+      <c r="E269" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19652,7 +19637,7 @@
       <c r="G269" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H269" s="70" t="inlineStr">
+      <c r="H269" s="69" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -19682,7 +19667,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N269" s="70" t="inlineStr">
+      <c r="N269" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -19699,7 +19684,7 @@
           <t>PS5-79-09</t>
         </is>
       </c>
-      <c r="B270" s="83" t="inlineStr">
+      <c r="B270" s="80" t="inlineStr">
         <is>
           <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
@@ -19710,7 +19695,7 @@
       <c r="D270" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E270" s="95" t="inlineStr">
+      <c r="E270" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19721,7 +19706,7 @@
       <c r="G270" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H270" s="70" t="inlineStr">
+      <c r="H270" s="69" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -19751,7 +19736,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N270" s="70" t="inlineStr">
+      <c r="N270" s="69" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -19768,7 +19753,7 @@
           <t>PS5-79-10</t>
         </is>
       </c>
-      <c r="B271" s="83" t="inlineStr">
+      <c r="B271" s="80" t="inlineStr">
         <is>
           <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
@@ -19779,7 +19764,7 @@
       <c r="D271" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E271" s="95" t="inlineStr">
+      <c r="E271" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19790,7 +19775,7 @@
       <c r="G271" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="H271" s="70" t="inlineStr">
+      <c r="H271" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -19820,7 +19805,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N271" s="70" t="inlineStr">
+      <c r="N271" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -19837,7 +19822,7 @@
           <t>PS5-79-11</t>
         </is>
       </c>
-      <c r="B272" s="83" t="inlineStr">
+      <c r="B272" s="80" t="inlineStr">
         <is>
           <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
@@ -19848,7 +19833,7 @@
       <c r="D272" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E272" s="95" t="inlineStr">
+      <c r="E272" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19859,7 +19844,7 @@
       <c r="G272" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H272" s="70" t="inlineStr">
+      <c r="H272" s="69" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -19889,7 +19874,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N272" s="70" t="inlineStr">
+      <c r="N272" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -19906,7 +19891,7 @@
           <t>PS5-79-12</t>
         </is>
       </c>
-      <c r="B273" s="83" t="inlineStr">
+      <c r="B273" s="80" t="inlineStr">
         <is>
           <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
@@ -19917,7 +19902,7 @@
       <c r="D273" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E273" s="95" t="inlineStr">
+      <c r="E273" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19928,7 +19913,7 @@
       <c r="G273" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="H273" s="70" t="inlineStr">
+      <c r="H273" s="69" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19958,7 +19943,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N273" s="70" t="inlineStr">
+      <c r="N273" s="69" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19975,7 +19960,7 @@
           <t>PS5-82-01</t>
         </is>
       </c>
-      <c r="B274" s="83" t="inlineStr">
+      <c r="B274" s="80" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
@@ -19986,7 +19971,7 @@
       <c r="D274" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E274" s="95" t="inlineStr">
+      <c r="E274" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19997,7 +19982,7 @@
       <c r="G274" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="H274" s="69" t="inlineStr">
+      <c r="H274" s="68" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -20027,7 +20012,7 @@
           <t>30/50</t>
         </is>
       </c>
-      <c r="N274" s="69" t="inlineStr">
+      <c r="N274" s="68" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -20044,7 +20029,7 @@
           <t>PS5-82-02</t>
         </is>
       </c>
-      <c r="B275" s="83" t="inlineStr">
+      <c r="B275" s="80" t="inlineStr">
         <is>
           <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
@@ -20055,7 +20040,7 @@
       <c r="D275" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E275" s="70" t="inlineStr">
+      <c r="E275" s="69" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
@@ -20066,7 +20051,7 @@
       <c r="G275" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H275" s="70" t="inlineStr">
+      <c r="H275" s="69" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -20096,7 +20081,7 @@
           <t>0/1</t>
         </is>
       </c>
-      <c r="N275" s="70" t="inlineStr">
+      <c r="N275" s="69" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -20113,7 +20098,7 @@
           <t>PS5-82-03</t>
         </is>
       </c>
-      <c r="B276" s="83" t="inlineStr">
+      <c r="B276" s="80" t="inlineStr">
         <is>
           <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
@@ -20124,7 +20109,7 @@
       <c r="D276" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E276" s="95" t="inlineStr">
+      <c r="E276" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20135,7 +20120,7 @@
       <c r="G276" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H276" s="70" t="inlineStr">
+      <c r="H276" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20165,7 +20150,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N276" s="70" t="inlineStr">
+      <c r="N276" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20182,7 +20167,7 @@
           <t>PS5-82-04</t>
         </is>
       </c>
-      <c r="B277" s="83" t="inlineStr">
+      <c r="B277" s="80" t="inlineStr">
         <is>
           <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
@@ -20193,7 +20178,7 @@
       <c r="D277" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E277" s="95" t="inlineStr">
+      <c r="E277" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20204,7 +20189,7 @@
       <c r="G277" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H277" s="69" t="inlineStr">
+      <c r="H277" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -20234,7 +20219,7 @@
           <t>6/8</t>
         </is>
       </c>
-      <c r="N277" s="69" t="inlineStr">
+      <c r="N277" s="68" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -20251,7 +20236,7 @@
           <t>PS5-82-05</t>
         </is>
       </c>
-      <c r="B278" s="83" t="inlineStr">
+      <c r="B278" s="80" t="inlineStr">
         <is>
           <t>PS5-82-05 - Office and Facilities building</t>
         </is>
@@ -20262,7 +20247,7 @@
       <c r="D278" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E278" s="95" t="inlineStr">
+      <c r="E278" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20273,7 +20258,7 @@
       <c r="G278" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H278" s="70" t="inlineStr">
+      <c r="H278" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20303,7 +20288,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N278" s="70" t="inlineStr">
+      <c r="N278" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20320,7 +20305,7 @@
           <t>PS5-82-06</t>
         </is>
       </c>
-      <c r="B279" s="83" t="inlineStr">
+      <c r="B279" s="80" t="inlineStr">
         <is>
           <t>PS5-82-06 - Guard House Building</t>
         </is>
@@ -20331,7 +20316,7 @@
       <c r="D279" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E279" s="95" t="inlineStr">
+      <c r="E279" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20342,7 +20327,7 @@
       <c r="G279" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H279" s="70" t="inlineStr">
+      <c r="H279" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20372,7 +20357,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N279" s="70" t="inlineStr">
+      <c r="N279" s="69" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20389,7 +20374,7 @@
           <t>PS5-82-07</t>
         </is>
       </c>
-      <c r="B280" s="83" t="inlineStr">
+      <c r="B280" s="80" t="inlineStr">
         <is>
           <t>PS5-82-07 - Guard Huts</t>
         </is>
@@ -20400,7 +20385,7 @@
       <c r="D280" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E280" s="95" t="inlineStr">
+      <c r="E280" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20411,7 +20396,7 @@
       <c r="G280" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H280" s="70" t="inlineStr">
+      <c r="H280" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20441,7 +20426,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N280" s="70" t="inlineStr">
+      <c r="N280" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20458,7 +20443,7 @@
           <t>PS5-83-01</t>
         </is>
       </c>
-      <c r="B281" s="83" t="inlineStr">
+      <c r="B281" s="80" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -20469,7 +20454,7 @@
       <c r="D281" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="E281" s="69" t="inlineStr">
+      <c r="E281" s="68" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20527,7 +20512,7 @@
           <t>PS5-84-01</t>
         </is>
       </c>
-      <c r="B282" s="83" t="inlineStr">
+      <c r="B282" s="80" t="inlineStr">
         <is>
           <t>PS5-84-01 - Generator Building</t>
         </is>
@@ -20538,7 +20523,7 @@
       <c r="D282" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E282" s="95" t="inlineStr">
+      <c r="E282" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20549,7 +20534,7 @@
       <c r="G282" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H282" s="70" t="inlineStr">
+      <c r="H282" s="69" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -20579,7 +20564,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N282" s="70" t="inlineStr">
+      <c r="N282" s="69" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -20596,7 +20581,7 @@
           <t>PS5-84-02</t>
         </is>
       </c>
-      <c r="B283" s="83" t="inlineStr">
+      <c r="B283" s="80" t="inlineStr">
         <is>
           <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
@@ -20607,7 +20592,7 @@
       <c r="D283" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E283" s="95" t="inlineStr">
+      <c r="E283" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20618,7 +20603,7 @@
       <c r="G283" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H283" s="70" t="inlineStr">
+      <c r="H283" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -20648,7 +20633,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N283" s="70" t="inlineStr">
+      <c r="N283" s="69" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -20665,7 +20650,7 @@
           <t>PS5-84-03</t>
         </is>
       </c>
-      <c r="B284" s="83" t="inlineStr">
+      <c r="B284" s="80" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -20676,7 +20661,7 @@
       <c r="D284" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E284" s="95" t="inlineStr">
+      <c r="E284" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20734,7 +20719,7 @@
           <t>PS5-86-01</t>
         </is>
       </c>
-      <c r="B285" s="83" t="inlineStr">
+      <c r="B285" s="80" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -20745,7 +20730,7 @@
       <c r="D285" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E285" s="95" t="inlineStr">
+      <c r="E285" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20803,7 +20788,7 @@
           <t>PS5-91-01</t>
         </is>
       </c>
-      <c r="B286" s="83" t="inlineStr">
+      <c r="B286" s="80" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -20814,7 +20799,7 @@
       <c r="D286" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E286" s="70" t="inlineStr">
+      <c r="E286" s="69" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -20872,7 +20857,7 @@
           <t>PS5-99-01</t>
         </is>
       </c>
-      <c r="B287" s="83" t="inlineStr">
+      <c r="B287" s="80" t="inlineStr">
         <is>
           <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
@@ -20883,7 +20868,7 @@
       <c r="D287" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E287" s="95" t="inlineStr">
+      <c r="E287" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20894,7 +20879,7 @@
       <c r="G287" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H287" s="70" t="inlineStr">
+      <c r="H287" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20924,7 +20909,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N287" s="70" t="inlineStr">
+      <c r="N287" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20941,7 +20926,7 @@
           <t>PS5-99-02</t>
         </is>
       </c>
-      <c r="B288" s="83" t="inlineStr">
+      <c r="B288" s="80" t="inlineStr">
         <is>
           <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
@@ -20952,7 +20937,7 @@
       <c r="D288" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E288" s="95" t="inlineStr">
+      <c r="E288" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20963,7 +20948,7 @@
       <c r="G288" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H288" s="70" t="inlineStr">
+      <c r="H288" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20993,7 +20978,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N288" s="70" t="inlineStr">
+      <c r="N288" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21010,7 +20995,7 @@
           <t>PS5-99-03</t>
         </is>
       </c>
-      <c r="B289" s="83" t="inlineStr">
+      <c r="B289" s="80" t="inlineStr">
         <is>
           <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
@@ -21021,7 +21006,7 @@
       <c r="D289" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E289" s="95" t="inlineStr">
+      <c r="E289" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21032,7 +21017,7 @@
       <c r="G289" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H289" s="70" t="inlineStr">
+      <c r="H289" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21062,7 +21047,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N289" s="70" t="inlineStr">
+      <c r="N289" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21079,7 +21064,7 @@
           <t>PS5-99-04</t>
         </is>
       </c>
-      <c r="B290" s="83" t="inlineStr">
+      <c r="B290" s="80" t="inlineStr">
         <is>
           <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
@@ -21090,7 +21075,7 @@
       <c r="D290" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E290" s="95" t="inlineStr">
+      <c r="E290" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21101,7 +21086,7 @@
       <c r="G290" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H290" s="70" t="inlineStr">
+      <c r="H290" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21131,7 +21116,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N290" s="70" t="inlineStr">
+      <c r="N290" s="69" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21148,7 +21133,7 @@
           <t>PS5-99-05</t>
         </is>
       </c>
-      <c r="B291" s="83" t="inlineStr">
+      <c r="B291" s="80" t="inlineStr">
         <is>
           <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
@@ -21159,7 +21144,7 @@
       <c r="D291" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E291" s="95" t="inlineStr">
+      <c r="E291" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21170,7 +21155,7 @@
       <c r="G291" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H291" s="70" t="inlineStr">
+      <c r="H291" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -21200,7 +21185,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N291" s="70" t="inlineStr">
+      <c r="N291" s="69" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -21217,7 +21202,7 @@
           <t>PS5-99-06</t>
         </is>
       </c>
-      <c r="B292" s="83" t="inlineStr">
+      <c r="B292" s="80" t="inlineStr">
         <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
@@ -21228,7 +21213,7 @@
       <c r="D292" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E292" s="95" t="inlineStr">
+      <c r="E292" s="92" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21239,7 +21224,7 @@
       <c r="G292" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H292" s="69" t="inlineStr">
+      <c r="H292" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -21269,7 +21254,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N292" s="69" t="inlineStr">
+      <c r="N292" s="68" t="inlineStr">
         <is>
           <t>67%</t>
         </is>

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -172,7 +172,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -309,6 +309,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFfff8e1"/>
         <bgColor rgb="FFfff8e1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -498,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -512,9 +518,6 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,10 +527,10 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -539,16 +542,19 @@
     <xf numFmtId="0" fontId="2" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -558,10 +564,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -573,21 +579,21 @@
     <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -677,6 +683,9 @@
     <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -698,10 +707,10 @@
     <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -713,7 +722,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,7 +737,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -731,28 +746,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1163,20 +1178,20 @@
           <t>PS5 COMPLETION PLATFORM  |  SUB SYSTEM - 290 subsystem(s)</t>
         </is>
       </c>
-      <c r="B1" s="97" t="n"/>
-      <c r="C1" s="97" t="n"/>
-      <c r="D1" s="97" t="n"/>
-      <c r="E1" s="97" t="n"/>
-      <c r="F1" s="97" t="n"/>
-      <c r="G1" s="97" t="n"/>
-      <c r="H1" s="97" t="n"/>
-      <c r="I1" s="97" t="n"/>
-      <c r="J1" s="97" t="n"/>
-      <c r="K1" s="97" t="n"/>
-      <c r="L1" s="97" t="n"/>
-      <c r="M1" s="97" t="n"/>
-      <c r="N1" s="97" t="n"/>
-      <c r="O1" s="98" t="n"/>
+      <c r="B1" s="100" t="n"/>
+      <c r="C1" s="100" t="n"/>
+      <c r="D1" s="100" t="n"/>
+      <c r="E1" s="100" t="n"/>
+      <c r="F1" s="100" t="n"/>
+      <c r="G1" s="100" t="n"/>
+      <c r="H1" s="100" t="n"/>
+      <c r="I1" s="100" t="n"/>
+      <c r="J1" s="100" t="n"/>
+      <c r="K1" s="100" t="n"/>
+      <c r="L1" s="100" t="n"/>
+      <c r="M1" s="100" t="n"/>
+      <c r="N1" s="100" t="n"/>
+      <c r="O1" s="101" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1261,7 +1276,7 @@
           <t>PS5-01-01</t>
         </is>
       </c>
-      <c r="B3" s="80" t="inlineStr">
+      <c r="B3" s="83" t="inlineStr">
         <is>
           <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
@@ -1272,7 +1287,7 @@
       <c r="D3" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="69" t="inlineStr">
+      <c r="E3" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -1330,7 +1345,7 @@
           <t>PS5-01-02</t>
         </is>
       </c>
-      <c r="B4" s="80" t="inlineStr">
+      <c r="B4" s="83" t="inlineStr">
         <is>
           <t>PS5-01-02 - Fire Water Pump A</t>
         </is>
@@ -1341,7 +1356,7 @@
       <c r="D4" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="69" t="inlineStr">
+      <c r="E4" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -1399,7 +1414,7 @@
           <t>PS5-01-03</t>
         </is>
       </c>
-      <c r="B5" s="80" t="inlineStr">
+      <c r="B5" s="83" t="inlineStr">
         <is>
           <t>PS5-01-03 - Fire Water Pump B</t>
         </is>
@@ -1410,7 +1425,7 @@
       <c r="D5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="69" t="inlineStr">
+      <c r="E5" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1468,7 +1483,7 @@
           <t>PS5-01-04</t>
         </is>
       </c>
-      <c r="B6" s="80" t="inlineStr">
+      <c r="B6" s="83" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -1479,7 +1494,7 @@
       <c r="D6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="69" t="inlineStr">
+      <c r="E6" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1537,7 +1552,7 @@
           <t>PS5-01-05</t>
         </is>
       </c>
-      <c r="B7" s="80" t="inlineStr">
+      <c r="B7" s="83" t="inlineStr">
         <is>
           <t>PS5-01-05 - Foam Skid</t>
         </is>
@@ -1548,7 +1563,7 @@
       <c r="D7" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="69" t="inlineStr">
+      <c r="E7" s="70" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -1606,7 +1621,7 @@
           <t>PS5-01-06</t>
         </is>
       </c>
-      <c r="B8" s="80" t="inlineStr">
+      <c r="B8" s="83" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -1617,7 +1632,7 @@
       <c r="D8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="69" t="inlineStr">
+      <c r="E8" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1675,7 +1690,7 @@
           <t>PS5-01-07</t>
         </is>
       </c>
-      <c r="B9" s="80" t="inlineStr">
+      <c r="B9" s="83" t="inlineStr">
         <is>
           <t>PS5-01-07 - Fire Water Ring Main &amp; Distribution</t>
         </is>
@@ -1686,7 +1701,7 @@
       <c r="D9" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="69" t="inlineStr">
+      <c r="E9" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1697,7 +1712,7 @@
       <c r="G9" s="23" t="n">
         <v>117</v>
       </c>
-      <c r="H9" s="68" t="inlineStr">
+      <c r="H9" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -1727,7 +1742,7 @@
           <t>86/87</t>
         </is>
       </c>
-      <c r="N9" s="68" t="inlineStr">
+      <c r="N9" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -1744,7 +1759,7 @@
           <t>PS5-01-08</t>
         </is>
       </c>
-      <c r="B10" s="80" t="inlineStr">
+      <c r="B10" s="83" t="inlineStr">
         <is>
           <t>PS5-01-08 - PS5 Deluge Valve Skid (PS5-01-UK-6100)</t>
         </is>
@@ -1755,7 +1770,7 @@
       <c r="D10" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="69" t="inlineStr">
+      <c r="E10" s="70" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -1766,7 +1781,7 @@
       <c r="G10" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H10" s="68" t="inlineStr">
+      <c r="H10" s="69" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -1796,7 +1811,7 @@
           <t>26/34</t>
         </is>
       </c>
-      <c r="N10" s="68" t="inlineStr">
+      <c r="N10" s="69" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -1813,7 +1828,7 @@
           <t>PS5-01-09</t>
         </is>
       </c>
-      <c r="B11" s="80" t="inlineStr">
+      <c r="B11" s="83" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -1824,7 +1839,7 @@
       <c r="D11" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="68" t="inlineStr">
+      <c r="E11" s="69" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1882,7 +1897,7 @@
           <t>PS5-01-10</t>
         </is>
       </c>
-      <c r="B12" s="80" t="inlineStr">
+      <c r="B12" s="83" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -1893,7 +1908,7 @@
       <c r="D12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="69" t="inlineStr">
+      <c r="E12" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -1951,7 +1966,7 @@
           <t>PS5-01-11</t>
         </is>
       </c>
-      <c r="B13" s="80" t="inlineStr">
+      <c r="B13" s="83" t="inlineStr">
         <is>
           <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
@@ -1962,7 +1977,7 @@
       <c r="D13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="69" t="inlineStr">
+      <c r="E13" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1973,7 +1988,7 @@
       <c r="G13" s="23" t="n">
         <v>39</v>
       </c>
-      <c r="H13" s="69" t="inlineStr">
+      <c r="H13" s="70" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -2003,7 +2018,7 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="N13" s="69" t="inlineStr">
+      <c r="N13" s="70" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -2020,7 +2035,7 @@
           <t>PS5-02-01</t>
         </is>
       </c>
-      <c r="B14" s="80" t="inlineStr">
+      <c r="B14" s="83" t="inlineStr">
         <is>
           <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
@@ -2031,7 +2046,7 @@
       <c r="D14" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="69" t="inlineStr">
+      <c r="E14" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2042,7 +2057,7 @@
       <c r="G14" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="69" t="inlineStr">
+      <c r="H14" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -2072,7 +2087,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N14" s="69" t="inlineStr">
+      <c r="N14" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -2089,7 +2104,7 @@
           <t>PS5-02-02</t>
         </is>
       </c>
-      <c r="B15" s="80" t="inlineStr">
+      <c r="B15" s="83" t="inlineStr">
         <is>
           <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
@@ -2100,7 +2115,7 @@
       <c r="D15" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="69" t="inlineStr">
+      <c r="E15" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2111,7 +2126,7 @@
       <c r="G15" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="69" t="inlineStr">
+      <c r="H15" s="70" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -2141,7 +2156,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N15" s="69" t="inlineStr">
+      <c r="N15" s="70" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -2158,7 +2173,7 @@
           <t>PS5-03-01</t>
         </is>
       </c>
-      <c r="B16" s="80" t="inlineStr">
+      <c r="B16" s="83" t="inlineStr">
         <is>
           <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
@@ -2169,7 +2184,7 @@
       <c r="D16" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="92" t="inlineStr">
+      <c r="E16" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2227,7 +2242,7 @@
           <t>PS5-03-03</t>
         </is>
       </c>
-      <c r="B17" s="80" t="inlineStr">
+      <c r="B17" s="83" t="inlineStr">
         <is>
           <t>PS5-03-03 - FZ-03 - Buildings Area</t>
         </is>
@@ -2238,7 +2253,7 @@
       <c r="D17" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="92" t="inlineStr">
+      <c r="E17" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2249,7 +2264,7 @@
       <c r="G17" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="69" t="inlineStr">
+      <c r="H17" s="70" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -2279,7 +2294,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N17" s="69" t="inlineStr">
+      <c r="N17" s="70" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -2296,7 +2311,7 @@
           <t>PS5-03-04</t>
         </is>
       </c>
-      <c r="B18" s="80" t="inlineStr">
+      <c r="B18" s="83" t="inlineStr">
         <is>
           <t>PS5-03-04 - FZ-04 - Utilities - Diesel and Firewater Pumps Areas</t>
         </is>
@@ -2307,7 +2322,7 @@
       <c r="D18" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="92" t="inlineStr">
+      <c r="E18" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2365,7 +2380,7 @@
           <t>PS5-03-06</t>
         </is>
       </c>
-      <c r="B19" s="80" t="inlineStr">
+      <c r="B19" s="83" t="inlineStr">
         <is>
           <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
@@ -2434,7 +2449,7 @@
           <t>PS5-03-07</t>
         </is>
       </c>
-      <c r="B20" s="80" t="inlineStr">
+      <c r="B20" s="83" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -2445,7 +2460,7 @@
       <c r="D20" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="92" t="inlineStr">
+      <c r="E20" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2503,7 +2518,7 @@
           <t>PS5-03-08</t>
         </is>
       </c>
-      <c r="B21" s="80" t="inlineStr">
+      <c r="B21" s="83" t="inlineStr">
         <is>
           <t>PS5-03-08 - FZ-08 - Utilities - Power Generation Area - External</t>
         </is>
@@ -2514,7 +2529,7 @@
       <c r="D21" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="92" t="inlineStr">
+      <c r="E21" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2572,7 +2587,7 @@
           <t>PS5-03-09</t>
         </is>
       </c>
-      <c r="B22" s="80" t="inlineStr">
+      <c r="B22" s="83" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -2583,7 +2598,7 @@
       <c r="D22" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="69" t="inlineStr">
+      <c r="E22" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2641,7 +2656,7 @@
           <t>PS5-03-10</t>
         </is>
       </c>
-      <c r="B23" s="80" t="inlineStr">
+      <c r="B23" s="83" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -2652,7 +2667,7 @@
       <c r="D23" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="92" t="inlineStr">
+      <c r="E23" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2710,7 +2725,7 @@
           <t>PS5-03-11</t>
         </is>
       </c>
-      <c r="B24" s="80" t="inlineStr">
+      <c r="B24" s="83" t="inlineStr">
         <is>
           <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
@@ -2721,7 +2736,7 @@
       <c r="D24" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="92" t="inlineStr">
+      <c r="E24" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2779,7 +2794,7 @@
           <t>PS5-03-12</t>
         </is>
       </c>
-      <c r="B25" s="80" t="inlineStr">
+      <c r="B25" s="83" t="inlineStr">
         <is>
           <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
@@ -2790,7 +2805,7 @@
       <c r="D25" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="92" t="inlineStr">
+      <c r="E25" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2848,7 +2863,7 @@
           <t>PS5-03-13</t>
         </is>
       </c>
-      <c r="B26" s="80" t="inlineStr">
+      <c r="B26" s="83" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -2859,7 +2874,7 @@
       <c r="D26" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="92" t="inlineStr">
+      <c r="E26" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2917,7 +2932,7 @@
           <t>PS5-03-14</t>
         </is>
       </c>
-      <c r="B27" s="80" t="inlineStr">
+      <c r="B27" s="83" t="inlineStr">
         <is>
           <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
@@ -2928,7 +2943,7 @@
       <c r="D27" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="69" t="inlineStr">
+      <c r="E27" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2939,7 +2954,7 @@
       <c r="G27" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H27" s="69" t="inlineStr">
+      <c r="H27" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2969,7 +2984,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N27" s="69" t="inlineStr">
+      <c r="N27" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2986,7 +3001,7 @@
           <t>PS5-03-15</t>
         </is>
       </c>
-      <c r="B28" s="80" t="inlineStr">
+      <c r="B28" s="83" t="inlineStr">
         <is>
           <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
@@ -2997,7 +3012,7 @@
       <c r="D28" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="92" t="inlineStr">
+      <c r="E28" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3008,7 +3023,7 @@
       <c r="G28" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="69" t="inlineStr">
+      <c r="H28" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3038,7 +3053,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N28" s="69" t="inlineStr">
+      <c r="N28" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3055,7 +3070,7 @@
           <t>PS5-03-16</t>
         </is>
       </c>
-      <c r="B29" s="80" t="inlineStr">
+      <c r="B29" s="83" t="inlineStr">
         <is>
           <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
@@ -3066,7 +3081,7 @@
       <c r="D29" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="92" t="inlineStr">
+      <c r="E29" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3077,7 +3092,7 @@
       <c r="G29" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="69" t="inlineStr">
+      <c r="H29" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3107,7 +3122,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N29" s="69" t="inlineStr">
+      <c r="N29" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3124,7 +3139,7 @@
           <t>PS5-03-17</t>
         </is>
       </c>
-      <c r="B30" s="80" t="inlineStr">
+      <c r="B30" s="83" t="inlineStr">
         <is>
           <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
@@ -3135,7 +3150,7 @@
       <c r="D30" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="92" t="inlineStr">
+      <c r="E30" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3146,7 +3161,7 @@
       <c r="G30" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="69" t="inlineStr">
+      <c r="H30" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3176,7 +3191,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N30" s="69" t="inlineStr">
+      <c r="N30" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3193,7 +3208,7 @@
           <t>PS5-03-18</t>
         </is>
       </c>
-      <c r="B31" s="80" t="inlineStr">
+      <c r="B31" s="83" t="inlineStr">
         <is>
           <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
@@ -3204,7 +3219,7 @@
       <c r="D31" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="92" t="inlineStr">
+      <c r="E31" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3215,7 +3230,7 @@
       <c r="G31" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="69" t="inlineStr">
+      <c r="H31" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3245,7 +3260,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N31" s="69" t="inlineStr">
+      <c r="N31" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3262,7 +3277,7 @@
           <t>PS5-03-19</t>
         </is>
       </c>
-      <c r="B32" s="80" t="inlineStr">
+      <c r="B32" s="83" t="inlineStr">
         <is>
           <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
@@ -3273,7 +3288,7 @@
       <c r="D32" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="92" t="inlineStr">
+      <c r="E32" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3284,7 +3299,7 @@
       <c r="G32" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="69" t="inlineStr">
+      <c r="H32" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3314,7 +3329,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N32" s="69" t="inlineStr">
+      <c r="N32" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3331,7 +3346,7 @@
           <t>PS5-03-20</t>
         </is>
       </c>
-      <c r="B33" s="80" t="inlineStr">
+      <c r="B33" s="83" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -3342,7 +3357,7 @@
       <c r="D33" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="69" t="inlineStr">
+      <c r="E33" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3400,7 +3415,7 @@
           <t>PS5-03-21</t>
         </is>
       </c>
-      <c r="B34" s="80" t="inlineStr">
+      <c r="B34" s="83" t="inlineStr">
         <is>
           <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
@@ -3411,7 +3426,7 @@
       <c r="D34" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="92" t="inlineStr">
+      <c r="E34" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3422,7 +3437,7 @@
       <c r="G34" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="69" t="inlineStr">
+      <c r="H34" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3452,7 +3467,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N34" s="69" t="inlineStr">
+      <c r="N34" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3469,7 +3484,7 @@
           <t>PS5-03-22</t>
         </is>
       </c>
-      <c r="B35" s="80" t="inlineStr">
+      <c r="B35" s="83" t="inlineStr">
         <is>
           <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
@@ -3480,7 +3495,7 @@
       <c r="D35" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="92" t="inlineStr">
+      <c r="E35" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3491,7 +3506,7 @@
       <c r="G35" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="69" t="inlineStr">
+      <c r="H35" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3521,7 +3536,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N35" s="69" t="inlineStr">
+      <c r="N35" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3538,7 +3553,7 @@
           <t>PS5-03-23</t>
         </is>
       </c>
-      <c r="B36" s="80" t="inlineStr">
+      <c r="B36" s="83" t="inlineStr">
         <is>
           <t>PS5-03-23 - FZ-E1 to E3 - EITS Building</t>
         </is>
@@ -3549,7 +3564,7 @@
       <c r="D36" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="69" t="inlineStr">
+      <c r="E36" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3560,7 +3575,7 @@
       <c r="G36" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="92" t="inlineStr">
+      <c r="H36" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3607,7 +3622,7 @@
           <t>PS5-03-24</t>
         </is>
       </c>
-      <c r="B37" s="80" t="inlineStr">
+      <c r="B37" s="83" t="inlineStr">
         <is>
           <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
@@ -3618,7 +3633,7 @@
       <c r="D37" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="92" t="inlineStr">
+      <c r="E37" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3629,7 +3644,7 @@
       <c r="G37" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="69" t="inlineStr">
+      <c r="H37" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3659,7 +3674,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N37" s="69" t="inlineStr">
+      <c r="N37" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3676,7 +3691,7 @@
           <t>PS5-03-25</t>
         </is>
       </c>
-      <c r="B38" s="80" t="inlineStr">
+      <c r="B38" s="83" t="inlineStr">
         <is>
           <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
@@ -3687,7 +3702,7 @@
       <c r="D38" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="92" t="inlineStr">
+      <c r="E38" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3698,7 +3713,7 @@
       <c r="G38" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="69" t="inlineStr">
+      <c r="H38" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3728,7 +3743,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N38" s="69" t="inlineStr">
+      <c r="N38" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3745,7 +3760,7 @@
           <t>PS5-04-01</t>
         </is>
       </c>
-      <c r="B39" s="80" t="inlineStr">
+      <c r="B39" s="83" t="inlineStr">
         <is>
           <t>PS5-04-01 - Office Building PCS System</t>
         </is>
@@ -3756,7 +3771,7 @@
       <c r="D39" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="92" t="inlineStr">
+      <c r="E39" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3767,7 +3782,7 @@
       <c r="G39" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="92" t="inlineStr">
+      <c r="H39" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3797,7 +3812,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N39" s="69" t="inlineStr">
+      <c r="N39" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3814,7 +3829,7 @@
           <t>PS5-04-02</t>
         </is>
       </c>
-      <c r="B40" s="80" t="inlineStr">
+      <c r="B40" s="83" t="inlineStr">
         <is>
           <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
@@ -3825,7 +3840,7 @@
       <c r="D40" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="92" t="inlineStr">
+      <c r="E40" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3836,7 +3851,7 @@
       <c r="G40" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="69" t="inlineStr">
+      <c r="H40" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3866,7 +3881,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N40" s="69" t="inlineStr">
+      <c r="N40" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3883,7 +3898,7 @@
           <t>PS5-04-03</t>
         </is>
       </c>
-      <c r="B41" s="80" t="inlineStr">
+      <c r="B41" s="83" t="inlineStr">
         <is>
           <t>PS5-04-03 - 33kV ICSS System</t>
         </is>
@@ -3894,7 +3909,7 @@
       <c r="D41" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="68" t="inlineStr">
+      <c r="E41" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -3905,7 +3920,7 @@
       <c r="G41" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="92" t="inlineStr">
+      <c r="H41" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3952,7 +3967,7 @@
           <t>PS5-04-04</t>
         </is>
       </c>
-      <c r="B42" s="80" t="inlineStr">
+      <c r="B42" s="83" t="inlineStr">
         <is>
           <t>PS5-04-04 - 33kV PCS System</t>
         </is>
@@ -3963,7 +3978,7 @@
       <c r="D42" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="E42" s="68" t="inlineStr">
+      <c r="E42" s="69" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -3974,7 +3989,7 @@
       <c r="G42" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="92" t="inlineStr">
+      <c r="H42" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4021,7 +4036,7 @@
           <t>PS5-04-05</t>
         </is>
       </c>
-      <c r="B43" s="80" t="inlineStr">
+      <c r="B43" s="83" t="inlineStr">
         <is>
           <t>PS5-04-05 - 33kV SIS/FGS System</t>
         </is>
@@ -4043,7 +4058,7 @@
       <c r="G43" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="92" t="inlineStr">
+      <c r="H43" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4073,7 +4088,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N43" s="68" t="inlineStr">
+      <c r="N43" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -4090,7 +4105,7 @@
           <t>PS5-05-01</t>
         </is>
       </c>
-      <c r="B44" s="80" t="inlineStr">
+      <c r="B44" s="83" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -4147,7 +4162,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O44" s="68" t="inlineStr">
+      <c r="O44" s="69" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4159,7 +4174,7 @@
           <t>PS5-05-02</t>
         </is>
       </c>
-      <c r="B45" s="80" t="inlineStr">
+      <c r="B45" s="83" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -4170,7 +4185,7 @@
       <c r="D45" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="69" t="inlineStr">
+      <c r="E45" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4228,7 +4243,7 @@
           <t>PS5-06-01</t>
         </is>
       </c>
-      <c r="B46" s="80" t="inlineStr">
+      <c r="B46" s="83" t="inlineStr">
         <is>
           <t>PS5-06-01 - AC UPS - EITS Building</t>
         </is>
@@ -4239,7 +4254,7 @@
       <c r="D46" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E46" s="68" t="inlineStr">
+      <c r="E46" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -4250,7 +4265,7 @@
       <c r="G46" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="92" t="inlineStr">
+      <c r="H46" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4280,7 +4295,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N46" s="68" t="inlineStr">
+      <c r="N46" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -4297,7 +4312,7 @@
           <t>PS5-06-02</t>
         </is>
       </c>
-      <c r="B47" s="80" t="inlineStr">
+      <c r="B47" s="83" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -4308,7 +4323,7 @@
       <c r="D47" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E47" s="69" t="inlineStr">
+      <c r="E47" s="70" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -4366,7 +4381,7 @@
           <t>PS5-06-03</t>
         </is>
       </c>
-      <c r="B48" s="80" t="inlineStr">
+      <c r="B48" s="83" t="inlineStr">
         <is>
           <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
@@ -4377,7 +4392,7 @@
       <c r="D48" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="92" t="inlineStr">
+      <c r="E48" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4388,7 +4403,7 @@
       <c r="G48" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="69" t="inlineStr">
+      <c r="H48" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4418,7 +4433,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N48" s="69" t="inlineStr">
+      <c r="N48" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4435,7 +4450,7 @@
           <t>PS5-06-04</t>
         </is>
       </c>
-      <c r="B49" s="80" t="inlineStr">
+      <c r="B49" s="83" t="inlineStr">
         <is>
           <t>PS5-06-04 - AC UPS - Guard House</t>
         </is>
@@ -4446,7 +4461,7 @@
       <c r="D49" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E49" s="92" t="inlineStr">
+      <c r="E49" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4457,7 +4472,7 @@
       <c r="G49" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="69" t="inlineStr">
+      <c r="H49" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4487,7 +4502,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N49" s="69" t="inlineStr">
+      <c r="N49" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4504,7 +4519,7 @@
           <t>PS5-06-05</t>
         </is>
       </c>
-      <c r="B50" s="80" t="inlineStr">
+      <c r="B50" s="83" t="inlineStr">
         <is>
           <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
@@ -4515,7 +4530,7 @@
       <c r="D50" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="92" t="inlineStr">
+      <c r="E50" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4526,7 +4541,7 @@
       <c r="G50" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="69" t="inlineStr">
+      <c r="H50" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4556,7 +4571,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N50" s="69" t="inlineStr">
+      <c r="N50" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4573,7 +4588,7 @@
           <t>PS5-08-01</t>
         </is>
       </c>
-      <c r="B51" s="80" t="inlineStr">
+      <c r="B51" s="83" t="inlineStr">
         <is>
           <t>PS5-08-01 - PAGA</t>
         </is>
@@ -4584,7 +4599,7 @@
       <c r="D51" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="69" t="inlineStr">
+      <c r="E51" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4595,7 +4610,7 @@
       <c r="G51" s="23" t="n">
         <v>82</v>
       </c>
-      <c r="H51" s="69" t="inlineStr">
+      <c r="H51" s="70" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -4625,7 +4640,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N51" s="69" t="inlineStr">
+      <c r="N51" s="70" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -4642,7 +4657,7 @@
           <t>PS5-08-03</t>
         </is>
       </c>
-      <c r="B52" s="80" t="inlineStr">
+      <c r="B52" s="83" t="inlineStr">
         <is>
           <t>PS5-08-03 - Telephone</t>
         </is>
@@ -4653,7 +4668,7 @@
       <c r="D52" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="92" t="inlineStr">
+      <c r="E52" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4664,7 +4679,7 @@
       <c r="G52" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H52" s="69" t="inlineStr">
+      <c r="H52" s="70" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -4694,7 +4709,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N52" s="69" t="inlineStr">
+      <c r="N52" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -4711,7 +4726,7 @@
           <t>PS5-08-04</t>
         </is>
       </c>
-      <c r="B53" s="80" t="inlineStr">
+      <c r="B53" s="83" t="inlineStr">
         <is>
           <t>PS5-08-04 - Hotline</t>
         </is>
@@ -4722,7 +4737,7 @@
       <c r="D53" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="92" t="inlineStr">
+      <c r="E53" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4733,7 +4748,7 @@
       <c r="G53" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="92" t="inlineStr">
+      <c r="H53" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4763,7 +4778,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N53" s="69" t="inlineStr">
+      <c r="N53" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4780,7 +4795,7 @@
           <t>PS5-08-07</t>
         </is>
       </c>
-      <c r="B54" s="80" t="inlineStr">
+      <c r="B54" s="83" t="inlineStr">
         <is>
           <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
@@ -4791,7 +4806,7 @@
       <c r="D54" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="92" t="inlineStr">
+      <c r="E54" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4802,7 +4817,7 @@
       <c r="G54" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="92" t="inlineStr">
+      <c r="H54" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4832,7 +4847,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N54" s="69" t="inlineStr">
+      <c r="N54" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4849,7 +4864,7 @@
           <t>PS5-08-11</t>
         </is>
       </c>
-      <c r="B55" s="80" t="inlineStr">
+      <c r="B55" s="83" t="inlineStr">
         <is>
           <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
@@ -4860,7 +4875,7 @@
       <c r="D55" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E55" s="69" t="inlineStr">
+      <c r="E55" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4871,7 +4886,7 @@
       <c r="G55" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H55" s="69" t="inlineStr">
+      <c r="H55" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4901,7 +4916,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N55" s="69" t="inlineStr">
+      <c r="N55" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4918,7 +4933,7 @@
           <t>PS5-08-12</t>
         </is>
       </c>
-      <c r="B56" s="80" t="inlineStr">
+      <c r="B56" s="83" t="inlineStr">
         <is>
           <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
@@ -4929,7 +4944,7 @@
       <c r="D56" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="92" t="inlineStr">
+      <c r="E56" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4940,7 +4955,7 @@
       <c r="G56" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="69" t="inlineStr">
+      <c r="H56" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4970,7 +4985,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N56" s="69" t="inlineStr">
+      <c r="N56" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4987,7 +5002,7 @@
           <t>PS5-08-13</t>
         </is>
       </c>
-      <c r="B57" s="80" t="inlineStr">
+      <c r="B57" s="83" t="inlineStr">
         <is>
           <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
@@ -4998,7 +5013,7 @@
       <c r="D57" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="68" t="inlineStr">
+      <c r="E57" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -5009,7 +5024,7 @@
       <c r="G57" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="69" t="inlineStr">
+      <c r="H57" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5039,7 +5054,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N57" s="69" t="inlineStr">
+      <c r="N57" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5056,7 +5071,7 @@
           <t>PS5-08-14</t>
         </is>
       </c>
-      <c r="B58" s="80" t="inlineStr">
+      <c r="B58" s="83" t="inlineStr">
         <is>
           <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
@@ -5067,7 +5082,7 @@
       <c r="D58" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E58" s="92" t="inlineStr">
+      <c r="E58" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5078,7 +5093,7 @@
       <c r="G58" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="69" t="inlineStr">
+      <c r="H58" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5108,7 +5123,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N58" s="69" t="inlineStr">
+      <c r="N58" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5125,7 +5140,7 @@
           <t>PS5-08-15</t>
         </is>
       </c>
-      <c r="B59" s="80" t="inlineStr">
+      <c r="B59" s="83" t="inlineStr">
         <is>
           <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
@@ -5136,7 +5151,7 @@
       <c r="D59" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E59" s="69" t="inlineStr">
+      <c r="E59" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -5147,7 +5162,7 @@
       <c r="G59" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="69" t="inlineStr">
+      <c r="H59" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5177,7 +5192,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N59" s="69" t="inlineStr">
+      <c r="N59" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5194,7 +5209,7 @@
           <t>PS5-08-23</t>
         </is>
       </c>
-      <c r="B60" s="80" t="inlineStr">
+      <c r="B60" s="83" t="inlineStr">
         <is>
           <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
@@ -5205,7 +5220,7 @@
       <c r="D60" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="69" t="inlineStr">
+      <c r="E60" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5216,7 +5231,7 @@
       <c r="G60" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="69" t="inlineStr">
+      <c r="H60" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5246,7 +5261,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N60" s="69" t="inlineStr">
+      <c r="N60" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5263,7 +5278,7 @@
           <t>PS5-08-34</t>
         </is>
       </c>
-      <c r="B61" s="80" t="inlineStr">
+      <c r="B61" s="83" t="inlineStr">
         <is>
           <t>PS5-08-34 - Satphone</t>
         </is>
@@ -5274,7 +5289,7 @@
       <c r="D61" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E61" s="92" t="inlineStr">
+      <c r="E61" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5285,7 +5300,7 @@
       <c r="G61" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="69" t="inlineStr">
+      <c r="H61" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5315,7 +5330,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N61" s="69" t="inlineStr">
+      <c r="N61" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5332,7 +5347,7 @@
           <t>PS5-08-35</t>
         </is>
       </c>
-      <c r="B62" s="80" t="inlineStr">
+      <c r="B62" s="83" t="inlineStr">
         <is>
           <t>PS5-08-35 - Optical Transport Network</t>
         </is>
@@ -5343,7 +5358,7 @@
       <c r="D62" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E62" s="69" t="inlineStr">
+      <c r="E62" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5354,7 +5369,7 @@
       <c r="G62" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="92" t="inlineStr">
+      <c r="H62" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5384,7 +5399,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N62" s="68" t="inlineStr">
+      <c r="N62" s="69" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -5401,7 +5416,7 @@
           <t>PS5-08-36</t>
         </is>
       </c>
-      <c r="B63" s="80" t="inlineStr">
+      <c r="B63" s="83" t="inlineStr">
         <is>
           <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
@@ -5412,7 +5427,7 @@
       <c r="D63" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E63" s="92" t="inlineStr">
+      <c r="E63" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5423,7 +5438,7 @@
       <c r="G63" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="69" t="inlineStr">
+      <c r="H63" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5453,7 +5468,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N63" s="69" t="inlineStr">
+      <c r="N63" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5470,7 +5485,7 @@
           <t>PS5-08-51</t>
         </is>
       </c>
-      <c r="B64" s="80" t="inlineStr">
+      <c r="B64" s="83" t="inlineStr">
         <is>
           <t>PS5-08-51 - Entertainment</t>
         </is>
@@ -5481,7 +5496,7 @@
       <c r="D64" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="92" t="inlineStr">
+      <c r="E64" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5492,7 +5507,7 @@
       <c r="G64" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H64" s="69" t="inlineStr">
+      <c r="H64" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5522,7 +5537,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N64" s="69" t="inlineStr">
+      <c r="N64" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5539,7 +5554,7 @@
           <t>PS5-08-52</t>
         </is>
       </c>
-      <c r="B65" s="80" t="inlineStr">
+      <c r="B65" s="83" t="inlineStr">
         <is>
           <t>PS5-08-52 - Process &amp; Security CCTV</t>
         </is>
@@ -5550,7 +5565,7 @@
       <c r="D65" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="92" t="inlineStr">
+      <c r="E65" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5561,7 +5576,7 @@
       <c r="G65" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="H65" s="69" t="inlineStr">
+      <c r="H65" s="70" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -5591,7 +5606,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N65" s="69" t="inlineStr">
+      <c r="N65" s="70" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -5608,7 +5623,7 @@
           <t>PS5-08-55</t>
         </is>
       </c>
-      <c r="B66" s="80" t="inlineStr">
+      <c r="B66" s="83" t="inlineStr">
         <is>
           <t>PS5-08-55 - Videoconference</t>
         </is>
@@ -5619,7 +5634,7 @@
       <c r="D66" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="92" t="inlineStr">
+      <c r="E66" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5630,7 +5645,7 @@
       <c r="G66" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H66" s="92" t="inlineStr">
+      <c r="H66" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5660,7 +5675,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N66" s="69" t="inlineStr">
+      <c r="N66" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5677,7 +5692,7 @@
           <t>PS5-08-61</t>
         </is>
       </c>
-      <c r="B67" s="80" t="inlineStr">
+      <c r="B67" s="83" t="inlineStr">
         <is>
           <t>PS5-08-61 - Meteocean</t>
         </is>
@@ -5688,7 +5703,7 @@
       <c r="D67" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="92" t="inlineStr">
+      <c r="E67" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5699,7 +5714,7 @@
       <c r="G67" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H67" s="69" t="inlineStr">
+      <c r="H67" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5729,7 +5744,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N67" s="69" t="inlineStr">
+      <c r="N67" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5746,7 +5761,7 @@
           <t>PS5-08-71</t>
         </is>
       </c>
-      <c r="B68" s="80" t="inlineStr">
+      <c r="B68" s="83" t="inlineStr">
         <is>
           <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
@@ -5757,7 +5772,7 @@
       <c r="D68" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E68" s="92" t="inlineStr">
+      <c r="E68" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5768,7 +5783,7 @@
       <c r="G68" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H68" s="69" t="inlineStr">
+      <c r="H68" s="70" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -5798,7 +5813,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N68" s="69" t="inlineStr">
+      <c r="N68" s="70" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -5815,7 +5830,7 @@
           <t>PS5-08-72</t>
         </is>
       </c>
-      <c r="B69" s="80" t="inlineStr">
+      <c r="B69" s="83" t="inlineStr">
         <is>
           <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
@@ -5826,7 +5841,7 @@
       <c r="D69" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E69" s="92" t="inlineStr">
+      <c r="E69" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5837,7 +5852,7 @@
       <c r="G69" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="69" t="inlineStr">
+      <c r="H69" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5867,7 +5882,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N69" s="69" t="inlineStr">
+      <c r="N69" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5884,7 +5899,7 @@
           <t>PS5-08-81</t>
         </is>
       </c>
-      <c r="B70" s="80" t="inlineStr">
+      <c r="B70" s="83" t="inlineStr">
         <is>
           <t>PS5-08-81 - Guard tour</t>
         </is>
@@ -5895,7 +5910,7 @@
       <c r="D70" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E70" s="92" t="inlineStr">
+      <c r="E70" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5906,7 +5921,7 @@
       <c r="G70" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H70" s="92" t="inlineStr">
+      <c r="H70" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5936,7 +5951,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N70" s="69" t="inlineStr">
+      <c r="N70" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5953,7 +5968,7 @@
           <t>PS5-08-82</t>
         </is>
       </c>
-      <c r="B71" s="80" t="inlineStr">
+      <c r="B71" s="83" t="inlineStr">
         <is>
           <t>PS5-08-82 - Key Management</t>
         </is>
@@ -5964,7 +5979,7 @@
       <c r="D71" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E71" s="92" t="inlineStr">
+      <c r="E71" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5975,7 +5990,7 @@
       <c r="G71" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H71" s="92" t="inlineStr">
+      <c r="H71" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6005,7 +6020,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N71" s="69" t="inlineStr">
+      <c r="N71" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6022,7 +6037,7 @@
           <t>PS5-08-83</t>
         </is>
       </c>
-      <c r="B72" s="80" t="inlineStr">
+      <c r="B72" s="83" t="inlineStr">
         <is>
           <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
@@ -6033,7 +6048,7 @@
       <c r="D72" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="92" t="inlineStr">
+      <c r="E72" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6044,7 +6059,7 @@
       <c r="G72" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="69" t="inlineStr">
+      <c r="H72" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6074,7 +6089,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N72" s="69" t="inlineStr">
+      <c r="N72" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6091,7 +6106,7 @@
           <t>PS5-08-85</t>
         </is>
       </c>
-      <c r="B73" s="80" t="inlineStr">
+      <c r="B73" s="83" t="inlineStr">
         <is>
           <t>PS5-08-85 - Access Control, POB &amp; e-Mustering</t>
         </is>
@@ -6113,7 +6128,7 @@
       <c r="G73" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="H73" s="69" t="inlineStr">
+      <c r="H73" s="70" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -6143,7 +6158,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N73" s="69" t="inlineStr">
+      <c r="N73" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -6160,7 +6175,7 @@
           <t>PS5-08-86</t>
         </is>
       </c>
-      <c r="B74" s="80" t="inlineStr">
+      <c r="B74" s="83" t="inlineStr">
         <is>
           <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
@@ -6171,7 +6186,7 @@
       <c r="D74" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="92" t="inlineStr">
+      <c r="E74" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6182,7 +6197,7 @@
       <c r="G74" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="92" t="inlineStr">
+      <c r="H74" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6212,7 +6227,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N74" s="69" t="inlineStr">
+      <c r="N74" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6229,7 +6244,7 @@
           <t>PS5-08-92</t>
         </is>
       </c>
-      <c r="B75" s="80" t="inlineStr">
+      <c r="B75" s="83" t="inlineStr">
         <is>
           <t>PS5-08-92 - Telecom Mast</t>
         </is>
@@ -6240,7 +6255,7 @@
       <c r="D75" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E75" s="92" t="inlineStr">
+      <c r="E75" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6251,7 +6266,7 @@
       <c r="G75" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H75" s="92" t="inlineStr">
+      <c r="H75" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6281,7 +6296,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N75" s="69" t="inlineStr">
+      <c r="N75" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6298,7 +6313,7 @@
           <t>PS5-08-93</t>
         </is>
       </c>
-      <c r="B76" s="80" t="inlineStr">
+      <c r="B76" s="83" t="inlineStr">
         <is>
           <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
@@ -6309,7 +6324,7 @@
       <c r="D76" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E76" s="92" t="inlineStr">
+      <c r="E76" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6320,7 +6335,7 @@
       <c r="G76" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H76" s="69" t="inlineStr">
+      <c r="H76" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6350,7 +6365,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N76" s="69" t="inlineStr">
+      <c r="N76" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6367,7 +6382,7 @@
           <t>PS5-09-01</t>
         </is>
       </c>
-      <c r="B77" s="80" t="inlineStr">
+      <c r="B77" s="83" t="inlineStr">
         <is>
           <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
@@ -6378,7 +6393,7 @@
       <c r="D77" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="92" t="inlineStr">
+      <c r="E77" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6389,7 +6404,7 @@
       <c r="G77" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H77" s="69" t="inlineStr">
+      <c r="H77" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6419,7 +6434,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N77" s="69" t="inlineStr">
+      <c r="N77" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6436,7 +6451,7 @@
           <t>PS5-09-02</t>
         </is>
       </c>
-      <c r="B78" s="80" t="inlineStr">
+      <c r="B78" s="83" t="inlineStr">
         <is>
           <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
@@ -6447,7 +6462,7 @@
       <c r="D78" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E78" s="92" t="inlineStr">
+      <c r="E78" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6458,7 +6473,7 @@
       <c r="G78" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H78" s="69" t="inlineStr">
+      <c r="H78" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6488,7 +6503,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N78" s="69" t="inlineStr">
+      <c r="N78" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6505,7 +6520,7 @@
           <t>PS5-09-03</t>
         </is>
       </c>
-      <c r="B79" s="80" t="inlineStr">
+      <c r="B79" s="83" t="inlineStr">
         <is>
           <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
@@ -6516,7 +6531,7 @@
       <c r="D79" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E79" s="69" t="inlineStr">
+      <c r="E79" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -6527,7 +6542,7 @@
       <c r="G79" s="23" t="n">
         <v>53</v>
       </c>
-      <c r="H79" s="69" t="inlineStr">
+      <c r="H79" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -6557,7 +6572,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N79" s="69" t="inlineStr">
+      <c r="N79" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -6574,7 +6589,7 @@
           <t>PS5-09-04</t>
         </is>
       </c>
-      <c r="B80" s="80" t="inlineStr">
+      <c r="B80" s="83" t="inlineStr">
         <is>
           <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
@@ -6585,7 +6600,7 @@
       <c r="D80" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E80" s="92" t="inlineStr">
+      <c r="E80" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6596,7 +6611,7 @@
       <c r="G80" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="69" t="inlineStr">
+      <c r="H80" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6626,7 +6641,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N80" s="69" t="inlineStr">
+      <c r="N80" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6643,7 +6658,7 @@
           <t>PS5-09-05</t>
         </is>
       </c>
-      <c r="B81" s="80" t="inlineStr">
+      <c r="B81" s="83" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -6654,7 +6669,7 @@
       <c r="D81" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="E81" s="68" t="inlineStr">
+      <c r="E81" s="69" t="inlineStr">
         <is>
           <t>56%</t>
         </is>
@@ -6712,7 +6727,7 @@
           <t>PS5-0H-01</t>
         </is>
       </c>
-      <c r="B82" s="80" t="inlineStr">
+      <c r="B82" s="83" t="inlineStr">
         <is>
           <t>PS5-0H-01 - HIPPS</t>
         </is>
@@ -6723,7 +6738,7 @@
       <c r="D82" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E82" s="69" t="inlineStr">
+      <c r="E82" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -6734,7 +6749,7 @@
       <c r="G82" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="92" t="inlineStr">
+      <c r="H82" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6764,7 +6779,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N82" s="68" t="inlineStr">
+      <c r="N82" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -6781,7 +6796,7 @@
           <t>PS5-25-01</t>
         </is>
       </c>
-      <c r="B83" s="80" t="inlineStr">
+      <c r="B83" s="83" t="inlineStr">
         <is>
           <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
@@ -6792,7 +6807,7 @@
       <c r="D83" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E83" s="69" t="inlineStr">
+      <c r="E83" s="70" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -6803,7 +6818,7 @@
       <c r="G83" s="23" t="n">
         <v>111</v>
       </c>
-      <c r="H83" s="68" t="inlineStr">
+      <c r="H83" s="69" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -6833,7 +6848,7 @@
           <t>42/46</t>
         </is>
       </c>
-      <c r="N83" s="68" t="inlineStr">
+      <c r="N83" s="69" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -6850,7 +6865,7 @@
           <t>PS5-25-02</t>
         </is>
       </c>
-      <c r="B84" s="80" t="inlineStr">
+      <c r="B84" s="83" t="inlineStr">
         <is>
           <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
@@ -6861,7 +6876,7 @@
       <c r="D84" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="E84" s="69" t="inlineStr">
+      <c r="E84" s="70" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -6872,7 +6887,7 @@
       <c r="G84" s="23" t="n">
         <v>175</v>
       </c>
-      <c r="H84" s="68" t="inlineStr">
+      <c r="H84" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -6902,7 +6917,7 @@
           <t>23/24</t>
         </is>
       </c>
-      <c r="N84" s="68" t="inlineStr">
+      <c r="N84" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -6919,7 +6934,7 @@
           <t>PS5-25-03</t>
         </is>
       </c>
-      <c r="B85" s="80" t="inlineStr">
+      <c r="B85" s="83" t="inlineStr">
         <is>
           <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
@@ -6930,7 +6945,7 @@
       <c r="D85" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="E85" s="69" t="inlineStr">
+      <c r="E85" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -6941,7 +6956,7 @@
       <c r="G85" s="23" t="n">
         <v>164</v>
       </c>
-      <c r="H85" s="68" t="inlineStr">
+      <c r="H85" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -6971,7 +6986,7 @@
           <t>23/24</t>
         </is>
       </c>
-      <c r="N85" s="68" t="inlineStr">
+      <c r="N85" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -6988,7 +7003,7 @@
           <t>PS5-25-04</t>
         </is>
       </c>
-      <c r="B86" s="80" t="inlineStr">
+      <c r="B86" s="83" t="inlineStr">
         <is>
           <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
@@ -6999,7 +7014,7 @@
       <c r="D86" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E86" s="69" t="inlineStr">
+      <c r="E86" s="70" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -7010,7 +7025,7 @@
       <c r="G86" s="23" t="n">
         <v>161</v>
       </c>
-      <c r="H86" s="68" t="inlineStr">
+      <c r="H86" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -7040,7 +7055,7 @@
           <t>23/24</t>
         </is>
       </c>
-      <c r="N86" s="68" t="inlineStr">
+      <c r="N86" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -7057,7 +7072,7 @@
           <t>PS5-25-05</t>
         </is>
       </c>
-      <c r="B87" s="80" t="inlineStr">
+      <c r="B87" s="83" t="inlineStr">
         <is>
           <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
@@ -7079,7 +7094,7 @@
       <c r="G87" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H87" s="68" t="inlineStr">
+      <c r="H87" s="69" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
@@ -7109,7 +7124,7 @@
           <t>8/9</t>
         </is>
       </c>
-      <c r="N87" s="68" t="inlineStr">
+      <c r="N87" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -7126,7 +7141,7 @@
           <t>PS5-25-06</t>
         </is>
       </c>
-      <c r="B88" s="80" t="inlineStr">
+      <c r="B88" s="83" t="inlineStr">
         <is>
           <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
@@ -7137,7 +7152,7 @@
       <c r="D88" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E88" s="69" t="inlineStr">
+      <c r="E88" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7148,7 +7163,7 @@
       <c r="G88" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H88" s="68" t="inlineStr">
+      <c r="H88" s="69" t="inlineStr">
         <is>
           <t>59%</t>
         </is>
@@ -7178,7 +7193,7 @@
           <t>17/19</t>
         </is>
       </c>
-      <c r="N88" s="68" t="inlineStr">
+      <c r="N88" s="69" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -7195,7 +7210,7 @@
           <t>PS5-25-07</t>
         </is>
       </c>
-      <c r="B89" s="80" t="inlineStr">
+      <c r="B89" s="83" t="inlineStr">
         <is>
           <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
@@ -7206,7 +7221,7 @@
       <c r="D89" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E89" s="69" t="inlineStr">
+      <c r="E89" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -7217,7 +7232,7 @@
       <c r="G89" s="23" t="n">
         <v>103</v>
       </c>
-      <c r="H89" s="68" t="inlineStr">
+      <c r="H89" s="69" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -7247,7 +7262,7 @@
           <t>33/35</t>
         </is>
       </c>
-      <c r="N89" s="68" t="inlineStr">
+      <c r="N89" s="69" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -7264,7 +7279,7 @@
           <t>PS5-28-01</t>
         </is>
       </c>
-      <c r="B90" s="80" t="inlineStr">
+      <c r="B90" s="83" t="inlineStr">
         <is>
           <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
@@ -7275,7 +7290,7 @@
       <c r="D90" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E90" s="92" t="inlineStr">
+      <c r="E90" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7286,7 +7301,7 @@
       <c r="G90" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H90" s="68" t="inlineStr">
+      <c r="H90" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -7316,7 +7331,7 @@
           <t>12/14</t>
         </is>
       </c>
-      <c r="N90" s="68" t="inlineStr">
+      <c r="N90" s="69" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -7333,7 +7348,7 @@
           <t>PS5-28-02</t>
         </is>
       </c>
-      <c r="B91" s="80" t="inlineStr">
+      <c r="B91" s="83" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -7344,7 +7359,7 @@
       <c r="D91" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E91" s="69" t="inlineStr">
+      <c r="E91" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7402,7 +7417,7 @@
           <t>PS5-28-03</t>
         </is>
       </c>
-      <c r="B92" s="80" t="inlineStr">
+      <c r="B92" s="83" t="inlineStr">
         <is>
           <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
@@ -7413,7 +7428,7 @@
       <c r="D92" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E92" s="69" t="inlineStr">
+      <c r="E92" s="70" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -7424,7 +7439,7 @@
       <c r="G92" s="23" t="n">
         <v>93</v>
       </c>
-      <c r="H92" s="68" t="inlineStr">
+      <c r="H92" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -7454,7 +7469,7 @@
           <t>54/56</t>
         </is>
       </c>
-      <c r="N92" s="68" t="inlineStr">
+      <c r="N92" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -7471,7 +7486,7 @@
           <t>PS5-28-04</t>
         </is>
       </c>
-      <c r="B93" s="80" t="inlineStr">
+      <c r="B93" s="83" t="inlineStr">
         <is>
           <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
@@ -7482,7 +7497,7 @@
       <c r="D93" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E93" s="69" t="inlineStr">
+      <c r="E93" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -7540,7 +7555,7 @@
           <t>PS5-28-05</t>
         </is>
       </c>
-      <c r="B94" s="80" t="inlineStr">
+      <c r="B94" s="83" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -7551,7 +7566,7 @@
       <c r="D94" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E94" s="69" t="inlineStr">
+      <c r="E94" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7609,7 +7624,7 @@
           <t>PS5-28-06</t>
         </is>
       </c>
-      <c r="B95" s="80" t="inlineStr">
+      <c r="B95" s="83" t="inlineStr">
         <is>
           <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
@@ -7620,7 +7635,7 @@
       <c r="D95" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E95" s="69" t="inlineStr">
+      <c r="E95" s="70" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -7661,7 +7676,7 @@
           <t>36/36</t>
         </is>
       </c>
-      <c r="N95" s="68" t="inlineStr">
+      <c r="N95" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -7678,7 +7693,7 @@
           <t>PS5-28-07</t>
         </is>
       </c>
-      <c r="B96" s="80" t="inlineStr">
+      <c r="B96" s="83" t="inlineStr">
         <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
@@ -7689,7 +7704,7 @@
       <c r="D96" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E96" s="69" t="inlineStr">
+      <c r="E96" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -7747,7 +7762,7 @@
           <t>PS5-28-08</t>
         </is>
       </c>
-      <c r="B97" s="80" t="inlineStr">
+      <c r="B97" s="83" t="inlineStr">
         <is>
           <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
@@ -7758,7 +7773,7 @@
       <c r="D97" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E97" s="69" t="inlineStr">
+      <c r="E97" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7769,7 +7784,7 @@
       <c r="G97" s="23" t="n">
         <v>34</v>
       </c>
-      <c r="H97" s="69" t="inlineStr">
+      <c r="H97" s="70" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
@@ -7799,7 +7814,7 @@
           <t>23/29</t>
         </is>
       </c>
-      <c r="N97" s="69" t="inlineStr">
+      <c r="N97" s="70" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -7816,7 +7831,7 @@
           <t>PS5-28-09</t>
         </is>
       </c>
-      <c r="B98" s="80" t="inlineStr">
+      <c r="B98" s="83" t="inlineStr">
         <is>
           <t>PS5-28-09 - Observation Basin</t>
         </is>
@@ -7827,7 +7842,7 @@
       <c r="D98" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E98" s="69" t="inlineStr">
+      <c r="E98" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7868,7 +7883,7 @@
           <t>13/14</t>
         </is>
       </c>
-      <c r="N98" s="68" t="inlineStr">
+      <c r="N98" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -7885,7 +7900,7 @@
           <t>PS5-28-10</t>
         </is>
       </c>
-      <c r="B99" s="80" t="inlineStr">
+      <c r="B99" s="83" t="inlineStr">
         <is>
           <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
@@ -7896,7 +7911,7 @@
       <c r="D99" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E99" s="69" t="inlineStr">
+      <c r="E99" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7907,7 +7922,7 @@
       <c r="G99" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H99" s="69" t="inlineStr">
+      <c r="H99" s="70" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -7937,7 +7952,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N99" s="69" t="inlineStr">
+      <c r="N99" s="70" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -7954,7 +7969,7 @@
           <t>PS5-28-11</t>
         </is>
       </c>
-      <c r="B100" s="80" t="inlineStr">
+      <c r="B100" s="83" t="inlineStr">
         <is>
           <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
@@ -7965,7 +7980,7 @@
       <c r="D100" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E100" s="69" t="inlineStr">
+      <c r="E100" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7976,7 +7991,7 @@
       <c r="G100" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H100" s="68" t="inlineStr">
+      <c r="H100" s="69" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -8006,7 +8021,7 @@
           <t>8/8</t>
         </is>
       </c>
-      <c r="N100" s="68" t="inlineStr">
+      <c r="N100" s="69" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -8023,7 +8038,7 @@
           <t>PS5-28-12</t>
         </is>
       </c>
-      <c r="B101" s="80" t="inlineStr">
+      <c r="B101" s="83" t="inlineStr">
         <is>
           <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
@@ -8034,7 +8049,7 @@
       <c r="D101" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E101" s="69" t="inlineStr">
+      <c r="E101" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8045,7 +8060,7 @@
       <c r="G101" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="H101" s="68" t="inlineStr">
+      <c r="H101" s="69" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8075,7 +8090,7 @@
           <t>28/43</t>
         </is>
       </c>
-      <c r="N101" s="68" t="inlineStr">
+      <c r="N101" s="69" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8092,7 +8107,7 @@
           <t>PS5-28-13</t>
         </is>
       </c>
-      <c r="B102" s="80" t="inlineStr">
+      <c r="B102" s="83" t="inlineStr">
         <is>
           <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
@@ -8103,7 +8118,7 @@
       <c r="D102" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E102" s="68" t="inlineStr">
+      <c r="E102" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8114,7 +8129,7 @@
       <c r="G102" s="23" t="n">
         <v>54</v>
       </c>
-      <c r="H102" s="68" t="inlineStr">
+      <c r="H102" s="69" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -8144,7 +8159,7 @@
           <t>34/35</t>
         </is>
       </c>
-      <c r="N102" s="68" t="inlineStr">
+      <c r="N102" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -8161,7 +8176,7 @@
           <t>PS5-28-14</t>
         </is>
       </c>
-      <c r="B103" s="80" t="inlineStr">
+      <c r="B103" s="83" t="inlineStr">
         <is>
           <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
@@ -8172,7 +8187,7 @@
       <c r="D103" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="68" t="inlineStr">
+      <c r="E103" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8183,7 +8198,7 @@
       <c r="G103" s="23" t="n">
         <v>53</v>
       </c>
-      <c r="H103" s="68" t="inlineStr">
+      <c r="H103" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -8213,7 +8228,7 @@
           <t>32/35</t>
         </is>
       </c>
-      <c r="N103" s="68" t="inlineStr">
+      <c r="N103" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8230,7 +8245,7 @@
           <t>PS5-28-15</t>
         </is>
       </c>
-      <c r="B104" s="80" t="inlineStr">
+      <c r="B104" s="83" t="inlineStr">
         <is>
           <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
@@ -8241,7 +8256,7 @@
       <c r="D104" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E104" s="68" t="inlineStr">
+      <c r="E104" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8252,7 +8267,7 @@
       <c r="G104" s="23" t="n">
         <v>52</v>
       </c>
-      <c r="H104" s="68" t="inlineStr">
+      <c r="H104" s="69" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -8282,7 +8297,7 @@
           <t>32/35</t>
         </is>
       </c>
-      <c r="N104" s="68" t="inlineStr">
+      <c r="N104" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -8299,7 +8314,7 @@
           <t>PS5-28-16</t>
         </is>
       </c>
-      <c r="B105" s="80" t="inlineStr">
+      <c r="B105" s="83" t="inlineStr">
         <is>
           <t>PS5-28-16 - LP Relief Header</t>
         </is>
@@ -8310,7 +8325,7 @@
       <c r="D105" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E105" s="92" t="inlineStr">
+      <c r="E105" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8351,7 +8366,7 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N105" s="68" t="inlineStr">
+      <c r="N105" s="69" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -8368,7 +8383,7 @@
           <t>PS5-28-17</t>
         </is>
       </c>
-      <c r="B106" s="80" t="inlineStr">
+      <c r="B106" s="83" t="inlineStr">
         <is>
           <t>PS5-28-17 - Reinjection Pump</t>
         </is>
@@ -8379,7 +8394,7 @@
       <c r="D106" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E106" s="69" t="inlineStr">
+      <c r="E106" s="70" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -8390,7 +8405,7 @@
       <c r="G106" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H106" s="68" t="inlineStr">
+      <c r="H106" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -8420,7 +8435,7 @@
           <t>24/24</t>
         </is>
       </c>
-      <c r="N106" s="68" t="inlineStr">
+      <c r="N106" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -8437,7 +8452,7 @@
           <t>PS5-50-01</t>
         </is>
       </c>
-      <c r="B107" s="80" t="inlineStr">
+      <c r="B107" s="83" t="inlineStr">
         <is>
           <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
@@ -8448,7 +8463,7 @@
       <c r="D107" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E107" s="92" t="inlineStr">
+      <c r="E107" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8459,7 +8474,7 @@
       <c r="G107" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H107" s="69" t="inlineStr">
+      <c r="H107" s="70" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8489,7 +8504,7 @@
           <t>9/13</t>
         </is>
       </c>
-      <c r="N107" s="69" t="inlineStr">
+      <c r="N107" s="70" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8506,7 +8521,7 @@
           <t>PS5-50-02</t>
         </is>
       </c>
-      <c r="B108" s="80" t="inlineStr">
+      <c r="B108" s="83" t="inlineStr">
         <is>
           <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
@@ -8517,7 +8532,7 @@
       <c r="D108" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E108" s="92" t="inlineStr">
+      <c r="E108" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8528,7 +8543,7 @@
       <c r="G108" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H108" s="69" t="inlineStr">
+      <c r="H108" s="70" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -8558,7 +8573,7 @@
           <t>10/13</t>
         </is>
       </c>
-      <c r="N108" s="69" t="inlineStr">
+      <c r="N108" s="70" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -8575,7 +8590,7 @@
           <t>PS5-50-03</t>
         </is>
       </c>
-      <c r="B109" s="80" t="inlineStr">
+      <c r="B109" s="83" t="inlineStr">
         <is>
           <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
@@ -8586,7 +8601,7 @@
       <c r="D109" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="69" t="inlineStr">
+      <c r="E109" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8597,7 +8612,7 @@
       <c r="G109" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H109" s="68" t="inlineStr">
+      <c r="H109" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -8627,7 +8642,7 @@
           <t>10/15</t>
         </is>
       </c>
-      <c r="N109" s="69" t="inlineStr">
+      <c r="N109" s="70" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8644,7 +8659,7 @@
           <t>PS5-53-01</t>
         </is>
       </c>
-      <c r="B110" s="80" t="inlineStr">
+      <c r="B110" s="83" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -8655,7 +8670,7 @@
       <c r="D110" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E110" s="68" t="inlineStr">
+      <c r="E110" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -8666,7 +8681,7 @@
       <c r="G110" s="23" t="n">
         <v>42</v>
       </c>
-      <c r="H110" s="68" t="inlineStr">
+      <c r="H110" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -8696,12 +8711,12 @@
           <t>27/30</t>
         </is>
       </c>
-      <c r="N110" s="68" t="inlineStr">
+      <c r="N110" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="O110" s="68" t="inlineStr">
+      <c r="O110" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -8713,7 +8728,7 @@
           <t>PS5-53-02</t>
         </is>
       </c>
-      <c r="B111" s="80" t="inlineStr">
+      <c r="B111" s="83" t="inlineStr">
         <is>
           <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
@@ -8724,7 +8739,7 @@
       <c r="D111" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="69" t="inlineStr">
+      <c r="E111" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8735,7 +8750,7 @@
       <c r="G111" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H111" s="68" t="inlineStr">
+      <c r="H111" s="69" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
@@ -8765,7 +8780,7 @@
           <t>8/8</t>
         </is>
       </c>
-      <c r="N111" s="68" t="inlineStr">
+      <c r="N111" s="69" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -8782,7 +8797,7 @@
           <t>PS5-53-03</t>
         </is>
       </c>
-      <c r="B112" s="80" t="inlineStr">
+      <c r="B112" s="83" t="inlineStr">
         <is>
           <t>PS5-53-03 - Water Softener Package</t>
         </is>
@@ -8793,7 +8808,7 @@
       <c r="D112" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E112" s="92" t="inlineStr">
+      <c r="E112" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8804,7 +8819,7 @@
       <c r="G112" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H112" s="68" t="inlineStr">
+      <c r="H112" s="69" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8834,7 +8849,7 @@
           <t>11/14</t>
         </is>
       </c>
-      <c r="N112" s="68" t="inlineStr">
+      <c r="N112" s="69" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
@@ -8851,7 +8866,7 @@
           <t>PS5-53-04</t>
         </is>
       </c>
-      <c r="B113" s="80" t="inlineStr">
+      <c r="B113" s="83" t="inlineStr">
         <is>
           <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
@@ -8862,7 +8877,7 @@
       <c r="D113" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="92" t="inlineStr">
+      <c r="E113" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8873,7 +8888,7 @@
       <c r="G113" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="69" t="inlineStr">
+      <c r="H113" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8903,7 +8918,7 @@
           <t>0/1</t>
         </is>
       </c>
-      <c r="N113" s="69" t="inlineStr">
+      <c r="N113" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8920,7 +8935,7 @@
           <t>PS5-53-05</t>
         </is>
       </c>
-      <c r="B114" s="80" t="inlineStr">
+      <c r="B114" s="83" t="inlineStr">
         <is>
           <t>PS5-53-05 - Water Distribution Header</t>
         </is>
@@ -8931,7 +8946,7 @@
       <c r="D114" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E114" s="92" t="inlineStr">
+      <c r="E114" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8989,7 +9004,7 @@
           <t>PS5-53-06</t>
         </is>
       </c>
-      <c r="B115" s="80" t="inlineStr">
+      <c r="B115" s="83" t="inlineStr">
         <is>
           <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
@@ -9000,7 +9015,7 @@
       <c r="D115" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E115" s="92" t="inlineStr">
+      <c r="E115" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9011,7 +9026,7 @@
       <c r="G115" s="23" t="n">
         <v>33</v>
       </c>
-      <c r="H115" s="68" t="inlineStr">
+      <c r="H115" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -9041,7 +9056,7 @@
           <t>33/39</t>
         </is>
       </c>
-      <c r="N115" s="68" t="inlineStr">
+      <c r="N115" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -9058,7 +9073,7 @@
           <t>PS5-60-01</t>
         </is>
       </c>
-      <c r="B116" s="80" t="inlineStr">
+      <c r="B116" s="83" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -9069,7 +9084,7 @@
       <c r="D116" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="E116" s="69" t="inlineStr">
+      <c r="E116" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -9127,7 +9142,7 @@
           <t>PS5-60-02</t>
         </is>
       </c>
-      <c r="B117" s="80" t="inlineStr">
+      <c r="B117" s="83" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -9138,7 +9153,7 @@
       <c r="D117" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E117" s="69" t="inlineStr">
+      <c r="E117" s="70" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -9196,7 +9211,7 @@
           <t>PS5-60-03</t>
         </is>
       </c>
-      <c r="B118" s="80" t="inlineStr">
+      <c r="B118" s="83" t="inlineStr">
         <is>
           <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9207,7 +9222,7 @@
       <c r="D118" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E118" s="69" t="inlineStr">
+      <c r="E118" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -9218,7 +9233,7 @@
       <c r="G118" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H118" s="68" t="inlineStr">
+      <c r="H118" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9248,7 +9263,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N118" s="68" t="inlineStr">
+      <c r="N118" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9265,7 +9280,7 @@
           <t>PS5-60-04</t>
         </is>
       </c>
-      <c r="B119" s="80" t="inlineStr">
+      <c r="B119" s="83" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -9276,7 +9291,7 @@
       <c r="D119" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E119" s="69" t="inlineStr">
+      <c r="E119" s="70" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -9334,7 +9349,7 @@
           <t>PS5-60-05</t>
         </is>
       </c>
-      <c r="B120" s="80" t="inlineStr">
+      <c r="B120" s="83" t="inlineStr">
         <is>
           <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
@@ -9345,7 +9360,7 @@
       <c r="D120" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E120" s="69" t="inlineStr">
+      <c r="E120" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9403,7 +9418,7 @@
           <t>PS5-60-06</t>
         </is>
       </c>
-      <c r="B121" s="80" t="inlineStr">
+      <c r="B121" s="83" t="inlineStr">
         <is>
           <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9414,7 +9429,7 @@
       <c r="D121" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="69" t="inlineStr">
+      <c r="E121" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9425,7 +9440,7 @@
       <c r="G121" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H121" s="68" t="inlineStr">
+      <c r="H121" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9455,7 +9470,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N121" s="68" t="inlineStr">
+      <c r="N121" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9472,7 +9487,7 @@
           <t>PS5-60-07</t>
         </is>
       </c>
-      <c r="B122" s="80" t="inlineStr">
+      <c r="B122" s="83" t="inlineStr">
         <is>
           <t>PS5-60-07 - Power Generation Package C</t>
         </is>
@@ -9483,7 +9498,7 @@
       <c r="D122" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E122" s="69" t="inlineStr">
+      <c r="E122" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -9541,7 +9556,7 @@
           <t>PS5-60-08</t>
         </is>
       </c>
-      <c r="B123" s="80" t="inlineStr">
+      <c r="B123" s="83" t="inlineStr">
         <is>
           <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
@@ -9552,7 +9567,7 @@
       <c r="D123" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E123" s="69" t="inlineStr">
+      <c r="E123" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9610,7 +9625,7 @@
           <t>PS5-60-09</t>
         </is>
       </c>
-      <c r="B124" s="80" t="inlineStr">
+      <c r="B124" s="83" t="inlineStr">
         <is>
           <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9621,7 +9636,7 @@
       <c r="D124" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E124" s="92" t="inlineStr">
+      <c r="E124" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9632,7 +9647,7 @@
       <c r="G124" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H124" s="68" t="inlineStr">
+      <c r="H124" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9662,7 +9677,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N124" s="68" t="inlineStr">
+      <c r="N124" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -9679,7 +9694,7 @@
           <t>PS5-60-10</t>
         </is>
       </c>
-      <c r="B125" s="80" t="inlineStr">
+      <c r="B125" s="83" t="inlineStr">
         <is>
           <t>PS5-60-10 - Power Generation Package D</t>
         </is>
@@ -9690,7 +9705,7 @@
       <c r="D125" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E125" s="69" t="inlineStr">
+      <c r="E125" s="70" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -9748,7 +9763,7 @@
           <t>PS5-60-11</t>
         </is>
       </c>
-      <c r="B126" s="80" t="inlineStr">
+      <c r="B126" s="83" t="inlineStr">
         <is>
           <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
@@ -9759,7 +9774,7 @@
       <c r="D126" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E126" s="92" t="inlineStr">
+      <c r="E126" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9817,7 +9832,7 @@
           <t>PS5-60-12</t>
         </is>
       </c>
-      <c r="B127" s="80" t="inlineStr">
+      <c r="B127" s="83" t="inlineStr">
         <is>
           <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9828,7 +9843,7 @@
       <c r="D127" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E127" s="92" t="inlineStr">
+      <c r="E127" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9839,7 +9854,7 @@
       <c r="G127" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H127" s="68" t="inlineStr">
+      <c r="H127" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9869,7 +9884,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N127" s="68" t="inlineStr">
+      <c r="N127" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9886,7 +9901,7 @@
           <t>PS5-60-13</t>
         </is>
       </c>
-      <c r="B128" s="80" t="inlineStr">
+      <c r="B128" s="83" t="inlineStr">
         <is>
           <t>PS5-60-13 - Power Generation Package E</t>
         </is>
@@ -9897,7 +9912,7 @@
       <c r="D128" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="E128" s="69" t="inlineStr">
+      <c r="E128" s="70" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -9955,7 +9970,7 @@
           <t>PS5-60-14</t>
         </is>
       </c>
-      <c r="B129" s="80" t="inlineStr">
+      <c r="B129" s="83" t="inlineStr">
         <is>
           <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
@@ -9966,7 +9981,7 @@
       <c r="D129" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E129" s="92" t="inlineStr">
+      <c r="E129" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10024,7 +10039,7 @@
           <t>PS5-60-15</t>
         </is>
       </c>
-      <c r="B130" s="80" t="inlineStr">
+      <c r="B130" s="83" t="inlineStr">
         <is>
           <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10035,7 +10050,7 @@
       <c r="D130" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E130" s="92" t="inlineStr">
+      <c r="E130" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10046,7 +10061,7 @@
       <c r="G130" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H130" s="68" t="inlineStr">
+      <c r="H130" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10076,7 +10091,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N130" s="68" t="inlineStr">
+      <c r="N130" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10093,7 +10108,7 @@
           <t>PS5-60-16</t>
         </is>
       </c>
-      <c r="B131" s="80" t="inlineStr">
+      <c r="B131" s="83" t="inlineStr">
         <is>
           <t>PS5-60-16 - Power Generation Package F</t>
         </is>
@@ -10104,7 +10119,7 @@
       <c r="D131" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E131" s="69" t="inlineStr">
+      <c r="E131" s="70" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -10162,7 +10177,7 @@
           <t>PS5-60-17</t>
         </is>
       </c>
-      <c r="B132" s="80" t="inlineStr">
+      <c r="B132" s="83" t="inlineStr">
         <is>
           <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
@@ -10173,7 +10188,7 @@
       <c r="D132" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E132" s="92" t="inlineStr">
+      <c r="E132" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10214,7 +10229,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N132" s="68" t="inlineStr">
+      <c r="N132" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -10231,7 +10246,7 @@
           <t>PS5-60-18</t>
         </is>
       </c>
-      <c r="B133" s="80" t="inlineStr">
+      <c r="B133" s="83" t="inlineStr">
         <is>
           <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10242,7 +10257,7 @@
       <c r="D133" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E133" s="92" t="inlineStr">
+      <c r="E133" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10253,7 +10268,7 @@
       <c r="G133" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H133" s="68" t="inlineStr">
+      <c r="H133" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -10283,7 +10298,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N133" s="68" t="inlineStr">
+      <c r="N133" s="69" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -10300,7 +10315,7 @@
           <t>PS5-60-19</t>
         </is>
       </c>
-      <c r="B134" s="80" t="inlineStr">
+      <c r="B134" s="83" t="inlineStr">
         <is>
           <t>PS5-60-19 - Power Generation Package G</t>
         </is>
@@ -10311,7 +10326,7 @@
       <c r="D134" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E134" s="69" t="inlineStr">
+      <c r="E134" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -10369,7 +10384,7 @@
           <t>PS5-60-20</t>
         </is>
       </c>
-      <c r="B135" s="80" t="inlineStr">
+      <c r="B135" s="83" t="inlineStr">
         <is>
           <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
@@ -10380,7 +10395,7 @@
       <c r="D135" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E135" s="92" t="inlineStr">
+      <c r="E135" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10391,7 +10406,7 @@
       <c r="G135" s="23" t="n">
         <v>37</v>
       </c>
-      <c r="H135" s="68" t="inlineStr">
+      <c r="H135" s="69" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -10421,7 +10436,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N135" s="68" t="inlineStr">
+      <c r="N135" s="69" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -10438,7 +10453,7 @@
           <t>PS5-60-21</t>
         </is>
       </c>
-      <c r="B136" s="80" t="inlineStr">
+      <c r="B136" s="83" t="inlineStr">
         <is>
           <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10449,7 +10464,7 @@
       <c r="D136" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E136" s="92" t="inlineStr">
+      <c r="E136" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10490,7 +10505,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N136" s="68" t="inlineStr">
+      <c r="N136" s="69" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -10507,7 +10522,7 @@
           <t>PS5-60-22</t>
         </is>
       </c>
-      <c r="B137" s="80" t="inlineStr">
+      <c r="B137" s="83" t="inlineStr">
         <is>
           <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
@@ -10518,7 +10533,7 @@
       <c r="D137" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E137" s="69" t="inlineStr">
+      <c r="E137" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10529,7 +10544,7 @@
       <c r="G137" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="H137" s="68" t="inlineStr">
+      <c r="H137" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -10559,7 +10574,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N137" s="68" t="inlineStr">
+      <c r="N137" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -10576,7 +10591,7 @@
           <t>PS5-60-23</t>
         </is>
       </c>
-      <c r="B138" s="80" t="inlineStr">
+      <c r="B138" s="83" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -10587,7 +10602,7 @@
       <c r="D138" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E138" s="69" t="inlineStr">
+      <c r="E138" s="70" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -10645,7 +10660,7 @@
           <t>PS5-60-24</t>
         </is>
       </c>
-      <c r="B139" s="80" t="inlineStr">
+      <c r="B139" s="83" t="inlineStr">
         <is>
           <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
@@ -10656,7 +10671,7 @@
       <c r="D139" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E139" s="69" t="inlineStr">
+      <c r="E139" s="70" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -10714,7 +10729,7 @@
           <t>PS5-60-25</t>
         </is>
       </c>
-      <c r="B140" s="80" t="inlineStr">
+      <c r="B140" s="83" t="inlineStr">
         <is>
           <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
@@ -10725,7 +10740,7 @@
       <c r="D140" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E140" s="69" t="inlineStr">
+      <c r="E140" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -10783,7 +10798,7 @@
           <t>PS5-60-26</t>
         </is>
       </c>
-      <c r="B141" s="80" t="inlineStr">
+      <c r="B141" s="83" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -10794,7 +10809,7 @@
       <c r="D141" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E141" s="69" t="inlineStr">
+      <c r="E141" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -10852,7 +10867,7 @@
           <t>PS5-60-27</t>
         </is>
       </c>
-      <c r="B142" s="80" t="inlineStr">
+      <c r="B142" s="83" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -10863,7 +10878,7 @@
       <c r="D142" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E142" s="69" t="inlineStr">
+      <c r="E142" s="70" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -10921,7 +10936,7 @@
           <t>PS5-60-28</t>
         </is>
       </c>
-      <c r="B143" s="80" t="inlineStr">
+      <c r="B143" s="83" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -10932,7 +10947,7 @@
       <c r="D143" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E143" s="69" t="inlineStr">
+      <c r="E143" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -10978,7 +10993,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O143" s="68" t="inlineStr">
+      <c r="O143" s="69" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -10990,7 +11005,7 @@
           <t>PS5-60-29</t>
         </is>
       </c>
-      <c r="B144" s="80" t="inlineStr">
+      <c r="B144" s="83" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -11001,7 +11016,7 @@
       <c r="D144" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E144" s="69" t="inlineStr">
+      <c r="E144" s="70" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -11059,7 +11074,7 @@
           <t>PS5-60-30</t>
         </is>
       </c>
-      <c r="B145" s="80" t="inlineStr">
+      <c r="B145" s="83" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -11070,7 +11085,7 @@
       <c r="D145" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E145" s="69" t="inlineStr">
+      <c r="E145" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -11128,7 +11143,7 @@
           <t>PS5-60-31</t>
         </is>
       </c>
-      <c r="B146" s="80" t="inlineStr">
+      <c r="B146" s="83" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -11139,7 +11154,7 @@
       <c r="D146" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E146" s="69" t="inlineStr">
+      <c r="E146" s="70" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -11197,7 +11212,7 @@
           <t>PS5-60-32</t>
         </is>
       </c>
-      <c r="B147" s="80" t="inlineStr">
+      <c r="B147" s="83" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -11208,7 +11223,7 @@
       <c r="D147" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E147" s="68" t="inlineStr">
+      <c r="E147" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11266,7 +11281,7 @@
           <t>PS5-60-33</t>
         </is>
       </c>
-      <c r="B148" s="80" t="inlineStr">
+      <c r="B148" s="83" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -11277,7 +11292,7 @@
       <c r="D148" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E148" s="68" t="inlineStr">
+      <c r="E148" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11335,7 +11350,7 @@
           <t>PS5-60-34</t>
         </is>
       </c>
-      <c r="B149" s="80" t="inlineStr">
+      <c r="B149" s="83" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -11346,7 +11361,7 @@
       <c r="D149" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E149" s="69" t="inlineStr">
+      <c r="E149" s="70" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -11404,7 +11419,7 @@
           <t>PS5-60-35</t>
         </is>
       </c>
-      <c r="B150" s="80" t="inlineStr">
+      <c r="B150" s="83" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -11415,7 +11430,7 @@
       <c r="D150" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E150" s="69" t="inlineStr">
+      <c r="E150" s="70" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -11473,7 +11488,7 @@
           <t>PS5-60-36</t>
         </is>
       </c>
-      <c r="B151" s="80" t="inlineStr">
+      <c r="B151" s="83" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -11484,7 +11499,7 @@
       <c r="D151" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E151" s="69" t="inlineStr">
+      <c r="E151" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -11542,7 +11557,7 @@
           <t>PS5-60-37</t>
         </is>
       </c>
-      <c r="B152" s="80" t="inlineStr">
+      <c r="B152" s="83" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -11553,7 +11568,7 @@
       <c r="D152" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E152" s="69" t="inlineStr">
+      <c r="E152" s="70" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -11611,7 +11626,7 @@
           <t>PS5-60-38</t>
         </is>
       </c>
-      <c r="B153" s="80" t="inlineStr">
+      <c r="B153" s="83" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -11622,7 +11637,7 @@
       <c r="D153" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E153" s="68" t="inlineStr">
+      <c r="E153" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11680,7 +11695,7 @@
           <t>PS5-60-39</t>
         </is>
       </c>
-      <c r="B154" s="80" t="inlineStr">
+      <c r="B154" s="83" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -11691,7 +11706,7 @@
       <c r="D154" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E154" s="68" t="inlineStr">
+      <c r="E154" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -11749,7 +11764,7 @@
           <t>PS5-60-40</t>
         </is>
       </c>
-      <c r="B155" s="80" t="inlineStr">
+      <c r="B155" s="83" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -11760,7 +11775,7 @@
       <c r="D155" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E155" s="68" t="inlineStr">
+      <c r="E155" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -11818,7 +11833,7 @@
           <t>PS5-60-41</t>
         </is>
       </c>
-      <c r="B156" s="80" t="inlineStr">
+      <c r="B156" s="83" t="inlineStr">
         <is>
           <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
@@ -11829,7 +11844,7 @@
       <c r="D156" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E156" s="68" t="inlineStr">
+      <c r="E156" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -11840,7 +11855,7 @@
       <c r="G156" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="H156" s="68" t="inlineStr">
+      <c r="H156" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -11870,7 +11885,7 @@
           <t>16/17</t>
         </is>
       </c>
-      <c r="N156" s="68" t="inlineStr">
+      <c r="N156" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -11887,7 +11902,7 @@
           <t>PS5-60-42</t>
         </is>
       </c>
-      <c r="B157" s="80" t="inlineStr">
+      <c r="B157" s="83" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -11898,7 +11913,7 @@
       <c r="D157" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E157" s="69" t="inlineStr">
+      <c r="E157" s="70" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -11956,7 +11971,7 @@
           <t>PS5-60-43</t>
         </is>
       </c>
-      <c r="B158" s="80" t="inlineStr">
+      <c r="B158" s="83" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -11967,7 +11982,7 @@
       <c r="D158" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E158" s="69" t="inlineStr">
+      <c r="E158" s="70" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -12025,7 +12040,7 @@
           <t>PS5-60-44</t>
         </is>
       </c>
-      <c r="B159" s="80" t="inlineStr">
+      <c r="B159" s="83" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -12036,7 +12051,7 @@
       <c r="D159" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E159" s="69" t="inlineStr">
+      <c r="E159" s="70" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -12094,7 +12109,7 @@
           <t>PS5-60-45</t>
         </is>
       </c>
-      <c r="B160" s="80" t="inlineStr">
+      <c r="B160" s="83" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -12105,7 +12120,7 @@
       <c r="D160" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E160" s="69" t="inlineStr">
+      <c r="E160" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -12163,7 +12178,7 @@
           <t>PS5-60-46</t>
         </is>
       </c>
-      <c r="B161" s="80" t="inlineStr">
+      <c r="B161" s="83" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -12174,7 +12189,7 @@
       <c r="D161" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E161" s="68" t="inlineStr">
+      <c r="E161" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -12232,7 +12247,7 @@
           <t>PS5-60-47</t>
         </is>
       </c>
-      <c r="B162" s="80" t="inlineStr">
+      <c r="B162" s="83" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -12243,7 +12258,7 @@
       <c r="D162" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E162" s="68" t="inlineStr">
+      <c r="E162" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -12301,7 +12316,7 @@
           <t>PS5-60-48</t>
         </is>
       </c>
-      <c r="B163" s="80" t="inlineStr">
+      <c r="B163" s="83" t="inlineStr">
         <is>
           <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
@@ -12312,7 +12327,7 @@
       <c r="D163" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E163" s="69" t="inlineStr">
+      <c r="E163" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -12370,7 +12385,7 @@
           <t>PS5-60-49</t>
         </is>
       </c>
-      <c r="B164" s="80" t="inlineStr">
+      <c r="B164" s="83" t="inlineStr">
         <is>
           <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
@@ -12381,7 +12396,7 @@
       <c r="D164" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E164" s="69" t="inlineStr">
+      <c r="E164" s="70" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -12439,7 +12454,7 @@
           <t>PS5-60-50</t>
         </is>
       </c>
-      <c r="B165" s="80" t="inlineStr">
+      <c r="B165" s="83" t="inlineStr">
         <is>
           <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
@@ -12450,7 +12465,7 @@
       <c r="D165" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E165" s="69" t="inlineStr">
+      <c r="E165" s="70" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -12508,7 +12523,7 @@
           <t>PS5-60-51</t>
         </is>
       </c>
-      <c r="B166" s="80" t="inlineStr">
+      <c r="B166" s="83" t="inlineStr">
         <is>
           <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
@@ -12519,7 +12534,7 @@
       <c r="D166" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E166" s="68" t="inlineStr">
+      <c r="E166" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -12577,7 +12592,7 @@
           <t>PS5-60-52</t>
         </is>
       </c>
-      <c r="B167" s="80" t="inlineStr">
+      <c r="B167" s="83" t="inlineStr">
         <is>
           <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
@@ -12588,7 +12603,7 @@
       <c r="D167" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E167" s="69" t="inlineStr">
+      <c r="E167" s="70" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -12599,7 +12614,7 @@
       <c r="G167" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="H167" s="68" t="inlineStr">
+      <c r="H167" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -12629,7 +12644,7 @@
           <t>15/15</t>
         </is>
       </c>
-      <c r="N167" s="68" t="inlineStr">
+      <c r="N167" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -12646,7 +12661,7 @@
           <t>PS5-60-53</t>
         </is>
       </c>
-      <c r="B168" s="80" t="inlineStr">
+      <c r="B168" s="83" t="inlineStr">
         <is>
           <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
@@ -12657,7 +12672,7 @@
       <c r="D168" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E168" s="68" t="inlineStr">
+      <c r="E168" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -12715,7 +12730,7 @@
           <t>PS5-60-54</t>
         </is>
       </c>
-      <c r="B169" s="80" t="inlineStr">
+      <c r="B169" s="83" t="inlineStr">
         <is>
           <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
@@ -12726,7 +12741,7 @@
       <c r="D169" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E169" s="68" t="inlineStr">
+      <c r="E169" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -12784,7 +12799,7 @@
           <t>PS5-60-55</t>
         </is>
       </c>
-      <c r="B170" s="80" t="inlineStr">
+      <c r="B170" s="83" t="inlineStr">
         <is>
           <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
@@ -12806,7 +12821,7 @@
       <c r="G170" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="H170" s="68" t="inlineStr">
+      <c r="H170" s="69" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -12836,7 +12851,7 @@
           <t>14/15</t>
         </is>
       </c>
-      <c r="N170" s="68" t="inlineStr">
+      <c r="N170" s="69" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -12853,7 +12868,7 @@
           <t>PS5-60-56</t>
         </is>
       </c>
-      <c r="B171" s="80" t="inlineStr">
+      <c r="B171" s="83" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -12864,7 +12879,7 @@
       <c r="D171" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E171" s="69" t="inlineStr">
+      <c r="E171" s="70" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -12922,7 +12937,7 @@
           <t>PS5-60-57</t>
         </is>
       </c>
-      <c r="B172" s="80" t="inlineStr">
+      <c r="B172" s="83" t="inlineStr">
         <is>
           <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
@@ -12933,7 +12948,7 @@
       <c r="D172" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E172" s="69" t="inlineStr">
+      <c r="E172" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12991,7 +13006,7 @@
           <t>PS5-60-58</t>
         </is>
       </c>
-      <c r="B173" s="80" t="inlineStr">
+      <c r="B173" s="83" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -13002,7 +13017,7 @@
       <c r="D173" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E173" s="69" t="inlineStr">
+      <c r="E173" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -13060,7 +13075,7 @@
           <t>PS5-60-59</t>
         </is>
       </c>
-      <c r="B174" s="80" t="inlineStr">
+      <c r="B174" s="83" t="inlineStr">
         <is>
           <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
@@ -13071,7 +13086,7 @@
       <c r="D174" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E174" s="69" t="inlineStr">
+      <c r="E174" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13129,7 +13144,7 @@
           <t>PS5-60-60</t>
         </is>
       </c>
-      <c r="B175" s="80" t="inlineStr">
+      <c r="B175" s="83" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -13140,7 +13155,7 @@
       <c r="D175" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E175" s="69" t="inlineStr">
+      <c r="E175" s="70" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -13198,7 +13213,7 @@
           <t>PS5-60-61</t>
         </is>
       </c>
-      <c r="B176" s="80" t="inlineStr">
+      <c r="B176" s="83" t="inlineStr">
         <is>
           <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
@@ -13209,7 +13224,7 @@
       <c r="D176" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E176" s="92" t="inlineStr">
+      <c r="E176" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13267,7 +13282,7 @@
           <t>PS5-60-62</t>
         </is>
       </c>
-      <c r="B177" s="80" t="inlineStr">
+      <c r="B177" s="83" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -13278,7 +13293,7 @@
       <c r="D177" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E177" s="69" t="inlineStr">
+      <c r="E177" s="70" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -13336,7 +13351,7 @@
           <t>PS5-60-63</t>
         </is>
       </c>
-      <c r="B178" s="80" t="inlineStr">
+      <c r="B178" s="83" t="inlineStr">
         <is>
           <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
@@ -13347,7 +13362,7 @@
       <c r="D178" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E178" s="92" t="inlineStr">
+      <c r="E178" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13405,7 +13420,7 @@
           <t>PS5-60-64</t>
         </is>
       </c>
-      <c r="B179" s="80" t="inlineStr">
+      <c r="B179" s="83" t="inlineStr">
         <is>
           <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
@@ -13416,7 +13431,7 @@
       <c r="D179" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E179" s="68" t="inlineStr">
+      <c r="E179" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -13474,7 +13489,7 @@
           <t>PS5-60-65</t>
         </is>
       </c>
-      <c r="B180" s="80" t="inlineStr">
+      <c r="B180" s="83" t="inlineStr">
         <is>
           <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
@@ -13485,7 +13500,7 @@
       <c r="D180" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E180" s="92" t="inlineStr">
+      <c r="E180" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13526,7 +13541,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N180" s="68" t="inlineStr">
+      <c r="N180" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13543,7 +13558,7 @@
           <t>PS5-60-66</t>
         </is>
       </c>
-      <c r="B181" s="80" t="inlineStr">
+      <c r="B181" s="83" t="inlineStr">
         <is>
           <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
@@ -13554,7 +13569,7 @@
       <c r="D181" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E181" s="69" t="inlineStr">
+      <c r="E181" s="70" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -13612,7 +13627,7 @@
           <t>PS5-60-67</t>
         </is>
       </c>
-      <c r="B182" s="80" t="inlineStr">
+      <c r="B182" s="83" t="inlineStr">
         <is>
           <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
@@ -13623,7 +13638,7 @@
       <c r="D182" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E182" s="92" t="inlineStr">
+      <c r="E182" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13664,7 +13679,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N182" s="68" t="inlineStr">
+      <c r="N182" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13681,7 +13696,7 @@
           <t>PS5-60-68</t>
         </is>
       </c>
-      <c r="B183" s="80" t="inlineStr">
+      <c r="B183" s="83" t="inlineStr">
         <is>
           <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
@@ -13692,7 +13707,7 @@
       <c r="D183" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E183" s="69" t="inlineStr">
+      <c r="E183" s="70" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -13703,7 +13718,7 @@
       <c r="G183" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H183" s="68" t="inlineStr">
+      <c r="H183" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13733,7 +13748,7 @@
           <t>16/17</t>
         </is>
       </c>
-      <c r="N183" s="68" t="inlineStr">
+      <c r="N183" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -13750,7 +13765,7 @@
           <t>PS5-60-69</t>
         </is>
       </c>
-      <c r="B184" s="80" t="inlineStr">
+      <c r="B184" s="83" t="inlineStr">
         <is>
           <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
@@ -13761,7 +13776,7 @@
       <c r="D184" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E184" s="92" t="inlineStr">
+      <c r="E184" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13772,7 +13787,7 @@
       <c r="G184" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="H184" s="68" t="inlineStr">
+      <c r="H184" s="69" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -13802,7 +13817,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N184" s="68" t="inlineStr">
+      <c r="N184" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -13819,7 +13834,7 @@
           <t>PS5-60-70</t>
         </is>
       </c>
-      <c r="B185" s="80" t="inlineStr">
+      <c r="B185" s="83" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -13830,7 +13845,7 @@
       <c r="D185" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="E185" s="69" t="inlineStr">
+      <c r="E185" s="70" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -13888,7 +13903,7 @@
           <t>PS5-60-71</t>
         </is>
       </c>
-      <c r="B186" s="80" t="inlineStr">
+      <c r="B186" s="83" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -13899,7 +13914,7 @@
       <c r="D186" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="E186" s="69" t="inlineStr">
+      <c r="E186" s="70" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
@@ -13957,7 +13972,7 @@
           <t>PS5-60-72</t>
         </is>
       </c>
-      <c r="B187" s="80" t="inlineStr">
+      <c r="B187" s="83" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -13968,7 +13983,7 @@
       <c r="D187" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="E187" s="69" t="inlineStr">
+      <c r="E187" s="70" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
@@ -14026,7 +14041,7 @@
           <t>PS5-60-73</t>
         </is>
       </c>
-      <c r="B188" s="80" t="inlineStr">
+      <c r="B188" s="83" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -14037,7 +14052,7 @@
       <c r="D188" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E188" s="69" t="inlineStr">
+      <c r="E188" s="70" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -14095,7 +14110,7 @@
           <t>PS5-60-74</t>
         </is>
       </c>
-      <c r="B189" s="80" t="inlineStr">
+      <c r="B189" s="83" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -14106,7 +14121,7 @@
       <c r="D189" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E189" s="69" t="inlineStr">
+      <c r="E189" s="70" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -14164,7 +14179,7 @@
           <t>PS5-60-75</t>
         </is>
       </c>
-      <c r="B190" s="80" t="inlineStr">
+      <c r="B190" s="83" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -14175,7 +14190,7 @@
       <c r="D190" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E190" s="69" t="inlineStr">
+      <c r="E190" s="70" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -14233,7 +14248,7 @@
           <t>PS5-60-76</t>
         </is>
       </c>
-      <c r="B191" s="80" t="inlineStr">
+      <c r="B191" s="83" t="inlineStr">
         <is>
           <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
@@ -14244,7 +14259,7 @@
       <c r="D191" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E191" s="69" t="inlineStr">
+      <c r="E191" s="70" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -14302,7 +14317,7 @@
           <t>PS5-61-01</t>
         </is>
       </c>
-      <c r="B192" s="80" t="inlineStr">
+      <c r="B192" s="83" t="inlineStr">
         <is>
           <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
@@ -14313,7 +14328,7 @@
       <c r="D192" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E192" s="69" t="inlineStr">
+      <c r="E192" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -14371,7 +14386,7 @@
           <t>PS5-61-02</t>
         </is>
       </c>
-      <c r="B193" s="80" t="inlineStr">
+      <c r="B193" s="83" t="inlineStr">
         <is>
           <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
@@ -14382,7 +14397,7 @@
       <c r="D193" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E193" s="69" t="inlineStr">
+      <c r="E193" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14423,7 +14438,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N193" s="68" t="inlineStr">
+      <c r="N193" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -14440,7 +14455,7 @@
           <t>PS5-61-03</t>
         </is>
       </c>
-      <c r="B194" s="80" t="inlineStr">
+      <c r="B194" s="83" t="inlineStr">
         <is>
           <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
@@ -14451,7 +14466,7 @@
       <c r="D194" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E194" s="69" t="inlineStr">
+      <c r="E194" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -14492,7 +14507,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N194" s="68" t="inlineStr">
+      <c r="N194" s="69" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -14509,7 +14524,7 @@
           <t>PS5-61-04</t>
         </is>
       </c>
-      <c r="B195" s="80" t="inlineStr">
+      <c r="B195" s="83" t="inlineStr">
         <is>
           <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
@@ -14520,7 +14535,7 @@
       <c r="D195" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E195" s="92" t="inlineStr">
+      <c r="E195" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14531,7 +14546,7 @@
       <c r="G195" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H195" s="69" t="inlineStr">
+      <c r="H195" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14561,7 +14576,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N195" s="69" t="inlineStr">
+      <c r="N195" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14578,7 +14593,7 @@
           <t>PS5-61-05</t>
         </is>
       </c>
-      <c r="B196" s="80" t="inlineStr">
+      <c r="B196" s="83" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -14647,7 +14662,7 @@
           <t>PS5-61-06</t>
         </is>
       </c>
-      <c r="B197" s="80" t="inlineStr">
+      <c r="B197" s="83" t="inlineStr">
         <is>
           <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
@@ -14669,7 +14684,7 @@
       <c r="G197" s="23" t="n">
         <v>63</v>
       </c>
-      <c r="H197" s="68" t="inlineStr">
+      <c r="H197" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -14699,7 +14714,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N197" s="68" t="inlineStr">
+      <c r="N197" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -14716,7 +14731,7 @@
           <t>PS5-61-07</t>
         </is>
       </c>
-      <c r="B198" s="80" t="inlineStr">
+      <c r="B198" s="83" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -14727,7 +14742,7 @@
       <c r="D198" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E198" s="69" t="inlineStr">
+      <c r="E198" s="70" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -14785,7 +14800,7 @@
           <t>PS5-61-08</t>
         </is>
       </c>
-      <c r="B199" s="80" t="inlineStr">
+      <c r="B199" s="83" t="inlineStr">
         <is>
           <t>PS5-61-08 - Electrical Control System</t>
         </is>
@@ -14796,7 +14811,7 @@
       <c r="D199" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E199" s="68" t="inlineStr">
+      <c r="E199" s="69" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -14807,7 +14822,7 @@
       <c r="G199" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H199" s="69" t="inlineStr">
+      <c r="H199" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -14837,7 +14852,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N199" s="69" t="inlineStr">
+      <c r="N199" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -14854,7 +14869,7 @@
           <t>PS5-61-09</t>
         </is>
       </c>
-      <c r="B200" s="80" t="inlineStr">
+      <c r="B200" s="83" t="inlineStr">
         <is>
           <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
@@ -14865,7 +14880,7 @@
       <c r="D200" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E200" s="92" t="inlineStr">
+      <c r="E200" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14876,7 +14891,7 @@
       <c r="G200" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H200" s="69" t="inlineStr">
+      <c r="H200" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -14906,7 +14921,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N200" s="69" t="inlineStr">
+      <c r="N200" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -14923,7 +14938,7 @@
           <t>PS5-61-10</t>
         </is>
       </c>
-      <c r="B201" s="80" t="inlineStr">
+      <c r="B201" s="83" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -14934,7 +14949,7 @@
       <c r="D201" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E201" s="92" t="inlineStr">
+      <c r="E201" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14992,7 +15007,7 @@
           <t>PS5-61-11</t>
         </is>
       </c>
-      <c r="B202" s="80" t="inlineStr">
+      <c r="B202" s="83" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -15003,7 +15018,7 @@
       <c r="D202" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E202" s="92" t="inlineStr">
+      <c r="E202" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15061,7 +15076,7 @@
           <t>PS5-61-12</t>
         </is>
       </c>
-      <c r="B203" s="80" t="inlineStr">
+      <c r="B203" s="83" t="inlineStr">
         <is>
           <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
@@ -15072,7 +15087,7 @@
       <c r="D203" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E203" s="92" t="inlineStr">
+      <c r="E203" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15083,7 +15098,7 @@
       <c r="G203" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H203" s="92" t="inlineStr">
+      <c r="H203" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15113,7 +15128,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N203" s="69" t="inlineStr">
+      <c r="N203" s="70" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -15130,7 +15145,7 @@
           <t>PS5-61-13</t>
         </is>
       </c>
-      <c r="B204" s="80" t="inlineStr">
+      <c r="B204" s="83" t="inlineStr">
         <is>
           <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
@@ -15141,7 +15156,7 @@
       <c r="D204" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E204" s="92" t="inlineStr">
+      <c r="E204" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15152,7 +15167,7 @@
       <c r="G204" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H204" s="69" t="inlineStr">
+      <c r="H204" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15182,7 +15197,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N204" s="69" t="inlineStr">
+      <c r="N204" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15199,7 +15214,7 @@
           <t>PS5-61-14</t>
         </is>
       </c>
-      <c r="B205" s="80" t="inlineStr">
+      <c r="B205" s="83" t="inlineStr">
         <is>
           <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
@@ -15210,7 +15225,7 @@
       <c r="D205" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E205" s="92" t="inlineStr">
+      <c r="E205" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15221,7 +15236,7 @@
       <c r="G205" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H205" s="69" t="inlineStr">
+      <c r="H205" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15251,7 +15266,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N205" s="69" t="inlineStr">
+      <c r="N205" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15268,7 +15283,7 @@
           <t>PS5-62-01</t>
         </is>
       </c>
-      <c r="B206" s="80" t="inlineStr">
+      <c r="B206" s="83" t="inlineStr">
         <is>
           <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
@@ -15290,7 +15305,7 @@
       <c r="G206" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H206" s="69" t="inlineStr">
+      <c r="H206" s="70" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -15320,7 +15335,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N206" s="69" t="inlineStr">
+      <c r="N206" s="70" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -15337,7 +15352,7 @@
           <t>PS5-62-02</t>
         </is>
       </c>
-      <c r="B207" s="80" t="inlineStr">
+      <c r="B207" s="83" t="inlineStr">
         <is>
           <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
@@ -15359,7 +15374,7 @@
       <c r="G207" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H207" s="69" t="inlineStr">
+      <c r="H207" s="70" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -15389,7 +15404,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N207" s="69" t="inlineStr">
+      <c r="N207" s="70" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -15406,7 +15421,7 @@
           <t>PS5-62-03</t>
         </is>
       </c>
-      <c r="B208" s="80" t="inlineStr">
+      <c r="B208" s="83" t="inlineStr">
         <is>
           <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
@@ -15417,7 +15432,7 @@
       <c r="D208" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E208" s="92" t="inlineStr">
+      <c r="E208" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15428,7 +15443,7 @@
       <c r="G208" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H208" s="68" t="inlineStr">
+      <c r="H208" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15458,7 +15473,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N208" s="68" t="inlineStr">
+      <c r="N208" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -15475,7 +15490,7 @@
           <t>PS5-62-04</t>
         </is>
       </c>
-      <c r="B209" s="80" t="inlineStr">
+      <c r="B209" s="83" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -15486,7 +15501,7 @@
       <c r="D209" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E209" s="92" t="inlineStr">
+      <c r="E209" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15544,7 +15559,7 @@
           <t>PS5-62-05</t>
         </is>
       </c>
-      <c r="B210" s="80" t="inlineStr">
+      <c r="B210" s="83" t="inlineStr">
         <is>
           <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
@@ -15555,7 +15570,7 @@
       <c r="D210" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E210" s="92" t="inlineStr">
+      <c r="E210" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15566,7 +15581,7 @@
       <c r="G210" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H210" s="69" t="inlineStr">
+      <c r="H210" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15596,7 +15611,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N210" s="69" t="inlineStr">
+      <c r="N210" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15613,7 +15628,7 @@
           <t>PS5-62-06</t>
         </is>
       </c>
-      <c r="B211" s="80" t="inlineStr">
+      <c r="B211" s="83" t="inlineStr">
         <is>
           <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
@@ -15624,7 +15639,7 @@
       <c r="D211" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E211" s="92" t="inlineStr">
+      <c r="E211" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15635,7 +15650,7 @@
       <c r="G211" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H211" s="69" t="inlineStr">
+      <c r="H211" s="70" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -15665,7 +15680,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N211" s="69" t="inlineStr">
+      <c r="N211" s="70" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -15682,7 +15697,7 @@
           <t>PS5-62-07</t>
         </is>
       </c>
-      <c r="B212" s="80" t="inlineStr">
+      <c r="B212" s="83" t="inlineStr">
         <is>
           <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
@@ -15693,7 +15708,7 @@
       <c r="D212" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E212" s="69" t="inlineStr">
+      <c r="E212" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15704,7 +15719,7 @@
       <c r="G212" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H212" s="69" t="inlineStr">
+      <c r="H212" s="70" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -15734,7 +15749,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N212" s="69" t="inlineStr">
+      <c r="N212" s="70" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -15751,7 +15766,7 @@
           <t>PS5-62-08</t>
         </is>
       </c>
-      <c r="B213" s="80" t="inlineStr">
+      <c r="B213" s="83" t="inlineStr">
         <is>
           <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
@@ -15762,7 +15777,7 @@
       <c r="D213" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E213" s="92" t="inlineStr">
+      <c r="E213" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15773,7 +15788,7 @@
       <c r="G213" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H213" s="69" t="inlineStr">
+      <c r="H213" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -15803,7 +15818,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N213" s="69" t="inlineStr">
+      <c r="N213" s="70" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -15820,7 +15835,7 @@
           <t>PS5-62-09</t>
         </is>
       </c>
-      <c r="B214" s="80" t="inlineStr">
+      <c r="B214" s="83" t="inlineStr">
         <is>
           <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
@@ -15831,7 +15846,7 @@
       <c r="D214" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E214" s="69" t="inlineStr">
+      <c r="E214" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15842,7 +15857,7 @@
       <c r="G214" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H214" s="69" t="inlineStr">
+      <c r="H214" s="70" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -15872,7 +15887,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N214" s="69" t="inlineStr">
+      <c r="N214" s="70" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -15889,7 +15904,7 @@
           <t>PS5-62-10</t>
         </is>
       </c>
-      <c r="B215" s="80" t="inlineStr">
+      <c r="B215" s="83" t="inlineStr">
         <is>
           <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
@@ -15900,7 +15915,7 @@
       <c r="D215" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E215" s="69" t="inlineStr">
+      <c r="E215" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15911,7 +15926,7 @@
       <c r="G215" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="H215" s="69" t="inlineStr">
+      <c r="H215" s="70" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -15941,7 +15956,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N215" s="69" t="inlineStr">
+      <c r="N215" s="70" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -15958,7 +15973,7 @@
           <t>PS5-62-11</t>
         </is>
       </c>
-      <c r="B216" s="80" t="inlineStr">
+      <c r="B216" s="83" t="inlineStr">
         <is>
           <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
@@ -15969,7 +15984,7 @@
       <c r="D216" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E216" s="92" t="inlineStr">
+      <c r="E216" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15980,7 +15995,7 @@
       <c r="G216" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H216" s="69" t="inlineStr">
+      <c r="H216" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -16010,7 +16025,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N216" s="69" t="inlineStr">
+      <c r="N216" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -16027,7 +16042,7 @@
           <t>PS5-62-12</t>
         </is>
       </c>
-      <c r="B217" s="80" t="inlineStr">
+      <c r="B217" s="83" t="inlineStr">
         <is>
           <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
@@ -16038,7 +16053,7 @@
       <c r="D217" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E217" s="92" t="inlineStr">
+      <c r="E217" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16049,7 +16064,7 @@
       <c r="G217" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H217" s="92" t="inlineStr">
+      <c r="H217" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16096,7 +16111,7 @@
           <t>PS5-62-13</t>
         </is>
       </c>
-      <c r="B218" s="80" t="inlineStr">
+      <c r="B218" s="83" t="inlineStr">
         <is>
           <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
@@ -16107,7 +16122,7 @@
       <c r="D218" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E218" s="69" t="inlineStr">
+      <c r="E218" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16118,7 +16133,7 @@
       <c r="G218" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H218" s="92" t="inlineStr">
+      <c r="H218" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16165,7 +16180,7 @@
           <t>PS5-62-14</t>
         </is>
       </c>
-      <c r="B219" s="80" t="inlineStr">
+      <c r="B219" s="83" t="inlineStr">
         <is>
           <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
@@ -16176,7 +16191,7 @@
       <c r="D219" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E219" s="92" t="inlineStr">
+      <c r="E219" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16187,7 +16202,7 @@
       <c r="G219" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H219" s="69" t="inlineStr">
+      <c r="H219" s="70" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16217,7 +16232,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N219" s="69" t="inlineStr">
+      <c r="N219" s="70" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16234,7 +16249,7 @@
           <t>PS5-62-15</t>
         </is>
       </c>
-      <c r="B220" s="80" t="inlineStr">
+      <c r="B220" s="83" t="inlineStr">
         <is>
           <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
@@ -16245,7 +16260,7 @@
       <c r="D220" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E220" s="92" t="inlineStr">
+      <c r="E220" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16256,7 +16271,7 @@
       <c r="G220" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H220" s="69" t="inlineStr">
+      <c r="H220" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16286,7 +16301,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N220" s="69" t="inlineStr">
+      <c r="N220" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16303,7 +16318,7 @@
           <t>PS5-62-16</t>
         </is>
       </c>
-      <c r="B221" s="80" t="inlineStr">
+      <c r="B221" s="83" t="inlineStr">
         <is>
           <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
@@ -16314,7 +16329,7 @@
       <c r="D221" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E221" s="92" t="inlineStr">
+      <c r="E221" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16325,7 +16340,7 @@
       <c r="G221" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H221" s="69" t="inlineStr">
+      <c r="H221" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16355,7 +16370,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N221" s="69" t="inlineStr">
+      <c r="N221" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16372,7 +16387,7 @@
           <t>PS5-62-17</t>
         </is>
       </c>
-      <c r="B222" s="80" t="inlineStr">
+      <c r="B222" s="83" t="inlineStr">
         <is>
           <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
@@ -16383,7 +16398,7 @@
       <c r="D222" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E222" s="92" t="inlineStr">
+      <c r="E222" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16394,7 +16409,7 @@
       <c r="G222" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H222" s="69" t="inlineStr">
+      <c r="H222" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16424,7 +16439,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N222" s="69" t="inlineStr">
+      <c r="N222" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16441,7 +16456,7 @@
           <t>PS5-62-18</t>
         </is>
       </c>
-      <c r="B223" s="80" t="inlineStr">
+      <c r="B223" s="83" t="inlineStr">
         <is>
           <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
@@ -16452,7 +16467,7 @@
       <c r="D223" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E223" s="92" t="inlineStr">
+      <c r="E223" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16463,7 +16478,7 @@
       <c r="G223" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H223" s="69" t="inlineStr">
+      <c r="H223" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16493,7 +16508,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N223" s="69" t="inlineStr">
+      <c r="N223" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16510,7 +16525,7 @@
           <t>PS5-62-19</t>
         </is>
       </c>
-      <c r="B224" s="80" t="inlineStr">
+      <c r="B224" s="83" t="inlineStr">
         <is>
           <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
@@ -16521,7 +16536,7 @@
       <c r="D224" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E224" s="92" t="inlineStr">
+      <c r="E224" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16532,7 +16547,7 @@
       <c r="G224" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H224" s="69" t="inlineStr">
+      <c r="H224" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16562,7 +16577,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N224" s="69" t="inlineStr">
+      <c r="N224" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16579,7 +16594,7 @@
           <t>PS5-62-20</t>
         </is>
       </c>
-      <c r="B225" s="80" t="inlineStr">
+      <c r="B225" s="83" t="inlineStr">
         <is>
           <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
@@ -16590,7 +16605,7 @@
       <c r="D225" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E225" s="92" t="inlineStr">
+      <c r="E225" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16601,7 +16616,7 @@
       <c r="G225" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H225" s="69" t="inlineStr">
+      <c r="H225" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16631,7 +16646,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N225" s="69" t="inlineStr">
+      <c r="N225" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16648,7 +16663,7 @@
           <t>PS5-63-01</t>
         </is>
       </c>
-      <c r="B226" s="80" t="inlineStr">
+      <c r="B226" s="83" t="inlineStr">
         <is>
           <t>PS5-63-01 - Electrical Earthing</t>
         </is>
@@ -16659,7 +16674,7 @@
       <c r="D226" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E226" s="69" t="inlineStr">
+      <c r="E226" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16670,7 +16685,7 @@
       <c r="G226" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="H226" s="69" t="inlineStr">
+      <c r="H226" s="70" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -16700,7 +16715,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N226" s="69" t="inlineStr">
+      <c r="N226" s="70" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -16717,7 +16732,7 @@
           <t>PS5-63-02</t>
         </is>
       </c>
-      <c r="B227" s="80" t="inlineStr">
+      <c r="B227" s="83" t="inlineStr">
         <is>
           <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
@@ -16728,7 +16743,7 @@
       <c r="D227" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E227" s="92" t="inlineStr">
+      <c r="E227" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16739,7 +16754,7 @@
       <c r="G227" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H227" s="69" t="inlineStr">
+      <c r="H227" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16769,7 +16784,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N227" s="69" t="inlineStr">
+      <c r="N227" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16786,7 +16801,7 @@
           <t>PS5-63-03</t>
         </is>
       </c>
-      <c r="B228" s="80" t="inlineStr">
+      <c r="B228" s="83" t="inlineStr">
         <is>
           <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
@@ -16797,7 +16812,7 @@
       <c r="D228" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E228" s="92" t="inlineStr">
+      <c r="E228" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16808,7 +16823,7 @@
       <c r="G228" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H228" s="68" t="inlineStr">
+      <c r="H228" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16838,7 +16853,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N228" s="68" t="inlineStr">
+      <c r="N228" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16855,7 +16870,7 @@
           <t>PS5-63-04</t>
         </is>
       </c>
-      <c r="B229" s="80" t="inlineStr">
+      <c r="B229" s="83" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -16866,7 +16881,7 @@
       <c r="D229" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E229" s="69" t="inlineStr">
+      <c r="E229" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -16877,7 +16892,7 @@
       <c r="G229" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H229" s="92" t="inlineStr">
+      <c r="H229" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16924,7 +16939,7 @@
           <t>PS5-63-05</t>
         </is>
       </c>
-      <c r="B230" s="80" t="inlineStr">
+      <c r="B230" s="83" t="inlineStr">
         <is>
           <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
@@ -16935,7 +16950,7 @@
       <c r="D230" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E230" s="92" t="inlineStr">
+      <c r="E230" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16946,7 +16961,7 @@
       <c r="G230" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H230" s="69" t="inlineStr">
+      <c r="H230" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16976,7 +16991,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N230" s="69" t="inlineStr">
+      <c r="N230" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16993,7 +17008,7 @@
           <t>PS5-63-06</t>
         </is>
       </c>
-      <c r="B231" s="80" t="inlineStr">
+      <c r="B231" s="83" t="inlineStr">
         <is>
           <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
@@ -17004,7 +17019,7 @@
       <c r="D231" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E231" s="92" t="inlineStr">
+      <c r="E231" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17015,7 +17030,7 @@
       <c r="G231" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H231" s="69" t="inlineStr">
+      <c r="H231" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17045,7 +17060,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N231" s="69" t="inlineStr">
+      <c r="N231" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17062,7 +17077,7 @@
           <t>PS5-63-07</t>
         </is>
       </c>
-      <c r="B232" s="80" t="inlineStr">
+      <c r="B232" s="83" t="inlineStr">
         <is>
           <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
@@ -17073,7 +17088,7 @@
       <c r="D232" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E232" s="92" t="inlineStr">
+      <c r="E232" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17084,7 +17099,7 @@
       <c r="G232" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H232" s="69" t="inlineStr">
+      <c r="H232" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17114,7 +17129,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N232" s="69" t="inlineStr">
+      <c r="N232" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17131,7 +17146,7 @@
           <t>PS5-71-01</t>
         </is>
       </c>
-      <c r="B233" s="80" t="inlineStr">
+      <c r="B233" s="83" t="inlineStr">
         <is>
           <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
@@ -17142,7 +17157,7 @@
       <c r="D233" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E233" s="69" t="inlineStr">
+      <c r="E233" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -17153,7 +17168,7 @@
       <c r="G233" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="H233" s="69" t="inlineStr">
+      <c r="H233" s="70" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -17183,7 +17198,7 @@
           <t>27/30</t>
         </is>
       </c>
-      <c r="N233" s="69" t="inlineStr">
+      <c r="N233" s="70" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -17200,7 +17215,7 @@
           <t>PS5-71-02</t>
         </is>
       </c>
-      <c r="B234" s="80" t="inlineStr">
+      <c r="B234" s="83" t="inlineStr">
         <is>
           <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
@@ -17211,7 +17226,7 @@
       <c r="D234" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E234" s="69" t="inlineStr">
+      <c r="E234" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -17222,7 +17237,7 @@
       <c r="G234" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H234" s="68" t="inlineStr">
+      <c r="H234" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -17252,7 +17267,7 @@
           <t>9/10</t>
         </is>
       </c>
-      <c r="N234" s="68" t="inlineStr">
+      <c r="N234" s="69" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -17269,7 +17284,7 @@
           <t>PS5-71-03</t>
         </is>
       </c>
-      <c r="B235" s="80" t="inlineStr">
+      <c r="B235" s="83" t="inlineStr">
         <is>
           <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
@@ -17280,7 +17295,7 @@
       <c r="D235" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E235" s="92" t="inlineStr">
+      <c r="E235" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17291,7 +17306,7 @@
       <c r="G235" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H235" s="92" t="inlineStr">
+      <c r="H235" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17321,7 +17336,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N235" s="69" t="inlineStr">
+      <c r="N235" s="70" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -17338,7 +17353,7 @@
           <t>PS5-71-04</t>
         </is>
       </c>
-      <c r="B236" s="80" t="inlineStr">
+      <c r="B236" s="83" t="inlineStr">
         <is>
           <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
@@ -17349,7 +17364,7 @@
       <c r="D236" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E236" s="68" t="inlineStr">
+      <c r="E236" s="69" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -17360,7 +17375,7 @@
       <c r="G236" s="23" t="n">
         <v>66</v>
       </c>
-      <c r="H236" s="68" t="inlineStr">
+      <c r="H236" s="69" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -17390,7 +17405,7 @@
           <t>42/47</t>
         </is>
       </c>
-      <c r="N236" s="68" t="inlineStr">
+      <c r="N236" s="69" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -17407,7 +17422,7 @@
           <t>PS5-71-05</t>
         </is>
       </c>
-      <c r="B237" s="80" t="inlineStr">
+      <c r="B237" s="83" t="inlineStr">
         <is>
           <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
@@ -17418,7 +17433,7 @@
       <c r="D237" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E237" s="69" t="inlineStr">
+      <c r="E237" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -17429,7 +17444,7 @@
       <c r="G237" s="23" t="n">
         <v>48</v>
       </c>
-      <c r="H237" s="68" t="inlineStr">
+      <c r="H237" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -17459,7 +17474,7 @@
           <t>13/14</t>
         </is>
       </c>
-      <c r="N237" s="68" t="inlineStr">
+      <c r="N237" s="69" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -17476,7 +17491,7 @@
           <t>PS5-71-06</t>
         </is>
       </c>
-      <c r="B238" s="80" t="inlineStr">
+      <c r="B238" s="83" t="inlineStr">
         <is>
           <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
@@ -17487,7 +17502,7 @@
       <c r="D238" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E238" s="68" t="inlineStr">
+      <c r="E238" s="69" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -17498,7 +17513,7 @@
       <c r="G238" s="23" t="n">
         <v>36</v>
       </c>
-      <c r="H238" s="68" t="inlineStr">
+      <c r="H238" s="69" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -17528,7 +17543,7 @@
           <t>21/22</t>
         </is>
       </c>
-      <c r="N238" s="68" t="inlineStr">
+      <c r="N238" s="69" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -17545,7 +17560,7 @@
           <t>PS5-71-07</t>
         </is>
       </c>
-      <c r="B239" s="80" t="inlineStr">
+      <c r="B239" s="83" t="inlineStr">
         <is>
           <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
@@ -17556,7 +17571,7 @@
       <c r="D239" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E239" s="69" t="inlineStr">
+      <c r="E239" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17567,7 +17582,7 @@
       <c r="G239" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H239" s="68" t="inlineStr">
+      <c r="H239" s="69" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17597,7 +17612,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N239" s="68" t="inlineStr">
+      <c r="N239" s="69" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17614,7 +17629,7 @@
           <t>PS5-71-08</t>
         </is>
       </c>
-      <c r="B240" s="80" t="inlineStr">
+      <c r="B240" s="83" t="inlineStr">
         <is>
           <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
@@ -17625,7 +17640,7 @@
       <c r="D240" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E240" s="69" t="inlineStr">
+      <c r="E240" s="70" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -17683,7 +17698,7 @@
           <t>PS5-71-09</t>
         </is>
       </c>
-      <c r="B241" s="80" t="inlineStr">
+      <c r="B241" s="83" t="inlineStr">
         <is>
           <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
@@ -17694,7 +17709,7 @@
       <c r="D241" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E241" s="69" t="inlineStr">
+      <c r="E241" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17752,7 +17767,7 @@
           <t>PS5-71-12</t>
         </is>
       </c>
-      <c r="B242" s="80" t="inlineStr">
+      <c r="B242" s="83" t="inlineStr">
         <is>
           <t>PS5-71-12 - CFO Service Tank</t>
         </is>
@@ -17763,7 +17778,7 @@
       <c r="D242" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="E242" s="68" t="inlineStr">
+      <c r="E242" s="69" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -17774,7 +17789,7 @@
       <c r="G242" s="23" t="n">
         <v>66</v>
       </c>
-      <c r="H242" s="68" t="inlineStr">
+      <c r="H242" s="69" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17804,7 +17819,7 @@
           <t>26/31</t>
         </is>
       </c>
-      <c r="N242" s="68" t="inlineStr">
+      <c r="N242" s="69" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -17821,7 +17836,7 @@
           <t>PS5-71-13</t>
         </is>
       </c>
-      <c r="B243" s="80" t="inlineStr">
+      <c r="B243" s="83" t="inlineStr">
         <is>
           <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
@@ -17832,7 +17847,7 @@
       <c r="D243" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E243" s="69" t="inlineStr">
+      <c r="E243" s="70" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -17843,7 +17858,7 @@
       <c r="G243" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="H243" s="68" t="inlineStr">
+      <c r="H243" s="69" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -17873,7 +17888,7 @@
           <t>12/14</t>
         </is>
       </c>
-      <c r="N243" s="68" t="inlineStr">
+      <c r="N243" s="69" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -17890,7 +17905,7 @@
           <t>PS5-71-14</t>
         </is>
       </c>
-      <c r="B244" s="80" t="inlineStr">
+      <c r="B244" s="83" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
@@ -17901,7 +17916,7 @@
       <c r="D244" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E244" s="69" t="inlineStr">
+      <c r="E244" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -17942,7 +17957,7 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N244" s="68" t="inlineStr">
+      <c r="N244" s="69" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -17959,7 +17974,7 @@
           <t>PS5-71-15</t>
         </is>
       </c>
-      <c r="B245" s="80" t="inlineStr">
+      <c r="B245" s="83" t="inlineStr">
         <is>
           <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
@@ -17970,7 +17985,7 @@
       <c r="D245" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E245" s="69" t="inlineStr">
+      <c r="E245" s="70" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
@@ -17981,7 +17996,7 @@
       <c r="G245" s="23" t="n">
         <v>41</v>
       </c>
-      <c r="H245" s="68" t="inlineStr">
+      <c r="H245" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -18011,7 +18026,7 @@
           <t>17/20</t>
         </is>
       </c>
-      <c r="N245" s="68" t="inlineStr">
+      <c r="N245" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -18028,7 +18043,7 @@
           <t>PS5-71-16</t>
         </is>
       </c>
-      <c r="B246" s="80" t="inlineStr">
+      <c r="B246" s="83" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
@@ -18039,7 +18054,7 @@
       <c r="D246" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E246" s="69" t="inlineStr">
+      <c r="E246" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18080,7 +18095,7 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N246" s="68" t="inlineStr">
+      <c r="N246" s="69" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -18097,7 +18112,7 @@
           <t>PS5-71-17</t>
         </is>
       </c>
-      <c r="B247" s="80" t="inlineStr">
+      <c r="B247" s="83" t="inlineStr">
         <is>
           <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
@@ -18108,7 +18123,7 @@
       <c r="D247" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E247" s="69" t="inlineStr">
+      <c r="E247" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18166,7 +18181,7 @@
           <t>PS5-71-18</t>
         </is>
       </c>
-      <c r="B248" s="80" t="inlineStr">
+      <c r="B248" s="83" t="inlineStr">
         <is>
           <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
@@ -18177,7 +18192,7 @@
       <c r="D248" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E248" s="68" t="inlineStr">
+      <c r="E248" s="69" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
@@ -18188,7 +18203,7 @@
       <c r="G248" s="23" t="n">
         <v>47</v>
       </c>
-      <c r="H248" s="68" t="inlineStr">
+      <c r="H248" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18218,7 +18233,7 @@
           <t>20/20</t>
         </is>
       </c>
-      <c r="N248" s="68" t="inlineStr">
+      <c r="N248" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18235,7 +18250,7 @@
           <t>PS5-71-19</t>
         </is>
       </c>
-      <c r="B249" s="80" t="inlineStr">
+      <c r="B249" s="83" t="inlineStr">
         <is>
           <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
@@ -18246,7 +18261,7 @@
       <c r="D249" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E249" s="69" t="inlineStr">
+      <c r="E249" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18257,7 +18272,7 @@
       <c r="G249" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="H249" s="68" t="inlineStr">
+      <c r="H249" s="69" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -18287,7 +18302,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N249" s="68" t="inlineStr">
+      <c r="N249" s="69" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -18304,7 +18319,7 @@
           <t>PS5-71-20</t>
         </is>
       </c>
-      <c r="B250" s="80" t="inlineStr">
+      <c r="B250" s="83" t="inlineStr">
         <is>
           <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
@@ -18315,7 +18330,7 @@
       <c r="D250" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E250" s="68" t="inlineStr">
+      <c r="E250" s="69" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -18326,7 +18341,7 @@
       <c r="G250" s="23" t="n">
         <v>49</v>
       </c>
-      <c r="H250" s="68" t="inlineStr">
+      <c r="H250" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18356,7 +18371,7 @@
           <t>20/20</t>
         </is>
       </c>
-      <c r="N250" s="68" t="inlineStr">
+      <c r="N250" s="69" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -18373,7 +18388,7 @@
           <t>PS5-71-21</t>
         </is>
       </c>
-      <c r="B251" s="80" t="inlineStr">
+      <c r="B251" s="83" t="inlineStr">
         <is>
           <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
@@ -18384,7 +18399,7 @@
       <c r="D251" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E251" s="69" t="inlineStr">
+      <c r="E251" s="70" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -18442,7 +18457,7 @@
           <t>PS5-71-22</t>
         </is>
       </c>
-      <c r="B252" s="80" t="inlineStr">
+      <c r="B252" s="83" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -18453,7 +18468,7 @@
       <c r="D252" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="E252" s="69" t="inlineStr">
+      <c r="E252" s="70" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -18511,7 +18526,7 @@
           <t>PS5-71-23</t>
         </is>
       </c>
-      <c r="B253" s="80" t="inlineStr">
+      <c r="B253" s="83" t="inlineStr">
         <is>
           <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
@@ -18522,7 +18537,7 @@
       <c r="D253" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E253" s="69" t="inlineStr">
+      <c r="E253" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -18533,7 +18548,7 @@
       <c r="G253" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H253" s="68" t="inlineStr">
+      <c r="H253" s="69" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -18563,7 +18578,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N253" s="68" t="inlineStr">
+      <c r="N253" s="69" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -18580,7 +18595,7 @@
           <t>PS5-74-01</t>
         </is>
       </c>
-      <c r="B254" s="80" t="inlineStr">
+      <c r="B254" s="83" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
@@ -18591,7 +18606,7 @@
       <c r="D254" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E254" s="69" t="inlineStr">
+      <c r="E254" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -18602,7 +18617,7 @@
       <c r="G254" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H254" s="68" t="inlineStr">
+      <c r="H254" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -18632,7 +18647,7 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="N254" s="68" t="inlineStr">
+      <c r="N254" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -18649,7 +18664,7 @@
           <t>PS5-74-02</t>
         </is>
       </c>
-      <c r="B255" s="80" t="inlineStr">
+      <c r="B255" s="83" t="inlineStr">
         <is>
           <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
@@ -18671,7 +18686,7 @@
       <c r="G255" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H255" s="68" t="inlineStr">
+      <c r="H255" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -18701,7 +18716,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N255" s="68" t="inlineStr">
+      <c r="N255" s="69" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -18718,7 +18733,7 @@
           <t>PS5-74-03</t>
         </is>
       </c>
-      <c r="B256" s="80" t="inlineStr">
+      <c r="B256" s="83" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -18729,7 +18744,7 @@
       <c r="D256" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E256" s="69" t="inlineStr">
+      <c r="E256" s="70" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -18787,7 +18802,7 @@
           <t>PS5-74-04</t>
         </is>
       </c>
-      <c r="B257" s="80" t="inlineStr">
+      <c r="B257" s="83" t="inlineStr">
         <is>
           <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
@@ -18798,7 +18813,7 @@
       <c r="D257" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E257" s="92" t="inlineStr">
+      <c r="E257" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18809,7 +18824,7 @@
       <c r="G257" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="H257" s="68" t="inlineStr">
+      <c r="H257" s="69" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -18839,7 +18854,7 @@
           <t>6/8</t>
         </is>
       </c>
-      <c r="N257" s="68" t="inlineStr">
+      <c r="N257" s="69" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
@@ -18856,7 +18871,7 @@
           <t>PS5-75-01</t>
         </is>
       </c>
-      <c r="B258" s="80" t="inlineStr">
+      <c r="B258" s="83" t="inlineStr">
         <is>
           <t>PS5-75-01 - DRA Injection Package</t>
         </is>
@@ -18867,7 +18882,7 @@
       <c r="D258" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E258" s="92" t="inlineStr">
+      <c r="E258" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18878,7 +18893,7 @@
       <c r="G258" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H258" s="69" t="inlineStr">
+      <c r="H258" s="70" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -18908,7 +18923,7 @@
           <t>12/15</t>
         </is>
       </c>
-      <c r="N258" s="69" t="inlineStr">
+      <c r="N258" s="70" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -18925,7 +18940,7 @@
           <t>PS5-75-02</t>
         </is>
       </c>
-      <c r="B259" s="80" t="inlineStr">
+      <c r="B259" s="83" t="inlineStr">
         <is>
           <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
@@ -18936,7 +18951,7 @@
       <c r="D259" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E259" s="69" t="inlineStr">
+      <c r="E259" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -18947,7 +18962,7 @@
       <c r="G259" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H259" s="68" t="inlineStr">
+      <c r="H259" s="69" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -18977,7 +18992,7 @@
           <t>13/14</t>
         </is>
       </c>
-      <c r="N259" s="68" t="inlineStr">
+      <c r="N259" s="69" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -18994,7 +19009,7 @@
           <t>PS5-75-03</t>
         </is>
       </c>
-      <c r="B260" s="80" t="inlineStr">
+      <c r="B260" s="83" t="inlineStr">
         <is>
           <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
@@ -19005,7 +19020,7 @@
       <c r="D260" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E260" s="69" t="inlineStr">
+      <c r="E260" s="70" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
@@ -19016,7 +19031,7 @@
       <c r="G260" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H260" s="68" t="inlineStr">
+      <c r="H260" s="69" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -19046,7 +19061,7 @@
           <t>12/15</t>
         </is>
       </c>
-      <c r="N260" s="68" t="inlineStr">
+      <c r="N260" s="69" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -19063,7 +19078,7 @@
           <t>PS5-78-01</t>
         </is>
       </c>
-      <c r="B261" s="80" t="inlineStr">
+      <c r="B261" s="83" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -19074,7 +19089,7 @@
       <c r="D261" s="23" t="n">
         <v>71</v>
       </c>
-      <c r="E261" s="68" t="inlineStr">
+      <c r="E261" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -19085,7 +19100,7 @@
       <c r="G261" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H261" s="68" t="inlineStr">
+      <c r="H261" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -19115,12 +19130,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N261" s="68" t="inlineStr">
+      <c r="N261" s="69" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
       </c>
-      <c r="O261" s="68" t="inlineStr">
+      <c r="O261" s="69" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -19132,7 +19147,7 @@
           <t>PS5-79-01</t>
         </is>
       </c>
-      <c r="B262" s="80" t="inlineStr">
+      <c r="B262" s="83" t="inlineStr">
         <is>
           <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
@@ -19143,7 +19158,7 @@
       <c r="D262" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E262" s="92" t="inlineStr">
+      <c r="E262" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19154,7 +19169,7 @@
       <c r="G262" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H262" s="69" t="inlineStr">
+      <c r="H262" s="70" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -19184,7 +19199,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N262" s="69" t="inlineStr">
+      <c r="N262" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19201,7 +19216,7 @@
           <t>PS5-79-02</t>
         </is>
       </c>
-      <c r="B263" s="80" t="inlineStr">
+      <c r="B263" s="83" t="inlineStr">
         <is>
           <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
@@ -19212,7 +19227,7 @@
       <c r="D263" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E263" s="92" t="inlineStr">
+      <c r="E263" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19223,7 +19238,7 @@
       <c r="G263" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H263" s="69" t="inlineStr">
+      <c r="H263" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19253,7 +19268,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N263" s="69" t="inlineStr">
+      <c r="N263" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -19270,7 +19285,7 @@
           <t>PS5-79-03</t>
         </is>
       </c>
-      <c r="B264" s="80" t="inlineStr">
+      <c r="B264" s="83" t="inlineStr">
         <is>
           <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
@@ -19281,7 +19296,7 @@
       <c r="D264" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E264" s="92" t="inlineStr">
+      <c r="E264" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19292,7 +19307,7 @@
       <c r="G264" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H264" s="69" t="inlineStr">
+      <c r="H264" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19322,7 +19337,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N264" s="69" t="inlineStr">
+      <c r="N264" s="70" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -19339,7 +19354,7 @@
           <t>PS5-79-04</t>
         </is>
       </c>
-      <c r="B265" s="80" t="inlineStr">
+      <c r="B265" s="83" t="inlineStr">
         <is>
           <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
@@ -19350,7 +19365,7 @@
       <c r="D265" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E265" s="92" t="inlineStr">
+      <c r="E265" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19361,7 +19376,7 @@
       <c r="G265" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H265" s="69" t="inlineStr">
+      <c r="H265" s="70" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19391,7 +19406,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N265" s="69" t="inlineStr">
+      <c r="N265" s="70" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19408,7 +19423,7 @@
           <t>PS5-79-05</t>
         </is>
       </c>
-      <c r="B266" s="80" t="inlineStr">
+      <c r="B266" s="83" t="inlineStr">
         <is>
           <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
@@ -19419,7 +19434,7 @@
       <c r="D266" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E266" s="92" t="inlineStr">
+      <c r="E266" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19430,7 +19445,7 @@
       <c r="G266" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H266" s="69" t="inlineStr">
+      <c r="H266" s="70" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -19460,7 +19475,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N266" s="69" t="inlineStr">
+      <c r="N266" s="70" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -19477,7 +19492,7 @@
           <t>PS5-79-06</t>
         </is>
       </c>
-      <c r="B267" s="80" t="inlineStr">
+      <c r="B267" s="83" t="inlineStr">
         <is>
           <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
@@ -19488,7 +19503,7 @@
       <c r="D267" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E267" s="92" t="inlineStr">
+      <c r="E267" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19499,7 +19514,7 @@
       <c r="G267" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H267" s="69" t="inlineStr">
+      <c r="H267" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -19529,7 +19544,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N267" s="69" t="inlineStr">
+      <c r="N267" s="70" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -19546,7 +19561,7 @@
           <t>PS5-79-07</t>
         </is>
       </c>
-      <c r="B268" s="80" t="inlineStr">
+      <c r="B268" s="83" t="inlineStr">
         <is>
           <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
@@ -19557,7 +19572,7 @@
       <c r="D268" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E268" s="92" t="inlineStr">
+      <c r="E268" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19568,7 +19583,7 @@
       <c r="G268" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H268" s="69" t="inlineStr">
+      <c r="H268" s="70" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -19598,7 +19613,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N268" s="69" t="inlineStr">
+      <c r="N268" s="70" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -19615,7 +19630,7 @@
           <t>PS5-79-08</t>
         </is>
       </c>
-      <c r="B269" s="80" t="inlineStr">
+      <c r="B269" s="83" t="inlineStr">
         <is>
           <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
@@ -19626,7 +19641,7 @@
       <c r="D269" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E269" s="92" t="inlineStr">
+      <c r="E269" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19637,7 +19652,7 @@
       <c r="G269" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H269" s="69" t="inlineStr">
+      <c r="H269" s="70" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -19667,7 +19682,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N269" s="69" t="inlineStr">
+      <c r="N269" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -19684,7 +19699,7 @@
           <t>PS5-79-09</t>
         </is>
       </c>
-      <c r="B270" s="80" t="inlineStr">
+      <c r="B270" s="83" t="inlineStr">
         <is>
           <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
@@ -19695,7 +19710,7 @@
       <c r="D270" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E270" s="92" t="inlineStr">
+      <c r="E270" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19706,7 +19721,7 @@
       <c r="G270" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H270" s="69" t="inlineStr">
+      <c r="H270" s="70" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -19736,7 +19751,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N270" s="69" t="inlineStr">
+      <c r="N270" s="70" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -19753,7 +19768,7 @@
           <t>PS5-79-10</t>
         </is>
       </c>
-      <c r="B271" s="80" t="inlineStr">
+      <c r="B271" s="83" t="inlineStr">
         <is>
           <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
@@ -19764,7 +19779,7 @@
       <c r="D271" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E271" s="92" t="inlineStr">
+      <c r="E271" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19775,7 +19790,7 @@
       <c r="G271" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="H271" s="69" t="inlineStr">
+      <c r="H271" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -19805,7 +19820,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N271" s="69" t="inlineStr">
+      <c r="N271" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -19822,7 +19837,7 @@
           <t>PS5-79-11</t>
         </is>
       </c>
-      <c r="B272" s="80" t="inlineStr">
+      <c r="B272" s="83" t="inlineStr">
         <is>
           <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
@@ -19833,7 +19848,7 @@
       <c r="D272" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E272" s="92" t="inlineStr">
+      <c r="E272" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19844,7 +19859,7 @@
       <c r="G272" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H272" s="69" t="inlineStr">
+      <c r="H272" s="70" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -19874,7 +19889,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N272" s="69" t="inlineStr">
+      <c r="N272" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -19891,7 +19906,7 @@
           <t>PS5-79-12</t>
         </is>
       </c>
-      <c r="B273" s="80" t="inlineStr">
+      <c r="B273" s="83" t="inlineStr">
         <is>
           <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
@@ -19902,7 +19917,7 @@
       <c r="D273" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E273" s="92" t="inlineStr">
+      <c r="E273" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19913,7 +19928,7 @@
       <c r="G273" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="H273" s="69" t="inlineStr">
+      <c r="H273" s="70" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19943,7 +19958,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N273" s="69" t="inlineStr">
+      <c r="N273" s="70" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -19960,7 +19975,7 @@
           <t>PS5-82-01</t>
         </is>
       </c>
-      <c r="B274" s="80" t="inlineStr">
+      <c r="B274" s="83" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
@@ -19971,7 +19986,7 @@
       <c r="D274" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E274" s="92" t="inlineStr">
+      <c r="E274" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19982,7 +19997,7 @@
       <c r="G274" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="H274" s="68" t="inlineStr">
+      <c r="H274" s="69" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -20012,7 +20027,7 @@
           <t>30/50</t>
         </is>
       </c>
-      <c r="N274" s="68" t="inlineStr">
+      <c r="N274" s="69" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -20029,7 +20044,7 @@
           <t>PS5-82-02</t>
         </is>
       </c>
-      <c r="B275" s="80" t="inlineStr">
+      <c r="B275" s="83" t="inlineStr">
         <is>
           <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
@@ -20040,7 +20055,7 @@
       <c r="D275" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E275" s="69" t="inlineStr">
+      <c r="E275" s="70" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
@@ -20051,7 +20066,7 @@
       <c r="G275" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H275" s="69" t="inlineStr">
+      <c r="H275" s="70" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -20081,7 +20096,7 @@
           <t>0/1</t>
         </is>
       </c>
-      <c r="N275" s="69" t="inlineStr">
+      <c r="N275" s="70" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -20098,7 +20113,7 @@
           <t>PS5-82-03</t>
         </is>
       </c>
-      <c r="B276" s="80" t="inlineStr">
+      <c r="B276" s="83" t="inlineStr">
         <is>
           <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
@@ -20109,7 +20124,7 @@
       <c r="D276" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E276" s="92" t="inlineStr">
+      <c r="E276" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20120,7 +20135,7 @@
       <c r="G276" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H276" s="69" t="inlineStr">
+      <c r="H276" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20150,7 +20165,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N276" s="69" t="inlineStr">
+      <c r="N276" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20167,7 +20182,7 @@
           <t>PS5-82-04</t>
         </is>
       </c>
-      <c r="B277" s="80" t="inlineStr">
+      <c r="B277" s="83" t="inlineStr">
         <is>
           <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
@@ -20178,7 +20193,7 @@
       <c r="D277" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E277" s="92" t="inlineStr">
+      <c r="E277" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20189,7 +20204,7 @@
       <c r="G277" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H277" s="68" t="inlineStr">
+      <c r="H277" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -20219,7 +20234,7 @@
           <t>6/8</t>
         </is>
       </c>
-      <c r="N277" s="68" t="inlineStr">
+      <c r="N277" s="69" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -20236,7 +20251,7 @@
           <t>PS5-82-05</t>
         </is>
       </c>
-      <c r="B278" s="80" t="inlineStr">
+      <c r="B278" s="83" t="inlineStr">
         <is>
           <t>PS5-82-05 - Office and Facilities building</t>
         </is>
@@ -20247,7 +20262,7 @@
       <c r="D278" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E278" s="92" t="inlineStr">
+      <c r="E278" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20258,7 +20273,7 @@
       <c r="G278" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H278" s="69" t="inlineStr">
+      <c r="H278" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20288,7 +20303,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N278" s="69" t="inlineStr">
+      <c r="N278" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20305,7 +20320,7 @@
           <t>PS5-82-06</t>
         </is>
       </c>
-      <c r="B279" s="80" t="inlineStr">
+      <c r="B279" s="83" t="inlineStr">
         <is>
           <t>PS5-82-06 - Guard House Building</t>
         </is>
@@ -20316,7 +20331,7 @@
       <c r="D279" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E279" s="92" t="inlineStr">
+      <c r="E279" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20327,7 +20342,7 @@
       <c r="G279" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H279" s="69" t="inlineStr">
+      <c r="H279" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20357,7 +20372,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N279" s="69" t="inlineStr">
+      <c r="N279" s="70" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -20374,7 +20389,7 @@
           <t>PS5-82-07</t>
         </is>
       </c>
-      <c r="B280" s="80" t="inlineStr">
+      <c r="B280" s="83" t="inlineStr">
         <is>
           <t>PS5-82-07 - Guard Huts</t>
         </is>
@@ -20385,7 +20400,7 @@
       <c r="D280" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E280" s="92" t="inlineStr">
+      <c r="E280" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20396,7 +20411,7 @@
       <c r="G280" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H280" s="69" t="inlineStr">
+      <c r="H280" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20426,7 +20441,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N280" s="69" t="inlineStr">
+      <c r="N280" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20443,7 +20458,7 @@
           <t>PS5-83-01</t>
         </is>
       </c>
-      <c r="B281" s="80" t="inlineStr">
+      <c r="B281" s="83" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -20454,7 +20469,7 @@
       <c r="D281" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="E281" s="68" t="inlineStr">
+      <c r="E281" s="69" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -20512,7 +20527,7 @@
           <t>PS5-84-01</t>
         </is>
       </c>
-      <c r="B282" s="80" t="inlineStr">
+      <c r="B282" s="83" t="inlineStr">
         <is>
           <t>PS5-84-01 - Generator Building</t>
         </is>
@@ -20523,7 +20538,7 @@
       <c r="D282" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E282" s="92" t="inlineStr">
+      <c r="E282" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20534,7 +20549,7 @@
       <c r="G282" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H282" s="69" t="inlineStr">
+      <c r="H282" s="70" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -20564,7 +20579,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N282" s="69" t="inlineStr">
+      <c r="N282" s="70" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -20581,7 +20596,7 @@
           <t>PS5-84-02</t>
         </is>
       </c>
-      <c r="B283" s="80" t="inlineStr">
+      <c r="B283" s="83" t="inlineStr">
         <is>
           <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
@@ -20592,7 +20607,7 @@
       <c r="D283" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E283" s="92" t="inlineStr">
+      <c r="E283" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20603,7 +20618,7 @@
       <c r="G283" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H283" s="69" t="inlineStr">
+      <c r="H283" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -20633,7 +20648,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N283" s="69" t="inlineStr">
+      <c r="N283" s="70" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -20650,7 +20665,7 @@
           <t>PS5-84-03</t>
         </is>
       </c>
-      <c r="B284" s="80" t="inlineStr">
+      <c r="B284" s="83" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -20661,7 +20676,7 @@
       <c r="D284" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E284" s="92" t="inlineStr">
+      <c r="E284" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20719,7 +20734,7 @@
           <t>PS5-86-01</t>
         </is>
       </c>
-      <c r="B285" s="80" t="inlineStr">
+      <c r="B285" s="83" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -20730,7 +20745,7 @@
       <c r="D285" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E285" s="92" t="inlineStr">
+      <c r="E285" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20788,7 +20803,7 @@
           <t>PS5-91-01</t>
         </is>
       </c>
-      <c r="B286" s="80" t="inlineStr">
+      <c r="B286" s="83" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -20799,7 +20814,7 @@
       <c r="D286" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E286" s="69" t="inlineStr">
+      <c r="E286" s="70" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -20857,7 +20872,7 @@
           <t>PS5-99-01</t>
         </is>
       </c>
-      <c r="B287" s="80" t="inlineStr">
+      <c r="B287" s="83" t="inlineStr">
         <is>
           <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
@@ -20868,7 +20883,7 @@
       <c r="D287" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E287" s="92" t="inlineStr">
+      <c r="E287" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20879,7 +20894,7 @@
       <c r="G287" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H287" s="69" t="inlineStr">
+      <c r="H287" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20909,7 +20924,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N287" s="69" t="inlineStr">
+      <c r="N287" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20926,7 +20941,7 @@
           <t>PS5-99-02</t>
         </is>
       </c>
-      <c r="B288" s="80" t="inlineStr">
+      <c r="B288" s="83" t="inlineStr">
         <is>
           <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
@@ -20937,7 +20952,7 @@
       <c r="D288" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E288" s="92" t="inlineStr">
+      <c r="E288" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20948,7 +20963,7 @@
       <c r="G288" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H288" s="69" t="inlineStr">
+      <c r="H288" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20978,7 +20993,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N288" s="69" t="inlineStr">
+      <c r="N288" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20995,7 +21010,7 @@
           <t>PS5-99-03</t>
         </is>
       </c>
-      <c r="B289" s="80" t="inlineStr">
+      <c r="B289" s="83" t="inlineStr">
         <is>
           <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
@@ -21006,7 +21021,7 @@
       <c r="D289" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E289" s="92" t="inlineStr">
+      <c r="E289" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21017,7 +21032,7 @@
       <c r="G289" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H289" s="69" t="inlineStr">
+      <c r="H289" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21047,7 +21062,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N289" s="69" t="inlineStr">
+      <c r="N289" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21064,7 +21079,7 @@
           <t>PS5-99-04</t>
         </is>
       </c>
-      <c r="B290" s="80" t="inlineStr">
+      <c r="B290" s="83" t="inlineStr">
         <is>
           <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
@@ -21075,7 +21090,7 @@
       <c r="D290" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E290" s="92" t="inlineStr">
+      <c r="E290" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21086,7 +21101,7 @@
       <c r="G290" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H290" s="69" t="inlineStr">
+      <c r="H290" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21116,7 +21131,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N290" s="69" t="inlineStr">
+      <c r="N290" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21133,7 +21148,7 @@
           <t>PS5-99-05</t>
         </is>
       </c>
-      <c r="B291" s="80" t="inlineStr">
+      <c r="B291" s="83" t="inlineStr">
         <is>
           <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
@@ -21144,7 +21159,7 @@
       <c r="D291" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E291" s="92" t="inlineStr">
+      <c r="E291" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21155,7 +21170,7 @@
       <c r="G291" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H291" s="69" t="inlineStr">
+      <c r="H291" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -21185,7 +21200,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N291" s="69" t="inlineStr">
+      <c r="N291" s="70" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -21202,7 +21217,7 @@
           <t>PS5-99-06</t>
         </is>
       </c>
-      <c r="B292" s="80" t="inlineStr">
+      <c r="B292" s="83" t="inlineStr">
         <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
@@ -21213,7 +21228,7 @@
       <c r="D292" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E292" s="92" t="inlineStr">
+      <c r="E292" s="95" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21224,7 +21239,7 @@
       <c r="G292" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H292" s="68" t="inlineStr">
+      <c r="H292" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -21254,7 +21269,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N292" s="68" t="inlineStr">
+      <c r="N292" s="69" t="inlineStr">
         <is>
           <t>67%</t>
         </is>

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 · SUBSYSTEM" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="6 · SUBSYSTEM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'6 · SUBSYSTEM'!$A$2:$O$297</definedName>

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -1351,14 +1351,14 @@
         </is>
       </c>
       <c r="C4" s="23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="23" t="n">
         <v>13</v>
       </c>
       <c r="E4" s="69" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="F4" s="23" t="n">
@@ -1420,14 +1420,14 @@
         </is>
       </c>
       <c r="C5" s="23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="23" t="n">
         <v>11</v>
       </c>
       <c r="E5" s="69" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="F5" s="23" t="n">
@@ -1710,11 +1710,11 @@
         <v>132</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H9" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>11/16</t>
         </is>
       </c>
       <c r="K9" s="23" t="inlineStr">
@@ -1779,11 +1779,11 @@
         <v>54</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>47</v>
-      </c>
-      <c r="H10" s="69" t="inlineStr">
-        <is>
-          <t>87%</t>
+        <v>53</v>
+      </c>
+      <c r="H10" s="54" t="inlineStr">
+        <is>
+          <t>98%</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="M10" s="23" t="inlineStr">
         <is>
-          <t>27/34</t>
+          <t>33/34</t>
         </is>
       </c>
       <c r="N10" s="69" t="inlineStr">
@@ -2055,11 +2055,11 @@
         <v>66</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="H14" s="70" t="inlineStr">
-        <is>
-          <t>14%</t>
+        <v>37</v>
+      </c>
+      <c r="H14" s="69" t="inlineStr">
+        <is>
+          <t>56%</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
@@ -2389,11 +2389,11 @@
         <v>7</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" s="70" t="inlineStr">
-        <is>
-          <t>43%</t>
+        <v>6</v>
+      </c>
+      <c r="E19" s="69" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
       <c r="F19" s="23" t="n">
@@ -4295,9 +4295,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N46" s="69" t="inlineStr">
-        <is>
-          <t>78%</t>
+      <c r="N46" s="54" t="inlineStr">
+        <is>
+          <t>99%</t>
         </is>
       </c>
       <c r="O46" s="28" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="N63" s="69" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="O63" s="28" t="inlineStr">
@@ -6747,11 +6747,11 @@
         <v>1106</v>
       </c>
       <c r="G82" s="23" t="n">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="H82" s="70" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="I82" s="23" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="J82" s="23" t="inlineStr">
         <is>
-          <t>0/620</t>
+          <t>29/620</t>
         </is>
       </c>
       <c r="K82" s="23" t="inlineStr">
@@ -7092,7 +7092,7 @@
         <v>223</v>
       </c>
       <c r="G87" s="23" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H87" s="69" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="I87" s="23" t="inlineStr">
         <is>
-          <t>77/95</t>
+          <t>78/95</t>
         </is>
       </c>
       <c r="J87" s="23" t="inlineStr">
@@ -7161,7 +7161,7 @@
         <v>220</v>
       </c>
       <c r="G88" s="23" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H88" s="54" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="I88" s="23" t="inlineStr">
         <is>
-          <t>87/92</t>
+          <t>88/92</t>
         </is>
       </c>
       <c r="J88" s="23" t="inlineStr">
@@ -7230,7 +7230,7 @@
         <v>220</v>
       </c>
       <c r="G89" s="23" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H89" s="54" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="I89" s="23" t="inlineStr">
         <is>
-          <t>87/92</t>
+          <t>88/92</t>
         </is>
       </c>
       <c r="J89" s="23" t="inlineStr">
@@ -7644,11 +7644,11 @@
         <v>104</v>
       </c>
       <c r="G95" s="23" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H95" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="I95" s="23" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="J95" s="23" t="inlineStr">
         <is>
-          <t>33/35</t>
+          <t>34/35</t>
         </is>
       </c>
       <c r="K95" s="23" t="inlineStr">
@@ -7920,11 +7920,11 @@
         <v>278</v>
       </c>
       <c r="G99" s="23" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H99" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I99" s="23" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="J99" s="23" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K99" s="23" t="inlineStr">
@@ -8127,16 +8127,16 @@
         <v>11</v>
       </c>
       <c r="G102" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H102" s="70" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="I102" s="23" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>3/8</t>
         </is>
       </c>
       <c r="J102" s="23" t="inlineStr">
@@ -8265,11 +8265,11 @@
         <v>43</v>
       </c>
       <c r="G104" s="23" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H104" s="54" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I104" s="23" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="M104" s="23" t="inlineStr">
         <is>
-          <t>39/43</t>
+          <t>43/43</t>
         </is>
       </c>
       <c r="N104" s="69" t="inlineStr">
@@ -8320,14 +8320,14 @@
         </is>
       </c>
       <c r="C105" s="23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D105" s="23" t="n">
         <v>2</v>
       </c>
       <c r="E105" s="70" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="F105" s="23" t="n">
@@ -8389,14 +8389,14 @@
         </is>
       </c>
       <c r="C106" s="23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D106" s="23" t="n">
         <v>2</v>
       </c>
       <c r="E106" s="70" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="F106" s="23" t="n">
@@ -8676,14 +8676,14 @@
         </is>
       </c>
       <c r="F110" s="23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G110" s="23" t="n">
         <v>14</v>
       </c>
       <c r="H110" s="69" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="I110" s="23" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="J110" s="23" t="inlineStr">
         <is>
-          <t>2/7</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="K110" s="23" t="inlineStr">
@@ -8745,14 +8745,14 @@
         </is>
       </c>
       <c r="F111" s="23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G111" s="23" t="n">
         <v>14</v>
       </c>
       <c r="H111" s="69" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="I111" s="23" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="J111" s="23" t="inlineStr">
         <is>
-          <t>2/7</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="K111" s="23" t="inlineStr">
@@ -8817,11 +8817,11 @@
         <v>25</v>
       </c>
       <c r="G112" s="23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H112" s="69" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="I112" s="23" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="L112" s="23" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="M112" s="23" t="inlineStr">
@@ -8875,11 +8875,11 @@
         <v>3</v>
       </c>
       <c r="D113" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="E113" s="69" t="inlineStr">
-        <is>
-          <t>67%</t>
+        <v>3</v>
+      </c>
+      <c r="E113" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="F113" s="23" t="n">
@@ -9217,12 +9217,12 @@
         </is>
       </c>
       <c r="C118" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E118" s="95" t="inlineStr">
+      <c r="E118" s="70" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9231,11 +9231,11 @@
         <v>39</v>
       </c>
       <c r="G118" s="23" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H118" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="I118" s="23" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="M118" s="23" t="inlineStr">
         <is>
-          <t>35/39</t>
+          <t>37/39</t>
         </is>
       </c>
       <c r="N118" s="69" t="inlineStr">
@@ -9289,11 +9289,11 @@
         <v>47</v>
       </c>
       <c r="D119" s="23" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E119" s="69" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="F119" s="23" t="n">
@@ -9358,11 +9358,11 @@
         <v>30</v>
       </c>
       <c r="D120" s="23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E120" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="F120" s="23" t="n">
@@ -9565,11 +9565,11 @@
         <v>22</v>
       </c>
       <c r="D123" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="E123" s="69" t="inlineStr">
-        <is>
-          <t>86%</t>
+        <v>21</v>
+      </c>
+      <c r="E123" s="54" t="inlineStr">
+        <is>
+          <t>95%</t>
         </is>
       </c>
       <c r="F123" s="23" t="n">
@@ -9772,11 +9772,11 @@
         <v>15</v>
       </c>
       <c r="D126" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="E126" s="70" t="inlineStr">
-        <is>
-          <t>33%</t>
+        <v>12</v>
+      </c>
+      <c r="E126" s="69" t="inlineStr">
+        <is>
+          <t>80%</t>
         </is>
       </c>
       <c r="F126" s="23" t="n">
@@ -9979,11 +9979,11 @@
         <v>11</v>
       </c>
       <c r="D129" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E129" s="70" t="inlineStr">
-        <is>
-          <t>27%</t>
+        <v>8</v>
+      </c>
+      <c r="E129" s="69" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
       <c r="F129" s="23" t="n">
@@ -10186,11 +10186,11 @@
         <v>14</v>
       </c>
       <c r="D132" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E132" s="70" t="inlineStr">
-        <is>
-          <t>21%</t>
+        <v>11</v>
+      </c>
+      <c r="E132" s="69" t="inlineStr">
+        <is>
+          <t>79%</t>
         </is>
       </c>
       <c r="F132" s="23" t="n">
@@ -10324,11 +10324,11 @@
         <v>14</v>
       </c>
       <c r="D134" s="23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E134" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="F134" s="23" t="n">
@@ -10600,11 +10600,11 @@
         <v>14</v>
       </c>
       <c r="D138" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E138" s="70" t="inlineStr">
-        <is>
-          <t>21%</t>
+        <v>11</v>
+      </c>
+      <c r="E138" s="69" t="inlineStr">
+        <is>
+          <t>79%</t>
         </is>
       </c>
       <c r="F138" s="23" t="n">
@@ -10738,11 +10738,11 @@
         <v>40</v>
       </c>
       <c r="D140" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="E140" s="70" t="inlineStr">
-        <is>
-          <t>42%</t>
+        <v>21</v>
+      </c>
+      <c r="E140" s="69" t="inlineStr">
+        <is>
+          <t>52%</t>
         </is>
       </c>
       <c r="F140" s="23" t="n">
@@ -12601,11 +12601,11 @@
         <v>4</v>
       </c>
       <c r="D167" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E167" s="69" t="inlineStr">
-        <is>
-          <t>75%</t>
+        <v>4</v>
+      </c>
+      <c r="E167" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="F167" s="23" t="n">
@@ -13153,11 +13153,11 @@
         <v>6</v>
       </c>
       <c r="D175" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E175" s="70" t="inlineStr">
-        <is>
-          <t>17%</t>
+        <v>6</v>
+      </c>
+      <c r="E175" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="F175" s="23" t="n">
@@ -13291,11 +13291,11 @@
         <v>9</v>
       </c>
       <c r="D177" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="E177" s="70" t="inlineStr">
-        <is>
-          <t>44%</t>
+        <v>9</v>
+      </c>
+      <c r="E177" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="F177" s="23" t="n">
@@ -14599,14 +14599,14 @@
         </is>
       </c>
       <c r="C196" s="23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D196" s="23" t="n">
         <v>10</v>
       </c>
       <c r="E196" s="70" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="F196" s="23" t="n">
@@ -14668,14 +14668,14 @@
         </is>
       </c>
       <c r="C197" s="23" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D197" s="23" t="n">
         <v>16</v>
       </c>
       <c r="E197" s="69" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="F197" s="23" t="n">
@@ -14748,7 +14748,7 @@
         </is>
       </c>
       <c r="F198" s="23" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G198" s="23" t="n">
         <v>0</v>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="I198" s="23" t="inlineStr">
         <is>
-          <t>0/18</t>
+          <t>0/23</t>
         </is>
       </c>
       <c r="J198" s="23" t="inlineStr">
@@ -15024,19 +15024,19 @@
         </is>
       </c>
       <c r="F202" s="23" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G202" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="H202" s="69" t="inlineStr">
-        <is>
-          <t>79%</t>
+      <c r="H202" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="I202" s="23" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>22/23</t>
         </is>
       </c>
       <c r="J202" s="23" t="inlineStr">
@@ -15335,9 +15335,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N206" s="70" t="inlineStr">
-        <is>
-          <t>32%</t>
+      <c r="N206" s="54" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
       <c r="O206" s="28" t="inlineStr">
@@ -17373,11 +17373,11 @@
         <v>94</v>
       </c>
       <c r="G236" s="23" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H236" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="I236" s="23" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="J236" s="23" t="inlineStr">
         <is>
-          <t>40/48</t>
+          <t>42/48</t>
         </is>
       </c>
       <c r="K236" s="23" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="N238" s="69" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="O238" s="28" t="inlineStr">
@@ -17580,11 +17580,11 @@
         <v>129</v>
       </c>
       <c r="G239" s="23" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H239" s="69" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="I239" s="23" t="inlineStr">
@@ -17594,7 +17594,7 @@
       </c>
       <c r="J239" s="23" t="inlineStr">
         <is>
-          <t>41/58</t>
+          <t>46/58</t>
         </is>
       </c>
       <c r="K239" s="23" t="inlineStr">
@@ -17649,11 +17649,11 @@
         <v>64</v>
       </c>
       <c r="G240" s="23" t="n">
-        <v>54</v>
-      </c>
-      <c r="H240" s="69" t="inlineStr">
-        <is>
-          <t>84%</t>
+        <v>58</v>
+      </c>
+      <c r="H240" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="I240" s="23" t="inlineStr">
@@ -17663,7 +17663,7 @@
       </c>
       <c r="J240" s="23" t="inlineStr">
         <is>
-          <t>25/35</t>
+          <t>29/35</t>
         </is>
       </c>
       <c r="K240" s="23" t="inlineStr">
@@ -17776,11 +17776,11 @@
         <v>23</v>
       </c>
       <c r="D242" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="E242" s="70" t="inlineStr">
-        <is>
-          <t>39%</t>
+        <v>17</v>
+      </c>
+      <c r="E242" s="69" t="inlineStr">
+        <is>
+          <t>74%</t>
         </is>
       </c>
       <c r="F242" s="23" t="n">
@@ -17914,11 +17914,11 @@
         <v>8</v>
       </c>
       <c r="D244" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E244" s="70" t="inlineStr">
-        <is>
-          <t>38%</t>
+        <v>6</v>
+      </c>
+      <c r="E244" s="69" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
       <c r="F244" s="23" t="n">
@@ -17994,11 +17994,11 @@
         <v>125</v>
       </c>
       <c r="G245" s="23" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H245" s="69" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="I245" s="23" t="inlineStr">
@@ -18008,7 +18008,7 @@
       </c>
       <c r="J245" s="23" t="inlineStr">
         <is>
-          <t>53/69</t>
+          <t>54/69</t>
         </is>
       </c>
       <c r="K245" s="23" t="inlineStr">
@@ -18190,11 +18190,11 @@
         <v>11</v>
       </c>
       <c r="D248" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E248" s="70" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F248" s="23" t="n">
@@ -18742,11 +18742,11 @@
         <v>9</v>
       </c>
       <c r="D256" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E256" s="69" t="inlineStr">
-        <is>
-          <t>89%</t>
+        <v>9</v>
+      </c>
+      <c r="E256" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="F256" s="23" t="n">
@@ -19374,16 +19374,16 @@
         <v>69</v>
       </c>
       <c r="G265" s="23" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H265" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="I265" s="23" t="inlineStr">
         <is>
-          <t>47/67</t>
+          <t>50/67</t>
         </is>
       </c>
       <c r="J265" s="23" t="inlineStr">
@@ -19719,16 +19719,16 @@
         <v>75</v>
       </c>
       <c r="G270" s="23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H270" s="70" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="I270" s="23" t="inlineStr">
         <is>
-          <t>8/73</t>
+          <t>11/73</t>
         </is>
       </c>
       <c r="J270" s="23" t="inlineStr">
@@ -19788,16 +19788,16 @@
         <v>75</v>
       </c>
       <c r="G271" s="23" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H271" s="69" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="I271" s="23" t="inlineStr">
         <is>
-          <t>38/73</t>
+          <t>48/73</t>
         </is>
       </c>
       <c r="J271" s="23" t="inlineStr">
@@ -19857,16 +19857,16 @@
         <v>75</v>
       </c>
       <c r="G272" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="H272" s="70" t="inlineStr">
-        <is>
-          <t>43%</t>
+        <v>44</v>
+      </c>
+      <c r="H272" s="69" t="inlineStr">
+        <is>
+          <t>59%</t>
         </is>
       </c>
       <c r="I272" s="23" t="inlineStr">
         <is>
-          <t>30/73</t>
+          <t>42/73</t>
         </is>
       </c>
       <c r="J272" s="23" t="inlineStr">
@@ -19926,16 +19926,16 @@
         <v>75</v>
       </c>
       <c r="G273" s="23" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H273" s="70" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="I273" s="23" t="inlineStr">
         <is>
-          <t>25/73</t>
+          <t>28/73</t>
         </is>
       </c>
       <c r="J273" s="23" t="inlineStr">
@@ -19995,16 +19995,16 @@
         <v>71</v>
       </c>
       <c r="G274" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="H274" s="70" t="inlineStr">
-        <is>
-          <t>42%</t>
+        <v>37</v>
+      </c>
+      <c r="H274" s="69" t="inlineStr">
+        <is>
+          <t>52%</t>
         </is>
       </c>
       <c r="I274" s="23" t="inlineStr">
         <is>
-          <t>28/69</t>
+          <t>35/69</t>
         </is>
       </c>
       <c r="J274" s="23" t="inlineStr">
@@ -20064,16 +20064,16 @@
         <v>71</v>
       </c>
       <c r="G275" s="23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H275" s="70" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="I275" s="23" t="inlineStr">
         <is>
-          <t>22/69</t>
+          <t>23/69</t>
         </is>
       </c>
       <c r="J275" s="23" t="inlineStr">
@@ -20133,16 +20133,16 @@
         <v>81</v>
       </c>
       <c r="G276" s="23" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H276" s="70" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="I276" s="23" t="inlineStr">
         <is>
-          <t>29/79</t>
+          <t>31/79</t>
         </is>
       </c>
       <c r="J276" s="23" t="inlineStr">
@@ -20260,11 +20260,11 @@
         <v>22</v>
       </c>
       <c r="D278" s="23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E278" s="70" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="F278" s="23" t="n">
@@ -21019,11 +21019,11 @@
         <v>196</v>
       </c>
       <c r="D289" s="23" t="n">
-        <v>168</v>
-      </c>
-      <c r="E289" s="69" t="inlineStr">
-        <is>
-          <t>86%</t>
+        <v>185</v>
+      </c>
+      <c r="E289" s="54" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="F289" s="23" t="n">

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -79,12 +79,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFed7d31"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
@@ -92,6 +86,12 @@
       <name val="Calibri"/>
       <color rgb="FF1A2A3A"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFed7d31"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -241,12 +241,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFe8d5c4"/>
         <bgColor rgb="FFe8d5c4"/>
       </patternFill>
@@ -315,6 +309,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
         <bgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -564,10 +564,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,9 +578,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -644,10 +644,13 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -671,40 +674,34 @@
     <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -712,6 +709,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -722,10 +722,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -740,13 +740,13 @@
     <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -773,16 +773,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1271,7 +1271,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>PS5-01-01</t>
         </is>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="N3" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O3" s="27" t="inlineStr">
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="O3" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>PS5-01-02</t>
         </is>
@@ -1399,17 +1399,17 @@
       </c>
       <c r="N4" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="O4" s="27" t="inlineStr">
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="O4" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>PS5-01-03</t>
         </is>
@@ -1468,17 +1468,17 @@
       </c>
       <c r="N5" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
-        </is>
-      </c>
-      <c r="O5" s="27" t="inlineStr">
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="O5" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>PS5-01-04</t>
         </is>
@@ -1540,14 +1540,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O6" s="27" t="inlineStr">
+      <c r="O6" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>PS5-01-05</t>
         </is>
@@ -1606,17 +1606,17 @@
       </c>
       <c r="N7" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
-        </is>
-      </c>
-      <c r="O7" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O7" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>PS5-01-06</t>
         </is>
@@ -1678,14 +1678,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O8" s="27" t="inlineStr">
+      <c r="O8" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>PS5-01-07</t>
         </is>
@@ -1742,19 +1742,19 @@
           <t>87/87</t>
         </is>
       </c>
-      <c r="N9" s="69" t="inlineStr">
-        <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="O9" s="27" t="inlineStr">
+      <c r="N9" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="O9" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>PS5-01-08</t>
         </is>
@@ -1811,19 +1811,19 @@
           <t>33/34</t>
         </is>
       </c>
-      <c r="N10" s="69" t="inlineStr">
-        <is>
-          <t>61%</t>
-        </is>
-      </c>
-      <c r="O10" s="27" t="inlineStr">
+      <c r="N10" s="54" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="O10" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>PS5-01-09</t>
         </is>
@@ -1885,14 +1885,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O11" s="27" t="inlineStr">
+      <c r="O11" s="28" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>PS5-01-10</t>
         </is>
@@ -1954,14 +1954,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O12" s="27" t="inlineStr">
+      <c r="O12" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>PS5-01-11</t>
         </is>
@@ -2018,19 +2018,19 @@
           <t>2/2</t>
         </is>
       </c>
-      <c r="N13" s="70" t="inlineStr">
-        <is>
-          <t>46%</t>
-        </is>
-      </c>
-      <c r="O13" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N13" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O13" s="28" t="inlineStr">
+        <is>
+          <t>FULL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>PS5-02-01</t>
         </is>
@@ -2087,19 +2087,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N14" s="70" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="O14" s="27" t="inlineStr">
+      <c r="N14" s="69" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="O14" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>PS5-02-02</t>
         </is>
@@ -2161,14 +2161,14 @@
           <t>1%</t>
         </is>
       </c>
-      <c r="O15" s="27" t="inlineStr">
+      <c r="O15" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>PS5-03-01</t>
         </is>
@@ -2227,17 +2227,17 @@
       </c>
       <c r="N16" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="O16" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O16" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>PS5-03-03</t>
         </is>
@@ -2299,14 +2299,14 @@
           <t>6%</t>
         </is>
       </c>
-      <c r="O17" s="27" t="inlineStr">
+      <c r="O17" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>PS5-03-04</t>
         </is>
@@ -2365,17 +2365,17 @@
       </c>
       <c r="N18" s="54" t="inlineStr">
         <is>
-          <t>91%</t>
-        </is>
-      </c>
-      <c r="O18" s="27" t="inlineStr">
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="O18" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>PS5-03-06</t>
         </is>
@@ -2434,17 +2434,17 @@
       </c>
       <c r="N19" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="O19" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O19" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>PS5-03-07</t>
         </is>
@@ -2506,14 +2506,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O20" s="27" t="inlineStr">
+      <c r="O20" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>PS5-03-08</t>
         </is>
@@ -2575,14 +2575,14 @@
           <t>98%</t>
         </is>
       </c>
-      <c r="O21" s="27" t="inlineStr">
+      <c r="O21" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>PS5-03-09</t>
         </is>
@@ -2644,14 +2644,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O22" s="27" t="inlineStr">
+      <c r="O22" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>PS5-03-10</t>
         </is>
@@ -2713,14 +2713,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O23" s="27" t="inlineStr">
+      <c r="O23" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>PS5-03-11</t>
         </is>
@@ -2779,17 +2779,17 @@
       </c>
       <c r="N24" s="54" t="inlineStr">
         <is>
-          <t>98%</t>
-        </is>
-      </c>
-      <c r="O24" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O24" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>PS5-03-12</t>
         </is>
@@ -2848,17 +2848,17 @@
       </c>
       <c r="N25" s="54" t="inlineStr">
         <is>
-          <t>91%</t>
-        </is>
-      </c>
-      <c r="O25" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O25" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>PS5-03-13</t>
         </is>
@@ -2920,14 +2920,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O26" s="27" t="inlineStr">
+      <c r="O26" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>PS5-03-14</t>
         </is>
@@ -2984,19 +2984,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N27" s="70" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="O27" s="27" t="inlineStr">
+      <c r="N27" s="69" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="O27" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>PS5-03-15</t>
         </is>
@@ -3058,14 +3058,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O28" s="27" t="inlineStr">
+      <c r="O28" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="inlineStr">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>PS5-03-16</t>
         </is>
@@ -3127,14 +3127,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O29" s="27" t="inlineStr">
+      <c r="O29" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>PS5-03-17</t>
         </is>
@@ -3196,14 +3196,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O30" s="27" t="inlineStr">
+      <c r="O30" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="inlineStr">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>PS5-03-18</t>
         </is>
@@ -3265,14 +3265,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O31" s="27" t="inlineStr">
+      <c r="O31" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>PS5-03-19</t>
         </is>
@@ -3334,14 +3334,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O32" s="27" t="inlineStr">
+      <c r="O32" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="inlineStr">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>PS5-03-20</t>
         </is>
@@ -3403,14 +3403,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O33" s="27" t="inlineStr">
+      <c r="O33" s="28" t="inlineStr">
         <is>
           <t>07-Aug-26</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>PS5-03-21</t>
         </is>
@@ -3472,14 +3472,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O34" s="27" t="inlineStr">
+      <c r="O34" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="inlineStr">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>PS5-03-22</t>
         </is>
@@ -3541,14 +3541,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O35" s="27" t="inlineStr">
+      <c r="O35" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="inlineStr">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>PS5-03-23</t>
         </is>
@@ -3610,14 +3610,14 @@
           <t>99%</t>
         </is>
       </c>
-      <c r="O36" s="27" t="inlineStr">
+      <c r="O36" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>PS5-03-24</t>
         </is>
@@ -3679,14 +3679,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O37" s="27" t="inlineStr">
+      <c r="O37" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="27" t="inlineStr">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>PS5-03-25</t>
         </is>
@@ -3748,14 +3748,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O38" s="27" t="inlineStr">
+      <c r="O38" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="27" t="inlineStr">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>PS5-04-01</t>
         </is>
@@ -3817,14 +3817,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O39" s="27" t="inlineStr">
+      <c r="O39" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="27" t="inlineStr">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t>PS5-04-02</t>
         </is>
@@ -3886,14 +3886,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O40" s="27" t="inlineStr">
+      <c r="O40" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="27" t="inlineStr">
+      <c r="A41" s="28" t="inlineStr">
         <is>
           <t>PS5-04-03</t>
         </is>
@@ -3952,17 +3952,17 @@
       </c>
       <c r="N41" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="O41" s="27" t="inlineStr">
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="O41" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="27" t="inlineStr">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t>PS5-04-04</t>
         </is>
@@ -4021,17 +4021,17 @@
       </c>
       <c r="N42" s="54" t="inlineStr">
         <is>
-          <t>98%</t>
-        </is>
-      </c>
-      <c r="O42" s="27" t="inlineStr">
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="O42" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="27" t="inlineStr">
+      <c r="A43" s="28" t="inlineStr">
         <is>
           <t>PS5-04-05</t>
         </is>
@@ -4093,14 +4093,14 @@
           <t>97%</t>
         </is>
       </c>
-      <c r="O43" s="27" t="inlineStr">
+      <c r="O43" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="27" t="inlineStr">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>PS5-05-01</t>
         </is>
@@ -4169,7 +4169,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="27" t="inlineStr">
+      <c r="A45" s="28" t="inlineStr">
         <is>
           <t>PS5-05-02</t>
         </is>
@@ -4238,7 +4238,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="27" t="inlineStr">
+      <c r="A46" s="28" t="inlineStr">
         <is>
           <t>PS5-06-01</t>
         </is>
@@ -4300,14 +4300,14 @@
           <t>99%</t>
         </is>
       </c>
-      <c r="O46" s="27" t="inlineStr">
+      <c r="O46" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="27" t="inlineStr">
+      <c r="A47" s="28" t="inlineStr">
         <is>
           <t>PS5-06-02</t>
         </is>
@@ -4369,14 +4369,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O47" s="27" t="inlineStr">
+      <c r="O47" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="27" t="inlineStr">
+      <c r="A48" s="28" t="inlineStr">
         <is>
           <t>PS5-06-03</t>
         </is>
@@ -4438,14 +4438,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O48" s="27" t="inlineStr">
+      <c r="O48" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="27" t="inlineStr">
+      <c r="A49" s="28" t="inlineStr">
         <is>
           <t>PS5-06-04</t>
         </is>
@@ -4507,14 +4507,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O49" s="27" t="inlineStr">
+      <c r="O49" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="27" t="inlineStr">
+      <c r="A50" s="28" t="inlineStr">
         <is>
           <t>PS5-06-05</t>
         </is>
@@ -4576,14 +4576,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O50" s="27" t="inlineStr">
+      <c r="O50" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="27" t="inlineStr">
+      <c r="A51" s="28" t="inlineStr">
         <is>
           <t>PS5-08-01</t>
         </is>
@@ -4645,14 +4645,14 @@
           <t>36%</t>
         </is>
       </c>
-      <c r="O51" s="27" t="inlineStr">
+      <c r="O51" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="27" t="inlineStr">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>PS5-08-01a</t>
         </is>
@@ -4714,14 +4714,14 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="O52" s="27" t="inlineStr">
+      <c r="O52" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="27" t="inlineStr">
+      <c r="A53" s="28" t="inlineStr">
         <is>
           <t>PS5-08-01b</t>
         </is>
@@ -4783,14 +4783,14 @@
           <t>14%</t>
         </is>
       </c>
-      <c r="O53" s="27" t="inlineStr">
+      <c r="O53" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="27" t="inlineStr">
+      <c r="A54" s="28" t="inlineStr">
         <is>
           <t>PS5-08-03</t>
         </is>
@@ -4849,17 +4849,17 @@
       </c>
       <c r="N54" s="70" t="inlineStr">
         <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="O54" s="27" t="inlineStr">
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="O54" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="27" t="inlineStr">
+      <c r="A55" s="28" t="inlineStr">
         <is>
           <t>PS5-08-04</t>
         </is>
@@ -4921,14 +4921,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O55" s="27" t="inlineStr">
+      <c r="O55" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="27" t="inlineStr">
+      <c r="A56" s="28" t="inlineStr">
         <is>
           <t>PS5-08-07</t>
         </is>
@@ -4990,14 +4990,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O56" s="27" t="inlineStr">
+      <c r="O56" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="27" t="inlineStr">
+      <c r="A57" s="28" t="inlineStr">
         <is>
           <t>PS5-08-11</t>
         </is>
@@ -5054,19 +5054,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N57" s="70" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="O57" s="27" t="inlineStr">
+      <c r="N57" s="69" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="O57" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="27" t="inlineStr">
+      <c r="A58" s="28" t="inlineStr">
         <is>
           <t>PS5-08-12</t>
         </is>
@@ -5128,14 +5128,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O58" s="27" t="inlineStr">
+      <c r="O58" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="27" t="inlineStr">
+      <c r="A59" s="28" t="inlineStr">
         <is>
           <t>PS5-08-13</t>
         </is>
@@ -5197,14 +5197,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O59" s="27" t="inlineStr">
+      <c r="O59" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="27" t="inlineStr">
+      <c r="A60" s="28" t="inlineStr">
         <is>
           <t>PS5-08-14</t>
         </is>
@@ -5266,14 +5266,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O60" s="27" t="inlineStr">
+      <c r="O60" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="27" t="inlineStr">
+      <c r="A61" s="28" t="inlineStr">
         <is>
           <t>PS5-08-15</t>
         </is>
@@ -5335,14 +5335,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O61" s="27" t="inlineStr">
+      <c r="O61" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="27" t="inlineStr">
+      <c r="A62" s="28" t="inlineStr">
         <is>
           <t>PS5-08-23</t>
         </is>
@@ -5404,14 +5404,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O62" s="27" t="inlineStr">
+      <c r="O62" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="27" t="inlineStr">
+      <c r="A63" s="28" t="inlineStr">
         <is>
           <t>PS5-08-34</t>
         </is>
@@ -5473,14 +5473,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O63" s="27" t="inlineStr">
+      <c r="O63" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="27" t="inlineStr">
+      <c r="A64" s="28" t="inlineStr">
         <is>
           <t>PS5-08-35</t>
         </is>
@@ -5539,17 +5539,17 @@
       </c>
       <c r="N64" s="69" t="inlineStr">
         <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="O64" s="27" t="inlineStr">
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="O64" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="27" t="inlineStr">
+      <c r="A65" s="28" t="inlineStr">
         <is>
           <t>PS5-08-36</t>
         </is>
@@ -5611,14 +5611,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O65" s="27" t="inlineStr">
+      <c r="O65" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="27" t="inlineStr">
+      <c r="A66" s="28" t="inlineStr">
         <is>
           <t>PS5-08-51</t>
         </is>
@@ -5680,14 +5680,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O66" s="27" t="inlineStr">
+      <c r="O66" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="27" t="inlineStr">
+      <c r="A67" s="28" t="inlineStr">
         <is>
           <t>PS5-08-52a</t>
         </is>
@@ -5749,14 +5749,14 @@
           <t>17%</t>
         </is>
       </c>
-      <c r="O67" s="27" t="inlineStr">
+      <c r="O67" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="27" t="inlineStr">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>PS5-08-52b</t>
         </is>
@@ -5818,14 +5818,14 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="O68" s="27" t="inlineStr">
+      <c r="O68" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="27" t="inlineStr">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>PS5-08-55</t>
         </is>
@@ -5887,14 +5887,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O69" s="27" t="inlineStr">
+      <c r="O69" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="27" t="inlineStr">
+      <c r="A70" s="28" t="inlineStr">
         <is>
           <t>PS5-08-61</t>
         </is>
@@ -5956,14 +5956,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O70" s="27" t="inlineStr">
+      <c r="O70" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="27" t="inlineStr">
+      <c r="A71" s="28" t="inlineStr">
         <is>
           <t>PS5-08-71</t>
         </is>
@@ -6025,14 +6025,14 @@
           <t>4%</t>
         </is>
       </c>
-      <c r="O71" s="27" t="inlineStr">
+      <c r="O71" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="27" t="inlineStr">
+      <c r="A72" s="28" t="inlineStr">
         <is>
           <t>PS5-08-72</t>
         </is>
@@ -6094,14 +6094,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O72" s="27" t="inlineStr">
+      <c r="O72" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="27" t="inlineStr">
+      <c r="A73" s="28" t="inlineStr">
         <is>
           <t>PS5-08-81</t>
         </is>
@@ -6163,14 +6163,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O73" s="27" t="inlineStr">
+      <c r="O73" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="27" t="inlineStr">
+      <c r="A74" s="28" t="inlineStr">
         <is>
           <t>PS5-08-82</t>
         </is>
@@ -6232,14 +6232,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O74" s="27" t="inlineStr">
+      <c r="O74" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="27" t="inlineStr">
+      <c r="A75" s="28" t="inlineStr">
         <is>
           <t>PS5-08-83</t>
         </is>
@@ -6301,14 +6301,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O75" s="27" t="inlineStr">
+      <c r="O75" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="27" t="inlineStr">
+      <c r="A76" s="28" t="inlineStr">
         <is>
           <t>PS5-08-85</t>
         </is>
@@ -6367,17 +6367,17 @@
       </c>
       <c r="N76" s="70" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="O76" s="27" t="inlineStr">
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="O76" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="27" t="inlineStr">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>PS5-08-85a</t>
         </is>
@@ -6439,14 +6439,14 @@
           <t>26%</t>
         </is>
       </c>
-      <c r="O77" s="27" t="inlineStr">
+      <c r="O77" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="27" t="inlineStr">
+      <c r="A78" s="28" t="inlineStr">
         <is>
           <t>PS5-08-85b</t>
         </is>
@@ -6508,14 +6508,14 @@
           <t>5%</t>
         </is>
       </c>
-      <c r="O78" s="27" t="inlineStr">
+      <c r="O78" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="27" t="inlineStr">
+      <c r="A79" s="28" t="inlineStr">
         <is>
           <t>PS5-08-86</t>
         </is>
@@ -6577,14 +6577,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O79" s="27" t="inlineStr">
+      <c r="O79" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="27" t="inlineStr">
+      <c r="A80" s="28" t="inlineStr">
         <is>
           <t>PS5-08-92</t>
         </is>
@@ -6646,14 +6646,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O80" s="27" t="inlineStr">
+      <c r="O80" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="27" t="inlineStr">
+      <c r="A81" s="28" t="inlineStr">
         <is>
           <t>PS5-08-93</t>
         </is>
@@ -6715,14 +6715,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O81" s="27" t="inlineStr">
+      <c r="O81" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="27" t="inlineStr">
+      <c r="A82" s="28" t="inlineStr">
         <is>
           <t>PS5-09-01</t>
         </is>
@@ -6784,14 +6784,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O82" s="27" t="inlineStr">
+      <c r="O82" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="27" t="inlineStr">
+      <c r="A83" s="28" t="inlineStr">
         <is>
           <t>PS5-09-02</t>
         </is>
@@ -6853,14 +6853,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O83" s="27" t="inlineStr">
+      <c r="O83" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="27" t="inlineStr">
+      <c r="A84" s="28" t="inlineStr">
         <is>
           <t>PS5-09-03</t>
         </is>
@@ -6885,11 +6885,11 @@
         <v>1106</v>
       </c>
       <c r="G84" s="23" t="n">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="H84" s="70" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="I84" s="23" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="J84" s="23" t="inlineStr">
         <is>
-          <t>58/620</t>
+          <t>93/620</t>
         </is>
       </c>
       <c r="K84" s="23" t="inlineStr">
@@ -6919,17 +6919,17 @@
       </c>
       <c r="N84" s="70" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="O84" s="27" t="inlineStr">
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="O84" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="27" t="inlineStr">
+      <c r="A85" s="28" t="inlineStr">
         <is>
           <t>PS5-09-04</t>
         </is>
@@ -6991,14 +6991,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O85" s="27" t="inlineStr">
+      <c r="O85" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="27" t="inlineStr">
+      <c r="A86" s="28" t="inlineStr">
         <is>
           <t>PS5-09-05</t>
         </is>
@@ -7060,14 +7060,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O86" s="27" t="inlineStr">
+      <c r="O86" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="27" t="inlineStr">
+      <c r="A87" s="28" t="inlineStr">
         <is>
           <t>PS5-0H-01</t>
         </is>
@@ -7126,17 +7126,17 @@
       </c>
       <c r="N87" s="69" t="inlineStr">
         <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="O87" s="27" t="inlineStr">
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="O87" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="27" t="inlineStr">
+      <c r="A88" s="28" t="inlineStr">
         <is>
           <t>PS5-25-01</t>
         </is>
@@ -7193,19 +7193,19 @@
           <t>44/46</t>
         </is>
       </c>
-      <c r="N88" s="69" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="O88" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N88" s="54" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="O88" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="27" t="inlineStr">
+      <c r="A89" s="28" t="inlineStr">
         <is>
           <t>PS5-25-02</t>
         </is>
@@ -7264,17 +7264,17 @@
       </c>
       <c r="N89" s="69" t="inlineStr">
         <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="O89" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="O89" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="27" t="inlineStr">
+      <c r="A90" s="28" t="inlineStr">
         <is>
           <t>PS5-25-03</t>
         </is>
@@ -7331,19 +7331,19 @@
           <t>24/24</t>
         </is>
       </c>
-      <c r="N90" s="69" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="O90" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N90" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="O90" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="27" t="inlineStr">
+      <c r="A91" s="28" t="inlineStr">
         <is>
           <t>PS5-25-04</t>
         </is>
@@ -7400,19 +7400,19 @@
           <t>24/24</t>
         </is>
       </c>
-      <c r="N91" s="69" t="inlineStr">
-        <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="O91" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N91" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="O91" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="27" t="inlineStr">
+      <c r="A92" s="28" t="inlineStr">
         <is>
           <t>PS5-25-05</t>
         </is>
@@ -7469,19 +7469,19 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N92" s="69" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="O92" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N92" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O92" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="27" t="inlineStr">
+      <c r="A93" s="28" t="inlineStr">
         <is>
           <t>PS5-25-06</t>
         </is>
@@ -7538,19 +7538,19 @@
           <t>19/19</t>
         </is>
       </c>
-      <c r="N93" s="69" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
-      <c r="O93" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N93" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="O93" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="27" t="inlineStr">
+      <c r="A94" s="28" t="inlineStr">
         <is>
           <t>PS5-25-07</t>
         </is>
@@ -7607,19 +7607,19 @@
           <t>34/35</t>
         </is>
       </c>
-      <c r="N94" s="69" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="O94" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N94" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="O94" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="27" t="inlineStr">
+      <c r="A95" s="28" t="inlineStr">
         <is>
           <t>PS5-28-01</t>
         </is>
@@ -7676,19 +7676,19 @@
           <t>13/14</t>
         </is>
       </c>
-      <c r="N95" s="69" t="inlineStr">
-        <is>
-          <t>79%</t>
-        </is>
-      </c>
-      <c r="O95" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N95" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="O95" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="27" t="inlineStr">
+      <c r="A96" s="28" t="inlineStr">
         <is>
           <t>PS5-28-02</t>
         </is>
@@ -7750,14 +7750,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O96" s="27" t="inlineStr">
+      <c r="O96" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="27" t="inlineStr">
+      <c r="A97" s="28" t="inlineStr">
         <is>
           <t>PS5-28-03</t>
         </is>
@@ -7814,19 +7814,19 @@
           <t>55/56</t>
         </is>
       </c>
-      <c r="N97" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="O97" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N97" s="54" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="O97" s="28" t="inlineStr">
+        <is>
+          <t>FULL</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="27" t="inlineStr">
+      <c r="A98" s="28" t="inlineStr">
         <is>
           <t>PS5-28-04</t>
         </is>
@@ -7885,17 +7885,17 @@
       </c>
       <c r="N98" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="O98" s="27" t="inlineStr">
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="O98" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="27" t="inlineStr">
+      <c r="A99" s="28" t="inlineStr">
         <is>
           <t>PS5-28-05</t>
         </is>
@@ -7957,14 +7957,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O99" s="27" t="inlineStr">
+      <c r="O99" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="27" t="inlineStr">
+      <c r="A100" s="28" t="inlineStr">
         <is>
           <t>PS5-28-06</t>
         </is>
@@ -8021,19 +8021,19 @@
           <t>36/36</t>
         </is>
       </c>
-      <c r="N100" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="O100" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N100" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O100" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="27" t="inlineStr">
+      <c r="A101" s="28" t="inlineStr">
         <is>
           <t>PS5-28-07</t>
         </is>
@@ -8092,17 +8092,17 @@
       </c>
       <c r="N101" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="O101" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O101" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="27" t="inlineStr">
+      <c r="A102" s="28" t="inlineStr">
         <is>
           <t>PS5-28-08</t>
         </is>
@@ -8159,19 +8159,19 @@
           <t>28/29</t>
         </is>
       </c>
-      <c r="N102" s="70" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="O102" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N102" s="54" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="O102" s="69" t="inlineStr">
+        <is>
+          <t>partial</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="27" t="inlineStr">
+      <c r="A103" s="28" t="inlineStr">
         <is>
           <t>PS5-28-09</t>
         </is>
@@ -8228,19 +8228,19 @@
           <t>13/14</t>
         </is>
       </c>
-      <c r="N103" s="69" t="inlineStr">
-        <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="O103" s="27" t="inlineStr">
+      <c r="N103" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="O103" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="27" t="inlineStr">
+      <c r="A104" s="28" t="inlineStr">
         <is>
           <t>PS5-28-10</t>
         </is>
@@ -8299,17 +8299,17 @@
       </c>
       <c r="N104" s="70" t="inlineStr">
         <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="O104" s="27" t="inlineStr">
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="O104" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="27" t="inlineStr">
+      <c r="A105" s="28" t="inlineStr">
         <is>
           <t>PS5-28-11</t>
         </is>
@@ -8366,19 +8366,19 @@
           <t>8/8</t>
         </is>
       </c>
-      <c r="N105" s="69" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="O105" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N105" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O105" s="28" t="inlineStr">
+        <is>
+          <t>FULL</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="27" t="inlineStr">
+      <c r="A106" s="28" t="inlineStr">
         <is>
           <t>PS5-28-12</t>
         </is>
@@ -8435,19 +8435,19 @@
           <t>43/43</t>
         </is>
       </c>
-      <c r="N106" s="69" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="O106" s="27" t="inlineStr">
+      <c r="N106" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O106" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="27" t="inlineStr">
+      <c r="A107" s="28" t="inlineStr">
         <is>
           <t>PS5-28-13</t>
         </is>
@@ -8504,19 +8504,19 @@
           <t>35/35</t>
         </is>
       </c>
-      <c r="N107" s="69" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="O107" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N107" s="54" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="O107" s="28" t="inlineStr">
+        <is>
+          <t>FULL</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="27" t="inlineStr">
+      <c r="A108" s="28" t="inlineStr">
         <is>
           <t>PS5-28-14</t>
         </is>
@@ -8573,19 +8573,19 @@
           <t>35/35</t>
         </is>
       </c>
-      <c r="N108" s="69" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="O108" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N108" s="54" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="O108" s="28" t="inlineStr">
+        <is>
+          <t>FULL</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="27" t="inlineStr">
+      <c r="A109" s="28" t="inlineStr">
         <is>
           <t>PS5-28-15</t>
         </is>
@@ -8642,19 +8642,19 @@
           <t>35/35</t>
         </is>
       </c>
-      <c r="N109" s="69" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="O109" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N109" s="54" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="O109" s="28" t="inlineStr">
+        <is>
+          <t>FULL</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="27" t="inlineStr">
+      <c r="A110" s="28" t="inlineStr">
         <is>
           <t>PS5-28-16</t>
         </is>
@@ -8711,19 +8711,19 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N110" s="69" t="inlineStr">
-        <is>
-          <t>82%</t>
-        </is>
-      </c>
-      <c r="O110" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N110" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O110" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="27" t="inlineStr">
+      <c r="A111" s="28" t="inlineStr">
         <is>
           <t>PS5-28-17</t>
         </is>
@@ -8780,19 +8780,19 @@
           <t>24/24</t>
         </is>
       </c>
-      <c r="N111" s="69" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="O111" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N111" s="54" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="O111" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="27" t="inlineStr">
+      <c r="A112" s="28" t="inlineStr">
         <is>
           <t>PS5-50-01</t>
         </is>
@@ -8849,19 +8849,19 @@
           <t>11/13</t>
         </is>
       </c>
-      <c r="N112" s="70" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="O112" s="27" t="inlineStr">
+      <c r="N112" s="69" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="O112" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="27" t="inlineStr">
+      <c r="A113" s="28" t="inlineStr">
         <is>
           <t>PS5-50-02</t>
         </is>
@@ -8918,19 +8918,19 @@
           <t>11/13</t>
         </is>
       </c>
-      <c r="N113" s="70" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="O113" s="27" t="inlineStr">
+      <c r="N113" s="69" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="O113" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="27" t="inlineStr">
+      <c r="A114" s="28" t="inlineStr">
         <is>
           <t>PS5-50-03</t>
         </is>
@@ -8987,19 +8987,19 @@
           <t>12/15</t>
         </is>
       </c>
-      <c r="N114" s="70" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="O114" s="27" t="inlineStr">
+      <c r="N114" s="69" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="O114" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="27" t="inlineStr">
+      <c r="A115" s="28" t="inlineStr">
         <is>
           <t>PS5-53-01</t>
         </is>
@@ -9056,9 +9056,9 @@
           <t>30/30</t>
         </is>
       </c>
-      <c r="N115" s="69" t="inlineStr">
-        <is>
-          <t>89%</t>
+      <c r="N115" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="O115" s="69" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="27" t="inlineStr">
+      <c r="A116" s="28" t="inlineStr">
         <is>
           <t>PS5-53-02</t>
         </is>
@@ -9125,19 +9125,19 @@
           <t>8/8</t>
         </is>
       </c>
-      <c r="N116" s="69" t="inlineStr">
-        <is>
-          <t>62%</t>
-        </is>
-      </c>
-      <c r="O116" s="27" t="inlineStr">
+      <c r="N116" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O116" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="27" t="inlineStr">
+      <c r="A117" s="28" t="inlineStr">
         <is>
           <t>PS5-53-03</t>
         </is>
@@ -9196,17 +9196,17 @@
       </c>
       <c r="N117" s="69" t="inlineStr">
         <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="O117" s="27" t="inlineStr">
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="O117" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="27" t="inlineStr">
+      <c r="A118" s="28" t="inlineStr">
         <is>
           <t>PS5-53-04</t>
         </is>
@@ -9265,17 +9265,17 @@
       </c>
       <c r="N118" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="O118" s="27" t="inlineStr">
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="O118" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="27" t="inlineStr">
+      <c r="A119" s="28" t="inlineStr">
         <is>
           <t>PS5-53-05</t>
         </is>
@@ -9334,17 +9334,17 @@
       </c>
       <c r="N119" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="O119" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O119" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="27" t="inlineStr">
+      <c r="A120" s="28" t="inlineStr">
         <is>
           <t>PS5-53-06</t>
         </is>
@@ -9401,19 +9401,19 @@
           <t>37/39</t>
         </is>
       </c>
-      <c r="N120" s="69" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="O120" s="27" t="inlineStr">
+      <c r="N120" s="54" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="O120" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="27" t="inlineStr">
+      <c r="A121" s="28" t="inlineStr">
         <is>
           <t>PS5-60-01</t>
         </is>
@@ -9475,14 +9475,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O121" s="27" t="inlineStr">
+      <c r="O121" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="27" t="inlineStr">
+      <c r="A122" s="28" t="inlineStr">
         <is>
           <t>PS5-60-02</t>
         </is>
@@ -9544,14 +9544,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O122" s="27" t="inlineStr">
+      <c r="O122" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="27" t="inlineStr">
+      <c r="A123" s="28" t="inlineStr">
         <is>
           <t>PS5-60-03</t>
         </is>
@@ -9608,19 +9608,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N123" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="O123" s="27" t="inlineStr">
+      <c r="N123" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O123" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="27" t="inlineStr">
+      <c r="A124" s="28" t="inlineStr">
         <is>
           <t>PS5-60-04</t>
         </is>
@@ -9682,14 +9682,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O124" s="27" t="inlineStr">
+      <c r="O124" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="27" t="inlineStr">
+      <c r="A125" s="28" t="inlineStr">
         <is>
           <t>PS5-60-05</t>
         </is>
@@ -9748,17 +9748,17 @@
       </c>
       <c r="N125" s="54" t="inlineStr">
         <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="O125" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O125" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="27" t="inlineStr">
+      <c r="A126" s="28" t="inlineStr">
         <is>
           <t>PS5-60-06</t>
         </is>
@@ -9815,19 +9815,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N126" s="69" t="inlineStr">
-        <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="O126" s="27" t="inlineStr">
+      <c r="N126" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O126" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="27" t="inlineStr">
+      <c r="A127" s="28" t="inlineStr">
         <is>
           <t>PS5-60-07</t>
         </is>
@@ -9889,14 +9889,14 @@
           <t>99%</t>
         </is>
       </c>
-      <c r="O127" s="27" t="inlineStr">
+      <c r="O127" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="27" t="inlineStr">
+      <c r="A128" s="28" t="inlineStr">
         <is>
           <t>PS5-60-08</t>
         </is>
@@ -9955,17 +9955,17 @@
       </c>
       <c r="N128" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="O128" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O128" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="27" t="inlineStr">
+      <c r="A129" s="28" t="inlineStr">
         <is>
           <t>PS5-60-09</t>
         </is>
@@ -10022,19 +10022,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N129" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="O129" s="27" t="inlineStr">
+      <c r="N129" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O129" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="27" t="inlineStr">
+      <c r="A130" s="28" t="inlineStr">
         <is>
           <t>PS5-60-10</t>
         </is>
@@ -10093,17 +10093,17 @@
       </c>
       <c r="N130" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="O130" s="27" t="inlineStr">
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="O130" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="27" t="inlineStr">
+      <c r="A131" s="28" t="inlineStr">
         <is>
           <t>PS5-60-11</t>
         </is>
@@ -10162,17 +10162,17 @@
       </c>
       <c r="N131" s="54" t="inlineStr">
         <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="O131" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O131" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="27" t="inlineStr">
+      <c r="A132" s="28" t="inlineStr">
         <is>
           <t>PS5-60-12</t>
         </is>
@@ -10229,19 +10229,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N132" s="69" t="inlineStr">
-        <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="O132" s="27" t="inlineStr">
+      <c r="N132" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O132" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="27" t="inlineStr">
+      <c r="A133" s="28" t="inlineStr">
         <is>
           <t>PS5-60-13</t>
         </is>
@@ -10300,17 +10300,17 @@
       </c>
       <c r="N133" s="54" t="inlineStr">
         <is>
-          <t>98%</t>
-        </is>
-      </c>
-      <c r="O133" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O133" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="27" t="inlineStr">
+      <c r="A134" s="28" t="inlineStr">
         <is>
           <t>PS5-60-14</t>
         </is>
@@ -10369,17 +10369,17 @@
       </c>
       <c r="N134" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="O134" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O134" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="27" t="inlineStr">
+      <c r="A135" s="28" t="inlineStr">
         <is>
           <t>PS5-60-15</t>
         </is>
@@ -10436,19 +10436,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N135" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="O135" s="27" t="inlineStr">
+      <c r="N135" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O135" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="27" t="inlineStr">
+      <c r="A136" s="28" t="inlineStr">
         <is>
           <t>PS5-60-16</t>
         </is>
@@ -10507,17 +10507,17 @@
       </c>
       <c r="N136" s="54" t="inlineStr">
         <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="O136" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="O136" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="27" t="inlineStr">
+      <c r="A137" s="28" t="inlineStr">
         <is>
           <t>PS5-60-17</t>
         </is>
@@ -10574,19 +10574,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N137" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="O137" s="27" t="inlineStr">
+      <c r="N137" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O137" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="27" t="inlineStr">
+      <c r="A138" s="28" t="inlineStr">
         <is>
           <t>PS5-60-18</t>
         </is>
@@ -10643,19 +10643,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N138" s="69" t="inlineStr">
-        <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="O138" s="27" t="inlineStr">
+      <c r="N138" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O138" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="27" t="inlineStr">
+      <c r="A139" s="28" t="inlineStr">
         <is>
           <t>PS5-60-19</t>
         </is>
@@ -10714,17 +10714,17 @@
       </c>
       <c r="N139" s="54" t="inlineStr">
         <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="O139" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="O139" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="27" t="inlineStr">
+      <c r="A140" s="28" t="inlineStr">
         <is>
           <t>PS5-60-20</t>
         </is>
@@ -10781,19 +10781,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N140" s="69" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="O140" s="27" t="inlineStr">
+      <c r="N140" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O140" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="27" t="inlineStr">
+      <c r="A141" s="28" t="inlineStr">
         <is>
           <t>PS5-60-21</t>
         </is>
@@ -10850,19 +10850,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N141" s="69" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="O141" s="27" t="inlineStr">
+      <c r="N141" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O141" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="27" t="inlineStr">
+      <c r="A142" s="28" t="inlineStr">
         <is>
           <t>PS5-60-22</t>
         </is>
@@ -10921,17 +10921,17 @@
       </c>
       <c r="N142" s="69" t="inlineStr">
         <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="O142" s="27" t="inlineStr">
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="O142" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="27" t="inlineStr">
+      <c r="A143" s="28" t="inlineStr">
         <is>
           <t>PS5-60-23</t>
         </is>
@@ -10993,14 +10993,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O143" s="27" t="inlineStr">
+      <c r="O143" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="27" t="inlineStr">
+      <c r="A144" s="28" t="inlineStr">
         <is>
           <t>PS5-60-24</t>
         </is>
@@ -11062,14 +11062,14 @@
           <t>95%</t>
         </is>
       </c>
-      <c r="O144" s="27" t="inlineStr">
+      <c r="O144" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="27" t="inlineStr">
+      <c r="A145" s="28" t="inlineStr">
         <is>
           <t>PS5-60-25</t>
         </is>
@@ -11131,14 +11131,14 @@
           <t>95%</t>
         </is>
       </c>
-      <c r="O145" s="27" t="inlineStr">
+      <c r="O145" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="27" t="inlineStr">
+      <c r="A146" s="28" t="inlineStr">
         <is>
           <t>PS5-60-26</t>
         </is>
@@ -11200,14 +11200,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O146" s="27" t="inlineStr">
+      <c r="O146" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="27" t="inlineStr">
+      <c r="A147" s="28" t="inlineStr">
         <is>
           <t>PS5-60-27</t>
         </is>
@@ -11269,14 +11269,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O147" s="27" t="inlineStr">
+      <c r="O147" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="27" t="inlineStr">
+      <c r="A148" s="28" t="inlineStr">
         <is>
           <t>PS5-60-28</t>
         </is>
@@ -11345,7 +11345,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="27" t="inlineStr">
+      <c r="A149" s="28" t="inlineStr">
         <is>
           <t>PS5-60-29</t>
         </is>
@@ -11407,14 +11407,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O149" s="27" t="inlineStr">
+      <c r="O149" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="27" t="inlineStr">
+      <c r="A150" s="28" t="inlineStr">
         <is>
           <t>PS5-60-30</t>
         </is>
@@ -11476,14 +11476,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O150" s="27" t="inlineStr">
+      <c r="O150" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="27" t="inlineStr">
+      <c r="A151" s="28" t="inlineStr">
         <is>
           <t>PS5-60-31</t>
         </is>
@@ -11545,14 +11545,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O151" s="27" t="inlineStr">
+      <c r="O151" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="27" t="inlineStr">
+      <c r="A152" s="28" t="inlineStr">
         <is>
           <t>PS5-60-32</t>
         </is>
@@ -11614,14 +11614,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O152" s="27" t="inlineStr">
+      <c r="O152" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="27" t="inlineStr">
+      <c r="A153" s="28" t="inlineStr">
         <is>
           <t>PS5-60-33</t>
         </is>
@@ -11683,14 +11683,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O153" s="27" t="inlineStr">
+      <c r="O153" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="27" t="inlineStr">
+      <c r="A154" s="28" t="inlineStr">
         <is>
           <t>PS5-60-34</t>
         </is>
@@ -11752,14 +11752,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O154" s="27" t="inlineStr">
+      <c r="O154" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="27" t="inlineStr">
+      <c r="A155" s="28" t="inlineStr">
         <is>
           <t>PS5-60-35</t>
         </is>
@@ -11828,7 +11828,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="27" t="inlineStr">
+      <c r="A156" s="28" t="inlineStr">
         <is>
           <t>PS5-60-36</t>
         </is>
@@ -11890,14 +11890,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O156" s="27" t="inlineStr">
+      <c r="O156" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="27" t="inlineStr">
+      <c r="A157" s="28" t="inlineStr">
         <is>
           <t>PS5-60-37</t>
         </is>
@@ -11959,14 +11959,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O157" s="27" t="inlineStr">
+      <c r="O157" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="27" t="inlineStr">
+      <c r="A158" s="28" t="inlineStr">
         <is>
           <t>PS5-60-38</t>
         </is>
@@ -12028,14 +12028,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O158" s="27" t="inlineStr">
+      <c r="O158" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="27" t="inlineStr">
+      <c r="A159" s="28" t="inlineStr">
         <is>
           <t>PS5-60-39</t>
         </is>
@@ -12097,14 +12097,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O159" s="27" t="inlineStr">
+      <c r="O159" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="27" t="inlineStr">
+      <c r="A160" s="28" t="inlineStr">
         <is>
           <t>PS5-60-40</t>
         </is>
@@ -12166,14 +12166,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O160" s="27" t="inlineStr">
+      <c r="O160" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="27" t="inlineStr">
+      <c r="A161" s="28" t="inlineStr">
         <is>
           <t>PS5-60-41</t>
         </is>
@@ -12230,19 +12230,19 @@
           <t>17/17</t>
         </is>
       </c>
-      <c r="N161" s="69" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="O161" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N161" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O161" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="27" t="inlineStr">
+      <c r="A162" s="28" t="inlineStr">
         <is>
           <t>PS5-60-42</t>
         </is>
@@ -12311,7 +12311,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="27" t="inlineStr">
+      <c r="A163" s="28" t="inlineStr">
         <is>
           <t>PS5-60-43</t>
         </is>
@@ -12373,14 +12373,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O163" s="27" t="inlineStr">
+      <c r="O163" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="27" t="inlineStr">
+      <c r="A164" s="28" t="inlineStr">
         <is>
           <t>PS5-60-44</t>
         </is>
@@ -12442,14 +12442,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O164" s="27" t="inlineStr">
+      <c r="O164" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="27" t="inlineStr">
+      <c r="A165" s="28" t="inlineStr">
         <is>
           <t>PS5-60-45</t>
         </is>
@@ -12511,14 +12511,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O165" s="27" t="inlineStr">
+      <c r="O165" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="27" t="inlineStr">
+      <c r="A166" s="28" t="inlineStr">
         <is>
           <t>PS5-60-46</t>
         </is>
@@ -12580,14 +12580,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O166" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="O166" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="27" t="inlineStr">
+      <c r="A167" s="28" t="inlineStr">
         <is>
           <t>PS5-60-47</t>
         </is>
@@ -12649,14 +12649,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O167" s="27" t="inlineStr">
+      <c r="O167" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="27" t="inlineStr">
+      <c r="A168" s="28" t="inlineStr">
         <is>
           <t>PS5-60-48</t>
         </is>
@@ -12715,17 +12715,17 @@
       </c>
       <c r="N168" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
-        </is>
-      </c>
-      <c r="O168" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O168" s="69" t="inlineStr">
+        <is>
+          <t>partial</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="27" t="inlineStr">
+      <c r="A169" s="28" t="inlineStr">
         <is>
           <t>PS5-60-49</t>
         </is>
@@ -12784,17 +12784,17 @@
       </c>
       <c r="N169" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="O169" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O169" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="27" t="inlineStr">
+      <c r="A170" s="28" t="inlineStr">
         <is>
           <t>PS5-60-50</t>
         </is>
@@ -12853,17 +12853,17 @@
       </c>
       <c r="N170" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="O170" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O170" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="27" t="inlineStr">
+      <c r="A171" s="28" t="inlineStr">
         <is>
           <t>PS5-60-51</t>
         </is>
@@ -12922,17 +12922,17 @@
       </c>
       <c r="N171" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="O171" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O171" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="27" t="inlineStr">
+      <c r="A172" s="28" t="inlineStr">
         <is>
           <t>PS5-60-52</t>
         </is>
@@ -12989,19 +12989,19 @@
           <t>15/15</t>
         </is>
       </c>
-      <c r="N172" s="69" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="O172" s="27" t="inlineStr">
+      <c r="N172" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O172" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="27" t="inlineStr">
+      <c r="A173" s="28" t="inlineStr">
         <is>
           <t>PS5-60-53</t>
         </is>
@@ -13060,17 +13060,17 @@
       </c>
       <c r="N173" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="O173" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O173" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="27" t="inlineStr">
+      <c r="A174" s="28" t="inlineStr">
         <is>
           <t>PS5-60-54</t>
         </is>
@@ -13129,17 +13129,17 @@
       </c>
       <c r="N174" s="54" t="inlineStr">
         <is>
-          <t>91%</t>
-        </is>
-      </c>
-      <c r="O174" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O174" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="27" t="inlineStr">
+      <c r="A175" s="28" t="inlineStr">
         <is>
           <t>PS5-60-55</t>
         </is>
@@ -13196,19 +13196,19 @@
           <t>15/15</t>
         </is>
       </c>
-      <c r="N175" s="69" t="inlineStr">
-        <is>
-          <t>74%</t>
-        </is>
-      </c>
-      <c r="O175" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N175" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O175" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="27" t="inlineStr">
+      <c r="A176" s="28" t="inlineStr">
         <is>
           <t>PS5-60-56</t>
         </is>
@@ -13270,14 +13270,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O176" s="27" t="inlineStr">
+      <c r="O176" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="27" t="inlineStr">
+      <c r="A177" s="28" t="inlineStr">
         <is>
           <t>PS5-60-57</t>
         </is>
@@ -13336,17 +13336,17 @@
       </c>
       <c r="N177" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="O177" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O177" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="27" t="inlineStr">
+      <c r="A178" s="28" t="inlineStr">
         <is>
           <t>PS5-60-58</t>
         </is>
@@ -13408,14 +13408,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O178" s="27" t="inlineStr">
+      <c r="O178" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="27" t="inlineStr">
+      <c r="A179" s="28" t="inlineStr">
         <is>
           <t>PS5-60-59</t>
         </is>
@@ -13474,17 +13474,17 @@
       </c>
       <c r="N179" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="O179" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O179" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="27" t="inlineStr">
+      <c r="A180" s="28" t="inlineStr">
         <is>
           <t>PS5-60-60</t>
         </is>
@@ -13546,14 +13546,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O180" s="27" t="inlineStr">
+      <c r="O180" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="27" t="inlineStr">
+      <c r="A181" s="28" t="inlineStr">
         <is>
           <t>PS5-60-61</t>
         </is>
@@ -13612,17 +13612,17 @@
       </c>
       <c r="N181" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="O181" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O181" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="27" t="inlineStr">
+      <c r="A182" s="28" t="inlineStr">
         <is>
           <t>PS5-60-62</t>
         </is>
@@ -13684,14 +13684,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O182" s="27" t="inlineStr">
+      <c r="O182" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="27" t="inlineStr">
+      <c r="A183" s="28" t="inlineStr">
         <is>
           <t>PS5-60-63</t>
         </is>
@@ -13750,17 +13750,17 @@
       </c>
       <c r="N183" s="54" t="inlineStr">
         <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="O183" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O183" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="27" t="inlineStr">
+      <c r="A184" s="28" t="inlineStr">
         <is>
           <t>PS5-60-64</t>
         </is>
@@ -13819,17 +13819,17 @@
       </c>
       <c r="N184" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="O184" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="O184" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="27" t="inlineStr">
+      <c r="A185" s="28" t="inlineStr">
         <is>
           <t>PS5-60-65</t>
         </is>
@@ -13886,19 +13886,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N185" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="O185" s="27" t="inlineStr">
+      <c r="N185" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O185" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="27" t="inlineStr">
+      <c r="A186" s="28" t="inlineStr">
         <is>
           <t>PS5-60-66</t>
         </is>
@@ -13957,17 +13957,17 @@
       </c>
       <c r="N186" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="O186" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="O186" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="27" t="inlineStr">
+      <c r="A187" s="28" t="inlineStr">
         <is>
           <t>PS5-60-67</t>
         </is>
@@ -14024,19 +14024,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N187" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="O187" s="27" t="inlineStr">
+      <c r="N187" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O187" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="27" t="inlineStr">
+      <c r="A188" s="28" t="inlineStr">
         <is>
           <t>PS5-60-68</t>
         </is>
@@ -14093,19 +14093,19 @@
           <t>16/17</t>
         </is>
       </c>
-      <c r="N188" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="O188" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N188" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="O188" s="69" t="inlineStr">
+        <is>
+          <t>partial</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="27" t="inlineStr">
+      <c r="A189" s="28" t="inlineStr">
         <is>
           <t>PS5-60-69</t>
         </is>
@@ -14162,19 +14162,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N189" s="69" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="O189" s="27" t="inlineStr">
+      <c r="N189" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O189" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="27" t="inlineStr">
+      <c r="A190" s="28" t="inlineStr">
         <is>
           <t>PS5-60-70</t>
         </is>
@@ -14236,14 +14236,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O190" s="27" t="inlineStr">
+      <c r="O190" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="27" t="inlineStr">
+      <c r="A191" s="28" t="inlineStr">
         <is>
           <t>PS5-60-71</t>
         </is>
@@ -14305,14 +14305,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O191" s="27" t="inlineStr">
+      <c r="O191" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="27" t="inlineStr">
+      <c r="A192" s="28" t="inlineStr">
         <is>
           <t>PS5-60-72</t>
         </is>
@@ -14374,14 +14374,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O192" s="27" t="inlineStr">
+      <c r="O192" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="27" t="inlineStr">
+      <c r="A193" s="28" t="inlineStr">
         <is>
           <t>PS5-60-73</t>
         </is>
@@ -14443,14 +14443,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O193" s="27" t="inlineStr">
+      <c r="O193" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="27" t="inlineStr">
+      <c r="A194" s="28" t="inlineStr">
         <is>
           <t>PS5-60-74</t>
         </is>
@@ -14512,14 +14512,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O194" s="27" t="inlineStr">
-        <is>
-          <t>PLATFORM ISSUE</t>
+      <c r="O194" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="27" t="inlineStr">
+      <c r="A195" s="28" t="inlineStr">
         <is>
           <t>PS5-60-75</t>
         </is>
@@ -14581,14 +14581,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O195" s="27" t="inlineStr">
+      <c r="O195" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="27" t="inlineStr">
+      <c r="A196" s="28" t="inlineStr">
         <is>
           <t>PS5-60-76</t>
         </is>
@@ -14647,17 +14647,17 @@
       </c>
       <c r="N196" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="O196" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O196" s="28" t="inlineStr">
+        <is>
+          <t>FULL</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="27" t="inlineStr">
+      <c r="A197" s="28" t="inlineStr">
         <is>
           <t>PS5-61-01</t>
         </is>
@@ -14719,14 +14719,14 @@
           <t>90%</t>
         </is>
       </c>
-      <c r="O197" s="27" t="inlineStr">
+      <c r="O197" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="27" t="inlineStr">
+      <c r="A198" s="28" t="inlineStr">
         <is>
           <t>PS5-61-02</t>
         </is>
@@ -14783,19 +14783,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N198" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="O198" s="27" t="inlineStr">
+      <c r="N198" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O198" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="27" t="inlineStr">
+      <c r="A199" s="28" t="inlineStr">
         <is>
           <t>PS5-61-03</t>
         </is>
@@ -14852,19 +14852,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N199" s="69" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="O199" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N199" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O199" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="27" t="inlineStr">
+      <c r="A200" s="28" t="inlineStr">
         <is>
           <t>PS5-61-04</t>
         </is>
@@ -14926,14 +14926,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O200" s="27" t="inlineStr">
+      <c r="O200" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="27" t="inlineStr">
+      <c r="A201" s="28" t="inlineStr">
         <is>
           <t>PS5-61-05</t>
         </is>
@@ -14995,14 +14995,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O201" s="27" t="inlineStr">
+      <c r="O201" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="27" t="inlineStr">
+      <c r="A202" s="28" t="inlineStr">
         <is>
           <t>PS5-61-06</t>
         </is>
@@ -15061,17 +15061,17 @@
       </c>
       <c r="N202" s="69" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="O202" s="27" t="inlineStr">
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="O202" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="27" t="inlineStr">
+      <c r="A203" s="28" t="inlineStr">
         <is>
           <t>PS5-61-07</t>
         </is>
@@ -15133,14 +15133,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O203" s="27" t="inlineStr">
+      <c r="O203" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="27" t="inlineStr">
+      <c r="A204" s="28" t="inlineStr">
         <is>
           <t>PS5-61-08</t>
         </is>
@@ -15197,19 +15197,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N204" s="70" t="inlineStr">
-        <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="O204" s="27" t="inlineStr">
+      <c r="N204" s="54" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="O204" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="27" t="inlineStr">
+      <c r="A205" s="28" t="inlineStr">
         <is>
           <t>PS5-61-09</t>
         </is>
@@ -15268,17 +15268,17 @@
       </c>
       <c r="N205" s="70" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="O205" s="27" t="inlineStr">
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="O205" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="27" t="inlineStr">
+      <c r="A206" s="28" t="inlineStr">
         <is>
           <t>PS5-61-10</t>
         </is>
@@ -15340,14 +15340,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O206" s="27" t="inlineStr">
+      <c r="O206" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="27" t="inlineStr">
+      <c r="A207" s="28" t="inlineStr">
         <is>
           <t>PS5-61-11</t>
         </is>
@@ -15409,14 +15409,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O207" s="27" t="inlineStr">
+      <c r="O207" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="27" t="inlineStr">
+      <c r="A208" s="28" t="inlineStr">
         <is>
           <t>PS5-61-12</t>
         </is>
@@ -15478,14 +15478,14 @@
           <t>92%</t>
         </is>
       </c>
-      <c r="O208" s="27" t="inlineStr">
+      <c r="O208" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="27" t="inlineStr">
+      <c r="A209" s="28" t="inlineStr">
         <is>
           <t>PS5-61-13</t>
         </is>
@@ -15547,14 +15547,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O209" s="27" t="inlineStr">
+      <c r="O209" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="27" t="inlineStr">
+      <c r="A210" s="28" t="inlineStr">
         <is>
           <t>PS5-61-14</t>
         </is>
@@ -15616,14 +15616,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O210" s="27" t="inlineStr">
+      <c r="O210" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="27" t="inlineStr">
+      <c r="A211" s="28" t="inlineStr">
         <is>
           <t>PS5-62-01</t>
         </is>
@@ -15682,17 +15682,17 @@
       </c>
       <c r="N211" s="70" t="inlineStr">
         <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="O211" s="27" t="inlineStr">
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="O211" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="27" t="inlineStr">
+      <c r="A212" s="28" t="inlineStr">
         <is>
           <t>PS5-62-02</t>
         </is>
@@ -15749,19 +15749,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N212" s="70" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="O212" s="27" t="inlineStr">
+      <c r="N212" s="69" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="O212" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="27" t="inlineStr">
+      <c r="A213" s="28" t="inlineStr">
         <is>
           <t>PS5-62-03</t>
         </is>
@@ -15818,19 +15818,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N213" s="69" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="O213" s="27" t="inlineStr">
+      <c r="N213" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O213" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="27" t="inlineStr">
+      <c r="A214" s="28" t="inlineStr">
         <is>
           <t>PS5-62-04</t>
         </is>
@@ -15892,14 +15892,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O214" s="27" t="inlineStr">
+      <c r="O214" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="27" t="inlineStr">
+      <c r="A215" s="28" t="inlineStr">
         <is>
           <t>PS5-62-05</t>
         </is>
@@ -15961,14 +15961,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O215" s="27" t="inlineStr">
+      <c r="O215" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="27" t="inlineStr">
+      <c r="A216" s="28" t="inlineStr">
         <is>
           <t>PS5-62-06</t>
         </is>
@@ -16030,14 +16030,14 @@
           <t>26%</t>
         </is>
       </c>
-      <c r="O216" s="27" t="inlineStr">
+      <c r="O216" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="27" t="inlineStr">
+      <c r="A217" s="28" t="inlineStr">
         <is>
           <t>PS5-62-07</t>
         </is>
@@ -16099,14 +16099,14 @@
           <t>35%</t>
         </is>
       </c>
-      <c r="O217" s="27" t="inlineStr">
+      <c r="O217" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="27" t="inlineStr">
+      <c r="A218" s="28" t="inlineStr">
         <is>
           <t>PS5-62-08</t>
         </is>
@@ -16131,51 +16131,51 @@
         <v>22</v>
       </c>
       <c r="G218" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H218" s="70" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I218" s="23" t="inlineStr">
+        <is>
+          <t>4/22</t>
+        </is>
+      </c>
+      <c r="J218" s="23" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="K218" s="23" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="L218" s="23" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="M218" s="23" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="N218" s="70" t="inlineStr">
+        <is>
           <t>9%</t>
         </is>
       </c>
-      <c r="I218" s="23" t="inlineStr">
-        <is>
-          <t>2/22</t>
-        </is>
-      </c>
-      <c r="J218" s="23" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="K218" s="23" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="L218" s="23" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="M218" s="23" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="N218" s="70" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="O218" s="27" t="inlineStr">
+      <c r="O218" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="27" t="inlineStr">
+      <c r="A219" s="28" t="inlineStr">
         <is>
           <t>PS5-62-09</t>
         </is>
@@ -16232,19 +16232,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N219" s="70" t="inlineStr">
-        <is>
-          <t>46%</t>
-        </is>
-      </c>
-      <c r="O219" s="27" t="inlineStr">
+      <c r="N219" s="69" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="O219" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="27" t="inlineStr">
+      <c r="A220" s="28" t="inlineStr">
         <is>
           <t>PS5-62-10</t>
         </is>
@@ -16303,17 +16303,17 @@
       </c>
       <c r="N220" s="70" t="inlineStr">
         <is>
-          <t>23%</t>
-        </is>
-      </c>
-      <c r="O220" s="27" t="inlineStr">
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="O220" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="27" t="inlineStr">
+      <c r="A221" s="28" t="inlineStr">
         <is>
           <t>PS5-62-11</t>
         </is>
@@ -16372,17 +16372,17 @@
       </c>
       <c r="N221" s="70" t="inlineStr">
         <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="O221" s="27" t="inlineStr">
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="O221" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="27" t="inlineStr">
+      <c r="A222" s="28" t="inlineStr">
         <is>
           <t>PS5-62-12</t>
         </is>
@@ -16444,14 +16444,14 @@
           <t>96%</t>
         </is>
       </c>
-      <c r="O222" s="27" t="inlineStr">
+      <c r="O222" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="27" t="inlineStr">
+      <c r="A223" s="28" t="inlineStr">
         <is>
           <t>PS5-62-13</t>
         </is>
@@ -16513,14 +16513,14 @@
           <t>97%</t>
         </is>
       </c>
-      <c r="O223" s="27" t="inlineStr">
+      <c r="O223" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="27" t="inlineStr">
+      <c r="A224" s="28" t="inlineStr">
         <is>
           <t>PS5-62-14</t>
         </is>
@@ -16582,14 +16582,14 @@
           <t>3%</t>
         </is>
       </c>
-      <c r="O224" s="27" t="inlineStr">
+      <c r="O224" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="27" t="inlineStr">
+      <c r="A225" s="28" t="inlineStr">
         <is>
           <t>PS5-62-15</t>
         </is>
@@ -16651,14 +16651,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O225" s="27" t="inlineStr">
+      <c r="O225" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="27" t="inlineStr">
+      <c r="A226" s="28" t="inlineStr">
         <is>
           <t>PS5-62-16</t>
         </is>
@@ -16720,14 +16720,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O226" s="27" t="inlineStr">
+      <c r="O226" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="27" t="inlineStr">
+      <c r="A227" s="28" t="inlineStr">
         <is>
           <t>PS5-62-17</t>
         </is>
@@ -16789,14 +16789,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O227" s="27" t="inlineStr">
+      <c r="O227" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="27" t="inlineStr">
+      <c r="A228" s="28" t="inlineStr">
         <is>
           <t>PS5-62-18</t>
         </is>
@@ -16858,14 +16858,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O228" s="27" t="inlineStr">
+      <c r="O228" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="27" t="inlineStr">
+      <c r="A229" s="28" t="inlineStr">
         <is>
           <t>PS5-62-19</t>
         </is>
@@ -16927,14 +16927,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O229" s="27" t="inlineStr">
+      <c r="O229" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="27" t="inlineStr">
+      <c r="A230" s="28" t="inlineStr">
         <is>
           <t>PS5-62-20</t>
         </is>
@@ -16996,14 +16996,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O230" s="27" t="inlineStr">
+      <c r="O230" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="27" t="inlineStr">
+      <c r="A231" s="28" t="inlineStr">
         <is>
           <t>PS5-63-01</t>
         </is>
@@ -17060,19 +17060,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N231" s="70" t="inlineStr">
-        <is>
-          <t>32%</t>
-        </is>
-      </c>
-      <c r="O231" s="27" t="inlineStr">
+      <c r="N231" s="69" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="O231" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="27" t="inlineStr">
+      <c r="A232" s="28" t="inlineStr">
         <is>
           <t>PS5-63-02</t>
         </is>
@@ -17134,14 +17134,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O232" s="27" t="inlineStr">
+      <c r="O232" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="27" t="inlineStr">
+      <c r="A233" s="28" t="inlineStr">
         <is>
           <t>PS5-63-03</t>
         </is>
@@ -17203,14 +17203,14 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="O233" s="27" t="inlineStr">
+      <c r="O233" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="27" t="inlineStr">
+      <c r="A234" s="28" t="inlineStr">
         <is>
           <t>PS5-63-04</t>
         </is>
@@ -17272,14 +17272,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O234" s="27" t="inlineStr">
+      <c r="O234" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="27" t="inlineStr">
+      <c r="A235" s="28" t="inlineStr">
         <is>
           <t>PS5-63-05</t>
         </is>
@@ -17341,14 +17341,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O235" s="27" t="inlineStr">
+      <c r="O235" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="27" t="inlineStr">
+      <c r="A236" s="28" t="inlineStr">
         <is>
           <t>PS5-63-06</t>
         </is>
@@ -17410,14 +17410,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O236" s="27" t="inlineStr">
+      <c r="O236" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="27" t="inlineStr">
+      <c r="A237" s="28" t="inlineStr">
         <is>
           <t>PS5-63-07</t>
         </is>
@@ -17479,14 +17479,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O237" s="27" t="inlineStr">
+      <c r="O237" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="27" t="inlineStr">
+      <c r="A238" s="28" t="inlineStr">
         <is>
           <t>PS5-71-01</t>
         </is>
@@ -17543,19 +17543,19 @@
           <t>29/30</t>
         </is>
       </c>
-      <c r="N238" s="70" t="inlineStr">
-        <is>
-          <t>41%</t>
-        </is>
-      </c>
-      <c r="O238" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N238" s="54" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="O238" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="27" t="inlineStr">
+      <c r="A239" s="28" t="inlineStr">
         <is>
           <t>PS5-71-02</t>
         </is>
@@ -17612,88 +17612,88 @@
           <t>10/10</t>
         </is>
       </c>
-      <c r="N239" s="69" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="O239" s="27" t="inlineStr">
+      <c r="N239" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O239" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="28" t="inlineStr">
+        <is>
+          <t>PS5-71-03</t>
+        </is>
+      </c>
+      <c r="B240" s="83" t="inlineStr">
+        <is>
+          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
+        </is>
+      </c>
+      <c r="C240" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" s="95" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F240" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" s="95" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I240" s="23" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="J240" s="23" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="K240" s="23" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="L240" s="23" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="M240" s="23" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="N240" s="69" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="O240" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="27" t="inlineStr">
-        <is>
-          <t>PS5-71-03</t>
-        </is>
-      </c>
-      <c r="B240" s="83" t="inlineStr">
-        <is>
-          <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
-        </is>
-      </c>
-      <c r="C240" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D240" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E240" s="95" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F240" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G240" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H240" s="95" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I240" s="23" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="J240" s="23" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="K240" s="23" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="L240" s="23" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="M240" s="23" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="N240" s="69" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="O240" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="241">
-      <c r="A241" s="27" t="inlineStr">
+      <c r="A241" s="28" t="inlineStr">
         <is>
           <t>PS5-71-04</t>
         </is>
@@ -17752,17 +17752,17 @@
       </c>
       <c r="N241" s="69" t="inlineStr">
         <is>
-          <t>51%</t>
-        </is>
-      </c>
-      <c r="O241" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="O241" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="27" t="inlineStr">
+      <c r="A242" s="28" t="inlineStr">
         <is>
           <t>PS5-71-05</t>
         </is>
@@ -17819,19 +17819,19 @@
           <t>14/14</t>
         </is>
       </c>
-      <c r="N242" s="69" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
-      </c>
-      <c r="O242" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N242" s="54" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="O242" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="27" t="inlineStr">
+      <c r="A243" s="28" t="inlineStr">
         <is>
           <t>PS5-71-06</t>
         </is>
@@ -17893,14 +17893,14 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="O243" s="27" t="inlineStr">
+      <c r="O243" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="27" t="inlineStr">
+      <c r="A244" s="28" t="inlineStr">
         <is>
           <t>PS5-71-07</t>
         </is>
@@ -17959,17 +17959,17 @@
       </c>
       <c r="N244" s="69" t="inlineStr">
         <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="O244" s="27" t="inlineStr">
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="O244" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="27" t="inlineStr">
+      <c r="A245" s="28" t="inlineStr">
         <is>
           <t>PS5-71-08</t>
         </is>
@@ -18028,17 +18028,17 @@
       </c>
       <c r="N245" s="54" t="inlineStr">
         <is>
-          <t>93%</t>
-        </is>
-      </c>
-      <c r="O245" s="27" t="inlineStr">
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="O245" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="27" t="inlineStr">
+      <c r="A246" s="28" t="inlineStr">
         <is>
           <t>PS5-71-09</t>
         </is>
@@ -18097,17 +18097,17 @@
       </c>
       <c r="N246" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="O246" s="27" t="inlineStr">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O246" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="27" t="inlineStr">
+      <c r="A247" s="28" t="inlineStr">
         <is>
           <t>PS5-71-12</t>
         </is>
@@ -18166,17 +18166,17 @@
       </c>
       <c r="N247" s="69" t="inlineStr">
         <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="O247" s="27" t="inlineStr">
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="O247" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="27" t="inlineStr">
+      <c r="A248" s="28" t="inlineStr">
         <is>
           <t>PS5-71-13</t>
         </is>
@@ -18235,17 +18235,17 @@
       </c>
       <c r="N248" s="69" t="inlineStr">
         <is>
-          <t>66%</t>
-        </is>
-      </c>
-      <c r="O248" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="O248" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="27" t="inlineStr">
+      <c r="A249" s="28" t="inlineStr">
         <is>
           <t>PS5-71-14</t>
         </is>
@@ -18302,19 +18302,19 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N249" s="69" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="O249" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N249" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O249" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="27" t="inlineStr">
+      <c r="A250" s="28" t="inlineStr">
         <is>
           <t>PS5-71-15</t>
         </is>
@@ -18373,17 +18373,17 @@
       </c>
       <c r="N250" s="69" t="inlineStr">
         <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="O250" s="27" t="inlineStr">
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="O250" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="27" t="inlineStr">
+      <c r="A251" s="28" t="inlineStr">
         <is>
           <t>PS5-71-16</t>
         </is>
@@ -18440,19 +18440,19 @@
           <t>9/9</t>
         </is>
       </c>
-      <c r="N251" s="69" t="inlineStr">
-        <is>
-          <t>82%</t>
-        </is>
-      </c>
-      <c r="O251" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N251" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O251" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="27" t="inlineStr">
+      <c r="A252" s="28" t="inlineStr">
         <is>
           <t>PS5-71-17</t>
         </is>
@@ -18511,17 +18511,17 @@
       </c>
       <c r="N252" s="54" t="inlineStr">
         <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="O252" s="27" t="inlineStr">
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="O252" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="27" t="inlineStr">
+      <c r="A253" s="28" t="inlineStr">
         <is>
           <t>PS5-71-18</t>
         </is>
@@ -18578,19 +18578,19 @@
           <t>20/20</t>
         </is>
       </c>
-      <c r="N253" s="69" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="O253" s="27" t="inlineStr">
+      <c r="N253" s="54" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="O253" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="27" t="inlineStr">
+      <c r="A254" s="28" t="inlineStr">
         <is>
           <t>PS5-71-19</t>
         </is>
@@ -18649,17 +18649,17 @@
       </c>
       <c r="N254" s="69" t="inlineStr">
         <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="O254" s="27" t="inlineStr">
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="O254" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="27" t="inlineStr">
+      <c r="A255" s="28" t="inlineStr">
         <is>
           <t>PS5-71-20</t>
         </is>
@@ -18721,14 +18721,14 @@
           <t>89%</t>
         </is>
       </c>
-      <c r="O255" s="27" t="inlineStr">
+      <c r="O255" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="27" t="inlineStr">
+      <c r="A256" s="28" t="inlineStr">
         <is>
           <t>PS5-71-21</t>
         </is>
@@ -18790,14 +18790,14 @@
           <t>91%</t>
         </is>
       </c>
-      <c r="O256" s="27" t="inlineStr">
+      <c r="O256" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="27" t="inlineStr">
+      <c r="A257" s="28" t="inlineStr">
         <is>
           <t>PS5-71-22</t>
         </is>
@@ -18859,14 +18859,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O257" s="27" t="inlineStr">
+      <c r="O257" s="28" t="inlineStr">
         <is>
           <t>DONE(full)</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="27" t="inlineStr">
+      <c r="A258" s="28" t="inlineStr">
         <is>
           <t>PS5-71-23</t>
         </is>
@@ -18923,19 +18923,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N258" s="69" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="O258" s="27" t="inlineStr">
+      <c r="N258" s="54" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="O258" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="27" t="inlineStr">
+      <c r="A259" s="28" t="inlineStr">
         <is>
           <t>PS5-74-01</t>
         </is>
@@ -18992,19 +18992,19 @@
           <t>1/1</t>
         </is>
       </c>
-      <c r="N259" s="69" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="O259" s="27" t="inlineStr">
+      <c r="N259" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O259" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="27" t="inlineStr">
+      <c r="A260" s="28" t="inlineStr">
         <is>
           <t>PS5-74-02</t>
         </is>
@@ -19063,17 +19063,17 @@
       </c>
       <c r="N260" s="69" t="inlineStr">
         <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="O260" s="27" t="inlineStr">
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="O260" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="27" t="inlineStr">
+      <c r="A261" s="28" t="inlineStr">
         <is>
           <t>PS5-74-03</t>
         </is>
@@ -19135,14 +19135,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O261" s="27" t="inlineStr">
+      <c r="O261" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="27" t="inlineStr">
+      <c r="A262" s="28" t="inlineStr">
         <is>
           <t>PS5-74-04</t>
         </is>
@@ -19199,19 +19199,19 @@
           <t>8/8</t>
         </is>
       </c>
-      <c r="N262" s="69" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
-      <c r="O262" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N262" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O262" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="27" t="inlineStr">
+      <c r="A263" s="28" t="inlineStr">
         <is>
           <t>PS5-75-01</t>
         </is>
@@ -19268,19 +19268,19 @@
           <t>14/15</t>
         </is>
       </c>
-      <c r="N263" s="70" t="inlineStr">
-        <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="O263" s="27" t="inlineStr">
+      <c r="N263" s="69" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="O263" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="27" t="inlineStr">
+      <c r="A264" s="28" t="inlineStr">
         <is>
           <t>PS5-75-02</t>
         </is>
@@ -19337,19 +19337,19 @@
           <t>14/14</t>
         </is>
       </c>
-      <c r="N264" s="69" t="inlineStr">
-        <is>
-          <t>62%</t>
-        </is>
-      </c>
-      <c r="O264" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N264" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O264" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="27" t="inlineStr">
+      <c r="A265" s="28" t="inlineStr">
         <is>
           <t>PS5-75-03</t>
         </is>
@@ -19406,19 +19406,19 @@
           <t>15/15</t>
         </is>
       </c>
-      <c r="N265" s="69" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="O265" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N265" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O265" s="28" t="inlineStr">
+        <is>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="27" t="inlineStr">
+      <c r="A266" s="28" t="inlineStr">
         <is>
           <t>PS5-78-01</t>
         </is>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="N266" s="69" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="O266" s="69" t="inlineStr">
@@ -19487,7 +19487,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="27" t="inlineStr">
+      <c r="A267" s="28" t="inlineStr">
         <is>
           <t>PS5-79-01</t>
         </is>
@@ -19544,19 +19544,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N267" s="70" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="O267" s="27" t="inlineStr">
+      <c r="N267" s="69" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="O267" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="27" t="inlineStr">
+      <c r="A268" s="28" t="inlineStr">
         <is>
           <t>PS5-79-02</t>
         </is>
@@ -19613,19 +19613,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N268" s="70" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="O268" s="27" t="inlineStr">
+      <c r="N268" s="69" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="O268" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="27" t="inlineStr">
+      <c r="A269" s="28" t="inlineStr">
         <is>
           <t>PS5-79-03</t>
         </is>
@@ -19684,17 +19684,17 @@
       </c>
       <c r="N269" s="70" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="O269" s="27" t="inlineStr">
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="O269" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="27" t="inlineStr">
+      <c r="A270" s="28" t="inlineStr">
         <is>
           <t>PS5-79-04</t>
         </is>
@@ -19753,17 +19753,17 @@
       </c>
       <c r="N270" s="70" t="inlineStr">
         <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="O270" s="27" t="inlineStr">
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="O270" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="27" t="inlineStr">
+      <c r="A271" s="28" t="inlineStr">
         <is>
           <t>PS5-79-05</t>
         </is>
@@ -19822,17 +19822,17 @@
       </c>
       <c r="N271" s="70" t="inlineStr">
         <is>
-          <t>24%</t>
-        </is>
-      </c>
-      <c r="O271" s="27" t="inlineStr">
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="O271" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="27" t="inlineStr">
+      <c r="A272" s="28" t="inlineStr">
         <is>
           <t>PS5-79-06</t>
         </is>
@@ -19891,17 +19891,17 @@
       </c>
       <c r="N272" s="70" t="inlineStr">
         <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="O272" s="27" t="inlineStr">
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="O272" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="27" t="inlineStr">
+      <c r="A273" s="28" t="inlineStr">
         <is>
           <t>PS5-79-07</t>
         </is>
@@ -19958,19 +19958,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N273" s="70" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="O273" s="27" t="inlineStr">
+      <c r="N273" s="69" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="O273" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="27" t="inlineStr">
+      <c r="A274" s="28" t="inlineStr">
         <is>
           <t>PS5-79-08</t>
         </is>
@@ -20027,19 +20027,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N274" s="70" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="O274" s="27" t="inlineStr">
+      <c r="N274" s="69" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="O274" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="27" t="inlineStr">
+      <c r="A275" s="28" t="inlineStr">
         <is>
           <t>PS5-79-09</t>
         </is>
@@ -20098,17 +20098,17 @@
       </c>
       <c r="N275" s="70" t="inlineStr">
         <is>
-          <t>17%</t>
-        </is>
-      </c>
-      <c r="O275" s="27" t="inlineStr">
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="O275" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="27" t="inlineStr">
+      <c r="A276" s="28" t="inlineStr">
         <is>
           <t>PS5-79-10</t>
         </is>
@@ -20165,19 +20165,19 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N276" s="70" t="inlineStr">
-        <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="O276" s="27" t="inlineStr">
+      <c r="N276" s="69" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="O276" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="27" t="inlineStr">
+      <c r="A277" s="28" t="inlineStr">
         <is>
           <t>PS5-79-11</t>
         </is>
@@ -20236,17 +20236,17 @@
       </c>
       <c r="N277" s="70" t="inlineStr">
         <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="O277" s="27" t="inlineStr">
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="O277" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="27" t="inlineStr">
+      <c r="A278" s="28" t="inlineStr">
         <is>
           <t>PS5-79-12</t>
         </is>
@@ -20305,17 +20305,17 @@
       </c>
       <c r="N278" s="70" t="inlineStr">
         <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="O278" s="27" t="inlineStr">
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="O278" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="27" t="inlineStr">
+      <c r="A279" s="28" t="inlineStr">
         <is>
           <t>PS5-82-01</t>
         </is>
@@ -20372,19 +20372,19 @@
           <t>50/50</t>
         </is>
       </c>
-      <c r="N279" s="69" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="O279" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N279" s="54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O279" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="27" t="inlineStr">
+      <c r="A280" s="28" t="inlineStr">
         <is>
           <t>PS5-82-02</t>
         </is>
@@ -20441,19 +20441,19 @@
           <t>0/1</t>
         </is>
       </c>
-      <c r="N280" s="70" t="inlineStr">
-        <is>
-          <t>17%</t>
-        </is>
-      </c>
-      <c r="O280" s="27" t="inlineStr">
+      <c r="N280" s="69" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="O280" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="27" t="inlineStr">
+      <c r="A281" s="28" t="inlineStr">
         <is>
           <t>PS5-82-03</t>
         </is>
@@ -20515,14 +20515,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O281" s="27" t="inlineStr">
+      <c r="O281" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="27" t="inlineStr">
+      <c r="A282" s="28" t="inlineStr">
         <is>
           <t>PS5-82-04</t>
         </is>
@@ -20581,17 +20581,17 @@
       </c>
       <c r="N282" s="69" t="inlineStr">
         <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="O282" s="27" t="inlineStr">
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="O282" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="27" t="inlineStr">
+      <c r="A283" s="28" t="inlineStr">
         <is>
           <t>PS5-82-05</t>
         </is>
@@ -20653,14 +20653,14 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="O283" s="27" t="inlineStr">
+      <c r="O283" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="27" t="inlineStr">
+      <c r="A284" s="28" t="inlineStr">
         <is>
           <t>PS5-82-06</t>
         </is>
@@ -20722,14 +20722,14 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="O284" s="27" t="inlineStr">
+      <c r="O284" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="27" t="inlineStr">
+      <c r="A285" s="28" t="inlineStr">
         <is>
           <t>PS5-82-07</t>
         </is>
@@ -20791,14 +20791,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O285" s="27" t="inlineStr">
+      <c r="O285" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="27" t="inlineStr">
+      <c r="A286" s="28" t="inlineStr">
         <is>
           <t>PS5-83-01</t>
         </is>
@@ -20860,14 +20860,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O286" s="27" t="inlineStr">
+      <c r="O286" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="27" t="inlineStr">
+      <c r="A287" s="28" t="inlineStr">
         <is>
           <t>PS5-84-01</t>
         </is>
@@ -20929,14 +20929,14 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="O287" s="27" t="inlineStr">
+      <c r="O287" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="27" t="inlineStr">
+      <c r="A288" s="28" t="inlineStr">
         <is>
           <t>PS5-84-02</t>
         </is>
@@ -20998,14 +20998,14 @@
           <t>11%</t>
         </is>
       </c>
-      <c r="O288" s="27" t="inlineStr">
+      <c r="O288" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="27" t="inlineStr">
+      <c r="A289" s="28" t="inlineStr">
         <is>
           <t>PS5-84-03</t>
         </is>
@@ -21067,14 +21067,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O289" s="27" t="inlineStr">
+      <c r="O289" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="27" t="inlineStr">
+      <c r="A290" s="28" t="inlineStr">
         <is>
           <t>PS5-86-01</t>
         </is>
@@ -21136,14 +21136,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O290" s="27" t="inlineStr">
+      <c r="O290" s="28" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="27" t="inlineStr">
+      <c r="A291" s="28" t="inlineStr">
         <is>
           <t>PS5-91-01</t>
         </is>
@@ -21205,14 +21205,14 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O291" s="27" t="inlineStr">
+      <c r="O291" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="27" t="inlineStr">
+      <c r="A292" s="28" t="inlineStr">
         <is>
           <t>PS5-99-01</t>
         </is>
@@ -21274,14 +21274,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O292" s="27" t="inlineStr">
+      <c r="O292" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="27" t="inlineStr">
+      <c r="A293" s="28" t="inlineStr">
         <is>
           <t>PS5-99-02</t>
         </is>
@@ -21340,17 +21340,17 @@
       </c>
       <c r="N293" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="O293" s="27" t="inlineStr">
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="O293" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="27" t="inlineStr">
+      <c r="A294" s="28" t="inlineStr">
         <is>
           <t>PS5-99-03</t>
         </is>
@@ -21409,17 +21409,17 @@
       </c>
       <c r="N294" s="70" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="O294" s="27" t="inlineStr">
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="O294" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="27" t="inlineStr">
+      <c r="A295" s="28" t="inlineStr">
         <is>
           <t>PS5-99-04</t>
         </is>
@@ -21481,14 +21481,14 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="O295" s="27" t="inlineStr">
+      <c r="O295" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="27" t="inlineStr">
+      <c r="A296" s="28" t="inlineStr">
         <is>
           <t>PS5-99-05</t>
         </is>
@@ -21550,14 +21550,14 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="O296" s="27" t="inlineStr">
+      <c r="O296" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="27" t="inlineStr">
+      <c r="A297" s="28" t="inlineStr">
         <is>
           <t>PS5-99-06</t>
         </is>
@@ -21619,7 +21619,7 @@
           <t>67%</t>
         </is>
       </c>
-      <c r="O297" s="27" t="inlineStr">
+      <c r="O297" s="28" t="inlineStr">
         <is>
           <t>RE WALKDOWN</t>
         </is>

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -1296,11 +1296,11 @@
         <v>86</v>
       </c>
       <c r="G3" s="23" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H3" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="I3" s="23" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="J3" s="23" t="inlineStr">
         <is>
-          <t>36/40</t>
+          <t>38/40</t>
         </is>
       </c>
       <c r="K3" s="23" t="inlineStr">
@@ -1365,11 +1365,11 @@
         <v>85</v>
       </c>
       <c r="G4" s="23" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H4" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="I4" s="23" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="J4" s="23" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>24/27</t>
         </is>
       </c>
       <c r="K4" s="23" t="inlineStr">
@@ -1434,11 +1434,11 @@
         <v>76</v>
       </c>
       <c r="G5" s="23" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H5" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="J5" s="23" t="inlineStr">
         <is>
-          <t>19/23</t>
+          <t>20/23</t>
         </is>
       </c>
       <c r="K5" s="23" t="inlineStr">
@@ -2055,11 +2055,11 @@
         <v>66</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H14" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
@@ -6885,7 +6885,7 @@
         <v>1106</v>
       </c>
       <c r="G84" s="23" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="H84" s="70" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I84" s="23" t="inlineStr">
         <is>
-          <t>42/380</t>
+          <t>50/380</t>
         </is>
       </c>
       <c r="J84" s="23" t="inlineStr">
@@ -7299,16 +7299,16 @@
         <v>220</v>
       </c>
       <c r="G90" s="23" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H90" s="54" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I90" s="23" t="inlineStr">
         <is>
-          <t>88/92</t>
+          <t>89/92</t>
         </is>
       </c>
       <c r="J90" s="23" t="inlineStr">
@@ -7368,16 +7368,16 @@
         <v>220</v>
       </c>
       <c r="G91" s="23" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H91" s="54" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I91" s="23" t="inlineStr">
         <is>
-          <t>88/92</t>
+          <t>89/92</t>
         </is>
       </c>
       <c r="J91" s="23" t="inlineStr">
@@ -8058,7 +8058,7 @@
         <v>278</v>
       </c>
       <c r="G101" s="23" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H101" s="54" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="I101" s="23" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="J101" s="23" t="inlineStr">
@@ -8265,11 +8265,11 @@
         <v>11</v>
       </c>
       <c r="G104" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H104" s="70" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="I104" s="23" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="J104" s="23" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="K104" s="23" t="inlineStr">
@@ -8472,11 +8472,11 @@
         <v>68</v>
       </c>
       <c r="G107" s="23" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H107" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I107" s="23" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="J107" s="23" t="inlineStr">
         <is>
-          <t>23/24</t>
+          <t>24/24</t>
         </is>
       </c>
       <c r="K107" s="23" t="inlineStr">
@@ -8541,11 +8541,11 @@
         <v>68</v>
       </c>
       <c r="G108" s="23" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H108" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I108" s="23" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="J108" s="23" t="inlineStr">
         <is>
-          <t>23/24</t>
+          <t>24/24</t>
         </is>
       </c>
       <c r="K108" s="23" t="inlineStr">
@@ -8610,11 +8610,11 @@
         <v>68</v>
       </c>
       <c r="G109" s="23" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H109" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I109" s="23" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="J109" s="23" t="inlineStr">
         <is>
-          <t>23/24</t>
+          <t>24/24</t>
         </is>
       </c>
       <c r="K109" s="23" t="inlineStr">
@@ -8748,11 +8748,11 @@
         <v>83</v>
       </c>
       <c r="G111" s="23" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H111" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="I111" s="23" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="J111" s="23" t="inlineStr">
         <is>
-          <t>35/37</t>
+          <t>36/37</t>
         </is>
       </c>
       <c r="K111" s="23" t="inlineStr">
@@ -8955,11 +8955,11 @@
         <v>25</v>
       </c>
       <c r="G114" s="23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H114" s="69" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="I114" s="23" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="M114" s="23" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
       <c r="N114" s="69" t="inlineStr">
@@ -9231,16 +9231,16 @@
         <v>11</v>
       </c>
       <c r="G118" s="23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H118" s="70" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="I118" s="23" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="J118" s="23" t="inlineStr">
@@ -9369,11 +9369,11 @@
         <v>39</v>
       </c>
       <c r="G120" s="23" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H120" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="I120" s="23" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="M120" s="23" t="inlineStr">
         <is>
-          <t>37/39</t>
+          <t>38/39</t>
         </is>
       </c>
       <c r="N120" s="54" t="inlineStr">
@@ -18132,16 +18132,16 @@
         <v>125</v>
       </c>
       <c r="G247" s="23" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H247" s="69" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="I247" s="23" t="inlineStr">
         <is>
-          <t>17/24</t>
+          <t>18/24</t>
         </is>
       </c>
       <c r="J247" s="23" t="inlineStr">
@@ -18201,11 +18201,11 @@
         <v>56</v>
       </c>
       <c r="G248" s="23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H248" s="69" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="I248" s="23" t="inlineStr">
@@ -18215,7 +18215,7 @@
       </c>
       <c r="J248" s="23" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>22/27</t>
         </is>
       </c>
       <c r="K248" s="23" t="inlineStr">
@@ -18753,11 +18753,11 @@
         <v>55</v>
       </c>
       <c r="G256" s="23" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H256" s="54" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="I256" s="23" t="inlineStr">
@@ -18767,7 +18767,7 @@
       </c>
       <c r="J256" s="23" t="inlineStr">
         <is>
-          <t>20/25</t>
+          <t>21/25</t>
         </is>
       </c>
       <c r="K256" s="23" t="inlineStr">
@@ -19236,16 +19236,16 @@
         <v>30</v>
       </c>
       <c r="G263" s="23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H263" s="69" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I263" s="23" t="inlineStr">
         <is>
-          <t>1/7</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="J263" s="23" t="inlineStr">

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -19857,16 +19857,16 @@
         <v>75</v>
       </c>
       <c r="G272" s="23" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H272" s="70" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="I272" s="23" t="inlineStr">
         <is>
-          <t>11/73</t>
+          <t>17/73</t>
         </is>
       </c>
       <c r="J272" s="23" t="inlineStr">
@@ -19926,16 +19926,16 @@
         <v>75</v>
       </c>
       <c r="G273" s="23" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H273" s="69" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="I273" s="23" t="inlineStr">
         <is>
-          <t>48/73</t>
+          <t>53/73</t>
         </is>
       </c>
       <c r="J273" s="23" t="inlineStr">
@@ -19995,16 +19995,16 @@
         <v>75</v>
       </c>
       <c r="G274" s="23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H274" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="I274" s="23" t="inlineStr">
         <is>
-          <t>42/73</t>
+          <t>44/73</t>
         </is>
       </c>
       <c r="J274" s="23" t="inlineStr">
@@ -20064,16 +20064,16 @@
         <v>75</v>
       </c>
       <c r="G275" s="23" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H275" s="70" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="I275" s="23" t="inlineStr">
         <is>
-          <t>28/73</t>
+          <t>30/73</t>
         </is>
       </c>
       <c r="J275" s="23" t="inlineStr">
@@ -20133,16 +20133,16 @@
         <v>71</v>
       </c>
       <c r="G276" s="23" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H276" s="69" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="I276" s="23" t="inlineStr">
         <is>
-          <t>35/69</t>
+          <t>37/69</t>
         </is>
       </c>
       <c r="J276" s="23" t="inlineStr">
@@ -20271,16 +20271,16 @@
         <v>81</v>
       </c>
       <c r="G278" s="23" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H278" s="70" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="I278" s="23" t="inlineStr">
         <is>
-          <t>31/79</t>
+          <t>36/79</t>
         </is>
       </c>
       <c r="J278" s="23" t="inlineStr">

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -241,6 +241,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFe8d5c4"/>
         <bgColor rgb="FFe8d5c4"/>
       </patternFill>
@@ -309,12 +315,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
         <bgColor rgb="FFBDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -570,7 +570,7 @@
     <xf numFmtId="0" fontId="9" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -644,13 +644,10 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -674,22 +671,25 @@
     <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,10 +698,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -710,7 +710,7 @@
     <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,10 +722,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -740,7 +740,7 @@
     <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -773,16 +773,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="N3" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O3" s="28" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="N41" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="O41" s="28" t="inlineStr">
@@ -6885,41 +6885,41 @@
         <v>1106</v>
       </c>
       <c r="G84" s="23" t="n">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="H84" s="70" t="inlineStr">
         <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="I84" s="23" t="inlineStr">
+        <is>
+          <t>50/380</t>
+        </is>
+      </c>
+      <c r="J84" s="23" t="inlineStr">
+        <is>
+          <t>117/620</t>
+        </is>
+      </c>
+      <c r="K84" s="23" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="L84" s="23" t="inlineStr">
+        <is>
+          <t>6/9</t>
+        </is>
+      </c>
+      <c r="M84" s="23" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="N84" s="70" t="inlineStr">
+        <is>
           <t>15%</t>
-        </is>
-      </c>
-      <c r="I84" s="23" t="inlineStr">
-        <is>
-          <t>50/380</t>
-        </is>
-      </c>
-      <c r="J84" s="23" t="inlineStr">
-        <is>
-          <t>93/620</t>
-        </is>
-      </c>
-      <c r="K84" s="23" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="L84" s="23" t="inlineStr">
-        <is>
-          <t>6/9</t>
-        </is>
-      </c>
-      <c r="M84" s="23" t="inlineStr">
-        <is>
-          <t>0/0</t>
-        </is>
-      </c>
-      <c r="N84" s="70" t="inlineStr">
-        <is>
-          <t>12%</t>
         </is>
       </c>
       <c r="O84" s="28" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="N87" s="69" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="O87" s="28" t="inlineStr">
@@ -8955,11 +8955,11 @@
         <v>25</v>
       </c>
       <c r="G114" s="23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H114" s="69" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="I114" s="23" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="M114" s="23" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
       <c r="N114" s="69" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="N218" s="70" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="O218" s="28" t="inlineStr">
@@ -19512,16 +19512,16 @@
         <v>69</v>
       </c>
       <c r="G267" s="23" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H267" s="69" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="I267" s="23" t="inlineStr">
         <is>
-          <t>50/67</t>
+          <t>56/67</t>
         </is>
       </c>
       <c r="J267" s="23" t="inlineStr">
@@ -19581,16 +19581,16 @@
         <v>71</v>
       </c>
       <c r="G268" s="23" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H268" s="69" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="I268" s="23" t="inlineStr">
         <is>
-          <t>48/69</t>
+          <t>54/69</t>
         </is>
       </c>
       <c r="J268" s="23" t="inlineStr">
@@ -19857,16 +19857,16 @@
         <v>75</v>
       </c>
       <c r="G272" s="23" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H272" s="70" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="I272" s="23" t="inlineStr">
         <is>
-          <t>17/73</t>
+          <t>27/73</t>
         </is>
       </c>
       <c r="J272" s="23" t="inlineStr">
@@ -19995,16 +19995,16 @@
         <v>75</v>
       </c>
       <c r="G274" s="23" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H274" s="69" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="I274" s="23" t="inlineStr">
         <is>
-          <t>44/73</t>
+          <t>45/73</t>
         </is>
       </c>
       <c r="J274" s="23" t="inlineStr">
@@ -20064,16 +20064,16 @@
         <v>75</v>
       </c>
       <c r="G275" s="23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H275" s="70" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="I275" s="23" t="inlineStr">
         <is>
-          <t>30/73</t>
+          <t>31/73</t>
         </is>
       </c>
       <c r="J275" s="23" t="inlineStr">
@@ -20133,16 +20133,16 @@
         <v>71</v>
       </c>
       <c r="G276" s="23" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H276" s="69" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="I276" s="23" t="inlineStr">
         <is>
-          <t>37/69</t>
+          <t>42/69</t>
         </is>
       </c>
       <c r="J276" s="23" t="inlineStr">

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -19512,16 +19512,16 @@
         <v>69</v>
       </c>
       <c r="G267" s="23" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H267" s="69" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="I267" s="23" t="inlineStr">
         <is>
-          <t>56/67</t>
+          <t>57/67</t>
         </is>
       </c>
       <c r="J267" s="23" t="inlineStr">
@@ -19995,16 +19995,16 @@
         <v>75</v>
       </c>
       <c r="G274" s="23" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H274" s="69" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="I274" s="23" t="inlineStr">
         <is>
-          <t>45/73</t>
+          <t>47/73</t>
         </is>
       </c>
       <c r="J274" s="23" t="inlineStr">
@@ -20064,16 +20064,16 @@
         <v>75</v>
       </c>
       <c r="G275" s="23" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H275" s="70" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="I275" s="23" t="inlineStr">
         <is>
-          <t>31/73</t>
+          <t>34/73</t>
         </is>
       </c>
       <c r="J275" s="23" t="inlineStr">
@@ -20133,16 +20133,16 @@
         <v>71</v>
       </c>
       <c r="G276" s="23" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H276" s="69" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="I276" s="23" t="inlineStr">
         <is>
-          <t>42/69</t>
+          <t>50/69</t>
         </is>
       </c>
       <c r="J276" s="23" t="inlineStr">

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,6 +101,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF8a97a5"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FFc00000"/>
       <sz val="10"/>
     </font>
@@ -116,6 +122,11 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="FF8a97a5"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FFb35900"/>
       <sz val="10"/>
     </font>
@@ -124,12 +135,6 @@
       <color rgb="FF0a58ca"/>
       <sz val="10"/>
       <u val="single"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF8a97a5"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -172,7 +177,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -237,12 +242,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1b4f72"/>
         <bgColor rgb="FF1b4f72"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFffeb9c"/>
-        <bgColor rgb="FFffeb9c"/>
       </patternFill>
     </fill>
     <fill>
@@ -319,6 +318,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFffeb9c"/>
+        <bgColor rgb="FFffeb9c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFed7d31"/>
         <bgColor rgb="FFed7d31"/>
       </patternFill>
@@ -339,6 +344,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFc6efce"/>
         <bgColor rgb="FFc6efce"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8a97a5"/>
+        <bgColor rgb="FF8a97a5"/>
       </patternFill>
     </fill>
     <fill>
@@ -504,36 +515,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -545,16 +553,19 @@
     <xf numFmtId="0" fontId="2" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -570,7 +581,7 @@
     <xf numFmtId="0" fontId="9" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -579,13 +590,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -593,7 +604,7 @@
     <xf numFmtId="0" fontId="3" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -644,10 +655,13 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -671,25 +685,22 @@
     <xf numFmtId="0" fontId="6" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -698,10 +709,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -710,10 +721,13 @@
     <xf numFmtId="0" fontId="5" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -722,25 +736,31 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -749,40 +769,37 @@
     <xf numFmtId="0" fontId="9" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1178,20 +1195,20 @@
           <t>PS5 COMPLETION PLATFORM  |  SUB SYSTEM - 295 subsystem(s)</t>
         </is>
       </c>
-      <c r="B1" s="100" t="n"/>
-      <c r="C1" s="100" t="n"/>
-      <c r="D1" s="100" t="n"/>
-      <c r="E1" s="100" t="n"/>
-      <c r="F1" s="100" t="n"/>
-      <c r="G1" s="100" t="n"/>
-      <c r="H1" s="100" t="n"/>
-      <c r="I1" s="100" t="n"/>
-      <c r="J1" s="100" t="n"/>
-      <c r="K1" s="100" t="n"/>
-      <c r="L1" s="100" t="n"/>
-      <c r="M1" s="100" t="n"/>
-      <c r="N1" s="100" t="n"/>
-      <c r="O1" s="101" t="n"/>
+      <c r="B1" s="102" t="n"/>
+      <c r="C1" s="102" t="n"/>
+      <c r="D1" s="102" t="n"/>
+      <c r="E1" s="102" t="n"/>
+      <c r="F1" s="102" t="n"/>
+      <c r="G1" s="102" t="n"/>
+      <c r="H1" s="102" t="n"/>
+      <c r="I1" s="102" t="n"/>
+      <c r="J1" s="102" t="n"/>
+      <c r="K1" s="102" t="n"/>
+      <c r="L1" s="102" t="n"/>
+      <c r="M1" s="102" t="n"/>
+      <c r="N1" s="102" t="n"/>
+      <c r="O1" s="103" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -1276,7 +1293,7 @@
           <t>PS5-01-01</t>
         </is>
       </c>
-      <c r="B3" s="83" t="inlineStr">
+      <c r="B3" s="86" t="inlineStr">
         <is>
           <t>PS5-01-01 - Fire Water Jockey Pump A/B</t>
         </is>
@@ -1330,7 +1347,7 @@
       </c>
       <c r="N3" s="54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="O3" s="28" t="inlineStr">
@@ -1345,7 +1362,7 @@
           <t>PS5-01-02</t>
         </is>
       </c>
-      <c r="B4" s="83" t="inlineStr">
+      <c r="B4" s="86" t="inlineStr">
         <is>
           <t>PS5-01-02 - Fire Water Pump A</t>
         </is>
@@ -1399,7 +1416,7 @@
       </c>
       <c r="N4" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="O4" s="28" t="inlineStr">
@@ -1414,7 +1431,7 @@
           <t>PS5-01-03</t>
         </is>
       </c>
-      <c r="B5" s="83" t="inlineStr">
+      <c r="B5" s="86" t="inlineStr">
         <is>
           <t>PS5-01-03 - Fire Water Pump B</t>
         </is>
@@ -1468,7 +1485,7 @@
       </c>
       <c r="N5" s="54" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="O5" s="28" t="inlineStr">
@@ -1483,7 +1500,7 @@
           <t>PS5-01-04</t>
         </is>
       </c>
-      <c r="B6" s="83" t="inlineStr">
+      <c r="B6" s="86" t="inlineStr">
         <is>
           <t>PS5-01-04 - Fire Water Pump Mini Flow Recycle</t>
         </is>
@@ -1552,7 +1569,7 @@
           <t>PS5-01-05</t>
         </is>
       </c>
-      <c r="B7" s="83" t="inlineStr">
+      <c r="B7" s="86" t="inlineStr">
         <is>
           <t>PS5-01-05 - Foam Skid</t>
         </is>
@@ -1621,7 +1638,7 @@
           <t>PS5-01-06</t>
         </is>
       </c>
-      <c r="B8" s="83" t="inlineStr">
+      <c r="B8" s="86" t="inlineStr">
         <is>
           <t>PS5-01-06 - Foam Concentrate Distribution</t>
         </is>
@@ -1690,7 +1707,7 @@
           <t>PS5-01-07</t>
         </is>
       </c>
-      <c r="B9" s="83" t="inlineStr">
+      <c r="B9" s="86" t="inlineStr">
         <is>
           <t>PS5-01-07 - Fire Water Ring Main &amp; Distribution</t>
         </is>
@@ -1759,7 +1776,7 @@
           <t>PS5-01-08</t>
         </is>
       </c>
-      <c r="B10" s="83" t="inlineStr">
+      <c r="B10" s="86" t="inlineStr">
         <is>
           <t>PS5-01-08 - PS5 Deluge Valve Skid (PS5-01-UK-6100)</t>
         </is>
@@ -1828,7 +1845,7 @@
           <t>PS5-01-09</t>
         </is>
       </c>
-      <c r="B11" s="83" t="inlineStr">
+      <c r="B11" s="86" t="inlineStr">
         <is>
           <t>PS5-01-09 - Inergen for EITS Building</t>
         </is>
@@ -1897,7 +1914,7 @@
           <t>PS5-01-10</t>
         </is>
       </c>
-      <c r="B12" s="83" t="inlineStr">
+      <c r="B12" s="86" t="inlineStr">
         <is>
           <t>PS5-01-10 - Water Mist Package</t>
         </is>
@@ -1966,7 +1983,7 @@
           <t>PS5-01-11</t>
         </is>
       </c>
-      <c r="B13" s="83" t="inlineStr">
+      <c r="B13" s="86" t="inlineStr">
         <is>
           <t>PS5-01-11 - Inergen for Power Gen Building</t>
         </is>
@@ -2035,7 +2052,7 @@
           <t>PS5-02-01</t>
         </is>
       </c>
-      <c r="B14" s="83" t="inlineStr">
+      <c r="B14" s="86" t="inlineStr">
         <is>
           <t>PS5-02-01 - Miscellaneous Safety equipment</t>
         </is>
@@ -2089,7 +2106,7 @@
       </c>
       <c r="N14" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="O14" s="28" t="inlineStr">
@@ -2104,7 +2121,7 @@
           <t>PS5-02-02</t>
         </is>
       </c>
-      <c r="B15" s="83" t="inlineStr">
+      <c r="B15" s="86" t="inlineStr">
         <is>
           <t>PS5-02-02 - Portable Fire Fighting Equipments</t>
         </is>
@@ -2173,7 +2190,7 @@
           <t>PS5-03-01</t>
         </is>
       </c>
-      <c r="B16" s="83" t="inlineStr">
+      <c r="B16" s="86" t="inlineStr">
         <is>
           <t>PS5-03-01 - FZ-01 - Process Area</t>
         </is>
@@ -2184,7 +2201,7 @@
       <c r="D16" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="95" t="inlineStr">
+      <c r="E16" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2242,7 +2259,7 @@
           <t>PS5-03-03</t>
         </is>
       </c>
-      <c r="B17" s="83" t="inlineStr">
+      <c r="B17" s="86" t="inlineStr">
         <is>
           <t>PS5-03-03 - FZ-03 - Buildings Area</t>
         </is>
@@ -2253,7 +2270,7 @@
       <c r="D17" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="95" t="inlineStr">
+      <c r="E17" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2311,7 +2328,7 @@
           <t>PS5-03-04</t>
         </is>
       </c>
-      <c r="B18" s="83" t="inlineStr">
+      <c r="B18" s="86" t="inlineStr">
         <is>
           <t>PS5-03-04 - FZ-04 - Utilities - Diesel and Firewater Pumps Areas</t>
         </is>
@@ -2322,7 +2339,7 @@
       <c r="D18" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="95" t="inlineStr">
+      <c r="E18" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2380,7 +2397,7 @@
           <t>PS5-03-06</t>
         </is>
       </c>
-      <c r="B19" s="83" t="inlineStr">
+      <c r="B19" s="86" t="inlineStr">
         <is>
           <t>PS5-03-06 - FZ-06 - Transformer Area</t>
         </is>
@@ -2449,7 +2466,7 @@
           <t>PS5-03-07</t>
         </is>
       </c>
-      <c r="B20" s="83" t="inlineStr">
+      <c r="B20" s="86" t="inlineStr">
         <is>
           <t>PS5-03-07 - FZ-07 - Pretreatment Area</t>
         </is>
@@ -2460,7 +2477,7 @@
       <c r="D20" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="95" t="inlineStr">
+      <c r="E20" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2518,7 +2535,7 @@
           <t>PS5-03-08</t>
         </is>
       </c>
-      <c r="B21" s="83" t="inlineStr">
+      <c r="B21" s="86" t="inlineStr">
         <is>
           <t>PS5-03-08 - FZ-08 - Utilities - Power Generation Area - External</t>
         </is>
@@ -2529,7 +2546,7 @@
       <c r="D21" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="95" t="inlineStr">
+      <c r="E21" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2587,7 +2604,7 @@
           <t>PS5-03-09</t>
         </is>
       </c>
-      <c r="B22" s="83" t="inlineStr">
+      <c r="B22" s="86" t="inlineStr">
         <is>
           <t>PS5-03-09 - FZ-09 - Power Generation Building - Engine Bay 1</t>
         </is>
@@ -2656,7 +2673,7 @@
           <t>PS5-03-10</t>
         </is>
       </c>
-      <c r="B23" s="83" t="inlineStr">
+      <c r="B23" s="86" t="inlineStr">
         <is>
           <t>PS5-03-10 - FZ-10 - Power Generation Building - Engine Bay 2</t>
         </is>
@@ -2667,7 +2684,7 @@
       <c r="D23" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="95" t="inlineStr">
+      <c r="E23" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2725,7 +2742,7 @@
           <t>PS5-03-11</t>
         </is>
       </c>
-      <c r="B24" s="83" t="inlineStr">
+      <c r="B24" s="86" t="inlineStr">
         <is>
           <t>PS5-03-11 - FZ-11 - Power Generation Building - Engine Bay 3</t>
         </is>
@@ -2736,7 +2753,7 @@
       <c r="D24" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="95" t="inlineStr">
+      <c r="E24" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2794,7 +2811,7 @@
           <t>PS5-03-12</t>
         </is>
       </c>
-      <c r="B25" s="83" t="inlineStr">
+      <c r="B25" s="86" t="inlineStr">
         <is>
           <t>PS5-03-12 - FZ-12 - Power Generation Building - Engine Bay 4</t>
         </is>
@@ -2805,7 +2822,7 @@
       <c r="D25" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="95" t="inlineStr">
+      <c r="E25" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2863,7 +2880,7 @@
           <t>PS5-03-13</t>
         </is>
       </c>
-      <c r="B26" s="83" t="inlineStr">
+      <c r="B26" s="86" t="inlineStr">
         <is>
           <t>PS5-03-13 - FZ-13 - Power Generation Building - Instrument Air Room</t>
         </is>
@@ -2874,7 +2891,7 @@
       <c r="D26" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="95" t="inlineStr">
+      <c r="E26" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2932,7 +2949,7 @@
           <t>PS5-03-14</t>
         </is>
       </c>
-      <c r="B27" s="83" t="inlineStr">
+      <c r="B27" s="86" t="inlineStr">
         <is>
           <t>PS5-03-14 - FZ-14 - Power Generation Building - Switchgear Room</t>
         </is>
@@ -3001,7 +3018,7 @@
           <t>PS5-03-15</t>
         </is>
       </c>
-      <c r="B28" s="83" t="inlineStr">
+      <c r="B28" s="86" t="inlineStr">
         <is>
           <t>PS5-03-15 - FZ-15 - Power Generation Building - Generator Room 1</t>
         </is>
@@ -3012,7 +3029,7 @@
       <c r="D28" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="95" t="inlineStr">
+      <c r="E28" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3070,7 +3087,7 @@
           <t>PS5-03-16</t>
         </is>
       </c>
-      <c r="B29" s="83" t="inlineStr">
+      <c r="B29" s="86" t="inlineStr">
         <is>
           <t>PS5-03-16 - FZ-16 - Power Generation Building - Generator Room 2</t>
         </is>
@@ -3081,7 +3098,7 @@
       <c r="D29" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="95" t="inlineStr">
+      <c r="E29" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3139,7 +3156,7 @@
           <t>PS5-03-17</t>
         </is>
       </c>
-      <c r="B30" s="83" t="inlineStr">
+      <c r="B30" s="86" t="inlineStr">
         <is>
           <t>PS5-03-17 - FZ-17 - Power Generation Building - Generator Room 3</t>
         </is>
@@ -3150,7 +3167,7 @@
       <c r="D30" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="95" t="inlineStr">
+      <c r="E30" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3208,7 +3225,7 @@
           <t>PS5-03-18</t>
         </is>
       </c>
-      <c r="B31" s="83" t="inlineStr">
+      <c r="B31" s="86" t="inlineStr">
         <is>
           <t>PS5-03-18 - FZ-18 - Power Generation Building - Generator Room 4</t>
         </is>
@@ -3219,7 +3236,7 @@
       <c r="D31" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="95" t="inlineStr">
+      <c r="E31" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3277,7 +3294,7 @@
           <t>PS5-03-19</t>
         </is>
       </c>
-      <c r="B32" s="83" t="inlineStr">
+      <c r="B32" s="86" t="inlineStr">
         <is>
           <t>PS5-03-19 - FZ-19 - Power Generation Building - Battery Room</t>
         </is>
@@ -3288,7 +3305,7 @@
       <c r="D32" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="95" t="inlineStr">
+      <c r="E32" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3346,7 +3363,7 @@
           <t>PS5-03-20</t>
         </is>
       </c>
-      <c r="B33" s="83" t="inlineStr">
+      <c r="B33" s="86" t="inlineStr">
         <is>
           <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
         </is>
@@ -3415,7 +3432,7 @@
           <t>PS5-03-21</t>
         </is>
       </c>
-      <c r="B34" s="83" t="inlineStr">
+      <c r="B34" s="86" t="inlineStr">
         <is>
           <t>PS5-03-21 - FZ-21 - Power Generation Building - Air Handling Unit</t>
         </is>
@@ -3426,7 +3443,7 @@
       <c r="D34" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="95" t="inlineStr">
+      <c r="E34" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3484,7 +3501,7 @@
           <t>PS5-03-22</t>
         </is>
       </c>
-      <c r="B35" s="83" t="inlineStr">
+      <c r="B35" s="86" t="inlineStr">
         <is>
           <t>PS5-03-22 - FZ-G1 - Guard House</t>
         </is>
@@ -3495,7 +3512,7 @@
       <c r="D35" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="95" t="inlineStr">
+      <c r="E35" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3553,7 +3570,7 @@
           <t>PS5-03-23</t>
         </is>
       </c>
-      <c r="B36" s="83" t="inlineStr">
+      <c r="B36" s="86" t="inlineStr">
         <is>
           <t>PS5-03-23 - FZ-E1 to E3 - EITS Building</t>
         </is>
@@ -3575,7 +3592,7 @@
       <c r="G36" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="95" t="inlineStr">
+      <c r="H36" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3622,7 +3639,7 @@
           <t>PS5-03-24</t>
         </is>
       </c>
-      <c r="B37" s="83" t="inlineStr">
+      <c r="B37" s="86" t="inlineStr">
         <is>
           <t>PS5-03-24 - FZ - Office and Facilities Building</t>
         </is>
@@ -3633,7 +3650,7 @@
       <c r="D37" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="95" t="inlineStr">
+      <c r="E37" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3691,7 +3708,7 @@
           <t>PS5-03-25</t>
         </is>
       </c>
-      <c r="B38" s="83" t="inlineStr">
+      <c r="B38" s="86" t="inlineStr">
         <is>
           <t>PS5-03-25 - FZ - Workshop &amp; Warehouse</t>
         </is>
@@ -3702,7 +3719,7 @@
       <c r="D38" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="95" t="inlineStr">
+      <c r="E38" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3760,7 +3777,7 @@
           <t>PS5-04-01</t>
         </is>
       </c>
-      <c r="B39" s="83" t="inlineStr">
+      <c r="B39" s="86" t="inlineStr">
         <is>
           <t>PS5-04-01 - Office Building PCS System</t>
         </is>
@@ -3771,7 +3788,7 @@
       <c r="D39" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="95" t="inlineStr">
+      <c r="E39" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3782,7 +3799,7 @@
       <c r="G39" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="95" t="inlineStr">
+      <c r="H39" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3829,7 +3846,7 @@
           <t>PS5-04-02</t>
         </is>
       </c>
-      <c r="B40" s="83" t="inlineStr">
+      <c r="B40" s="86" t="inlineStr">
         <is>
           <t>PS5-04-02 - Office Building SIS/FGS System</t>
         </is>
@@ -3840,7 +3857,7 @@
       <c r="D40" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="95" t="inlineStr">
+      <c r="E40" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3898,7 +3915,7 @@
           <t>PS5-04-03</t>
         </is>
       </c>
-      <c r="B41" s="83" t="inlineStr">
+      <c r="B41" s="86" t="inlineStr">
         <is>
           <t>PS5-04-03 - 33kV ICSS System</t>
         </is>
@@ -3920,7 +3937,7 @@
       <c r="G41" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="95" t="inlineStr">
+      <c r="H41" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3967,7 +3984,7 @@
           <t>PS5-04-04</t>
         </is>
       </c>
-      <c r="B42" s="83" t="inlineStr">
+      <c r="B42" s="86" t="inlineStr">
         <is>
           <t>PS5-04-04 - 33kV PCS System</t>
         </is>
@@ -3989,7 +4006,7 @@
       <c r="G42" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="95" t="inlineStr">
+      <c r="H42" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4036,7 +4053,7 @@
           <t>PS5-04-05</t>
         </is>
       </c>
-      <c r="B43" s="83" t="inlineStr">
+      <c r="B43" s="86" t="inlineStr">
         <is>
           <t>PS5-04-05 - 33kV SIS/FGS System</t>
         </is>
@@ -4058,7 +4075,7 @@
       <c r="G43" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="95" t="inlineStr">
+      <c r="H43" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4105,7 +4122,7 @@
           <t>PS5-05-01</t>
         </is>
       </c>
-      <c r="B44" s="83" t="inlineStr">
+      <c r="B44" s="86" t="inlineStr">
         <is>
           <t>PS5-05-01 - Emergency Diesel Generator Package</t>
         </is>
@@ -4174,7 +4191,7 @@
           <t>PS5-05-02</t>
         </is>
       </c>
-      <c r="B45" s="83" t="inlineStr">
+      <c r="B45" s="86" t="inlineStr">
         <is>
           <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
         </is>
@@ -4243,7 +4260,7 @@
           <t>PS5-06-01</t>
         </is>
       </c>
-      <c r="B46" s="83" t="inlineStr">
+      <c r="B46" s="86" t="inlineStr">
         <is>
           <t>PS5-06-01 - AC UPS - EITS Building</t>
         </is>
@@ -4265,7 +4282,7 @@
       <c r="G46" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="95" t="inlineStr">
+      <c r="H46" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4312,7 +4329,7 @@
           <t>PS5-06-02</t>
         </is>
       </c>
-      <c r="B47" s="83" t="inlineStr">
+      <c r="B47" s="86" t="inlineStr">
         <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
@@ -4381,7 +4398,7 @@
           <t>PS5-06-03</t>
         </is>
       </c>
-      <c r="B48" s="83" t="inlineStr">
+      <c r="B48" s="86" t="inlineStr">
         <is>
           <t>PS5-06-03 - AC UPS - Office &amp; Facilities Building</t>
         </is>
@@ -4392,7 +4409,7 @@
       <c r="D48" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="95" t="inlineStr">
+      <c r="E48" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4450,7 +4467,7 @@
           <t>PS5-06-04</t>
         </is>
       </c>
-      <c r="B49" s="83" t="inlineStr">
+      <c r="B49" s="86" t="inlineStr">
         <is>
           <t>PS5-06-04 - AC UPS - Guard House</t>
         </is>
@@ -4461,7 +4478,7 @@
       <c r="D49" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E49" s="95" t="inlineStr">
+      <c r="E49" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4519,7 +4536,7 @@
           <t>PS5-06-05</t>
         </is>
       </c>
-      <c r="B50" s="83" t="inlineStr">
+      <c r="B50" s="86" t="inlineStr">
         <is>
           <t>PS5-06-05 - AC UPS - Workshop &amp; Warehouse</t>
         </is>
@@ -4530,7 +4547,7 @@
       <c r="D50" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="95" t="inlineStr">
+      <c r="E50" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4588,7 +4605,7 @@
           <t>PS5-08-01</t>
         </is>
       </c>
-      <c r="B51" s="83" t="inlineStr">
+      <c r="B51" s="86" t="inlineStr">
         <is>
           <t>PS5-08-01</t>
         </is>
@@ -4610,7 +4627,7 @@
       <c r="G51" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="95" t="inlineStr">
+      <c r="H51" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4640,9 +4657,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N51" s="70" t="inlineStr">
-        <is>
-          <t>36%</t>
+      <c r="N51" s="75" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="28" t="inlineStr">
@@ -4657,7 +4674,7 @@
           <t>PS5-08-01a</t>
         </is>
       </c>
-      <c r="B52" s="83" t="inlineStr">
+      <c r="B52" s="86" t="inlineStr">
         <is>
           <t>PS5-08-01a - PAGA (Required for SU)</t>
         </is>
@@ -4668,7 +4685,7 @@
       <c r="D52" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="95" t="inlineStr">
+      <c r="E52" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4709,9 +4726,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N52" s="70" t="inlineStr">
-        <is>
-          <t>20%</t>
+      <c r="N52" s="69" t="inlineStr">
+        <is>
+          <t>74%</t>
         </is>
       </c>
       <c r="O52" s="28" t="inlineStr">
@@ -4726,7 +4743,7 @@
           <t>PS5-08-01b</t>
         </is>
       </c>
-      <c r="B53" s="83" t="inlineStr">
+      <c r="B53" s="86" t="inlineStr">
         <is>
           <t>PS5-08-01b - PAGA (Not required for SU)</t>
         </is>
@@ -4737,7 +4754,7 @@
       <c r="D53" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="95" t="inlineStr">
+      <c r="E53" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4780,7 +4797,7 @@
       </c>
       <c r="N53" s="70" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="O53" s="28" t="inlineStr">
@@ -4795,7 +4812,7 @@
           <t>PS5-08-03</t>
         </is>
       </c>
-      <c r="B54" s="83" t="inlineStr">
+      <c r="B54" s="86" t="inlineStr">
         <is>
           <t>PS5-08-03 - Telephone</t>
         </is>
@@ -4806,7 +4823,7 @@
       <c r="D54" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="95" t="inlineStr">
+      <c r="E54" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4864,7 +4881,7 @@
           <t>PS5-08-04</t>
         </is>
       </c>
-      <c r="B55" s="83" t="inlineStr">
+      <c r="B55" s="86" t="inlineStr">
         <is>
           <t>PS5-08-04 - Hotline</t>
         </is>
@@ -4875,7 +4892,7 @@
       <c r="D55" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E55" s="95" t="inlineStr">
+      <c r="E55" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4886,7 +4903,7 @@
       <c r="G55" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="95" t="inlineStr">
+      <c r="H55" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4933,7 +4950,7 @@
           <t>PS5-08-07</t>
         </is>
       </c>
-      <c r="B56" s="83" t="inlineStr">
+      <c r="B56" s="86" t="inlineStr">
         <is>
           <t>PS5-08-07 - Multi-Channel Voice Recorder</t>
         </is>
@@ -4944,7 +4961,7 @@
       <c r="D56" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="95" t="inlineStr">
+      <c r="E56" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4955,7 +4972,7 @@
       <c r="G56" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="95" t="inlineStr">
+      <c r="H56" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5002,7 +5019,7 @@
           <t>PS5-08-11</t>
         </is>
       </c>
-      <c r="B57" s="83" t="inlineStr">
+      <c r="B57" s="86" t="inlineStr">
         <is>
           <t>PS5-08-11 - Corporate LAN  (SIE)</t>
         </is>
@@ -5071,7 +5088,7 @@
           <t>PS5-08-12</t>
         </is>
       </c>
-      <c r="B58" s="83" t="inlineStr">
+      <c r="B58" s="86" t="inlineStr">
         <is>
           <t>PS5-08-12 - Corporate Wireless LAN (SIE)</t>
         </is>
@@ -5082,7 +5099,7 @@
       <c r="D58" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E58" s="95" t="inlineStr">
+      <c r="E58" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5140,7 +5157,7 @@
           <t>PS5-08-13</t>
         </is>
       </c>
-      <c r="B59" s="83" t="inlineStr">
+      <c r="B59" s="86" t="inlineStr">
         <is>
           <t>PS5-08-13 - Safety Data Network (SII SP3 SAF)</t>
         </is>
@@ -5209,7 +5226,7 @@
           <t>PS5-08-14</t>
         </is>
       </c>
-      <c r="B60" s="83" t="inlineStr">
+      <c r="B60" s="86" t="inlineStr">
         <is>
           <t>PS5-08-14 - Industrial Data Network (SII SP1)</t>
         </is>
@@ -5220,7 +5237,7 @@
       <c r="D60" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="95" t="inlineStr">
+      <c r="E60" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5278,7 +5295,7 @@
           <t>PS5-08-15</t>
         </is>
       </c>
-      <c r="B61" s="83" t="inlineStr">
+      <c r="B61" s="86" t="inlineStr">
         <is>
           <t>PS5-08-15 - Security Data Network (SII SP3 SEC)</t>
         </is>
@@ -5347,7 +5364,7 @@
           <t>PS5-08-23</t>
         </is>
       </c>
-      <c r="B62" s="83" t="inlineStr">
+      <c r="B62" s="86" t="inlineStr">
         <is>
           <t>PS5-08-23 - VHF Trunk Radio System</t>
         </is>
@@ -5416,7 +5433,7 @@
           <t>PS5-08-34</t>
         </is>
       </c>
-      <c r="B63" s="83" t="inlineStr">
+      <c r="B63" s="86" t="inlineStr">
         <is>
           <t>PS5-08-34 - Satphone</t>
         </is>
@@ -5427,7 +5444,7 @@
       <c r="D63" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E63" s="95" t="inlineStr">
+      <c r="E63" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5485,7 +5502,7 @@
           <t>PS5-08-35</t>
         </is>
       </c>
-      <c r="B64" s="83" t="inlineStr">
+      <c r="B64" s="86" t="inlineStr">
         <is>
           <t>PS5-08-35 - Optical Transport Network</t>
         </is>
@@ -5507,7 +5524,7 @@
       <c r="G64" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H64" s="95" t="inlineStr">
+      <c r="H64" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5554,7 +5571,7 @@
           <t>PS5-08-36</t>
         </is>
       </c>
-      <c r="B65" s="83" t="inlineStr">
+      <c r="B65" s="86" t="inlineStr">
         <is>
           <t>PS5-08-36 - Pipeline FO Cable &amp; EPRS</t>
         </is>
@@ -5565,7 +5582,7 @@
       <c r="D65" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="95" t="inlineStr">
+      <c r="E65" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5623,7 +5640,7 @@
           <t>PS5-08-51</t>
         </is>
       </c>
-      <c r="B66" s="83" t="inlineStr">
+      <c r="B66" s="86" t="inlineStr">
         <is>
           <t>PS5-08-51 - Entertainment</t>
         </is>
@@ -5634,7 +5651,7 @@
       <c r="D66" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="95" t="inlineStr">
+      <c r="E66" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5692,7 +5709,7 @@
           <t>PS5-08-52a</t>
         </is>
       </c>
-      <c r="B67" s="83" t="inlineStr">
+      <c r="B67" s="86" t="inlineStr">
         <is>
           <t>PS5-08-52a - Process &amp; Security CCTV (Required for SU)</t>
         </is>
@@ -5703,7 +5720,7 @@
       <c r="D67" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="95" t="inlineStr">
+      <c r="E67" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5746,7 +5763,7 @@
       </c>
       <c r="N67" s="70" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="O67" s="28" t="inlineStr">
@@ -5761,7 +5778,7 @@
           <t>PS5-08-52b</t>
         </is>
       </c>
-      <c r="B68" s="83" t="inlineStr">
+      <c r="B68" s="86" t="inlineStr">
         <is>
           <t>PS5-08-52b - Process &amp; Security CCTV (Not required for SU)</t>
         </is>
@@ -5772,7 +5789,7 @@
       <c r="D68" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E68" s="95" t="inlineStr">
+      <c r="E68" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5815,7 +5832,7 @@
       </c>
       <c r="N68" s="70" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="O68" s="28" t="inlineStr">
@@ -5830,7 +5847,7 @@
           <t>PS5-08-55</t>
         </is>
       </c>
-      <c r="B69" s="83" t="inlineStr">
+      <c r="B69" s="86" t="inlineStr">
         <is>
           <t>PS5-08-55 - Videoconference</t>
         </is>
@@ -5841,7 +5858,7 @@
       <c r="D69" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E69" s="95" t="inlineStr">
+      <c r="E69" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5852,7 +5869,7 @@
       <c r="G69" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="95" t="inlineStr">
+      <c r="H69" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5899,7 +5916,7 @@
           <t>PS5-08-61</t>
         </is>
       </c>
-      <c r="B70" s="83" t="inlineStr">
+      <c r="B70" s="86" t="inlineStr">
         <is>
           <t>PS5-08-61 - Meteocean</t>
         </is>
@@ -5910,7 +5927,7 @@
       <c r="D70" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E70" s="95" t="inlineStr">
+      <c r="E70" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5968,7 +5985,7 @@
           <t>PS5-08-71</t>
         </is>
       </c>
-      <c r="B71" s="83" t="inlineStr">
+      <c r="B71" s="86" t="inlineStr">
         <is>
           <t>PS5-08-71 - Structured Cabling (CAT6)</t>
         </is>
@@ -5979,7 +5996,7 @@
       <c r="D71" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E71" s="95" t="inlineStr">
+      <c r="E71" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6037,7 +6054,7 @@
           <t>PS5-08-72</t>
         </is>
       </c>
-      <c r="B72" s="83" t="inlineStr">
+      <c r="B72" s="86" t="inlineStr">
         <is>
           <t>PS5-08-72 - Structured Cabling (FO)</t>
         </is>
@@ -6048,7 +6065,7 @@
       <c r="D72" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="95" t="inlineStr">
+      <c r="E72" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6106,7 +6123,7 @@
           <t>PS5-08-81</t>
         </is>
       </c>
-      <c r="B73" s="83" t="inlineStr">
+      <c r="B73" s="86" t="inlineStr">
         <is>
           <t>PS5-08-81 - Guard tour</t>
         </is>
@@ -6117,7 +6134,7 @@
       <c r="D73" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E73" s="95" t="inlineStr">
+      <c r="E73" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6128,7 +6145,7 @@
       <c r="G73" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="95" t="inlineStr">
+      <c r="H73" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6175,7 +6192,7 @@
           <t>PS5-08-82</t>
         </is>
       </c>
-      <c r="B74" s="83" t="inlineStr">
+      <c r="B74" s="86" t="inlineStr">
         <is>
           <t>PS5-08-82 - Key Management</t>
         </is>
@@ -6186,7 +6203,7 @@
       <c r="D74" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="95" t="inlineStr">
+      <c r="E74" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6197,7 +6214,7 @@
       <c r="G74" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="95" t="inlineStr">
+      <c r="H74" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6244,7 +6261,7 @@
           <t>PS5-08-83</t>
         </is>
       </c>
-      <c r="B75" s="83" t="inlineStr">
+      <c r="B75" s="86" t="inlineStr">
         <is>
           <t>PS5-08-83 - Perimeter &amp; Pipeline intrusion detection system</t>
         </is>
@@ -6255,7 +6272,7 @@
       <c r="D75" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E75" s="95" t="inlineStr">
+      <c r="E75" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6313,7 +6330,7 @@
           <t>PS5-08-85</t>
         </is>
       </c>
-      <c r="B76" s="83" t="inlineStr">
+      <c r="B76" s="86" t="inlineStr">
         <is>
           <t>PS5-08-85</t>
         </is>
@@ -6335,7 +6352,7 @@
       <c r="G76" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H76" s="95" t="inlineStr">
+      <c r="H76" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6365,9 +6382,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N76" s="70" t="inlineStr">
-        <is>
-          <t>16%</t>
+      <c r="N76" s="69" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="O76" s="28" t="inlineStr">
@@ -6382,7 +6399,7 @@
           <t>PS5-08-85a</t>
         </is>
       </c>
-      <c r="B77" s="83" t="inlineStr">
+      <c r="B77" s="86" t="inlineStr">
         <is>
           <t>PS5-08-85a - Access Control, POB &amp; e-Mustering (Required for SU)</t>
         </is>
@@ -6393,7 +6410,7 @@
       <c r="D77" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="95" t="inlineStr">
+      <c r="E77" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6436,7 +6453,7 @@
       </c>
       <c r="N77" s="70" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="O77" s="28" t="inlineStr">
@@ -6451,7 +6468,7 @@
           <t>PS5-08-85b</t>
         </is>
       </c>
-      <c r="B78" s="83" t="inlineStr">
+      <c r="B78" s="86" t="inlineStr">
         <is>
           <t>PS5-08-85b - Access Control, POB &amp; e-Mustering (Not required for SU)</t>
         </is>
@@ -6462,7 +6479,7 @@
       <c r="D78" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E78" s="95" t="inlineStr">
+      <c r="E78" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6505,7 +6522,7 @@
       </c>
       <c r="N78" s="70" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="O78" s="28" t="inlineStr">
@@ -6520,7 +6537,7 @@
           <t>PS5-08-86</t>
         </is>
       </c>
-      <c r="B79" s="83" t="inlineStr">
+      <c r="B79" s="86" t="inlineStr">
         <is>
           <t>PS5-08-86 - Integrated Security Management System</t>
         </is>
@@ -6531,7 +6548,7 @@
       <c r="D79" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E79" s="95" t="inlineStr">
+      <c r="E79" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6542,7 +6559,7 @@
       <c r="G79" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H79" s="95" t="inlineStr">
+      <c r="H79" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6589,7 +6606,7 @@
           <t>PS5-08-92</t>
         </is>
       </c>
-      <c r="B80" s="83" t="inlineStr">
+      <c r="B80" s="86" t="inlineStr">
         <is>
           <t>PS5-08-92 - Telecom Mast</t>
         </is>
@@ -6600,7 +6617,7 @@
       <c r="D80" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E80" s="95" t="inlineStr">
+      <c r="E80" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6611,7 +6628,7 @@
       <c r="G80" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="95" t="inlineStr">
+      <c r="H80" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6658,7 +6675,7 @@
           <t>PS5-08-93</t>
         </is>
       </c>
-      <c r="B81" s="83" t="inlineStr">
+      <c r="B81" s="86" t="inlineStr">
         <is>
           <t>PS5-08-93 - Telecom Monitoring System</t>
         </is>
@@ -6669,7 +6686,7 @@
       <c r="D81" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E81" s="95" t="inlineStr">
+      <c r="E81" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6727,7 +6744,7 @@
           <t>PS5-09-01</t>
         </is>
       </c>
-      <c r="B82" s="83" t="inlineStr">
+      <c r="B82" s="86" t="inlineStr">
         <is>
           <t>PS5-09-01 - HVAC for Office and Facilities building</t>
         </is>
@@ -6738,7 +6755,7 @@
       <c r="D82" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E82" s="95" t="inlineStr">
+      <c r="E82" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6796,7 +6813,7 @@
           <t>PS5-09-02</t>
         </is>
       </c>
-      <c r="B83" s="83" t="inlineStr">
+      <c r="B83" s="86" t="inlineStr">
         <is>
           <t>PS5-09-02 - HVAC for Guard House</t>
         </is>
@@ -6807,7 +6824,7 @@
       <c r="D83" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E83" s="95" t="inlineStr">
+      <c r="E83" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6865,7 +6882,7 @@
           <t>PS5-09-03</t>
         </is>
       </c>
-      <c r="B84" s="83" t="inlineStr">
+      <c r="B84" s="86" t="inlineStr">
         <is>
           <t>PS5-09-03 - HVAC for Generator Building</t>
         </is>
@@ -6919,7 +6936,7 @@
       </c>
       <c r="N84" s="70" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="O84" s="28" t="inlineStr">
@@ -6934,7 +6951,7 @@
           <t>PS5-09-04</t>
         </is>
       </c>
-      <c r="B85" s="83" t="inlineStr">
+      <c r="B85" s="86" t="inlineStr">
         <is>
           <t>PS5-09-04 - HVAC for Workshop &amp; Warehouse</t>
         </is>
@@ -6945,7 +6962,7 @@
       <c r="D85" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E85" s="95" t="inlineStr">
+      <c r="E85" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7003,7 +7020,7 @@
           <t>PS5-09-05</t>
         </is>
       </c>
-      <c r="B86" s="83" t="inlineStr">
+      <c r="B86" s="86" t="inlineStr">
         <is>
           <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
@@ -7072,7 +7089,7 @@
           <t>PS5-0H-01</t>
         </is>
       </c>
-      <c r="B87" s="83" t="inlineStr">
+      <c r="B87" s="86" t="inlineStr">
         <is>
           <t>PS5-0H-01 - HIPPS</t>
         </is>
@@ -7094,7 +7111,7 @@
       <c r="G87" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="95" t="inlineStr">
+      <c r="H87" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7141,7 +7158,7 @@
           <t>PS5-25-01</t>
         </is>
       </c>
-      <c r="B88" s="83" t="inlineStr">
+      <c r="B88" s="86" t="inlineStr">
         <is>
           <t>PS5-25-01 - Export Pipeline Pig Receiver</t>
         </is>
@@ -7210,7 +7227,7 @@
           <t>PS5-25-02</t>
         </is>
       </c>
-      <c r="B89" s="83" t="inlineStr">
+      <c r="B89" s="86" t="inlineStr">
         <is>
           <t>PS5-25-02 - Crude Oil Export Pump A</t>
         </is>
@@ -7279,7 +7296,7 @@
           <t>PS5-25-03</t>
         </is>
       </c>
-      <c r="B90" s="83" t="inlineStr">
+      <c r="B90" s="86" t="inlineStr">
         <is>
           <t>PS5-25-03 - Crude Oil Export Pump B</t>
         </is>
@@ -7333,7 +7350,7 @@
       </c>
       <c r="N90" s="54" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="O90" s="28" t="inlineStr">
@@ -7348,7 +7365,7 @@
           <t>PS5-25-04</t>
         </is>
       </c>
-      <c r="B91" s="83" t="inlineStr">
+      <c r="B91" s="86" t="inlineStr">
         <is>
           <t>PS5-25-04 - Crude Oil Export Pump C</t>
         </is>
@@ -7402,7 +7419,7 @@
       </c>
       <c r="N91" s="54" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="O91" s="28" t="inlineStr">
@@ -7417,7 +7434,7 @@
           <t>PS5-25-05</t>
         </is>
       </c>
-      <c r="B92" s="83" t="inlineStr">
+      <c r="B92" s="86" t="inlineStr">
         <is>
           <t>PS5-25-05 - Crude Oil Export Pumps Bypass</t>
         </is>
@@ -7486,7 +7503,7 @@
           <t>PS5-25-06</t>
         </is>
       </c>
-      <c r="B93" s="83" t="inlineStr">
+      <c r="B93" s="86" t="inlineStr">
         <is>
           <t>PS5-25-06 - Crude Oil Export Pumps Discharge</t>
         </is>
@@ -7555,7 +7572,7 @@
           <t>PS5-25-07</t>
         </is>
       </c>
-      <c r="B94" s="83" t="inlineStr">
+      <c r="B94" s="86" t="inlineStr">
         <is>
           <t>PS5-25-07 - Export Pipeline Pig Launcher</t>
         </is>
@@ -7624,7 +7641,7 @@
           <t>PS5-28-01</t>
         </is>
       </c>
-      <c r="B95" s="83" t="inlineStr">
+      <c r="B95" s="86" t="inlineStr">
         <is>
           <t>PS5-28-01 - Closed Drain Header 1</t>
         </is>
@@ -7635,7 +7652,7 @@
       <c r="D95" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="95" t="inlineStr">
+      <c r="E95" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7693,7 +7710,7 @@
           <t>PS5-28-02</t>
         </is>
       </c>
-      <c r="B96" s="83" t="inlineStr">
+      <c r="B96" s="86" t="inlineStr">
         <is>
           <t>PS5-28-02 - Closed Drain Header 2</t>
         </is>
@@ -7762,7 +7779,7 @@
           <t>PS5-28-03</t>
         </is>
       </c>
-      <c r="B97" s="83" t="inlineStr">
+      <c r="B97" s="86" t="inlineStr">
         <is>
           <t>PS5-28-03 - Closed Drain Drum and Pump 01</t>
         </is>
@@ -7831,7 +7848,7 @@
           <t>PS5-28-04</t>
         </is>
       </c>
-      <c r="B98" s="83" t="inlineStr">
+      <c r="B98" s="86" t="inlineStr">
         <is>
           <t>PS5-28-04 - Closed Drain Drum and Pump 02</t>
         </is>
@@ -7900,7 +7917,7 @@
           <t>PS5-28-05</t>
         </is>
       </c>
-      <c r="B99" s="83" t="inlineStr">
+      <c r="B99" s="86" t="inlineStr">
         <is>
           <t>PS5-28-05 - HP Relief Header</t>
         </is>
@@ -7969,7 +7986,7 @@
           <t>PS5-28-06</t>
         </is>
       </c>
-      <c r="B100" s="83" t="inlineStr">
+      <c r="B100" s="86" t="inlineStr">
         <is>
           <t>PS5-28-06 - Relief Drum and Pump</t>
         </is>
@@ -8038,7 +8055,7 @@
           <t>PS5-28-07</t>
         </is>
       </c>
-      <c r="B101" s="83" t="inlineStr">
+      <c r="B101" s="86" t="inlineStr">
         <is>
           <t>PS5-28-07 - Open Drains (OD2)</t>
         </is>
@@ -8107,7 +8124,7 @@
           <t>PS5-28-08</t>
         </is>
       </c>
-      <c r="B102" s="83" t="inlineStr">
+      <c r="B102" s="86" t="inlineStr">
         <is>
           <t>PS5-28-08 - Open Drain Sump and Pumps</t>
         </is>
@@ -8176,7 +8193,7 @@
           <t>PS5-28-09</t>
         </is>
       </c>
-      <c r="B103" s="83" t="inlineStr">
+      <c r="B103" s="86" t="inlineStr">
         <is>
           <t>PS5-28-09 - Observation Basin</t>
         </is>
@@ -8245,7 +8262,7 @@
           <t>PS5-28-10</t>
         </is>
       </c>
-      <c r="B104" s="83" t="inlineStr">
+      <c r="B104" s="86" t="inlineStr">
         <is>
           <t>PS5-28-10 - Oil Skimmer Package</t>
         </is>
@@ -8299,7 +8316,7 @@
       </c>
       <c r="N104" s="70" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="O104" s="28" t="inlineStr">
@@ -8314,7 +8331,7 @@
           <t>PS5-28-11</t>
         </is>
       </c>
-      <c r="B105" s="83" t="inlineStr">
+      <c r="B105" s="86" t="inlineStr">
         <is>
           <t>PS5-28-11 - Open Drain Interceptor</t>
         </is>
@@ -8383,7 +8400,7 @@
           <t>PS5-28-12</t>
         </is>
       </c>
-      <c r="B106" s="83" t="inlineStr">
+      <c r="B106" s="86" t="inlineStr">
         <is>
           <t>PS5-28-12 - Open Drains (OD3)</t>
         </is>
@@ -8452,7 +8469,7 @@
           <t>PS5-28-13</t>
         </is>
       </c>
-      <c r="B107" s="83" t="inlineStr">
+      <c r="B107" s="86" t="inlineStr">
         <is>
           <t>PS5-28-13 - Seal Oil Drain Drum &amp; Pump A</t>
         </is>
@@ -8506,7 +8523,7 @@
       </c>
       <c r="N107" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O107" s="28" t="inlineStr">
@@ -8521,7 +8538,7 @@
           <t>PS5-28-14</t>
         </is>
       </c>
-      <c r="B108" s="83" t="inlineStr">
+      <c r="B108" s="86" t="inlineStr">
         <is>
           <t>PS5-28-14 - Seal Oil Drain Drum &amp; Pump B</t>
         </is>
@@ -8575,7 +8592,7 @@
       </c>
       <c r="N108" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O108" s="28" t="inlineStr">
@@ -8590,7 +8607,7 @@
           <t>PS5-28-15</t>
         </is>
       </c>
-      <c r="B109" s="83" t="inlineStr">
+      <c r="B109" s="86" t="inlineStr">
         <is>
           <t>PS5-28-15 - Seal Oil Drain Drum &amp; Pump C</t>
         </is>
@@ -8644,7 +8661,7 @@
       </c>
       <c r="N109" s="54" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O109" s="28" t="inlineStr">
@@ -8659,7 +8676,7 @@
           <t>PS5-28-16</t>
         </is>
       </c>
-      <c r="B110" s="83" t="inlineStr">
+      <c r="B110" s="86" t="inlineStr">
         <is>
           <t>PS5-28-16 - LP Relief Header</t>
         </is>
@@ -8670,7 +8687,7 @@
       <c r="D110" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="95" t="inlineStr">
+      <c r="E110" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8728,7 +8745,7 @@
           <t>PS5-28-17</t>
         </is>
       </c>
-      <c r="B111" s="83" t="inlineStr">
+      <c r="B111" s="86" t="inlineStr">
         <is>
           <t>PS5-28-17 - Reinjection Pump</t>
         </is>
@@ -8782,7 +8799,7 @@
       </c>
       <c r="N111" s="54" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="O111" s="28" t="inlineStr">
@@ -8797,7 +8814,7 @@
           <t>PS5-50-01</t>
         </is>
       </c>
-      <c r="B112" s="83" t="inlineStr">
+      <c r="B112" s="86" t="inlineStr">
         <is>
           <t>PS5-50-01 - Water Well Submersible Pumps (3100)</t>
         </is>
@@ -8808,7 +8825,7 @@
       <c r="D112" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E112" s="95" t="inlineStr">
+      <c r="E112" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8866,7 +8883,7 @@
           <t>PS5-50-02</t>
         </is>
       </c>
-      <c r="B113" s="83" t="inlineStr">
+      <c r="B113" s="86" t="inlineStr">
         <is>
           <t>PS5-50-02 - Water Well Submersible Pumps (3200)</t>
         </is>
@@ -8877,7 +8894,7 @@
       <c r="D113" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="95" t="inlineStr">
+      <c r="E113" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8935,7 +8952,7 @@
           <t>PS5-50-03</t>
         </is>
       </c>
-      <c r="B114" s="83" t="inlineStr">
+      <c r="B114" s="86" t="inlineStr">
         <is>
           <t>PS5-50-03 - Water Pre-Treatment Package</t>
         </is>
@@ -8989,7 +9006,7 @@
       </c>
       <c r="N114" s="69" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="O114" s="28" t="inlineStr">
@@ -9004,7 +9021,7 @@
           <t>PS5-53-01</t>
         </is>
       </c>
-      <c r="B115" s="83" t="inlineStr">
+      <c r="B115" s="86" t="inlineStr">
         <is>
           <t>PS5-53-01 - Utility Water / Storage Tank</t>
         </is>
@@ -9073,7 +9090,7 @@
           <t>PS5-53-02</t>
         </is>
       </c>
-      <c r="B116" s="83" t="inlineStr">
+      <c r="B116" s="86" t="inlineStr">
         <is>
           <t>PS5-53-02 - Water Distribution Pump A/B</t>
         </is>
@@ -9132,7 +9149,7 @@
       </c>
       <c r="O116" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9159,7 @@
           <t>PS5-53-03</t>
         </is>
       </c>
-      <c r="B117" s="83" t="inlineStr">
+      <c r="B117" s="86" t="inlineStr">
         <is>
           <t>PS5-53-03 - Water Softener Package</t>
         </is>
@@ -9153,7 +9170,7 @@
       <c r="D117" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E117" s="95" t="inlineStr">
+      <c r="E117" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9211,7 +9228,7 @@
           <t>PS5-53-04</t>
         </is>
       </c>
-      <c r="B118" s="83" t="inlineStr">
+      <c r="B118" s="86" t="inlineStr">
         <is>
           <t>PS5-53-04 - Water Treatment Purification Package</t>
         </is>
@@ -9222,7 +9239,7 @@
       <c r="D118" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E118" s="95" t="inlineStr">
+      <c r="E118" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9265,7 +9282,7 @@
       </c>
       <c r="N118" s="70" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="O118" s="28" t="inlineStr">
@@ -9280,7 +9297,7 @@
           <t>PS5-53-05</t>
         </is>
       </c>
-      <c r="B119" s="83" t="inlineStr">
+      <c r="B119" s="86" t="inlineStr">
         <is>
           <t>PS5-53-05 - Water Distribution Header</t>
         </is>
@@ -9291,7 +9308,7 @@
       <c r="D119" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E119" s="95" t="inlineStr">
+      <c r="E119" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9349,7 +9366,7 @@
           <t>PS5-53-06</t>
         </is>
       </c>
-      <c r="B120" s="83" t="inlineStr">
+      <c r="B120" s="86" t="inlineStr">
         <is>
           <t>PS5-53-06 - Water Distribution Consumers</t>
         </is>
@@ -9360,7 +9377,7 @@
       <c r="D120" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E120" s="95" t="inlineStr">
+      <c r="E120" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9418,7 +9435,7 @@
           <t>PS5-60-01</t>
         </is>
       </c>
-      <c r="B121" s="83" t="inlineStr">
+      <c r="B121" s="86" t="inlineStr">
         <is>
           <t>PS5-60-01 - Power Generation Package A</t>
         </is>
@@ -9487,7 +9504,7 @@
           <t>PS5-60-02</t>
         </is>
       </c>
-      <c r="B122" s="83" t="inlineStr">
+      <c r="B122" s="86" t="inlineStr">
         <is>
           <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
@@ -9556,7 +9573,7 @@
           <t>PS5-60-03</t>
         </is>
       </c>
-      <c r="B123" s="83" t="inlineStr">
+      <c r="B123" s="86" t="inlineStr">
         <is>
           <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9625,7 +9642,7 @@
           <t>PS5-60-04</t>
         </is>
       </c>
-      <c r="B124" s="83" t="inlineStr">
+      <c r="B124" s="86" t="inlineStr">
         <is>
           <t>PS5-60-04 - Power Generation Package B</t>
         </is>
@@ -9694,7 +9711,7 @@
           <t>PS5-60-05</t>
         </is>
       </c>
-      <c r="B125" s="83" t="inlineStr">
+      <c r="B125" s="86" t="inlineStr">
         <is>
           <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
@@ -9763,7 +9780,7 @@
           <t>PS5-60-06</t>
         </is>
       </c>
-      <c r="B126" s="83" t="inlineStr">
+      <c r="B126" s="86" t="inlineStr">
         <is>
           <t>PS5-60-06 - Power Gen Package B Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9832,7 +9849,7 @@
           <t>PS5-60-07</t>
         </is>
       </c>
-      <c r="B127" s="83" t="inlineStr">
+      <c r="B127" s="86" t="inlineStr">
         <is>
           <t>PS5-60-07 - Power Generation Package C</t>
         </is>
@@ -9901,7 +9918,7 @@
           <t>PS5-60-08</t>
         </is>
       </c>
-      <c r="B128" s="83" t="inlineStr">
+      <c r="B128" s="86" t="inlineStr">
         <is>
           <t>PS5-60-08 - Power Gen Package C (UCP)</t>
         </is>
@@ -9970,7 +9987,7 @@
           <t>PS5-60-09</t>
         </is>
       </c>
-      <c r="B129" s="83" t="inlineStr">
+      <c r="B129" s="86" t="inlineStr">
         <is>
           <t>PS5-60-09 - Power Gen Package C Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -9981,7 +9998,7 @@
       <c r="D129" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E129" s="95" t="inlineStr">
+      <c r="E129" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10039,7 +10056,7 @@
           <t>PS5-60-10</t>
         </is>
       </c>
-      <c r="B130" s="83" t="inlineStr">
+      <c r="B130" s="86" t="inlineStr">
         <is>
           <t>PS5-60-10 - Power Generation Package D</t>
         </is>
@@ -10108,7 +10125,7 @@
           <t>PS5-60-11</t>
         </is>
       </c>
-      <c r="B131" s="83" t="inlineStr">
+      <c r="B131" s="86" t="inlineStr">
         <is>
           <t>PS5-60-11 - Power Gen Package D (UCP)</t>
         </is>
@@ -10119,7 +10136,7 @@
       <c r="D131" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E131" s="95" t="inlineStr">
+      <c r="E131" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10177,7 +10194,7 @@
           <t>PS5-60-12</t>
         </is>
       </c>
-      <c r="B132" s="83" t="inlineStr">
+      <c r="B132" s="86" t="inlineStr">
         <is>
           <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10188,7 +10205,7 @@
       <c r="D132" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E132" s="95" t="inlineStr">
+      <c r="E132" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10246,7 +10263,7 @@
           <t>PS5-60-13</t>
         </is>
       </c>
-      <c r="B133" s="83" t="inlineStr">
+      <c r="B133" s="86" t="inlineStr">
         <is>
           <t>PS5-60-13 - Power Generation Package E</t>
         </is>
@@ -10315,7 +10332,7 @@
           <t>PS5-60-14</t>
         </is>
       </c>
-      <c r="B134" s="83" t="inlineStr">
+      <c r="B134" s="86" t="inlineStr">
         <is>
           <t>PS5-60-14 - Power Gen Package E (UCP)</t>
         </is>
@@ -10326,7 +10343,7 @@
       <c r="D134" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E134" s="95" t="inlineStr">
+      <c r="E134" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10384,7 +10401,7 @@
           <t>PS5-60-15</t>
         </is>
       </c>
-      <c r="B135" s="83" t="inlineStr">
+      <c r="B135" s="86" t="inlineStr">
         <is>
           <t>PS5-60-15 - Power Gen Package E Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10395,7 +10412,7 @@
       <c r="D135" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E135" s="95" t="inlineStr">
+      <c r="E135" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10453,7 +10470,7 @@
           <t>PS5-60-16</t>
         </is>
       </c>
-      <c r="B136" s="83" t="inlineStr">
+      <c r="B136" s="86" t="inlineStr">
         <is>
           <t>PS5-60-16 - Power Generation Package F</t>
         </is>
@@ -10522,7 +10539,7 @@
           <t>PS5-60-17</t>
         </is>
       </c>
-      <c r="B137" s="83" t="inlineStr">
+      <c r="B137" s="86" t="inlineStr">
         <is>
           <t>PS5-60-17 - Power Gen Package F (UCP)</t>
         </is>
@@ -10533,7 +10550,7 @@
       <c r="D137" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E137" s="95" t="inlineStr">
+      <c r="E137" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10591,7 +10608,7 @@
           <t>PS5-60-18</t>
         </is>
       </c>
-      <c r="B138" s="83" t="inlineStr">
+      <c r="B138" s="86" t="inlineStr">
         <is>
           <t>PS5-60-18 - Power Gen Package F Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10602,7 +10619,7 @@
       <c r="D138" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E138" s="95" t="inlineStr">
+      <c r="E138" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10660,7 +10677,7 @@
           <t>PS5-60-19</t>
         </is>
       </c>
-      <c r="B139" s="83" t="inlineStr">
+      <c r="B139" s="86" t="inlineStr">
         <is>
           <t>PS5-60-19 - Power Generation Package G</t>
         </is>
@@ -10729,7 +10746,7 @@
           <t>PS5-60-20</t>
         </is>
       </c>
-      <c r="B140" s="83" t="inlineStr">
+      <c r="B140" s="86" t="inlineStr">
         <is>
           <t>PS5-60-20 - Power Gen Package G (UCP)</t>
         </is>
@@ -10740,7 +10757,7 @@
       <c r="D140" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E140" s="95" t="inlineStr">
+      <c r="E140" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10798,7 +10815,7 @@
           <t>PS5-60-21</t>
         </is>
       </c>
-      <c r="B141" s="83" t="inlineStr">
+      <c r="B141" s="86" t="inlineStr">
         <is>
           <t>PS5-60-21 - Power Gen Package G Generator Auxiliary MCCs &amp; DBs</t>
         </is>
@@ -10809,7 +10826,7 @@
       <c r="D141" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E141" s="95" t="inlineStr">
+      <c r="E141" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -10867,7 +10884,7 @@
           <t>PS5-60-22</t>
         </is>
       </c>
-      <c r="B142" s="83" t="inlineStr">
+      <c r="B142" s="86" t="inlineStr">
         <is>
           <t>PS5-60-22 - Power Gen Master UCP</t>
         </is>
@@ -10936,7 +10953,7 @@
           <t>PS5-60-23</t>
         </is>
       </c>
-      <c r="B143" s="83" t="inlineStr">
+      <c r="B143" s="86" t="inlineStr">
         <is>
           <t>PS5-60-23 - Instrument Air Distribution lines</t>
         </is>
@@ -11005,7 +11022,7 @@
           <t>PS5-60-24</t>
         </is>
       </c>
-      <c r="B144" s="83" t="inlineStr">
+      <c r="B144" s="86" t="inlineStr">
         <is>
           <t>PS5-60-24 - Cooling Water Tank &amp; Pump</t>
         </is>
@@ -11074,7 +11091,7 @@
           <t>PS5-60-25</t>
         </is>
       </c>
-      <c r="B145" s="83" t="inlineStr">
+      <c r="B145" s="86" t="inlineStr">
         <is>
           <t>PS5-60-25 - Cooling Water Maintenance Tank &amp; Return Pump</t>
         </is>
@@ -11143,7 +11160,7 @@
           <t>PS5-60-26</t>
         </is>
       </c>
-      <c r="B146" s="83" t="inlineStr">
+      <c r="B146" s="86" t="inlineStr">
         <is>
           <t>PS5-60-26 - Instrument Air Compressor Skid</t>
         </is>
@@ -11212,7 +11229,7 @@
           <t>PS5-60-27</t>
         </is>
       </c>
-      <c r="B147" s="83" t="inlineStr">
+      <c r="B147" s="86" t="inlineStr">
         <is>
           <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
@@ -11281,7 +11298,7 @@
           <t>PS5-60-28</t>
         </is>
       </c>
-      <c r="B148" s="83" t="inlineStr">
+      <c r="B148" s="86" t="inlineStr">
         <is>
           <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
@@ -11350,7 +11367,7 @@
           <t>PS5-60-29</t>
         </is>
       </c>
-      <c r="B149" s="83" t="inlineStr">
+      <c r="B149" s="86" t="inlineStr">
         <is>
           <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
         </is>
@@ -11419,7 +11436,7 @@
           <t>PS5-60-30</t>
         </is>
       </c>
-      <c r="B150" s="83" t="inlineStr">
+      <c r="B150" s="86" t="inlineStr">
         <is>
           <t>PS5-60-30 - Air Receiver C &amp; Air Regulator C</t>
         </is>
@@ -11488,7 +11505,7 @@
           <t>PS5-60-31</t>
         </is>
       </c>
-      <c r="B151" s="83" t="inlineStr">
+      <c r="B151" s="86" t="inlineStr">
         <is>
           <t>PS5-60-31 - Air Receiver D &amp; Air Regulator D</t>
         </is>
@@ -11557,7 +11574,7 @@
           <t>PS5-60-32</t>
         </is>
       </c>
-      <c r="B152" s="83" t="inlineStr">
+      <c r="B152" s="86" t="inlineStr">
         <is>
           <t>PS5-60-32 - Air Receiver E &amp; Air Regulator E</t>
         </is>
@@ -11626,7 +11643,7 @@
           <t>PS5-60-33</t>
         </is>
       </c>
-      <c r="B153" s="83" t="inlineStr">
+      <c r="B153" s="86" t="inlineStr">
         <is>
           <t>PS5-60-33 - Air Receiver F &amp; Air Regulator F</t>
         </is>
@@ -11695,7 +11712,7 @@
           <t>PS5-60-34</t>
         </is>
       </c>
-      <c r="B154" s="83" t="inlineStr">
+      <c r="B154" s="86" t="inlineStr">
         <is>
           <t>PS5-60-34 - Air Receiver G &amp; Air Regulator G</t>
         </is>
@@ -11764,7 +11781,7 @@
           <t>PS5-60-35</t>
         </is>
       </c>
-      <c r="B155" s="83" t="inlineStr">
+      <c r="B155" s="86" t="inlineStr">
         <is>
           <t>PS5-60-35 - Injector Tip Cooling Module A</t>
         </is>
@@ -11833,7 +11850,7 @@
           <t>PS5-60-36</t>
         </is>
       </c>
-      <c r="B156" s="83" t="inlineStr">
+      <c r="B156" s="86" t="inlineStr">
         <is>
           <t>PS5-60-36 - Injector Tip Cooling Module B</t>
         </is>
@@ -11902,7 +11919,7 @@
           <t>PS5-60-37</t>
         </is>
       </c>
-      <c r="B157" s="83" t="inlineStr">
+      <c r="B157" s="86" t="inlineStr">
         <is>
           <t>PS5-60-37 - Injector Tip Cooling Module C</t>
         </is>
@@ -11971,7 +11988,7 @@
           <t>PS5-60-38</t>
         </is>
       </c>
-      <c r="B158" s="83" t="inlineStr">
+      <c r="B158" s="86" t="inlineStr">
         <is>
           <t>PS5-60-38 - Injector Tip Cooling Module D</t>
         </is>
@@ -12040,7 +12057,7 @@
           <t>PS5-60-39</t>
         </is>
       </c>
-      <c r="B159" s="83" t="inlineStr">
+      <c r="B159" s="86" t="inlineStr">
         <is>
           <t>PS5-60-39 - Injector Tip Cooling Module E</t>
         </is>
@@ -12109,7 +12126,7 @@
           <t>PS5-60-40</t>
         </is>
       </c>
-      <c r="B160" s="83" t="inlineStr">
+      <c r="B160" s="86" t="inlineStr">
         <is>
           <t>PS5-60-40 - Injector Tip Cooling Module F</t>
         </is>
@@ -12178,7 +12195,7 @@
           <t>PS5-60-41</t>
         </is>
       </c>
-      <c r="B161" s="83" t="inlineStr">
+      <c r="B161" s="86" t="inlineStr">
         <is>
           <t>PS5-60-41 - Injector Tip Cooling Module G</t>
         </is>
@@ -12247,7 +12264,7 @@
           <t>PS5-60-42</t>
         </is>
       </c>
-      <c r="B162" s="83" t="inlineStr">
+      <c r="B162" s="86" t="inlineStr">
         <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
@@ -12316,7 +12333,7 @@
           <t>PS5-60-43</t>
         </is>
       </c>
-      <c r="B163" s="83" t="inlineStr">
+      <c r="B163" s="86" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
@@ -12385,7 +12402,7 @@
           <t>PS5-60-44</t>
         </is>
       </c>
-      <c r="B164" s="83" t="inlineStr">
+      <c r="B164" s="86" t="inlineStr">
         <is>
           <t>PS5-60-44 - Oil Mist Separator Skid PS5-60-VS-9100C</t>
         </is>
@@ -12454,7 +12471,7 @@
           <t>PS5-60-45</t>
         </is>
       </c>
-      <c r="B165" s="83" t="inlineStr">
+      <c r="B165" s="86" t="inlineStr">
         <is>
           <t>PS5-60-45 - Oil Mist Separator Skid PS5-60-VS-9100D</t>
         </is>
@@ -12523,7 +12540,7 @@
           <t>PS5-60-46</t>
         </is>
       </c>
-      <c r="B166" s="83" t="inlineStr">
+      <c r="B166" s="86" t="inlineStr">
         <is>
           <t>PS5-60-46 - Oil Mist Separator Skid PS5-60-VS-9100E</t>
         </is>
@@ -12592,7 +12609,7 @@
           <t>PS5-60-47</t>
         </is>
       </c>
-      <c r="B167" s="83" t="inlineStr">
+      <c r="B167" s="86" t="inlineStr">
         <is>
           <t>PS5-60-47 - Oil Mist Separator Skid PS5-60-VS-9100F</t>
         </is>
@@ -12661,7 +12678,7 @@
           <t>PS5-60-48</t>
         </is>
       </c>
-      <c r="B168" s="83" t="inlineStr">
+      <c r="B168" s="86" t="inlineStr">
         <is>
           <t>PS5-60-48 - Oil Mist Separator Skid PS5-60-VS-9100G</t>
         </is>
@@ -12718,9 +12735,9 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="O168" s="69" t="inlineStr">
-        <is>
-          <t>partial</t>
+      <c r="O168" s="28" t="inlineStr">
+        <is>
+          <t>full</t>
         </is>
       </c>
     </row>
@@ -12730,7 +12747,7 @@
           <t>PS5-60-49</t>
         </is>
       </c>
-      <c r="B169" s="83" t="inlineStr">
+      <c r="B169" s="86" t="inlineStr">
         <is>
           <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
@@ -12799,7 +12816,7 @@
           <t>PS5-60-50</t>
         </is>
       </c>
-      <c r="B170" s="83" t="inlineStr">
+      <c r="B170" s="86" t="inlineStr">
         <is>
           <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
@@ -12868,7 +12885,7 @@
           <t>PS5-60-51</t>
         </is>
       </c>
-      <c r="B171" s="83" t="inlineStr">
+      <c r="B171" s="86" t="inlineStr">
         <is>
           <t>PS5-60-51 - Lube Oil Separator Module PS5-60-UO-81100C</t>
         </is>
@@ -12937,7 +12954,7 @@
           <t>PS5-60-52</t>
         </is>
       </c>
-      <c r="B172" s="83" t="inlineStr">
+      <c r="B172" s="86" t="inlineStr">
         <is>
           <t>PS5-60-52 - Lube Oil Separator Module PS5-60-UO-81100D</t>
         </is>
@@ -13006,7 +13023,7 @@
           <t>PS5-60-53</t>
         </is>
       </c>
-      <c r="B173" s="83" t="inlineStr">
+      <c r="B173" s="86" t="inlineStr">
         <is>
           <t>PS5-60-53 - Lube Oil Separator Module PS5-60-UO-81100E</t>
         </is>
@@ -13075,7 +13092,7 @@
           <t>PS5-60-54</t>
         </is>
       </c>
-      <c r="B174" s="83" t="inlineStr">
+      <c r="B174" s="86" t="inlineStr">
         <is>
           <t>PS5-60-54 - Lube Oil Separator Module PS5-60-UO-81100F</t>
         </is>
@@ -13144,7 +13161,7 @@
           <t>PS5-60-55</t>
         </is>
       </c>
-      <c r="B175" s="83" t="inlineStr">
+      <c r="B175" s="86" t="inlineStr">
         <is>
           <t>PS5-60-55 - Lube Oil Separator Module PS5-60-UO-81100G</t>
         </is>
@@ -13213,7 +13230,7 @@
           <t>PS5-60-56</t>
         </is>
       </c>
-      <c r="B176" s="83" t="inlineStr">
+      <c r="B176" s="86" t="inlineStr">
         <is>
           <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
@@ -13282,7 +13299,7 @@
           <t>PS5-60-57</t>
         </is>
       </c>
-      <c r="B177" s="83" t="inlineStr">
+      <c r="B177" s="86" t="inlineStr">
         <is>
           <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
@@ -13351,7 +13368,7 @@
           <t>PS5-60-58</t>
         </is>
       </c>
-      <c r="B178" s="83" t="inlineStr">
+      <c r="B178" s="86" t="inlineStr">
         <is>
           <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
@@ -13420,7 +13437,7 @@
           <t>PS5-60-59</t>
         </is>
       </c>
-      <c r="B179" s="83" t="inlineStr">
+      <c r="B179" s="86" t="inlineStr">
         <is>
           <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
@@ -13489,7 +13506,7 @@
           <t>PS5-60-60</t>
         </is>
       </c>
-      <c r="B180" s="83" t="inlineStr">
+      <c r="B180" s="86" t="inlineStr">
         <is>
           <t>PS5-60-60 - Fuel Conditioning Module PS5-60-UZ-8900C</t>
         </is>
@@ -13558,7 +13575,7 @@
           <t>PS5-60-61</t>
         </is>
       </c>
-      <c r="B181" s="83" t="inlineStr">
+      <c r="B181" s="86" t="inlineStr">
         <is>
           <t>PS5-60-61 - Fuel Conditioning Module PS5-60-UZ-8900C (UCP)</t>
         </is>
@@ -13569,7 +13586,7 @@
       <c r="D181" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E181" s="95" t="inlineStr">
+      <c r="E181" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13627,7 +13644,7 @@
           <t>PS5-60-62</t>
         </is>
       </c>
-      <c r="B182" s="83" t="inlineStr">
+      <c r="B182" s="86" t="inlineStr">
         <is>
           <t>PS5-60-62 - Fuel Conditioning Module PS5-60-UZ-8900D</t>
         </is>
@@ -13696,7 +13713,7 @@
           <t>PS5-60-63</t>
         </is>
       </c>
-      <c r="B183" s="83" t="inlineStr">
+      <c r="B183" s="86" t="inlineStr">
         <is>
           <t>PS5-60-63 - Fuel Conditioning Module PS5-60-UZ-8900D (UCP)</t>
         </is>
@@ -13707,7 +13724,7 @@
       <c r="D183" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E183" s="95" t="inlineStr">
+      <c r="E183" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13765,7 +13782,7 @@
           <t>PS5-60-64</t>
         </is>
       </c>
-      <c r="B184" s="83" t="inlineStr">
+      <c r="B184" s="86" t="inlineStr">
         <is>
           <t>PS5-60-64 - Fuel Conditioning Module PS5-60-UZ-8900E</t>
         </is>
@@ -13834,7 +13851,7 @@
           <t>PS5-60-65</t>
         </is>
       </c>
-      <c r="B185" s="83" t="inlineStr">
+      <c r="B185" s="86" t="inlineStr">
         <is>
           <t>PS5-60-65 - Fuel Conditioning Module PS5-60-UZ-8900E (UCP)</t>
         </is>
@@ -13845,7 +13862,7 @@
       <c r="D185" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E185" s="95" t="inlineStr">
+      <c r="E185" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13903,7 +13920,7 @@
           <t>PS5-60-66</t>
         </is>
       </c>
-      <c r="B186" s="83" t="inlineStr">
+      <c r="B186" s="86" t="inlineStr">
         <is>
           <t>PS5-60-66 - Fuel Conditioning Module PS5-60-UZ-8900F</t>
         </is>
@@ -13972,7 +13989,7 @@
           <t>PS5-60-67</t>
         </is>
       </c>
-      <c r="B187" s="83" t="inlineStr">
+      <c r="B187" s="86" t="inlineStr">
         <is>
           <t>PS5-60-67 - Fuel Conditioning Module PS5-60-UZ-8900F (UCP)</t>
         </is>
@@ -13983,7 +14000,7 @@
       <c r="D187" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E187" s="95" t="inlineStr">
+      <c r="E187" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14041,7 +14058,7 @@
           <t>PS5-60-68</t>
         </is>
       </c>
-      <c r="B188" s="83" t="inlineStr">
+      <c r="B188" s="86" t="inlineStr">
         <is>
           <t>PS5-60-68 - Fuel Conditioning Module PS5-60-UZ-8900G</t>
         </is>
@@ -14110,7 +14127,7 @@
           <t>PS5-60-69</t>
         </is>
       </c>
-      <c r="B189" s="83" t="inlineStr">
+      <c r="B189" s="86" t="inlineStr">
         <is>
           <t>PS5-60-69 - Fuel Conditioning Module PS5-60-UZ-8900G (UCP)</t>
         </is>
@@ -14121,7 +14138,7 @@
       <c r="D189" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E189" s="95" t="inlineStr">
+      <c r="E189" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14179,7 +14196,7 @@
           <t>PS5-60-70</t>
         </is>
       </c>
-      <c r="B190" s="83" t="inlineStr">
+      <c r="B190" s="86" t="inlineStr">
         <is>
           <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
@@ -14248,7 +14265,7 @@
           <t>PS5-60-71</t>
         </is>
       </c>
-      <c r="B191" s="83" t="inlineStr">
+      <c r="B191" s="86" t="inlineStr">
         <is>
           <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
@@ -14317,7 +14334,7 @@
           <t>PS5-60-72</t>
         </is>
       </c>
-      <c r="B192" s="83" t="inlineStr">
+      <c r="B192" s="86" t="inlineStr">
         <is>
           <t>PS5-60-72 - Engine C Cooling system</t>
         </is>
@@ -14386,7 +14403,7 @@
           <t>PS5-60-73</t>
         </is>
       </c>
-      <c r="B193" s="83" t="inlineStr">
+      <c r="B193" s="86" t="inlineStr">
         <is>
           <t>PS5-60-73 - Engine D Cooling system</t>
         </is>
@@ -14455,7 +14472,7 @@
           <t>PS5-60-74</t>
         </is>
       </c>
-      <c r="B194" s="83" t="inlineStr">
+      <c r="B194" s="86" t="inlineStr">
         <is>
           <t>PS5-60-74 - Engine E Cooling system</t>
         </is>
@@ -14524,7 +14541,7 @@
           <t>PS5-60-75</t>
         </is>
       </c>
-      <c r="B195" s="83" t="inlineStr">
+      <c r="B195" s="86" t="inlineStr">
         <is>
           <t>PS5-60-75 - Engine F Cooling system</t>
         </is>
@@ -14593,7 +14610,7 @@
           <t>PS5-60-76</t>
         </is>
       </c>
-      <c r="B196" s="83" t="inlineStr">
+      <c r="B196" s="86" t="inlineStr">
         <is>
           <t>PS5-60-76 - Engine G Cooling system</t>
         </is>
@@ -14662,7 +14679,7 @@
           <t>PS5-61-01</t>
         </is>
       </c>
-      <c r="B197" s="83" t="inlineStr">
+      <c r="B197" s="86" t="inlineStr">
         <is>
           <t>PS5-61-01 - 33kV Switchboard EITS Building (PS5-61-IJ-0001)</t>
         </is>
@@ -14731,7 +14748,7 @@
           <t>PS5-61-02</t>
         </is>
       </c>
-      <c r="B198" s="83" t="inlineStr">
+      <c r="B198" s="86" t="inlineStr">
         <is>
           <t>PS5-61-02 - 6.6kV Switchboard and Transformer LLHT North - EITS Building (PS5-61-IJ-0010)</t>
         </is>
@@ -14800,7 +14817,7 @@
           <t>PS5-61-03</t>
         </is>
       </c>
-      <c r="B199" s="83" t="inlineStr">
+      <c r="B199" s="86" t="inlineStr">
         <is>
           <t>PS5-61-03 - 6.6kV Switchboard and Transformer LLHT South - EITS Building (PS5-61-IJ-0011)</t>
         </is>
@@ -14869,7 +14886,7 @@
           <t>PS5-61-04</t>
         </is>
       </c>
-      <c r="B200" s="83" t="inlineStr">
+      <c r="B200" s="86" t="inlineStr">
         <is>
           <t>PS5-61-04 - 0.4kV Switchboard Office &amp; Facilities Building (PS5-61-IK-0005)</t>
         </is>
@@ -14880,7 +14897,7 @@
       <c r="D200" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E200" s="95" t="inlineStr">
+      <c r="E200" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14938,7 +14955,7 @@
           <t>PS5-61-05</t>
         </is>
       </c>
-      <c r="B201" s="83" t="inlineStr">
+      <c r="B201" s="86" t="inlineStr">
         <is>
           <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
@@ -15007,7 +15024,7 @@
           <t>PS5-61-06</t>
         </is>
       </c>
-      <c r="B202" s="83" t="inlineStr">
+      <c r="B202" s="86" t="inlineStr">
         <is>
           <t>PS5-61-06 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0006)</t>
         </is>
@@ -15076,7 +15093,7 @@
           <t>PS5-61-07</t>
         </is>
       </c>
-      <c r="B203" s="83" t="inlineStr">
+      <c r="B203" s="86" t="inlineStr">
         <is>
           <t>PS5-61-07 - 0.4kV Switchboard EITS Building (PS5-61-IK-0001)</t>
         </is>
@@ -15145,7 +15162,7 @@
           <t>PS5-61-08</t>
         </is>
       </c>
-      <c r="B204" s="83" t="inlineStr">
+      <c r="B204" s="86" t="inlineStr">
         <is>
           <t>PS5-61-08 - Electrical Control System</t>
         </is>
@@ -15214,7 +15231,7 @@
           <t>PS5-61-09</t>
         </is>
       </c>
-      <c r="B205" s="83" t="inlineStr">
+      <c r="B205" s="86" t="inlineStr">
         <is>
           <t>PS5-61-09 - Outdoor Power Distribution Board - PS5-61-IG-0014</t>
         </is>
@@ -15225,7 +15242,7 @@
       <c r="D205" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E205" s="95" t="inlineStr">
+      <c r="E205" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15283,7 +15300,7 @@
           <t>PS5-61-10</t>
         </is>
       </c>
-      <c r="B206" s="83" t="inlineStr">
+      <c r="B206" s="86" t="inlineStr">
         <is>
           <t>PS5-61-10 - Outdoor Valves Distribution Board - PS5-61-IG-0042</t>
         </is>
@@ -15294,7 +15311,7 @@
       <c r="D206" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E206" s="95" t="inlineStr">
+      <c r="E206" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15352,7 +15369,7 @@
           <t>PS5-61-11</t>
         </is>
       </c>
-      <c r="B207" s="83" t="inlineStr">
+      <c r="B207" s="86" t="inlineStr">
         <is>
           <t>PS5-61-11 - Outdoor Valves Distribution Board - PS5-61-IG-0043</t>
         </is>
@@ -15363,7 +15380,7 @@
       <c r="D207" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E207" s="95" t="inlineStr">
+      <c r="E207" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15421,7 +15438,7 @@
           <t>PS5-61-12</t>
         </is>
       </c>
-      <c r="B208" s="83" t="inlineStr">
+      <c r="B208" s="86" t="inlineStr">
         <is>
           <t>PS5-61-12 - EITS 33kV Bld. Normal Auxiliary DP - PS5-61-IG-0008</t>
         </is>
@@ -15432,7 +15449,7 @@
       <c r="D208" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E208" s="95" t="inlineStr">
+      <c r="E208" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15443,7 +15460,7 @@
       <c r="G208" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H208" s="95" t="inlineStr">
+      <c r="H208" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15490,7 +15507,7 @@
           <t>PS5-61-13</t>
         </is>
       </c>
-      <c r="B209" s="83" t="inlineStr">
+      <c r="B209" s="86" t="inlineStr">
         <is>
           <t>PS5-61-13 - Power Distribution Board Office Building - PS5-61-IG-0020</t>
         </is>
@@ -15501,7 +15518,7 @@
       <c r="D209" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E209" s="95" t="inlineStr">
+      <c r="E209" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15559,7 +15576,7 @@
           <t>PS5-61-14</t>
         </is>
       </c>
-      <c r="B210" s="83" t="inlineStr">
+      <c r="B210" s="86" t="inlineStr">
         <is>
           <t>PS5-61-14 - Power Distribution Board Workshop &amp; Warehouse - PS5-61-IG-0009</t>
         </is>
@@ -15570,7 +15587,7 @@
       <c r="D210" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E210" s="95" t="inlineStr">
+      <c r="E210" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15628,7 +15645,7 @@
           <t>PS5-62-01</t>
         </is>
       </c>
-      <c r="B211" s="83" t="inlineStr">
+      <c r="B211" s="86" t="inlineStr">
         <is>
           <t>PS5-62-01 - Lighting Control Panel - PS5-62-IE-0001</t>
         </is>
@@ -15697,7 +15714,7 @@
           <t>PS5-62-02</t>
         </is>
       </c>
-      <c r="B212" s="83" t="inlineStr">
+      <c r="B212" s="86" t="inlineStr">
         <is>
           <t>PS5-62-02 - Lighting Control Panel - PS5-62-IE-0002</t>
         </is>
@@ -15766,7 +15783,7 @@
           <t>PS5-62-03</t>
         </is>
       </c>
-      <c r="B213" s="83" t="inlineStr">
+      <c r="B213" s="86" t="inlineStr">
         <is>
           <t>PS5-62-03 - Outdoor Emergency Lighting DB  - PS5-05-IG-0004</t>
         </is>
@@ -15777,7 +15794,7 @@
       <c r="D213" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E213" s="95" t="inlineStr">
+      <c r="E213" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15835,7 +15852,7 @@
           <t>PS5-62-04</t>
         </is>
       </c>
-      <c r="B214" s="83" t="inlineStr">
+      <c r="B214" s="86" t="inlineStr">
         <is>
           <t>PS5-62-04 - Outdoor Emergency Lighting DB  - PS5-05-IG-0006</t>
         </is>
@@ -15846,7 +15863,7 @@
       <c r="D214" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E214" s="95" t="inlineStr">
+      <c r="E214" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15904,7 +15921,7 @@
           <t>PS5-62-05</t>
         </is>
       </c>
-      <c r="B215" s="83" t="inlineStr">
+      <c r="B215" s="86" t="inlineStr">
         <is>
           <t>PS5-62-05 - Guard House Emergency L&amp;SP DB  - PS5-05-IG-0007</t>
         </is>
@@ -15915,7 +15932,7 @@
       <c r="D215" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E215" s="95" t="inlineStr">
+      <c r="E215" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15973,7 +15990,7 @@
           <t>PS5-62-06</t>
         </is>
       </c>
-      <c r="B216" s="83" t="inlineStr">
+      <c r="B216" s="86" t="inlineStr">
         <is>
           <t>PS5-62-06 - CRO Generator Building Emergency Lighting DB  - PS5-05-IG-0025</t>
         </is>
@@ -15984,7 +16001,7 @@
       <c r="D216" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E216" s="95" t="inlineStr">
+      <c r="E216" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16042,7 +16059,7 @@
           <t>PS5-62-07</t>
         </is>
       </c>
-      <c r="B217" s="83" t="inlineStr">
+      <c r="B217" s="86" t="inlineStr">
         <is>
           <t>PS5-62-07 - CRO Generator Electrical Building Emergency Lighting DB  - PS5-05-IG-0026</t>
         </is>
@@ -16111,7 +16128,7 @@
           <t>PS5-62-08</t>
         </is>
       </c>
-      <c r="B218" s="83" t="inlineStr">
+      <c r="B218" s="86" t="inlineStr">
         <is>
           <t>PS5-62-08 - Outdoor Normal Lighting  DB  - PS5-61-IG-0006</t>
         </is>
@@ -16122,7 +16139,7 @@
       <c r="D218" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E218" s="95" t="inlineStr">
+      <c r="E218" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16180,7 +16197,7 @@
           <t>PS5-62-09</t>
         </is>
       </c>
-      <c r="B219" s="83" t="inlineStr">
+      <c r="B219" s="86" t="inlineStr">
         <is>
           <t>PS5-62-09 - Outdoor Normal Lighting DB  - PS5-61-IG-0007</t>
         </is>
@@ -16249,7 +16266,7 @@
           <t>PS5-62-10</t>
         </is>
       </c>
-      <c r="B220" s="83" t="inlineStr">
+      <c r="B220" s="86" t="inlineStr">
         <is>
           <t>PS5-62-10 - CRO Generator Building Normal L&amp;SP DB  - PS5-61-IG-0015</t>
         </is>
@@ -16303,7 +16320,7 @@
       </c>
       <c r="N220" s="70" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="O220" s="28" t="inlineStr">
@@ -16318,7 +16335,7 @@
           <t>PS5-62-11</t>
         </is>
       </c>
-      <c r="B221" s="83" t="inlineStr">
+      <c r="B221" s="86" t="inlineStr">
         <is>
           <t>PS5-62-11 - CRO Generator Electrical Building Normal L&amp;SP DB  - PS5-61-IG-0016</t>
         </is>
@@ -16329,7 +16346,7 @@
       <c r="D221" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E221" s="95" t="inlineStr">
+      <c r="E221" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16387,7 +16404,7 @@
           <t>PS5-62-12</t>
         </is>
       </c>
-      <c r="B222" s="83" t="inlineStr">
+      <c r="B222" s="86" t="inlineStr">
         <is>
           <t>PS5-62-12 - EITS 33kV Bld. Emergency L&amp;SP DP - PS5-05-IG-0003</t>
         </is>
@@ -16398,7 +16415,7 @@
       <c r="D222" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E222" s="95" t="inlineStr">
+      <c r="E222" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16409,7 +16426,7 @@
       <c r="G222" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H222" s="95" t="inlineStr">
+      <c r="H222" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16456,7 +16473,7 @@
           <t>PS5-62-13</t>
         </is>
       </c>
-      <c r="B223" s="83" t="inlineStr">
+      <c r="B223" s="86" t="inlineStr">
         <is>
           <t>PS5-62-13 - EITS 33kV Bld. Normal L&amp;SP DP - PS5-61-IG-0003</t>
         </is>
@@ -16478,7 +16495,7 @@
       <c r="G223" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H223" s="95" t="inlineStr">
+      <c r="H223" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16525,7 +16542,7 @@
           <t>PS5-62-14</t>
         </is>
       </c>
-      <c r="B224" s="83" t="inlineStr">
+      <c r="B224" s="86" t="inlineStr">
         <is>
           <t>PS5-62-14 - Office Building Emergency L&amp;SP DB - PS5-05-IG-0002</t>
         </is>
@@ -16536,7 +16553,7 @@
       <c r="D224" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E224" s="95" t="inlineStr">
+      <c r="E224" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16594,7 +16611,7 @@
           <t>PS5-62-15</t>
         </is>
       </c>
-      <c r="B225" s="83" t="inlineStr">
+      <c r="B225" s="86" t="inlineStr">
         <is>
           <t>PS5-62-15 - Office Building Normal L&amp;SP DB - PS5-61-IG-0002</t>
         </is>
@@ -16605,7 +16622,7 @@
       <c r="D225" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E225" s="95" t="inlineStr">
+      <c r="E225" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16663,7 +16680,7 @@
           <t>PS5-62-16</t>
         </is>
       </c>
-      <c r="B226" s="83" t="inlineStr">
+      <c r="B226" s="86" t="inlineStr">
         <is>
           <t>PS5-62-16 - Guard Hut A Normal L&amp;SP DB - PS5-61-IG-0111</t>
         </is>
@@ -16674,7 +16691,7 @@
       <c r="D226" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E226" s="95" t="inlineStr">
+      <c r="E226" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16732,7 +16749,7 @@
           <t>PS5-62-17</t>
         </is>
       </c>
-      <c r="B227" s="83" t="inlineStr">
+      <c r="B227" s="86" t="inlineStr">
         <is>
           <t>PS5-62-17 - Guard Hut B Normal L&amp;SP DB - PS5-61-IG-0112</t>
         </is>
@@ -16743,7 +16760,7 @@
       <c r="D227" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E227" s="95" t="inlineStr">
+      <c r="E227" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16801,7 +16818,7 @@
           <t>PS5-62-18</t>
         </is>
       </c>
-      <c r="B228" s="83" t="inlineStr">
+      <c r="B228" s="86" t="inlineStr">
         <is>
           <t>PS5-62-18 - Workshop &amp; Warehouse Normal L&amp;SP DB - PS5-61-IG-0004</t>
         </is>
@@ -16812,7 +16829,7 @@
       <c r="D228" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E228" s="95" t="inlineStr">
+      <c r="E228" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16870,7 +16887,7 @@
           <t>PS5-62-19</t>
         </is>
       </c>
-      <c r="B229" s="83" t="inlineStr">
+      <c r="B229" s="86" t="inlineStr">
         <is>
           <t>PS5-62-19 - Workshop &amp; Warehouse Emergency L&amp;SP DB - PS5-05-IG-0101</t>
         </is>
@@ -16881,7 +16898,7 @@
       <c r="D229" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E229" s="95" t="inlineStr">
+      <c r="E229" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -16939,7 +16956,7 @@
           <t>PS5-62-20</t>
         </is>
       </c>
-      <c r="B230" s="83" t="inlineStr">
+      <c r="B230" s="86" t="inlineStr">
         <is>
           <t>PS5-62-20 - Office Building Normal L&amp;SP DB - PS5-61-IG-0010</t>
         </is>
@@ -16950,7 +16967,7 @@
       <c r="D230" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E230" s="95" t="inlineStr">
+      <c r="E230" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17008,7 +17025,7 @@
           <t>PS5-63-01</t>
         </is>
       </c>
-      <c r="B231" s="83" t="inlineStr">
+      <c r="B231" s="86" t="inlineStr">
         <is>
           <t>PS5-63-01 - Electrical Earthing</t>
         </is>
@@ -17062,7 +17079,7 @@
       </c>
       <c r="N231" s="69" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="O231" s="28" t="inlineStr">
@@ -17077,7 +17094,7 @@
           <t>PS5-63-02</t>
         </is>
       </c>
-      <c r="B232" s="83" t="inlineStr">
+      <c r="B232" s="86" t="inlineStr">
         <is>
           <t>PS5-63-02 - Electrical Earthing - Office and Facilities building</t>
         </is>
@@ -17088,7 +17105,7 @@
       <c r="D232" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E232" s="95" t="inlineStr">
+      <c r="E232" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17146,7 +17163,7 @@
           <t>PS5-63-03</t>
         </is>
       </c>
-      <c r="B233" s="83" t="inlineStr">
+      <c r="B233" s="86" t="inlineStr">
         <is>
           <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
         </is>
@@ -17157,7 +17174,7 @@
       <c r="D233" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E233" s="95" t="inlineStr">
+      <c r="E233" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17215,7 +17232,7 @@
           <t>PS5-63-04</t>
         </is>
       </c>
-      <c r="B234" s="83" t="inlineStr">
+      <c r="B234" s="86" t="inlineStr">
         <is>
           <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
         </is>
@@ -17237,7 +17254,7 @@
       <c r="G234" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H234" s="95" t="inlineStr">
+      <c r="H234" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17284,7 +17301,7 @@
           <t>PS5-63-05</t>
         </is>
       </c>
-      <c r="B235" s="83" t="inlineStr">
+      <c r="B235" s="86" t="inlineStr">
         <is>
           <t>PS5-63-05 - Electrical Earthing - Guard Hut A &amp; B</t>
         </is>
@@ -17295,7 +17312,7 @@
       <c r="D235" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E235" s="95" t="inlineStr">
+      <c r="E235" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17353,7 +17370,7 @@
           <t>PS5-63-06</t>
         </is>
       </c>
-      <c r="B236" s="83" t="inlineStr">
+      <c r="B236" s="86" t="inlineStr">
         <is>
           <t>PS5-63-06 - Electrical Earthing - Guard House</t>
         </is>
@@ -17364,7 +17381,7 @@
       <c r="D236" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E236" s="95" t="inlineStr">
+      <c r="E236" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17422,7 +17439,7 @@
           <t>PS5-63-07</t>
         </is>
       </c>
-      <c r="B237" s="83" t="inlineStr">
+      <c r="B237" s="86" t="inlineStr">
         <is>
           <t>PS5-63-07 - Electrical Earthing - Workshop &amp; Warehouse</t>
         </is>
@@ -17433,7 +17450,7 @@
       <c r="D237" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E237" s="95" t="inlineStr">
+      <c r="E237" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17491,7 +17508,7 @@
           <t>PS5-71-01</t>
         </is>
       </c>
-      <c r="B238" s="83" t="inlineStr">
+      <c r="B238" s="86" t="inlineStr">
         <is>
           <t>PS5-71-01 - CFO Storage Tank Feed Heater</t>
         </is>
@@ -17560,7 +17577,7 @@
           <t>PS5-71-02</t>
         </is>
       </c>
-      <c r="B239" s="83" t="inlineStr">
+      <c r="B239" s="86" t="inlineStr">
         <is>
           <t>PS5-71-02 - CFO Allocation Metering Package</t>
         </is>
@@ -17629,7 +17646,7 @@
           <t>PS5-71-03</t>
         </is>
       </c>
-      <c r="B240" s="83" t="inlineStr">
+      <c r="B240" s="86" t="inlineStr">
         <is>
           <t>PS5-71-03 - CFO Allocation Metering Package (UCP)</t>
         </is>
@@ -17640,7 +17657,7 @@
       <c r="D240" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E240" s="95" t="inlineStr">
+      <c r="E240" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17651,7 +17668,7 @@
       <c r="G240" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H240" s="95" t="inlineStr">
+      <c r="H240" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17698,7 +17715,7 @@
           <t>PS5-71-04</t>
         </is>
       </c>
-      <c r="B241" s="83" t="inlineStr">
+      <c r="B241" s="86" t="inlineStr">
         <is>
           <t>PS5-71-04 - CFO Storage Tank</t>
         </is>
@@ -17767,7 +17784,7 @@
           <t>PS5-71-05</t>
         </is>
       </c>
-      <c r="B242" s="83" t="inlineStr">
+      <c r="B242" s="86" t="inlineStr">
         <is>
           <t>PS5-71-05 - CFO Transfer Pump A/B</t>
         </is>
@@ -17836,7 +17853,7 @@
           <t>PS5-71-06</t>
         </is>
       </c>
-      <c r="B243" s="83" t="inlineStr">
+      <c r="B243" s="86" t="inlineStr">
         <is>
           <t>PS5-71-06 - Crude Fuel Separation Module</t>
         </is>
@@ -17905,7 +17922,7 @@
           <t>PS5-71-07</t>
         </is>
       </c>
-      <c r="B244" s="83" t="inlineStr">
+      <c r="B244" s="86" t="inlineStr">
         <is>
           <t>PS5-71-07 - Crude Fuel Separation Module (UCP)</t>
         </is>
@@ -17974,7 +17991,7 @@
           <t>PS5-71-08</t>
         </is>
       </c>
-      <c r="B245" s="83" t="inlineStr">
+      <c r="B245" s="86" t="inlineStr">
         <is>
           <t>PS5-71-08 - CFO Pre-Pressure Modules</t>
         </is>
@@ -18043,7 +18060,7 @@
           <t>PS5-71-09</t>
         </is>
       </c>
-      <c r="B246" s="83" t="inlineStr">
+      <c r="B246" s="86" t="inlineStr">
         <is>
           <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
         </is>
@@ -18112,7 +18129,7 @@
           <t>PS5-71-12</t>
         </is>
       </c>
-      <c r="B247" s="83" t="inlineStr">
+      <c r="B247" s="86" t="inlineStr">
         <is>
           <t>PS5-71-12 - CFO Service Tank</t>
         </is>
@@ -18166,7 +18183,7 @@
       </c>
       <c r="N247" s="69" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="O247" s="28" t="inlineStr">
@@ -18181,7 +18198,7 @@
           <t>PS5-71-13</t>
         </is>
       </c>
-      <c r="B248" s="83" t="inlineStr">
+      <c r="B248" s="86" t="inlineStr">
         <is>
           <t>PS5-71-13 - CFO Service Pump A/B</t>
         </is>
@@ -18235,7 +18252,7 @@
       </c>
       <c r="N248" s="69" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="O248" s="28" t="inlineStr">
@@ -18250,7 +18267,7 @@
           <t>PS5-71-14</t>
         </is>
       </c>
-      <c r="B249" s="83" t="inlineStr">
+      <c r="B249" s="86" t="inlineStr">
         <is>
           <t>PS5-71-14 - Diesel Fuel Transfer and Dispensing Station</t>
         </is>
@@ -18319,7 +18336,7 @@
           <t>PS5-71-15</t>
         </is>
       </c>
-      <c r="B250" s="83" t="inlineStr">
+      <c r="B250" s="86" t="inlineStr">
         <is>
           <t>PS5-71-15 - Diesel Fuel Storage Tank</t>
         </is>
@@ -18388,7 +18405,7 @@
           <t>PS5-71-16</t>
         </is>
       </c>
-      <c r="B251" s="83" t="inlineStr">
+      <c r="B251" s="86" t="inlineStr">
         <is>
           <t>PS5-71-16 - Diesel Fuel Supply Pump A/B</t>
         </is>
@@ -18457,7 +18474,7 @@
           <t>PS5-71-17</t>
         </is>
       </c>
-      <c r="B252" s="83" t="inlineStr">
+      <c r="B252" s="86" t="inlineStr">
         <is>
           <t>PS5-71-17 - Diesel Fuel Distribution Header</t>
         </is>
@@ -18526,7 +18543,7 @@
           <t>PS5-71-18</t>
         </is>
       </c>
-      <c r="B253" s="83" t="inlineStr">
+      <c r="B253" s="86" t="inlineStr">
         <is>
           <t>PS5-71-18 - Diesel Separator Module</t>
         </is>
@@ -18595,7 +18612,7 @@
           <t>PS5-71-19</t>
         </is>
       </c>
-      <c r="B254" s="83" t="inlineStr">
+      <c r="B254" s="86" t="inlineStr">
         <is>
           <t>PS5-71-19 - Diesel Separator Module (UCP)</t>
         </is>
@@ -18664,7 +18681,7 @@
           <t>PS5-71-20</t>
         </is>
       </c>
-      <c r="B255" s="83" t="inlineStr">
+      <c r="B255" s="86" t="inlineStr">
         <is>
           <t>PS5-71-20 - Diesel Fuel Day Tank</t>
         </is>
@@ -18733,7 +18750,7 @@
           <t>PS5-71-21</t>
         </is>
       </c>
-      <c r="B256" s="83" t="inlineStr">
+      <c r="B256" s="86" t="inlineStr">
         <is>
           <t>PS5-71-21 - Diesel Transfer Pump A/B</t>
         </is>
@@ -18787,7 +18804,7 @@
       </c>
       <c r="N256" s="54" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="O256" s="28" t="inlineStr">
@@ -18802,7 +18819,7 @@
           <t>PS5-71-22</t>
         </is>
       </c>
-      <c r="B257" s="83" t="inlineStr">
+      <c r="B257" s="86" t="inlineStr">
         <is>
           <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
@@ -18871,7 +18888,7 @@
           <t>PS5-71-23</t>
         </is>
       </c>
-      <c r="B258" s="83" t="inlineStr">
+      <c r="B258" s="86" t="inlineStr">
         <is>
           <t>PS5-71-23 - Diesel Fuel Pre Pressure Module (UCP)</t>
         </is>
@@ -18940,7 +18957,7 @@
           <t>PS5-74-01</t>
         </is>
       </c>
-      <c r="B259" s="83" t="inlineStr">
+      <c r="B259" s="86" t="inlineStr">
         <is>
           <t>PS5-74-01 - N2 Generation Skid</t>
         </is>
@@ -19009,7 +19026,7 @@
           <t>PS5-74-02</t>
         </is>
       </c>
-      <c r="B260" s="83" t="inlineStr">
+      <c r="B260" s="86" t="inlineStr">
         <is>
           <t>PS5-74-02 - N2 Generation Skid (UCP)</t>
         </is>
@@ -19078,7 +19095,7 @@
           <t>PS5-74-03</t>
         </is>
       </c>
-      <c r="B261" s="83" t="inlineStr">
+      <c r="B261" s="86" t="inlineStr">
         <is>
           <t>PS5-74-03 - Nitrogen Receiver</t>
         </is>
@@ -19147,7 +19164,7 @@
           <t>PS5-74-04</t>
         </is>
       </c>
-      <c r="B262" s="83" t="inlineStr">
+      <c r="B262" s="86" t="inlineStr">
         <is>
           <t>PS5-74-04 - Nitrogen Distribution Header</t>
         </is>
@@ -19158,7 +19175,7 @@
       <c r="D262" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E262" s="95" t="inlineStr">
+      <c r="E262" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19216,7 +19233,7 @@
           <t>PS5-75-01</t>
         </is>
       </c>
-      <c r="B263" s="83" t="inlineStr">
+      <c r="B263" s="86" t="inlineStr">
         <is>
           <t>PS5-75-01 - DRA Injection Package</t>
         </is>
@@ -19227,7 +19244,7 @@
       <c r="D263" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E263" s="95" t="inlineStr">
+      <c r="E263" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19270,7 +19287,7 @@
       </c>
       <c r="N263" s="69" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="O263" s="28" t="inlineStr">
@@ -19285,7 +19302,7 @@
           <t>PS5-75-02</t>
         </is>
       </c>
-      <c r="B264" s="83" t="inlineStr">
+      <c r="B264" s="86" t="inlineStr">
         <is>
           <t>PS5-75-02 - Biocide Injection Package</t>
         </is>
@@ -19354,7 +19371,7 @@
           <t>PS5-75-03</t>
         </is>
       </c>
-      <c r="B265" s="83" t="inlineStr">
+      <c r="B265" s="86" t="inlineStr">
         <is>
           <t>PS5-75-03 - Corrosion Inhibitor Injection Package</t>
         </is>
@@ -19423,7 +19440,7 @@
           <t>PS5-78-01</t>
         </is>
       </c>
-      <c r="B266" s="83" t="inlineStr">
+      <c r="B266" s="86" t="inlineStr">
         <is>
           <t>PS5-78-01 - Lifting and handling equipment</t>
         </is>
@@ -19492,7 +19509,7 @@
           <t>PS5-79-01</t>
         </is>
       </c>
-      <c r="B267" s="83" t="inlineStr">
+      <c r="B267" s="86" t="inlineStr">
         <is>
           <t>PS5-79-01 - Electrical Heat Tracing Transformer/Distribution Board 1 (PS5-79-IG-0001)</t>
         </is>
@@ -19503,7 +19520,7 @@
       <c r="D267" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E267" s="95" t="inlineStr">
+      <c r="E267" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19561,7 +19578,7 @@
           <t>PS5-79-02</t>
         </is>
       </c>
-      <c r="B268" s="83" t="inlineStr">
+      <c r="B268" s="86" t="inlineStr">
         <is>
           <t>PS5-79-02 - Electrical Heat Tracing Transformer/Distribution Board 2 (PS5-79-IG-0002)</t>
         </is>
@@ -19572,7 +19589,7 @@
       <c r="D268" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E268" s="95" t="inlineStr">
+      <c r="E268" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19615,7 +19632,7 @@
       </c>
       <c r="N268" s="69" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="O268" s="28" t="inlineStr">
@@ -19630,7 +19647,7 @@
           <t>PS5-79-03</t>
         </is>
       </c>
-      <c r="B269" s="83" t="inlineStr">
+      <c r="B269" s="86" t="inlineStr">
         <is>
           <t>PS5-79-03 - Electrical Heat Tracing Transformer/Distribution Board 3 (PS5-79-IG-0003)</t>
         </is>
@@ -19641,7 +19658,7 @@
       <c r="D269" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E269" s="95" t="inlineStr">
+      <c r="E269" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19699,7 +19716,7 @@
           <t>PS5-79-04</t>
         </is>
       </c>
-      <c r="B270" s="83" t="inlineStr">
+      <c r="B270" s="86" t="inlineStr">
         <is>
           <t>PS5-79-04 - Electrical Heat Tracing Transformer/Distribution Board 4 (PS5-79-IG-0004)</t>
         </is>
@@ -19710,7 +19727,7 @@
       <c r="D270" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E270" s="95" t="inlineStr">
+      <c r="E270" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19768,7 +19785,7 @@
           <t>PS5-79-05</t>
         </is>
       </c>
-      <c r="B271" s="83" t="inlineStr">
+      <c r="B271" s="86" t="inlineStr">
         <is>
           <t>PS5-79-05 - Electrical Heat Tracing Transformer/Distribution Board 5 (PS5-79-IG-0005)</t>
         </is>
@@ -19779,7 +19796,7 @@
       <c r="D271" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E271" s="95" t="inlineStr">
+      <c r="E271" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19837,7 +19854,7 @@
           <t>PS5-79-06</t>
         </is>
       </c>
-      <c r="B272" s="83" t="inlineStr">
+      <c r="B272" s="86" t="inlineStr">
         <is>
           <t>PS5-79-06 - Electrical Heat Tracing Transformer/Distribution Board 6 (PS5-79-IG-0006)</t>
         </is>
@@ -19848,7 +19865,7 @@
       <c r="D272" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E272" s="95" t="inlineStr">
+      <c r="E272" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19891,7 +19908,7 @@
       </c>
       <c r="N272" s="70" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="O272" s="28" t="inlineStr">
@@ -19906,7 +19923,7 @@
           <t>PS5-79-07</t>
         </is>
       </c>
-      <c r="B273" s="83" t="inlineStr">
+      <c r="B273" s="86" t="inlineStr">
         <is>
           <t>PS5-79-07 - Electrical Heat Tracing Transformer/Distribution Board 7 (PS5-79-IG-0007)</t>
         </is>
@@ -19917,7 +19934,7 @@
       <c r="D273" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E273" s="95" t="inlineStr">
+      <c r="E273" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -19960,7 +19977,7 @@
       </c>
       <c r="N273" s="69" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="O273" s="28" t="inlineStr">
@@ -19975,7 +19992,7 @@
           <t>PS5-79-08</t>
         </is>
       </c>
-      <c r="B274" s="83" t="inlineStr">
+      <c r="B274" s="86" t="inlineStr">
         <is>
           <t>PS5-79-08 - Electrical Heat Tracing Transformer/Distribution Board 8 (PS5-79-IG-0008)</t>
         </is>
@@ -19986,7 +20003,7 @@
       <c r="D274" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E274" s="95" t="inlineStr">
+      <c r="E274" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20029,7 +20046,7 @@
       </c>
       <c r="N274" s="69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="O274" s="28" t="inlineStr">
@@ -20044,7 +20061,7 @@
           <t>PS5-79-09</t>
         </is>
       </c>
-      <c r="B275" s="83" t="inlineStr">
+      <c r="B275" s="86" t="inlineStr">
         <is>
           <t>PS5-79-09 - Electrical Heat Tracing Transformer/Distribution Board 9 (PS5-79-IG-0009)</t>
         </is>
@@ -20055,7 +20072,7 @@
       <c r="D275" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E275" s="95" t="inlineStr">
+      <c r="E275" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20098,7 +20115,7 @@
       </c>
       <c r="N275" s="70" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="O275" s="28" t="inlineStr">
@@ -20113,7 +20130,7 @@
           <t>PS5-79-10</t>
         </is>
       </c>
-      <c r="B276" s="83" t="inlineStr">
+      <c r="B276" s="86" t="inlineStr">
         <is>
           <t>PS5-79-10 - Electrical Heat Tracing Transformer/Distribution Board 10 (PS5-79-IG-0010)</t>
         </is>
@@ -20124,7 +20141,7 @@
       <c r="D276" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E276" s="95" t="inlineStr">
+      <c r="E276" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20167,7 +20184,7 @@
       </c>
       <c r="N276" s="69" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="O276" s="28" t="inlineStr">
@@ -20182,7 +20199,7 @@
           <t>PS5-79-11</t>
         </is>
       </c>
-      <c r="B277" s="83" t="inlineStr">
+      <c r="B277" s="86" t="inlineStr">
         <is>
           <t>PS5-79-11 - Electrical Heat Tracing Transformer/Distribution Board 11 (PS5-79-IG-0011)</t>
         </is>
@@ -20193,7 +20210,7 @@
       <c r="D277" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E277" s="95" t="inlineStr">
+      <c r="E277" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20251,7 +20268,7 @@
           <t>PS5-79-12</t>
         </is>
       </c>
-      <c r="B278" s="83" t="inlineStr">
+      <c r="B278" s="86" t="inlineStr">
         <is>
           <t>PS5-79-12 - Electrical Heat Tracing Transformer/Distribution Board 12 (PS5-79-IG-0012)</t>
         </is>
@@ -20262,7 +20279,7 @@
       <c r="D278" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E278" s="95" t="inlineStr">
+      <c r="E278" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20305,7 +20322,7 @@
       </c>
       <c r="N278" s="70" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="O278" s="28" t="inlineStr">
@@ -20320,7 +20337,7 @@
           <t>PS5-82-01</t>
         </is>
       </c>
-      <c r="B279" s="83" t="inlineStr">
+      <c r="B279" s="86" t="inlineStr">
         <is>
           <t>PS5-82-01 - Sanitary Sewage Collection</t>
         </is>
@@ -20331,7 +20348,7 @@
       <c r="D279" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E279" s="95" t="inlineStr">
+      <c r="E279" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20389,7 +20406,7 @@
           <t>PS5-82-02</t>
         </is>
       </c>
-      <c r="B280" s="83" t="inlineStr">
+      <c r="B280" s="86" t="inlineStr">
         <is>
           <t>PS5-82-02 - Sewage Treatment Plant Package</t>
         </is>
@@ -20458,7 +20475,7 @@
           <t>PS5-82-03</t>
         </is>
       </c>
-      <c r="B281" s="83" t="inlineStr">
+      <c r="B281" s="86" t="inlineStr">
         <is>
           <t>PS5-82-03 - Sewage Treatment Plant Package (UCP)</t>
         </is>
@@ -20469,7 +20486,7 @@
       <c r="D281" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E281" s="95" t="inlineStr">
+      <c r="E281" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20527,7 +20544,7 @@
           <t>PS5-82-04</t>
         </is>
       </c>
-      <c r="B282" s="83" t="inlineStr">
+      <c r="B282" s="86" t="inlineStr">
         <is>
           <t>PS5-82-04 - Sewage Treatment Plant Discharge Piping</t>
         </is>
@@ -20538,7 +20555,7 @@
       <c r="D282" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E282" s="95" t="inlineStr">
+      <c r="E282" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20596,7 +20613,7 @@
           <t>PS5-82-05</t>
         </is>
       </c>
-      <c r="B283" s="83" t="inlineStr">
+      <c r="B283" s="86" t="inlineStr">
         <is>
           <t>PS5-82-05 - Office and Facilities building</t>
         </is>
@@ -20607,7 +20624,7 @@
       <c r="D283" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E283" s="95" t="inlineStr">
+      <c r="E283" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20665,7 +20682,7 @@
           <t>PS5-82-06</t>
         </is>
       </c>
-      <c r="B284" s="83" t="inlineStr">
+      <c r="B284" s="86" t="inlineStr">
         <is>
           <t>PS5-82-06 - Guard House Building</t>
         </is>
@@ -20676,7 +20693,7 @@
       <c r="D284" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E284" s="95" t="inlineStr">
+      <c r="E284" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20734,7 +20751,7 @@
           <t>PS5-82-07</t>
         </is>
       </c>
-      <c r="B285" s="83" t="inlineStr">
+      <c r="B285" s="86" t="inlineStr">
         <is>
           <t>PS5-82-07 - Guard Huts</t>
         </is>
@@ -20745,7 +20762,7 @@
       <c r="D285" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E285" s="95" t="inlineStr">
+      <c r="E285" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20803,7 +20820,7 @@
           <t>PS5-83-01</t>
         </is>
       </c>
-      <c r="B286" s="83" t="inlineStr">
+      <c r="B286" s="86" t="inlineStr">
         <is>
           <t>PS5-83-01 - EITS Building</t>
         </is>
@@ -20872,7 +20889,7 @@
           <t>PS5-84-01</t>
         </is>
       </c>
-      <c r="B287" s="83" t="inlineStr">
+      <c r="B287" s="86" t="inlineStr">
         <is>
           <t>PS5-84-01 - Generator Building</t>
         </is>
@@ -20883,7 +20900,7 @@
       <c r="D287" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E287" s="95" t="inlineStr">
+      <c r="E287" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -20941,7 +20958,7 @@
           <t>PS5-84-02</t>
         </is>
       </c>
-      <c r="B288" s="83" t="inlineStr">
+      <c r="B288" s="86" t="inlineStr">
         <is>
           <t>PS5-84-02 - Workshop &amp; Warehouse</t>
         </is>
@@ -20952,7 +20969,7 @@
       <c r="D288" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E288" s="95" t="inlineStr">
+      <c r="E288" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21010,7 +21027,7 @@
           <t>PS5-84-03</t>
         </is>
       </c>
-      <c r="B289" s="83" t="inlineStr">
+      <c r="B289" s="86" t="inlineStr">
         <is>
           <t>PS5-84-03 - Shelters</t>
         </is>
@@ -21021,7 +21038,7 @@
       <c r="D289" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E289" s="95" t="inlineStr">
+      <c r="E289" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21079,7 +21096,7 @@
           <t>PS5-86-01</t>
         </is>
       </c>
-      <c r="B290" s="83" t="inlineStr">
+      <c r="B290" s="86" t="inlineStr">
         <is>
           <t>PS5-86-01 - Shelters</t>
         </is>
@@ -21090,7 +21107,7 @@
       <c r="D290" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E290" s="95" t="inlineStr">
+      <c r="E290" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21148,7 +21165,7 @@
           <t>PS5-91-01</t>
         </is>
       </c>
-      <c r="B291" s="83" t="inlineStr">
+      <c r="B291" s="86" t="inlineStr">
         <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
@@ -21217,7 +21234,7 @@
           <t>PS5-99-01</t>
         </is>
       </c>
-      <c r="B292" s="83" t="inlineStr">
+      <c r="B292" s="86" t="inlineStr">
         <is>
           <t>PS5-99-01 - Area Completion for Building area</t>
         </is>
@@ -21228,7 +21245,7 @@
       <c r="D292" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E292" s="95" t="inlineStr">
+      <c r="E292" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21286,7 +21303,7 @@
           <t>PS5-99-02</t>
         </is>
       </c>
-      <c r="B293" s="83" t="inlineStr">
+      <c r="B293" s="86" t="inlineStr">
         <is>
           <t>PS5-99-02 - Area Completion for Utility area</t>
         </is>
@@ -21297,7 +21314,7 @@
       <c r="D293" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E293" s="95" t="inlineStr">
+      <c r="E293" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21355,7 +21372,7 @@
           <t>PS5-99-03</t>
         </is>
       </c>
-      <c r="B294" s="83" t="inlineStr">
+      <c r="B294" s="86" t="inlineStr">
         <is>
           <t>PS5-99-03 - Area Completion for Power Distribution area</t>
         </is>
@@ -21366,7 +21383,7 @@
       <c r="D294" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E294" s="95" t="inlineStr">
+      <c r="E294" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21424,7 +21441,7 @@
           <t>PS5-99-04</t>
         </is>
       </c>
-      <c r="B295" s="83" t="inlineStr">
+      <c r="B295" s="86" t="inlineStr">
         <is>
           <t>PS5-99-04 - Area Completion for Process area</t>
         </is>
@@ -21435,7 +21452,7 @@
       <c r="D295" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E295" s="95" t="inlineStr">
+      <c r="E295" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21493,7 +21510,7 @@
           <t>PS5-99-05</t>
         </is>
       </c>
-      <c r="B296" s="83" t="inlineStr">
+      <c r="B296" s="86" t="inlineStr">
         <is>
           <t>PS5-99-05 - Area Completion for CFO area</t>
         </is>
@@ -21504,7 +21521,7 @@
       <c r="D296" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E296" s="95" t="inlineStr">
+      <c r="E296" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -21562,7 +21579,7 @@
           <t>PS5-99-06</t>
         </is>
       </c>
-      <c r="B297" s="83" t="inlineStr">
+      <c r="B297" s="86" t="inlineStr">
         <is>
           <t>PS5-99-06 - Area Completion for Power Generation area</t>
         </is>
@@ -21573,7 +21590,7 @@
       <c r="D297" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E297" s="95" t="inlineStr">
+      <c r="E297" s="75" t="inlineStr">
         <is>
           <t>0%</t>
         </is>

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -4726,9 +4726,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="N52" s="69" t="inlineStr">
-        <is>
-          <t>74%</t>
+      <c r="N52" s="70" t="inlineStr">
+        <is>
+          <t>9%</t>
         </is>
       </c>
       <c r="O52" s="28" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="N53" s="70" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="O53" s="28" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="N67" s="70" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="O67" s="28" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="N68" s="70" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="O68" s="28" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="N77" s="70" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="O77" s="28" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="N78" s="70" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="O78" s="28" t="inlineStr">
